--- a/docs/Micro250_stocks.xlsx
+++ b/docs/Micro250_stocks.xlsx
@@ -551,7 +551,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>ENTERO</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -560,37 +560,37 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>582.45</v>
+        <v>1753.5</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>81.7</v>
+        <v>84.83</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>73.53</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>67.79000000000001</v>
+        <v>73.34</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>38.61</v>
+        <v>48.91</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>457.87</v>
+        <v>1230.59</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>450.36</v>
+        <v>1217.4</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>1093717</v>
+        <v>336245</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>14228</v>
+        <v>7872</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>EMIL</t>
+          <t>SHILPAMED</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -599,37 +599,37 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>191.06</v>
+        <v>901.85</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>80.77</v>
+        <v>83.28</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>75.68000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>61.39</v>
+        <v>83.19</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>51.2</v>
+        <v>58.82</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>127.46</v>
+        <v>548.64</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>126.42</v>
+        <v>514.79</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>10322576</v>
+        <v>2468767</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>7184</v>
+        <v>17677</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>SHILPAMED</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -638,37 +638,37 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>820.95</v>
+        <v>1609.7</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>76.93000000000001</v>
+        <v>75.34</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>87.72</v>
+        <v>75.19</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>81.04000000000001</v>
+        <v>70.08</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>57.03</v>
+        <v>38.4</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>527.17</v>
+        <v>1151.43</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>496.89</v>
+        <v>1095.5</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>2297386</v>
+        <v>171023</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>15939</v>
+        <v>10537</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>EPL</t>
+          <t>YATHARTH</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -677,37 +677,37 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>270.1</v>
+        <v>967.4</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>75.34999999999999</v>
+        <v>73.98</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>67.88</v>
+        <v>67.87</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>62.24</v>
+        <v>67.09</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>27.92</v>
+        <v>27.13</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>224.94</v>
+        <v>798.29</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>223.14</v>
+        <v>775.11</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>1537837</v>
+        <v>386755</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>8507</v>
+        <v>9321</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -716,37 +716,37 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>357.5</v>
+        <v>723.75</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>73.69</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>71.93000000000001</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>65.92</v>
+        <v>85.97</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>41.45</v>
+        <v>23.36</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>293.94</v>
+        <v>441.75</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>288.86</v>
+        <v>390.7</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>2831391</v>
+        <v>2045777</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>13632</v>
+        <v>37194</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>VARROC</t>
+          <t>WELENT</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>824.25</v>
+        <v>676.6</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>73.19</v>
+        <v>71.12</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>74.42</v>
+        <v>70.64</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>68.76000000000001</v>
+        <v>65.53</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>52.78</v>
+        <v>30.02</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>624.6900000000001</v>
+        <v>549.99</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>610.6</v>
+        <v>540.8</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>811831</v>
+        <v>546968</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>12452</v>
+        <v>9090</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>PARAS</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -794,37 +794,37 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1499.6</v>
+        <v>1696.8</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>72.16</v>
+        <v>68.45999999999999</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>73.42</v>
+        <v>78.25</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>71.48999999999999</v>
+        <v>80.34</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>38.25</v>
+        <v>53.24</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1013.66</v>
+        <v>1270.35</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>958.89</v>
+        <v>1203.23</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1278644</v>
+        <v>333777</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>12085</v>
+        <v>22521</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>PRICOLLTD</t>
+          <t>KRBL</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -833,37 +833,37 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>797.2</v>
+        <v>437.65</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>70.98999999999999</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>75.66</v>
+        <v>68.97</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>70.75</v>
+        <v>59.72</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>52.24</v>
+        <v>44.55</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>619.4299999999999</v>
+        <v>367.18</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>603.5700000000001</v>
+        <v>364.58</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>653898</v>
+        <v>829341</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>9716</v>
+        <v>10017</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>MANORAMA</t>
+          <t>VARROC</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -872,37 +872,37 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1927.3</v>
+        <v>813.15</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>69.56999999999999</v>
+        <v>67.64</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>74.95999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>71.05</v>
+        <v>69.06</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>40.06</v>
+        <v>51.82</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1510.86</v>
+        <v>636.84</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1473.89</v>
+        <v>620.62</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>689475</v>
+        <v>832542</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>12166</v>
+        <v>12558</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2183.8</v>
+        <v>567.2</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>69.43000000000001</v>
+        <v>67.41</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>82.67</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>81.45999999999999</v>
+        <v>67.28</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>44.27</v>
+        <v>39.13</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1469.09</v>
+        <v>466.44</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1371.42</v>
+        <v>457.41</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>480709</v>
+        <v>1201817</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>14590</v>
+        <v>14020</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -950,37 +950,37 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>328.3</v>
+        <v>329.7</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>68.70999999999999</v>
+        <v>67.39</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>78.18000000000001</v>
+        <v>74.62</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>75.95</v>
+        <v>67.61</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>42.86</v>
+        <v>45.16</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>256.9</v>
+        <v>240.77</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>246.71</v>
+        <v>232.65</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>3209659</v>
+        <v>4429364</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>12416</v>
+        <v>14941</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -989,37 +989,37 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1482.1</v>
+        <v>2231.7</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>68.54000000000001</v>
+        <v>67.13</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>71.09</v>
+        <v>83.47</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>67.73</v>
+        <v>81.91</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>31.36</v>
+        <v>47.05</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1125.24</v>
+        <v>1515.61</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1073.16</v>
+        <v>1411.46</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>161157</v>
+        <v>492169</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>9702</v>
+        <v>14910</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>SKYGOLD</t>
+          <t>MSTCLTD</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1028,37 +1028,37 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>803.5</v>
+        <v>722.25</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>68.31</v>
+        <v>66.14</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>81.45999999999999</v>
+        <v>66.56999999999999</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>81.65000000000001</v>
+        <v>60.67</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>48.02</v>
+        <v>30.17</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>522.66</v>
+        <v>559.76</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>488.32</v>
+        <v>546.95</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1229041</v>
+        <v>352859</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>12444</v>
+        <v>5137</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>AZAD</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1067,37 +1067,37 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2837.8</v>
+        <v>212.97</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>68.3</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>70.66</v>
+        <v>68.55</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>72.70999999999999</v>
+        <v>65.69</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>25.98</v>
+        <v>29.37</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>2091.92</v>
+        <v>182.21</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2007.51</v>
+        <v>177.75</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>635620</v>
+        <v>2623902</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>18327</v>
+        <v>6859</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>AZAD</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1106,37 +1106,37 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>320.85</v>
+        <v>2802.4</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>68.26000000000001</v>
+        <v>64.17</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>73.39</v>
+        <v>70.89</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>66.86</v>
+        <v>72.84</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>40.68</v>
+        <v>28.99</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>233.71</v>
+        <v>2129.07</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>226.8</v>
+        <v>2038.85</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>4382534</v>
+        <v>609227</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>14560</v>
+        <v>18409</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>CUPID</t>
+          <t>MANORAMA</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1145,37 +1145,37 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>284.58</v>
+        <v>1887.2</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>67.95</v>
+        <v>63.99</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>88.06</v>
+        <v>71.56</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>93.15000000000001</v>
+        <v>70.41</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>24.89</v>
+        <v>44.56</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>160.01</v>
+        <v>1531.15</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>141.29</v>
+        <v>1490.56</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>36783558</v>
+        <v>688369</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>38266</v>
+        <v>11926</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GOKULAGRO</t>
+          <t>RBA</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1184,37 +1184,37 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>242.8</v>
+        <v>100.97</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>67.84</v>
+        <v>63.32</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>65.64</v>
+        <v>73.09</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>67.43000000000001</v>
+        <v>60.04</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>33.83</v>
+        <v>61.53</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>209.87</v>
+        <v>75.33</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>203.36</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>673924</v>
+        <v>16851452</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>7165</v>
+        <v>7190</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>ALIVUS</t>
+          <t>TMB</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1223,37 +1223,37 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1370</v>
+        <v>893.85</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>67.41</v>
+        <v>63.25</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>73.36</v>
+        <v>71.37</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>72.17</v>
+        <v>77.13</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>48.43</v>
+        <v>35.03</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1095.61</v>
+        <v>722.28</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1071.16</v>
+        <v>686.0599999999999</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>153727</v>
+        <v>509869</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>16585</v>
+        <v>14031</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>WELENT</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1262,37 +1262,37 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>631.45</v>
+        <v>354.5</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>67.17</v>
+        <v>62.89</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>66.14</v>
+        <v>75.8</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>63.25</v>
+        <v>68.14</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>23</v>
+        <v>34.98</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>543.41</v>
+        <v>297.83</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>535.46</v>
+        <v>292.02</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>486006</v>
+        <v>2803525</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>8563</v>
+        <v>14411</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>SKYGOLD</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1301,37 +1301,37 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>643.85</v>
+        <v>811.4</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>67.05</v>
+        <v>62.59</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>73.61</v>
+        <v>81.81</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>69.12</v>
+        <v>81.84</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>63.89</v>
+        <v>51.3</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>488.33</v>
+        <v>542.38</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>480.82</v>
+        <v>504.87</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1305068</v>
+        <v>1262985</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>12246</v>
+        <v>12566</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>MSTCLTD</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1340,37 +1340,37 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>701.45</v>
+        <v>327.15</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>66.56</v>
+        <v>62.54</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>64.65000000000001</v>
+        <v>78.56</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>59.52</v>
+        <v>76.16</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>22.56</v>
+        <v>46.43</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>550.46</v>
+        <v>260.87</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>539.48</v>
+        <v>250.13</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>351977</v>
+        <v>3378401</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>4938</v>
+        <v>12493</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>ALKYLAMINE</t>
+          <t>GOKULAGRO</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1379,37 +1379,37 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2052.7</v>
+        <v>244.48</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>66.54000000000001</v>
+        <v>62.53</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>68.79000000000001</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>55.2</v>
+        <v>67.64</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>26.45</v>
+        <v>40.51</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1739.75</v>
+        <v>211.79</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1735.47</v>
+        <v>205.06</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>136203</v>
+        <v>763770</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>10499</v>
+        <v>7210</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>AKUMS</t>
+          <t>TDPOWERSYS</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1418,37 +1418,37 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>752.9</v>
+        <v>752.7</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>66.31999999999999</v>
+        <v>62.49</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>72.93000000000001</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>63.88</v>
+        <v>78.59</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>44.2</v>
+        <v>31.74</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>585.6</v>
+        <v>556.85</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>570.75</v>
+        <v>520.21</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>351350</v>
+        <v>3124217</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>11483</v>
+        <v>23519</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>DIACABS</t>
+          <t>AKUMS</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1457,37 +1457,37 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>353.9</v>
+        <v>761.2</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>66.17</v>
+        <v>62.36</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>83.5</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>81.04000000000001</v>
+        <v>65.22</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>55.66</v>
+        <v>45.25</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>216.58</v>
+        <v>596.6</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>201.16</v>
+        <v>579.0599999999999</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>5316798</v>
+        <v>362397</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>21297</v>
+        <v>11829</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>ALIVUS</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1496,37 +1496,37 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1634.4</v>
+        <v>1358.2</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>65.66</v>
+        <v>61.9</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>75.95999999999999</v>
+        <v>73.26000000000001</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>79.09999999999999</v>
+        <v>72.15000000000001</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>55.4</v>
+        <v>44.63</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1237.91</v>
+        <v>1112.48</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1175.08</v>
+        <v>1085.22</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>320211</v>
+        <v>131141</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>21590</v>
+        <v>16577</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>ENTERO</t>
+          <t>ALKYLAMINE</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1535,31 +1535,31 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1408.4</v>
+        <v>2045</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>65.33</v>
+        <v>61.48</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>65.27</v>
+        <v>68.38</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>63.06</v>
+        <v>55.11</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>39.17</v>
+        <v>31.14</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1205.14</v>
+        <v>1757</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1197.77</v>
+        <v>1749.12</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>153619</v>
+        <v>139727</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>6196</v>
+        <v>10474</v>
       </c>
     </row>
     <row r="28">
@@ -1574,37 +1574,37 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3900.2</v>
+        <v>3859</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>64.93000000000001</v>
+        <v>60.98</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>81.04000000000001</v>
+        <v>80.12</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>84.14</v>
+        <v>84.04000000000001</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>40.03</v>
+        <v>34.72</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2775.27</v>
+        <v>2857.27</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2581.82</v>
+        <v>2655.28</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>269630</v>
+        <v>257763</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>24193</v>
+        <v>24082</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>HCG</t>
+          <t>DIACABS</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1613,37 +1613,37 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>730.45</v>
+        <v>349.4</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>63.8</v>
+        <v>60.7</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>70.27</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>66.2</v>
+        <v>80.66</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>29.88</v>
+        <v>42.66</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>640.33</v>
+        <v>226.53</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>632.87</v>
+        <v>209.67</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>228345</v>
+        <v>4911830</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>10839</v>
+        <v>20897</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>LUMAXTECH</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1652,37 +1652,37 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>582.8</v>
+        <v>1930.6</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>63.37</v>
+        <v>60.65</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>67.34</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>56.46</v>
+        <v>71.08</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>33.82</v>
+        <v>42.72</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>507.77</v>
+        <v>1608.23</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>504.81</v>
+        <v>1545.87</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>529359</v>
+        <v>361003</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>8564</v>
+        <v>13533</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>EDELWEISS</t>
+          <t>PRICOLLTD</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1691,37 +1691,37 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>126.62</v>
+        <v>770.65</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>62.93</v>
+        <v>59.47</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>60.71</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>61.29</v>
+        <v>69.59</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>20.76</v>
+        <v>44.24</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>115.83</v>
+        <v>629.88</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>114.56</v>
+        <v>612.2</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>3549113</v>
+        <v>639908</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>12180</v>
+        <v>9393</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>ICIL</t>
+          <t>EMIL</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1730,37 +1730,37 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>443.55</v>
+        <v>177.35</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>62.51</v>
+        <v>59.21</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>66.04000000000001</v>
+        <v>69.7</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>64.43000000000001</v>
+        <v>59.85</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>27.38</v>
+        <v>44.99</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>344.51</v>
+        <v>131.65</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>332.82</v>
+        <v>129.67</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>1390033</v>
+        <v>10335654</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>8785</v>
+        <v>6824</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>PGIL</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1769,37 +1769,37 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>2377.6</v>
+        <v>580.05</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>62.19</v>
+        <v>59.02</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>70.84999999999999</v>
+        <v>66.48999999999999</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>75.17</v>
+        <v>56.23</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>43.31</v>
+        <v>36.59</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1811.46</v>
+        <v>512.72</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>1737.57</v>
+        <v>508.74</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>170201</v>
+        <v>538210</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>11022</v>
+        <v>8523</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>UJJIVANSFB</t>
+          <t>INDIAGLYCO</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1808,37 +1808,37 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>72.06999999999999</v>
+        <v>1178.3</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>61.29</v>
+        <v>58.32</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>67.39</v>
+        <v>62.59</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>66.93000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>45.97</v>
+        <v>31.16</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>60.48</v>
+        <v>1028.57</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>58.63</v>
+        <v>1003.32</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>22352422</v>
+        <v>256406</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>14043</v>
+        <v>7898</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>RATEGAIN</t>
+          <t>PARAS</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1847,31 +1847,31 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>990.05</v>
+        <v>1439.7</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>60.91</v>
+        <v>58.2</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>75.23</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>68.33</v>
+        <v>70.39</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>26.89</v>
+        <v>40.19</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>766.8200000000001</v>
+        <v>1042.41</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>734.33</v>
+        <v>983.27</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>561274</v>
+        <v>1375690</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>11722</v>
+        <v>11602</v>
       </c>
     </row>
     <row r="36">
@@ -1886,37 +1886,37 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>2259.1</v>
+        <v>2230.2</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>60.11</v>
+        <v>56.64</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>68.78</v>
+        <v>67.52</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>63.64</v>
+        <v>63.33</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>28.64</v>
+        <v>25.77</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>1786.58</v>
+        <v>1811.88</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>1725.35</v>
+        <v>1747.16</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>213935</v>
+        <v>204790</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>6106</v>
+        <v>6051</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>SHAILY</t>
+          <t>EPL</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1925,37 +1925,37 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>3321</v>
+        <v>251.94</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>59.85</v>
+        <v>56.12</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>68.68000000000001</v>
+        <v>60.23</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>73.89</v>
+        <v>59.79</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>45.12</v>
+        <v>31.94</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>2687.09</v>
+        <v>227.46</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>2568.98</v>
+        <v>225.17</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>198590</v>
+        <v>1732350</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>15275</v>
+        <v>8070</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>TMB</t>
+          <t>SMLMAH</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1964,37 +1964,37 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>869.7</v>
+        <v>5194</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>59.06</v>
+        <v>56.04</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>70.77</v>
+        <v>61.57</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>76.84999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>34.85</v>
+        <v>37.93</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>711.15</v>
+        <v>4209.03</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>675.87</v>
+        <v>4033.87</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>524248</v>
+        <v>239572</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>13912</v>
+        <v>7506</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GAEL</t>
+          <t>SHAILY</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -2003,37 +2003,37 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>177.46</v>
+        <v>3270.4</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>57.94</v>
+        <v>54.92</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>65.39</v>
+        <v>66.52</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>68.81999999999999</v>
+        <v>73.44</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>31.99</v>
+        <v>38.26</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>151.82</v>
+        <v>2723.96</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>147.14</v>
+        <v>2602.53</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1978242</v>
+        <v>191946</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>8140</v>
+        <v>15042</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>INDIAGLYCO</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -2042,37 +2042,37 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>1146.5</v>
+        <v>606.05</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>57.47</v>
+        <v>53.7</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>60.44</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>64.52</v>
+        <v>69.86</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>27.9</v>
+        <v>56.48</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>1017.66</v>
+        <v>496.42</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>993.91</v>
+        <v>487.58</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>253820</v>
+        <v>1307171</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>7685</v>
+        <v>12481</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>SMLMAH</t>
+          <t>ICIL</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -2081,37 +2081,37 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>5159.5</v>
+        <v>423.4</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>56.43</v>
+        <v>53.53</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>63.79</v>
+        <v>64.16</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>66.81999999999999</v>
+        <v>63.81</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>36.9</v>
+        <v>26.89</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>4139.38</v>
+        <v>348.75</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>3973.31</v>
+        <v>336.67</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>244316</v>
+        <v>1405152</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>7705</v>
+        <v>8614</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>PGIL</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -2120,37 +2120,37 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>627.15</v>
+        <v>2294.8</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>56.38</v>
+        <v>53.28</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>70.89</v>
+        <v>66.93000000000001</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>83.70999999999999</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>21.86</v>
+        <v>39.34</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>425.4</v>
+        <v>1845.18</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>375.94</v>
+        <v>1767.03</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>2149959</v>
+        <v>165327</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>32230</v>
+        <v>10690</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>MTARTECH</t>
+          <t>OPTIEMUS</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -2159,37 +2159,37 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>7029.5</v>
+        <v>576.45</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>55.97</v>
+        <v>52.28</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>60.06</v>
+        <v>60.18</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>70.26000000000001</v>
+        <v>55.38</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>23.9</v>
+        <v>26.03</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>5658.94</v>
+        <v>501.84</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>5164.43</v>
+        <v>501.59</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>187609</v>
+        <v>298049</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>21622</v>
+        <v>5226</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>JSFB</t>
+          <t>HCG</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -2198,37 +2198,37 @@
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>562.85</v>
+        <v>699.95</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>55.31</v>
+        <v>50.13</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>69.2</v>
+        <v>61.45</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>62.16</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>25.75</v>
+        <v>26.89</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>474.92</v>
+        <v>645.17</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>467.78</v>
+        <v>637.02</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>1250664</v>
+        <v>166036</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>6158</v>
+        <v>10396</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>JLHL</t>
+          <t>THYROCARE</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -2237,37 +2237,37 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>317.7</v>
+        <v>581.45</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>55.13</v>
+        <v>48.47</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>62.24</v>
+        <v>62.85</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>57.28</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>27.62</v>
+        <v>24.86</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>284.24</v>
+        <v>501.03</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>282.46</v>
+        <v>480.61</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>210017</v>
+        <v>1228794</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>10155</v>
+        <v>9301</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>RAIN</t>
+          <t>RATEGAIN</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -2276,31 +2276,31 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>208.61</v>
+        <v>918.25</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>47.92</v>
+        <v>47.4</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>65.5</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>60.13</v>
+        <v>66.39</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>26.9</v>
+        <v>25.88</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>175.6</v>
+        <v>775.85</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>168.55</v>
+        <v>742.63</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>5728968</v>
+        <v>537541</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>7017</v>
+        <v>11058</v>
       </c>
     </row>
   </sheetData>
@@ -2407,7 +2407,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>MANYAVAR</t>
+          <t>ENTERO</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2416,22 +2416,22 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>547.35</v>
+        <v>1753.5</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>82.28</v>
+        <v>84.83</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>67.47</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>40.11</v>
+        <v>73.34</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>SHILPAMED</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2440,22 +2440,22 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>582.45</v>
+        <v>901.85</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>81.7</v>
+        <v>83.28</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>73.53</v>
+        <v>90.2</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>67.79000000000001</v>
+        <v>83.19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>EMIL</t>
+          <t>BALUFORGE</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2464,22 +2464,22 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>191.06</v>
+        <v>632.9</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>80.77</v>
+        <v>76.41</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>75.68000000000001</v>
+        <v>69.98</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>61.39</v>
+        <v>56.16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>UTLSOLAR</t>
+          <t>ELECTCAST</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2488,22 +2488,22 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>477.5</v>
+        <v>81.5</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>77.2</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>82.65000000000001</v>
+        <v>56.03</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v/>
+        <v>45.77</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SHILPAMED</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2512,22 +2512,22 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>820.95</v>
+        <v>1609.7</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>76.93000000000001</v>
+        <v>75.34</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>87.72</v>
+        <v>75.19</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>81.04000000000001</v>
+        <v>70.08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>EPL</t>
+          <t>GPPL</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2536,22 +2536,22 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>270.1</v>
+        <v>168.75</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>75.34999999999999</v>
+        <v>74.42</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>67.88</v>
+        <v>61.8</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>62.24</v>
+        <v>54.96</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>BALUFORGE</t>
+          <t>YATHARTH</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2560,22 +2560,22 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>555.4</v>
+        <v>967.4</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>75.18000000000001</v>
+        <v>73.98</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>61.66</v>
+        <v>67.87</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>52.25</v>
+        <v>67.09</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>HERITGFOOD</t>
+          <t>MANYAVAR</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2584,22 +2584,22 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>378.75</v>
+        <v>544.55</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>74.77</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>60.77</v>
+        <v>67.95</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>50.35</v>
+        <v>40.37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>SUDEEPPHRM</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2608,22 +2608,22 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>357.5</v>
+        <v>1152.1</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>73.69</v>
+        <v>73.2</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>71.93000000000001</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>65.92</v>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>LUMAXTECH</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2632,22 +2632,22 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2043.7</v>
+        <v>723.75</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>73.65000000000001</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>65.67</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>71.13</v>
+        <v>85.97</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>VARROC</t>
+          <t>SUDARSCHEM</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2656,22 +2656,22 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>824.25</v>
+        <v>1252.8</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>73.19</v>
+        <v>72.48999999999999</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>74.42</v>
+        <v>70.75</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>68.76000000000001</v>
+        <v>61.22</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>BLACKBUCK</t>
+          <t>QUESS</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -2680,22 +2680,22 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>631.05</v>
+        <v>372.25</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>73.11</v>
+        <v>71.47</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>58.9</v>
+        <v>78.95</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>61.65</v>
+        <v>53.88</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>RBA</t>
+          <t>INOXINDIA</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -2704,22 +2704,22 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>104.24</v>
+        <v>2177.9</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>72.77</v>
+        <v>71.23</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>77.51000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>61.19</v>
+        <v>82.56999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>PARAS</t>
+          <t>WELENT</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -2728,22 +2728,22 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1499.6</v>
+        <v>676.6</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>72.16</v>
+        <v>71.12</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>73.42</v>
+        <v>70.64</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>71.48999999999999</v>
+        <v>65.53</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GMMPFAUDLR</t>
+          <t>MAHSEAMLES</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -2752,22 +2752,22 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1018.2</v>
+        <v>642.05</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>71.64</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>62.1</v>
+        <v>64.67</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>47.61</v>
+        <v>54.62</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KRBL</t>
+          <t>SMARTWORKS</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -2776,22 +2776,22 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>406.95</v>
+        <v>540.6</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>71.42</v>
+        <v>68.62</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>63.1</v>
+        <v>65.94</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>57.08</v>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>VOLTAMP</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -2800,22 +2800,22 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>10869.5</v>
+        <v>1696.8</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>71.34</v>
+        <v>68.45999999999999</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>63.77</v>
+        <v>78.25</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>58.69</v>
+        <v>80.34</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>BECTORFOOD</t>
+          <t>KRBL</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2824,22 +2824,22 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>254.83</v>
+        <v>437.65</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>71.08</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>69.20999999999999</v>
+        <v>68.97</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>54.08</v>
+        <v>59.72</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>PRICOLLTD</t>
+          <t>HCC</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -2848,22 +2848,22 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>797.2</v>
+        <v>24.64</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>70.98999999999999</v>
+        <v>67.77</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>75.66</v>
+        <v>57.66</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>70.75</v>
+        <v>49.18</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>HAPPSTMNDS</t>
+          <t>GMMPFAUDLR</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -2872,22 +2872,22 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>444.55</v>
+        <v>1025.15</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>70.34</v>
+        <v>67.64</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>63.45</v>
+        <v>62.43</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>40.2</v>
+        <v>47.75</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>SUDARSCHEM</t>
+          <t>VARROC</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -2896,22 +2896,22 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1215.1</v>
+        <v>813.15</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>69.81</v>
+        <v>67.64</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>68.73999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>60.03</v>
+        <v>69.06</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GPPL</t>
+          <t>PRUDENT</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -2920,22 +2920,22 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>163.54</v>
+        <v>3473.5</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>69.75</v>
+        <v>67.53</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>57.36</v>
+        <v>69.04000000000001</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>53.37</v>
+        <v>66.41</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>MANORAMA</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -2944,22 +2944,22 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1927.3</v>
+        <v>567.2</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>69.56999999999999</v>
+        <v>67.41</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>74.95999999999999</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>71.05</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -2968,22 +2968,22 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2183.8</v>
+        <v>329.7</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>69.43000000000001</v>
+        <v>67.39</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>82.67</v>
+        <v>74.62</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>81.45999999999999</v>
+        <v>67.61</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>SUDEEPPHRM</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -2992,22 +2992,22 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1107.8</v>
+        <v>2231.7</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>69.23999999999999</v>
+        <v>67.13</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>77.40000000000001</v>
+        <v>83.47</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v/>
+        <v>81.91</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>PRAJIND</t>
+          <t>BALAMINES</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -3016,22 +3016,22 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>358.45</v>
+        <v>2425.8</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>68.92</v>
+        <v>66.95999999999999</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>50.86</v>
+        <v>68.73</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>44.04</v>
+        <v>64.06</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>MSTCLTD</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -3040,22 +3040,22 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>328.3</v>
+        <v>722.25</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>68.70999999999999</v>
+        <v>66.14</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>78.18000000000001</v>
+        <v>66.56999999999999</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>75.95</v>
+        <v>60.67</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3064,22 +3064,22 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1482.1</v>
+        <v>212.97</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>68.54000000000001</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>71.09</v>
+        <v>68.55</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>67.73</v>
+        <v>65.69</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>SKYGOLD</t>
+          <t>QPOWER</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -3088,22 +3088,22 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>803.5</v>
+        <v>1363.1</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>68.31</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>81.45999999999999</v>
+        <v>65.7</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>81.65000000000001</v>
+        <v>68.45</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>AZAD</t>
+          <t>HERITGFOOD</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -3112,22 +3112,22 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2837.8</v>
+        <v>378.15</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>68.3</v>
+        <v>65.34</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>70.66</v>
+        <v>56.45</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>72.70999999999999</v>
+        <v>49.21</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>VOLTAMP</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -3136,22 +3136,22 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>320.85</v>
+        <v>11038.5</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>68.26000000000001</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>73.39</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>66.86</v>
+        <v>59.19</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>CUPID</t>
+          <t>PCJEWELLER</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -3160,22 +3160,22 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>284.58</v>
+        <v>10.94</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>67.95</v>
+        <v>64.89</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>88.06</v>
+        <v>59.92</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>93.15000000000001</v>
+        <v>52.81</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GOKULAGRO</t>
+          <t>WAKEFIT</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -3184,22 +3184,22 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>242.8</v>
+        <v>144.71</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>67.84</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>65.64</v>
+        <v>52.02</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>67.43000000000001</v>
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>RENUKA</t>
+          <t>AZAD</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -3208,22 +3208,22 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>25.14</v>
+        <v>2802.4</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>67.48</v>
+        <v>64.17</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>54.31</v>
+        <v>70.89</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>41.72</v>
+        <v>72.84</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>ALIVUS</t>
+          <t>SKFINDUS</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -3232,22 +3232,22 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>1370</v>
+        <v>2891.6</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>67.41</v>
+        <v>64.06</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>73.36</v>
+        <v>66.61</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>72.17</v>
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>WAKEFIT</t>
+          <t>GODREJAGRO</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -3256,22 +3256,22 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>141.36</v>
+        <v>614.75</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>67.23999999999999</v>
+        <v>64</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>50.2</v>
+        <v>58.72</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v/>
+        <v>50</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>WELENT</t>
+          <t>MANORAMA</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -3280,22 +3280,22 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>631.45</v>
+        <v>1887.2</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>67.17</v>
+        <v>63.99</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>66.14</v>
+        <v>71.56</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>63.25</v>
+        <v>70.41</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>RUBICON</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -3304,22 +3304,22 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>643.85</v>
+        <v>1804.4</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>67.05</v>
+        <v>63.69</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>73.61</v>
+        <v>86.79000000000001</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>69.12</v>
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>MSTCLTD</t>
+          <t>RBA</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -3328,22 +3328,22 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>701.45</v>
+        <v>100.97</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>66.56</v>
+        <v>63.32</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>64.65000000000001</v>
+        <v>73.09</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>59.52</v>
+        <v>60.04</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>ALKYLAMINE</t>
+          <t>TMB</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -3352,22 +3352,22 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>2052.7</v>
+        <v>893.85</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>66.54000000000001</v>
+        <v>63.25</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>68.79000000000001</v>
+        <v>71.37</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>55.2</v>
+        <v>77.13</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>QUESS</t>
+          <t>CUPID</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -3376,22 +3376,22 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>338.25</v>
+        <v>282.33</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>66.52</v>
+        <v>62.91</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>74.15000000000001</v>
+        <v>86.75</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>50.28</v>
+        <v>93.09</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>AKUMS</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -3400,22 +3400,22 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>752.9</v>
+        <v>354.5</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>66.31999999999999</v>
+        <v>62.89</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>72.93000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>63.88</v>
+        <v>68.14</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>DIACABS</t>
+          <t>SKYGOLD</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -3424,22 +3424,22 @@
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>353.9</v>
+        <v>811.4</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>66.17</v>
+        <v>62.59</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>83.5</v>
+        <v>81.81</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>81.04000000000001</v>
+        <v>81.84</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>DYNAMATECH</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -3448,22 +3448,22 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>11765</v>
+        <v>327.15</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>66.11</v>
+        <v>62.54</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>59.04</v>
+        <v>78.56</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>67.2</v>
+        <v>76.16</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>VMART</t>
+          <t>GOKULAGRO</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -3472,22 +3472,22 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>838.85</v>
+        <v>244.48</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>65.81</v>
+        <v>62.53</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>65.83</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>56.61</v>
+        <v>67.64</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>TDPOWERSYS</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -3496,22 +3496,22 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>1634.4</v>
+        <v>752.7</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>65.66</v>
+        <v>62.49</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>75.95999999999999</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>79.09999999999999</v>
+        <v>78.59</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>ENTERO</t>
+          <t>AKUMS</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -3520,22 +3520,22 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>1408.4</v>
+        <v>761.2</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>65.33</v>
+        <v>62.36</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>65.27</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>63.06</v>
+        <v>65.22</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>WESTLIFE</t>
+          <t>CSBBANK</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -3544,22 +3544,22 @@
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>594.5</v>
+        <v>348.8</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>65.09999999999999</v>
+        <v>62.26</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>63.83</v>
+        <v>44.05</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>47.36</v>
+        <v>46.93</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>LOTUSDEV</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -3568,22 +3568,22 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>203.59</v>
+        <v>186.21</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>64.97</v>
+        <v>62.11</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>64.53</v>
+        <v>61.35</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>63.96</v>
+        <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>SANSERA</t>
+          <t>ALIVUS</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -3592,22 +3592,22 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>3900.2</v>
+        <v>1358.2</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>64.93000000000001</v>
+        <v>61.9</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>81.04000000000001</v>
+        <v>73.26000000000001</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>84.14</v>
+        <v>72.15000000000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>VGUARD</t>
+          <t>ALKYLAMINE</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -3616,22 +3616,22 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>336.85</v>
+        <v>2045</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>64.67</v>
+        <v>61.48</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>57.54</v>
+        <v>68.38</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>49.05</v>
+        <v>55.11</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>ELLEN</t>
+          <t>PRAJIND</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -3640,22 +3640,22 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>324.35</v>
+        <v>354.4</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>64.27</v>
+        <v>61.47</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>59.34</v>
+        <v>51.88</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v/>
+        <v>44.37</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>RUBICON</t>
+          <t>ORKLAINDIA</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -3664,13 +3664,13 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>1724.7</v>
+        <v>595.4</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>64.25</v>
+        <v>61.45</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>85.34999999999999</v>
+        <v>49.3</v>
       </c>
       <c r="F54" s="4" t="n">
         <v/>
@@ -3679,7 +3679,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>SMARTWORKS</t>
+          <t>INDIGOPNTS</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -3688,22 +3688,22 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>511.3</v>
+        <v>1170.2</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>63.96</v>
+        <v>61.37</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>63.51</v>
+        <v>65.13</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v/>
+        <v>50.36</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>ATLANTAELE</t>
+          <t>ETHOSLTD</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -3712,22 +3712,22 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>1846.9</v>
+        <v>2891</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>63.94</v>
+        <v>61.32</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>62.99</v>
+        <v>63.59</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v/>
+        <v>57.12</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>HCG</t>
+          <t>SANSERA</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -3736,22 +3736,22 @@
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>730.45</v>
+        <v>3859</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>63.8</v>
+        <v>60.98</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>70.27</v>
+        <v>80.12</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>66.2</v>
+        <v>84.04000000000001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>RATNAMANI</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -3760,22 +3760,22 @@
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>582.8</v>
+        <v>2611.1</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>63.37</v>
+        <v>60.77</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>67.34</v>
+        <v>54.69</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>56.46</v>
+        <v>50.81</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>AEQUS</t>
+          <t>DIACABS</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -3784,22 +3784,22 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>259.22</v>
+        <v>349.4</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>63.33</v>
+        <v>60.7</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>73.19</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v/>
+        <v>80.66</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>LUMAXTECH</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -3808,22 +3808,22 @@
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>113.17</v>
+        <v>1930.6</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>63</v>
+        <v>60.65</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>54.06</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>44.18</v>
+        <v>71.08</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>EDELWEISS</t>
+          <t>JAIBALAJI</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -3832,22 +3832,22 @@
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>126.62</v>
+        <v>70.16</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>62.93</v>
+        <v>60.06</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>60.71</v>
+        <v>50.06</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>61.29</v>
+        <v>42.65</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>UTLSOLAR</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -3856,13 +3856,13 @@
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>2165.8</v>
+        <v>443.35</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>62.56</v>
+        <v>59.95</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>76.06999999999999</v>
+        <v>74.05</v>
       </c>
       <c r="F62" s="4" t="n">
         <v/>
@@ -3871,7 +3871,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>ICIL</t>
+          <t>VMART</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -3880,22 +3880,22 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>443.55</v>
+        <v>836.05</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>62.51</v>
+        <v>59.78</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>66.04000000000001</v>
+        <v>62.63</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>64.43000000000001</v>
+        <v>55.7</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>PGIL</t>
+          <t>PRICOLLTD</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -3904,22 +3904,22 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>2377.6</v>
+        <v>770.65</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>62.19</v>
+        <v>59.47</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>70.84999999999999</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>75.17</v>
+        <v>69.59</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>JAYNECOIND</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -3928,22 +3928,22 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>829.25</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>61.81</v>
+        <v>59.46</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>61.4</v>
+        <v>58.87</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>57.7</v>
+        <v>63.33</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>BLUESTONE</t>
+          <t>EMIL</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -3952,22 +3952,22 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>846.4</v>
+        <v>177.35</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>61.8</v>
+        <v>59.21</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>78.31999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v/>
+        <v>59.85</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>PCJEWELLER</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -3976,22 +3976,22 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>10.22</v>
+        <v>580.05</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>61.38</v>
+        <v>59.02</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>55</v>
+        <v>66.48999999999999</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>50.79</v>
+        <v>56.23</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>PRUDENT</t>
+          <t>DYNAMATECH</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -4000,22 +4000,22 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>3363.5</v>
+        <v>11492</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>61.31</v>
+        <v>59.01</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>67.48</v>
+        <v>57.73</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>65.66</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>UJJIVANSFB</t>
+          <t>MAHSCOOTER</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -4024,22 +4024,22 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>72.06999999999999</v>
+        <v>13696</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>61.29</v>
+        <v>58.93</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>67.39</v>
+        <v>55.91</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>66.93000000000001</v>
+        <v>58.88</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>ETHOSLTD</t>
+          <t>VGUARD</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -4048,22 +4048,22 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>2867.6</v>
+        <v>331.5</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>61.26</v>
+        <v>58.5</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>62.5</v>
+        <v>58.08</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>56.58</v>
+        <v>49.31</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>RATEGAIN</t>
+          <t>INDIAGLYCO</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -4072,22 +4072,22 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>990.05</v>
+        <v>1178.3</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>60.91</v>
+        <v>58.32</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>75.23</v>
+        <v>62.59</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>68.33</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>QPOWER</t>
+          <t>PARKHOSPS</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -4096,22 +4096,22 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>1305.6</v>
+        <v>290.15</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>60.85</v>
+        <v>58.22</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>61.05</v>
+        <v>66.31</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>66.18000000000001</v>
+        <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>SHRIPISTON</t>
+          <t>PARAS</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -4120,22 +4120,22 @@
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>4513.8</v>
+        <v>1439.7</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>60.34</v>
+        <v>58.2</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>75.91</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>79.44</v>
+        <v>70.39</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>NEOGEN</t>
+          <t>STYL</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -4144,22 +4144,22 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>2259.1</v>
+        <v>399.95</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>60.11</v>
+        <v>57.51</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>68.78</v>
+        <v>66.88</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>63.64</v>
+        <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>SHAILY</t>
+          <t>ELLEN</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -4168,22 +4168,22 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>3321</v>
+        <v>319.8</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>59.85</v>
+        <v>57.41</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>68.68000000000001</v>
+        <v>56.85</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>73.89</v>
+        <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>TMB</t>
+          <t>WABAG</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -4192,22 +4192,22 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>869.7</v>
+        <v>2086.1</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>59.06</v>
+        <v>57.07</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>70.77</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>76.84999999999999</v>
+        <v>68.83</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>JAYNECOIND</t>
+          <t>FEDFINA</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -4216,22 +4216,22 @@
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>93.68000000000001</v>
+        <v>157.94</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>58.67</v>
+        <v>57</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>59.68</v>
+        <v>57.97</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>63.55</v>
+        <v>59.76</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>GHCL</t>
+          <t>METROPOLIS</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -4240,22 +4240,22 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>443.15</v>
+        <v>576.9</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>58.54</v>
+        <v>56.7</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>44.61</v>
+        <v>62.34</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>42.81</v>
+        <v>63.36</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>EMBDL</t>
+          <t>NEOGEN</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -4264,22 +4264,22 @@
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>64.87</v>
+        <v>2230.2</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>58.51</v>
+        <v>56.64</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>52.28</v>
+        <v>67.52</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>43.5</v>
+        <v>63.33</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>JKPAPER</t>
+          <t>GRWRHITECH</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -4288,22 +4288,22 @@
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>391.8</v>
+        <v>7224.5</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>58.5</v>
+        <v>56.2</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>60</v>
+        <v>75.86</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>54.36</v>
+        <v>70.27</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>WABAG</t>
+          <t>EPL</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -4312,22 +4312,22 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>2057.9</v>
+        <v>251.94</v>
       </c>
       <c r="D81" s="4" t="n">
-        <v>58.28</v>
+        <v>56.12</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>63.57</v>
+        <v>60.23</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>67.44</v>
+        <v>59.79</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>CRAMC</t>
+          <t>JKPAPER</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -4336,22 +4336,22 @@
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>264.7</v>
+        <v>391.55</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>58.05</v>
+        <v>56.04</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>54.32</v>
+        <v>59.89</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v/>
+        <v>54.33</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GAEL</t>
+          <t>SMLMAH</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -4360,22 +4360,22 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>177.46</v>
+        <v>5194</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>57.94</v>
+        <v>56.04</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>65.39</v>
+        <v>61.57</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>68.81999999999999</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>IFBIND</t>
+          <t>EDELWEISS</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -4384,22 +4384,22 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>1402.9</v>
+        <v>125.42</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>57.6</v>
+        <v>55.87</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>58.72</v>
+        <v>57.35</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>51.44</v>
+        <v>60.25</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>SKIPPER</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -4408,22 +4408,22 @@
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>555.45</v>
+        <v>813.5</v>
       </c>
       <c r="D85" s="4" t="n">
-        <v>57.52</v>
+        <v>55.58</v>
       </c>
       <c r="E85" s="4" t="n">
-        <v>62.87</v>
+        <v>63.42</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>61.85</v>
+        <v>58.77</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>INDIAGLYCO</t>
+          <t>SHAILY</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -4432,22 +4432,22 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>1146.5</v>
+        <v>3270.4</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>57.47</v>
+        <v>54.92</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>60.44</v>
+        <v>66.52</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>64.52</v>
+        <v>73.44</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>GODREJAGRO</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -4456,22 +4456,22 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>581.65</v>
+        <v>108.43</v>
       </c>
       <c r="D87" s="4" t="n">
-        <v>57.41</v>
+        <v>54.5</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>50.89</v>
+        <v>50.5</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>47.02</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>NETWORK18</t>
+          <t>PRSMJOHNSN</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -4480,22 +4480,22 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>30.59</v>
+        <v>111.18</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>57.33</v>
+        <v>54.28</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>39.63</v>
+        <v>41.07</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>35.35</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>FEDFINA</t>
+          <t>MTARTECH</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -4504,22 +4504,22 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>156.84</v>
+        <v>6997</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>57.27</v>
+        <v>54.23</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>56.41</v>
+        <v>59.71</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>59.1</v>
+        <v>70.15000000000001</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>CAMPUS</t>
+          <t>AGARWALEYE</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -4528,22 +4528,22 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>228.15</v>
+        <v>507.8</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>57.27</v>
+        <v>53.94</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>45.07</v>
+        <v>57.35</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>42.66</v>
+        <v>57.98</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>INDIGOPNTS</t>
+          <t>CAMPUS</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -4552,22 +4552,22 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>1130.7</v>
+        <v>226.14</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>56.82</v>
+        <v>53.93</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>65.13</v>
+        <v>44.05</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>50.36</v>
+        <v>42.19</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>MAHSEAMLES</t>
+          <t>ATLANTAELE</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -4576,22 +4576,22 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>610.6</v>
+        <v>1745.1</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>56.69</v>
+        <v>53.84</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>59.18</v>
+        <v>57.92</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>52.56</v>
+        <v/>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>JYOTHYLAB</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -4600,22 +4600,22 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>208.46</v>
+        <v>606.05</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>56.48</v>
+        <v>53.7</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>42.06</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>38.22</v>
+        <v>69.86</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>SMLMAH</t>
+          <t>APLLTD</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -4624,22 +4624,22 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>5159.5</v>
+        <v>824</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>56.43</v>
+        <v>53.58</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>63.79</v>
+        <v>55.49</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>66.81999999999999</v>
+        <v>48.89</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>SKFINDIA</t>
+          <t>ICIL</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -4648,22 +4648,22 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>1596.5</v>
+        <v>423.4</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>56.43</v>
+        <v>53.53</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>41.82</v>
+        <v>64.16</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>33.39</v>
+        <v>63.81</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>SHRIPISTON</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -4672,22 +4672,22 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>627.15</v>
+        <v>4498.4</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>56.38</v>
+        <v>53.52</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>70.89</v>
+        <v>74.64</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>83.70999999999999</v>
+        <v>79.26000000000001</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>ELECTCAST</t>
+          <t>GHCL</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -4696,22 +4696,22 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>73.87</v>
+        <v>440.15</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>56.27</v>
+        <v>53.44</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>47.39</v>
+        <v>44.3</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>42.65</v>
+        <v>42.71</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>MTARTECH</t>
+          <t>PGIL</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -4720,22 +4720,22 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>7029.5</v>
+        <v>2294.8</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>55.97</v>
+        <v>53.28</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>60.06</v>
+        <v>66.93000000000001</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>70.26000000000001</v>
+        <v>74.29000000000001</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>JSFB</t>
+          <t>AXISCADES</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -4744,22 +4744,22 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>562.85</v>
+        <v>1612.9</v>
       </c>
       <c r="D99" s="4" t="n">
-        <v>55.31</v>
+        <v>53.24</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>69.2</v>
+        <v>47.95</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>62.16</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>JLHL</t>
+          <t>WESTLIFE</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -4768,22 +4768,22 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>317.7</v>
+        <v>563.25</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>55.13</v>
+        <v>53.02</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>62.24</v>
+        <v>57.17</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>57.28</v>
+        <v>43.92</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>STYL</t>
+          <t>TEXRAIL</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -4792,22 +4792,22 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>392.55</v>
+        <v>109.44</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>55.08</v>
+        <v>52.96</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>65.5</v>
+        <v>48.64</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v/>
+        <v>44.03</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>SKFINDUS</t>
+          <t>SUNTECK</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -4816,22 +4816,22 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>2753.7</v>
+        <v>307.5</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>54.2</v>
+        <v>52.95</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>60.64</v>
+        <v>43.46</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v/>
+        <v>41.28</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>SHAREINDIA</t>
+          <t>V2RETAIL</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -4840,22 +4840,22 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>175.28</v>
+        <v>222.4</v>
       </c>
       <c r="D103" s="4" t="n">
-        <v>54.16</v>
+        <v>52.86</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>58.91</v>
+        <v>52.26</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>48.15</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>GRWRHITECH</t>
+          <t>AARTIDRUGS</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -4864,22 +4864,22 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>7109.5</v>
+        <v>417.9</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>53.57</v>
+        <v>52.74</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>74.97</v>
+        <v>58.36</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>69.76000000000001</v>
+        <v>49.53</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENGG</t>
+          <t>BLUESTONE</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -4888,22 +4888,22 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>92.25</v>
+        <v>800.5</v>
       </c>
       <c r="D105" s="4" t="n">
-        <v>53.39</v>
+        <v>52.51</v>
       </c>
       <c r="E105" s="4" t="n">
-        <v>66.78</v>
+        <v>69.48</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>65.2</v>
+        <v/>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>BAJAJELEC</t>
+          <t>OPTIEMUS</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -4912,22 +4912,22 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>351.65</v>
+        <v>576.45</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>52.82</v>
+        <v>52.28</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>45.79</v>
+        <v>60.18</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>32.2</v>
+        <v>55.38</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>EQUITASBNK</t>
+          <t>BLACKBUCK</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -4936,22 +4936,22 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>76.59999999999999</v>
+        <v>588.2</v>
       </c>
       <c r="D107" s="4" t="n">
-        <v>51.95</v>
+        <v>52.28</v>
       </c>
       <c r="E107" s="4" t="n">
-        <v>58.29</v>
+        <v>52.04</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>55.86</v>
+        <v>57.09</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>AXISCADES</t>
+          <t>TVSSCS</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -4960,22 +4960,22 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>1600.6</v>
+        <v>131.56</v>
       </c>
       <c r="D108" s="4" t="n">
-        <v>51.74</v>
+        <v>52.25</v>
       </c>
       <c r="E108" s="4" t="n">
-        <v>48.07</v>
+        <v>54.1</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>59.58</v>
+        <v>47.54</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>AARTIDRUGS</t>
+          <t>SANDUMA</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -4984,22 +4984,22 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>414.75</v>
+        <v>205.45</v>
       </c>
       <c r="D109" s="4" t="n">
-        <v>51.6</v>
+        <v>52.21</v>
       </c>
       <c r="E109" s="4" t="n">
-        <v>58.01</v>
+        <v>49.71</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>49.39</v>
+        <v>55.82</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>KIRLOSBROS</t>
+          <t>POWERMECH</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -5008,22 +5008,22 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>1918.2</v>
+        <v>2547.4</v>
       </c>
       <c r="D110" s="4" t="n">
-        <v>51.5</v>
+        <v>52.2</v>
       </c>
       <c r="E110" s="4" t="n">
-        <v>58.14</v>
+        <v>53.41</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>55.62</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>VIYASH</t>
+          <t>JYOTHYLAB</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -5032,22 +5032,22 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>265.85</v>
+        <v>207.4</v>
       </c>
       <c r="D111" s="4" t="n">
-        <v>51.21</v>
+        <v>52.04</v>
       </c>
       <c r="E111" s="4" t="n">
-        <v>60.11</v>
+        <v>43.68</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>64.22</v>
+        <v>38.64</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>CENTURYPLY</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -5056,22 +5056,22 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>772.75</v>
+        <v>543.35</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>51.17</v>
+        <v>51.89</v>
       </c>
       <c r="E112" s="4" t="n">
-        <v>48.94</v>
+        <v>63.64</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>51.45</v>
+        <v>67.81999999999999</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>JAIBALAJI</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -5080,22 +5080,22 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>66.08</v>
+        <v>207.71</v>
       </c>
       <c r="D113" s="4" t="n">
-        <v>50.97</v>
+        <v>51.53</v>
       </c>
       <c r="E113" s="4" t="n">
-        <v>45</v>
+        <v>55.07</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>40.77</v>
+        <v>55.17</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>ZAGGLE</t>
+          <t>SKFINDIA</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -5104,22 +5104,22 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>200.12</v>
+        <v>1571.3</v>
       </c>
       <c r="D114" s="4" t="n">
-        <v>50.92</v>
+        <v>51.39</v>
       </c>
       <c r="E114" s="4" t="n">
-        <v>37.27</v>
+        <v>40.25</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>39.1</v>
+        <v>32.99</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>TRIVENI</t>
+          <t>AEQUS</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -5128,22 +5128,22 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>295.28</v>
+        <v>246.66</v>
       </c>
       <c r="D115" s="4" t="n">
-        <v>50.73</v>
+        <v>51.07</v>
       </c>
       <c r="E115" s="4" t="n">
-        <v>41.88</v>
+        <v>65.89</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>44.63</v>
+        <v/>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>MIDHANI</t>
+          <t>SKIPPER</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -5152,22 +5152,22 @@
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>420.5</v>
+        <v>546.25</v>
       </c>
       <c r="D116" s="4" t="n">
-        <v>50.45</v>
+        <v>51.06</v>
       </c>
       <c r="E116" s="4" t="n">
-        <v>57.22</v>
+        <v>60.78</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>56.05</v>
+        <v>61.28</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>PICCADIL</t>
+          <t>RENUKA</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -5176,22 +5176,22 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>709.4</v>
+        <v>23.43</v>
       </c>
       <c r="D117" s="4" t="n">
-        <v>50.3</v>
+        <v>50.99</v>
       </c>
       <c r="E117" s="4" t="n">
-        <v>59.64</v>
+        <v>49.83</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v/>
+        <v>40.06</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>IMFA</t>
+          <t>VIYASH</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -5200,22 +5200,22 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>1421.9</v>
+        <v>267.4</v>
       </c>
       <c r="D118" s="4" t="n">
-        <v>50.17</v>
+        <v>50.95</v>
       </c>
       <c r="E118" s="4" t="n">
-        <v>51.22</v>
+        <v>57.07</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>61.65</v>
+        <v>63.15</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENT</t>
+          <t>SAATVIKGL</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -5224,22 +5224,22 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>78.55</v>
+        <v>428.4</v>
       </c>
       <c r="D119" s="4" t="n">
-        <v>50.16</v>
+        <v>50.81</v>
       </c>
       <c r="E119" s="4" t="n">
-        <v>58.39</v>
+        <v>46.22</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>60.16</v>
+        <v/>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>GSFC</t>
+          <t>SOUTHBANK</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -5248,22 +5248,22 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>160.61</v>
+        <v>45.73</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>50.11</v>
+        <v>50.76</v>
       </c>
       <c r="E120" s="4" t="n">
-        <v>42.16</v>
+        <v>58.25</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>44.02</v>
+        <v>68.92</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>CELLO</t>
+          <t>BECTORFOOD</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -5272,22 +5272,22 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>363.6</v>
+        <v>232.87</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>49.57</v>
+        <v>50.59</v>
       </c>
       <c r="E121" s="4" t="n">
-        <v>37.77</v>
+        <v>58.84</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>30.54</v>
+        <v>50.43</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>YATHARTH</t>
+          <t>CRAMC</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -5296,22 +5296,22 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>847.85</v>
+        <v>258.9</v>
       </c>
       <c r="D122" s="4" t="n">
-        <v>49.56</v>
+        <v>50.51</v>
       </c>
       <c r="E122" s="4" t="n">
-        <v>58.06</v>
+        <v>51.29</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>62.83</v>
+        <v/>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>PURVA</t>
+          <t>NESCO</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -5320,22 +5320,22 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>216.4</v>
+        <v>1048.4</v>
       </c>
       <c r="D123" s="4" t="n">
-        <v>49.48</v>
+        <v>50.39</v>
       </c>
       <c r="E123" s="4" t="n">
-        <v>50.3</v>
+        <v>42.49</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>46.09</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>ARVINDFASN</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -5344,22 +5344,22 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>536.95</v>
+        <v>449.4</v>
       </c>
       <c r="D124" s="4" t="n">
-        <v>49.46</v>
+        <v>50.3</v>
       </c>
       <c r="E124" s="4" t="n">
-        <v>62.73</v>
+        <v>47.92</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>67.43000000000001</v>
+        <v>49.31</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>APLLTD</t>
+          <t>HCG</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -5368,22 +5368,22 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>814.1</v>
+        <v>699.95</v>
       </c>
       <c r="D125" s="4" t="n">
-        <v>49.25</v>
+        <v>50.13</v>
       </c>
       <c r="E125" s="4" t="n">
-        <v>57.37</v>
+        <v>61.45</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>49.4</v>
+        <v>64.20999999999999</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>AGARWALEYE</t>
+          <t>HAPPSTMNDS</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -5392,22 +5392,22 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>500.2</v>
+        <v>408</v>
       </c>
       <c r="D126" s="4" t="n">
-        <v>49.21</v>
+        <v>50.11</v>
       </c>
       <c r="E126" s="4" t="n">
-        <v>55.82</v>
+        <v>53.1</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>56.99</v>
+        <v>35.34</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>INOXINDIA</t>
+          <t>SAFARI</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -5416,22 +5416,22 @@
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>1923.6</v>
+        <v>1522.2</v>
       </c>
       <c r="D127" s="4" t="n">
-        <v>48.98</v>
+        <v>50.07</v>
       </c>
       <c r="E127" s="4" t="n">
-        <v>71.48999999999999</v>
+        <v>42.4</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>79.53</v>
+        <v>41.04</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>V2RETAIL</t>
+          <t>SENCO</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -5440,22 +5440,22 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>220.05</v>
+        <v>362.75</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>48.65</v>
+        <v>49.48</v>
       </c>
       <c r="E128" s="4" t="n">
-        <v>51.45</v>
+        <v>52.42</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>63.6</v>
+        <v>50.36</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>JUSTDIAL</t>
+          <t>MIDHANI</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -5464,22 +5464,22 @@
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>674.05</v>
+        <v>417.75</v>
       </c>
       <c r="D129" s="4" t="n">
-        <v>48.43</v>
+        <v>49.27</v>
       </c>
       <c r="E129" s="4" t="n">
-        <v>57.19</v>
+        <v>55.42</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>46.05</v>
+        <v>55.51</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>ARVINDFASN</t>
+          <t>VIPIND</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -5488,22 +5488,22 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>448.35</v>
+        <v>304.3</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>48.43</v>
+        <v>49.13</v>
       </c>
       <c r="E130" s="4" t="n">
-        <v>47.23</v>
+        <v>44.16</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>49</v>
+        <v>36.91</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>GOKEX</t>
+          <t>TIPSMUSIC</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -5512,22 +5512,22 @@
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>797.6</v>
+        <v>660</v>
       </c>
       <c r="D131" s="4" t="n">
-        <v>48.42</v>
+        <v>49.11</v>
       </c>
       <c r="E131" s="4" t="n">
-        <v>54.35</v>
+        <v>52.17</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>51.41</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>RAIN</t>
+          <t>KIRLOSBROS</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -5536,22 +5536,22 @@
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>208.61</v>
+        <v>1899.3</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>47.92</v>
+        <v>49.05</v>
       </c>
       <c r="E132" s="4" t="n">
-        <v>65.5</v>
+        <v>58.59</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>60.13</v>
+        <v>55.78</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>RATNAMANI</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -5560,22 +5560,22 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>2354.4</v>
+        <v>2083.2</v>
       </c>
       <c r="D133" s="4" t="n">
-        <v>47.9</v>
+        <v>48.82</v>
       </c>
       <c r="E133" s="4" t="n">
-        <v>46.4</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>45.07</v>
+        <v/>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>RAYMONDLSL</t>
+          <t>ASTRAMICRO</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -5584,22 +5584,22 @@
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>730.85</v>
+        <v>1706.6</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>47.83</v>
+        <v>48.56</v>
       </c>
       <c r="E134" s="4" t="n">
-        <v>39.28</v>
+        <v>64</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>26</v>
+        <v>71.58</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>VIKRAMSOLR</t>
+          <t>REDTAPE</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -5608,22 +5608,22 @@
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>173.23</v>
+        <v>126.01</v>
       </c>
       <c r="D135" s="4" t="n">
-        <v>47.76</v>
+        <v>48.56</v>
       </c>
       <c r="E135" s="4" t="n">
-        <v>39.12</v>
+        <v>47.49</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v/>
+        <v>34.85</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>LXCHEM</t>
+          <t>THYROCARE</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -5632,22 +5632,22 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>173.21</v>
+        <v>581.45</v>
       </c>
       <c r="D136" s="4" t="n">
-        <v>47.71</v>
+        <v>48.47</v>
       </c>
       <c r="E136" s="4" t="n">
-        <v>57.92</v>
+        <v>62.85</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>45.69</v>
+        <v>69.48999999999999</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>VIPIND</t>
+          <t>JSFB</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -5656,22 +5656,22 @@
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>302.6</v>
+        <v>544.55</v>
       </c>
       <c r="D137" s="4" t="n">
-        <v>47.49</v>
+        <v>48.17</v>
       </c>
       <c r="E137" s="4" t="n">
-        <v>45.05</v>
+        <v>59.77</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>37.38</v>
+        <v>57.64</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>HCC</t>
+          <t>VIKRAMSOLR</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -5680,22 +5680,22 @@
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>21.03</v>
+        <v>172.71</v>
       </c>
       <c r="D138" s="4" t="n">
-        <v>47.45</v>
+        <v>47.91</v>
       </c>
       <c r="E138" s="4" t="n">
-        <v>47.72</v>
+        <v>38.96</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>45.46</v>
+        <v/>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>MAHSCOOTER</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -5704,22 +5704,22 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>13138</v>
+        <v>5502</v>
       </c>
       <c r="D139" s="4" t="n">
-        <v>47.39</v>
+        <v>47.88</v>
       </c>
       <c r="E139" s="4" t="n">
-        <v>51.3</v>
+        <v>56.72</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>56.65</v>
+        <v>70.27</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>POWERMECH</t>
+          <t>EMBDL</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -5728,22 +5728,22 @@
         </is>
       </c>
       <c r="C140" s="4" t="n">
-        <v>2502.4</v>
+        <v>62.16</v>
       </c>
       <c r="D140" s="4" t="n">
-        <v>46.67</v>
+        <v>47.79</v>
       </c>
       <c r="E140" s="4" t="n">
-        <v>50.13</v>
+        <v>49.76</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>51.33</v>
+        <v>42.67</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>PRSMJOHNSN</t>
+          <t>GAEL</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -5752,22 +5752,22 @@
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>107.97</v>
+        <v>166.98</v>
       </c>
       <c r="D141" s="4" t="n">
-        <v>46.46</v>
+        <v>47.41</v>
       </c>
       <c r="E141" s="4" t="n">
-        <v>36.42</v>
+        <v>57.65</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>38.73</v>
+        <v>64.31999999999999</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>GRINDWELL</t>
+          <t>RATEGAIN</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -5776,22 +5776,22 @@
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>2059.3</v>
+        <v>918.25</v>
       </c>
       <c r="D142" s="4" t="n">
-        <v>46.45</v>
+        <v>47.4</v>
       </c>
       <c r="E142" s="4" t="n">
-        <v>59.01</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>56.91</v>
+        <v>66.39</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>CAPILLARY</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -5800,22 +5800,22 @@
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>5457</v>
+        <v>508.95</v>
       </c>
       <c r="D143" s="4" t="n">
-        <v>46.36</v>
+        <v>47.22</v>
       </c>
       <c r="E143" s="4" t="n">
-        <v>57.32</v>
+        <v>44.29</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>70.5</v>
+        <v/>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>BBOX</t>
+          <t>NFL</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -5824,22 +5824,22 @@
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>775.65</v>
+        <v>71.36</v>
       </c>
       <c r="D144" s="4" t="n">
-        <v>46.21</v>
+        <v>47.15</v>
       </c>
       <c r="E144" s="4" t="n">
-        <v>51.04</v>
+        <v>40.63</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>60.07</v>
+        <v>42.73</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>STAR</t>
+          <t>APOLLO</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -5848,22 +5848,22 @@
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>993</v>
+        <v>387.45</v>
       </c>
       <c r="D145" s="4" t="n">
-        <v>45.91</v>
+        <v>47.15</v>
       </c>
       <c r="E145" s="4" t="n">
-        <v>47.06</v>
+        <v>57.19</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>54.57</v>
+        <v>67.34999999999999</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>TANLA</t>
+          <t>JLHL</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -5872,22 +5872,22 @@
         </is>
       </c>
       <c r="C146" s="4" t="n">
-        <v>572.8</v>
+        <v>307.45</v>
       </c>
       <c r="D146" s="4" t="n">
-        <v>45.9</v>
+        <v>47.13</v>
       </c>
       <c r="E146" s="4" t="n">
-        <v>55.92</v>
+        <v>57.3</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>47.8</v>
+        <v>55.33</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>BALAMINES</t>
+          <t>EUREKAFORB</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -5896,22 +5896,22 @@
         </is>
       </c>
       <c r="C147" s="4" t="n">
-        <v>2078.2</v>
+        <v>433.15</v>
       </c>
       <c r="D147" s="4" t="n">
-        <v>45.87</v>
+        <v>47.13</v>
       </c>
       <c r="E147" s="4" t="n">
-        <v>60.98</v>
+        <v>40.39</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>58.74</v>
+        <v>39.11</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>KANSAINER</t>
+          <t>LXCHEM</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -5920,22 +5920,22 @@
         </is>
       </c>
       <c r="C148" s="4" t="n">
-        <v>201.51</v>
+        <v>171.34</v>
       </c>
       <c r="D148" s="4" t="n">
-        <v>45.61</v>
+        <v>46.91</v>
       </c>
       <c r="E148" s="4" t="n">
-        <v>49.37</v>
+        <v>56.59</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>42.61</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>GMRP&amp;UI</t>
+          <t>PURVA</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -5944,22 +5944,22 @@
         </is>
       </c>
       <c r="C149" s="4" t="n">
-        <v>96.58</v>
+        <v>214.22</v>
       </c>
       <c r="D149" s="4" t="n">
-        <v>45.57</v>
+        <v>46.9</v>
       </c>
       <c r="E149" s="4" t="n">
-        <v>40.86</v>
+        <v>48.45</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>49.2</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>SOUTHBANK</t>
+          <t>TRIVENI</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -5968,22 +5968,22 @@
         </is>
       </c>
       <c r="C150" s="4" t="n">
-        <v>45.16</v>
+        <v>283.82</v>
       </c>
       <c r="D150" s="4" t="n">
-        <v>45.36</v>
+        <v>46.54</v>
       </c>
       <c r="E150" s="4" t="n">
-        <v>57.24</v>
+        <v>40.6</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>68.09999999999999</v>
+        <v>43.56</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>OPTIEMUS</t>
+          <t>IFBIND</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -5992,22 +5992,22 @@
         </is>
       </c>
       <c r="C151" s="4" t="n">
-        <v>551.75</v>
+        <v>1351.6</v>
       </c>
       <c r="D151" s="4" t="n">
-        <v>45.32</v>
+        <v>46.46</v>
       </c>
       <c r="E151" s="4" t="n">
-        <v>55.92</v>
+        <v>53.57</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>53.2</v>
+        <v>50.15</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>ASTRAMICRO</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -6016,22 +6016,22 @@
         </is>
       </c>
       <c r="C152" s="4" t="n">
-        <v>1684.2</v>
+        <v>157.69</v>
       </c>
       <c r="D152" s="4" t="n">
-        <v>45.15</v>
+        <v>46.32</v>
       </c>
       <c r="E152" s="4" t="n">
-        <v>62.16</v>
+        <v>49.44</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>69.66</v>
+        <v>54.51</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>LOTUSDEV</t>
+          <t>IIFLCAPS</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -6040,22 +6040,22 @@
         </is>
       </c>
       <c r="C153" s="4" t="n">
-        <v>166.16</v>
+        <v>334.4</v>
       </c>
       <c r="D153" s="4" t="n">
-        <v>45.15</v>
+        <v>45.83</v>
       </c>
       <c r="E153" s="4" t="n">
-        <v>54.02</v>
+        <v>52.07</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v/>
+        <v>57.4</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>AVL</t>
+          <t>KSCL</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -6064,22 +6064,22 @@
         </is>
       </c>
       <c r="C154" s="4" t="n">
-        <v>611</v>
+        <v>785</v>
       </c>
       <c r="D154" s="4" t="n">
-        <v>45.14</v>
+        <v>45.67</v>
       </c>
       <c r="E154" s="4" t="n">
-        <v>55.75</v>
+        <v>40.69</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>60.7</v>
+        <v>43.73</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>KNRCON</t>
+          <t>ZAGGLE</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -6088,22 +6088,22 @@
         </is>
       </c>
       <c r="C155" s="4" t="n">
-        <v>127</v>
+        <v>190.26</v>
       </c>
       <c r="D155" s="4" t="n">
-        <v>45.06</v>
+        <v>45.58</v>
       </c>
       <c r="E155" s="4" t="n">
-        <v>45.92</v>
+        <v>34.43</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>35.45</v>
+        <v>38.26</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>PNGJL</t>
+          <t>MEDPLUS</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -6112,22 +6112,22 @@
         </is>
       </c>
       <c r="C156" s="4" t="n">
-        <v>609.45</v>
+        <v>688.35</v>
       </c>
       <c r="D156" s="4" t="n">
-        <v>44.98</v>
+        <v>45.43</v>
       </c>
       <c r="E156" s="4" t="n">
-        <v>50.46</v>
+        <v>31.38</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>49.1</v>
+        <v>40.06</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>APOLLO</t>
+          <t>SHAREINDIA</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -6136,22 +6136,22 @@
         </is>
       </c>
       <c r="C157" s="4" t="n">
-        <v>384.55</v>
+        <v>169.02</v>
       </c>
       <c r="D157" s="4" t="n">
-        <v>44.6</v>
+        <v>45.21</v>
       </c>
       <c r="E157" s="4" t="n">
-        <v>56.73</v>
+        <v>55.44</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>66.93000000000001</v>
+        <v>47.07</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>TSFINV</t>
+          <t>ROUTE</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -6160,16 +6160,16 @@
         </is>
       </c>
       <c r="C158" s="4" t="n">
-        <v>424.7</v>
+        <v>509.35</v>
       </c>
       <c r="D158" s="4" t="n">
-        <v>44.49</v>
+        <v>45.01</v>
       </c>
       <c r="E158" s="4" t="n">
-        <v>48.57</v>
+        <v>42.63</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>53.7</v>
+        <v>30.54</v>
       </c>
     </row>
     <row r="159">
@@ -6184,22 +6184,22 @@
         </is>
       </c>
       <c r="C159" s="4" t="n">
-        <v>625.45</v>
+        <v>623.65</v>
       </c>
       <c r="D159" s="4" t="n">
-        <v>44.46</v>
+        <v>44.97</v>
       </c>
       <c r="E159" s="4" t="n">
-        <v>48.23</v>
+        <v>48.33</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>56.53</v>
+        <v>56.58</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>TIPSMUSIC</t>
+          <t>FINPIPE</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -6208,46 +6208,46 @@
         </is>
       </c>
       <c r="C160" s="4" t="n">
-        <v>651.05</v>
+        <v>160.54</v>
       </c>
       <c r="D160" s="4" t="n">
-        <v>44.45</v>
+        <v>44.8</v>
       </c>
       <c r="E160" s="4" t="n">
-        <v>52.62</v>
+        <v>40.66</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>57.89</v>
+        <v>41.81</v>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="inlineStr">
-        <is>
-          <t>CAPILLARY</t>
-        </is>
-      </c>
-      <c r="B161" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C161" s="4" t="n">
-        <v>502.35</v>
-      </c>
-      <c r="D161" s="4" t="n">
-        <v>44.3</v>
-      </c>
-      <c r="E161" s="4" t="n">
-        <v>44.43</v>
-      </c>
-      <c r="F161" s="4" t="n">
-        <v/>
+      <c r="A161" s="5" t="inlineStr">
+        <is>
+          <t>LLOYDSENGG</t>
+        </is>
+      </c>
+      <c r="B161" s="6" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C161" s="7" t="n">
+        <v>86.73999999999999</v>
+      </c>
+      <c r="D161" s="7" t="n">
+        <v>44.67</v>
+      </c>
+      <c r="E161" s="7" t="n">
+        <v>62.27</v>
+      </c>
+      <c r="F161" s="7" t="n">
+        <v>63.51</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>CENTURYPLY</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -6256,22 +6256,22 @@
         </is>
       </c>
       <c r="C162" s="4" t="n">
-        <v>156.56</v>
+        <v>751.75</v>
       </c>
       <c r="D162" s="4" t="n">
-        <v>44.29</v>
+        <v>44.6</v>
       </c>
       <c r="E162" s="4" t="n">
-        <v>48.88</v>
+        <v>47.09</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>54.14</v>
+        <v>50.77</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>MEDPLUS</t>
+          <t>SUPRIYA</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -6280,46 +6280,46 @@
         </is>
       </c>
       <c r="C163" s="4" t="n">
-        <v>689.55</v>
+        <v>804.15</v>
       </c>
       <c r="D163" s="4" t="n">
-        <v>44.28</v>
+        <v>44.54</v>
       </c>
       <c r="E163" s="4" t="n">
-        <v>32.68</v>
+        <v>49.94</v>
       </c>
       <c r="F163" s="4" t="n">
-        <v>40.89</v>
+        <v>56.08</v>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="5" t="inlineStr">
-        <is>
-          <t>THYROCARE</t>
-        </is>
-      </c>
-      <c r="B164" s="6" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C164" s="7" t="n">
-        <v>565.55</v>
-      </c>
-      <c r="D164" s="7" t="n">
-        <v>44.17</v>
-      </c>
-      <c r="E164" s="7" t="n">
-        <v>60.61</v>
-      </c>
-      <c r="F164" s="7" t="n">
-        <v>67.47</v>
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>ORIENTCEM</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C164" s="4" t="n">
+        <v>131.41</v>
+      </c>
+      <c r="D164" s="4" t="n">
+        <v>44.48</v>
+      </c>
+      <c r="E164" s="4" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="F164" s="4" t="n">
+        <v>35.26</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>DBL</t>
+          <t>EQUITASBNK</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -6328,22 +6328,22 @@
         </is>
       </c>
       <c r="C165" s="4" t="n">
-        <v>415</v>
+        <v>74.17</v>
       </c>
       <c r="D165" s="4" t="n">
-        <v>43.79</v>
+        <v>44.16</v>
       </c>
       <c r="E165" s="4" t="n">
-        <v>44.82</v>
+        <v>53.7</v>
       </c>
       <c r="F165" s="4" t="n">
-        <v>46.95</v>
+        <v>54.11</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>JKLAKSHMI</t>
+          <t>STAR</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -6352,22 +6352,22 @@
         </is>
       </c>
       <c r="C166" s="4" t="n">
-        <v>557.9</v>
+        <v>983</v>
       </c>
       <c r="D166" s="4" t="n">
-        <v>43.67</v>
+        <v>44.07</v>
       </c>
       <c r="E166" s="4" t="n">
-        <v>36.88</v>
+        <v>51</v>
       </c>
       <c r="F166" s="4" t="n">
-        <v>39.12</v>
+        <v>56.41</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>FINPIPE</t>
+          <t>GRINDWELL</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -6376,22 +6376,22 @@
         </is>
       </c>
       <c r="C167" s="4" t="n">
-        <v>160.44</v>
+        <v>2024.1</v>
       </c>
       <c r="D167" s="4" t="n">
-        <v>43.54</v>
+        <v>44.02</v>
       </c>
       <c r="E167" s="4" t="n">
-        <v>40.53</v>
+        <v>58.87</v>
       </c>
       <c r="F167" s="4" t="n">
-        <v>41.79</v>
+        <v>56.85</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>TEXRAIL</t>
+          <t>SHARDACROP</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -6400,22 +6400,22 @@
         </is>
       </c>
       <c r="C168" s="4" t="n">
-        <v>105.48</v>
+        <v>793.05</v>
       </c>
       <c r="D168" s="4" t="n">
-        <v>43.49</v>
+        <v>43.96</v>
       </c>
       <c r="E168" s="4" t="n">
-        <v>43.16</v>
+        <v>39.37</v>
       </c>
       <c r="F168" s="4" t="n">
-        <v>42.91</v>
+        <v>50.11</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>CSBBANK</t>
+          <t>RELIGARE</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -6424,22 +6424,22 @@
         </is>
       </c>
       <c r="C169" s="4" t="n">
-        <v>322.9</v>
+        <v>234.2</v>
       </c>
       <c r="D169" s="4" t="n">
-        <v>43.48</v>
+        <v>43.93</v>
       </c>
       <c r="E169" s="4" t="n">
-        <v>39.83</v>
+        <v>46.19</v>
       </c>
       <c r="F169" s="4" t="n">
-        <v>45.01</v>
+        <v>49.97</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>KIRLPNU</t>
+          <t>DBREALTY</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -6448,22 +6448,22 @@
         </is>
       </c>
       <c r="C170" s="4" t="n">
-        <v>748.8</v>
+        <v>107.37</v>
       </c>
       <c r="D170" s="4" t="n">
-        <v>43.46</v>
+        <v>43.81</v>
       </c>
       <c r="E170" s="4" t="n">
-        <v>51.23</v>
+        <v>44.66</v>
       </c>
       <c r="F170" s="4" t="n">
-        <v>56.57</v>
+        <v>43.51</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>SUNTECK</t>
+          <t>UJJIVANSFB</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -6472,22 +6472,22 @@
         </is>
       </c>
       <c r="C171" s="4" t="n">
-        <v>296.35</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="D171" s="4" t="n">
-        <v>43.22</v>
+        <v>43.57</v>
       </c>
       <c r="E171" s="4" t="n">
-        <v>39.74</v>
+        <v>59.14</v>
       </c>
       <c r="F171" s="4" t="n">
-        <v>40.32</v>
+        <v>62.99</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>SUPRIYA</t>
+          <t>RAIN</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -6496,22 +6496,22 @@
         </is>
       </c>
       <c r="C172" s="4" t="n">
-        <v>811.7</v>
+        <v>199.31</v>
       </c>
       <c r="D172" s="4" t="n">
-        <v>43</v>
+        <v>43.56</v>
       </c>
       <c r="E172" s="4" t="n">
-        <v>50.06</v>
+        <v>59.8</v>
       </c>
       <c r="F172" s="4" t="n">
-        <v>56.15</v>
+        <v>58.13</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>DATAMATICS</t>
+          <t>IMFA</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -6520,22 +6520,22 @@
         </is>
       </c>
       <c r="C173" s="4" t="n">
-        <v>820.9</v>
+        <v>1370.7</v>
       </c>
       <c r="D173" s="4" t="n">
-        <v>42.71</v>
+        <v>43.55</v>
       </c>
       <c r="E173" s="4" t="n">
-        <v>52</v>
+        <v>50.32</v>
       </c>
       <c r="F173" s="4" t="n">
-        <v>56.12</v>
+        <v>61.16</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>CERA</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -6544,22 +6544,22 @@
         </is>
       </c>
       <c r="C174" s="4" t="n">
-        <v>5858.5</v>
+        <v>201.04</v>
       </c>
       <c r="D174" s="4" t="n">
-        <v>42</v>
+        <v>43.41</v>
       </c>
       <c r="E174" s="4" t="n">
-        <v>53.01</v>
+        <v>48.35</v>
       </c>
       <c r="F174" s="4" t="n">
-        <v>48.95</v>
+        <v>42.98</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>SENCO</t>
+          <t>NETWORK18</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -6568,22 +6568,22 @@
         </is>
       </c>
       <c r="C175" s="4" t="n">
-        <v>345.4</v>
+        <v>28.8</v>
       </c>
       <c r="D175" s="4" t="n">
-        <v>41.81</v>
+        <v>43.26</v>
       </c>
       <c r="E175" s="4" t="n">
-        <v>50</v>
+        <v>37.16</v>
       </c>
       <c r="F175" s="4" t="n">
-        <v>49.42</v>
+        <v>34.61</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>REDTAPE</t>
+          <t>CELLO</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -6592,22 +6592,22 @@
         </is>
       </c>
       <c r="C176" s="4" t="n">
-        <v>123.98</v>
+        <v>350.8</v>
       </c>
       <c r="D176" s="4" t="n">
-        <v>41.62</v>
+        <v>43.25</v>
       </c>
       <c r="E176" s="4" t="n">
-        <v>45.07</v>
+        <v>35.55</v>
       </c>
       <c r="F176" s="4" t="n">
-        <v>34.59</v>
+        <v>29.08</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>PARKHOSPS</t>
+          <t>GSFC</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -6616,22 +6616,22 @@
         </is>
       </c>
       <c r="C177" s="4" t="n">
-        <v>272.6</v>
+        <v>157.97</v>
       </c>
       <c r="D177" s="4" t="n">
-        <v>41.47</v>
+        <v>43.2</v>
       </c>
       <c r="E177" s="4" t="n">
-        <v>61.21</v>
+        <v>41.91</v>
       </c>
       <c r="F177" s="4" t="n">
-        <v/>
+        <v>43.95</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>PRIVISCL</t>
+          <t>KANSAINER</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -6640,22 +6640,22 @@
         </is>
       </c>
       <c r="C178" s="4" t="n">
-        <v>3479.7</v>
+        <v>198.44</v>
       </c>
       <c r="D178" s="4" t="n">
-        <v>41.25</v>
+        <v>42.78</v>
       </c>
       <c r="E178" s="4" t="n">
-        <v>56.6</v>
+        <v>43.9</v>
       </c>
       <c r="F178" s="4" t="n">
-        <v>67.23</v>
+        <v>39.62</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>MASTEK</t>
+          <t>BAJAJELEC</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -6664,22 +6664,22 @@
         </is>
       </c>
       <c r="C179" s="4" t="n">
-        <v>1705.2</v>
+        <v>334.8</v>
       </c>
       <c r="D179" s="4" t="n">
-        <v>41.25</v>
+        <v>42.64</v>
       </c>
       <c r="E179" s="4" t="n">
-        <v>47.66</v>
+        <v>40.92</v>
       </c>
       <c r="F179" s="4" t="n">
-        <v>42.78</v>
+        <v>30.04</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>METROPOLIS</t>
+          <t>CCAVENUE</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -6688,22 +6688,22 @@
         </is>
       </c>
       <c r="C180" s="4" t="n">
-        <v>540.8</v>
+        <v>15.27</v>
       </c>
       <c r="D180" s="4" t="n">
-        <v>40.52</v>
+        <v>42.17</v>
       </c>
       <c r="E180" s="4" t="n">
-        <v>56.9</v>
+        <v>47.69</v>
       </c>
       <c r="F180" s="4" t="n">
-        <v>58.94</v>
+        <v>42.74</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>WEWORK</t>
+          <t>AVL</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -6712,22 +6712,22 @@
         </is>
       </c>
       <c r="C181" s="4" t="n">
-        <v>682.9</v>
+        <v>592.3</v>
       </c>
       <c r="D181" s="4" t="n">
-        <v>40.45</v>
+        <v>42.03</v>
       </c>
       <c r="E181" s="4" t="n">
-        <v>56.49</v>
+        <v>53.85</v>
       </c>
       <c r="F181" s="4" t="n">
-        <v/>
+        <v>59.35</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>REFEX</t>
+          <t>RTNINDIA</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -6736,22 +6736,22 @@
         </is>
       </c>
       <c r="C182" s="4" t="n">
-        <v>293.95</v>
+        <v>30.24</v>
       </c>
       <c r="D182" s="4" t="n">
-        <v>40.31</v>
+        <v>41.97</v>
       </c>
       <c r="E182" s="4" t="n">
-        <v>49.65</v>
+        <v>39.19</v>
       </c>
       <c r="F182" s="4" t="n">
-        <v>49.53</v>
+        <v>39.22</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>SHAKTIPUMP</t>
+          <t>IONEXCHANG</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -6760,22 +6760,22 @@
         </is>
       </c>
       <c r="C183" s="4" t="n">
-        <v>506.2</v>
+        <v>376</v>
       </c>
       <c r="D183" s="4" t="n">
-        <v>40.18</v>
+        <v>41.96</v>
       </c>
       <c r="E183" s="4" t="n">
-        <v>38.82</v>
+        <v>45.79</v>
       </c>
       <c r="F183" s="4" t="n">
-        <v>44.36</v>
+        <v>44.18</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>RALLIS</t>
+          <t>GOKEX</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -6784,22 +6784,22 @@
         </is>
       </c>
       <c r="C184" s="4" t="n">
-        <v>212.85</v>
+        <v>774.9</v>
       </c>
       <c r="D184" s="4" t="n">
-        <v>40.18</v>
+        <v>41.35</v>
       </c>
       <c r="E184" s="4" t="n">
-        <v>34.73</v>
+        <v>50.33</v>
       </c>
       <c r="F184" s="4" t="n">
-        <v>42.39</v>
+        <v>50.23</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>NESCO</t>
+          <t>JSLL</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -6808,22 +6808,22 @@
         </is>
       </c>
       <c r="C185" s="4" t="n">
-        <v>1032.6</v>
+        <v>512.5</v>
       </c>
       <c r="D185" s="4" t="n">
-        <v>40.05</v>
+        <v>41.33</v>
       </c>
       <c r="E185" s="4" t="n">
-        <v>40.81</v>
+        <v>38.79</v>
       </c>
       <c r="F185" s="4" t="n">
-        <v>48.95</v>
+        <v>40.72</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>ORKLAINDIA</t>
+          <t>ADVENZYMES</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -6832,22 +6832,22 @@
         </is>
       </c>
       <c r="C186" s="4" t="n">
-        <v>550.35</v>
+        <v>299.8</v>
       </c>
       <c r="D186" s="4" t="n">
-        <v>39.95</v>
+        <v>41.1</v>
       </c>
       <c r="E186" s="4" t="n">
-        <v>35.67</v>
+        <v>42.43</v>
       </c>
       <c r="F186" s="4" t="n">
-        <v/>
+        <v>47.04</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>INOXGREEN</t>
+          <t>GREAVESCOT</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -6856,22 +6856,22 @@
         </is>
       </c>
       <c r="C187" s="4" t="n">
-        <v>175.08</v>
+        <v>194.41</v>
       </c>
       <c r="D187" s="4" t="n">
-        <v>39.76</v>
+        <v>41.02</v>
       </c>
       <c r="E187" s="4" t="n">
-        <v>48.4</v>
+        <v>49.57</v>
       </c>
       <c r="F187" s="4" t="n">
-        <v>52.3</v>
+        <v>51.51</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>SANDUMA</t>
+          <t>HEMIPROP</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -6880,22 +6880,22 @@
         </is>
       </c>
       <c r="C188" s="4" t="n">
-        <v>196.95</v>
+        <v>130.56</v>
       </c>
       <c r="D188" s="4" t="n">
-        <v>39.68</v>
+        <v>40.91</v>
       </c>
       <c r="E188" s="4" t="n">
-        <v>46.51</v>
+        <v>43.86</v>
       </c>
       <c r="F188" s="4" t="n">
-        <v>54.31</v>
+        <v>46.39</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>SAFARI</t>
+          <t>MOIL</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -6904,22 +6904,22 @@
         </is>
       </c>
       <c r="C189" s="4" t="n">
-        <v>1490.2</v>
+        <v>258.25</v>
       </c>
       <c r="D189" s="4" t="n">
-        <v>39.66</v>
+        <v>40.71</v>
       </c>
       <c r="E189" s="4" t="n">
-        <v>41.46</v>
+        <v>37.05</v>
       </c>
       <c r="F189" s="4" t="n">
-        <v>40.76</v>
+        <v>42.16</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>DBREALTY</t>
+          <t>KIRLPNU</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -6928,22 +6928,22 @@
         </is>
       </c>
       <c r="C190" s="4" t="n">
-        <v>106.08</v>
+        <v>731.5</v>
       </c>
       <c r="D190" s="4" t="n">
-        <v>39.63</v>
+        <v>40.65</v>
       </c>
       <c r="E190" s="4" t="n">
-        <v>43.72</v>
+        <v>48.35</v>
       </c>
       <c r="F190" s="4" t="n">
-        <v>43.27</v>
+        <v>55.26</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>BIRLACORPN</t>
+          <t>PNGJL</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -6952,22 +6952,22 @@
         </is>
       </c>
       <c r="C191" s="4" t="n">
-        <v>891.5</v>
+        <v>594.55</v>
       </c>
       <c r="D191" s="4" t="n">
-        <v>39.62</v>
+        <v>40.38</v>
       </c>
       <c r="E191" s="4" t="n">
-        <v>41.6</v>
+        <v>49.76</v>
       </c>
       <c r="F191" s="4" t="n">
-        <v>39.68</v>
+        <v>48.68</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>ORIENTCEM</t>
+          <t>LLOYDSENT</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -6976,22 +6976,22 @@
         </is>
       </c>
       <c r="C192" s="4" t="n">
-        <v>130.86</v>
+        <v>73.53</v>
       </c>
       <c r="D192" s="4" t="n">
-        <v>39.58</v>
+        <v>40.17</v>
       </c>
       <c r="E192" s="4" t="n">
-        <v>36.87</v>
+        <v>53.28</v>
       </c>
       <c r="F192" s="4" t="n">
-        <v>35.28</v>
+        <v>57.41</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>TIMETECHNO</t>
+          <t>BBOX</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -7000,22 +7000,22 @@
         </is>
       </c>
       <c r="C193" s="4" t="n">
-        <v>187.48</v>
+        <v>738</v>
       </c>
       <c r="D193" s="4" t="n">
-        <v>39.54</v>
+        <v>40.13</v>
       </c>
       <c r="E193" s="4" t="n">
-        <v>49.24</v>
+        <v>48.57</v>
       </c>
       <c r="F193" s="4" t="n">
-        <v>52.18</v>
+        <v>58.91</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>SPARC</t>
+          <t>PRIVISCL</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -7024,22 +7024,22 @@
         </is>
       </c>
       <c r="C194" s="4" t="n">
-        <v>199.59</v>
+        <v>3456.6</v>
       </c>
       <c r="D194" s="4" t="n">
-        <v>39.39</v>
+        <v>39.94</v>
       </c>
       <c r="E194" s="4" t="n">
-        <v>51.87</v>
+        <v>55.58</v>
       </c>
       <c r="F194" s="4" t="n">
-        <v>53.12</v>
+        <v>66.72</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>TARC</t>
+          <t>DBL</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -7048,22 +7048,22 @@
         </is>
       </c>
       <c r="C195" s="4" t="n">
-        <v>121.74</v>
+        <v>407.55</v>
       </c>
       <c r="D195" s="4" t="n">
-        <v>39.37</v>
+        <v>39.72</v>
       </c>
       <c r="E195" s="4" t="n">
-        <v>43.41</v>
+        <v>43.24</v>
       </c>
       <c r="F195" s="4" t="n">
-        <v>45.26</v>
+        <v>46.12</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>TARC</t>
+          <t>TIMETECHNO</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -7072,22 +7072,22 @@
         </is>
       </c>
       <c r="C196" s="4" t="n">
-        <v>121.74</v>
+        <v>186.29</v>
       </c>
       <c r="D196" s="4" t="n">
-        <v>39.37</v>
+        <v>39.65</v>
       </c>
       <c r="E196" s="4" t="n">
-        <v>43.41</v>
+        <v>48.59</v>
       </c>
       <c r="F196" s="4" t="n">
-        <v>45.26</v>
+        <v>51.92</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>ADVENZYMES</t>
+          <t>REFEX</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -7096,22 +7096,22 @@
         </is>
       </c>
       <c r="C197" s="4" t="n">
-        <v>300</v>
+        <v>287.55</v>
       </c>
       <c r="D197" s="4" t="n">
-        <v>39.35</v>
+        <v>39.45</v>
       </c>
       <c r="E197" s="4" t="n">
-        <v>42.49</v>
+        <v>47.86</v>
       </c>
       <c r="F197" s="4" t="n">
-        <v>47.07</v>
+        <v>48.93</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>RELAXO</t>
+          <t>PICCADIL</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -7120,22 +7120,22 @@
         </is>
       </c>
       <c r="C198" s="4" t="n">
-        <v>376.6</v>
+        <v>651.25</v>
       </c>
       <c r="D198" s="4" t="n">
-        <v>39.3</v>
+        <v>39.45</v>
       </c>
       <c r="E198" s="4" t="n">
-        <v>51.02</v>
+        <v>51.63</v>
       </c>
       <c r="F198" s="4" t="n">
-        <v>38.42</v>
+        <v/>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>INDIASHLTR</t>
+          <t>WEWORK</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -7144,22 +7144,22 @@
         </is>
       </c>
       <c r="C199" s="4" t="n">
-        <v>675.3</v>
+        <v>675.35</v>
       </c>
       <c r="D199" s="4" t="n">
-        <v>39.26</v>
+        <v>39.32</v>
       </c>
       <c r="E199" s="4" t="n">
-        <v>35.33</v>
+        <v>57.51</v>
       </c>
       <c r="F199" s="4" t="n">
-        <v>41.6</v>
+        <v/>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>FIEMIND</t>
+          <t>CRIZAC</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -7168,22 +7168,22 @@
         </is>
       </c>
       <c r="C200" s="4" t="n">
-        <v>2190.6</v>
+        <v>175.78</v>
       </c>
       <c r="D200" s="4" t="n">
-        <v>39.07</v>
+        <v>39.26</v>
       </c>
       <c r="E200" s="4" t="n">
-        <v>48.87</v>
+        <v>33.71</v>
       </c>
       <c r="F200" s="4" t="n">
-        <v>63.53</v>
+        <v/>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>RCF</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -7192,22 +7192,22 @@
         </is>
       </c>
       <c r="C201" s="4" t="n">
-        <v>499.95</v>
+        <v>119.81</v>
       </c>
       <c r="D201" s="4" t="n">
-        <v>38.87</v>
+        <v>39.08</v>
       </c>
       <c r="E201" s="4" t="n">
-        <v>38.28</v>
+        <v>41.38</v>
       </c>
       <c r="F201" s="4" t="n">
-        <v>40.76</v>
+        <v>44.36</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>KSB</t>
+          <t>BIRLACORPN</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -7216,22 +7216,22 @@
         </is>
       </c>
       <c r="C202" s="4" t="n">
-        <v>802.5</v>
+        <v>881.2</v>
       </c>
       <c r="D202" s="4" t="n">
-        <v>38.6</v>
+        <v>38.93</v>
       </c>
       <c r="E202" s="4" t="n">
-        <v>44.59</v>
+        <v>40.84</v>
       </c>
       <c r="F202" s="4" t="n">
-        <v>51.38</v>
+        <v>39.36</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>IIFLCAPS</t>
+          <t>TRANSRAILL</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -7240,22 +7240,22 @@
         </is>
       </c>
       <c r="C203" s="4" t="n">
-        <v>333.15</v>
+        <v>458.5</v>
       </c>
       <c r="D203" s="4" t="n">
-        <v>38.29</v>
+        <v>38.69</v>
       </c>
       <c r="E203" s="4" t="n">
-        <v>53.41</v>
+        <v>37.92</v>
       </c>
       <c r="F203" s="4" t="n">
-        <v>57.76</v>
+        <v>42.05</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>JUSTDIAL</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -7264,22 +7264,22 @@
         </is>
       </c>
       <c r="C204" s="4" t="n">
-        <v>199.01</v>
+        <v>640.5</v>
       </c>
       <c r="D204" s="4" t="n">
-        <v>37.9</v>
+        <v>38.51</v>
       </c>
       <c r="E204" s="4" t="n">
-        <v>46.54</v>
+        <v>60.8</v>
       </c>
       <c r="F204" s="4" t="n">
-        <v>42.24</v>
+        <v>47.68</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>RTNINDIA</t>
+          <t>INOXGREEN</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -7288,22 +7288,22 @@
         </is>
       </c>
       <c r="C205" s="4" t="n">
-        <v>30.03</v>
+        <v>172.18</v>
       </c>
       <c r="D205" s="4" t="n">
-        <v>37.75</v>
+        <v>38.49</v>
       </c>
       <c r="E205" s="4" t="n">
-        <v>39.65</v>
+        <v>46.8</v>
       </c>
       <c r="F205" s="4" t="n">
-        <v>39.33</v>
+        <v>51.71</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>IONEXCHANG</t>
+          <t>KNRCON</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -7312,22 +7312,22 @@
         </is>
       </c>
       <c r="C206" s="4" t="n">
-        <v>373.1</v>
+        <v>122.45</v>
       </c>
       <c r="D206" s="4" t="n">
-        <v>37.74</v>
+        <v>38.48</v>
       </c>
       <c r="E206" s="4" t="n">
-        <v>45.13</v>
+        <v>44.62</v>
       </c>
       <c r="F206" s="4" t="n">
-        <v>43.95</v>
+        <v>34.75</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>JAMNAAUTO</t>
+          <t>SURYAROSNI</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -7336,22 +7336,22 @@
         </is>
       </c>
       <c r="C207" s="4" t="n">
-        <v>121.41</v>
+        <v>220.46</v>
       </c>
       <c r="D207" s="4" t="n">
-        <v>37.64</v>
+        <v>38.45</v>
       </c>
       <c r="E207" s="4" t="n">
-        <v>46.91</v>
+        <v>41.51</v>
       </c>
       <c r="F207" s="4" t="n">
-        <v>53.55</v>
+        <v>45.57</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>VAIBHAVGBL</t>
+          <t>SWSOLAR</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -7360,22 +7360,22 @@
         </is>
       </c>
       <c r="C208" s="4" t="n">
-        <v>226.85</v>
+        <v>195.37</v>
       </c>
       <c r="D208" s="4" t="n">
-        <v>37.62</v>
+        <v>38.43</v>
       </c>
       <c r="E208" s="4" t="n">
-        <v>47.76</v>
+        <v>43.91</v>
       </c>
       <c r="F208" s="4" t="n">
-        <v>46.27</v>
+        <v>40.51</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>KSCL</t>
+          <t>KSB</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -7384,22 +7384,22 @@
         </is>
       </c>
       <c r="C209" s="4" t="n">
-        <v>773.4</v>
+        <v>793.85</v>
       </c>
       <c r="D209" s="4" t="n">
-        <v>37.58</v>
+        <v>38.03</v>
       </c>
       <c r="E209" s="4" t="n">
-        <v>36.7</v>
+        <v>43.61</v>
       </c>
       <c r="F209" s="4" t="n">
-        <v>42.57</v>
+        <v>50.95</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>SAMHI</t>
+          <t>RALLIS</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -7408,22 +7408,22 @@
         </is>
       </c>
       <c r="C210" s="4" t="n">
-        <v>159.56</v>
+        <v>210.24</v>
       </c>
       <c r="D210" s="4" t="n">
-        <v>37.43</v>
+        <v>37.97</v>
       </c>
       <c r="E210" s="4" t="n">
-        <v>44.74</v>
+        <v>33.67</v>
       </c>
       <c r="F210" s="4" t="n">
-        <v>45.63</v>
+        <v>42.06</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>ROUTE</t>
+          <t>KITEX</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -7432,22 +7432,22 @@
         </is>
       </c>
       <c r="C211" s="4" t="n">
-        <v>502.3</v>
+        <v>129.86</v>
       </c>
       <c r="D211" s="4" t="n">
-        <v>37.4</v>
+        <v>37.62</v>
       </c>
       <c r="E211" s="4" t="n">
-        <v>40.86</v>
+        <v>34.67</v>
       </c>
       <c r="F211" s="4" t="n">
-        <v>30.3</v>
+        <v>43.52</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>IXIGO</t>
+          <t>JAMNAAUTO</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -7456,22 +7456,22 @@
         </is>
       </c>
       <c r="C212" s="4" t="n">
-        <v>170.3</v>
+        <v>119.88</v>
       </c>
       <c r="D212" s="4" t="n">
-        <v>37.36</v>
+        <v>37.56</v>
       </c>
       <c r="E212" s="4" t="n">
-        <v>43.5</v>
+        <v>46.57</v>
       </c>
       <c r="F212" s="4" t="n">
-        <v>44.37</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>RELIGARE</t>
+          <t>JKLAKSHMI</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -7480,22 +7480,22 @@
         </is>
       </c>
       <c r="C213" s="4" t="n">
-        <v>231.65</v>
+        <v>544.2</v>
       </c>
       <c r="D213" s="4" t="n">
-        <v>37.32</v>
+        <v>36.84</v>
       </c>
       <c r="E213" s="4" t="n">
-        <v>45.45</v>
+        <v>33.9</v>
       </c>
       <c r="F213" s="4" t="n">
-        <v>49.69</v>
+        <v>38.16</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>HEMIPROP</t>
+          <t>SHAKTIPUMP</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -7504,22 +7504,22 @@
         </is>
       </c>
       <c r="C214" s="4" t="n">
-        <v>130.58</v>
+        <v>493.55</v>
       </c>
       <c r="D214" s="4" t="n">
-        <v>37.27</v>
+        <v>36.82</v>
       </c>
       <c r="E214" s="4" t="n">
-        <v>44.34</v>
+        <v>37.33</v>
       </c>
       <c r="F214" s="4" t="n">
-        <v>46.57</v>
+        <v>43.89</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>NFL</t>
+          <t>VAIBHAVGBL</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -7528,22 +7528,22 @@
         </is>
       </c>
       <c r="C215" s="4" t="n">
-        <v>70.3</v>
+        <v>222.2</v>
       </c>
       <c r="D215" s="4" t="n">
-        <v>37.15</v>
+        <v>36.8</v>
       </c>
       <c r="E215" s="4" t="n">
-        <v>38.52</v>
+        <v>46.22</v>
       </c>
       <c r="F215" s="4" t="n">
-        <v>42.39</v>
+        <v>45.68</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>GREAVESCOT</t>
+          <t>RTNPOWER</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -7552,22 +7552,22 @@
         </is>
       </c>
       <c r="C216" s="4" t="n">
-        <v>192.48</v>
+        <v>7.95</v>
       </c>
       <c r="D216" s="4" t="n">
-        <v>36.92</v>
+        <v>36.56</v>
       </c>
       <c r="E216" s="4" t="n">
-        <v>48.9</v>
+        <v>35.68</v>
       </c>
       <c r="F216" s="4" t="n">
-        <v>51.2</v>
+        <v>43</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>CMSINFO</t>
+          <t>GMRP&amp;UI</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -7576,22 +7576,22 @@
         </is>
       </c>
       <c r="C217" s="4" t="n">
-        <v>247</v>
+        <v>93.34999999999999</v>
       </c>
       <c r="D217" s="4" t="n">
-        <v>36.84</v>
+        <v>36.55</v>
       </c>
       <c r="E217" s="4" t="n">
-        <v>31.71</v>
+        <v>37.47</v>
       </c>
       <c r="F217" s="4" t="n">
-        <v>33.23</v>
+        <v>47.96</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>TRANSRAILL</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -7600,22 +7600,22 @@
         </is>
       </c>
       <c r="C218" s="4" t="n">
-        <v>459.85</v>
+        <v>483.95</v>
       </c>
       <c r="D218" s="4" t="n">
-        <v>36.6</v>
+        <v>36.49</v>
       </c>
       <c r="E218" s="4" t="n">
-        <v>39.04</v>
+        <v>35.91</v>
       </c>
       <c r="F218" s="4" t="n">
-        <v>42.51</v>
+        <v>39.68</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>HGINFRA</t>
+          <t>ASHAPURMIN</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -7624,22 +7624,22 @@
         </is>
       </c>
       <c r="C219" s="4" t="n">
-        <v>513.7</v>
+        <v>582.1</v>
       </c>
       <c r="D219" s="4" t="n">
-        <v>36.46</v>
+        <v>36.44</v>
       </c>
       <c r="E219" s="4" t="n">
-        <v>35.66</v>
+        <v>42.61</v>
       </c>
       <c r="F219" s="4" t="n">
-        <v>34.77</v>
+        <v>52.59</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>CCAVENUE</t>
+          <t>AWFIS</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -7648,22 +7648,22 @@
         </is>
       </c>
       <c r="C220" s="4" t="n">
-        <v>14.95</v>
+        <v>257.65</v>
       </c>
       <c r="D220" s="4" t="n">
-        <v>36.41</v>
+        <v>36.36</v>
       </c>
       <c r="E220" s="4" t="n">
-        <v>47.14</v>
+        <v>31.4</v>
       </c>
       <c r="F220" s="4" t="n">
-        <v>42.53</v>
+        <v>29.3</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>JSLL</t>
+          <t>TARC</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -7672,22 +7672,22 @@
         </is>
       </c>
       <c r="C221" s="4" t="n">
-        <v>506.2</v>
+        <v>117.9</v>
       </c>
       <c r="D221" s="4" t="n">
-        <v>36.36</v>
+        <v>35.54</v>
       </c>
       <c r="E221" s="4" t="n">
-        <v>37.84</v>
+        <v>39.59</v>
       </c>
       <c r="F221" s="4" t="n">
-        <v>40.57</v>
+        <v>43.96</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>BORORENEW</t>
+          <t>TARC</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -7696,22 +7696,22 @@
         </is>
       </c>
       <c r="C222" s="4" t="n">
-        <v>543</v>
+        <v>117.9</v>
       </c>
       <c r="D222" s="4" t="n">
-        <v>36.17</v>
+        <v>35.54</v>
       </c>
       <c r="E222" s="4" t="n">
-        <v>50.26</v>
+        <v>39.59</v>
       </c>
       <c r="F222" s="4" t="n">
-        <v>52.25</v>
+        <v>43.96</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>TVSSCS</t>
+          <t>RAYMONDLSL</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -7720,22 +7720,22 @@
         </is>
       </c>
       <c r="C223" s="4" t="n">
-        <v>121.44</v>
+        <v>691.35</v>
       </c>
       <c r="D223" s="4" t="n">
-        <v>35.55</v>
+        <v>35.49</v>
       </c>
       <c r="E223" s="4" t="n">
-        <v>47.77</v>
+        <v>35.64</v>
       </c>
       <c r="F223" s="4" t="n">
-        <v>44.4</v>
+        <v>24.45</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>AWFIS</t>
+          <t>DATAMATICS</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -7744,22 +7744,22 @@
         </is>
       </c>
       <c r="C224" s="4" t="n">
-        <v>263</v>
+        <v>791.9</v>
       </c>
       <c r="D224" s="4" t="n">
-        <v>35.3</v>
+        <v>34.9</v>
       </c>
       <c r="E224" s="4" t="n">
-        <v>34.07</v>
+        <v>48.86</v>
       </c>
       <c r="F224" s="4" t="n">
-        <v>30.14</v>
+        <v>54.48</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>SFL</t>
+          <t>CERA</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -7768,16 +7768,16 @@
         </is>
       </c>
       <c r="C225" s="4" t="n">
-        <v>664.95</v>
+        <v>5662</v>
       </c>
       <c r="D225" s="4" t="n">
-        <v>35.28</v>
+        <v>34.76</v>
       </c>
       <c r="E225" s="4" t="n">
-        <v>50.56</v>
+        <v>47.86</v>
       </c>
       <c r="F225" s="4" t="n">
-        <v>46.31</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="226">
@@ -7792,13 +7792,13 @@
         </is>
       </c>
       <c r="C226" s="4" t="n">
-        <v>304.75</v>
+        <v>298.4</v>
       </c>
       <c r="D226" s="4" t="n">
-        <v>34.65</v>
+        <v>34.74</v>
       </c>
       <c r="E226" s="4" t="n">
-        <v>32.91</v>
+        <v>32.41</v>
       </c>
       <c r="F226" s="4" t="n">
         <v/>
@@ -7807,7 +7807,7 @@
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>AVANTIFEED</t>
+          <t>TANLA</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -7816,22 +7816,22 @@
         </is>
       </c>
       <c r="C227" s="4" t="n">
-        <v>847.5</v>
+        <v>531.5</v>
       </c>
       <c r="D227" s="4" t="n">
-        <v>34.53</v>
+        <v>34.74</v>
       </c>
       <c r="E227" s="4" t="n">
-        <v>37.71</v>
+        <v>50.75</v>
       </c>
       <c r="F227" s="4" t="n">
-        <v>51</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>SAATVIKGL</t>
+          <t>FIEMIND</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -7840,22 +7840,22 @@
         </is>
       </c>
       <c r="C228" s="4" t="n">
-        <v>401</v>
+        <v>2087.7</v>
       </c>
       <c r="D228" s="4" t="n">
-        <v>34.35</v>
+        <v>34.63</v>
       </c>
       <c r="E228" s="4" t="n">
-        <v>45.27</v>
+        <v>44.22</v>
       </c>
       <c r="F228" s="4" t="n">
-        <v/>
+        <v>59.18</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>ALOKINDS</t>
+          <t>TSFINV</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -7864,22 +7864,22 @@
         </is>
       </c>
       <c r="C229" s="4" t="n">
-        <v>11.54</v>
+        <v>404.2</v>
       </c>
       <c r="D229" s="4" t="n">
-        <v>34.26</v>
+        <v>34.54</v>
       </c>
       <c r="E229" s="4" t="n">
-        <v>35.9</v>
+        <v>46.51</v>
       </c>
       <c r="F229" s="4" t="n">
-        <v>36.31</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>EUREKAFORB</t>
+          <t>ASHOKA</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -7888,22 +7888,22 @@
         </is>
       </c>
       <c r="C230" s="4" t="n">
-        <v>416.2</v>
+        <v>112.65</v>
       </c>
       <c r="D230" s="4" t="n">
-        <v>33.66</v>
+        <v>34.35</v>
       </c>
       <c r="E230" s="4" t="n">
-        <v>36.93</v>
+        <v>34.99</v>
       </c>
       <c r="F230" s="4" t="n">
-        <v>38.09</v>
+        <v>40.79</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>ASHAPURMIN</t>
+          <t>CMSINFO</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -7912,22 +7912,22 @@
         </is>
       </c>
       <c r="C231" s="4" t="n">
-        <v>590.25</v>
+        <v>239.95</v>
       </c>
       <c r="D231" s="4" t="n">
-        <v>33.55</v>
+        <v>34.1</v>
       </c>
       <c r="E231" s="4" t="n">
-        <v>43.38</v>
+        <v>30.61</v>
       </c>
       <c r="F231" s="4" t="n">
-        <v>52.96</v>
+        <v>32.79</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>PNCINFRA</t>
+          <t>INDIASHLTR</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -7936,22 +7936,22 @@
         </is>
       </c>
       <c r="C232" s="4" t="n">
-        <v>206.76</v>
+        <v>650.3</v>
       </c>
       <c r="D232" s="4" t="n">
-        <v>33.3</v>
+        <v>33.83</v>
       </c>
       <c r="E232" s="4" t="n">
-        <v>42.15</v>
+        <v>32.36</v>
       </c>
       <c r="F232" s="4" t="n">
-        <v>40.86</v>
+        <v>39.54</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>SWSOLAR</t>
+          <t>SAMHI</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -7960,22 +7960,22 @@
         </is>
       </c>
       <c r="C233" s="4" t="n">
-        <v>196.48</v>
+        <v>156.01</v>
       </c>
       <c r="D233" s="4" t="n">
-        <v>33.12</v>
+        <v>33.34</v>
       </c>
       <c r="E233" s="4" t="n">
-        <v>42.44</v>
+        <v>42.91</v>
       </c>
       <c r="F233" s="4" t="n">
-        <v>40.25</v>
+        <v>44.83</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>WEBELSOLAR</t>
+          <t>IXIGO</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -7984,22 +7984,22 @@
         </is>
       </c>
       <c r="C234" s="4" t="n">
-        <v>82.84999999999999</v>
+        <v>163.36</v>
       </c>
       <c r="D234" s="4" t="n">
-        <v>32.85</v>
+        <v>33.23</v>
       </c>
       <c r="E234" s="4" t="n">
-        <v>40.12</v>
+        <v>41.49</v>
       </c>
       <c r="F234" s="4" t="n">
-        <v>47.21</v>
+        <v>42.85</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>WAAREERTL</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -8008,22 +8008,22 @@
         </is>
       </c>
       <c r="C235" s="4" t="n">
-        <v>767.4</v>
+        <v>874.95</v>
       </c>
       <c r="D235" s="4" t="n">
-        <v>32.45</v>
+        <v>32.87</v>
       </c>
       <c r="E235" s="4" t="n">
-        <v>62.56</v>
+        <v>40.49</v>
       </c>
       <c r="F235" s="4" t="n">
-        <v>79.01000000000001</v>
+        <v>42.05</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>SUBROS</t>
+          <t>AURIONPRO</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -8032,22 +8032,22 @@
         </is>
       </c>
       <c r="C236" s="4" t="n">
-        <v>735.55</v>
+        <v>688</v>
       </c>
       <c r="D236" s="4" t="n">
-        <v>31.96</v>
+        <v>32.49</v>
       </c>
       <c r="E236" s="4" t="n">
-        <v>43.87</v>
+        <v>36.09</v>
       </c>
       <c r="F236" s="4" t="n">
-        <v>49.82</v>
+        <v>38.64</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>AURIONPRO</t>
+          <t>ANUP</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -8056,22 +8056,22 @@
         </is>
       </c>
       <c r="C237" s="4" t="n">
-        <v>695.55</v>
+        <v>1801.3</v>
       </c>
       <c r="D237" s="4" t="n">
-        <v>31.34</v>
+        <v>32.19</v>
       </c>
       <c r="E237" s="4" t="n">
-        <v>34.52</v>
+        <v>41.28</v>
       </c>
       <c r="F237" s="4" t="n">
-        <v>38.31</v>
+        <v>45.75</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>STARCEMENT</t>
+          <t>AVANTIFEED</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -8080,22 +8080,22 @@
         </is>
       </c>
       <c r="C238" s="4" t="n">
-        <v>194.37</v>
+        <v>826.75</v>
       </c>
       <c r="D238" s="4" t="n">
-        <v>30.75</v>
+        <v>32.07</v>
       </c>
       <c r="E238" s="4" t="n">
-        <v>35.36</v>
+        <v>36.63</v>
       </c>
       <c r="F238" s="4" t="n">
-        <v>45.66</v>
+        <v>50.24</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>ANUP</t>
+          <t>RELAXO</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -8104,22 +8104,22 @@
         </is>
       </c>
       <c r="C239" s="4" t="n">
-        <v>1811.8</v>
+        <v>356.1</v>
       </c>
       <c r="D239" s="4" t="n">
-        <v>29.4</v>
+        <v>31.67</v>
       </c>
       <c r="E239" s="4" t="n">
-        <v>41.57</v>
+        <v>47.38</v>
       </c>
       <c r="F239" s="4" t="n">
-        <v>45.87</v>
+        <v>37.01</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>SURYAROSNI</t>
+          <t>MASTEK</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -8128,22 +8128,22 @@
         </is>
       </c>
       <c r="C240" s="4" t="n">
-        <v>216.03</v>
+        <v>1611.6</v>
       </c>
       <c r="D240" s="4" t="n">
-        <v>29.29</v>
+        <v>31.46</v>
       </c>
       <c r="E240" s="4" t="n">
-        <v>41.21</v>
+        <v>57.11</v>
       </c>
       <c r="F240" s="4" t="n">
-        <v>45.49</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>CRIZAC</t>
+          <t>SUBROS</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -8152,22 +8152,22 @@
         </is>
       </c>
       <c r="C241" s="4" t="n">
-        <v>171.34</v>
+        <v>728.9</v>
       </c>
       <c r="D241" s="4" t="n">
-        <v>28.39</v>
+        <v>30.57</v>
       </c>
       <c r="E241" s="4" t="n">
-        <v>33.67</v>
+        <v>43.14</v>
       </c>
       <c r="F241" s="4" t="n">
-        <v/>
+        <v>49.51</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>MOIL</t>
+          <t>SFL</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -8176,22 +8176,22 @@
         </is>
       </c>
       <c r="C242" s="4" t="n">
-        <v>252.75</v>
+        <v>636.3</v>
       </c>
       <c r="D242" s="4" t="n">
-        <v>28.26</v>
+        <v>29.65</v>
       </c>
       <c r="E242" s="4" t="n">
-        <v>34.32</v>
+        <v>46.94</v>
       </c>
       <c r="F242" s="4" t="n">
-        <v>41.5</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>STYRENIX</t>
+          <t>HGINFRA</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -8200,22 +8200,22 @@
         </is>
       </c>
       <c r="C243" s="4" t="n">
-        <v>2081.6</v>
+        <v>496.5</v>
       </c>
       <c r="D243" s="4" t="n">
-        <v>28.11</v>
+        <v>29.63</v>
       </c>
       <c r="E243" s="4" t="n">
-        <v>44.62</v>
+        <v>33.69</v>
       </c>
       <c r="F243" s="4" t="n">
-        <v>49.02</v>
+        <v>34.28</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>ASHOKA</t>
+          <t>KPIGREEN</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -8224,22 +8224,22 @@
         </is>
       </c>
       <c r="C244" s="4" t="n">
-        <v>112.07</v>
+        <v>314.25</v>
       </c>
       <c r="D244" s="4" t="n">
-        <v>27.36</v>
+        <v>29.53</v>
       </c>
       <c r="E244" s="4" t="n">
-        <v>35.94</v>
+        <v>30.34</v>
       </c>
       <c r="F244" s="4" t="n">
-        <v>41.03</v>
+        <v>42.42</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>WAAREERTL</t>
+          <t>PNCINFRA</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
@@ -8248,22 +8248,22 @@
         </is>
       </c>
       <c r="C245" s="4" t="n">
-        <v>875.3</v>
+        <v>198.34</v>
       </c>
       <c r="D245" s="4" t="n">
-        <v>27.1</v>
+        <v>28.53</v>
       </c>
       <c r="E245" s="4" t="n">
-        <v>39.96</v>
+        <v>38.4</v>
       </c>
       <c r="F245" s="4" t="n">
-        <v>41.87</v>
+        <v>39.61</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>RCF</t>
+          <t>WEBELSOLAR</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -8272,22 +8272,22 @@
         </is>
       </c>
       <c r="C246" s="4" t="n">
-        <v>118.16</v>
+        <v>77.84</v>
       </c>
       <c r="D246" s="4" t="n">
-        <v>25.84</v>
+        <v>28.28</v>
       </c>
       <c r="E246" s="4" t="n">
-        <v>39.4</v>
+        <v>37.38</v>
       </c>
       <c r="F246" s="4" t="n">
-        <v>43.86</v>
+        <v>46</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>AHLUCONT</t>
+          <t>STYRENIX</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -8296,22 +8296,22 @@
         </is>
       </c>
       <c r="C247" s="4" t="n">
-        <v>693.5</v>
+        <v>2020.8</v>
       </c>
       <c r="D247" s="4" t="n">
-        <v>25.71</v>
+        <v>25.96</v>
       </c>
       <c r="E247" s="4" t="n">
-        <v>34.01</v>
+        <v>42.32</v>
       </c>
       <c r="F247" s="4" t="n">
-        <v>43.04</v>
+        <v>47.81</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>KITEX</t>
+          <t>BORORENEW</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -8320,22 +8320,22 @@
         </is>
       </c>
       <c r="C248" s="4" t="n">
-        <v>124.73</v>
+        <v>502.25</v>
       </c>
       <c r="D248" s="4" t="n">
-        <v>23.78</v>
+        <v>25.48</v>
       </c>
       <c r="E248" s="4" t="n">
-        <v>32.29</v>
+        <v>43.72</v>
       </c>
       <c r="F248" s="4" t="n">
-        <v>42.99</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>KPIGREEN</t>
+          <t>STARCEMENT</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
@@ -8344,22 +8344,22 @@
         </is>
       </c>
       <c r="C249" s="4" t="n">
-        <v>312.6</v>
+        <v>188.68</v>
       </c>
       <c r="D249" s="4" t="n">
-        <v>23.5</v>
+        <v>23.18</v>
       </c>
       <c r="E249" s="4" t="n">
-        <v>29.79</v>
+        <v>31.69</v>
       </c>
       <c r="F249" s="4" t="n">
-        <v>42.31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>SANOFICONR</t>
+          <t>AHLUCONT</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -8368,22 +8368,22 @@
         </is>
       </c>
       <c r="C250" s="4" t="n">
-        <v>4213.1</v>
+        <v>641.1</v>
       </c>
       <c r="D250" s="4" t="n">
-        <v>23.39</v>
+        <v>23.1</v>
       </c>
       <c r="E250" s="4" t="n">
-        <v>40.18</v>
+        <v>29.91</v>
       </c>
       <c r="F250" s="4" t="n">
-        <v>41.83</v>
+        <v>41.26</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>SHARDACROP</t>
+          <t>SANOFICONR</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
@@ -8392,22 +8392,22 @@
         </is>
       </c>
       <c r="C251" s="4" t="n">
-        <v>760.9</v>
+        <v>4150</v>
       </c>
       <c r="D251" s="4" t="n">
-        <v>22.41</v>
+        <v>21.22</v>
       </c>
       <c r="E251" s="4" t="n">
-        <v>36.6</v>
+        <v>39.97</v>
       </c>
       <c r="F251" s="4" t="n">
-        <v>49.31</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>RTNPOWER</t>
+          <t>ALOKINDS</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
@@ -8416,16 +8416,16 @@
         </is>
       </c>
       <c r="C252" s="4" t="n">
-        <v>7.77</v>
+        <v>9.24</v>
       </c>
       <c r="D252" s="4" t="n">
-        <v>21.18</v>
+        <v>10.22</v>
       </c>
       <c r="E252" s="4" t="n">
-        <v>34.67</v>
+        <v>25.31</v>
       </c>
       <c r="F252" s="4" t="n">
-        <v>42.83</v>
+        <v>32.4</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Micro250_stocks.xlsx
+++ b/docs/Micro250_stocks.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L46"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -560,37 +560,37 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>1753.5</v>
+        <v>1848</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>84.83</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>77.90000000000001</v>
+        <v>78.31999999999999</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>73.34</v>
+        <v>73.73</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>48.91</v>
+        <v>59.67</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1230.59</v>
+        <v>1268.33</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>1217.4</v>
+        <v>1247.09</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>336245</v>
+        <v>364215</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>7872</v>
+        <v>7954</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>SHILPAMED</t>
+          <t>WELENT</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -599,37 +599,37 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>901.85</v>
+        <v>764.75</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>83.28</v>
+        <v>81.38</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>90.2</v>
+        <v>80.8</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>83.19</v>
+        <v>72.29000000000001</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>58.82</v>
+        <v>37.59</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>548.64</v>
+        <v>560.55</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>514.79</v>
+        <v>549.12</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>2468767</v>
+        <v>712546</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>17677</v>
+        <v>11034</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>SHILPAMED</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -638,37 +638,37 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1609.7</v>
+        <v>964.15</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>75.34</v>
+        <v>75.61</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>75.19</v>
+        <v>91.48</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>70.08</v>
+        <v>84.42</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>38.4</v>
+        <v>65.44</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>1151.43</v>
+        <v>577.8200000000001</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>1095.5</v>
+        <v>538.9400000000001</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>171023</v>
+        <v>2682728</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>10537</v>
+        <v>18857</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>YATHARTH</t>
+          <t>SMLMAH</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -677,37 +677,37 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>967.4</v>
+        <v>6298.5</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>73.98</v>
+        <v>74.97</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>67.87</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>67.09</v>
+        <v>70.19</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>27.13</v>
+        <v>42.23</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>798.29</v>
+        <v>4309.57</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>775.11</v>
+        <v>4120.15</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>386755</v>
+        <v>258334</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>9321</v>
+        <v>9115</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>YATHARTH</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -716,37 +716,37 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>723.75</v>
+        <v>991.1</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>72.51000000000001</v>
+        <v>69.45</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>76.31999999999999</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>85.97</v>
+        <v>67.44</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>23.36</v>
+        <v>38.89</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>441.75</v>
+        <v>809.95</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>390.7</v>
+        <v>785</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>2045777</v>
+        <v>420012</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>37194</v>
+        <v>9550</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>WELENT</t>
+          <t>INOXINDIA</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>676.6</v>
+        <v>2247.8</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>71.12</v>
+        <v>68.72</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>70.64</v>
+        <v>81.16</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>65.53</v>
+        <v>84.14</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>30.02</v>
+        <v>24.97</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>549.99</v>
+        <v>1678.37</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>540.8</v>
+        <v>1592.65</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>546968</v>
+        <v>359311</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>9090</v>
+        <v>20438</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>MANORAMA</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -794,37 +794,37 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1696.8</v>
+        <v>1993.4</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>68.45999999999999</v>
+        <v>67.91</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>78.25</v>
+        <v>74.92</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>80.34</v>
+        <v>72.23</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>53.24</v>
+        <v>45.96</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1270.35</v>
+        <v>1559.38</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1203.23</v>
+        <v>1514.17</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>333777</v>
+        <v>748025</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>22521</v>
+        <v>12583</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>KRBL</t>
+          <t>EDELWEISS</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -833,37 +833,37 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>437.65</v>
+        <v>136.08</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>68.29000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>68.97</v>
+        <v>64.31</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>59.72</v>
+        <v>63.63</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>44.55</v>
+        <v>31.37</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>367.18</v>
+        <v>117.58</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>364.58</v>
+        <v>116.09</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>829341</v>
+        <v>5147406</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>10017</v>
+        <v>12880</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>VARROC</t>
+          <t>BALAMINES</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -872,37 +872,37 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>813.15</v>
+        <v>2525.2</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>67.64</v>
+        <v>67.7</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>74.90000000000001</v>
+        <v>71.37</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>69.06</v>
+        <v>66.02</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>51.82</v>
+        <v>24.02</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>636.84</v>
+        <v>1847.19</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>620.62</v>
+        <v>1762.27</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>832542</v>
+        <v>258032</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>12558</v>
+        <v>8182</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>TMB</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>567.2</v>
+        <v>942.45</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>67.41</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>70.98999999999999</v>
+        <v>74.83</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>67.28</v>
+        <v>78.70999999999999</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>39.13</v>
+        <v>40.12</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>466.44</v>
+        <v>734.73</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>457.41</v>
+        <v>697.23</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1201817</v>
+        <v>528048</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>14020</v>
+        <v>14765</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -950,37 +950,37 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>329.7</v>
+        <v>220.74</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>67.39</v>
+        <v>67.28</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>74.62</v>
+        <v>71.44</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>67.61</v>
+        <v>67.03</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>45.16</v>
+        <v>37.61</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>240.77</v>
+        <v>184.74</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>232.65</v>
+        <v>179.88</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>4429364</v>
+        <v>2838957</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>14941</v>
+        <v>7112</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -989,37 +989,37 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2231.7</v>
+        <v>340.1</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>67.13</v>
+        <v>67.16</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>83.47</v>
+        <v>80.31</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>81.91</v>
+        <v>77.17</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>47.05</v>
+        <v>46.01</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1515.61</v>
+        <v>266.53</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1411.46</v>
+        <v>255.04</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>492169</v>
+        <v>3418019</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>14910</v>
+        <v>12862</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>MSTCLTD</t>
+          <t>ALIVUS</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1028,37 +1028,37 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>722.25</v>
+        <v>1418.8</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>66.14</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>66.56999999999999</v>
+        <v>74.39</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>60.67</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>30.17</v>
+        <v>46.42</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>559.76</v>
+        <v>1127.73</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>546.95</v>
+        <v>1097.39</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>352859</v>
+        <v>205062</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>5137</v>
+        <v>16774</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1067,37 +1067,37 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>212.97</v>
+        <v>368.65</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>65.76000000000001</v>
+        <v>65.95</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>68.55</v>
+        <v>72.63</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>65.69</v>
+        <v>67</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>29.37</v>
+        <v>32.11</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>182.21</v>
+        <v>303.31</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>177.75</v>
+        <v>296.51</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2623902</v>
+        <v>2919161</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>6859</v>
+        <v>14182</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>AZAD</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1106,37 +1106,37 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2802.4</v>
+        <v>1578.7</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>64.17</v>
+        <v>65.34</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>70.89</v>
+        <v>72.5</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>72.84</v>
+        <v>69.58</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>28.99</v>
+        <v>43.28</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2129.07</v>
+        <v>1176.5</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2038.85</v>
+        <v>1117.18</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>609227</v>
+        <v>208995</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>18409</v>
+        <v>10334</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>MANORAMA</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1145,37 +1145,37 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1887.2</v>
+        <v>713.25</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>63.99</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>71.56</v>
+        <v>77.5</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>70.41</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>44.56</v>
+        <v>24.86</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1531.15</v>
+        <v>455.8</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1490.56</v>
+        <v>403.29</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>688369</v>
+        <v>1920425</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>11926</v>
+        <v>38487</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>RBA</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1184,37 +1184,37 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>100.97</v>
+        <v>596.7</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>63.32</v>
+        <v>65.02</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>73.09</v>
+        <v>69.04000000000001</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>60.04</v>
+        <v>57.67</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>61.53</v>
+        <v>38.36</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>75.33</v>
+        <v>517.24</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>74.34999999999999</v>
+        <v>512.46</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>16851452</v>
+        <v>622145</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>7190</v>
+        <v>8768</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>TMB</t>
+          <t>AKUMS</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1223,37 +1223,37 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>893.85</v>
+        <v>780.55</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>63.25</v>
+        <v>64.91</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>71.37</v>
+        <v>73.13</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>77.13</v>
+        <v>64.22</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>35.03</v>
+        <v>46.98</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>722.28</v>
+        <v>608.1799999999999</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>686.0599999999999</v>
+        <v>588.76</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>509869</v>
+        <v>391183</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>14031</v>
+        <v>11724</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>JKPAPER</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1262,37 +1262,37 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>354.5</v>
+        <v>410.15</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>62.89</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>75.8</v>
+        <v>63.93</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>68.14</v>
+        <v>56.05</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>34.98</v>
+        <v>41.5</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>297.83</v>
+        <v>367.15</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>292.02</v>
+        <v>365.74</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2803525</v>
+        <v>521219</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>14411</v>
+        <v>7358</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>SKYGOLD</t>
+          <t>MSTCLTD</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1301,37 +1301,37 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>811.4</v>
+        <v>744.25</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>62.59</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>81.81</v>
+        <v>66.89</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>81.84</v>
+        <v>60.42</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>51.3</v>
+        <v>34.87</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>542.38</v>
+        <v>570.88</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>504.87</v>
+        <v>555.66</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1262985</v>
+        <v>341892</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>12566</v>
+        <v>5169</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>QUESS</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1340,37 +1340,37 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>327.15</v>
+        <v>366.55</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>62.54</v>
+        <v>63.19</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>78.56</v>
+        <v>72.03</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>76.16</v>
+        <v>51.8</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>46.43</v>
+        <v>51.08</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>260.87</v>
+        <v>269.03</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>250.13</v>
+        <v>268.97</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>3378401</v>
+        <v>1387631</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>12493</v>
+        <v>5299</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GOKULAGRO</t>
+          <t>SUDARSCHEM</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1379,37 +1379,37 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>244.48</v>
+        <v>1222.8</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>62.53</v>
+        <v>61.61</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>66.18000000000001</v>
+        <v>66.95999999999999</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>67.64</v>
+        <v>59.49</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>40.51</v>
+        <v>35.25</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>211.79</v>
+        <v>1013.14</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>205.06</v>
+        <v>1012.06</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>763770</v>
+        <v>564062</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>7210</v>
+        <v>9734</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1418,37 +1418,37 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>752.7</v>
+        <v>326.75</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>62.49</v>
+        <v>61.53</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>71.04000000000001</v>
+        <v>73.34</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>78.59</v>
+        <v>67.39</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>31.74</v>
+        <v>42.84</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>556.85</v>
+        <v>246.37</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>520.21</v>
+        <v>237.4</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>3124217</v>
+        <v>4601759</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>23519</v>
+        <v>14807</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>AKUMS</t>
+          <t>KRBL</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1457,37 +1457,37 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>761.2</v>
+        <v>424.9</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>62.36</v>
+        <v>61.17</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>74.65000000000001</v>
+        <v>63.41</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>65.22</v>
+        <v>58.4</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>45.25</v>
+        <v>47.02</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>596.6</v>
+        <v>370.13</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>579.0599999999999</v>
+        <v>366.95</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>362397</v>
+        <v>864219</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>11829</v>
+        <v>9658</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>ALIVUS</t>
+          <t>LUMAXTECH</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1496,37 +1496,37 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1358.2</v>
+        <v>1985.4</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>61.9</v>
+        <v>59.5</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>73.26000000000001</v>
+        <v>63.55</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>72.15000000000001</v>
+        <v>68.02</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>44.63</v>
+        <v>40.33</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1112.48</v>
+        <v>1634.69</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1085.22</v>
+        <v>1568.8</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>131141</v>
+        <v>383013</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>16577</v>
+        <v>13304</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>ALKYLAMINE</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1535,37 +1535,37 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2045</v>
+        <v>1654.7</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>61.48</v>
+        <v>58.89</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>68.38</v>
+        <v>70.88</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>55.11</v>
+        <v>75.69</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>31.14</v>
+        <v>48.41</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1757</v>
+        <v>1291.1</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1749.12</v>
+        <v>1221.79</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>139727</v>
+        <v>340810</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>10474</v>
+        <v>21576</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>SANSERA</t>
+          <t>VARROC</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1574,37 +1574,37 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3859</v>
+        <v>826.35</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>60.98</v>
+        <v>58.04</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>80.12</v>
+        <v>75.22</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>84.04000000000001</v>
+        <v>67.31</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>34.72</v>
+        <v>49.63</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2857.27</v>
+        <v>652.6</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2655.28</v>
+        <v>633.5599999999999</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>257763</v>
+        <v>901764</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>24082</v>
+        <v>12627</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>DIACABS</t>
+          <t>AZAD</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1613,37 +1613,37 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>349.4</v>
+        <v>2766.9</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>60.7</v>
+        <v>57.78</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>80.68000000000001</v>
+        <v>67.7</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>80.66</v>
+        <v>70.53</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>42.66</v>
+        <v>30.45</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>226.53</v>
+        <v>2173.66</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>209.67</v>
+        <v>2076.74</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4911830</v>
+        <v>582230</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>20897</v>
+        <v>17936</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>LUMAXTECH</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1652,37 +1652,37 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1930.6</v>
+        <v>2196.6</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>60.65</v>
+        <v>56.96</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>65.48999999999999</v>
+        <v>80.55</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>71.08</v>
+        <v>76.18000000000001</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>42.72</v>
+        <v>44.89</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1608.23</v>
+        <v>1563.87</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>1545.87</v>
+        <v>1452.96</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>361003</v>
+        <v>544738</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>13533</v>
+        <v>14691</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>PRICOLLTD</t>
+          <t>TDPOWERSYS</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1691,37 +1691,37 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>770.65</v>
+        <v>740.1</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>59.47</v>
+        <v>56.65</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>69.98999999999999</v>
+        <v>68.94</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>69.59</v>
+        <v>75.19</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>44.24</v>
+        <v>31.03</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>629.88</v>
+        <v>569.0700000000001</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>612.2</v>
+        <v>531.25</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>639908</v>
+        <v>3249124</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>9393</v>
+        <v>23125</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>EMIL</t>
+          <t>RBA</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1730,37 +1730,37 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>177.35</v>
+        <v>97.89</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>59.21</v>
+        <v>56.54</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>69.7</v>
+        <v>68.2</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>59.85</v>
+        <v>58.43</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>44.99</v>
+        <v>54.66</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>131.65</v>
+        <v>76.52</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>129.67</v>
+        <v>75.25</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>10335654</v>
+        <v>16847552</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>6824</v>
+        <v>6918</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>ALKYLAMINE</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1769,37 +1769,37 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>580.05</v>
+        <v>2003.2</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>59.02</v>
+        <v>55.24</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>66.48999999999999</v>
+        <v>66.03</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>56.23</v>
+        <v>54.57</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>36.59</v>
+        <v>26.86</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>512.72</v>
+        <v>1773.26</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>508.74</v>
+        <v>1762.14</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>538210</v>
+        <v>145029</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>8523</v>
+        <v>10336</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>INDIAGLYCO</t>
+          <t>ICIL</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1808,31 +1808,31 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>1178.3</v>
+        <v>437.35</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>58.32</v>
+        <v>54.03</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>62.59</v>
+        <v>65.95999999999999</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>65.5</v>
+        <v>63.63</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>31.16</v>
+        <v>30.88</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1028.57</v>
+        <v>354.92</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>1003.32</v>
+        <v>341.91</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>256406</v>
+        <v>1553756</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>7898</v>
+        <v>8908</v>
       </c>
     </row>
     <row r="35">
@@ -1847,37 +1847,37 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1439.7</v>
+        <v>1411.5</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>58.2</v>
+        <v>53.96</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>69.18000000000001</v>
+        <v>67.41</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>70.39</v>
+        <v>69.37</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>40.19</v>
+        <v>34.51</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1042.41</v>
+        <v>1061.48</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>983.27</v>
+        <v>1000.04</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>1375690</v>
+        <v>1365832</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>11602</v>
+        <v>11402</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>NEOGEN</t>
+          <t>SHAILY</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1886,37 +1886,37 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>2230.2</v>
+        <v>3267.1</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>56.64</v>
+        <v>53.82</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>67.52</v>
+        <v>66.7</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>63.33</v>
+        <v>73.51000000000001</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>25.77</v>
+        <v>33.64</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>1811.88</v>
+        <v>2751.03</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>1747.16</v>
+        <v>2627.96</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>204790</v>
+        <v>176648</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>6051</v>
+        <v>15079</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>EPL</t>
+          <t>EMIL</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1925,37 +1925,37 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>251.94</v>
+        <v>173.74</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>56.12</v>
+        <v>53.35</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>60.23</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>59.79</v>
+        <v>58.58</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>31.94</v>
+        <v>35.69</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>227.46</v>
+        <v>134.53</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>225.17</v>
+        <v>131.89</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>1732350</v>
+        <v>10407286</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>8070</v>
+        <v>6685</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>SMLMAH</t>
+          <t>SANSERA</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1964,37 +1964,37 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>5194</v>
+        <v>3789.6</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>56.04</v>
+        <v>52.95</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>61.57</v>
+        <v>76.17</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>65.5</v>
+        <v>78.48</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>37.93</v>
+        <v>33.87</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>4209.03</v>
+        <v>2910.22</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>4033.87</v>
+        <v>2702.65</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>239572</v>
+        <v>222486</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>7506</v>
+        <v>23605</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>SHAILY</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -2003,37 +2003,37 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>3270.4</v>
+        <v>618.85</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>54.92</v>
+        <v>52.92</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>66.52</v>
+        <v>70.84</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>73.44</v>
+        <v>65.84</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>38.26</v>
+        <v>50.13</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>2723.96</v>
+        <v>506.96</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>2602.53</v>
+        <v>496.01</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>191946</v>
+        <v>1301938</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>15042</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>HCG</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -2042,37 +2042,37 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>606.05</v>
+        <v>703.45</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>53.7</v>
+        <v>50.51</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>74.73999999999999</v>
+        <v>62.12</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>69.86</v>
+        <v>62.54</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>56.48</v>
+        <v>29.13</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>496.42</v>
+        <v>649.2</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>487.58</v>
+        <v>640.54</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>1307171</v>
+        <v>169316</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>12481</v>
+        <v>10454</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>ICIL</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -2081,31 +2081,31 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>423.4</v>
+        <v>535.1</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>53.53</v>
+        <v>49.87</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>64.16</v>
+        <v>62.2</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>63.81</v>
+        <v>63.54</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>26.89</v>
+        <v>31.19</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>348.75</v>
+        <v>471.7</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>336.67</v>
+        <v>461.98</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>1405152</v>
+        <v>1248527</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>8614</v>
+        <v>13226</v>
       </c>
     </row>
     <row r="42">
@@ -2120,37 +2120,37 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>2294.8</v>
+        <v>2278.3</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>53.28</v>
+        <v>48.9</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>66.93000000000001</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>74.29000000000001</v>
+        <v>69.62</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>39.34</v>
+        <v>37.23</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>1845.18</v>
+        <v>1883.79</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>1767.03</v>
+        <v>1800.42</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>165327</v>
+        <v>166690</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>10690</v>
+        <v>10524</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>OPTIEMUS</t>
+          <t>NEOGEN</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -2159,37 +2159,37 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>576.45</v>
+        <v>2137.1</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>52.28</v>
+        <v>48.59</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>60.18</v>
+        <v>63.13</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>55.38</v>
+        <v>61.41</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>26.03</v>
+        <v>24.88</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>501.84</v>
+        <v>1834.74</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>501.59</v>
+        <v>1767.37</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>298049</v>
+        <v>205236</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>5226</v>
+        <v>5854</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>HCG</t>
+          <t>THYROCARE</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -2198,37 +2198,37 @@
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>699.95</v>
+        <v>578.65</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>50.13</v>
+        <v>47.55</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>61.45</v>
+        <v>61.22</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>64.20999999999999</v>
+        <v>66.92</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>26.89</v>
+        <v>20.45</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>645.17</v>
+        <v>506.56</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>637.02</v>
+        <v>485.76</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>166036</v>
+        <v>792028</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>10396</v>
+        <v>9170</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>THYROCARE</t>
+          <t>SKYGOLD</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -2237,70 +2237,31 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>581.45</v>
+        <v>742</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>48.47</v>
+        <v>47.17</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>62.85</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>69.48999999999999</v>
+        <v>78.78</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>24.86</v>
+        <v>42.12</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>501.03</v>
+        <v>554.22</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>480.61</v>
+        <v>515.42</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>1228794</v>
+        <v>1227001</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>9301</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>RATEGAIN</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="n">
-        <v>918.25</v>
-      </c>
-      <c r="D46" s="4" t="n">
-        <v>47.4</v>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>66.09999999999999</v>
-      </c>
-      <c r="F46" s="4" t="n">
-        <v>66.39</v>
-      </c>
-      <c r="G46" s="4" t="n">
-        <v>25.88</v>
-      </c>
-      <c r="H46" s="4" t="n">
-        <v>775.85</v>
-      </c>
-      <c r="I46" s="4" t="n">
-        <v>742.63</v>
-      </c>
-      <c r="J46" s="4" t="n">
-        <v>537541</v>
-      </c>
-      <c r="K46" s="4" t="n">
-        <v>11058</v>
+        <v>12103</v>
       </c>
     </row>
   </sheetData>
@@ -2349,7 +2310,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId45"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2416,22 +2376,22 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>1753.5</v>
+        <v>1848</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>84.83</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>77.90000000000001</v>
+        <v>78.31999999999999</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>73.34</v>
+        <v>73.73</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>SHILPAMED</t>
+          <t>SUDEEPPHRM</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2440,22 +2400,22 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>901.85</v>
+        <v>1329.3</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>83.28</v>
+        <v>85.39</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>90.2</v>
+        <v>84.05</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>83.19</v>
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>BALUFORGE</t>
+          <t>MANYAVAR</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2464,22 +2424,22 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>632.9</v>
+        <v>594.2</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>76.41</v>
+        <v>82.58</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>69.98</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>56.16</v>
+        <v>43.79</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>ELECTCAST</t>
+          <t>WELENT</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2488,22 +2448,22 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>81.5</v>
+        <v>764.75</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>75.65000000000001</v>
+        <v>81.38</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>56.03</v>
+        <v>80.8</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>45.77</v>
+        <v>72.29000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>GMMPFAUDLR</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2512,22 +2472,22 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1609.7</v>
+        <v>1147.9</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>75.34</v>
+        <v>79.2</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>75.19</v>
+        <v>70.2</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>70.08</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>GPPL</t>
+          <t>MAHSEAMLES</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2536,22 +2496,22 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>168.75</v>
+        <v>688.1</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>74.42</v>
+        <v>76.53</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>61.8</v>
+        <v>70.42</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>54.96</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>YATHARTH</t>
+          <t>SHILPAMED</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2560,22 +2520,22 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>967.4</v>
+        <v>964.15</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>73.98</v>
+        <v>75.61</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>67.87</v>
+        <v>91.48</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>67.09</v>
+        <v>84.42</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MANYAVAR</t>
+          <t>SMLMAH</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2584,22 +2544,22 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>544.55</v>
+        <v>6298.5</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>73.95999999999999</v>
+        <v>74.97</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>67.95</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>40.37</v>
+        <v>70.19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>SUDEEPPHRM</t>
+          <t>ELECTCAST</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2608,22 +2568,22 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1152.1</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>73.2</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>78.93000000000001</v>
+        <v>58.17</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v/>
+        <v>46.62</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>SKFINDUS</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2632,22 +2592,22 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>723.75</v>
+        <v>3062.8</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>72.51000000000001</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>76.31999999999999</v>
+        <v>67.97</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>85.97</v>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SUDARSCHEM</t>
+          <t>QPOWER</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2656,22 +2616,22 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1252.8</v>
+        <v>1495.3</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>72.48999999999999</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>70.75</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>61.22</v>
+        <v>69.56</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>QUESS</t>
+          <t>GODREJAGRO</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -2680,22 +2640,22 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>372.25</v>
+        <v>658.95</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>71.47</v>
+        <v>69.47</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>78.95</v>
+        <v>64.89</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>53.88</v>
+        <v>52.89</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>INOXINDIA</t>
+          <t>YATHARTH</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -2704,22 +2664,22 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2177.9</v>
+        <v>991.1</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>71.23</v>
+        <v>69.45</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>78.2</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>82.56999999999999</v>
+        <v>67.44</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>WELENT</t>
+          <t>INOXINDIA</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -2728,22 +2688,22 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>676.6</v>
+        <v>2247.8</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>71.12</v>
+        <v>68.72</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>70.64</v>
+        <v>81.16</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>65.53</v>
+        <v>84.14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>MAHSEAMLES</t>
+          <t>PCJEWELLER</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -2752,22 +2712,22 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>642.05</v>
+        <v>11.86</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>68.95999999999999</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>64.67</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>54.62</v>
+        <v>55.33</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>SMARTWORKS</t>
+          <t>MANORAMA</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -2776,22 +2736,22 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>540.6</v>
+        <v>1993.4</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>68.62</v>
+        <v>67.91</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>65.94</v>
+        <v>74.92</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v/>
+        <v>72.23</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>EDELWEISS</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -2800,22 +2760,22 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1696.8</v>
+        <v>136.08</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>68.45999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>78.25</v>
+        <v>64.31</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>80.34</v>
+        <v>63.63</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>KRBL</t>
+          <t>BALAMINES</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2824,22 +2784,22 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>437.65</v>
+        <v>2525.2</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>68.29000000000001</v>
+        <v>67.7</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>68.97</v>
+        <v>71.37</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>59.72</v>
+        <v>66.02</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>HCC</t>
+          <t>TMB</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -2848,22 +2808,22 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>24.64</v>
+        <v>942.45</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>67.77</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>57.66</v>
+        <v>74.83</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>49.18</v>
+        <v>78.70999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GMMPFAUDLR</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -2872,22 +2832,22 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1025.15</v>
+        <v>220.74</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>67.64</v>
+        <v>67.28</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>62.43</v>
+        <v>71.44</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>47.75</v>
+        <v>67.03</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>VARROC</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -2896,22 +2856,22 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>813.15</v>
+        <v>340.1</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>67.64</v>
+        <v>67.16</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>74.90000000000001</v>
+        <v>80.31</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>69.06</v>
+        <v>77.17</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>PRUDENT</t>
+          <t>ALIVUS</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -2920,22 +2880,22 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>3473.5</v>
+        <v>1418.8</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>67.53</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>69.04000000000001</v>
+        <v>74.39</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>66.41</v>
+        <v>70.98999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -2944,22 +2904,22 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>567.2</v>
+        <v>368.65</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>67.41</v>
+        <v>65.95</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>70.98999999999999</v>
+        <v>72.63</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>67.28</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>RATNAMANI</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -2968,22 +2928,22 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>329.7</v>
+        <v>2727</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>67.39</v>
+        <v>65.8</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>74.62</v>
+        <v>57.86</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>67.61</v>
+        <v>53.14</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>WAKEFIT</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -2992,22 +2952,22 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2231.7</v>
+        <v>149.64</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>67.13</v>
+        <v>65.45</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>83.47</v>
+        <v>55.6</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>81.91</v>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>BALAMINES</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -3016,22 +2976,22 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2425.8</v>
+        <v>1578.7</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>66.95999999999999</v>
+        <v>65.34</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>68.73</v>
+        <v>72.5</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>64.06</v>
+        <v>69.58</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>MSTCLTD</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -3040,22 +3000,22 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>722.25</v>
+        <v>713.25</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>66.14</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>66.56999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>60.67</v>
+        <v>86.48999999999999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3064,22 +3024,22 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>212.97</v>
+        <v>596.7</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>65.76000000000001</v>
+        <v>65.02</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>68.55</v>
+        <v>69.04000000000001</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>65.69</v>
+        <v>57.67</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>QPOWER</t>
+          <t>TEXRAIL</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -3088,22 +3048,22 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1363.1</v>
+        <v>115.99</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>65.68000000000001</v>
+        <v>65</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>65.7</v>
+        <v>54.94</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>68.45</v>
+        <v>46.09</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>HERITGFOOD</t>
+          <t>AKUMS</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -3112,22 +3072,22 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>378.15</v>
+        <v>780.55</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>65.34</v>
+        <v>64.91</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>56.45</v>
+        <v>73.13</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>49.21</v>
+        <v>64.22</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>VOLTAMP</t>
+          <t>SKIPPER</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -3136,22 +3096,22 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>11038.5</v>
+        <v>591.1</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>65.26000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>64.93000000000001</v>
+        <v>67.53</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>59.19</v>
+        <v>64.61</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>PCJEWELLER</t>
+          <t>JKPAPER</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -3160,22 +3120,22 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>10.94</v>
+        <v>410.15</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>64.89</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>59.92</v>
+        <v>63.93</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>52.81</v>
+        <v>56.05</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>WAKEFIT</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -3184,22 +3144,22 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>144.71</v>
+        <v>868.1</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>64.54000000000001</v>
+        <v>64.5</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>52.02</v>
+        <v>64.91</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v/>
+        <v>59.58</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>AZAD</t>
+          <t>VOLTAMP</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -3208,22 +3168,22 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>2802.4</v>
+        <v>11182</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>64.17</v>
+        <v>64.31999999999999</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>70.89</v>
+        <v>67.45</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>72.84</v>
+        <v>60.39</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>SKFINDUS</t>
+          <t>MSTCLTD</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -3232,22 +3192,22 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>2891.6</v>
+        <v>744.25</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>64.06</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>66.61</v>
+        <v>66.89</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v/>
+        <v>60.42</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GODREJAGRO</t>
+          <t>RELIGARE</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -3256,22 +3216,22 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>614.75</v>
+        <v>257.08</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>64</v>
+        <v>64.22</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>58.72</v>
+        <v>56.69</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>50</v>
+        <v>54.73</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>MANORAMA</t>
+          <t>INDIGOPNTS</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -3280,22 +3240,22 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>1887.2</v>
+        <v>1185.8</v>
       </c>
       <c r="D38" s="4" t="n">
         <v>63.99</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>71.56</v>
+        <v>68.45999999999999</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>70.41</v>
+        <v>51.75</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>RUBICON</t>
+          <t>AXISCADES</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -3304,22 +3264,22 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>1804.4</v>
+        <v>1730.4</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>63.69</v>
+        <v>63.93</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>86.79000000000001</v>
+        <v>53.24</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v/>
+        <v>61.8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>RBA</t>
+          <t>IONEXCHANG</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -3328,22 +3288,22 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>100.97</v>
+        <v>409.2</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>63.32</v>
+        <v>63.45</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>73.09</v>
+        <v>54.14</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>60.04</v>
+        <v>48.37</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>TMB</t>
+          <t>QUESS</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -3352,22 +3312,22 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>893.85</v>
+        <v>366.55</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>63.25</v>
+        <v>63.19</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>71.37</v>
+        <v>72.03</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>77.13</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>CUPID</t>
+          <t>STAR</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -3376,22 +3336,22 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>282.33</v>
+        <v>1059.6</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>62.91</v>
+        <v>62.81</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>86.75</v>
+        <v>55.24</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>93.09</v>
+        <v>58.26</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>ATLANTAELE</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -3400,22 +3360,22 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>354.5</v>
+        <v>1881.7</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>62.89</v>
+        <v>62.38</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>75.8</v>
+        <v>62.3</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>68.14</v>
+        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>SKYGOLD</t>
+          <t>ELLEN</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -3424,22 +3384,22 @@
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>811.4</v>
+        <v>331.85</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>62.59</v>
+        <v>61.95</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>81.81</v>
+        <v>59.39</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>81.84</v>
+        <v>37.21</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>METROPOLIS</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -3448,22 +3408,22 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>327.15</v>
+        <v>591.9</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>62.54</v>
+        <v>61.81</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>78.56</v>
+        <v>62.38</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>76.16</v>
+        <v>63.42</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GOKULAGRO</t>
+          <t>SUDARSCHEM</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -3472,22 +3432,22 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>244.48</v>
+        <v>1222.8</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>62.53</v>
+        <v>61.61</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>66.18000000000001</v>
+        <v>66.95999999999999</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>67.64</v>
+        <v>59.49</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -3496,22 +3456,22 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>752.7</v>
+        <v>326.75</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>62.49</v>
+        <v>61.53</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>71.04000000000001</v>
+        <v>73.34</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>78.59</v>
+        <v>67.39</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>AKUMS</t>
+          <t>CUPID</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -3520,22 +3480,22 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>761.2</v>
+        <v>283.15</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>62.36</v>
+        <v>61.48</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>74.65000000000001</v>
+        <v>86.83</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>65.22</v>
+        <v>93.11</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>CSBBANK</t>
+          <t>SMARTWORKS</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -3544,22 +3504,22 @@
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>348.8</v>
+        <v>531.4</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>62.26</v>
+        <v>61.34</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>44.05</v>
+        <v>66.36</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>46.93</v>
+        <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>LOTUSDEV</t>
+          <t>GPPL</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -3568,22 +3528,22 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>186.21</v>
+        <v>161.62</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>62.11</v>
+        <v>61.26</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>61.35</v>
+        <v>59</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v/>
+        <v>54.22</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>ALIVUS</t>
+          <t>KRBL</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -3592,22 +3552,22 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>1358.2</v>
+        <v>424.9</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>61.9</v>
+        <v>61.17</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>73.26000000000001</v>
+        <v>63.41</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>72.15000000000001</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>ALKYLAMINE</t>
+          <t>SOUTHBANK</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -3616,22 +3576,22 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>2045</v>
+        <v>47.29</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>61.48</v>
+        <v>60.66</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>68.38</v>
+        <v>62.77</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>55.11</v>
+        <v>71.06999999999999</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>PRAJIND</t>
+          <t>HERITGFOOD</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -3640,22 +3600,22 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>354.4</v>
+        <v>382.35</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>61.47</v>
+        <v>60.26</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>51.88</v>
+        <v>59.96</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>44.37</v>
+        <v>50.68</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>ORKLAINDIA</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -3664,22 +3624,22 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>595.4</v>
+        <v>111.65</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>61.45</v>
+        <v>59.85</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>49.3</v>
+        <v>53.03</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v/>
+        <v>43.95</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>INDIGOPNTS</t>
+          <t>LUMAXTECH</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -3688,22 +3648,22 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>1170.2</v>
+        <v>1985.4</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>61.37</v>
+        <v>59.5</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>65.13</v>
+        <v>63.55</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>50.36</v>
+        <v>68.02</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>ETHOSLTD</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -3712,22 +3672,22 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>2891</v>
+        <v>562.5</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>61.32</v>
+        <v>59.17</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>63.59</v>
+        <v>65.63</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>57.12</v>
+        <v>68.67</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>SANSERA</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -3736,22 +3696,22 @@
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>3859</v>
+        <v>1654.7</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>60.98</v>
+        <v>58.89</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>80.12</v>
+        <v>70.88</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>84.04000000000001</v>
+        <v>75.69</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>RATNAMANI</t>
+          <t>LOTUSDEV</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -3760,22 +3720,22 @@
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>2611.1</v>
+        <v>184.64</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>60.77</v>
+        <v>58.1</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>54.69</v>
+        <v>63.28</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>50.81</v>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>DIACABS</t>
+          <t>VARROC</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -3784,22 +3744,22 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>349.4</v>
+        <v>826.35</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>60.7</v>
+        <v>58.04</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>80.68000000000001</v>
+        <v>75.22</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>80.66</v>
+        <v>67.31</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>LUMAXTECH</t>
+          <t>AZAD</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -3808,22 +3768,22 @@
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>1930.6</v>
+        <v>2766.9</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>60.65</v>
+        <v>57.78</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>65.48999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>71.08</v>
+        <v>70.53</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>JAIBALAJI</t>
+          <t>RUBICON</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -3832,22 +3792,22 @@
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>70.16</v>
+        <v>1768.3</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>60.06</v>
+        <v>57.52</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>50.06</v>
+        <v>82.83</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>42.65</v>
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>UTLSOLAR</t>
+          <t>MTARTECH</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -3856,16 +3816,16 @@
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>443.35</v>
+        <v>7161</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>59.95</v>
+        <v>57.5</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>74.05</v>
+        <v>60.95</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v/>
+        <v>70.70999999999999</v>
       </c>
     </row>
     <row r="63">
@@ -3880,22 +3840,22 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>836.05</v>
+        <v>839.1</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>59.78</v>
+        <v>57.35</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>62.63</v>
+        <v>63.09</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>55.7</v>
+        <v>55.53</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>PRICOLLTD</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -3904,22 +3864,22 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>770.65</v>
+        <v>2196.6</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>59.47</v>
+        <v>56.96</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>69.98999999999999</v>
+        <v>80.55</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>69.59</v>
+        <v>76.18000000000001</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>JAYNECOIND</t>
+          <t>ORKLAINDIA</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -3928,22 +3888,22 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>99.09999999999999</v>
+        <v>588.5</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>59.46</v>
+        <v>56.72</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>58.87</v>
+        <v>48.97</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>63.33</v>
+        <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>EMIL</t>
+          <t>MAHSCOOTER</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -3952,22 +3912,22 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>177.35</v>
+        <v>13639</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>59.21</v>
+        <v>56.67</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>69.7</v>
+        <v>54.98</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>59.85</v>
+        <v>58.39</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>TDPOWERSYS</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -3976,22 +3936,22 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>580.05</v>
+        <v>740.1</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>59.02</v>
+        <v>56.65</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>66.48999999999999</v>
+        <v>68.94</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>56.23</v>
+        <v>75.19</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>DYNAMATECH</t>
+          <t>BALUFORGE</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -4000,22 +3960,22 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>11492</v>
+        <v>574.1</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>59.01</v>
+        <v>56.63</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>57.73</v>
+        <v>59.24</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>66.7</v>
+        <v>52.64</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>MAHSCOOTER</t>
+          <t>RBA</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -4024,22 +3984,22 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>13696</v>
+        <v>97.89</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>58.93</v>
+        <v>56.54</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>55.91</v>
+        <v>68.2</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>58.88</v>
+        <v>58.43</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>VGUARD</t>
+          <t>GSFC</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -4048,22 +4008,22 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>331.5</v>
+        <v>161.86</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>58.5</v>
+        <v>56.5</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>58.08</v>
+        <v>48.22</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>49.31</v>
+        <v>45.69</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>INDIAGLYCO</t>
+          <t>AGARWALEYE</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -4072,22 +4032,22 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>1178.3</v>
+        <v>514.1</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>58.32</v>
+        <v>56.39</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>62.59</v>
+        <v>58.62</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>65.5</v>
+        <v>58.77</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>PARKHOSPS</t>
+          <t>SUPRIYA</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -4096,22 +4056,22 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>290.15</v>
+        <v>852.85</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>58.22</v>
+        <v>56.35</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>66.31</v>
+        <v>54.35</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v/>
+        <v>58.15</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>PARAS</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -4120,22 +4080,22 @@
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>1439.7</v>
+        <v>2127.8</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>58.2</v>
+        <v>56.28</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>69.18000000000001</v>
+        <v>69.78</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>70.39</v>
+        <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>STYL</t>
+          <t>VGUARD</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -4144,22 +4104,22 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>399.95</v>
+        <v>335.4</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>57.51</v>
+        <v>56.27</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>66.88</v>
+        <v>59.03</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v/>
+        <v>49.62</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>ELLEN</t>
+          <t>AARTIDRUGS</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -4168,22 +4128,22 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>319.8</v>
+        <v>425.85</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>57.41</v>
+        <v>56.17</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>56.85</v>
+        <v>62.21</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v/>
+        <v>51.19</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>WABAG</t>
+          <t>RAIN</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -4192,16 +4152,16 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>2086.1</v>
+        <v>215.72</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>57.07</v>
+        <v>55.99</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>66.20999999999999</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>68.83</v>
+        <v>60.38</v>
       </c>
     </row>
     <row r="77">
@@ -4216,22 +4176,22 @@
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>157.94</v>
+        <v>157.86</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>57</v>
+        <v>55.76</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>57.97</v>
+        <v>59.9</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>59.76</v>
+        <v>60.67</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>METROPOLIS</t>
+          <t>TARC</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -4240,22 +4200,22 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>576.9</v>
+        <v>126.99</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>56.7</v>
+        <v>55.71</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>62.34</v>
+        <v>46.99</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>63.36</v>
+        <v>46.38</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>NEOGEN</t>
+          <t>TARC</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -4264,22 +4224,22 @@
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>2230.2</v>
+        <v>126.99</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>56.64</v>
+        <v>55.71</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>67.52</v>
+        <v>46.99</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>63.33</v>
+        <v>46.38</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GRWRHITECH</t>
+          <t>JAIBALAJI</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -4288,22 +4248,22 @@
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>7224.5</v>
+        <v>69.73</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>56.2</v>
+        <v>55.64</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>75.86</v>
+        <v>50.5</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>70.27</v>
+        <v>42.95</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>EPL</t>
+          <t>DYNAMATECH</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -4312,22 +4272,22 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>251.94</v>
+        <v>11532</v>
       </c>
       <c r="D81" s="4" t="n">
-        <v>56.12</v>
+        <v>55.45</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>60.23</v>
+        <v>59.18</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>59.79</v>
+        <v>66.26000000000001</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>JKPAPER</t>
+          <t>JUSTDIAL</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -4336,22 +4296,22 @@
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>391.55</v>
+        <v>697.35</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>56.04</v>
+        <v>55.27</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>59.89</v>
+        <v>58.75</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>54.33</v>
+        <v>46.97</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>SMLMAH</t>
+          <t>ALKYLAMINE</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -4360,22 +4320,22 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>5194</v>
+        <v>2003.2</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>56.04</v>
+        <v>55.24</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>61.57</v>
+        <v>66.03</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>65.5</v>
+        <v>54.57</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>EDELWEISS</t>
+          <t>IIFLCAPS</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -4384,22 +4344,22 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>125.42</v>
+        <v>338.05</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>55.87</v>
+        <v>54.78</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>57.35</v>
+        <v>55.95</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>60.25</v>
+        <v>58.44</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>SHRIPISTON</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -4408,22 +4368,22 @@
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>813.5</v>
+        <v>4551.3</v>
       </c>
       <c r="D85" s="4" t="n">
-        <v>55.58</v>
+        <v>54.59</v>
       </c>
       <c r="E85" s="4" t="n">
-        <v>63.42</v>
+        <v>72.97</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>58.77</v>
+        <v>77.66</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>SHAILY</t>
+          <t>PRSMJOHNSN</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -4432,22 +4392,22 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>3270.4</v>
+        <v>111.31</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>54.92</v>
+        <v>54.36</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>66.52</v>
+        <v>41.01</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>73.44</v>
+        <v>40.19</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>PRICOLLTD</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -4456,22 +4416,22 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>108.43</v>
+        <v>768.4</v>
       </c>
       <c r="D87" s="4" t="n">
-        <v>54.5</v>
+        <v>54.33</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>50.5</v>
+        <v>68.8</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>42.8</v>
+        <v>67.06999999999999</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>PRSMJOHNSN</t>
+          <t>HCC</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -4480,22 +4440,22 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>111.18</v>
+        <v>22.98</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>54.28</v>
+        <v>54.26</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>41.07</v>
+        <v>52.7</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>40.2</v>
+        <v>47.52</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>MTARTECH</t>
+          <t>ICIL</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -4504,22 +4464,22 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>6997</v>
+        <v>437.35</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>54.23</v>
+        <v>54.03</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>59.71</v>
+        <v>65.95999999999999</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>70.15000000000001</v>
+        <v>63.63</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>AGARWALEYE</t>
+          <t>VIPIND</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -4528,22 +4488,22 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>507.8</v>
+        <v>310.35</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>53.94</v>
+        <v>54.02</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>57.35</v>
+        <v>47.76</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>57.98</v>
+        <v>38.53</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>CAMPUS</t>
+          <t>PARAS</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -4552,22 +4512,22 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>226.14</v>
+        <v>1411.5</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>53.93</v>
+        <v>53.96</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>44.05</v>
+        <v>67.41</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>42.19</v>
+        <v>69.37</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>ATLANTAELE</t>
+          <t>SHAILY</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -4576,22 +4536,22 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>1745.1</v>
+        <v>3267.1</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>53.84</v>
+        <v>53.82</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>57.92</v>
+        <v>66.7</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v/>
+        <v>73.51000000000001</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>PARKHOSPS</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -4600,22 +4560,22 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>606.05</v>
+        <v>286.7</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>53.7</v>
+        <v>53.69</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>74.73999999999999</v>
+        <v>63.88</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>69.86</v>
+        <v/>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>APLLTD</t>
+          <t>EMIL</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -4624,22 +4584,22 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>824</v>
+        <v>173.74</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>53.58</v>
+        <v>53.35</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>55.49</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>48.89</v>
+        <v>58.58</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>ICIL</t>
+          <t>LXCHEM</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -4648,22 +4608,22 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>423.4</v>
+        <v>175.58</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>53.53</v>
+        <v>53.34</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>64.16</v>
+        <v>56.99</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>63.81</v>
+        <v>45.76</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>SHRIPISTON</t>
+          <t>RENUKA</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -4672,22 +4632,22 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>4498.4</v>
+        <v>24.04</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>53.52</v>
+        <v>53.14</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>74.64</v>
+        <v>49.39</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>79.26000000000001</v>
+        <v>40.29</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>GHCL</t>
+          <t>SANSERA</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -4696,22 +4656,22 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>440.15</v>
+        <v>3789.6</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>53.44</v>
+        <v>52.95</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>44.3</v>
+        <v>76.17</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>42.71</v>
+        <v>78.48</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>PGIL</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -4720,22 +4680,22 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>2294.8</v>
+        <v>618.85</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>53.28</v>
+        <v>52.92</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>66.93000000000001</v>
+        <v>70.84</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>74.29000000000001</v>
+        <v>65.84</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>AXISCADES</t>
+          <t>BLUESTONE</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -4744,22 +4704,22 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>1612.9</v>
+        <v>804.9</v>
       </c>
       <c r="D99" s="4" t="n">
-        <v>53.24</v>
+        <v>52.55</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>47.95</v>
+        <v>72.58</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>59.52</v>
+        <v/>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>WESTLIFE</t>
+          <t>ASTRAMICRO</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -4768,22 +4728,22 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>563.25</v>
+        <v>1729</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>53.02</v>
+        <v>52.52</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>57.17</v>
+        <v>64.92</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>43.92</v>
+        <v>71.01000000000001</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>TEXRAIL</t>
+          <t>KIRLPNU</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -4792,22 +4752,22 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>109.44</v>
+        <v>759.8</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>52.96</v>
+        <v>52.45</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>48.64</v>
+        <v>52.53</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>44.03</v>
+        <v>56.86</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>SUNTECK</t>
+          <t>MASTEK</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -4816,22 +4776,22 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>307.5</v>
+        <v>1772.9</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>52.95</v>
+        <v>52.2</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>43.46</v>
+        <v>51.34</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>41.28</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>V2RETAIL</t>
+          <t>BLACKBUCK</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -4840,22 +4800,22 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>222.4</v>
+        <v>586.1</v>
       </c>
       <c r="D103" s="4" t="n">
-        <v>52.86</v>
+        <v>51.39</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>52.26</v>
+        <v>51.75</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>63.92</v>
+        <v>56.52</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>AARTIDRUGS</t>
+          <t>UTLSOLAR</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -4864,22 +4824,22 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>417.9</v>
+        <v>429.75</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>52.74</v>
+        <v>51.34</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>58.36</v>
+        <v>68.59</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>49.53</v>
+        <v/>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>BLUESTONE</t>
+          <t>PRUDENT</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -4888,22 +4848,22 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>800.5</v>
+        <v>3328.5</v>
       </c>
       <c r="D105" s="4" t="n">
-        <v>52.51</v>
+        <v>51.09</v>
       </c>
       <c r="E105" s="4" t="n">
-        <v>69.48</v>
+        <v>65.37</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v/>
+        <v>62.41</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>OPTIEMUS</t>
+          <t>STYL</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -4912,22 +4872,22 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>576.45</v>
+        <v>387.05</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>52.28</v>
+        <v>51.01</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>60.18</v>
+        <v>61.71</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>55.38</v>
+        <v/>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>BLACKBUCK</t>
+          <t>VIYASH</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -4936,22 +4896,22 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>588.2</v>
+        <v>265.85</v>
       </c>
       <c r="D107" s="4" t="n">
-        <v>52.28</v>
+        <v>50.8</v>
       </c>
       <c r="E107" s="4" t="n">
-        <v>52.04</v>
+        <v>56.52</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>57.09</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>TVSSCS</t>
+          <t>PNGJL</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -4960,22 +4920,22 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>131.56</v>
+        <v>609.05</v>
       </c>
       <c r="D108" s="4" t="n">
-        <v>52.25</v>
+        <v>50.78</v>
       </c>
       <c r="E108" s="4" t="n">
-        <v>54.1</v>
+        <v>51.4</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>47.54</v>
+        <v>49.82</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>SANDUMA</t>
+          <t>EPL</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -4984,22 +4944,22 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>205.45</v>
+        <v>246.55</v>
       </c>
       <c r="D109" s="4" t="n">
-        <v>52.21</v>
+        <v>50.64</v>
       </c>
       <c r="E109" s="4" t="n">
-        <v>49.71</v>
+        <v>57.75</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>55.82</v>
+        <v>57.44</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>POWERMECH</t>
+          <t>HCG</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -5008,22 +4968,22 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>2547.4</v>
+        <v>703.45</v>
       </c>
       <c r="D110" s="4" t="n">
-        <v>52.2</v>
+        <v>50.51</v>
       </c>
       <c r="E110" s="4" t="n">
-        <v>53.41</v>
+        <v>62.12</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>52.56</v>
+        <v>62.54</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>JYOTHYLAB</t>
+          <t>CCAVENUE</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -5032,22 +4992,22 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>207.4</v>
+        <v>15.7</v>
       </c>
       <c r="D111" s="4" t="n">
-        <v>52.04</v>
+        <v>50.49</v>
       </c>
       <c r="E111" s="4" t="n">
-        <v>43.68</v>
+        <v>49.88</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>38.64</v>
+        <v>44.08</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>TVSSCS</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -5056,22 +5016,22 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>543.35</v>
+        <v>129.53</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>51.89</v>
+        <v>50.47</v>
       </c>
       <c r="E112" s="4" t="n">
-        <v>63.64</v>
+        <v>53.31</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>67.81999999999999</v>
+        <v>47.38</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>SPARC</t>
+          <t>CAMPUS</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -5080,22 +5040,22 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>207.71</v>
+        <v>223.97</v>
       </c>
       <c r="D113" s="4" t="n">
-        <v>51.53</v>
+        <v>50.32</v>
       </c>
       <c r="E113" s="4" t="n">
-        <v>55.07</v>
+        <v>42.56</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>55.17</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>SKFINDIA</t>
+          <t>APOLLO</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -5104,22 +5064,22 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>1571.3</v>
+        <v>388.9</v>
       </c>
       <c r="D114" s="4" t="n">
-        <v>51.39</v>
+        <v>50.23</v>
       </c>
       <c r="E114" s="4" t="n">
-        <v>40.25</v>
+        <v>57.43</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>32.99</v>
+        <v>67.37</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>AEQUS</t>
+          <t>MIDHANI</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -5128,22 +5088,22 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>246.66</v>
+        <v>418.8</v>
       </c>
       <c r="D115" s="4" t="n">
-        <v>51.07</v>
+        <v>50.21</v>
       </c>
       <c r="E115" s="4" t="n">
-        <v>65.89</v>
+        <v>55.68</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v/>
+        <v>55.63</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>SKIPPER</t>
+          <t>WABAG</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -5152,22 +5112,22 @@
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>546.25</v>
+        <v>2005.3</v>
       </c>
       <c r="D116" s="4" t="n">
-        <v>51.06</v>
+        <v>50.11</v>
       </c>
       <c r="E116" s="4" t="n">
-        <v>60.78</v>
+        <v>61.52</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>61.28</v>
+        <v>67.51000000000001</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>RENUKA</t>
+          <t>GRWRHITECH</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -5176,22 +5136,22 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>23.43</v>
+        <v>7100</v>
       </c>
       <c r="D117" s="4" t="n">
-        <v>50.99</v>
+        <v>50.11</v>
       </c>
       <c r="E117" s="4" t="n">
-        <v>49.83</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>40.06</v>
+        <v>69.42</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>VIYASH</t>
+          <t>GHCL</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -5200,22 +5160,22 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>267.4</v>
+        <v>437.55</v>
       </c>
       <c r="D118" s="4" t="n">
-        <v>50.95</v>
+        <v>50.04</v>
       </c>
       <c r="E118" s="4" t="n">
-        <v>57.07</v>
+        <v>42.69</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>63.15</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>SAATVIKGL</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -5224,22 +5184,22 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>428.4</v>
+        <v>535.1</v>
       </c>
       <c r="D119" s="4" t="n">
-        <v>50.81</v>
+        <v>49.87</v>
       </c>
       <c r="E119" s="4" t="n">
-        <v>46.22</v>
+        <v>62.2</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v/>
+        <v>63.54</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>SOUTHBANK</t>
+          <t>ASHOKA</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -5248,22 +5208,22 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>45.73</v>
+        <v>117.32</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>50.76</v>
+        <v>49.82</v>
       </c>
       <c r="E120" s="4" t="n">
-        <v>58.25</v>
+        <v>38.23</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>68.92</v>
+        <v>41.18</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>BECTORFOOD</t>
+          <t>SAATVIKGL</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -5272,22 +5232,22 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>232.87</v>
+        <v>424.4</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>50.59</v>
+        <v>49.7</v>
       </c>
       <c r="E121" s="4" t="n">
-        <v>58.84</v>
+        <v>46.84</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>50.43</v>
+        <v/>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>CRAMC</t>
+          <t>SENCO</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -5296,16 +5256,16 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>258.9</v>
+        <v>358.65</v>
       </c>
       <c r="D122" s="4" t="n">
-        <v>50.51</v>
+        <v>49.45</v>
       </c>
       <c r="E122" s="4" t="n">
-        <v>51.29</v>
+        <v>53.31</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v/>
+        <v>50.76</v>
       </c>
     </row>
     <row r="123">
@@ -5320,22 +5280,22 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>1048.4</v>
+        <v>1044.8</v>
       </c>
       <c r="D123" s="4" t="n">
-        <v>50.39</v>
+        <v>49.42</v>
       </c>
       <c r="E123" s="4" t="n">
-        <v>42.49</v>
+        <v>42.41</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>49.6</v>
+        <v>49.59</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>ARVINDFASN</t>
+          <t>ETHOSLTD</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -5344,22 +5304,22 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>449.4</v>
+        <v>2793.1</v>
       </c>
       <c r="D124" s="4" t="n">
-        <v>50.3</v>
+        <v>49.03</v>
       </c>
       <c r="E124" s="4" t="n">
-        <v>47.92</v>
+        <v>59.17</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>49.31</v>
+        <v>55.24</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>HCG</t>
+          <t>PGIL</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -5368,22 +5328,22 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>699.95</v>
+        <v>2278.3</v>
       </c>
       <c r="D125" s="4" t="n">
-        <v>50.13</v>
+        <v>48.9</v>
       </c>
       <c r="E125" s="4" t="n">
-        <v>61.45</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>64.20999999999999</v>
+        <v>69.62</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>HAPPSTMNDS</t>
+          <t>NEOGEN</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -5392,22 +5352,22 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>408</v>
+        <v>2137.1</v>
       </c>
       <c r="D126" s="4" t="n">
-        <v>50.11</v>
+        <v>48.59</v>
       </c>
       <c r="E126" s="4" t="n">
-        <v>53.1</v>
+        <v>63.13</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>35.34</v>
+        <v>61.41</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>SAFARI</t>
+          <t>INOXGREEN</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -5416,22 +5376,22 @@
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>1522.2</v>
+        <v>175.1</v>
       </c>
       <c r="D127" s="4" t="n">
-        <v>50.07</v>
+        <v>48.51</v>
       </c>
       <c r="E127" s="4" t="n">
-        <v>42.4</v>
+        <v>47.19</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>41.04</v>
+        <v>51.89</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>SENCO</t>
+          <t>KNRCON</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -5440,22 +5400,22 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>362.75</v>
+        <v>124.66</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>49.48</v>
+        <v>48.37</v>
       </c>
       <c r="E128" s="4" t="n">
-        <v>52.42</v>
+        <v>44.69</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>50.36</v>
+        <v>34.95</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>MIDHANI</t>
+          <t>TIPSMUSIC</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -5464,22 +5424,22 @@
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>417.75</v>
+        <v>652.05</v>
       </c>
       <c r="D129" s="4" t="n">
-        <v>49.27</v>
+        <v>48.24</v>
       </c>
       <c r="E129" s="4" t="n">
-        <v>55.42</v>
+        <v>52.43</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>55.51</v>
+        <v>57.65</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>VIPIND</t>
+          <t>PRAJIND</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -5488,22 +5448,22 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>304.3</v>
+        <v>335.55</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>49.13</v>
+        <v>48.2</v>
       </c>
       <c r="E130" s="4" t="n">
-        <v>44.16</v>
+        <v>48.13</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>36.91</v>
+        <v>43.35</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>TIPSMUSIC</t>
+          <t>OPTIEMUS</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -5512,22 +5472,22 @@
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>660</v>
+        <v>564.85</v>
       </c>
       <c r="D131" s="4" t="n">
-        <v>49.11</v>
+        <v>48.03</v>
       </c>
       <c r="E131" s="4" t="n">
-        <v>52.17</v>
+        <v>58.58</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>57.6</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>KIRLOSBROS</t>
+          <t>GAEL</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -5536,22 +5496,22 @@
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>1899.3</v>
+        <v>167.81</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>49.05</v>
+        <v>47.62</v>
       </c>
       <c r="E132" s="4" t="n">
-        <v>58.59</v>
+        <v>58.08</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>55.78</v>
+        <v>63.18</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>THYROCARE</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -5560,22 +5520,22 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>2083.2</v>
+        <v>578.65</v>
       </c>
       <c r="D133" s="4" t="n">
-        <v>48.82</v>
+        <v>47.55</v>
       </c>
       <c r="E133" s="4" t="n">
-        <v>68.76000000000001</v>
+        <v>61.22</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v/>
+        <v>66.92</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>ASTRAMICRO</t>
+          <t>SAFARI</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -5584,22 +5544,22 @@
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>1706.6</v>
+        <v>1509.5</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>48.56</v>
+        <v>47.53</v>
       </c>
       <c r="E134" s="4" t="n">
-        <v>64</v>
+        <v>44.67</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>71.58</v>
+        <v>42.03</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>REDTAPE</t>
+          <t>KIRLOSBROS</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -5608,22 +5568,22 @@
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>126.01</v>
+        <v>1881.3</v>
       </c>
       <c r="D135" s="4" t="n">
-        <v>48.56</v>
+        <v>47.27</v>
       </c>
       <c r="E135" s="4" t="n">
-        <v>47.49</v>
+        <v>54.67</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>34.85</v>
+        <v>54.55</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>THYROCARE</t>
+          <t>INDIASHLTR</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -5632,22 +5592,22 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>581.45</v>
+        <v>673.1</v>
       </c>
       <c r="D136" s="4" t="n">
-        <v>48.47</v>
+        <v>47.24</v>
       </c>
       <c r="E136" s="4" t="n">
-        <v>62.85</v>
+        <v>38.34</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>69.48999999999999</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>JSFB</t>
+          <t>SKYGOLD</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -5656,22 +5616,22 @@
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>544.55</v>
+        <v>742</v>
       </c>
       <c r="D137" s="4" t="n">
-        <v>48.17</v>
+        <v>47.17</v>
       </c>
       <c r="E137" s="4" t="n">
-        <v>59.77</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>57.64</v>
+        <v>78.78</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>VIKRAMSOLR</t>
+          <t>KSB</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -5680,22 +5640,22 @@
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>172.71</v>
+        <v>810.6</v>
       </c>
       <c r="D138" s="4" t="n">
-        <v>47.91</v>
+        <v>47.08</v>
       </c>
       <c r="E138" s="4" t="n">
-        <v>38.96</v>
+        <v>46.71</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v/>
+        <v>52.02</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>ARVINDFASN</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -5704,22 +5664,22 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>5502</v>
+        <v>446.5</v>
       </c>
       <c r="D139" s="4" t="n">
-        <v>47.88</v>
+        <v>46.99</v>
       </c>
       <c r="E139" s="4" t="n">
-        <v>56.72</v>
+        <v>46.73</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>70.27</v>
+        <v>48.73</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>EMBDL</t>
+          <t>AVL</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -5728,22 +5688,22 @@
         </is>
       </c>
       <c r="C140" s="4" t="n">
-        <v>62.16</v>
+        <v>600.4</v>
       </c>
       <c r="D140" s="4" t="n">
-        <v>47.79</v>
+        <v>46.75</v>
       </c>
       <c r="E140" s="4" t="n">
-        <v>49.76</v>
+        <v>55.48</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>42.67</v>
+        <v>60.69</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>GAEL</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -5752,22 +5712,22 @@
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>166.98</v>
+        <v>156.29</v>
       </c>
       <c r="D141" s="4" t="n">
-        <v>47.41</v>
+        <v>46.65</v>
       </c>
       <c r="E141" s="4" t="n">
-        <v>57.65</v>
+        <v>48.73</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>64.31999999999999</v>
+        <v>53.93</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>RATEGAIN</t>
+          <t>SHAREINDIA</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -5776,22 +5736,22 @@
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>918.25</v>
+        <v>169.27</v>
       </c>
       <c r="D142" s="4" t="n">
-        <v>47.4</v>
+        <v>46.57</v>
       </c>
       <c r="E142" s="4" t="n">
-        <v>66.09999999999999</v>
+        <v>56.58</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>66.39</v>
+        <v>47.48</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>CAPILLARY</t>
+          <t>AEQUS</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -5800,13 +5760,13 @@
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>508.95</v>
+        <v>242.18</v>
       </c>
       <c r="D143" s="4" t="n">
-        <v>47.22</v>
+        <v>46.53</v>
       </c>
       <c r="E143" s="4" t="n">
-        <v>44.29</v>
+        <v>63.91</v>
       </c>
       <c r="F143" s="4" t="n">
         <v/>
@@ -5815,7 +5775,7 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>NFL</t>
+          <t>JSFB</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -5824,22 +5784,22 @@
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>71.36</v>
+        <v>535.1</v>
       </c>
       <c r="D144" s="4" t="n">
-        <v>47.15</v>
+        <v>46.46</v>
       </c>
       <c r="E144" s="4" t="n">
-        <v>40.63</v>
+        <v>58.54</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>42.73</v>
+        <v>56.98</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>APOLLO</t>
+          <t>TRIVENI</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -5848,22 +5808,22 @@
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>387.45</v>
+        <v>280.5</v>
       </c>
       <c r="D145" s="4" t="n">
-        <v>47.15</v>
+        <v>46.4</v>
       </c>
       <c r="E145" s="4" t="n">
-        <v>57.19</v>
+        <v>39.8</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>67.34999999999999</v>
+        <v>43.24</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>JLHL</t>
+          <t>EUREKAFORB</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -5872,22 +5832,22 @@
         </is>
       </c>
       <c r="C146" s="4" t="n">
-        <v>307.45</v>
+        <v>429.25</v>
       </c>
       <c r="D146" s="4" t="n">
-        <v>47.13</v>
+        <v>46.4</v>
       </c>
       <c r="E146" s="4" t="n">
-        <v>57.3</v>
+        <v>39.66</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>55.33</v>
+        <v>38.75</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>EUREKAFORB</t>
+          <t>SKFINDIA</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -5896,22 +5856,22 @@
         </is>
       </c>
       <c r="C147" s="4" t="n">
-        <v>433.15</v>
+        <v>1540.6</v>
       </c>
       <c r="D147" s="4" t="n">
-        <v>47.13</v>
+        <v>46.32</v>
       </c>
       <c r="E147" s="4" t="n">
-        <v>40.39</v>
+        <v>39.12</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>39.11</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>LXCHEM</t>
+          <t>BECTORFOOD</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -5920,22 +5880,22 @@
         </is>
       </c>
       <c r="C148" s="4" t="n">
-        <v>171.34</v>
+        <v>225.96</v>
       </c>
       <c r="D148" s="4" t="n">
-        <v>46.91</v>
+        <v>45.76</v>
       </c>
       <c r="E148" s="4" t="n">
-        <v>56.59</v>
+        <v>56</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>45.3</v>
+        <v>49.16</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>PURVA</t>
+          <t>GOKULAGRO</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -5944,22 +5904,22 @@
         </is>
       </c>
       <c r="C149" s="4" t="n">
-        <v>214.22</v>
+        <v>231.17</v>
       </c>
       <c r="D149" s="4" t="n">
-        <v>46.9</v>
+        <v>45.75</v>
       </c>
       <c r="E149" s="4" t="n">
-        <v>48.45</v>
+        <v>57.73</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>45.44</v>
+        <v>63.86</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>TRIVENI</t>
+          <t>BAJAJELEC</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -5968,22 +5928,22 @@
         </is>
       </c>
       <c r="C150" s="4" t="n">
-        <v>283.82</v>
+        <v>334.2</v>
       </c>
       <c r="D150" s="4" t="n">
-        <v>46.54</v>
+        <v>45.74</v>
       </c>
       <c r="E150" s="4" t="n">
-        <v>40.6</v>
+        <v>40.53</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>43.56</v>
+        <v>30.43</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>IFBIND</t>
+          <t>TIMETECHNO</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -5992,22 +5952,22 @@
         </is>
       </c>
       <c r="C151" s="4" t="n">
-        <v>1351.6</v>
+        <v>189.36</v>
       </c>
       <c r="D151" s="4" t="n">
-        <v>46.46</v>
+        <v>45.47</v>
       </c>
       <c r="E151" s="4" t="n">
-        <v>53.57</v>
+        <v>49.91</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>50.15</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -6016,22 +5976,22 @@
         </is>
       </c>
       <c r="C152" s="4" t="n">
-        <v>157.69</v>
+        <v>199.47</v>
       </c>
       <c r="D152" s="4" t="n">
-        <v>46.32</v>
+        <v>45.29</v>
       </c>
       <c r="E152" s="4" t="n">
-        <v>49.44</v>
+        <v>52.27</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>54.51</v>
+        <v>53.63</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>IIFLCAPS</t>
+          <t>WESTLIFE</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -6040,46 +6000,46 @@
         </is>
       </c>
       <c r="C153" s="4" t="n">
-        <v>334.4</v>
+        <v>540.55</v>
       </c>
       <c r="D153" s="4" t="n">
-        <v>45.83</v>
+        <v>44.91</v>
       </c>
       <c r="E153" s="4" t="n">
-        <v>52.07</v>
+        <v>52.57</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>57.4</v>
+        <v>42.02</v>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="inlineStr">
-        <is>
-          <t>KSCL</t>
-        </is>
-      </c>
-      <c r="B154" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C154" s="4" t="n">
-        <v>785</v>
-      </c>
-      <c r="D154" s="4" t="n">
-        <v>45.67</v>
-      </c>
-      <c r="E154" s="4" t="n">
-        <v>40.69</v>
-      </c>
-      <c r="F154" s="4" t="n">
-        <v>43.73</v>
+      <c r="A154" s="5" t="inlineStr">
+        <is>
+          <t>DIACABS</t>
+        </is>
+      </c>
+      <c r="B154" s="6" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C154" s="7" t="n">
+        <v>322.9</v>
+      </c>
+      <c r="D154" s="7" t="n">
+        <v>44.88</v>
+      </c>
+      <c r="E154" s="7" t="n">
+        <v>73.64</v>
+      </c>
+      <c r="F154" s="7" t="n">
+        <v>76.73</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>ZAGGLE</t>
+          <t>APLLTD</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -6088,22 +6048,22 @@
         </is>
       </c>
       <c r="C155" s="4" t="n">
-        <v>190.26</v>
+        <v>803.65</v>
       </c>
       <c r="D155" s="4" t="n">
-        <v>45.58</v>
+        <v>44.59</v>
       </c>
       <c r="E155" s="4" t="n">
-        <v>34.43</v>
+        <v>54.29</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>38.26</v>
+        <v>48.53</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>MEDPLUS</t>
+          <t>FINPIPE</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -6112,22 +6072,22 @@
         </is>
       </c>
       <c r="C156" s="4" t="n">
-        <v>688.35</v>
+        <v>158.9</v>
       </c>
       <c r="D156" s="4" t="n">
-        <v>45.43</v>
+        <v>44.56</v>
       </c>
       <c r="E156" s="4" t="n">
-        <v>31.38</v>
+        <v>39.23</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>40.06</v>
+        <v>41.51</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>SHAREINDIA</t>
+          <t>VIKRAMSOLR</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -6136,22 +6096,22 @@
         </is>
       </c>
       <c r="C157" s="4" t="n">
-        <v>169.02</v>
+        <v>168.45</v>
       </c>
       <c r="D157" s="4" t="n">
-        <v>45.21</v>
+        <v>44.4</v>
       </c>
       <c r="E157" s="4" t="n">
-        <v>55.44</v>
+        <v>37.6</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>47.07</v>
+        <v/>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>ROUTE</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -6160,22 +6120,22 @@
         </is>
       </c>
       <c r="C158" s="4" t="n">
-        <v>509.35</v>
+        <v>5332</v>
       </c>
       <c r="D158" s="4" t="n">
-        <v>45.01</v>
+        <v>44.4</v>
       </c>
       <c r="E158" s="4" t="n">
-        <v>42.63</v>
+        <v>55.26</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>30.54</v>
+        <v>69.16</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>BANCOINDIA</t>
+          <t>SUNTECK</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -6184,22 +6144,22 @@
         </is>
       </c>
       <c r="C159" s="4" t="n">
-        <v>623.65</v>
+        <v>297.75</v>
       </c>
       <c r="D159" s="4" t="n">
-        <v>44.97</v>
+        <v>44.37</v>
       </c>
       <c r="E159" s="4" t="n">
-        <v>48.33</v>
+        <v>41.6</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>56.58</v>
+        <v>40.58</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>FINPIPE</t>
+          <t>PURVA</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -6208,40 +6168,40 @@
         </is>
       </c>
       <c r="C160" s="4" t="n">
-        <v>160.54</v>
+        <v>211.09</v>
       </c>
       <c r="D160" s="4" t="n">
-        <v>44.8</v>
+        <v>44.04</v>
       </c>
       <c r="E160" s="4" t="n">
-        <v>40.66</v>
+        <v>55.76</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>41.81</v>
+        <v>48.29</v>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="5" t="inlineStr">
-        <is>
-          <t>LLOYDSENGG</t>
-        </is>
-      </c>
-      <c r="B161" s="6" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C161" s="7" t="n">
-        <v>86.73999999999999</v>
-      </c>
-      <c r="D161" s="7" t="n">
-        <v>44.67</v>
-      </c>
-      <c r="E161" s="7" t="n">
-        <v>62.27</v>
-      </c>
-      <c r="F161" s="7" t="n">
-        <v>63.51</v>
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>CSBBANK</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C161" s="4" t="n">
+        <v>324.95</v>
+      </c>
+      <c r="D161" s="4" t="n">
+        <v>44.02</v>
+      </c>
+      <c r="E161" s="4" t="n">
+        <v>42.21</v>
+      </c>
+      <c r="F161" s="4" t="n">
+        <v>45.92</v>
       </c>
     </row>
     <row r="162">
@@ -6256,22 +6216,22 @@
         </is>
       </c>
       <c r="C162" s="4" t="n">
-        <v>751.75</v>
+        <v>749.2</v>
       </c>
       <c r="D162" s="4" t="n">
-        <v>44.6</v>
+        <v>43.81</v>
       </c>
       <c r="E162" s="4" t="n">
-        <v>47.09</v>
+        <v>45.93</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>50.77</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>SUPRIYA</t>
+          <t>ROUTE</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -6280,22 +6240,22 @@
         </is>
       </c>
       <c r="C163" s="4" t="n">
-        <v>804.15</v>
+        <v>503.65</v>
       </c>
       <c r="D163" s="4" t="n">
-        <v>44.54</v>
+        <v>43.77</v>
       </c>
       <c r="E163" s="4" t="n">
-        <v>49.94</v>
+        <v>41.16</v>
       </c>
       <c r="F163" s="4" t="n">
-        <v>56.08</v>
+        <v>30.35</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>ORIENTCEM</t>
+          <t>NFL</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -6304,22 +6264,22 @@
         </is>
       </c>
       <c r="C164" s="4" t="n">
-        <v>131.41</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="D164" s="4" t="n">
-        <v>44.48</v>
+        <v>43.69</v>
       </c>
       <c r="E164" s="4" t="n">
-        <v>36.75</v>
+        <v>39.56</v>
       </c>
       <c r="F164" s="4" t="n">
-        <v>35.26</v>
+        <v>42.51</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>EQUITASBNK</t>
+          <t>JAMNAAUTO</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -6328,22 +6288,22 @@
         </is>
       </c>
       <c r="C165" s="4" t="n">
-        <v>74.17</v>
+        <v>122.04</v>
       </c>
       <c r="D165" s="4" t="n">
-        <v>44.16</v>
+        <v>43.47</v>
       </c>
       <c r="E165" s="4" t="n">
-        <v>53.7</v>
+        <v>46.51</v>
       </c>
       <c r="F165" s="4" t="n">
-        <v>54.11</v>
+        <v>53.23</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>STAR</t>
+          <t>ORIENTCEM</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -6352,22 +6312,22 @@
         </is>
       </c>
       <c r="C166" s="4" t="n">
-        <v>983</v>
+        <v>129.68</v>
       </c>
       <c r="D166" s="4" t="n">
-        <v>44.07</v>
+        <v>43.37</v>
       </c>
       <c r="E166" s="4" t="n">
-        <v>51</v>
+        <v>35.44</v>
       </c>
       <c r="F166" s="4" t="n">
-        <v>56.41</v>
+        <v>35.03</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>GRINDWELL</t>
+          <t>JYOTHYLAB</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -6376,22 +6336,22 @@
         </is>
       </c>
       <c r="C167" s="4" t="n">
-        <v>2024.1</v>
+        <v>200.5</v>
       </c>
       <c r="D167" s="4" t="n">
-        <v>44.02</v>
+        <v>43.22</v>
       </c>
       <c r="E167" s="4" t="n">
-        <v>58.87</v>
+        <v>40.76</v>
       </c>
       <c r="F167" s="4" t="n">
-        <v>56.85</v>
+        <v>37.75</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>SHARDACROP</t>
+          <t>GREAVESCOT</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -6400,22 +6360,22 @@
         </is>
       </c>
       <c r="C168" s="4" t="n">
-        <v>793.05</v>
+        <v>195.56</v>
       </c>
       <c r="D168" s="4" t="n">
-        <v>43.96</v>
+        <v>43.18</v>
       </c>
       <c r="E168" s="4" t="n">
-        <v>39.37</v>
+        <v>49.99</v>
       </c>
       <c r="F168" s="4" t="n">
-        <v>50.11</v>
+        <v>51.67</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>RELIGARE</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -6424,22 +6384,22 @@
         </is>
       </c>
       <c r="C169" s="4" t="n">
-        <v>234.2</v>
+        <v>495.2</v>
       </c>
       <c r="D169" s="4" t="n">
-        <v>43.93</v>
+        <v>42.87</v>
       </c>
       <c r="E169" s="4" t="n">
-        <v>46.19</v>
+        <v>41.64</v>
       </c>
       <c r="F169" s="4" t="n">
-        <v>49.97</v>
+        <v>42.07</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>DBREALTY</t>
+          <t>V2RETAIL</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -6448,22 +6408,22 @@
         </is>
       </c>
       <c r="C170" s="4" t="n">
-        <v>107.37</v>
+        <v>216.5</v>
       </c>
       <c r="D170" s="4" t="n">
-        <v>43.81</v>
+        <v>42.79</v>
       </c>
       <c r="E170" s="4" t="n">
-        <v>44.66</v>
+        <v>49.55</v>
       </c>
       <c r="F170" s="4" t="n">
-        <v>43.51</v>
+        <v>61.89</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>UJJIVANSFB</t>
+          <t>BANCOINDIA</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -6472,22 +6432,22 @@
         </is>
       </c>
       <c r="C171" s="4" t="n">
-        <v>67.84999999999999</v>
+        <v>616.9</v>
       </c>
       <c r="D171" s="4" t="n">
-        <v>43.57</v>
+        <v>42.76</v>
       </c>
       <c r="E171" s="4" t="n">
-        <v>59.14</v>
+        <v>48.2</v>
       </c>
       <c r="F171" s="4" t="n">
-        <v>62.99</v>
+        <v>56.51</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>RAIN</t>
+          <t>BIRLACORPN</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -6496,22 +6456,22 @@
         </is>
       </c>
       <c r="C172" s="4" t="n">
-        <v>199.31</v>
+        <v>880.9</v>
       </c>
       <c r="D172" s="4" t="n">
-        <v>43.56</v>
+        <v>42.73</v>
       </c>
       <c r="E172" s="4" t="n">
-        <v>59.8</v>
+        <v>41.72</v>
       </c>
       <c r="F172" s="4" t="n">
-        <v>58.13</v>
+        <v>39.98</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>IMFA</t>
+          <t>KITEX</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -6520,22 +6480,22 @@
         </is>
       </c>
       <c r="C173" s="4" t="n">
-        <v>1370.7</v>
+        <v>128.85</v>
       </c>
       <c r="D173" s="4" t="n">
-        <v>43.55</v>
+        <v>42.54</v>
       </c>
       <c r="E173" s="4" t="n">
-        <v>50.32</v>
+        <v>34.99</v>
       </c>
       <c r="F173" s="4" t="n">
-        <v>61.16</v>
+        <v>43.69</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>SANDUMA</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -6544,22 +6504,22 @@
         </is>
       </c>
       <c r="C174" s="4" t="n">
-        <v>201.04</v>
+        <v>197.83</v>
       </c>
       <c r="D174" s="4" t="n">
-        <v>43.41</v>
+        <v>42.21</v>
       </c>
       <c r="E174" s="4" t="n">
-        <v>48.35</v>
+        <v>46.23</v>
       </c>
       <c r="F174" s="4" t="n">
-        <v>42.98</v>
+        <v>53.99</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>NETWORK18</t>
+          <t>LLOYDSENGG</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -6568,22 +6528,22 @@
         </is>
       </c>
       <c r="C175" s="4" t="n">
-        <v>28.8</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="D175" s="4" t="n">
-        <v>43.26</v>
+        <v>41.98</v>
       </c>
       <c r="E175" s="4" t="n">
-        <v>37.16</v>
+        <v>58.99</v>
       </c>
       <c r="F175" s="4" t="n">
-        <v>34.61</v>
+        <v>61.82</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>CELLO</t>
+          <t>CRAMC</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -6592,22 +6552,22 @@
         </is>
       </c>
       <c r="C176" s="4" t="n">
-        <v>350.8</v>
+        <v>251.5</v>
       </c>
       <c r="D176" s="4" t="n">
-        <v>43.25</v>
+        <v>41.73</v>
       </c>
       <c r="E176" s="4" t="n">
-        <v>35.55</v>
+        <v>46.43</v>
       </c>
       <c r="F176" s="4" t="n">
-        <v>29.08</v>
+        <v/>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>GSFC</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -6616,22 +6576,22 @@
         </is>
       </c>
       <c r="C177" s="4" t="n">
-        <v>157.97</v>
+        <v>195.66</v>
       </c>
       <c r="D177" s="4" t="n">
-        <v>43.2</v>
+        <v>41.21</v>
       </c>
       <c r="E177" s="4" t="n">
-        <v>41.91</v>
+        <v>48.32</v>
       </c>
       <c r="F177" s="4" t="n">
-        <v>43.95</v>
+        <v>43.12</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>KANSAINER</t>
+          <t>IFBIND</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -6640,22 +6600,22 @@
         </is>
       </c>
       <c r="C178" s="4" t="n">
-        <v>198.44</v>
+        <v>1311.8</v>
       </c>
       <c r="D178" s="4" t="n">
-        <v>42.78</v>
+        <v>41.01</v>
       </c>
       <c r="E178" s="4" t="n">
-        <v>43.9</v>
+        <v>50.92</v>
       </c>
       <c r="F178" s="4" t="n">
-        <v>39.62</v>
+        <v>49.37</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>BAJAJELEC</t>
+          <t>WEWORK</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -6664,22 +6624,22 @@
         </is>
       </c>
       <c r="C179" s="4" t="n">
-        <v>334.8</v>
+        <v>666.95</v>
       </c>
       <c r="D179" s="4" t="n">
-        <v>42.64</v>
+        <v>40.91</v>
       </c>
       <c r="E179" s="4" t="n">
-        <v>40.92</v>
+        <v>53.68</v>
       </c>
       <c r="F179" s="4" t="n">
-        <v>30.04</v>
+        <v/>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>CCAVENUE</t>
+          <t>JAYNECOIND</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -6688,22 +6648,22 @@
         </is>
       </c>
       <c r="C180" s="4" t="n">
-        <v>15.27</v>
+        <v>89.04000000000001</v>
       </c>
       <c r="D180" s="4" t="n">
-        <v>42.17</v>
+        <v>40.78</v>
       </c>
       <c r="E180" s="4" t="n">
-        <v>47.69</v>
+        <v>49.64</v>
       </c>
       <c r="F180" s="4" t="n">
-        <v>42.74</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>AVL</t>
+          <t>KANSAINER</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -6712,22 +6672,22 @@
         </is>
       </c>
       <c r="C181" s="4" t="n">
-        <v>592.3</v>
+        <v>195.11</v>
       </c>
       <c r="D181" s="4" t="n">
-        <v>42.03</v>
+        <v>40.69</v>
       </c>
       <c r="E181" s="4" t="n">
-        <v>53.85</v>
+        <v>43.1</v>
       </c>
       <c r="F181" s="4" t="n">
-        <v>59.35</v>
+        <v>39.48</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>RTNINDIA</t>
+          <t>ZAGGLE</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -6736,22 +6696,22 @@
         </is>
       </c>
       <c r="C182" s="4" t="n">
-        <v>30.24</v>
+        <v>182.63</v>
       </c>
       <c r="D182" s="4" t="n">
-        <v>41.97</v>
+        <v>40.57</v>
       </c>
       <c r="E182" s="4" t="n">
-        <v>39.19</v>
+        <v>31.9</v>
       </c>
       <c r="F182" s="4" t="n">
-        <v>39.22</v>
+        <v>37.45</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>IONEXCHANG</t>
+          <t>GOKEX</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -6760,22 +6720,22 @@
         </is>
       </c>
       <c r="C183" s="4" t="n">
-        <v>376</v>
+        <v>767.65</v>
       </c>
       <c r="D183" s="4" t="n">
-        <v>41.96</v>
+        <v>40.44</v>
       </c>
       <c r="E183" s="4" t="n">
-        <v>45.79</v>
+        <v>53.02</v>
       </c>
       <c r="F183" s="4" t="n">
-        <v>44.18</v>
+        <v>51.08</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>GOKEX</t>
+          <t>ADVENZYMES</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -6784,22 +6744,22 @@
         </is>
       </c>
       <c r="C184" s="4" t="n">
-        <v>774.9</v>
+        <v>296</v>
       </c>
       <c r="D184" s="4" t="n">
-        <v>41.35</v>
+        <v>40.41</v>
       </c>
       <c r="E184" s="4" t="n">
-        <v>50.33</v>
+        <v>40.46</v>
       </c>
       <c r="F184" s="4" t="n">
-        <v>50.23</v>
+        <v>46.19</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>JSLL</t>
+          <t>GRINDWELL</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -6808,22 +6768,22 @@
         </is>
       </c>
       <c r="C185" s="4" t="n">
-        <v>512.5</v>
+        <v>1974.4</v>
       </c>
       <c r="D185" s="4" t="n">
-        <v>41.33</v>
+        <v>40.27</v>
       </c>
       <c r="E185" s="4" t="n">
-        <v>38.79</v>
+        <v>53.09</v>
       </c>
       <c r="F185" s="4" t="n">
-        <v>40.72</v>
+        <v>54.12</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>ADVENZYMES</t>
+          <t>EQUITASBNK</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -6832,22 +6792,22 @@
         </is>
       </c>
       <c r="C186" s="4" t="n">
-        <v>299.8</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="D186" s="4" t="n">
-        <v>41.1</v>
+        <v>40.25</v>
       </c>
       <c r="E186" s="4" t="n">
-        <v>42.43</v>
+        <v>52.14</v>
       </c>
       <c r="F186" s="4" t="n">
-        <v>47.04</v>
+        <v>53.39</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>GREAVESCOT</t>
+          <t>CMSINFO</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -6856,22 +6816,22 @@
         </is>
       </c>
       <c r="C187" s="4" t="n">
-        <v>194.41</v>
+        <v>244.86</v>
       </c>
       <c r="D187" s="4" t="n">
-        <v>41.02</v>
+        <v>40.22</v>
       </c>
       <c r="E187" s="4" t="n">
-        <v>49.57</v>
+        <v>31.14</v>
       </c>
       <c r="F187" s="4" t="n">
-        <v>51.51</v>
+        <v>32.88</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>HEMIPROP</t>
+          <t>NETWORK18</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -6880,22 +6840,22 @@
         </is>
       </c>
       <c r="C188" s="4" t="n">
-        <v>130.56</v>
+        <v>27.55</v>
       </c>
       <c r="D188" s="4" t="n">
-        <v>40.91</v>
+        <v>39.72</v>
       </c>
       <c r="E188" s="4" t="n">
-        <v>43.86</v>
+        <v>36.2</v>
       </c>
       <c r="F188" s="4" t="n">
-        <v>46.39</v>
+        <v>34.99</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>MOIL</t>
+          <t>FIEMIND</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -6904,22 +6864,22 @@
         </is>
       </c>
       <c r="C189" s="4" t="n">
-        <v>258.25</v>
+        <v>2085.8</v>
       </c>
       <c r="D189" s="4" t="n">
-        <v>40.71</v>
+        <v>39.58</v>
       </c>
       <c r="E189" s="4" t="n">
-        <v>37.05</v>
+        <v>44.15</v>
       </c>
       <c r="F189" s="4" t="n">
-        <v>42.16</v>
+        <v>58.68</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>KIRLPNU</t>
+          <t>JSLL</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -6928,22 +6888,22 @@
         </is>
       </c>
       <c r="C190" s="4" t="n">
-        <v>731.5</v>
+        <v>501.45</v>
       </c>
       <c r="D190" s="4" t="n">
-        <v>40.65</v>
+        <v>39.36</v>
       </c>
       <c r="E190" s="4" t="n">
-        <v>48.35</v>
+        <v>39.32</v>
       </c>
       <c r="F190" s="4" t="n">
-        <v>55.26</v>
+        <v>40.87</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>PNGJL</t>
+          <t>REFEX</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -6952,22 +6912,22 @@
         </is>
       </c>
       <c r="C191" s="4" t="n">
-        <v>594.55</v>
+        <v>282.55</v>
       </c>
       <c r="D191" s="4" t="n">
-        <v>40.38</v>
+        <v>39.33</v>
       </c>
       <c r="E191" s="4" t="n">
-        <v>49.76</v>
+        <v>46.45</v>
       </c>
       <c r="F191" s="4" t="n">
-        <v>48.68</v>
+        <v>48.47</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENT</t>
+          <t>SHARDACROP</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -6976,22 +6936,22 @@
         </is>
       </c>
       <c r="C192" s="4" t="n">
-        <v>73.53</v>
+        <v>768.35</v>
       </c>
       <c r="D192" s="4" t="n">
-        <v>40.17</v>
+        <v>39.18</v>
       </c>
       <c r="E192" s="4" t="n">
-        <v>53.28</v>
+        <v>38.16</v>
       </c>
       <c r="F192" s="4" t="n">
-        <v>57.41</v>
+        <v>49.58</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>BBOX</t>
+          <t>AWFIS</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -7000,22 +6960,22 @@
         </is>
       </c>
       <c r="C193" s="4" t="n">
-        <v>738</v>
+        <v>256.5</v>
       </c>
       <c r="D193" s="4" t="n">
-        <v>40.13</v>
+        <v>39.13</v>
       </c>
       <c r="E193" s="4" t="n">
-        <v>48.57</v>
+        <v>34.2</v>
       </c>
       <c r="F193" s="4" t="n">
-        <v>58.91</v>
+        <v>29.88</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>PRIVISCL</t>
+          <t>CELLO</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -7024,22 +6984,22 @@
         </is>
       </c>
       <c r="C194" s="4" t="n">
-        <v>3456.6</v>
+        <v>343.45</v>
       </c>
       <c r="D194" s="4" t="n">
-        <v>39.94</v>
+        <v>39.06</v>
       </c>
       <c r="E194" s="4" t="n">
-        <v>55.58</v>
+        <v>33.79</v>
       </c>
       <c r="F194" s="4" t="n">
-        <v>66.72</v>
+        <v>28.67</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>DBL</t>
+          <t>RALLIS</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -7048,22 +7008,22 @@
         </is>
       </c>
       <c r="C195" s="4" t="n">
-        <v>407.55</v>
+        <v>208.82</v>
       </c>
       <c r="D195" s="4" t="n">
-        <v>39.72</v>
+        <v>38.86</v>
       </c>
       <c r="E195" s="4" t="n">
-        <v>43.24</v>
+        <v>33.33</v>
       </c>
       <c r="F195" s="4" t="n">
-        <v>46.12</v>
+        <v>42.05</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>TIMETECHNO</t>
+          <t>TSFINV</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -7072,22 +7032,22 @@
         </is>
       </c>
       <c r="C196" s="4" t="n">
-        <v>186.29</v>
+        <v>406.05</v>
       </c>
       <c r="D196" s="4" t="n">
-        <v>39.65</v>
+        <v>38.82</v>
       </c>
       <c r="E196" s="4" t="n">
-        <v>48.59</v>
+        <v>45.98</v>
       </c>
       <c r="F196" s="4" t="n">
-        <v>51.92</v>
+        <v>52.58</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>REFEX</t>
+          <t>LLOYDSENT</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -7096,22 +7056,22 @@
         </is>
       </c>
       <c r="C197" s="4" t="n">
-        <v>287.55</v>
+        <v>71.97</v>
       </c>
       <c r="D197" s="4" t="n">
-        <v>39.45</v>
+        <v>38.62</v>
       </c>
       <c r="E197" s="4" t="n">
-        <v>47.86</v>
+        <v>54.02</v>
       </c>
       <c r="F197" s="4" t="n">
-        <v>48.93</v>
+        <v>57.62</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>PICCADIL</t>
+          <t>CERA</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -7120,22 +7080,22 @@
         </is>
       </c>
       <c r="C198" s="4" t="n">
-        <v>651.25</v>
+        <v>5683.5</v>
       </c>
       <c r="D198" s="4" t="n">
-        <v>39.45</v>
+        <v>38.36</v>
       </c>
       <c r="E198" s="4" t="n">
-        <v>51.63</v>
+        <v>51.08</v>
       </c>
       <c r="F198" s="4" t="n">
-        <v/>
+        <v>48.4</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>WEWORK</t>
+          <t>UJJIVANSFB</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -7144,22 +7104,22 @@
         </is>
       </c>
       <c r="C199" s="4" t="n">
-        <v>675.35</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="D199" s="4" t="n">
-        <v>39.32</v>
+        <v>38.04</v>
       </c>
       <c r="E199" s="4" t="n">
-        <v>57.51</v>
+        <v>53.44</v>
       </c>
       <c r="F199" s="4" t="n">
-        <v/>
+        <v>59.73</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>CRIZAC</t>
+          <t>VAIBHAVGBL</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -7168,22 +7128,22 @@
         </is>
       </c>
       <c r="C200" s="4" t="n">
-        <v>175.78</v>
+        <v>218.74</v>
       </c>
       <c r="D200" s="4" t="n">
-        <v>39.26</v>
+        <v>37.46</v>
       </c>
       <c r="E200" s="4" t="n">
-        <v>33.71</v>
+        <v>45.24</v>
       </c>
       <c r="F200" s="4" t="n">
-        <v/>
+        <v>45.31</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>RCF</t>
+          <t>MEDPLUS</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -7192,22 +7152,22 @@
         </is>
       </c>
       <c r="C201" s="4" t="n">
-        <v>119.81</v>
+        <v>660.65</v>
       </c>
       <c r="D201" s="4" t="n">
-        <v>39.08</v>
+        <v>37.42</v>
       </c>
       <c r="E201" s="4" t="n">
-        <v>41.38</v>
+        <v>31.38</v>
       </c>
       <c r="F201" s="4" t="n">
-        <v>44.36</v>
+        <v>40.21</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>BIRLACORPN</t>
+          <t>MOIL</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -7216,22 +7176,22 @@
         </is>
       </c>
       <c r="C202" s="4" t="n">
-        <v>881.2</v>
+        <v>250.68</v>
       </c>
       <c r="D202" s="4" t="n">
-        <v>38.93</v>
+        <v>37.13</v>
       </c>
       <c r="E202" s="4" t="n">
-        <v>40.84</v>
+        <v>35.31</v>
       </c>
       <c r="F202" s="4" t="n">
-        <v>39.36</v>
+        <v>41.71</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>TRANSRAILL</t>
+          <t>IXIGO</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -7240,22 +7200,22 @@
         </is>
       </c>
       <c r="C203" s="4" t="n">
-        <v>458.5</v>
+        <v>162.15</v>
       </c>
       <c r="D203" s="4" t="n">
-        <v>38.69</v>
+        <v>37.03</v>
       </c>
       <c r="E203" s="4" t="n">
-        <v>37.92</v>
+        <v>42.88</v>
       </c>
       <c r="F203" s="4" t="n">
-        <v>42.05</v>
+        <v>43.89</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>JUSTDIAL</t>
+          <t>GMRP&amp;UI</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -7264,22 +7224,22 @@
         </is>
       </c>
       <c r="C204" s="4" t="n">
-        <v>640.5</v>
+        <v>91.69</v>
       </c>
       <c r="D204" s="4" t="n">
-        <v>38.51</v>
+        <v>36.92</v>
       </c>
       <c r="E204" s="4" t="n">
-        <v>60.8</v>
+        <v>40.67</v>
       </c>
       <c r="F204" s="4" t="n">
-        <v>47.68</v>
+        <v>48.94</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>INOXGREEN</t>
+          <t>RATEGAIN</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -7288,22 +7248,22 @@
         </is>
       </c>
       <c r="C205" s="4" t="n">
-        <v>172.18</v>
+        <v>851.15</v>
       </c>
       <c r="D205" s="4" t="n">
-        <v>38.49</v>
+        <v>36.81</v>
       </c>
       <c r="E205" s="4" t="n">
-        <v>46.8</v>
+        <v>55.41</v>
       </c>
       <c r="F205" s="4" t="n">
-        <v>51.71</v>
+        <v>60.42</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>KNRCON</t>
+          <t>CAPILLARY</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -7312,22 +7272,22 @@
         </is>
       </c>
       <c r="C206" s="4" t="n">
-        <v>122.45</v>
+        <v>480.05</v>
       </c>
       <c r="D206" s="4" t="n">
-        <v>38.48</v>
+        <v>36.77</v>
       </c>
       <c r="E206" s="4" t="n">
-        <v>44.62</v>
+        <v>42.28</v>
       </c>
       <c r="F206" s="4" t="n">
-        <v>34.75</v>
+        <v/>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>SURYAROSNI</t>
+          <t>DBL</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -7336,22 +7296,22 @@
         </is>
       </c>
       <c r="C207" s="4" t="n">
-        <v>220.46</v>
+        <v>398.55</v>
       </c>
       <c r="D207" s="4" t="n">
-        <v>38.45</v>
+        <v>36.74</v>
       </c>
       <c r="E207" s="4" t="n">
-        <v>41.51</v>
+        <v>42.01</v>
       </c>
       <c r="F207" s="4" t="n">
-        <v>45.57</v>
+        <v>45.46</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>SWSOLAR</t>
+          <t>SANOFICONR</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -7360,22 +7320,22 @@
         </is>
       </c>
       <c r="C208" s="4" t="n">
-        <v>195.37</v>
+        <v>4205.4</v>
       </c>
       <c r="D208" s="4" t="n">
-        <v>38.43</v>
+        <v>36.6</v>
       </c>
       <c r="E208" s="4" t="n">
-        <v>43.91</v>
+        <v>39.65</v>
       </c>
       <c r="F208" s="4" t="n">
-        <v>40.51</v>
+        <v>41.97</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>KSB</t>
+          <t>BBOX</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -7384,22 +7344,22 @@
         </is>
       </c>
       <c r="C209" s="4" t="n">
-        <v>793.85</v>
+        <v>712.25</v>
       </c>
       <c r="D209" s="4" t="n">
-        <v>38.03</v>
+        <v>36.48</v>
       </c>
       <c r="E209" s="4" t="n">
-        <v>43.61</v>
+        <v>45.76</v>
       </c>
       <c r="F209" s="4" t="n">
-        <v>50.95</v>
+        <v>57.08</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>RALLIS</t>
+          <t>JLHL</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -7408,22 +7368,22 @@
         </is>
       </c>
       <c r="C210" s="4" t="n">
-        <v>210.24</v>
+        <v>290.3</v>
       </c>
       <c r="D210" s="4" t="n">
-        <v>37.97</v>
+        <v>36.25</v>
       </c>
       <c r="E210" s="4" t="n">
-        <v>33.67</v>
+        <v>49.69</v>
       </c>
       <c r="F210" s="4" t="n">
-        <v>42.06</v>
+        <v>52.02</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>KITEX</t>
+          <t>ANUP</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -7432,22 +7392,22 @@
         </is>
       </c>
       <c r="C211" s="4" t="n">
-        <v>129.86</v>
+        <v>1808</v>
       </c>
       <c r="D211" s="4" t="n">
-        <v>37.62</v>
+        <v>35.72</v>
       </c>
       <c r="E211" s="4" t="n">
-        <v>34.67</v>
+        <v>40.76</v>
       </c>
       <c r="F211" s="4" t="n">
-        <v>43.52</v>
+        <v>45.54</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>JAMNAAUTO</t>
+          <t>DBREALTY</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -7456,22 +7416,22 @@
         </is>
       </c>
       <c r="C212" s="4" t="n">
-        <v>119.88</v>
+        <v>102.57</v>
       </c>
       <c r="D212" s="4" t="n">
-        <v>37.56</v>
+        <v>35.66</v>
       </c>
       <c r="E212" s="4" t="n">
-        <v>46.57</v>
+        <v>41.88</v>
       </c>
       <c r="F212" s="4" t="n">
-        <v>53.3</v>
+        <v>42.63</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>JKLAKSHMI</t>
+          <t>SFL</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -7480,22 +7440,22 @@
         </is>
       </c>
       <c r="C213" s="4" t="n">
-        <v>544.2</v>
+        <v>646.8</v>
       </c>
       <c r="D213" s="4" t="n">
-        <v>36.84</v>
+        <v>35.62</v>
       </c>
       <c r="E213" s="4" t="n">
-        <v>33.9</v>
+        <v>48.34</v>
       </c>
       <c r="F213" s="4" t="n">
-        <v>38.16</v>
+        <v>45.54</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>SHAKTIPUMP</t>
+          <t>PRIVISCL</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -7504,22 +7464,22 @@
         </is>
       </c>
       <c r="C214" s="4" t="n">
-        <v>493.55</v>
+        <v>3367.3</v>
       </c>
       <c r="D214" s="4" t="n">
-        <v>36.82</v>
+        <v>35.5</v>
       </c>
       <c r="E214" s="4" t="n">
-        <v>37.33</v>
+        <v>51.42</v>
       </c>
       <c r="F214" s="4" t="n">
-        <v>43.89</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>VAIBHAVGBL</t>
+          <t>AURIONPRO</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -7528,22 +7488,22 @@
         </is>
       </c>
       <c r="C215" s="4" t="n">
-        <v>222.2</v>
+        <v>686.45</v>
       </c>
       <c r="D215" s="4" t="n">
-        <v>36.8</v>
+        <v>35.34</v>
       </c>
       <c r="E215" s="4" t="n">
-        <v>46.22</v>
+        <v>34.76</v>
       </c>
       <c r="F215" s="4" t="n">
-        <v>45.68</v>
+        <v>38.12</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>RTNPOWER</t>
+          <t>REDTAPE</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -7552,22 +7512,22 @@
         </is>
       </c>
       <c r="C216" s="4" t="n">
-        <v>7.95</v>
+        <v>117.48</v>
       </c>
       <c r="D216" s="4" t="n">
-        <v>36.56</v>
+        <v>34.9</v>
       </c>
       <c r="E216" s="4" t="n">
-        <v>35.68</v>
+        <v>43.79</v>
       </c>
       <c r="F216" s="4" t="n">
-        <v>43</v>
+        <v>34.37</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>GMRP&amp;UI</t>
+          <t>TANLA</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -7576,22 +7536,22 @@
         </is>
       </c>
       <c r="C217" s="4" t="n">
-        <v>93.34999999999999</v>
+        <v>514.8</v>
       </c>
       <c r="D217" s="4" t="n">
-        <v>36.55</v>
+        <v>34.81</v>
       </c>
       <c r="E217" s="4" t="n">
-        <v>37.47</v>
+        <v>46.65</v>
       </c>
       <c r="F217" s="4" t="n">
-        <v>47.96</v>
+        <v>44.84</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>HAPPSTMNDS</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -7600,22 +7560,22 @@
         </is>
       </c>
       <c r="C218" s="4" t="n">
-        <v>483.95</v>
+        <v>354</v>
       </c>
       <c r="D218" s="4" t="n">
-        <v>36.49</v>
+        <v>34.45</v>
       </c>
       <c r="E218" s="4" t="n">
-        <v>35.91</v>
+        <v>42.16</v>
       </c>
       <c r="F218" s="4" t="n">
-        <v>39.68</v>
+        <v>31.21</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>ASHAPURMIN</t>
+          <t>SURYAROSNI</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -7624,22 +7584,22 @@
         </is>
       </c>
       <c r="C219" s="4" t="n">
-        <v>582.1</v>
+        <v>216.49</v>
       </c>
       <c r="D219" s="4" t="n">
-        <v>36.44</v>
+        <v>34.33</v>
       </c>
       <c r="E219" s="4" t="n">
-        <v>42.61</v>
+        <v>40.18</v>
       </c>
       <c r="F219" s="4" t="n">
-        <v>52.59</v>
+        <v>45.06</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>AWFIS</t>
+          <t>KSCL</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -7648,22 +7608,22 @@
         </is>
       </c>
       <c r="C220" s="4" t="n">
-        <v>257.65</v>
+        <v>744.1</v>
       </c>
       <c r="D220" s="4" t="n">
-        <v>36.36</v>
+        <v>34.1</v>
       </c>
       <c r="E220" s="4" t="n">
-        <v>31.4</v>
+        <v>36.71</v>
       </c>
       <c r="F220" s="4" t="n">
-        <v>29.3</v>
+        <v>41.87</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>TARC</t>
+          <t>PICCADIL</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -7672,22 +7632,22 @@
         </is>
       </c>
       <c r="C221" s="4" t="n">
-        <v>117.9</v>
+        <v>620.5</v>
       </c>
       <c r="D221" s="4" t="n">
-        <v>35.54</v>
+        <v>33.99</v>
       </c>
       <c r="E221" s="4" t="n">
-        <v>39.59</v>
+        <v>47.46</v>
       </c>
       <c r="F221" s="4" t="n">
-        <v>43.96</v>
+        <v/>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>TARC</t>
+          <t>DATAMATICS</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -7696,22 +7656,22 @@
         </is>
       </c>
       <c r="C222" s="4" t="n">
-        <v>117.9</v>
+        <v>774.85</v>
       </c>
       <c r="D222" s="4" t="n">
-        <v>35.54</v>
+        <v>33.91</v>
       </c>
       <c r="E222" s="4" t="n">
-        <v>39.59</v>
+        <v>45.92</v>
       </c>
       <c r="F222" s="4" t="n">
-        <v>43.96</v>
+        <v>52.87</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>RAYMONDLSL</t>
+          <t>WAAREERTL</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -7720,22 +7680,22 @@
         </is>
       </c>
       <c r="C223" s="4" t="n">
-        <v>691.35</v>
+        <v>858.95</v>
       </c>
       <c r="D223" s="4" t="n">
-        <v>35.49</v>
+        <v>33.56</v>
       </c>
       <c r="E223" s="4" t="n">
-        <v>35.64</v>
+        <v>38.38</v>
       </c>
       <c r="F223" s="4" t="n">
-        <v>24.45</v>
+        <v>40.97</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>DATAMATICS</t>
+          <t>RCF</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -7744,22 +7704,22 @@
         </is>
       </c>
       <c r="C224" s="4" t="n">
-        <v>791.9</v>
+        <v>114.52</v>
       </c>
       <c r="D224" s="4" t="n">
-        <v>34.9</v>
+        <v>33.04</v>
       </c>
       <c r="E224" s="4" t="n">
-        <v>48.86</v>
+        <v>37.48</v>
       </c>
       <c r="F224" s="4" t="n">
-        <v>54.48</v>
+        <v>43.09</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>CERA</t>
+          <t>EMBDL</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -7768,22 +7728,22 @@
         </is>
       </c>
       <c r="C225" s="4" t="n">
-        <v>5662</v>
+        <v>57.53</v>
       </c>
       <c r="D225" s="4" t="n">
-        <v>34.76</v>
+        <v>32.99</v>
       </c>
       <c r="E225" s="4" t="n">
-        <v>47.86</v>
+        <v>44.04</v>
       </c>
       <c r="F225" s="4" t="n">
-        <v>47.32</v>
+        <v>40.96</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>OSWALPUMPS</t>
+          <t>SWSOLAR</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -7792,22 +7752,22 @@
         </is>
       </c>
       <c r="C226" s="4" t="n">
-        <v>298.4</v>
+        <v>187.79</v>
       </c>
       <c r="D226" s="4" t="n">
-        <v>34.74</v>
+        <v>32.34</v>
       </c>
       <c r="E226" s="4" t="n">
-        <v>32.41</v>
+        <v>40.72</v>
       </c>
       <c r="F226" s="4" t="n">
-        <v/>
+        <v>39.76</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>TANLA</t>
+          <t>IMFA</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -7816,22 +7776,22 @@
         </is>
       </c>
       <c r="C227" s="4" t="n">
-        <v>531.5</v>
+        <v>1281.7</v>
       </c>
       <c r="D227" s="4" t="n">
-        <v>34.74</v>
+        <v>32.26</v>
       </c>
       <c r="E227" s="4" t="n">
-        <v>50.75</v>
+        <v>44.95</v>
       </c>
       <c r="F227" s="4" t="n">
-        <v>46.2</v>
+        <v>58.16</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>FIEMIND</t>
+          <t>SAMHI</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -7840,22 +7800,22 @@
         </is>
       </c>
       <c r="C228" s="4" t="n">
-        <v>2087.7</v>
+        <v>152.59</v>
       </c>
       <c r="D228" s="4" t="n">
-        <v>34.63</v>
+        <v>31.48</v>
       </c>
       <c r="E228" s="4" t="n">
-        <v>44.22</v>
+        <v>41.86</v>
       </c>
       <c r="F228" s="4" t="n">
-        <v>59.18</v>
+        <v>44.35</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>TSFINV</t>
+          <t>KPIGREEN</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -7864,22 +7824,22 @@
         </is>
       </c>
       <c r="C229" s="4" t="n">
-        <v>404.2</v>
+        <v>307</v>
       </c>
       <c r="D229" s="4" t="n">
-        <v>34.54</v>
+        <v>31.16</v>
       </c>
       <c r="E229" s="4" t="n">
-        <v>46.51</v>
+        <v>29.26</v>
       </c>
       <c r="F229" s="4" t="n">
-        <v>52.8</v>
+        <v>42.03</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>ASHOKA</t>
+          <t>HEMIPROP</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -7888,22 +7848,22 @@
         </is>
       </c>
       <c r="C230" s="4" t="n">
-        <v>112.65</v>
+        <v>125.93</v>
       </c>
       <c r="D230" s="4" t="n">
-        <v>34.35</v>
+        <v>31.02</v>
       </c>
       <c r="E230" s="4" t="n">
-        <v>34.99</v>
+        <v>41.13</v>
       </c>
       <c r="F230" s="4" t="n">
-        <v>40.79</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>CMSINFO</t>
+          <t>POWERMECH</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -7912,22 +7872,22 @@
         </is>
       </c>
       <c r="C231" s="4" t="n">
-        <v>239.95</v>
+        <v>2306.1</v>
       </c>
       <c r="D231" s="4" t="n">
-        <v>34.1</v>
+        <v>30.82</v>
       </c>
       <c r="E231" s="4" t="n">
-        <v>30.61</v>
+        <v>42.79</v>
       </c>
       <c r="F231" s="4" t="n">
-        <v>32.79</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>INDIASHLTR</t>
+          <t>WEBELSOLAR</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -7936,22 +7896,22 @@
         </is>
       </c>
       <c r="C232" s="4" t="n">
-        <v>650.3</v>
+        <v>74.53</v>
       </c>
       <c r="D232" s="4" t="n">
-        <v>33.83</v>
+        <v>30.68</v>
       </c>
       <c r="E232" s="4" t="n">
-        <v>32.36</v>
+        <v>35.63</v>
       </c>
       <c r="F232" s="4" t="n">
-        <v>39.54</v>
+        <v>45.18</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>SAMHI</t>
+          <t>ASHAPURMIN</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -7960,22 +7920,22 @@
         </is>
       </c>
       <c r="C233" s="4" t="n">
-        <v>156.01</v>
+        <v>547.95</v>
       </c>
       <c r="D233" s="4" t="n">
-        <v>33.34</v>
+        <v>30.29</v>
       </c>
       <c r="E233" s="4" t="n">
-        <v>42.91</v>
+        <v>39.71</v>
       </c>
       <c r="F233" s="4" t="n">
-        <v>44.83</v>
+        <v>51.18</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>IXIGO</t>
+          <t>RAYMONDLSL</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -7984,22 +7944,22 @@
         </is>
       </c>
       <c r="C234" s="4" t="n">
-        <v>163.36</v>
+        <v>647.85</v>
       </c>
       <c r="D234" s="4" t="n">
-        <v>33.23</v>
+        <v>29.75</v>
       </c>
       <c r="E234" s="4" t="n">
-        <v>41.49</v>
+        <v>33.08</v>
       </c>
       <c r="F234" s="4" t="n">
-        <v>42.85</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>WAAREERTL</t>
+          <t>RTNINDIA</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -8008,22 +7968,22 @@
         </is>
       </c>
       <c r="C235" s="4" t="n">
-        <v>874.95</v>
+        <v>27.82</v>
       </c>
       <c r="D235" s="4" t="n">
-        <v>32.87</v>
+        <v>28.9</v>
       </c>
       <c r="E235" s="4" t="n">
-        <v>40.49</v>
+        <v>34.25</v>
       </c>
       <c r="F235" s="4" t="n">
-        <v>42.05</v>
+        <v>37.86</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>AURIONPRO</t>
+          <t>HGINFRA</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -8032,22 +7992,22 @@
         </is>
       </c>
       <c r="C236" s="4" t="n">
-        <v>688</v>
+        <v>479.9</v>
       </c>
       <c r="D236" s="4" t="n">
-        <v>32.49</v>
+        <v>28.83</v>
       </c>
       <c r="E236" s="4" t="n">
-        <v>36.09</v>
+        <v>31.9</v>
       </c>
       <c r="F236" s="4" t="n">
-        <v>38.64</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>ANUP</t>
+          <t>STYRENIX</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -8056,22 +8016,22 @@
         </is>
       </c>
       <c r="C237" s="4" t="n">
-        <v>1801.3</v>
+        <v>2007</v>
       </c>
       <c r="D237" s="4" t="n">
-        <v>32.19</v>
+        <v>28.66</v>
       </c>
       <c r="E237" s="4" t="n">
-        <v>41.28</v>
+        <v>43.47</v>
       </c>
       <c r="F237" s="4" t="n">
-        <v>45.75</v>
+        <v>48.37</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>AVANTIFEED</t>
+          <t>RTNPOWER</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -8080,16 +8040,16 @@
         </is>
       </c>
       <c r="C238" s="4" t="n">
-        <v>826.75</v>
+        <v>7.36</v>
       </c>
       <c r="D238" s="4" t="n">
-        <v>32.07</v>
+        <v>28.61</v>
       </c>
       <c r="E238" s="4" t="n">
-        <v>36.63</v>
+        <v>30.66</v>
       </c>
       <c r="F238" s="4" t="n">
-        <v>50.24</v>
+        <v>41.35</v>
       </c>
     </row>
     <row r="239">
@@ -8104,22 +8064,22 @@
         </is>
       </c>
       <c r="C239" s="4" t="n">
-        <v>356.1</v>
+        <v>343.95</v>
       </c>
       <c r="D239" s="4" t="n">
-        <v>31.67</v>
+        <v>28.4</v>
       </c>
       <c r="E239" s="4" t="n">
-        <v>47.38</v>
+        <v>45.27</v>
       </c>
       <c r="F239" s="4" t="n">
-        <v>37.01</v>
+        <v>36.14</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>MASTEK</t>
+          <t>SHAKTIPUMP</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -8128,22 +8088,22 @@
         </is>
       </c>
       <c r="C240" s="4" t="n">
-        <v>1611.6</v>
+        <v>473</v>
       </c>
       <c r="D240" s="4" t="n">
-        <v>31.46</v>
+        <v>28.3</v>
       </c>
       <c r="E240" s="4" t="n">
-        <v>57.11</v>
+        <v>34.39</v>
       </c>
       <c r="F240" s="4" t="n">
-        <v>46.5</v>
+        <v>42.91</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>SUBROS</t>
+          <t>AVANTIFEED</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -8152,22 +8112,22 @@
         </is>
       </c>
       <c r="C241" s="4" t="n">
-        <v>728.9</v>
+        <v>795.85</v>
       </c>
       <c r="D241" s="4" t="n">
-        <v>30.57</v>
+        <v>28.21</v>
       </c>
       <c r="E241" s="4" t="n">
-        <v>43.14</v>
+        <v>35.16</v>
       </c>
       <c r="F241" s="4" t="n">
-        <v>49.51</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>SFL</t>
+          <t>OSWALPUMPS</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -8176,22 +8136,22 @@
         </is>
       </c>
       <c r="C242" s="4" t="n">
-        <v>636.3</v>
+        <v>279.55</v>
       </c>
       <c r="D242" s="4" t="n">
-        <v>29.65</v>
+        <v>27.77</v>
       </c>
       <c r="E242" s="4" t="n">
-        <v>46.94</v>
+        <v>30.41</v>
       </c>
       <c r="F242" s="4" t="n">
-        <v>45.03</v>
+        <v>26.49</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>HGINFRA</t>
+          <t>CRIZAC</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -8200,22 +8160,22 @@
         </is>
       </c>
       <c r="C243" s="4" t="n">
-        <v>496.5</v>
+        <v>162.27</v>
       </c>
       <c r="D243" s="4" t="n">
-        <v>29.63</v>
+        <v>27.36</v>
       </c>
       <c r="E243" s="4" t="n">
-        <v>33.69</v>
+        <v>30.01</v>
       </c>
       <c r="F243" s="4" t="n">
-        <v>34.28</v>
+        <v/>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>KPIGREEN</t>
+          <t>BORORENEW</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -8224,22 +8184,22 @@
         </is>
       </c>
       <c r="C244" s="4" t="n">
-        <v>314.25</v>
+        <v>499.15</v>
       </c>
       <c r="D244" s="4" t="n">
-        <v>29.53</v>
+        <v>26.87</v>
       </c>
       <c r="E244" s="4" t="n">
-        <v>30.34</v>
+        <v>43.32</v>
       </c>
       <c r="F244" s="4" t="n">
-        <v>42.42</v>
+        <v>48.67</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>PNCINFRA</t>
+          <t>TRANSRAILL</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
@@ -8248,22 +8208,22 @@
         </is>
       </c>
       <c r="C245" s="4" t="n">
-        <v>198.34</v>
+        <v>427.45</v>
       </c>
       <c r="D245" s="4" t="n">
-        <v>28.53</v>
+        <v>26.49</v>
       </c>
       <c r="E245" s="4" t="n">
-        <v>38.4</v>
+        <v>34.47</v>
       </c>
       <c r="F245" s="4" t="n">
-        <v>39.61</v>
+        <v>40.58</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>WEBELSOLAR</t>
+          <t>JKLAKSHMI</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -8272,22 +8232,22 @@
         </is>
       </c>
       <c r="C246" s="4" t="n">
-        <v>77.84</v>
+        <v>515.7</v>
       </c>
       <c r="D246" s="4" t="n">
-        <v>28.28</v>
+        <v>24.76</v>
       </c>
       <c r="E246" s="4" t="n">
-        <v>37.38</v>
+        <v>30.34</v>
       </c>
       <c r="F246" s="4" t="n">
-        <v>46</v>
+        <v>36.87</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>STYRENIX</t>
+          <t>PNCINFRA</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -8296,22 +8256,22 @@
         </is>
       </c>
       <c r="C247" s="4" t="n">
-        <v>2020.8</v>
+        <v>182.97</v>
       </c>
       <c r="D247" s="4" t="n">
-        <v>25.96</v>
+        <v>23.98</v>
       </c>
       <c r="E247" s="4" t="n">
-        <v>42.32</v>
+        <v>34.9</v>
       </c>
       <c r="F247" s="4" t="n">
-        <v>47.81</v>
+        <v>38.35</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>BORORENEW</t>
+          <t>SUBROS</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -8320,16 +8280,16 @@
         </is>
       </c>
       <c r="C248" s="4" t="n">
-        <v>502.25</v>
+        <v>705.85</v>
       </c>
       <c r="D248" s="4" t="n">
-        <v>25.48</v>
+        <v>23.75</v>
       </c>
       <c r="E248" s="4" t="n">
-        <v>43.72</v>
+        <v>41.36</v>
       </c>
       <c r="F248" s="4" t="n">
-        <v>48.9</v>
+        <v>48.75</v>
       </c>
     </row>
     <row r="249">
@@ -8344,16 +8304,16 @@
         </is>
       </c>
       <c r="C249" s="4" t="n">
-        <v>188.68</v>
+        <v>184.47</v>
       </c>
       <c r="D249" s="4" t="n">
-        <v>23.18</v>
+        <v>22.25</v>
       </c>
       <c r="E249" s="4" t="n">
-        <v>31.69</v>
+        <v>34.27</v>
       </c>
       <c r="F249" s="4" t="n">
-        <v>44</v>
+        <v>44.99</v>
       </c>
     </row>
     <row r="250">
@@ -8368,22 +8328,22 @@
         </is>
       </c>
       <c r="C250" s="4" t="n">
-        <v>641.1</v>
+        <v>595.45</v>
       </c>
       <c r="D250" s="4" t="n">
-        <v>23.1</v>
+        <v>18.47</v>
       </c>
       <c r="E250" s="4" t="n">
-        <v>29.91</v>
+        <v>27.21</v>
       </c>
       <c r="F250" s="4" t="n">
-        <v>41.26</v>
+        <v>39.95</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>SANOFICONR</t>
+          <t>ALOKINDS</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
@@ -8392,22 +8352,22 @@
         </is>
       </c>
       <c r="C251" s="4" t="n">
-        <v>4150</v>
+        <v>7.83</v>
       </c>
       <c r="D251" s="4" t="n">
-        <v>21.22</v>
+        <v>14.35</v>
       </c>
       <c r="E251" s="4" t="n">
-        <v>39.97</v>
+        <v>21.23</v>
       </c>
       <c r="F251" s="4" t="n">
-        <v>41.7</v>
+        <v>30.34</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>ALOKINDS</t>
+          <t>INDIAGLYCO</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
@@ -8416,16 +8376,16 @@
         </is>
       </c>
       <c r="C252" s="4" t="n">
-        <v>9.24</v>
+        <v>248</v>
       </c>
       <c r="D252" s="4" t="n">
-        <v>10.22</v>
+        <v>13.12</v>
       </c>
       <c r="E252" s="4" t="n">
-        <v>25.31</v>
+        <v>23.25</v>
       </c>
       <c r="F252" s="4" t="n">
-        <v>32.4</v>
+        <v>35.3</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Micro250_stocks.xlsx
+++ b/docs/Micro250_stocks.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:L48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -551,7 +551,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ENTERO</t>
+          <t>MAHSEAMLES</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -560,37 +560,37 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>1848</v>
+        <v>718.95</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>85.76000000000001</v>
+        <v>77.76000000000001</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>78.31999999999999</v>
+        <v>75.28</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>73.73</v>
+        <v>59.95</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>59.67</v>
+        <v>53.21</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1268.33</v>
+        <v>601.91</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>1247.09</v>
+        <v>600.36</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>364215</v>
+        <v>341241</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>7954</v>
+        <v>9767</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>WELENT</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -599,37 +599,37 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>764.75</v>
+        <v>854.75</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>81.38</v>
+        <v>77.73999999999999</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>80.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>72.29000000000001</v>
+        <v>88.94</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>37.59</v>
+        <v>30.3</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>560.55</v>
+        <v>474.93</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>549.12</v>
+        <v>419.76</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>712546</v>
+        <v>1888026</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>11034</v>
+        <v>46132</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>SHILPAMED</t>
+          <t>WELENT</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -638,31 +638,31 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>964.15</v>
+        <v>797.95</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>75.61</v>
+        <v>75.19</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>91.48</v>
+        <v>75.42</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>84.42</v>
+        <v>71.2</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>65.44</v>
+        <v>48.59</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>577.8200000000001</v>
+        <v>575.6</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>538.9400000000001</v>
+        <v>561.17</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>2682728</v>
+        <v>729164</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>18857</v>
+        <v>10662</v>
       </c>
     </row>
     <row r="5">
@@ -677,37 +677,37 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>6298.5</v>
+        <v>6583</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>74.97</v>
+        <v>70.98</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>70.51000000000001</v>
+        <v>72.28</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>70.19</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>42.23</v>
+        <v>49.53</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>4309.57</v>
+        <v>4446.1</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>4120.15</v>
+        <v>4232.06</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>258334</v>
+        <v>148841</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>9115</v>
+        <v>9527</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>YATHARTH</t>
+          <t>MANORAMA</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -716,37 +716,37 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>991.1</v>
+        <v>2084.2</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>69.45</v>
+        <v>69.23999999999999</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>69.48999999999999</v>
+        <v>76.70999999999999</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>67.44</v>
+        <v>73.23999999999999</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>38.89</v>
+        <v>49.79</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>809.95</v>
+        <v>1580.08</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>785</v>
+        <v>1530.84</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>420012</v>
+        <v>769380</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>9550</v>
+        <v>12976</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>INOXINDIA</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2247.8</v>
+        <v>227.13</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>68.72</v>
+        <v>69.12</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>81.16</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>84.14</v>
+        <v>67.98</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>24.97</v>
+        <v>43.43</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1678.37</v>
+        <v>186.91</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1592.65</v>
+        <v>181.7</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>359311</v>
+        <v>2717753</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>20438</v>
+        <v>7293</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>MANORAMA</t>
+          <t>ENTERO</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -794,37 +794,37 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1993.4</v>
+        <v>1792.9</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>67.91</v>
+        <v>68.04000000000001</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>74.92</v>
+        <v>77.31</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>72.23</v>
+        <v>73.48</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>45.96</v>
+        <v>65</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1559.38</v>
+        <v>1305.29</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1514.17</v>
+        <v>1276.68</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>748025</v>
+        <v>378821</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>12583</v>
+        <v>7901</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>EDELWEISS</t>
+          <t>NEOGEN</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -833,37 +833,37 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>136.08</v>
+        <v>2388.9</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>67.8</v>
+        <v>67.45999999999999</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>64.31</v>
+        <v>70</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>63.63</v>
+        <v>65.89</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>31.37</v>
+        <v>27.75</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>117.58</v>
+        <v>1856.36</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>116.09</v>
+        <v>1786.52</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>5147406</v>
+        <v>207371</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>12880</v>
+        <v>6498</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>BALAMINES</t>
+          <t>SUDARSCHEM</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -872,37 +872,37 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2525.2</v>
+        <v>1270.8</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>67.7</v>
+        <v>66.44</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>71.37</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>66.02</v>
+        <v>60.63</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>24.02</v>
+        <v>37.25</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1847.19</v>
+        <v>1025.27</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1762.27</v>
+        <v>1020.71</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>258032</v>
+        <v>582644</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>8182</v>
+        <v>9937</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>TMB</t>
+          <t>SHILPAMED</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>942.45</v>
+        <v>939.9</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>67.40000000000001</v>
+        <v>66.17</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>74.83</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>78.70999999999999</v>
+        <v>84.36</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>40.12</v>
+        <v>63.54</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>734.73</v>
+        <v>597.1900000000001</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>697.23</v>
+        <v>555.26</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>528048</v>
+        <v>2776095</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>14765</v>
+        <v>18798</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>SANSERA</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -950,37 +950,37 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>220.74</v>
+        <v>4129.9</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>67.28</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>71.44</v>
+        <v>80.8</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>67.03</v>
+        <v>85.42</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>37.61</v>
+        <v>35.72</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>184.74</v>
+        <v>2983.15</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>179.88</v>
+        <v>2768.17</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2838957</v>
+        <v>244390</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>7112</v>
+        <v>25772</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>TDPOWERSYS</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -989,37 +989,37 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>340.1</v>
+        <v>804.9</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>67.16</v>
+        <v>65.29000000000001</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>80.31</v>
+        <v>73.3</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>77.17</v>
+        <v>80.13</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>46.01</v>
+        <v>32.36</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>266.53</v>
+        <v>581.72</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>255.04</v>
+        <v>542.58</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>3418019</v>
+        <v>2885840</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>12862</v>
+        <v>25150</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>ALIVUS</t>
+          <t>MIDHANI</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1028,31 +1028,31 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1418.8</v>
+        <v>463.35</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>66.40000000000001</v>
+        <v>63.82</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>74.39</v>
+        <v>62.02</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>70.98999999999999</v>
+        <v>58.15</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>46.42</v>
+        <v>20.8</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1127.73</v>
+        <v>400.12</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1097.39</v>
+        <v>393.32</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>205062</v>
+        <v>2902208</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>16774</v>
+        <v>8382</v>
       </c>
     </row>
     <row r="15">
@@ -1067,37 +1067,37 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>368.65</v>
+        <v>370.3</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>65.95</v>
+        <v>63.75</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>72.63</v>
+        <v>72.97</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>67</v>
+        <v>67.38</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>32.11</v>
+        <v>31.66</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>303.31</v>
+        <v>306.88</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>296.51</v>
+        <v>299.5</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2919161</v>
+        <v>2804707</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>14182</v>
+        <v>14245</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>VARROC</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1106,37 +1106,37 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1578.7</v>
+        <v>872</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>65.34</v>
+        <v>63.68</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>72.5</v>
+        <v>78.3</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>69.58</v>
+        <v>71.09</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>43.28</v>
+        <v>47.44</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1176.5</v>
+        <v>663.4299999999999</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1117.18</v>
+        <v>642.38</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>208995</v>
+        <v>965698</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>10334</v>
+        <v>13324</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>INOXINDIA</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1145,37 +1145,37 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>713.25</v>
+        <v>2246.6</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>65.26000000000001</v>
+        <v>63.04</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>77.5</v>
+        <v>81.04000000000001</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>86.48999999999999</v>
+        <v>84.12</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>24.86</v>
+        <v>30.07</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>455.8</v>
+        <v>1714.3</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>403.29</v>
+        <v>1624.07</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1920425</v>
+        <v>384073</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>38487</v>
+        <v>20427</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>YATHARTH</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1184,37 +1184,37 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>596.7</v>
+        <v>977.2</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>65.02</v>
+        <v>62.5</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>69.04000000000001</v>
+        <v>65.75</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>57.67</v>
+        <v>65.73</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>38.36</v>
+        <v>42.58</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>517.24</v>
+        <v>816.58</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>512.46</v>
+        <v>790.78</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>622145</v>
+        <v>430437</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>8768</v>
+        <v>9311</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>AKUMS</t>
+          <t>EMIL</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1223,31 +1223,31 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>780.55</v>
+        <v>188.38</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>64.91</v>
+        <v>62.19</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>73.13</v>
+        <v>71.45</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>64.22</v>
+        <v>61.75</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>46.98</v>
+        <v>34.89</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>608.1799999999999</v>
+        <v>137.26</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>588.76</v>
+        <v>134.03</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>391183</v>
+        <v>10739503</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>11724</v>
+        <v>7248</v>
       </c>
     </row>
     <row r="20">
@@ -1262,37 +1262,37 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>410.15</v>
+        <v>415.15</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>64.76000000000001</v>
+        <v>62</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>63.93</v>
+        <v>66.12</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>56.05</v>
+        <v>57.04</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>41.5</v>
+        <v>48.35</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>367.15</v>
+        <v>370.07</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>365.74</v>
+        <v>367.85</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>521219</v>
+        <v>477484</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>7358</v>
+        <v>7511</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>MSTCLTD</t>
+          <t>SKYGOLD</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1301,37 +1301,37 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>744.25</v>
+        <v>827.4</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>64.23999999999999</v>
+        <v>61.5</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>66.89</v>
+        <v>78.54000000000001</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>60.42</v>
+        <v>82.26000000000001</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>34.87</v>
+        <v>36.53</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>570.88</v>
+        <v>574.14</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>555.66</v>
+        <v>532.66</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>341892</v>
+        <v>1233215</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>5169</v>
+        <v>12814</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>QUESS</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1340,37 +1340,37 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>366.55</v>
+        <v>1584.6</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>63.19</v>
+        <v>60.67</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>72.03</v>
+        <v>73</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>51.8</v>
+        <v>69.86</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>51.08</v>
+        <v>48.49</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>269.03</v>
+        <v>1199.35</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>268.97</v>
+        <v>1136.77</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1387631</v>
+        <v>230477</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>5299</v>
+        <v>10431</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>SUDARSCHEM</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1379,37 +1379,37 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1222.8</v>
+        <v>329.4</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>61.61</v>
+        <v>60.52</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>66.95999999999999</v>
+        <v>73.78</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>59.49</v>
+        <v>67.64</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>35.25</v>
+        <v>40.85</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1013.14</v>
+        <v>250.8</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1012.06</v>
+        <v>241.17</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>564062</v>
+        <v>4771656</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>9734</v>
+        <v>14927</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>AZAD</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1418,37 +1418,37 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>326.75</v>
+        <v>2849.1</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>61.53</v>
+        <v>60.41</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>73.34</v>
+        <v>69.16</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>67.39</v>
+        <v>72.58</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>42.84</v>
+        <v>27.89</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>246.37</v>
+        <v>2223.05</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>237.4</v>
+        <v>2119.85</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4601759</v>
+        <v>556662</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>14807</v>
+        <v>18400</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>KRBL</t>
+          <t>AKUMS</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1457,37 +1457,37 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>424.9</v>
+        <v>776.35</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>61.17</v>
+        <v>60.32</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>63.41</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>58.4</v>
+        <v>65.41</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>47.02</v>
+        <v>38.59</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>370.13</v>
+        <v>619.41</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>366.95</v>
+        <v>598.48</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>864219</v>
+        <v>416081</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>9658</v>
+        <v>11886</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>LUMAXTECH</t>
+          <t>DIACABS</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1496,37 +1496,37 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1985.4</v>
+        <v>351.5</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>59.5</v>
+        <v>59.7</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>63.55</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>68.02</v>
+        <v>81.81</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>40.33</v>
+        <v>27.41</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1634.69</v>
+        <v>237.68</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1568.8</v>
+        <v>219.34</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>383013</v>
+        <v>1441405</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>13304</v>
+        <v>22072</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1535,37 +1535,37 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1654.7</v>
+        <v>332.55</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>58.89</v>
+        <v>59.29</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>70.88</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>75.69</v>
+        <v>73.34</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>48.41</v>
+        <v>40.94</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1291.1</v>
+        <v>269.98</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1221.79</v>
+        <v>258.11</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>340810</v>
+        <v>2934241</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>21576</v>
+        <v>12304</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>VARROC</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1574,37 +1574,37 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>826.35</v>
+        <v>569.8</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>58.04</v>
+        <v>58.48</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>75.22</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>67.31</v>
+        <v>70</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>49.63</v>
+        <v>20.76</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>652.6</v>
+        <v>473.76</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>633.5599999999999</v>
+        <v>452.29</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>901764</v>
+        <v>810373</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>12627</v>
+        <v>15076</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>AZAD</t>
+          <t>ALIVUS</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1613,37 +1613,37 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2766.9</v>
+        <v>1390.2</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>57.78</v>
+        <v>58.25</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>67.7</v>
+        <v>75.48</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>70.53</v>
+        <v>72.63</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>30.45</v>
+        <v>42.8</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>2173.66</v>
+        <v>1141.23</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>2076.74</v>
+        <v>1109.99</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>582230</v>
+        <v>214330</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>17936</v>
+        <v>17026</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>EDELWEISS</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1652,37 +1652,37 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2196.6</v>
+        <v>132.43</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>56.96</v>
+        <v>57.57</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>80.55</v>
+        <v>62.07</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>76.18000000000001</v>
+        <v>62.98</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>44.89</v>
+        <v>28.08</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1563.87</v>
+        <v>117.41</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>1452.96</v>
+        <v>115.73</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>544738</v>
+        <v>7386542</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>14691</v>
+        <v>12535</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>KRBL</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1691,37 +1691,37 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>740.1</v>
+        <v>423.25</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>56.65</v>
+        <v>57.32</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>68.94</v>
+        <v>63.1</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>75.19</v>
+        <v>58.28</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>31.03</v>
+        <v>47.06</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>569.0700000000001</v>
+        <v>373.12</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>531.25</v>
+        <v>369.32</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>3249124</v>
+        <v>909412</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>23125</v>
+        <v>9637</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>RBA</t>
+          <t>TMB</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1730,37 +1730,37 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>97.89</v>
+        <v>910.9</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>56.54</v>
+        <v>56.85</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>68.2</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>58.43</v>
+        <v>76.06</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>54.66</v>
+        <v>41.61</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>76.52</v>
+        <v>746.89</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>75.25</v>
+        <v>708.3200000000001</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>16847552</v>
+        <v>173819</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>6918</v>
+        <v>14424</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>ALKYLAMINE</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1769,37 +1769,37 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>2003.2</v>
+        <v>2227</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>55.24</v>
+        <v>56.74</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>66.03</v>
+        <v>81.87</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>54.57</v>
+        <v>78.70999999999999</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>26.86</v>
+        <v>41.95</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1773.26</v>
+        <v>1591.57</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>1762.14</v>
+        <v>1477.16</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>145029</v>
+        <v>531379</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>10336</v>
+        <v>15145</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>ICIL</t>
+          <t>MSTCLTD</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1808,37 +1808,37 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>437.35</v>
+        <v>737.55</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>54.03</v>
+        <v>56.65</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>65.95999999999999</v>
+        <v>67.2</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>63.63</v>
+        <v>60.69</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>30.88</v>
+        <v>40.45</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>354.92</v>
+        <v>583.0700000000001</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>341.91</v>
+        <v>565.59</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>1553756</v>
+        <v>395801</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>8908</v>
+        <v>5199</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>PARAS</t>
+          <t>RAIN</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1847,37 +1847,37 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1411.5</v>
+        <v>217.28</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>53.96</v>
+        <v>55.68</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>67.41</v>
+        <v>65.59</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>69.37</v>
+        <v>60.41</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>34.51</v>
+        <v>20.45</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1061.48</v>
+        <v>180.73</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>1000.04</v>
+        <v>173.39</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>1365832</v>
+        <v>5796631</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>11402</v>
+        <v>7264</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>SHAILY</t>
+          <t>PGIL</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1886,37 +1886,37 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>3267.1</v>
+        <v>1189.2</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>53.82</v>
+        <v>55.41</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>66.7</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>73.51000000000001</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>33.64</v>
+        <v>34.06</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>2751.03</v>
+        <v>953.29</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>2627.96</v>
+        <v>910.5</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>176648</v>
+        <v>345645</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>15079</v>
+        <v>10972</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>EMIL</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1925,37 +1925,37 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>173.74</v>
+        <v>1640.3</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>53.35</v>
+        <v>54.82</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>67.48999999999999</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>58.58</v>
+        <v>79.05</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>35.69</v>
+        <v>37.98</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>134.53</v>
+        <v>1308.79</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>131.89</v>
+        <v>1238.26</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>10407286</v>
+        <v>337589</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>6685</v>
+        <v>22228</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>SANSERA</t>
+          <t>RBA</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1964,37 +1964,37 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>3789.6</v>
+        <v>98.05</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>52.95</v>
+        <v>54.75</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>76.17</v>
+        <v>68.73</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>78.48</v>
+        <v>58.95</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>33.87</v>
+        <v>49.17</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>2910.22</v>
+        <v>77.88</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>2702.65</v>
+        <v>76.33</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>222486</v>
+        <v>16811685</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>23605</v>
+        <v>6982</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -2003,37 +2003,37 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>618.85</v>
+        <v>562.4</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>52.92</v>
+        <v>54.48</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>70.84</v>
+        <v>64.73</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>65.84</v>
+        <v>56.54</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>50.13</v>
+        <v>36</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>506.96</v>
+        <v>503.39</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>496.01</v>
+        <v>497.76</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1301938</v>
+        <v>697917</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>12200</v>
+        <v>8264</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>HCG</t>
+          <t>PARAS</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -2042,37 +2042,37 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>703.45</v>
+        <v>1435.6</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>50.51</v>
+        <v>54.02</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>62.12</v>
+        <v>68.14</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>62.54</v>
+        <v>70.31</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>29.13</v>
+        <v>31.94</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>649.2</v>
+        <v>1086.77</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>640.54</v>
+        <v>1021.61</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>169316</v>
+        <v>1463084</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>10454</v>
+        <v>11569</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -2081,37 +2081,37 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>535.1</v>
+        <v>622.4</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>49.87</v>
+        <v>53.58</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>62.2</v>
+        <v>71.48</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>63.54</v>
+        <v>66.56</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>31.19</v>
+        <v>42.97</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>471.7</v>
+        <v>512.72</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>461.98</v>
+        <v>500.76</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>1248527</v>
+        <v>1296445</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>13226</v>
+        <v>12313</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>PGIL</t>
+          <t>LUMAXTECH</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -2120,37 +2120,37 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>2278.3</v>
+        <v>1942.6</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>48.9</v>
+        <v>53.54</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>64.98999999999999</v>
+        <v>64.94</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>69.62</v>
+        <v>69.39</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>37.23</v>
+        <v>33.73</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>1883.79</v>
+        <v>1655.37</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>1800.42</v>
+        <v>1587.66</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>166690</v>
+        <v>383186</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>10524</v>
+        <v>13589</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>NEOGEN</t>
+          <t>ICIL</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -2159,37 +2159,37 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>2137.1</v>
+        <v>439.45</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>48.59</v>
+        <v>53.4</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>63.13</v>
+        <v>64.42</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>61.41</v>
+        <v>62.82</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>24.88</v>
+        <v>34.25</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>1834.74</v>
+        <v>359.65</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>1767.37</v>
+        <v>345.91</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>205236</v>
+        <v>1601468</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>5854</v>
+        <v>8779</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>THYROCARE</t>
+          <t>BALAMINES</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -2198,37 +2198,37 @@
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>578.65</v>
+        <v>2342.6</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>47.55</v>
+        <v>52.19</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>61.22</v>
+        <v>61.11</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>66.92</v>
+        <v>61.88</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>20.45</v>
+        <v>27.11</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>506.56</v>
+        <v>1877.81</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>485.76</v>
+        <v>1789.21</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>792028</v>
+        <v>238029</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>9170</v>
+        <v>7376</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>SKYGOLD</t>
+          <t>QUESS</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -2237,31 +2237,148 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>742</v>
+        <v>348</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>47.17</v>
+        <v>51.96</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>76.04000000000001</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>78.78</v>
+        <v>51.11</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>42.12</v>
+        <v>35.67</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>554.22</v>
+        <v>275.11</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>515.42</v>
+        <v>273.45</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>1227001</v>
+        <v>792142</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>12103</v>
+        <v>5199</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>AARTIPHARM</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>825.75</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>51.88</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>60.25</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>57.77</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>32.01</v>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>742.67</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>741.49</v>
+      </c>
+      <c r="J46" s="4" t="n">
+        <v>1048227</v>
+      </c>
+      <c r="K46" s="4" t="n">
+        <v>7499</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>SHAILY</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>3279.5</v>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>50.88</v>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>73.56</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>31.68</v>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>2795.27</v>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>2667.89</v>
+      </c>
+      <c r="J47" s="4" t="n">
+        <v>179142</v>
+      </c>
+      <c r="K47" s="4" t="n">
+        <v>15084</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>HCG</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>700.9</v>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>49.72</v>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>60.29</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>61.82</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>29.74</v>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>651.91</v>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>643.03</v>
+      </c>
+      <c r="J48" s="4" t="n">
+        <v>171696</v>
+      </c>
+      <c r="K48" s="4" t="n">
+        <v>10360</v>
       </c>
     </row>
   </sheetData>
@@ -2310,6 +2427,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId47"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2367,7 +2487,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ENTERO</t>
+          <t>GMMPFAUDLR</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2376,22 +2496,22 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>1848</v>
+        <v>1319.2</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>85.76000000000001</v>
+        <v>87.64</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>78.31999999999999</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>73.73</v>
+        <v>56.32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>SUDEEPPHRM</t>
+          <t>STAR</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2400,22 +2520,22 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>1329.3</v>
+        <v>1217</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>85.39</v>
+        <v>81.23999999999999</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>84.05</v>
+        <v>65.3</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v/>
+        <v>63.04</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>MANYAVAR</t>
+          <t>MAHSEAMLES</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2424,22 +2544,22 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>594.2</v>
+        <v>718.95</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>82.58</v>
+        <v>77.76000000000001</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>73.34999999999999</v>
+        <v>75.28</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>43.79</v>
+        <v>59.95</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>WELENT</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2448,22 +2568,22 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>764.75</v>
+        <v>854.75</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>81.38</v>
+        <v>77.73999999999999</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>80.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>72.29000000000001</v>
+        <v>88.94</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>GMMPFAUDLR</t>
+          <t>WELENT</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2472,22 +2592,22 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1147.9</v>
+        <v>797.95</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>79.2</v>
+        <v>75.19</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>70.2</v>
+        <v>75.42</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>51.8</v>
+        <v>71.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>MAHSEAMLES</t>
+          <t>SHAREINDIA</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2496,22 +2616,22 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>688.1</v>
+        <v>196.32</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>76.53</v>
+        <v>74.19</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>70.42</v>
+        <v>66.91</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>57.3</v>
+        <v>52.92</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>SHILPAMED</t>
+          <t>ELLEN</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2520,22 +2640,22 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>964.15</v>
+        <v>373.5</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>75.61</v>
+        <v>73.16</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>91.48</v>
+        <v>67.61</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>84.42</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>SMLMAH</t>
+          <t>PCJEWELLER</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2544,22 +2664,22 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>6298.5</v>
+        <v>13.7</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>74.97</v>
+        <v>73.02</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>70.51000000000001</v>
+        <v>72.81</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>70.19</v>
+        <v>59.64</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ELECTCAST</t>
+          <t>MANYAVAR</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2568,22 +2688,22 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>83.84999999999999</v>
+        <v>582.35</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>73.81999999999999</v>
+        <v>71.89</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>58.17</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>46.62</v>
+        <v>42.96</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SKFINDUS</t>
+          <t>LOTUSDEV</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2592,13 +2712,13 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3062.8</v>
+        <v>209.27</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>71.56999999999999</v>
+        <v>71.87</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>67.97</v>
+        <v>67.55</v>
       </c>
       <c r="F11" s="4" t="n">
         <v/>
@@ -2607,7 +2727,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>QPOWER</t>
+          <t>IONEXCHANG</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2616,22 +2736,22 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1495.3</v>
+        <v>445.7</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>69.54000000000001</v>
+        <v>71.13</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>67.81999999999999</v>
+        <v>60.3</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>69.56</v>
+        <v>51.63</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>GODREJAGRO</t>
+          <t>SMLMAH</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -2640,22 +2760,22 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>658.95</v>
+        <v>6583</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>69.47</v>
+        <v>70.98</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>64.89</v>
+        <v>72.28</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>52.89</v>
+        <v>71.23999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>YATHARTH</t>
+          <t>GODREJAGRO</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -2664,22 +2784,22 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>991.1</v>
+        <v>675.85</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>69.45</v>
+        <v>69.37</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>69.48999999999999</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>67.44</v>
+        <v>55.17</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>INOXINDIA</t>
+          <t>WABAG</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -2688,22 +2808,22 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2247.8</v>
+        <v>2277.9</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>68.72</v>
+        <v>69.27</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>81.16</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>84.14</v>
+        <v>71.92</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>PCJEWELLER</t>
+          <t>MANORAMA</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -2712,22 +2832,22 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>11.86</v>
+        <v>2084.2</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>68.65000000000001</v>
+        <v>69.23999999999999</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>65.15000000000001</v>
+        <v>76.70999999999999</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>55.33</v>
+        <v>73.23999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>MANORAMA</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -2736,22 +2856,22 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1993.4</v>
+        <v>227.13</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>67.91</v>
+        <v>69.12</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>74.92</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>72.23</v>
+        <v>67.98</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>EDELWEISS</t>
+          <t>RATNAMANI</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -2760,22 +2880,22 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>136.08</v>
+        <v>2823</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>67.8</v>
+        <v>68.12</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>64.31</v>
+        <v>60.05</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>63.63</v>
+        <v>54.74</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>BALAMINES</t>
+          <t>ENTERO</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2784,22 +2904,22 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>2525.2</v>
+        <v>1792.9</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>67.7</v>
+        <v>68.04000000000001</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>71.37</v>
+        <v>77.31</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>66.02</v>
+        <v>73.48</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>TMB</t>
+          <t>WAKEFIT</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -2808,22 +2928,22 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>942.45</v>
+        <v>155.13</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>67.40000000000001</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>74.83</v>
+        <v>57.39</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>78.70999999999999</v>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>NEOGEN</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -2832,22 +2952,22 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>220.74</v>
+        <v>2388.9</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>67.28</v>
+        <v>67.45999999999999</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>71.44</v>
+        <v>70</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>67.03</v>
+        <v>65.89</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>SUDARSCHEM</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -2856,22 +2976,22 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>340.1</v>
+        <v>1270.8</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>67.16</v>
+        <v>66.44</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>80.31</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>77.17</v>
+        <v>60.63</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>ALIVUS</t>
+          <t>APOLLO</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -2880,22 +3000,22 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1418.8</v>
+        <v>422.25</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>66.40000000000001</v>
+        <v>66.19</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>74.39</v>
+        <v>62.7</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>70.98999999999999</v>
+        <v>69.72</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>HERITGFOOD</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -2904,22 +3024,22 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>368.65</v>
+        <v>398.05</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>65.95</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>72.63</v>
+        <v>68.17</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>67</v>
+        <v>54.39</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>RATNAMANI</t>
+          <t>AXISCADES</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -2928,22 +3048,22 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2727</v>
+        <v>1831.8</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>65.8</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>57.86</v>
+        <v>57.97</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>53.14</v>
+        <v>63.99</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>WAKEFIT</t>
+          <t>SHILPAMED</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -2952,22 +3072,22 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>149.64</v>
+        <v>939.9</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>65.45</v>
+        <v>66.17</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>55.6</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v/>
+        <v>84.36</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>SANSERA</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -2976,22 +3096,22 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1578.7</v>
+        <v>4129.9</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>65.34</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>72.5</v>
+        <v>80.8</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>69.58</v>
+        <v>85.42</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>JAMNAAUTO</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -3000,22 +3120,22 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>713.25</v>
+        <v>135.46</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>65.26000000000001</v>
+        <v>65.75</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>77.5</v>
+        <v>55.51</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>86.48999999999999</v>
+        <v>58.38</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>PRSMJOHNSN</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3024,22 +3144,22 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>596.7</v>
+        <v>115.22</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>65.02</v>
+        <v>65.62</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>69.04000000000001</v>
+        <v>44.28</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>57.67</v>
+        <v>41.23</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>TEXRAIL</t>
+          <t>BLUESTONE</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -3048,22 +3168,22 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>115.99</v>
+        <v>890.35</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>65</v>
+        <v>65.3</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>54.94</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>46.09</v>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>AKUMS</t>
+          <t>TDPOWERSYS</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -3072,22 +3192,22 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>780.55</v>
+        <v>804.9</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>64.91</v>
+        <v>65.29000000000001</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>73.13</v>
+        <v>73.3</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>64.22</v>
+        <v>80.13</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>SKIPPER</t>
+          <t>AWFIS</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -3096,22 +3216,22 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>591.1</v>
+        <v>293.2</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>64.8</v>
+        <v>64.72</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>67.53</v>
+        <v>44.64</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>64.61</v>
+        <v>34.19</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>JKPAPER</t>
+          <t>DYNAMATECH</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -3120,22 +3240,22 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>410.15</v>
+        <v>12097</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>64.76000000000001</v>
+        <v>64.64</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>63.93</v>
+        <v>62.02</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>56.05</v>
+        <v>68.84</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>RELIGARE</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -3144,22 +3264,22 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>868.1</v>
+        <v>258.78</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>64.5</v>
+        <v>64.37</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>64.91</v>
+        <v>56.56</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>59.58</v>
+        <v>54.68</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>VOLTAMP</t>
+          <t>MIDHANI</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -3168,22 +3288,22 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>11182</v>
+        <v>463.35</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>64.31999999999999</v>
+        <v>63.82</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>67.45</v>
+        <v>62.02</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>60.39</v>
+        <v>58.15</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>MSTCLTD</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -3192,22 +3312,22 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>744.25</v>
+        <v>370.3</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>64.23999999999999</v>
+        <v>63.75</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>66.89</v>
+        <v>72.97</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>60.42</v>
+        <v>67.38</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>RELIGARE</t>
+          <t>VARROC</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -3216,22 +3336,22 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>257.08</v>
+        <v>872</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>64.22</v>
+        <v>63.68</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>56.69</v>
+        <v>78.3</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>54.73</v>
+        <v>71.09</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>INDIGOPNTS</t>
+          <t>TEXRAIL</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -3240,22 +3360,22 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>1185.8</v>
+        <v>117.81</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>63.99</v>
+        <v>63.66</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>68.45999999999999</v>
+        <v>57.17</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>51.75</v>
+        <v>46.85</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>AXISCADES</t>
+          <t>TSFINV</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -3264,22 +3384,22 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>1730.4</v>
+        <v>441.15</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>63.93</v>
+        <v>63.15</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>53.24</v>
+        <v>53.4</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>61.8</v>
+        <v>55.16</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>IONEXCHANG</t>
+          <t>INOXINDIA</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -3288,22 +3408,22 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>409.2</v>
+        <v>2246.6</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>63.45</v>
+        <v>63.04</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>54.14</v>
+        <v>81.04000000000001</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>48.37</v>
+        <v>84.12</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>QUESS</t>
+          <t>NESCO</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -3312,22 +3432,22 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>366.55</v>
+        <v>1102.2</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>63.19</v>
+        <v>62.99</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>72.03</v>
+        <v>49.58</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>51.8</v>
+        <v>52.51</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>STAR</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -3336,22 +3456,22 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>1059.6</v>
+        <v>2200.8</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>62.81</v>
+        <v>62.85</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>55.24</v>
+        <v>75.48</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>58.26</v>
+        <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>ATLANTAELE</t>
+          <t>YATHARTH</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -3360,22 +3480,22 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>1881.7</v>
+        <v>977.2</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>62.38</v>
+        <v>62.5</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>62.3</v>
+        <v>65.75</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v/>
+        <v>65.73</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>ELLEN</t>
+          <t>EMIL</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -3384,22 +3504,22 @@
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>331.85</v>
+        <v>188.38</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>61.95</v>
+        <v>62.19</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>59.39</v>
+        <v>71.45</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>37.21</v>
+        <v>61.75</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>METROPOLIS</t>
+          <t>SUPRIYA</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -3408,22 +3528,22 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>591.9</v>
+        <v>901.75</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>61.81</v>
+        <v>62.09</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>62.38</v>
+        <v>58.25</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>63.42</v>
+        <v>60.04</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>SUDARSCHEM</t>
+          <t>JKPAPER</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -3432,22 +3552,22 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>1222.8</v>
+        <v>415.15</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>61.61</v>
+        <v>62</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>66.95999999999999</v>
+        <v>66.12</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>59.49</v>
+        <v>57.04</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>CRIZAC</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -3456,22 +3576,22 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>326.75</v>
+        <v>186.68</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>61.53</v>
+        <v>61.94</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>73.34</v>
+        <v>43.88</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>67.39</v>
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>CUPID</t>
+          <t>SKYGOLD</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -3480,22 +3600,22 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>283.15</v>
+        <v>827.4</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>61.48</v>
+        <v>61.5</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>86.83</v>
+        <v>78.54000000000001</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>93.11</v>
+        <v>82.26000000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>SMARTWORKS</t>
+          <t>QPOWER</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -3504,22 +3624,22 @@
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>531.4</v>
+        <v>1458.2</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>61.34</v>
+        <v>60.88</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>66.36</v>
+        <v>63.31</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v/>
+        <v>68.16</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GPPL</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -3528,22 +3648,22 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>161.62</v>
+        <v>1584.6</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>61.26</v>
+        <v>60.67</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>54.22</v>
+        <v>69.86</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>KRBL</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -3552,22 +3672,22 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>424.9</v>
+        <v>329.4</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>61.17</v>
+        <v>60.52</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>63.41</v>
+        <v>73.78</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>58.4</v>
+        <v>67.64</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>SOUTHBANK</t>
+          <t>AZAD</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -3576,22 +3696,22 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>47.29</v>
+        <v>2849.1</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>60.66</v>
+        <v>60.41</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>62.77</v>
+        <v>69.16</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>71.06999999999999</v>
+        <v>72.58</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>HERITGFOOD</t>
+          <t>AARTIDRUGS</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -3600,22 +3720,22 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>382.35</v>
+        <v>437</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>60.26</v>
+        <v>60.41</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>59.96</v>
+        <v>60.76</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>50.68</v>
+        <v>50.82</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>AKUMS</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -3624,22 +3744,22 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>111.65</v>
+        <v>776.35</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>59.85</v>
+        <v>60.32</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>53.03</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>43.95</v>
+        <v>65.41</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>LUMAXTECH</t>
+          <t>GPPL</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -3648,22 +3768,22 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>1985.4</v>
+        <v>162.27</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>59.5</v>
+        <v>60.18</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>63.55</v>
+        <v>58.6</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>68.02</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>METROPOLIS</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -3672,22 +3792,22 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>562.5</v>
+        <v>595.65</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>59.17</v>
+        <v>59.96</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>65.63</v>
+        <v>61.47</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>68.67</v>
+        <v>63.1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>DIACABS</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -3696,22 +3816,22 @@
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>1654.7</v>
+        <v>351.5</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>58.89</v>
+        <v>59.7</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>70.88</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>75.69</v>
+        <v>81.81</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>LOTUSDEV</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -3720,22 +3840,22 @@
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>184.64</v>
+        <v>332.55</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>58.1</v>
+        <v>59.29</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>63.28</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v/>
+        <v>73.34</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>VARROC</t>
+          <t>CCAVENUE</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -3744,22 +3864,22 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>826.35</v>
+        <v>16.29</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>58.04</v>
+        <v>58.88</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>75.22</v>
+        <v>52.8</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>67.31</v>
+        <v>45.57</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>AZAD</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -3768,22 +3888,22 @@
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>2766.9</v>
+        <v>569.8</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>57.78</v>
+        <v>58.48</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>67.7</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>70.53</v>
+        <v>70</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>RUBICON</t>
+          <t>BECTORFOOD</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -3792,22 +3912,22 @@
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>1768.3</v>
+        <v>242.5</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>57.52</v>
+        <v>58.38</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>82.83</v>
+        <v>61.05</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v/>
+        <v>52.42</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>MTARTECH</t>
+          <t>ALIVUS</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -3816,22 +3936,22 @@
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>7161</v>
+        <v>1390.2</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>57.5</v>
+        <v>58.25</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>60.95</v>
+        <v>75.48</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>70.70999999999999</v>
+        <v>72.63</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>VMART</t>
+          <t>SUDEEPPHRM</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -3840,22 +3960,22 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>839.1</v>
+        <v>1213.5</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>57.35</v>
+        <v>58.13</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>63.09</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>55.53</v>
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>SFL</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -3864,22 +3984,22 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>2196.6</v>
+        <v>697.95</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>56.96</v>
+        <v>57.77</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>80.55</v>
+        <v>54.25</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>76.18000000000001</v>
+        <v>48</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>ORKLAINDIA</t>
+          <t>EDELWEISS</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -3888,22 +4008,22 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>588.5</v>
+        <v>132.43</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>56.72</v>
+        <v>57.57</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>48.97</v>
+        <v>62.07</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v/>
+        <v>62.98</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>MAHSCOOTER</t>
+          <t>SMARTWORKS</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -3912,22 +4032,22 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>13639</v>
+        <v>535.55</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>56.67</v>
+        <v>57.42</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>54.98</v>
+        <v>63.04</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>58.39</v>
+        <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>CUPID</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -3936,22 +4056,22 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>740.1</v>
+        <v>280</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>56.65</v>
+        <v>57.38</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>68.94</v>
+        <v>84.8</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>75.19</v>
+        <v>92.84</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>BALUFORGE</t>
+          <t>KRBL</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -3960,22 +4080,22 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>574.1</v>
+        <v>423.25</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>56.63</v>
+        <v>57.32</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>59.24</v>
+        <v>63.1</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>52.64</v>
+        <v>58.28</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>RBA</t>
+          <t>TMB</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -3984,22 +4104,22 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>97.89</v>
+        <v>910.9</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>56.54</v>
+        <v>56.85</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>68.2</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>58.43</v>
+        <v>76.06</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GSFC</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -4008,22 +4128,22 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>161.86</v>
+        <v>2227</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>56.5</v>
+        <v>56.74</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>48.22</v>
+        <v>81.87</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>45.69</v>
+        <v>78.70999999999999</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>AGARWALEYE</t>
+          <t>RENUKA</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -4032,22 +4152,22 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>514.1</v>
+        <v>24.87</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>56.39</v>
+        <v>56.7</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>58.62</v>
+        <v>53.09</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>58.77</v>
+        <v>41.29</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>SUPRIYA</t>
+          <t>MSTCLTD</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -4056,22 +4176,22 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>852.85</v>
+        <v>737.55</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>56.35</v>
+        <v>56.65</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>54.35</v>
+        <v>67.2</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>58.15</v>
+        <v>60.69</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>ELECTCAST</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -4080,22 +4200,22 @@
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>2127.8</v>
+        <v>79.86</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>56.28</v>
+        <v>56.43</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>69.78</v>
+        <v>50.82</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v/>
+        <v>44.55</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>VGUARD</t>
+          <t>SKFINDUS</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -4104,22 +4224,22 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>335.4</v>
+        <v>2935.4</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>56.27</v>
+        <v>56.34</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>59.03</v>
+        <v>61.79</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>49.62</v>
+        <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>AARTIDRUGS</t>
+          <t>RUBICON</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -4128,22 +4248,22 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>425.85</v>
+        <v>1790</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>56.17</v>
+        <v>56.27</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>62.21</v>
+        <v>84.27</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>51.19</v>
+        <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>RAIN</t>
+          <t>TARC</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -4152,22 +4272,22 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>215.72</v>
+        <v>128.56</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>55.99</v>
+        <v>56.23</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>65.51000000000001</v>
+        <v>50.17</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>60.38</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>FEDFINA</t>
+          <t>TARC</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -4176,22 +4296,22 @@
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>157.86</v>
+        <v>128.56</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>55.76</v>
+        <v>56.23</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>59.9</v>
+        <v>50.17</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>60.67</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>TARC</t>
+          <t>MTARTECH</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -4200,22 +4320,22 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>126.99</v>
+        <v>7312.5</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>55.71</v>
+        <v>56.22</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>46.99</v>
+        <v>62.12</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>46.38</v>
+        <v>71.23</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>TARC</t>
+          <t>WESTLIFE</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -4224,22 +4344,22 @@
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>126.99</v>
+        <v>569.6</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>55.71</v>
+        <v>55.79</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>46.99</v>
+        <v>58.18</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>46.38</v>
+        <v>45.46</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>JAIBALAJI</t>
+          <t>VOLTAMP</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -4248,22 +4368,22 @@
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>69.73</v>
+        <v>10924</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>55.64</v>
+        <v>55.73</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>50.5</v>
+        <v>64.8</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>42.95</v>
+        <v>59.78</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>DYNAMATECH</t>
+          <t>RAIN</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -4272,22 +4392,22 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>11532</v>
+        <v>217.28</v>
       </c>
       <c r="D81" s="4" t="n">
-        <v>55.45</v>
+        <v>55.68</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>59.18</v>
+        <v>65.59</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>66.26000000000001</v>
+        <v>60.41</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>JUSTDIAL</t>
+          <t>PGIL</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -4296,22 +4416,22 @@
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>697.35</v>
+        <v>1189.2</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>55.27</v>
+        <v>55.41</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>58.75</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>46.97</v>
+        <v>72.84999999999999</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>ALKYLAMINE</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -4320,22 +4440,22 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>2003.2</v>
+        <v>1640.3</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>55.24</v>
+        <v>54.82</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>66.03</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>54.57</v>
+        <v>79.05</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>IIFLCAPS</t>
+          <t>RBA</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -4344,22 +4464,22 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>338.05</v>
+        <v>98.05</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>54.78</v>
+        <v>54.75</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>55.95</v>
+        <v>68.73</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>58.44</v>
+        <v>58.95</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>SHRIPISTON</t>
+          <t>UTLSOLAR</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -4368,22 +4488,22 @@
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>4551.3</v>
+        <v>441.25</v>
       </c>
       <c r="D85" s="4" t="n">
-        <v>54.59</v>
+        <v>54.5</v>
       </c>
       <c r="E85" s="4" t="n">
-        <v>72.97</v>
+        <v>70.70999999999999</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>77.66</v>
+        <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>PRSMJOHNSN</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -4392,22 +4512,22 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>111.31</v>
+        <v>562.4</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>54.36</v>
+        <v>54.48</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>41.01</v>
+        <v>64.73</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>40.19</v>
+        <v>56.54</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>PRICOLLTD</t>
+          <t>PARAS</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -4416,22 +4536,22 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>768.4</v>
+        <v>1435.6</v>
       </c>
       <c r="D87" s="4" t="n">
-        <v>54.33</v>
+        <v>54.02</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>68.8</v>
+        <v>68.14</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>67.06999999999999</v>
+        <v>70.31</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>HCC</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -4440,22 +4560,22 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>22.98</v>
+        <v>207.11</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>54.26</v>
+        <v>54</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>52.7</v>
+        <v>51.66</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>47.52</v>
+        <v>44.92</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>ICIL</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -4464,22 +4584,22 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>437.35</v>
+        <v>622.4</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>54.03</v>
+        <v>53.58</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>65.95999999999999</v>
+        <v>71.48</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>63.63</v>
+        <v>66.56</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>VIPIND</t>
+          <t>LUMAXTECH</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -4488,22 +4608,22 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>310.35</v>
+        <v>1942.6</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>54.02</v>
+        <v>53.54</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>47.76</v>
+        <v>64.94</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>38.53</v>
+        <v>69.39</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>PARAS</t>
+          <t>ICIL</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -4512,22 +4632,22 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>1411.5</v>
+        <v>439.45</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>53.96</v>
+        <v>53.4</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>67.41</v>
+        <v>64.42</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>69.37</v>
+        <v>62.82</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>SHAILY</t>
+          <t>FEDFINA</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -4536,22 +4656,22 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>3267.1</v>
+        <v>158.88</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>53.82</v>
+        <v>53.14</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>66.7</v>
+        <v>56.66</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>73.51000000000001</v>
+        <v>59.67</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>PARKHOSPS</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -4560,22 +4680,22 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>286.7</v>
+        <v>108.35</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>53.69</v>
+        <v>52.78</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>63.88</v>
+        <v>50.42</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v/>
+        <v>42.88</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>EMIL</t>
+          <t>ARVINDFASN</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -4584,22 +4704,22 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>173.74</v>
+        <v>453.4</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>53.35</v>
+        <v>52.37</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>67.48999999999999</v>
+        <v>46.73</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>58.58</v>
+        <v>48.73</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>LXCHEM</t>
+          <t>GSFC</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -4608,22 +4728,22 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>175.58</v>
+        <v>155.95</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>53.34</v>
+        <v>52.32</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>56.99</v>
+        <v>46.12</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>45.76</v>
+        <v>45.02</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>RENUKA</t>
+          <t>ATLANTAELE</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -4632,22 +4752,22 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>24.04</v>
+        <v>1805.4</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>53.14</v>
+        <v>52.32</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>49.39</v>
+        <v>57.41</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>40.29</v>
+        <v/>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>SANSERA</t>
+          <t>TVSSCS</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -4656,22 +4776,22 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>3789.6</v>
+        <v>130.49</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>52.95</v>
+        <v>52.3</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>76.17</v>
+        <v>53.36</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>78.48</v>
+        <v>47.41</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>PRICOLLTD</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -4680,22 +4800,22 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>618.85</v>
+        <v>761.4</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>52.92</v>
+        <v>52.26</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>70.84</v>
+        <v>68.02</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>65.84</v>
+        <v>66.72</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>BLUESTONE</t>
+          <t>BALAMINES</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -4704,22 +4824,22 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>804.9</v>
+        <v>2342.6</v>
       </c>
       <c r="D99" s="4" t="n">
-        <v>52.55</v>
+        <v>52.19</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>72.58</v>
+        <v>61.11</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v/>
+        <v>61.88</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>ASTRAMICRO</t>
+          <t>INOXGREEN</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -4728,22 +4848,22 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>1729</v>
+        <v>178.21</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>52.52</v>
+        <v>52.04</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>64.92</v>
+        <v>48.68</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>71.01000000000001</v>
+        <v>52.36</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>KIRLPNU</t>
+          <t>QUESS</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -4752,22 +4872,22 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>759.8</v>
+        <v>348</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>52.45</v>
+        <v>51.96</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>52.53</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>56.86</v>
+        <v>51.11</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>MASTEK</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -4776,16 +4896,16 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>1772.9</v>
+        <v>825.75</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>52.2</v>
+        <v>51.88</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>51.34</v>
+        <v>60.25</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>44.4</v>
+        <v>57.77</v>
       </c>
     </row>
     <row r="103">
@@ -4800,22 +4920,22 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>586.1</v>
+        <v>585.9</v>
       </c>
       <c r="D103" s="4" t="n">
-        <v>51.39</v>
+        <v>51.67</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>51.75</v>
+        <v>57.01</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>56.52</v>
+        <v>61.34</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>UTLSOLAR</t>
+          <t>TIPSMUSIC</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -4824,22 +4944,22 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>429.75</v>
+        <v>658.4</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>51.34</v>
+        <v>51.48</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>68.59</v>
+        <v>54.27</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v/>
+        <v>58.54</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>PRUDENT</t>
+          <t>PRIVISCL</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -4848,22 +4968,22 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>3328.5</v>
+        <v>3495.6</v>
       </c>
       <c r="D105" s="4" t="n">
-        <v>51.09</v>
+        <v>51.44</v>
       </c>
       <c r="E105" s="4" t="n">
-        <v>65.37</v>
+        <v>58.4</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>62.41</v>
+        <v>68.08</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>STYL</t>
+          <t>IIFLCAPS</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -4872,22 +4992,22 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>387.05</v>
+        <v>337.3</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>51.01</v>
+        <v>50.96</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>61.71</v>
+        <v>54.67</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v/>
+        <v>58.2</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>VIYASH</t>
+          <t>SHAILY</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -4896,22 +5016,22 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>265.85</v>
+        <v>3279.5</v>
       </c>
       <c r="D107" s="4" t="n">
-        <v>50.8</v>
+        <v>50.88</v>
       </c>
       <c r="E107" s="4" t="n">
-        <v>56.52</v>
+        <v>66.8</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>62.97</v>
+        <v>73.56</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>PNGJL</t>
+          <t>AGARWALEYE</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -4920,22 +5040,22 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>609.05</v>
+        <v>508.4</v>
       </c>
       <c r="D108" s="4" t="n">
-        <v>50.78</v>
+        <v>50.8</v>
       </c>
       <c r="E108" s="4" t="n">
-        <v>51.4</v>
+        <v>56.96</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>49.82</v>
+        <v>57.76</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>EPL</t>
+          <t>STARCEMENT</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -4944,22 +5064,22 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>246.55</v>
+        <v>194.68</v>
       </c>
       <c r="D109" s="4" t="n">
-        <v>50.64</v>
+        <v>50.75</v>
       </c>
       <c r="E109" s="4" t="n">
-        <v>57.75</v>
+        <v>39.36</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>57.44</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>HCG</t>
+          <t>PRUDENT</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -4968,22 +5088,22 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>703.45</v>
+        <v>3318.8</v>
       </c>
       <c r="D110" s="4" t="n">
-        <v>50.51</v>
+        <v>50.68</v>
       </c>
       <c r="E110" s="4" t="n">
-        <v>62.12</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>62.54</v>
+        <v>63.09</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>CCAVENUE</t>
+          <t>STYL</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -4992,22 +5112,22 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>15.7</v>
+        <v>385.9</v>
       </c>
       <c r="D111" s="4" t="n">
-        <v>50.49</v>
+        <v>50.59</v>
       </c>
       <c r="E111" s="4" t="n">
-        <v>49.88</v>
+        <v>62.36</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>44.08</v>
+        <v/>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>TVSSCS</t>
+          <t>PNGJL</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -5016,22 +5136,22 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>129.53</v>
+        <v>611.05</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>50.47</v>
+        <v>50.57</v>
       </c>
       <c r="E112" s="4" t="n">
-        <v>53.31</v>
+        <v>52.04</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>47.38</v>
+        <v>50.19</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>CAMPUS</t>
+          <t>HCC</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -5040,22 +5160,22 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>223.97</v>
+        <v>22.73</v>
       </c>
       <c r="D113" s="4" t="n">
-        <v>50.32</v>
+        <v>50.34</v>
       </c>
       <c r="E113" s="4" t="n">
-        <v>42.56</v>
+        <v>51.97</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>41.67</v>
+        <v>47.28</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>APOLLO</t>
+          <t>SOUTHBANK</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -5064,22 +5184,22 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>388.9</v>
+        <v>46.08</v>
       </c>
       <c r="D114" s="4" t="n">
-        <v>50.23</v>
+        <v>50.29</v>
       </c>
       <c r="E114" s="4" t="n">
-        <v>57.43</v>
+        <v>58.8</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>67.37</v>
+        <v>70.04000000000001</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>MIDHANI</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -5088,22 +5208,22 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>418.8</v>
+        <v>535.75</v>
       </c>
       <c r="D115" s="4" t="n">
-        <v>50.21</v>
+        <v>50.16</v>
       </c>
       <c r="E115" s="4" t="n">
-        <v>55.68</v>
+        <v>58.9</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>55.63</v>
+        <v>61.93</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>WABAG</t>
+          <t>VMART</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -5112,22 +5232,22 @@
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>2005.3</v>
+        <v>817.8</v>
       </c>
       <c r="D116" s="4" t="n">
-        <v>50.11</v>
+        <v>49.97</v>
       </c>
       <c r="E116" s="4" t="n">
-        <v>61.52</v>
+        <v>60.41</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>67.51000000000001</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>GRWRHITECH</t>
+          <t>VGUARD</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -5136,22 +5256,22 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>7100</v>
+        <v>328.75</v>
       </c>
       <c r="D117" s="4" t="n">
-        <v>50.11</v>
+        <v>49.95</v>
       </c>
       <c r="E117" s="4" t="n">
-        <v>72.06999999999999</v>
+        <v>52.08</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>69.42</v>
+        <v>47.42</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>GHCL</t>
+          <t>ADVENZYMES</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -5160,22 +5280,22 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>437.55</v>
+        <v>303.35</v>
       </c>
       <c r="D118" s="4" t="n">
-        <v>50.04</v>
+        <v>49.85</v>
       </c>
       <c r="E118" s="4" t="n">
-        <v>42.69</v>
+        <v>40.55</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>42.2</v>
+        <v>46.22</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>OPTIEMUS</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -5184,22 +5304,22 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>535.1</v>
+        <v>566.25</v>
       </c>
       <c r="D119" s="4" t="n">
-        <v>49.87</v>
+        <v>49.84</v>
       </c>
       <c r="E119" s="4" t="n">
-        <v>62.2</v>
+        <v>58.09</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>63.54</v>
+        <v>54.59</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>ASHOKA</t>
+          <t>HCG</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -5208,22 +5328,22 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>117.32</v>
+        <v>700.9</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>49.82</v>
+        <v>49.72</v>
       </c>
       <c r="E120" s="4" t="n">
-        <v>38.23</v>
+        <v>60.29</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>41.18</v>
+        <v>61.82</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>SAATVIKGL</t>
+          <t>ORKLAINDIA</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -5232,13 +5352,13 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>424.4</v>
+        <v>578.5</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>49.7</v>
+        <v>49.61</v>
       </c>
       <c r="E121" s="4" t="n">
-        <v>46.84</v>
+        <v>48.18</v>
       </c>
       <c r="F121" s="4" t="n">
         <v/>
@@ -5247,7 +5367,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>SENCO</t>
+          <t>SHAKTIPUMP</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -5256,22 +5376,22 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>358.65</v>
+        <v>493.8</v>
       </c>
       <c r="D122" s="4" t="n">
-        <v>49.45</v>
+        <v>49.53</v>
       </c>
       <c r="E122" s="4" t="n">
-        <v>53.31</v>
+        <v>39.57</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>50.76</v>
+        <v>44.03</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>NESCO</t>
+          <t>JAIBALAJI</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -5280,22 +5400,22 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>1044.8</v>
+        <v>67.53</v>
       </c>
       <c r="D123" s="4" t="n">
-        <v>49.42</v>
+        <v>49.41</v>
       </c>
       <c r="E123" s="4" t="n">
-        <v>42.41</v>
+        <v>46.45</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>49.59</v>
+        <v>41.81</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>ETHOSLTD</t>
+          <t>BANCOINDIA</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -5304,22 +5424,22 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>2793.1</v>
+        <v>619.5</v>
       </c>
       <c r="D124" s="4" t="n">
-        <v>49.03</v>
+        <v>48.67</v>
       </c>
       <c r="E124" s="4" t="n">
-        <v>59.17</v>
+        <v>48.12</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>55.24</v>
+        <v>56.46</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>PGIL</t>
+          <t>BAJAJELEC</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -5328,22 +5448,22 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>2278.3</v>
+        <v>337.75</v>
       </c>
       <c r="D125" s="4" t="n">
-        <v>48.9</v>
+        <v>48.52</v>
       </c>
       <c r="E125" s="4" t="n">
-        <v>64.98999999999999</v>
+        <v>42.08</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>69.62</v>
+        <v>30.94</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>NEOGEN</t>
+          <t>AVL</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -5352,22 +5472,22 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>2137.1</v>
+        <v>603.55</v>
       </c>
       <c r="D126" s="4" t="n">
-        <v>48.59</v>
+        <v>48.32</v>
       </c>
       <c r="E126" s="4" t="n">
-        <v>63.13</v>
+        <v>58.29</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>61.41</v>
+        <v>62.35</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>INOXGREEN</t>
+          <t>KNRCON</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -5376,22 +5496,22 @@
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>175.1</v>
+        <v>123.68</v>
       </c>
       <c r="D127" s="4" t="n">
-        <v>48.51</v>
+        <v>48.13</v>
       </c>
       <c r="E127" s="4" t="n">
-        <v>47.19</v>
+        <v>45.42</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>51.89</v>
+        <v>35.25</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>KNRCON</t>
+          <t>PURVA</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -5400,22 +5520,22 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>124.66</v>
+        <v>214.16</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>48.37</v>
+        <v>48.05</v>
       </c>
       <c r="E128" s="4" t="n">
-        <v>44.69</v>
+        <v>46.83</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>34.95</v>
+        <v>44.77</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>TIPSMUSIC</t>
+          <t>SKIPPER</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -5424,22 +5544,22 @@
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>652.05</v>
+        <v>551.55</v>
       </c>
       <c r="D129" s="4" t="n">
-        <v>48.24</v>
+        <v>47.94</v>
       </c>
       <c r="E129" s="4" t="n">
-        <v>52.43</v>
+        <v>58.07</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>57.65</v>
+        <v>61.73</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>PRAJIND</t>
+          <t>SHRIPISTON</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -5448,22 +5568,22 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>335.55</v>
+        <v>4447.4</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>48.2</v>
+        <v>47.84</v>
       </c>
       <c r="E130" s="4" t="n">
-        <v>48.13</v>
+        <v>65.56</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>43.35</v>
+        <v>73.76000000000001</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>OPTIEMUS</t>
+          <t>DBL</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -5472,22 +5592,22 @@
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>564.85</v>
+        <v>407.75</v>
       </c>
       <c r="D131" s="4" t="n">
-        <v>48.03</v>
+        <v>47.51</v>
       </c>
       <c r="E131" s="4" t="n">
-        <v>58.58</v>
+        <v>42.7</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>54.77</v>
+        <v>45.72</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>GAEL</t>
+          <t>LXCHEM</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -5496,22 +5616,22 @@
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>167.81</v>
+        <v>170.63</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>47.62</v>
+        <v>47.42</v>
       </c>
       <c r="E132" s="4" t="n">
-        <v>58.08</v>
+        <v>59.02</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>63.18</v>
+        <v>46.64</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>THYROCARE</t>
+          <t>APLLTD</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -5520,22 +5640,22 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>578.65</v>
+        <v>810.95</v>
       </c>
       <c r="D133" s="4" t="n">
-        <v>47.55</v>
+        <v>47.4</v>
       </c>
       <c r="E133" s="4" t="n">
-        <v>61.22</v>
+        <v>54.84</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>66.92</v>
+        <v>48.69</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>SAFARI</t>
+          <t>INDIASHLTR</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -5544,22 +5664,22 @@
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>1509.5</v>
+        <v>672.15</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>47.53</v>
+        <v>47.29</v>
       </c>
       <c r="E134" s="4" t="n">
-        <v>44.67</v>
+        <v>35.28</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>42.03</v>
+        <v>39.84</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>KIRLOSBROS</t>
+          <t>BALUFORGE</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -5568,22 +5688,22 @@
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>1881.3</v>
+        <v>536.65</v>
       </c>
       <c r="D135" s="4" t="n">
-        <v>47.27</v>
+        <v>47.19</v>
       </c>
       <c r="E135" s="4" t="n">
-        <v>54.67</v>
+        <v>53.66</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>54.55</v>
+        <v>50.57</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>INDIASHLTR</t>
+          <t>STYRENIX</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -5592,22 +5712,22 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>673.1</v>
+        <v>2113.1</v>
       </c>
       <c r="D136" s="4" t="n">
-        <v>47.24</v>
+        <v>47.17</v>
       </c>
       <c r="E136" s="4" t="n">
-        <v>38.34</v>
+        <v>47.04</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>42.8</v>
+        <v>49.87</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>SKYGOLD</t>
+          <t>ASTRAMICRO</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -5616,22 +5736,22 @@
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>742</v>
+        <v>1680.6</v>
       </c>
       <c r="D137" s="4" t="n">
-        <v>47.17</v>
+        <v>47.08</v>
       </c>
       <c r="E137" s="4" t="n">
-        <v>76.04000000000001</v>
+        <v>61.43</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>78.78</v>
+        <v>70.15000000000001</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>KSB</t>
+          <t>UJJIVANSFB</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -5640,22 +5760,22 @@
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>810.6</v>
+        <v>66.52</v>
       </c>
       <c r="D138" s="4" t="n">
-        <v>47.08</v>
+        <v>47.06</v>
       </c>
       <c r="E138" s="4" t="n">
-        <v>46.71</v>
+        <v>54.96</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>52.02</v>
+        <v>60.72</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>ARVINDFASN</t>
+          <t>RAYMONDLSL</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -5664,22 +5784,22 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>446.5</v>
+        <v>687.65</v>
       </c>
       <c r="D139" s="4" t="n">
-        <v>46.99</v>
+        <v>47.06</v>
       </c>
       <c r="E139" s="4" t="n">
-        <v>46.73</v>
+        <v>38</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>48.73</v>
+        <v>25.89</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>AVL</t>
+          <t>WEWORK</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -5688,22 +5808,22 @@
         </is>
       </c>
       <c r="C140" s="4" t="n">
-        <v>600.4</v>
+        <v>676.95</v>
       </c>
       <c r="D140" s="4" t="n">
-        <v>46.75</v>
+        <v>46.29</v>
       </c>
       <c r="E140" s="4" t="n">
-        <v>55.48</v>
+        <v>54.12</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>60.69</v>
+        <v/>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>V2RETAIL</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -5712,22 +5832,22 @@
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>156.29</v>
+        <v>218.13</v>
       </c>
       <c r="D141" s="4" t="n">
-        <v>46.65</v>
+        <v>46.18</v>
       </c>
       <c r="E141" s="4" t="n">
-        <v>48.73</v>
+        <v>50.41</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>53.93</v>
+        <v>62.44</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>SHAREINDIA</t>
+          <t>GMRP&amp;UI</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -5736,22 +5856,22 @@
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>169.27</v>
+        <v>94.06999999999999</v>
       </c>
       <c r="D142" s="4" t="n">
-        <v>46.57</v>
+        <v>46.14</v>
       </c>
       <c r="E142" s="4" t="n">
-        <v>56.58</v>
+        <v>39.3</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>47.48</v>
+        <v>48.44</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>AEQUS</t>
+          <t>PARKHOSPS</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -5760,13 +5880,13 @@
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>242.18</v>
+        <v>279.3</v>
       </c>
       <c r="D143" s="4" t="n">
-        <v>46.53</v>
+        <v>45.96</v>
       </c>
       <c r="E143" s="4" t="n">
-        <v>63.91</v>
+        <v>60.05</v>
       </c>
       <c r="F143" s="4" t="n">
         <v/>
@@ -5775,7 +5895,7 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>JSFB</t>
+          <t>BBOX</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -5784,22 +5904,22 @@
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>535.1</v>
+        <v>744.85</v>
       </c>
       <c r="D144" s="4" t="n">
-        <v>46.46</v>
+        <v>45.9</v>
       </c>
       <c r="E144" s="4" t="n">
-        <v>58.54</v>
+        <v>53.38</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>56.98</v>
+        <v>60.96</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>TRIVENI</t>
+          <t>VIPIND</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -5808,22 +5928,22 @@
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>280.5</v>
+        <v>301.55</v>
       </c>
       <c r="D145" s="4" t="n">
-        <v>46.4</v>
+        <v>45.73</v>
       </c>
       <c r="E145" s="4" t="n">
-        <v>39.8</v>
+        <v>42.74</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>43.24</v>
+        <v>36.29</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>EUREKAFORB</t>
+          <t>JUSTDIAL</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -5832,22 +5952,22 @@
         </is>
       </c>
       <c r="C146" s="4" t="n">
-        <v>429.25</v>
+        <v>668.75</v>
       </c>
       <c r="D146" s="4" t="n">
-        <v>46.4</v>
+        <v>45.42</v>
       </c>
       <c r="E146" s="4" t="n">
-        <v>39.66</v>
+        <v>54.17</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>38.75</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>SKFINDIA</t>
+          <t>JSLL</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -5856,22 +5976,22 @@
         </is>
       </c>
       <c r="C147" s="4" t="n">
-        <v>1540.6</v>
+        <v>511.85</v>
       </c>
       <c r="D147" s="4" t="n">
-        <v>46.32</v>
+        <v>45.4</v>
       </c>
       <c r="E147" s="4" t="n">
-        <v>39.12</v>
+        <v>38.89</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>32.7</v>
+        <v>40.72</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>BECTORFOOD</t>
+          <t>SAMHI</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -5880,22 +6000,22 @@
         </is>
       </c>
       <c r="C148" s="4" t="n">
-        <v>225.96</v>
+        <v>157.07</v>
       </c>
       <c r="D148" s="4" t="n">
-        <v>45.76</v>
+        <v>45.29</v>
       </c>
       <c r="E148" s="4" t="n">
-        <v>56</v>
+        <v>44.11</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>49.16</v>
+        <v>45.12</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>GOKULAGRO</t>
+          <t>SAFARI</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -5904,22 +6024,22 @@
         </is>
       </c>
       <c r="C149" s="4" t="n">
-        <v>231.17</v>
+        <v>1501.6</v>
       </c>
       <c r="D149" s="4" t="n">
-        <v>45.75</v>
+        <v>45.18</v>
       </c>
       <c r="E149" s="4" t="n">
-        <v>57.73</v>
+        <v>45</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>63.86</v>
+        <v>42.17</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>BAJAJELEC</t>
+          <t>JAYNECOIND</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -5928,22 +6048,22 @@
         </is>
       </c>
       <c r="C150" s="4" t="n">
-        <v>334.2</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="D150" s="4" t="n">
-        <v>45.74</v>
+        <v>45.16</v>
       </c>
       <c r="E150" s="4" t="n">
-        <v>40.53</v>
+        <v>50.42</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>30.43</v>
+        <v>58.93</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>TIMETECHNO</t>
+          <t>KSB</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -5952,22 +6072,22 @@
         </is>
       </c>
       <c r="C151" s="4" t="n">
-        <v>189.36</v>
+        <v>804.2</v>
       </c>
       <c r="D151" s="4" t="n">
-        <v>45.47</v>
+        <v>45.08</v>
       </c>
       <c r="E151" s="4" t="n">
-        <v>49.91</v>
+        <v>45.44</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>52.4</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>SPARC</t>
+          <t>GAEL</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -5976,22 +6096,22 @@
         </is>
       </c>
       <c r="C152" s="4" t="n">
-        <v>199.47</v>
+        <v>164.8</v>
       </c>
       <c r="D152" s="4" t="n">
-        <v>45.29</v>
+        <v>44.94</v>
       </c>
       <c r="E152" s="4" t="n">
-        <v>52.27</v>
+        <v>54.63</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>53.63</v>
+        <v>60.62</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>WESTLIFE</t>
+          <t>EPL</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -6000,46 +6120,46 @@
         </is>
       </c>
       <c r="C153" s="4" t="n">
-        <v>540.55</v>
+        <v>239.3</v>
       </c>
       <c r="D153" s="4" t="n">
-        <v>44.91</v>
+        <v>44.75</v>
       </c>
       <c r="E153" s="4" t="n">
-        <v>52.57</v>
+        <v>53.9</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>42.02</v>
+        <v>55.47</v>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="5" t="inlineStr">
-        <is>
-          <t>DIACABS</t>
-        </is>
-      </c>
-      <c r="B154" s="6" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C154" s="7" t="n">
-        <v>322.9</v>
-      </c>
-      <c r="D154" s="7" t="n">
-        <v>44.88</v>
-      </c>
-      <c r="E154" s="7" t="n">
-        <v>73.64</v>
-      </c>
-      <c r="F154" s="7" t="n">
-        <v>76.73</v>
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>VIYASH</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="n">
+        <v>257.6</v>
+      </c>
+      <c r="D154" s="4" t="n">
+        <v>44.59</v>
+      </c>
+      <c r="E154" s="4" t="n">
+        <v>53.52</v>
+      </c>
+      <c r="F154" s="4" t="n">
+        <v>61.24</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>APLLTD</t>
+          <t>SKFINDIA</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -6048,22 +6168,22 @@
         </is>
       </c>
       <c r="C155" s="4" t="n">
-        <v>803.65</v>
+        <v>1531.6</v>
       </c>
       <c r="D155" s="4" t="n">
-        <v>44.59</v>
+        <v>44.54</v>
       </c>
       <c r="E155" s="4" t="n">
-        <v>54.29</v>
+        <v>37.52</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>48.53</v>
+        <v>32.48</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>FINPIPE</t>
+          <t>ZAGGLE</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -6072,22 +6192,22 @@
         </is>
       </c>
       <c r="C156" s="4" t="n">
-        <v>158.9</v>
+        <v>183.93</v>
       </c>
       <c r="D156" s="4" t="n">
-        <v>44.56</v>
+        <v>44.35</v>
       </c>
       <c r="E156" s="4" t="n">
-        <v>39.23</v>
+        <v>35.26</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>41.51</v>
+        <v>38.14</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>VIKRAMSOLR</t>
+          <t>GOKEX</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -6096,46 +6216,46 @@
         </is>
       </c>
       <c r="C157" s="4" t="n">
-        <v>168.45</v>
+        <v>774.2</v>
       </c>
       <c r="D157" s="4" t="n">
-        <v>44.4</v>
+        <v>44.32</v>
       </c>
       <c r="E157" s="4" t="n">
-        <v>37.6</v>
+        <v>52.49</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v/>
+        <v>50.93</v>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="inlineStr">
-        <is>
-          <t>THANGAMAYL</t>
-        </is>
-      </c>
-      <c r="B158" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C158" s="4" t="n">
-        <v>5332</v>
-      </c>
-      <c r="D158" s="4" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="E158" s="4" t="n">
-        <v>55.26</v>
-      </c>
-      <c r="F158" s="4" t="n">
-        <v>69.16</v>
+      <c r="A158" s="5" t="inlineStr">
+        <is>
+          <t>GRWRHITECH</t>
+        </is>
+      </c>
+      <c r="B158" s="6" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C158" s="7" t="n">
+        <v>6905</v>
+      </c>
+      <c r="D158" s="7" t="n">
+        <v>44.15</v>
+      </c>
+      <c r="E158" s="7" t="n">
+        <v>67.72</v>
+      </c>
+      <c r="F158" s="7" t="n">
+        <v>67.95999999999999</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>SUNTECK</t>
+          <t>DATAMATICS</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -6144,22 +6264,22 @@
         </is>
       </c>
       <c r="C159" s="4" t="n">
-        <v>297.75</v>
+        <v>775.45</v>
       </c>
       <c r="D159" s="4" t="n">
-        <v>44.37</v>
+        <v>44.03</v>
       </c>
       <c r="E159" s="4" t="n">
-        <v>41.6</v>
+        <v>45.95</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>40.58</v>
+        <v>52.88</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>PURVA</t>
+          <t>SENCO</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -6168,22 +6288,22 @@
         </is>
       </c>
       <c r="C160" s="4" t="n">
-        <v>211.09</v>
+        <v>346.4</v>
       </c>
       <c r="D160" s="4" t="n">
-        <v>44.04</v>
+        <v>43.36</v>
       </c>
       <c r="E160" s="4" t="n">
-        <v>55.76</v>
+        <v>50.08</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>48.29</v>
+        <v>49.58</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>CSBBANK</t>
+          <t>SANDUMA</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -6192,22 +6312,22 @@
         </is>
       </c>
       <c r="C161" s="4" t="n">
-        <v>324.95</v>
+        <v>196.74</v>
       </c>
       <c r="D161" s="4" t="n">
-        <v>44.02</v>
+        <v>43.28</v>
       </c>
       <c r="E161" s="4" t="n">
-        <v>42.21</v>
+        <v>43.05</v>
       </c>
       <c r="F161" s="4" t="n">
-        <v>45.92</v>
+        <v>52.26</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>CENTURYPLY</t>
+          <t>PRAJIND</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -6216,22 +6336,22 @@
         </is>
       </c>
       <c r="C162" s="4" t="n">
-        <v>749.2</v>
+        <v>326.85</v>
       </c>
       <c r="D162" s="4" t="n">
-        <v>43.81</v>
+        <v>43.24</v>
       </c>
       <c r="E162" s="4" t="n">
-        <v>45.93</v>
+        <v>44.39</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>50.3</v>
+        <v>42.35</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>ROUTE</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -6240,22 +6360,22 @@
         </is>
       </c>
       <c r="C163" s="4" t="n">
-        <v>503.65</v>
+        <v>196.01</v>
       </c>
       <c r="D163" s="4" t="n">
-        <v>43.77</v>
+        <v>42.63</v>
       </c>
       <c r="E163" s="4" t="n">
-        <v>41.16</v>
+        <v>51.09</v>
       </c>
       <c r="F163" s="4" t="n">
-        <v>30.35</v>
+        <v>52.95</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>NFL</t>
+          <t>MAHSCOOTER</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -6264,22 +6384,22 @@
         </is>
       </c>
       <c r="C164" s="4" t="n">
-        <v>70.51000000000001</v>
+        <v>13098</v>
       </c>
       <c r="D164" s="4" t="n">
-        <v>43.69</v>
+        <v>42.47</v>
       </c>
       <c r="E164" s="4" t="n">
-        <v>39.56</v>
+        <v>49</v>
       </c>
       <c r="F164" s="4" t="n">
-        <v>42.51</v>
+        <v>54.96</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>JAMNAAUTO</t>
+          <t>ROUTE</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -6288,22 +6408,22 @@
         </is>
       </c>
       <c r="C165" s="4" t="n">
-        <v>122.04</v>
+        <v>500.75</v>
       </c>
       <c r="D165" s="4" t="n">
-        <v>43.47</v>
+        <v>42.45</v>
       </c>
       <c r="E165" s="4" t="n">
-        <v>46.51</v>
+        <v>39.66</v>
       </c>
       <c r="F165" s="4" t="n">
-        <v>53.23</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>ORIENTCEM</t>
+          <t>VIKRAMSOLR</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -6312,22 +6432,22 @@
         </is>
       </c>
       <c r="C166" s="4" t="n">
-        <v>129.68</v>
+        <v>165.61</v>
       </c>
       <c r="D166" s="4" t="n">
-        <v>43.37</v>
+        <v>42.43</v>
       </c>
       <c r="E166" s="4" t="n">
-        <v>35.44</v>
+        <v>37.08</v>
       </c>
       <c r="F166" s="4" t="n">
-        <v>35.03</v>
+        <v/>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>JYOTHYLAB</t>
+          <t>RATEGAIN</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -6336,22 +6456,22 @@
         </is>
       </c>
       <c r="C167" s="4" t="n">
-        <v>200.5</v>
+        <v>866.45</v>
       </c>
       <c r="D167" s="4" t="n">
-        <v>43.22</v>
+        <v>42.25</v>
       </c>
       <c r="E167" s="4" t="n">
-        <v>40.76</v>
+        <v>57.81</v>
       </c>
       <c r="F167" s="4" t="n">
-        <v>37.75</v>
+        <v>62.21</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>GREAVESCOT</t>
+          <t>LLOYDSENGG</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -6360,22 +6480,22 @@
         </is>
       </c>
       <c r="C168" s="4" t="n">
-        <v>195.56</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="D168" s="4" t="n">
-        <v>43.18</v>
+        <v>41.97</v>
       </c>
       <c r="E168" s="4" t="n">
-        <v>49.99</v>
+        <v>57.13</v>
       </c>
       <c r="F168" s="4" t="n">
-        <v>51.67</v>
+        <v>60.88</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>GREAVESCOT</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -6384,22 +6504,22 @@
         </is>
       </c>
       <c r="C169" s="4" t="n">
-        <v>495.2</v>
+        <v>193.6</v>
       </c>
       <c r="D169" s="4" t="n">
-        <v>42.87</v>
+        <v>41.92</v>
       </c>
       <c r="E169" s="4" t="n">
-        <v>41.64</v>
+        <v>48.73</v>
       </c>
       <c r="F169" s="4" t="n">
-        <v>42.07</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>V2RETAIL</t>
+          <t>ASHOKA</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -6408,22 +6528,22 @@
         </is>
       </c>
       <c r="C170" s="4" t="n">
-        <v>216.5</v>
+        <v>113.53</v>
       </c>
       <c r="D170" s="4" t="n">
-        <v>42.79</v>
+        <v>41.69</v>
       </c>
       <c r="E170" s="4" t="n">
-        <v>49.55</v>
+        <v>37.07</v>
       </c>
       <c r="F170" s="4" t="n">
-        <v>61.89</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>BANCOINDIA</t>
+          <t>AVANTIFEED</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -6432,22 +6552,22 @@
         </is>
       </c>
       <c r="C171" s="4" t="n">
-        <v>616.9</v>
+        <v>815.3</v>
       </c>
       <c r="D171" s="4" t="n">
-        <v>42.76</v>
+        <v>41.58</v>
       </c>
       <c r="E171" s="4" t="n">
-        <v>48.2</v>
+        <v>35.16</v>
       </c>
       <c r="F171" s="4" t="n">
-        <v>56.51</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>BIRLACORPN</t>
+          <t>THYROCARE</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -6456,22 +6576,22 @@
         </is>
       </c>
       <c r="C172" s="4" t="n">
-        <v>880.9</v>
+        <v>557.7</v>
       </c>
       <c r="D172" s="4" t="n">
-        <v>42.73</v>
+        <v>41.5</v>
       </c>
       <c r="E172" s="4" t="n">
-        <v>41.72</v>
+        <v>56.14</v>
       </c>
       <c r="F172" s="4" t="n">
-        <v>39.98</v>
+        <v>63.82</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>KITEX</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -6480,22 +6600,22 @@
         </is>
       </c>
       <c r="C173" s="4" t="n">
-        <v>128.85</v>
+        <v>152.78</v>
       </c>
       <c r="D173" s="4" t="n">
-        <v>42.54</v>
+        <v>41.32</v>
       </c>
       <c r="E173" s="4" t="n">
-        <v>34.99</v>
+        <v>46.91</v>
       </c>
       <c r="F173" s="4" t="n">
-        <v>43.69</v>
+        <v>52.74</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>SANDUMA</t>
+          <t>GOKULAGRO</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -6504,22 +6624,22 @@
         </is>
       </c>
       <c r="C174" s="4" t="n">
-        <v>197.83</v>
+        <v>226.4</v>
       </c>
       <c r="D174" s="4" t="n">
-        <v>42.21</v>
+        <v>40.94</v>
       </c>
       <c r="E174" s="4" t="n">
-        <v>46.23</v>
+        <v>55.18</v>
       </c>
       <c r="F174" s="4" t="n">
-        <v>53.99</v>
+        <v>62.68</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENGG</t>
+          <t>POWERMECH</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -6528,22 +6648,22 @@
         </is>
       </c>
       <c r="C175" s="4" t="n">
-        <v>84.20999999999999</v>
+        <v>2379.4</v>
       </c>
       <c r="D175" s="4" t="n">
-        <v>41.98</v>
+        <v>40.89</v>
       </c>
       <c r="E175" s="4" t="n">
-        <v>58.99</v>
+        <v>47.56</v>
       </c>
       <c r="F175" s="4" t="n">
-        <v>61.82</v>
+        <v>50</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>CRAMC</t>
+          <t>SHARDACROP</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -6552,22 +6672,22 @@
         </is>
       </c>
       <c r="C176" s="4" t="n">
-        <v>251.5</v>
+        <v>765.55</v>
       </c>
       <c r="D176" s="4" t="n">
-        <v>41.73</v>
+        <v>40.81</v>
       </c>
       <c r="E176" s="4" t="n">
-        <v>46.43</v>
+        <v>37.93</v>
       </c>
       <c r="F176" s="4" t="n">
-        <v/>
+        <v>49.47</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>TIMETECHNO</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -6576,22 +6696,22 @@
         </is>
       </c>
       <c r="C177" s="4" t="n">
-        <v>195.66</v>
+        <v>184.87</v>
       </c>
       <c r="D177" s="4" t="n">
-        <v>41.21</v>
+        <v>40.71</v>
       </c>
       <c r="E177" s="4" t="n">
-        <v>48.32</v>
+        <v>45.51</v>
       </c>
       <c r="F177" s="4" t="n">
-        <v>43.12</v>
+        <v>50.65</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>IFBIND</t>
+          <t>MASTEK</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -6600,22 +6720,22 @@
         </is>
       </c>
       <c r="C178" s="4" t="n">
-        <v>1311.8</v>
+        <v>1610</v>
       </c>
       <c r="D178" s="4" t="n">
-        <v>41.01</v>
+        <v>40.56</v>
       </c>
       <c r="E178" s="4" t="n">
-        <v>50.92</v>
+        <v>44.96</v>
       </c>
       <c r="F178" s="4" t="n">
-        <v>49.37</v>
+        <v>41.54</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>WEWORK</t>
+          <t>KIRLPNU</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -6624,22 +6744,22 @@
         </is>
       </c>
       <c r="C179" s="4" t="n">
-        <v>666.95</v>
+        <v>719.7</v>
       </c>
       <c r="D179" s="4" t="n">
-        <v>40.91</v>
+        <v>40.31</v>
       </c>
       <c r="E179" s="4" t="n">
-        <v>53.68</v>
+        <v>47.97</v>
       </c>
       <c r="F179" s="4" t="n">
-        <v/>
+        <v>55.05</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>JAYNECOIND</t>
+          <t>ALKYLAMINE</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -6648,22 +6768,22 @@
         </is>
       </c>
       <c r="C180" s="4" t="n">
-        <v>89.04000000000001</v>
+        <v>1867.5</v>
       </c>
       <c r="D180" s="4" t="n">
-        <v>40.78</v>
+        <v>40.02</v>
       </c>
       <c r="E180" s="4" t="n">
-        <v>49.64</v>
+        <v>54.54</v>
       </c>
       <c r="F180" s="4" t="n">
-        <v>58.5</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>KANSAINER</t>
+          <t>TRIVENI</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -6672,22 +6792,22 @@
         </is>
       </c>
       <c r="C181" s="4" t="n">
-        <v>195.11</v>
+        <v>263.95</v>
       </c>
       <c r="D181" s="4" t="n">
-        <v>40.69</v>
+        <v>39.81</v>
       </c>
       <c r="E181" s="4" t="n">
-        <v>43.1</v>
+        <v>37.49</v>
       </c>
       <c r="F181" s="4" t="n">
-        <v>39.48</v>
+        <v>41.79</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>ZAGGLE</t>
+          <t>FINPIPE</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -6696,22 +6816,22 @@
         </is>
       </c>
       <c r="C182" s="4" t="n">
-        <v>182.63</v>
+        <v>153.45</v>
       </c>
       <c r="D182" s="4" t="n">
-        <v>40.57</v>
+        <v>39.73</v>
       </c>
       <c r="E182" s="4" t="n">
-        <v>31.9</v>
+        <v>37.44</v>
       </c>
       <c r="F182" s="4" t="n">
-        <v>37.45</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>GOKEX</t>
+          <t>MEDPLUS</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -6720,22 +6840,22 @@
         </is>
       </c>
       <c r="C183" s="4" t="n">
-        <v>767.65</v>
+        <v>658.05</v>
       </c>
       <c r="D183" s="4" t="n">
-        <v>40.44</v>
+        <v>39.63</v>
       </c>
       <c r="E183" s="4" t="n">
-        <v>53.02</v>
+        <v>29.71</v>
       </c>
       <c r="F183" s="4" t="n">
-        <v>51.08</v>
+        <v>39.02</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>ADVENZYMES</t>
+          <t>JSFB</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -6744,22 +6864,22 @@
         </is>
       </c>
       <c r="C184" s="4" t="n">
-        <v>296</v>
+        <v>514.75</v>
       </c>
       <c r="D184" s="4" t="n">
-        <v>40.41</v>
+        <v>39.41</v>
       </c>
       <c r="E184" s="4" t="n">
-        <v>40.46</v>
+        <v>54.79</v>
       </c>
       <c r="F184" s="4" t="n">
-        <v>46.19</v>
+        <v>54.96</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>GRINDWELL</t>
+          <t>INDIGOPNTS</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -6768,16 +6888,16 @@
         </is>
       </c>
       <c r="C185" s="4" t="n">
-        <v>1974.4</v>
+        <v>1077.8</v>
       </c>
       <c r="D185" s="4" t="n">
-        <v>40.27</v>
+        <v>39.07</v>
       </c>
       <c r="E185" s="4" t="n">
-        <v>53.09</v>
+        <v>54.54</v>
       </c>
       <c r="F185" s="4" t="n">
-        <v>54.12</v>
+        <v>48.29</v>
       </c>
     </row>
     <row r="186">
@@ -6792,22 +6912,22 @@
         </is>
       </c>
       <c r="C186" s="4" t="n">
-        <v>73.04000000000001</v>
+        <v>72.63</v>
       </c>
       <c r="D186" s="4" t="n">
-        <v>40.25</v>
+        <v>39.01</v>
       </c>
       <c r="E186" s="4" t="n">
-        <v>52.14</v>
+        <v>52.46</v>
       </c>
       <c r="F186" s="4" t="n">
-        <v>53.39</v>
+        <v>53.54</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>CMSINFO</t>
+          <t>JYOTHYLAB</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -6816,22 +6936,22 @@
         </is>
       </c>
       <c r="C187" s="4" t="n">
-        <v>244.86</v>
+        <v>195.65</v>
       </c>
       <c r="D187" s="4" t="n">
-        <v>40.22</v>
+        <v>38.93</v>
       </c>
       <c r="E187" s="4" t="n">
-        <v>31.14</v>
+        <v>37.75</v>
       </c>
       <c r="F187" s="4" t="n">
-        <v>32.88</v>
+        <v>37.04</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>NETWORK18</t>
+          <t>KIRLOSBROS</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -6840,22 +6960,22 @@
         </is>
       </c>
       <c r="C188" s="4" t="n">
-        <v>27.55</v>
+        <v>1818.3</v>
       </c>
       <c r="D188" s="4" t="n">
-        <v>39.72</v>
+        <v>38.64</v>
       </c>
       <c r="E188" s="4" t="n">
-        <v>36.2</v>
+        <v>49.39</v>
       </c>
       <c r="F188" s="4" t="n">
-        <v>34.99</v>
+        <v>52.71</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>FIEMIND</t>
+          <t>ETHOSLTD</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -6864,22 +6984,22 @@
         </is>
       </c>
       <c r="C189" s="4" t="n">
-        <v>2085.8</v>
+        <v>2687.4</v>
       </c>
       <c r="D189" s="4" t="n">
-        <v>39.58</v>
+        <v>38.62</v>
       </c>
       <c r="E189" s="4" t="n">
-        <v>44.15</v>
+        <v>51.77</v>
       </c>
       <c r="F189" s="4" t="n">
-        <v>58.68</v>
+        <v>52.21</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>JSLL</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -6888,22 +7008,22 @@
         </is>
       </c>
       <c r="C190" s="4" t="n">
-        <v>501.45</v>
+        <v>5081.5</v>
       </c>
       <c r="D190" s="4" t="n">
-        <v>39.36</v>
+        <v>38.34</v>
       </c>
       <c r="E190" s="4" t="n">
-        <v>39.32</v>
+        <v>52.5</v>
       </c>
       <c r="F190" s="4" t="n">
-        <v>40.87</v>
+        <v>66.77</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>REFEX</t>
+          <t>SUBROS</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -6912,22 +7032,22 @@
         </is>
       </c>
       <c r="C191" s="4" t="n">
-        <v>282.55</v>
+        <v>709.6</v>
       </c>
       <c r="D191" s="4" t="n">
-        <v>39.33</v>
+        <v>38.25</v>
       </c>
       <c r="E191" s="4" t="n">
-        <v>46.45</v>
+        <v>41.04</v>
       </c>
       <c r="F191" s="4" t="n">
-        <v>48.47</v>
+        <v>48.61</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>SHARDACROP</t>
+          <t>IFBIND</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -6936,22 +7056,22 @@
         </is>
       </c>
       <c r="C192" s="4" t="n">
-        <v>768.35</v>
+        <v>1283.2</v>
       </c>
       <c r="D192" s="4" t="n">
-        <v>39.18</v>
+        <v>38.07</v>
       </c>
       <c r="E192" s="4" t="n">
-        <v>38.16</v>
+        <v>50.44</v>
       </c>
       <c r="F192" s="4" t="n">
-        <v>49.58</v>
+        <v>49.24</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>AWFIS</t>
+          <t>WEBELSOLAR</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -6960,22 +7080,22 @@
         </is>
       </c>
       <c r="C193" s="4" t="n">
-        <v>256.5</v>
+        <v>75.84</v>
       </c>
       <c r="D193" s="4" t="n">
-        <v>39.13</v>
+        <v>37.81</v>
       </c>
       <c r="E193" s="4" t="n">
-        <v>34.2</v>
+        <v>36.89</v>
       </c>
       <c r="F193" s="4" t="n">
-        <v>29.88</v>
+        <v>45.51</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>CELLO</t>
+          <t>HGINFRA</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -6984,22 +7104,22 @@
         </is>
       </c>
       <c r="C194" s="4" t="n">
-        <v>343.45</v>
+        <v>487.25</v>
       </c>
       <c r="D194" s="4" t="n">
-        <v>39.06</v>
+        <v>37.76</v>
       </c>
       <c r="E194" s="4" t="n">
-        <v>33.79</v>
+        <v>32.43</v>
       </c>
       <c r="F194" s="4" t="n">
-        <v>28.67</v>
+        <v>33.87</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>RALLIS</t>
+          <t>CAMPUS</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -7008,22 +7128,22 @@
         </is>
       </c>
       <c r="C195" s="4" t="n">
-        <v>208.82</v>
+        <v>214.36</v>
       </c>
       <c r="D195" s="4" t="n">
-        <v>38.86</v>
+        <v>37.63</v>
       </c>
       <c r="E195" s="4" t="n">
-        <v>33.33</v>
+        <v>38.28</v>
       </c>
       <c r="F195" s="4" t="n">
-        <v>42.05</v>
+        <v>40.13</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>TSFINV</t>
+          <t>KITEX</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -7032,22 +7152,22 @@
         </is>
       </c>
       <c r="C196" s="4" t="n">
-        <v>406.05</v>
+        <v>125.65</v>
       </c>
       <c r="D196" s="4" t="n">
-        <v>38.82</v>
+        <v>37.63</v>
       </c>
       <c r="E196" s="4" t="n">
-        <v>45.98</v>
+        <v>33.06</v>
       </c>
       <c r="F196" s="4" t="n">
-        <v>52.58</v>
+        <v>42.79</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENT</t>
+          <t>NFL</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -7056,22 +7176,22 @@
         </is>
       </c>
       <c r="C197" s="4" t="n">
-        <v>71.97</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="D197" s="4" t="n">
-        <v>38.62</v>
+        <v>37.56</v>
       </c>
       <c r="E197" s="4" t="n">
-        <v>54.02</v>
+        <v>37.75</v>
       </c>
       <c r="F197" s="4" t="n">
-        <v>57.62</v>
+        <v>42.03</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>CERA</t>
+          <t>MOIL</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -7080,22 +7200,22 @@
         </is>
       </c>
       <c r="C198" s="4" t="n">
-        <v>5683.5</v>
+        <v>250.18</v>
       </c>
       <c r="D198" s="4" t="n">
-        <v>38.36</v>
+        <v>37.51</v>
       </c>
       <c r="E198" s="4" t="n">
-        <v>51.08</v>
+        <v>33.23</v>
       </c>
       <c r="F198" s="4" t="n">
-        <v>48.4</v>
+        <v>40.55</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>UJJIVANSFB</t>
+          <t>SURYAROSNI</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -7104,22 +7224,22 @@
         </is>
       </c>
       <c r="C199" s="4" t="n">
-        <v>64.43000000000001</v>
+        <v>216.05</v>
       </c>
       <c r="D199" s="4" t="n">
-        <v>38.04</v>
+        <v>37.4</v>
       </c>
       <c r="E199" s="4" t="n">
-        <v>53.44</v>
+        <v>39.42</v>
       </c>
       <c r="F199" s="4" t="n">
-        <v>59.73</v>
+        <v>44.77</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>VAIBHAVGBL</t>
+          <t>CERA</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -7128,22 +7248,22 @@
         </is>
       </c>
       <c r="C200" s="4" t="n">
-        <v>218.74</v>
+        <v>5614</v>
       </c>
       <c r="D200" s="4" t="n">
-        <v>37.46</v>
+        <v>36.95</v>
       </c>
       <c r="E200" s="4" t="n">
-        <v>45.24</v>
+        <v>46.43</v>
       </c>
       <c r="F200" s="4" t="n">
-        <v>45.31</v>
+        <v>46.75</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>MEDPLUS</t>
+          <t>NETWORK18</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -7152,22 +7272,22 @@
         </is>
       </c>
       <c r="C201" s="4" t="n">
-        <v>660.65</v>
+        <v>26.64</v>
       </c>
       <c r="D201" s="4" t="n">
-        <v>37.42</v>
+        <v>36.7</v>
       </c>
       <c r="E201" s="4" t="n">
-        <v>31.38</v>
+        <v>32.44</v>
       </c>
       <c r="F201" s="4" t="n">
-        <v>40.21</v>
+        <v>33.49</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>MOIL</t>
+          <t>SUNTECK</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -7176,22 +7296,22 @@
         </is>
       </c>
       <c r="C202" s="4" t="n">
-        <v>250.68</v>
+        <v>288</v>
       </c>
       <c r="D202" s="4" t="n">
-        <v>37.13</v>
+        <v>36.53</v>
       </c>
       <c r="E202" s="4" t="n">
-        <v>35.31</v>
+        <v>38.46</v>
       </c>
       <c r="F202" s="4" t="n">
-        <v>41.71</v>
+        <v>39.55</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>IXIGO</t>
+          <t>LLOYDSENT</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -7200,22 +7320,22 @@
         </is>
       </c>
       <c r="C203" s="4" t="n">
-        <v>162.15</v>
+        <v>70.01000000000001</v>
       </c>
       <c r="D203" s="4" t="n">
-        <v>37.03</v>
+        <v>36.49</v>
       </c>
       <c r="E203" s="4" t="n">
-        <v>42.88</v>
+        <v>48.7</v>
       </c>
       <c r="F203" s="4" t="n">
-        <v>43.89</v>
+        <v>54.98</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>GMRP&amp;UI</t>
+          <t>VAIBHAVGBL</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -7224,22 +7344,22 @@
         </is>
       </c>
       <c r="C204" s="4" t="n">
-        <v>91.69</v>
+        <v>215.96</v>
       </c>
       <c r="D204" s="4" t="n">
-        <v>36.92</v>
+        <v>36.4</v>
       </c>
       <c r="E204" s="4" t="n">
-        <v>40.67</v>
+        <v>43.08</v>
       </c>
       <c r="F204" s="4" t="n">
-        <v>48.94</v>
+        <v>44.48</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>RATEGAIN</t>
+          <t>IXIGO</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -7248,22 +7368,22 @@
         </is>
       </c>
       <c r="C205" s="4" t="n">
-        <v>851.15</v>
+        <v>158.63</v>
       </c>
       <c r="D205" s="4" t="n">
-        <v>36.81</v>
+        <v>36.33</v>
       </c>
       <c r="E205" s="4" t="n">
-        <v>55.41</v>
+        <v>40.41</v>
       </c>
       <c r="F205" s="4" t="n">
-        <v>60.42</v>
+        <v>41.81</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>CAPILLARY</t>
+          <t>SAATVIKGL</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -7272,13 +7392,13 @@
         </is>
       </c>
       <c r="C206" s="4" t="n">
-        <v>480.05</v>
+        <v>402.05</v>
       </c>
       <c r="D206" s="4" t="n">
-        <v>36.77</v>
+        <v>36.21</v>
       </c>
       <c r="E206" s="4" t="n">
-        <v>42.28</v>
+        <v>40.08</v>
       </c>
       <c r="F206" s="4" t="n">
         <v/>
@@ -7287,7 +7407,7 @@
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>DBL</t>
+          <t>CSBBANK</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -7296,22 +7416,22 @@
         </is>
       </c>
       <c r="C207" s="4" t="n">
-        <v>398.55</v>
+        <v>307.6</v>
       </c>
       <c r="D207" s="4" t="n">
-        <v>36.74</v>
+        <v>35.82</v>
       </c>
       <c r="E207" s="4" t="n">
-        <v>42.01</v>
+        <v>37.25</v>
       </c>
       <c r="F207" s="4" t="n">
-        <v>45.46</v>
+        <v>43.06</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>SANOFICONR</t>
+          <t>REFEX</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -7320,22 +7440,22 @@
         </is>
       </c>
       <c r="C208" s="4" t="n">
-        <v>4205.4</v>
+        <v>273.55</v>
       </c>
       <c r="D208" s="4" t="n">
-        <v>36.6</v>
+        <v>35.82</v>
       </c>
       <c r="E208" s="4" t="n">
-        <v>39.65</v>
+        <v>43.94</v>
       </c>
       <c r="F208" s="4" t="n">
-        <v>41.97</v>
+        <v>47.61</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>BBOX</t>
+          <t>KANSAINER</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -7344,22 +7464,22 @@
         </is>
       </c>
       <c r="C209" s="4" t="n">
-        <v>712.25</v>
+        <v>191.11</v>
       </c>
       <c r="D209" s="4" t="n">
-        <v>36.48</v>
+        <v>35.64</v>
       </c>
       <c r="E209" s="4" t="n">
-        <v>45.76</v>
+        <v>40.28</v>
       </c>
       <c r="F209" s="4" t="n">
-        <v>57.08</v>
+        <v>38.11</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>JLHL</t>
+          <t>REDTAPE</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -7368,22 +7488,22 @@
         </is>
       </c>
       <c r="C210" s="4" t="n">
-        <v>290.3</v>
+        <v>115.06</v>
       </c>
       <c r="D210" s="4" t="n">
-        <v>36.25</v>
+        <v>35.41</v>
       </c>
       <c r="E210" s="4" t="n">
-        <v>49.69</v>
+        <v>41.11</v>
       </c>
       <c r="F210" s="4" t="n">
-        <v>52.02</v>
+        <v>33.99</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>ANUP</t>
+          <t>GRINDWELL</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -7392,22 +7512,22 @@
         </is>
       </c>
       <c r="C211" s="4" t="n">
-        <v>1808</v>
+        <v>1907.7</v>
       </c>
       <c r="D211" s="4" t="n">
-        <v>35.72</v>
+        <v>35.28</v>
       </c>
       <c r="E211" s="4" t="n">
-        <v>40.76</v>
+        <v>48.91</v>
       </c>
       <c r="F211" s="4" t="n">
-        <v>45.54</v>
+        <v>52.04</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>DBREALTY</t>
+          <t>CELLO</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -7416,22 +7536,22 @@
         </is>
       </c>
       <c r="C212" s="4" t="n">
-        <v>102.57</v>
+        <v>332.8</v>
       </c>
       <c r="D212" s="4" t="n">
-        <v>35.66</v>
+        <v>35.09</v>
       </c>
       <c r="E212" s="4" t="n">
-        <v>41.88</v>
+        <v>32</v>
       </c>
       <c r="F212" s="4" t="n">
-        <v>42.63</v>
+        <v>28.13</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>SFL</t>
+          <t>ORIENTCEM</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -7440,22 +7560,22 @@
         </is>
       </c>
       <c r="C213" s="4" t="n">
-        <v>646.8</v>
+        <v>125.58</v>
       </c>
       <c r="D213" s="4" t="n">
-        <v>35.62</v>
+        <v>34.95</v>
       </c>
       <c r="E213" s="4" t="n">
-        <v>48.34</v>
+        <v>32.41</v>
       </c>
       <c r="F213" s="4" t="n">
-        <v>45.54</v>
+        <v>34.37</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>PRIVISCL</t>
+          <t>GHCL</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -7464,22 +7584,22 @@
         </is>
       </c>
       <c r="C214" s="4" t="n">
-        <v>3367.3</v>
+        <v>424.7</v>
       </c>
       <c r="D214" s="4" t="n">
-        <v>35.5</v>
+        <v>34.89</v>
       </c>
       <c r="E214" s="4" t="n">
-        <v>51.42</v>
+        <v>37.96</v>
       </c>
       <c r="F214" s="4" t="n">
-        <v>64.5</v>
+        <v>40.86</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>AURIONPRO</t>
+          <t>OSWALPUMPS</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -7488,22 +7608,22 @@
         </is>
       </c>
       <c r="C215" s="4" t="n">
-        <v>686.45</v>
+        <v>282.45</v>
       </c>
       <c r="D215" s="4" t="n">
-        <v>35.34</v>
+        <v>34.85</v>
       </c>
       <c r="E215" s="4" t="n">
-        <v>34.76</v>
+        <v>31.32</v>
       </c>
       <c r="F215" s="4" t="n">
-        <v>38.12</v>
+        <v>26.64</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>REDTAPE</t>
+          <t>AURIONPRO</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -7512,22 +7632,22 @@
         </is>
       </c>
       <c r="C216" s="4" t="n">
-        <v>117.48</v>
+        <v>671.15</v>
       </c>
       <c r="D216" s="4" t="n">
-        <v>34.9</v>
+        <v>34.72</v>
       </c>
       <c r="E216" s="4" t="n">
-        <v>43.79</v>
+        <v>34.09</v>
       </c>
       <c r="F216" s="4" t="n">
-        <v>34.37</v>
+        <v>37.87</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>TANLA</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -7536,22 +7656,22 @@
         </is>
       </c>
       <c r="C217" s="4" t="n">
-        <v>514.8</v>
+        <v>470.45</v>
       </c>
       <c r="D217" s="4" t="n">
-        <v>34.81</v>
+        <v>34.42</v>
       </c>
       <c r="E217" s="4" t="n">
-        <v>46.65</v>
+        <v>35.8</v>
       </c>
       <c r="F217" s="4" t="n">
-        <v>44.84</v>
+        <v>38.55</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>HAPPSTMNDS</t>
+          <t>IMFA</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -7560,22 +7680,22 @@
         </is>
       </c>
       <c r="C218" s="4" t="n">
-        <v>354</v>
+        <v>1279.1</v>
       </c>
       <c r="D218" s="4" t="n">
-        <v>34.45</v>
+        <v>34.36</v>
       </c>
       <c r="E218" s="4" t="n">
-        <v>42.16</v>
+        <v>42.29</v>
       </c>
       <c r="F218" s="4" t="n">
-        <v>31.21</v>
+        <v>56.57</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>SURYAROSNI</t>
+          <t>CAPILLARY</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -7584,22 +7704,22 @@
         </is>
       </c>
       <c r="C219" s="4" t="n">
-        <v>216.49</v>
+        <v>461.95</v>
       </c>
       <c r="D219" s="4" t="n">
-        <v>34.33</v>
+        <v>33.97</v>
       </c>
       <c r="E219" s="4" t="n">
-        <v>40.18</v>
+        <v>37.77</v>
       </c>
       <c r="F219" s="4" t="n">
-        <v>45.06</v>
+        <v/>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>KSCL</t>
+          <t>BORORENEW</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -7608,22 +7728,22 @@
         </is>
       </c>
       <c r="C220" s="4" t="n">
-        <v>744.1</v>
+        <v>502.2</v>
       </c>
       <c r="D220" s="4" t="n">
-        <v>34.1</v>
+        <v>33.68</v>
       </c>
       <c r="E220" s="4" t="n">
-        <v>36.71</v>
+        <v>42.85</v>
       </c>
       <c r="F220" s="4" t="n">
-        <v>41.87</v>
+        <v>48.43</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>PICCADIL</t>
+          <t>AEQUS</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -7632,13 +7752,13 @@
         </is>
       </c>
       <c r="C221" s="4" t="n">
-        <v>620.5</v>
+        <v>225.97</v>
       </c>
       <c r="D221" s="4" t="n">
-        <v>33.99</v>
+        <v>33.59</v>
       </c>
       <c r="E221" s="4" t="n">
-        <v>47.46</v>
+        <v>56.19</v>
       </c>
       <c r="F221" s="4" t="n">
         <v/>
@@ -7647,7 +7767,7 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>DATAMATICS</t>
+          <t>FIEMIND</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -7656,22 +7776,22 @@
         </is>
       </c>
       <c r="C222" s="4" t="n">
-        <v>774.85</v>
+        <v>1986.8</v>
       </c>
       <c r="D222" s="4" t="n">
-        <v>33.91</v>
+        <v>33.26</v>
       </c>
       <c r="E222" s="4" t="n">
-        <v>45.92</v>
+        <v>41.04</v>
       </c>
       <c r="F222" s="4" t="n">
-        <v>52.87</v>
+        <v>56.39</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>WAAREERTL</t>
+          <t>ASHAPURMIN</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -7680,22 +7800,22 @@
         </is>
       </c>
       <c r="C223" s="4" t="n">
-        <v>858.95</v>
+        <v>542.9</v>
       </c>
       <c r="D223" s="4" t="n">
-        <v>33.56</v>
+        <v>32.96</v>
       </c>
       <c r="E223" s="4" t="n">
-        <v>38.38</v>
+        <v>38.96</v>
       </c>
       <c r="F223" s="4" t="n">
-        <v>40.97</v>
+        <v>50.81</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>RCF</t>
+          <t>TANLA</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -7704,22 +7824,22 @@
         </is>
       </c>
       <c r="C224" s="4" t="n">
-        <v>114.52</v>
+        <v>502.8</v>
       </c>
       <c r="D224" s="4" t="n">
-        <v>33.04</v>
+        <v>32.66</v>
       </c>
       <c r="E224" s="4" t="n">
-        <v>37.48</v>
+        <v>43.63</v>
       </c>
       <c r="F224" s="4" t="n">
-        <v>43.09</v>
+        <v>43.77</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>EMBDL</t>
+          <t>SANOFICONR</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -7728,22 +7848,22 @@
         </is>
       </c>
       <c r="C225" s="4" t="n">
-        <v>57.53</v>
+        <v>4089.6</v>
       </c>
       <c r="D225" s="4" t="n">
-        <v>32.99</v>
+        <v>32.24</v>
       </c>
       <c r="E225" s="4" t="n">
-        <v>44.04</v>
+        <v>35.11</v>
       </c>
       <c r="F225" s="4" t="n">
-        <v>40.96</v>
+        <v>38.89</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>SWSOLAR</t>
+          <t>EUREKAFORB</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -7752,22 +7872,22 @@
         </is>
       </c>
       <c r="C226" s="4" t="n">
-        <v>187.79</v>
+        <v>394.15</v>
       </c>
       <c r="D226" s="4" t="n">
-        <v>32.34</v>
+        <v>31.73</v>
       </c>
       <c r="E226" s="4" t="n">
-        <v>40.72</v>
+        <v>34.63</v>
       </c>
       <c r="F226" s="4" t="n">
-        <v>39.76</v>
+        <v>36.34</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>IMFA</t>
+          <t>CRAMC</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -7776,22 +7896,22 @@
         </is>
       </c>
       <c r="C227" s="4" t="n">
-        <v>1281.7</v>
+        <v>238.9</v>
       </c>
       <c r="D227" s="4" t="n">
-        <v>32.26</v>
+        <v>31</v>
       </c>
       <c r="E227" s="4" t="n">
-        <v>44.95</v>
+        <v>40.26</v>
       </c>
       <c r="F227" s="4" t="n">
-        <v>58.16</v>
+        <v/>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>SAMHI</t>
+          <t>CENTURYPLY</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -7800,22 +7920,22 @@
         </is>
       </c>
       <c r="C228" s="4" t="n">
-        <v>152.59</v>
+        <v>717.05</v>
       </c>
       <c r="D228" s="4" t="n">
-        <v>31.48</v>
+        <v>30.94</v>
       </c>
       <c r="E228" s="4" t="n">
-        <v>41.86</v>
+        <v>39.9</v>
       </c>
       <c r="F228" s="4" t="n">
-        <v>44.35</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>KPIGREEN</t>
+          <t>PICCADIL</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -7824,22 +7944,22 @@
         </is>
       </c>
       <c r="C229" s="4" t="n">
-        <v>307</v>
+        <v>600.5</v>
       </c>
       <c r="D229" s="4" t="n">
-        <v>31.16</v>
+        <v>30.7</v>
       </c>
       <c r="E229" s="4" t="n">
-        <v>29.26</v>
+        <v>45.93</v>
       </c>
       <c r="F229" s="4" t="n">
-        <v>42.03</v>
+        <v/>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>HEMIPROP</t>
+          <t>JLHL</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -7848,22 +7968,22 @@
         </is>
       </c>
       <c r="C230" s="4" t="n">
-        <v>125.93</v>
+        <v>281</v>
       </c>
       <c r="D230" s="4" t="n">
-        <v>31.02</v>
+        <v>30.57</v>
       </c>
       <c r="E230" s="4" t="n">
-        <v>41.13</v>
+        <v>46.44</v>
       </c>
       <c r="F230" s="4" t="n">
-        <v>45.34</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>POWERMECH</t>
+          <t>RCF</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -7872,22 +7992,22 @@
         </is>
       </c>
       <c r="C231" s="4" t="n">
-        <v>2306.1</v>
+        <v>112.57</v>
       </c>
       <c r="D231" s="4" t="n">
-        <v>30.82</v>
+        <v>30.43</v>
       </c>
       <c r="E231" s="4" t="n">
-        <v>42.79</v>
+        <v>34.96</v>
       </c>
       <c r="F231" s="4" t="n">
-        <v>48.2</v>
+        <v>41.91</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>WEBELSOLAR</t>
+          <t>DBREALTY</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -7896,22 +8016,22 @@
         </is>
       </c>
       <c r="C232" s="4" t="n">
-        <v>74.53</v>
+        <v>97.79000000000001</v>
       </c>
       <c r="D232" s="4" t="n">
-        <v>30.68</v>
+        <v>29.73</v>
       </c>
       <c r="E232" s="4" t="n">
-        <v>35.63</v>
+        <v>39.26</v>
       </c>
       <c r="F232" s="4" t="n">
-        <v>45.18</v>
+        <v>41.75</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>ASHAPURMIN</t>
+          <t>CMSINFO</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -7920,22 +8040,22 @@
         </is>
       </c>
       <c r="C233" s="4" t="n">
-        <v>547.95</v>
+        <v>225.19</v>
       </c>
       <c r="D233" s="4" t="n">
-        <v>30.29</v>
+        <v>29.71</v>
       </c>
       <c r="E233" s="4" t="n">
-        <v>39.71</v>
+        <v>27.12</v>
       </c>
       <c r="F233" s="4" t="n">
-        <v>51.18</v>
+        <v>31.22</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>RAYMONDLSL</t>
+          <t>HAPPSTMNDS</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -7944,16 +8064,16 @@
         </is>
       </c>
       <c r="C234" s="4" t="n">
-        <v>647.85</v>
+        <v>332.35</v>
       </c>
       <c r="D234" s="4" t="n">
-        <v>29.75</v>
+        <v>29.65</v>
       </c>
       <c r="E234" s="4" t="n">
-        <v>33.08</v>
+        <v>38.71</v>
       </c>
       <c r="F234" s="4" t="n">
-        <v>23.9</v>
+        <v>29.83</v>
       </c>
     </row>
     <row r="235">
@@ -7968,22 +8088,22 @@
         </is>
       </c>
       <c r="C235" s="4" t="n">
-        <v>27.82</v>
+        <v>27.6</v>
       </c>
       <c r="D235" s="4" t="n">
-        <v>28.9</v>
+        <v>29.6</v>
       </c>
       <c r="E235" s="4" t="n">
-        <v>34.25</v>
+        <v>33.99</v>
       </c>
       <c r="F235" s="4" t="n">
-        <v>37.86</v>
+        <v>37.79</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>HGINFRA</t>
+          <t>EMBDL</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -7992,22 +8112,22 @@
         </is>
       </c>
       <c r="C236" s="4" t="n">
-        <v>479.9</v>
+        <v>55.28</v>
       </c>
       <c r="D236" s="4" t="n">
-        <v>28.83</v>
+        <v>29.17</v>
       </c>
       <c r="E236" s="4" t="n">
-        <v>31.9</v>
+        <v>41.81</v>
       </c>
       <c r="F236" s="4" t="n">
-        <v>33.8</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>STYRENIX</t>
+          <t>BIRLACORPN</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -8016,22 +8136,22 @@
         </is>
       </c>
       <c r="C237" s="4" t="n">
-        <v>2007</v>
+        <v>825.15</v>
       </c>
       <c r="D237" s="4" t="n">
-        <v>28.66</v>
+        <v>28.42</v>
       </c>
       <c r="E237" s="4" t="n">
-        <v>43.47</v>
+        <v>35.93</v>
       </c>
       <c r="F237" s="4" t="n">
-        <v>48.37</v>
+        <v>37.08</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>RTNPOWER</t>
+          <t>RALLIS</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -8040,22 +8160,22 @@
         </is>
       </c>
       <c r="C238" s="4" t="n">
-        <v>7.36</v>
+        <v>201.99</v>
       </c>
       <c r="D238" s="4" t="n">
-        <v>28.61</v>
+        <v>28.3</v>
       </c>
       <c r="E238" s="4" t="n">
-        <v>30.66</v>
+        <v>30.48</v>
       </c>
       <c r="F238" s="4" t="n">
-        <v>41.35</v>
+        <v>41.03</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>RELAXO</t>
+          <t>KSCL</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -8064,22 +8184,22 @@
         </is>
       </c>
       <c r="C239" s="4" t="n">
-        <v>343.95</v>
+        <v>718.05</v>
       </c>
       <c r="D239" s="4" t="n">
-        <v>28.4</v>
+        <v>27.55</v>
       </c>
       <c r="E239" s="4" t="n">
-        <v>45.27</v>
+        <v>34.31</v>
       </c>
       <c r="F239" s="4" t="n">
-        <v>36.14</v>
+        <v>40.71</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>SHAKTIPUMP</t>
+          <t>JKLAKSHMI</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -8088,22 +8208,22 @@
         </is>
       </c>
       <c r="C240" s="4" t="n">
-        <v>473</v>
+        <v>505.9</v>
       </c>
       <c r="D240" s="4" t="n">
-        <v>28.3</v>
+        <v>27.12</v>
       </c>
       <c r="E240" s="4" t="n">
-        <v>34.39</v>
+        <v>29.06</v>
       </c>
       <c r="F240" s="4" t="n">
-        <v>42.91</v>
+        <v>36.37</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>AVANTIFEED</t>
+          <t>SWSOLAR</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -8112,22 +8232,22 @@
         </is>
       </c>
       <c r="C241" s="4" t="n">
-        <v>795.85</v>
+        <v>180.22</v>
       </c>
       <c r="D241" s="4" t="n">
-        <v>28.21</v>
+        <v>26.51</v>
       </c>
       <c r="E241" s="4" t="n">
-        <v>35.16</v>
+        <v>38.73</v>
       </c>
       <c r="F241" s="4" t="n">
-        <v>49.17</v>
+        <v>39.26</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>OSWALPUMPS</t>
+          <t>WAAREERTL</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -8136,22 +8256,22 @@
         </is>
       </c>
       <c r="C242" s="4" t="n">
-        <v>279.55</v>
+        <v>833.85</v>
       </c>
       <c r="D242" s="4" t="n">
-        <v>27.77</v>
+        <v>26.4</v>
       </c>
       <c r="E242" s="4" t="n">
-        <v>30.41</v>
+        <v>35.64</v>
       </c>
       <c r="F242" s="4" t="n">
-        <v>26.49</v>
+        <v>39.56</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>CRIZAC</t>
+          <t>TRANSRAILL</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -8160,22 +8280,22 @@
         </is>
       </c>
       <c r="C243" s="4" t="n">
-        <v>162.27</v>
+        <v>410.35</v>
       </c>
       <c r="D243" s="4" t="n">
-        <v>27.36</v>
+        <v>25.29</v>
       </c>
       <c r="E243" s="4" t="n">
-        <v>30.01</v>
+        <v>32.18</v>
       </c>
       <c r="F243" s="4" t="n">
-        <v/>
+        <v>39.53</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>BORORENEW</t>
+          <t>RTNPOWER</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -8184,22 +8304,22 @@
         </is>
       </c>
       <c r="C244" s="4" t="n">
-        <v>499.15</v>
+        <v>7.17</v>
       </c>
       <c r="D244" s="4" t="n">
-        <v>26.87</v>
+        <v>24.92</v>
       </c>
       <c r="E244" s="4" t="n">
-        <v>43.32</v>
+        <v>29.23</v>
       </c>
       <c r="F244" s="4" t="n">
-        <v>48.67</v>
+        <v>40.82</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>TRANSRAILL</t>
+          <t>ANUP</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
@@ -8208,22 +8328,22 @@
         </is>
       </c>
       <c r="C245" s="4" t="n">
-        <v>427.45</v>
+        <v>1664.3</v>
       </c>
       <c r="D245" s="4" t="n">
-        <v>26.49</v>
+        <v>24.41</v>
       </c>
       <c r="E245" s="4" t="n">
-        <v>34.47</v>
+        <v>36.61</v>
       </c>
       <c r="F245" s="4" t="n">
-        <v>40.58</v>
+        <v>43.83</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>JKLAKSHMI</t>
+          <t>HEMIPROP</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -8232,22 +8352,22 @@
         </is>
       </c>
       <c r="C246" s="4" t="n">
-        <v>515.7</v>
+        <v>120.95</v>
       </c>
       <c r="D246" s="4" t="n">
-        <v>24.76</v>
+        <v>23.91</v>
       </c>
       <c r="E246" s="4" t="n">
-        <v>30.34</v>
+        <v>36.85</v>
       </c>
       <c r="F246" s="4" t="n">
-        <v>36.87</v>
+        <v>43.58</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>PNCINFRA</t>
+          <t>RELAXO</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -8256,22 +8376,22 @@
         </is>
       </c>
       <c r="C247" s="4" t="n">
-        <v>182.97</v>
+        <v>326.9</v>
       </c>
       <c r="D247" s="4" t="n">
-        <v>23.98</v>
+        <v>23.85</v>
       </c>
       <c r="E247" s="4" t="n">
-        <v>34.9</v>
+        <v>41.96</v>
       </c>
       <c r="F247" s="4" t="n">
-        <v>38.35</v>
+        <v>34.81</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>SUBROS</t>
+          <t>KPIGREEN</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -8280,22 +8400,22 @@
         </is>
       </c>
       <c r="C248" s="4" t="n">
-        <v>705.85</v>
+        <v>287.5</v>
       </c>
       <c r="D248" s="4" t="n">
-        <v>23.75</v>
+        <v>23.78</v>
       </c>
       <c r="E248" s="4" t="n">
-        <v>41.36</v>
+        <v>25.8</v>
       </c>
       <c r="F248" s="4" t="n">
-        <v>48.75</v>
+        <v>40.35</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>STARCEMENT</t>
+          <t>PNCINFRA</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
@@ -8304,16 +8424,16 @@
         </is>
       </c>
       <c r="C249" s="4" t="n">
-        <v>184.47</v>
+        <v>175.4</v>
       </c>
       <c r="D249" s="4" t="n">
-        <v>22.25</v>
+        <v>22.63</v>
       </c>
       <c r="E249" s="4" t="n">
-        <v>34.27</v>
+        <v>32.85</v>
       </c>
       <c r="F249" s="4" t="n">
-        <v>44.99</v>
+        <v>37.55</v>
       </c>
     </row>
     <row r="250">
@@ -8328,22 +8448,22 @@
         </is>
       </c>
       <c r="C250" s="4" t="n">
-        <v>595.45</v>
+        <v>592.3</v>
       </c>
       <c r="D250" s="4" t="n">
-        <v>18.47</v>
+        <v>21.66</v>
       </c>
       <c r="E250" s="4" t="n">
-        <v>27.21</v>
+        <v>27.53</v>
       </c>
       <c r="F250" s="4" t="n">
-        <v>39.95</v>
+        <v>40.01</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>ALOKINDS</t>
+          <t>INDIAGLYCO</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
@@ -8352,22 +8472,22 @@
         </is>
       </c>
       <c r="C251" s="4" t="n">
-        <v>7.83</v>
+        <v>294.9</v>
       </c>
       <c r="D251" s="4" t="n">
-        <v>14.35</v>
+        <v>18.23</v>
       </c>
       <c r="E251" s="4" t="n">
-        <v>21.23</v>
+        <v>25.15</v>
       </c>
       <c r="F251" s="4" t="n">
-        <v>30.34</v>
+        <v>35.94</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>INDIAGLYCO</t>
+          <t>ALOKINDS</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
@@ -8376,16 +8496,16 @@
         </is>
       </c>
       <c r="C252" s="4" t="n">
-        <v>248</v>
+        <v>7.36</v>
       </c>
       <c r="D252" s="4" t="n">
-        <v>13.12</v>
+        <v>12.63</v>
       </c>
       <c r="E252" s="4" t="n">
-        <v>23.25</v>
+        <v>20.07</v>
       </c>
       <c r="F252" s="4" t="n">
-        <v>35.3</v>
+        <v>29.69</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Micro250_stocks.xlsx
+++ b/docs/Micro250_stocks.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L48"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -551,7 +551,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>MAHSEAMLES</t>
+          <t>SHAREINDIA</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -560,37 +560,37 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>718.95</v>
+        <v>228.15</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>77.76000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>75.28</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>59.95</v>
+        <v>57.41</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>53.21</v>
+        <v>40.88</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>601.91</v>
+        <v>162.5</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>600.36</v>
+        <v>162.16</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>341241</v>
+        <v>5635199</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>9767</v>
+        <v>4993</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>YATHARTH</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -599,37 +599,37 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>854.75</v>
+        <v>1139.5</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>77.73999999999999</v>
+        <v>80.27</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>82.90000000000001</v>
+        <v>75.62</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>88.94</v>
+        <v>72.27</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>30.3</v>
+        <v>46.4</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>474.93</v>
+        <v>834.37</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>419.76</v>
+        <v>806.08</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>1888026</v>
+        <v>769562</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>46132</v>
+        <v>10980</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>WELENT</t>
+          <t>SHILPAMED</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -638,37 +638,37 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>797.95</v>
+        <v>1021.1</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>75.19</v>
+        <v>70.03</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>75.42</v>
+        <v>92.03</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>71.2</v>
+        <v>85.47</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>48.59</v>
+        <v>49.45</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>575.6</v>
+        <v>620.4</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>561.17</v>
+        <v>574.9299999999999</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>729164</v>
+        <v>1591545</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>10662</v>
+        <v>19971</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>SMLMAH</t>
+          <t>NEOGEN</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -677,37 +677,37 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>6583</v>
+        <v>2488.4</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>70.98</v>
+        <v>69.81999999999999</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>72.28</v>
+        <v>72.69</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>71.23999999999999</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>49.53</v>
+        <v>28.64</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>4446.1</v>
+        <v>1900.98</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>4232.06</v>
+        <v>1827.16</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>148841</v>
+        <v>238874</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>9527</v>
+        <v>7476</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>MANORAMA</t>
+          <t>MAHSEAMLES</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -716,37 +716,37 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>2084.2</v>
+        <v>720.2</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>69.23999999999999</v>
+        <v>67.83</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>76.70999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>73.23999999999999</v>
+        <v>59.25</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>49.79</v>
+        <v>53.85</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1580.08</v>
+        <v>610.24</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>1530.84</v>
+        <v>606.74</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>769380</v>
+        <v>387177</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>12976</v>
+        <v>9615</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>JKPAPER</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>227.13</v>
+        <v>430.6</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>69.12</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>73.34999999999999</v>
+        <v>69.91</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>67.98</v>
+        <v>58.82</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>43.43</v>
+        <v>45.23</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>186.91</v>
+        <v>373.04</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>181.7</v>
+        <v>370.27</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2717753</v>
+        <v>497377</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>7293</v>
+        <v>7808</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ENTERO</t>
+          <t>EMIL</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -794,37 +794,37 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1792.9</v>
+        <v>196.28</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>68.04000000000001</v>
+        <v>65.37</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>77.31</v>
+        <v>73.34</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>73.48</v>
+        <v>63.03</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>65</v>
+        <v>29.42</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1305.29</v>
+        <v>140.99</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1276.68</v>
+        <v>137.01</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>378821</v>
+        <v>8455167</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>7901</v>
+        <v>7552</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>NEOGEN</t>
+          <t>SANSERA</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -833,37 +833,37 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2388.9</v>
+        <v>4259.9</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>67.45999999999999</v>
+        <v>65.02</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>70</v>
+        <v>82.23999999999999</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>65.89</v>
+        <v>86.04000000000001</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>27.75</v>
+        <v>31.22</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1856.36</v>
+        <v>3047.76</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1786.52</v>
+        <v>2827.62</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>207371</v>
+        <v>227912</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>6498</v>
+        <v>26583</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>SUDARSCHEM</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -872,37 +872,37 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1270.8</v>
+        <v>568.7</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>66.44</v>
+        <v>63.1</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>68.31999999999999</v>
+        <v>65.86</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>60.63</v>
+        <v>67.48</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>37.25</v>
+        <v>20.46</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1025.27</v>
+        <v>478.56</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1020.71</v>
+        <v>468</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>582644</v>
+        <v>1013759</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>9937</v>
+        <v>14098</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SHILPAMED</t>
+          <t>WELENT</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>939.9</v>
+        <v>768</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>66.17</v>
+        <v>62.69</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>90.84999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>84.36</v>
+        <v>72.66</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>63.54</v>
+        <v>47.38</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>597.1900000000001</v>
+        <v>582.97</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>555.26</v>
+        <v>567.12</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>2776095</v>
+        <v>899284</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>18798</v>
+        <v>11166</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SANSERA</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -950,37 +950,37 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>4129.9</v>
+        <v>584.85</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>66.01000000000001</v>
+        <v>61.81</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>80.8</v>
+        <v>68.97</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>85.42</v>
+        <v>58.77</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>35.72</v>
+        <v>31.44</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2983.15</v>
+        <v>506.18</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>2768.17</v>
+        <v>500.08</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>244390</v>
+        <v>901561</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>25772</v>
+        <v>8653</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -989,37 +989,37 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>804.9</v>
+        <v>818.8</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>65.29000000000001</v>
+        <v>61.46</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>73.3</v>
+        <v>72.92</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>80.13</v>
+        <v>87.76000000000001</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>32.36</v>
+        <v>28.96</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>581.72</v>
+        <v>507.7</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>542.58</v>
+        <v>448.35</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2885840</v>
+        <v>1689806</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>25150</v>
+        <v>42091</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>MIDHANI</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1028,37 +1028,37 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>463.35</v>
+        <v>656.25</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>63.82</v>
+        <v>61.36</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>62.02</v>
+        <v>74.8</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>58.15</v>
+        <v>70.87</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>20.8</v>
+        <v>39.82</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>400.12</v>
+        <v>520.02</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>393.32</v>
+        <v>506.89</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>2902208</v>
+        <v>382607</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>8382</v>
+        <v>12937</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>SMLMAH</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1067,37 +1067,37 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>370.3</v>
+        <v>6292.5</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>63.75</v>
+        <v>60.41</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>72.97</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>67.38</v>
+        <v>70.16</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>31.66</v>
+        <v>41.57</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>306.88</v>
+        <v>4563.3</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>299.5</v>
+        <v>4331.34</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2804707</v>
+        <v>117304</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>14245</v>
+        <v>9106</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>VARROC</t>
+          <t>EDELWEISS</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1106,37 +1106,37 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>872</v>
+        <v>136.25</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>63.68</v>
+        <v>60.25</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>78.3</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>71.09</v>
+        <v>64.12</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>47.44</v>
+        <v>24.43</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>663.4299999999999</v>
+        <v>118.13</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>642.38</v>
+        <v>116.44</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>965698</v>
+        <v>7571363</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>13324</v>
+        <v>12896</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>INOXINDIA</t>
+          <t>DIACABS</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1145,37 +1145,37 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2246.6</v>
+        <v>366.8</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>63.04</v>
+        <v>58.18</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>81.04000000000001</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>84.12</v>
+        <v>81.69</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>30.07</v>
+        <v>29.92</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1714.3</v>
+        <v>247.88</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1624.07</v>
+        <v>228.11</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>384073</v>
+        <v>1112136</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>20427</v>
+        <v>21937</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>YATHARTH</t>
+          <t>ENTERO</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1184,37 +1184,37 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>977.2</v>
+        <v>1731.8</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>62.5</v>
+        <v>58.07</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>65.75</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>65.73</v>
+        <v>69.19</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>42.58</v>
+        <v>58.87</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>816.58</v>
+        <v>1323.81</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>790.78</v>
+        <v>1290.59</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>430437</v>
+        <v>384343</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>9311</v>
+        <v>7540</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>EMIL</t>
+          <t>VARROC</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1223,37 +1223,37 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>188.38</v>
+        <v>851.15</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>62.19</v>
+        <v>56.89</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>71.45</v>
+        <v>75.97</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>61.75</v>
+        <v>70.64</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>34.89</v>
+        <v>42.62</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>137.26</v>
+        <v>672.98</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>134.03</v>
+        <v>650.46</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>10739503</v>
+        <v>906032</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>7248</v>
+        <v>13164</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>JKPAPER</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1262,37 +1262,37 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>415.15</v>
+        <v>218.35</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>62</v>
+        <v>56.31</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>66.12</v>
+        <v>66.52</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>57.04</v>
+        <v>66.61</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>48.35</v>
+        <v>39.06</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>370.07</v>
+        <v>189.6</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>367.85</v>
+        <v>184.04</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>477484</v>
+        <v>2647330</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>7511</v>
+        <v>7035</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>SKYGOLD</t>
+          <t>AKUMS</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1301,37 +1301,37 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>827.4</v>
+        <v>766.7</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>61.5</v>
+        <v>55.97</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>78.54000000000001</v>
+        <v>74.64</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>82.26000000000001</v>
+        <v>65.87</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>36.53</v>
+        <v>37.6</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>574.14</v>
+        <v>627.16</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>532.66</v>
+        <v>604.77</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1233215</v>
+        <v>419165</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>12814</v>
+        <v>11999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>ICIL</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1340,37 +1340,37 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1584.6</v>
+        <v>447.35</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>60.67</v>
+        <v>55.35</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>73</v>
+        <v>64.97</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>69.86</v>
+        <v>63.32</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>48.49</v>
+        <v>26.85</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1199.35</v>
+        <v>365.91</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1136.77</v>
+        <v>351.49</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>230477</v>
+        <v>1591294</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>10431</v>
+        <v>8860</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>TDPOWERSYS</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1379,37 +1379,37 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>329.4</v>
+        <v>763.75</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>60.52</v>
+        <v>55.17</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>73.78</v>
+        <v>66.88</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>67.64</v>
+        <v>77.77</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>40.85</v>
+        <v>26.74</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>250.8</v>
+        <v>592.08</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>241.17</v>
+        <v>552.33</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>4771656</v>
+        <v>3014416</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>14927</v>
+        <v>23864</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>AZAD</t>
+          <t>OPTIEMUS</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1418,37 +1418,37 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2849.1</v>
+        <v>590.1</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>60.41</v>
+        <v>54.65</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>69.16</v>
+        <v>60.85</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>72.58</v>
+        <v>55.85</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>27.89</v>
+        <v>20.38</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2223.05</v>
+        <v>515.91</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2119.85</v>
+        <v>512.74</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>556662</v>
+        <v>291647</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>18400</v>
+        <v>5321</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>AKUMS</t>
+          <t>QUESS</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1457,37 +1457,37 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>776.35</v>
+        <v>353</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>60.32</v>
+        <v>54.63</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>74.01000000000001</v>
+        <v>70.11</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>65.41</v>
+        <v>51.48</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>38.59</v>
+        <v>28.55</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>619.41</v>
+        <v>278.87</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>598.48</v>
+        <v>276.63</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>416081</v>
+        <v>723252</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>11886</v>
+        <v>5253</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>DIACABS</t>
+          <t>AZAD</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1496,37 +1496,37 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>351.5</v>
+        <v>2790.3</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>59.7</v>
+        <v>54.43</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>78.01000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>81.81</v>
+        <v>70.89</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>27.41</v>
+        <v>25.85</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>237.68</v>
+        <v>2254.09</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>219.34</v>
+        <v>2147.95</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1441405</v>
+        <v>561233</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>22072</v>
+        <v>18020</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1535,37 +1535,37 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>332.55</v>
+        <v>2216.1</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>59.29</v>
+        <v>53.59</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>70.90000000000001</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>73.34</v>
+        <v>84.45999999999999</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>40.94</v>
+        <v>35.94</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>269.98</v>
+        <v>1634.12</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>258.11</v>
+        <v>1515.29</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2934241</v>
+        <v>683654</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>12304</v>
+        <v>16973</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1574,31 +1574,31 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>569.8</v>
+        <v>362.55</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>58.48</v>
+        <v>53.33</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>68.56999999999999</v>
+        <v>72.41</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>70</v>
+        <v>67.16</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>20.76</v>
+        <v>28.02</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>473.76</v>
+        <v>310.49</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>452.29</v>
+        <v>302.77</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>810373</v>
+        <v>1667992</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>15076</v>
+        <v>14209</v>
       </c>
     </row>
     <row r="29">
@@ -1613,37 +1613,37 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1390.2</v>
+        <v>1370.6</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>58.25</v>
+        <v>53.26</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>75.48</v>
+        <v>77.68000000000001</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>72.63</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>42.8</v>
+        <v>37.26</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1141.23</v>
+        <v>1153.26</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>1109.99</v>
+        <v>1120.19</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>214330</v>
+        <v>175094</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>17026</v>
+        <v>17566</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>EDELWEISS</t>
+          <t>SKYGOLD</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1652,37 +1652,37 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>132.43</v>
+        <v>792.6</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>57.57</v>
+        <v>52.51</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>62.07</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>62.98</v>
+        <v>79.03</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>28.08</v>
+        <v>31.36</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>117.41</v>
+        <v>583.11</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>115.73</v>
+        <v>540.59</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>7386542</v>
+        <v>1207763</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>12535</v>
+        <v>12137</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>KRBL</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1691,37 +1691,37 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>423.25</v>
+        <v>320.15</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>57.32</v>
+        <v>52.36</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>63.1</v>
+        <v>69.53</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>58.28</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>47.06</v>
+        <v>32.11</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>373.12</v>
+        <v>256.29</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>369.32</v>
+        <v>245.94</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>909412</v>
+        <v>4892714</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>9637</v>
+        <v>14508</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>TMB</t>
+          <t>SUDARSCHEM</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1730,37 +1730,37 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>910.9</v>
+        <v>1205.4</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>56.85</v>
+        <v>51.93</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>70.56999999999999</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>76.06</v>
+        <v>61.34</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>41.61</v>
+        <v>30.8</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>746.89</v>
+        <v>1037.71</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>708.3200000000001</v>
+        <v>1030.9</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>173819</v>
+        <v>552474</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>14424</v>
+        <v>10060</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>LUMAXTECH</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1769,37 +1769,37 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>2227</v>
+        <v>1941.8</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>56.74</v>
+        <v>51.73</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>81.87</v>
+        <v>68.34</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>78.70999999999999</v>
+        <v>72.66</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>41.95</v>
+        <v>28.46</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1591.57</v>
+        <v>1672.3</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>1477.16</v>
+        <v>1603.44</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>531379</v>
+        <v>369866</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>15145</v>
+        <v>14332</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>MSTCLTD</t>
+          <t>TMB</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1808,37 +1808,37 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>737.55</v>
+        <v>895.75</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>56.65</v>
+        <v>50.92</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>67.2</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>60.69</v>
+        <v>74.3</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>40.45</v>
+        <v>34.58</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>583.0700000000001</v>
+        <v>756.96</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>565.59</v>
+        <v>717.9</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>395801</v>
+        <v>160697</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>5199</v>
+        <v>14184</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>RAIN</t>
+          <t>INOXINDIA</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1847,37 +1847,37 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>217.28</v>
+        <v>2098.8</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>55.68</v>
+        <v>50.81</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>65.59</v>
+        <v>68.04000000000001</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>60.41</v>
+        <v>80.37</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>20.45</v>
+        <v>26.29</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>180.73</v>
+        <v>1733.15</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>173.39</v>
+        <v>1641.55</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>5796631</v>
+        <v>403839</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>7264</v>
+        <v>19083</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>PGIL</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1886,37 +1886,37 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>1189.2</v>
+        <v>318.2</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>55.41</v>
+        <v>50.63</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>67.70999999999999</v>
+        <v>67.08</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>72.84999999999999</v>
+        <v>71.25</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>34.06</v>
+        <v>34.29</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>953.29</v>
+        <v>268.59</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>910.5</v>
+        <v>256.73</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>345645</v>
+        <v>2599083</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>10972</v>
+        <v>11867</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>MANORAMA</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1925,31 +1925,31 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>1640.3</v>
+        <v>1916.4</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>54.82</v>
+        <v>50.49</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>72.79000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>79.05</v>
+        <v>71.8</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>37.98</v>
+        <v>46.15</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>1308.79</v>
+        <v>1607.39</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>1238.26</v>
+        <v>1553.88</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>337589</v>
+        <v>779483</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>22228</v>
+        <v>12416</v>
       </c>
     </row>
     <row r="38">
@@ -1964,37 +1964,37 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>98.05</v>
+        <v>95.12</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>54.75</v>
+        <v>49.26</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>68.73</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>58.95</v>
+        <v>57.28</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>49.17</v>
+        <v>39.55</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>77.88</v>
+        <v>79.06</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>76.33</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>16811685</v>
+        <v>7395983</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>6982</v>
+        <v>6773</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>MSTCLTD</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -2003,37 +2003,37 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>562.4</v>
+        <v>695.45</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>54.48</v>
+        <v>49.22</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>64.73</v>
+        <v>66.25</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>56.54</v>
+        <v>60.31</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>36</v>
+        <v>35.95</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>503.39</v>
+        <v>581.4</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>497.76</v>
+        <v>563.23</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>697917</v>
+        <v>409740</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>8264</v>
+        <v>5097</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>PARAS</t>
+          <t>PGIL</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -2042,37 +2042,37 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>1435.6</v>
+        <v>1143.1</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>54.02</v>
+        <v>48.68</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>68.14</v>
+        <v>63.18</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>70.31</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>31.94</v>
+        <v>31.13</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>1086.77</v>
+        <v>964.14</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>1021.61</v>
+        <v>920.22</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>1463084</v>
+        <v>319428</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>11569</v>
+        <v>10588</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -2081,37 +2081,37 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>622.4</v>
+        <v>1603.1</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>53.58</v>
+        <v>47.91</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>71.48</v>
+        <v>68.41</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>66.56</v>
+        <v>75.98</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>42.97</v>
+        <v>32.96</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>512.72</v>
+        <v>1329.52</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>500.76</v>
+        <v>1257.22</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>1296445</v>
+        <v>209101</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>12313</v>
+        <v>21635</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>LUMAXTECH</t>
+          <t>PARAS</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -2120,37 +2120,37 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>1942.6</v>
+        <v>1370.9</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>53.54</v>
+        <v>46.79</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>64.94</v>
+        <v>63.48</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>69.39</v>
+        <v>67.38</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>33.73</v>
+        <v>28.31</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>1655.37</v>
+        <v>1106.23</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>1587.66</v>
+        <v>1039.21</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>383186</v>
+        <v>1413123</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>13589</v>
+        <v>11062</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>ICIL</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -2159,226 +2159,31 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>439.45</v>
+        <v>1446.2</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>53.4</v>
+        <v>45.99</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>64.42</v>
+        <v>61.16</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>62.82</v>
+        <v>64.69</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>34.25</v>
+        <v>38.78</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>359.65</v>
+        <v>1222.07</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>345.91</v>
+        <v>1157.64</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>1601468</v>
+        <v>270778</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>8779</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>BALAMINES</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="n">
-        <v>2342.6</v>
-      </c>
-      <c r="D44" s="4" t="n">
-        <v>52.19</v>
-      </c>
-      <c r="E44" s="4" t="n">
-        <v>61.11</v>
-      </c>
-      <c r="F44" s="4" t="n">
-        <v>61.88</v>
-      </c>
-      <c r="G44" s="4" t="n">
-        <v>27.11</v>
-      </c>
-      <c r="H44" s="4" t="n">
-        <v>1877.81</v>
-      </c>
-      <c r="I44" s="4" t="n">
-        <v>1789.21</v>
-      </c>
-      <c r="J44" s="4" t="n">
-        <v>238029</v>
-      </c>
-      <c r="K44" s="4" t="n">
-        <v>7376</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>QUESS</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="n">
-        <v>348</v>
-      </c>
-      <c r="D45" s="4" t="n">
-        <v>51.96</v>
-      </c>
-      <c r="E45" s="4" t="n">
-        <v>69.48999999999999</v>
-      </c>
-      <c r="F45" s="4" t="n">
-        <v>51.11</v>
-      </c>
-      <c r="G45" s="4" t="n">
-        <v>35.67</v>
-      </c>
-      <c r="H45" s="4" t="n">
-        <v>275.11</v>
-      </c>
-      <c r="I45" s="4" t="n">
-        <v>273.45</v>
-      </c>
-      <c r="J45" s="4" t="n">
-        <v>792142</v>
-      </c>
-      <c r="K45" s="4" t="n">
-        <v>5199</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>AARTIPHARM</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="n">
-        <v>825.75</v>
-      </c>
-      <c r="D46" s="4" t="n">
-        <v>51.88</v>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>60.25</v>
-      </c>
-      <c r="F46" s="4" t="n">
-        <v>57.77</v>
-      </c>
-      <c r="G46" s="4" t="n">
-        <v>32.01</v>
-      </c>
-      <c r="H46" s="4" t="n">
-        <v>742.67</v>
-      </c>
-      <c r="I46" s="4" t="n">
-        <v>741.49</v>
-      </c>
-      <c r="J46" s="4" t="n">
-        <v>1048227</v>
-      </c>
-      <c r="K46" s="4" t="n">
-        <v>7499</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>SHAILY</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="n">
-        <v>3279.5</v>
-      </c>
-      <c r="D47" s="4" t="n">
-        <v>50.88</v>
-      </c>
-      <c r="E47" s="4" t="n">
-        <v>66.8</v>
-      </c>
-      <c r="F47" s="4" t="n">
-        <v>73.56</v>
-      </c>
-      <c r="G47" s="4" t="n">
-        <v>31.68</v>
-      </c>
-      <c r="H47" s="4" t="n">
-        <v>2795.27</v>
-      </c>
-      <c r="I47" s="4" t="n">
-        <v>2667.89</v>
-      </c>
-      <c r="J47" s="4" t="n">
-        <v>179142</v>
-      </c>
-      <c r="K47" s="4" t="n">
-        <v>15084</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>HCG</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="n">
-        <v>700.9</v>
-      </c>
-      <c r="D48" s="4" t="n">
-        <v>49.72</v>
-      </c>
-      <c r="E48" s="4" t="n">
-        <v>60.29</v>
-      </c>
-      <c r="F48" s="4" t="n">
-        <v>61.82</v>
-      </c>
-      <c r="G48" s="4" t="n">
-        <v>29.74</v>
-      </c>
-      <c r="H48" s="4" t="n">
-        <v>651.91</v>
-      </c>
-      <c r="I48" s="4" t="n">
-        <v>643.03</v>
-      </c>
-      <c r="J48" s="4" t="n">
-        <v>171696</v>
-      </c>
-      <c r="K48" s="4" t="n">
-        <v>10360</v>
+        <v>9467</v>
       </c>
     </row>
   </sheetData>
@@ -2425,11 +2230,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId47"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2496,22 +2296,22 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>1319.2</v>
+        <v>1467</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>87.64</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>76.95999999999999</v>
+        <v>81.47</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>56.32</v>
+        <v>60.04</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>STAR</t>
+          <t>SHAREINDIA</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2520,22 +2320,22 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>1217</v>
+        <v>228.15</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>81.23999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>65.3</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>63.04</v>
+        <v>57.41</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>MAHSEAMLES</t>
+          <t>YATHARTH</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2544,22 +2344,22 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>718.95</v>
+        <v>1139.5</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>77.76000000000001</v>
+        <v>80.27</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>75.28</v>
+        <v>75.62</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>59.95</v>
+        <v>72.27</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>LOTUSDEV</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2568,22 +2368,22 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>854.75</v>
+        <v>215.13</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>77.73999999999999</v>
+        <v>72.14</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>82.90000000000001</v>
+        <v>68.95</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>88.94</v>
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>WELENT</t>
+          <t>SHILPAMED</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2592,22 +2392,22 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>797.95</v>
+        <v>1021.1</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>75.19</v>
+        <v>70.03</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>75.42</v>
+        <v>92.03</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>71.2</v>
+        <v>85.47</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>SHAREINDIA</t>
+          <t>NEOGEN</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2616,22 +2416,22 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>196.32</v>
+        <v>2488.4</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>74.19</v>
+        <v>69.81999999999999</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>66.91</v>
+        <v>72.69</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>52.92</v>
+        <v>67.48999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ELLEN</t>
+          <t>STAR</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2640,22 +2440,22 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>373.5</v>
+        <v>1200.2</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>73.16</v>
+        <v>69.13</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>67.61</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>45.62</v>
+        <v>64.25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>PCJEWELLER</t>
+          <t>MAHSEAMLES</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2664,22 +2464,22 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>13.7</v>
+        <v>720.2</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>73.02</v>
+        <v>67.83</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>72.81</v>
+        <v>71.75</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>59.64</v>
+        <v>59.25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>MANYAVAR</t>
+          <t>JKPAPER</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2688,22 +2488,22 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>582.35</v>
+        <v>430.6</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>71.89</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>70.09999999999999</v>
+        <v>69.91</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>42.96</v>
+        <v>58.82</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>LOTUSDEV</t>
+          <t>EMIL</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2712,22 +2512,22 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>209.27</v>
+        <v>196.28</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>71.87</v>
+        <v>65.37</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>67.55</v>
+        <v>73.34</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v/>
+        <v>63.03</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>IONEXCHANG</t>
+          <t>SANSERA</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2736,22 +2536,22 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>445.7</v>
+        <v>4259.9</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>71.13</v>
+        <v>65.02</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>60.3</v>
+        <v>82.23999999999999</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>51.63</v>
+        <v>86.04000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>SMLMAH</t>
+          <t>QPOWER</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -2760,22 +2560,22 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>6583</v>
+        <v>1536.1</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>70.98</v>
+        <v>64.06</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>72.28</v>
+        <v>67.06</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>71.23999999999999</v>
+        <v>70.23999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>GODREJAGRO</t>
+          <t>ELLEN</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -2784,22 +2584,22 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>675.85</v>
+        <v>371</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>69.37</v>
+        <v>63.92</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>69.20999999999999</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>55.17</v>
+        <v>44.53</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>WABAG</t>
+          <t>BLACKBUCK</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -2808,22 +2608,22 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2277.9</v>
+        <v>632.4</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>69.27</v>
+        <v>63.26</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>69.40000000000001</v>
+        <v>57.52</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>71.92</v>
+        <v>61.74</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>MANORAMA</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -2832,22 +2632,22 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2084.2</v>
+        <v>568.7</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>69.23999999999999</v>
+        <v>63.1</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>76.70999999999999</v>
+        <v>65.86</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>73.23999999999999</v>
+        <v>67.48</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>WELENT</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -2856,22 +2656,22 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>227.13</v>
+        <v>768</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>69.12</v>
+        <v>62.69</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>73.34999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>67.98</v>
+        <v>72.66</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>RATNAMANI</t>
+          <t>HERITGFOOD</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -2880,22 +2680,22 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2823</v>
+        <v>408.65</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>68.12</v>
+        <v>62.65</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>60.05</v>
+        <v>68.31</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>54.74</v>
+        <v>54.46</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>ENTERO</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2904,22 +2704,22 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1792.9</v>
+        <v>584.85</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>68.04000000000001</v>
+        <v>61.81</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>77.31</v>
+        <v>68.97</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>73.48</v>
+        <v>58.77</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>WAKEFIT</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -2928,22 +2728,22 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>155.13</v>
+        <v>818.8</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>67.73999999999999</v>
+        <v>61.46</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>57.39</v>
+        <v>72.92</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v/>
+        <v>87.76000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>NEOGEN</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -2952,22 +2752,22 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2388.9</v>
+        <v>656.25</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>67.45999999999999</v>
+        <v>61.36</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>70</v>
+        <v>74.8</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>65.89</v>
+        <v>70.87</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>SUDARSCHEM</t>
+          <t>APLLTD</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -2976,22 +2776,22 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1270.8</v>
+        <v>845.75</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>66.44</v>
+        <v>61.35</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>68.31999999999999</v>
+        <v>61.25</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>60.63</v>
+        <v>50.89</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>APOLLO</t>
+          <t>DYNAMATECH</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -3000,22 +2800,22 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>422.25</v>
+        <v>12061</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>66.19</v>
+        <v>61</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>62.7</v>
+        <v>61.64</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>69.72</v>
+        <v>68.72</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>HERITGFOOD</t>
+          <t>AVL</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3024,22 +2824,22 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>398.05</v>
+        <v>633.25</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>66.18000000000001</v>
+        <v>60.93</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>68.17</v>
+        <v>61.56</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>54.39</v>
+        <v>64.20999999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>AXISCADES</t>
+          <t>SMLMAH</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -3048,22 +2848,22 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1831.8</v>
+        <v>6292.5</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>66.18000000000001</v>
+        <v>60.41</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>57.97</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>63.99</v>
+        <v>70.16</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>SHILPAMED</t>
+          <t>EDELWEISS</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -3072,22 +2872,22 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>939.9</v>
+        <v>136.25</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>66.17</v>
+        <v>60.25</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>90.84999999999999</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>84.36</v>
+        <v>64.12</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>SANSERA</t>
+          <t>TSFINV</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -3096,22 +2896,22 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>4129.9</v>
+        <v>438.5</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>66.01000000000001</v>
+        <v>60.01</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>80.8</v>
+        <v>57</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>85.42</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>JAMNAAUTO</t>
+          <t>IONEXCHANG</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -3120,22 +2920,22 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>135.46</v>
+        <v>426.25</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>65.75</v>
+        <v>59.16</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>55.51</v>
+        <v>59.5</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>58.38</v>
+        <v>51.34</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>PRSMJOHNSN</t>
+          <t>PCJEWELLER</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3144,22 +2944,22 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>115.22</v>
+        <v>12.72</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>65.62</v>
+        <v>59.15</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>44.28</v>
+        <v>64.66</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>41.23</v>
+        <v>57.45</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>BLUESTONE</t>
+          <t>AXISCADES</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -3168,22 +2968,22 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>890.35</v>
+        <v>1811.2</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>65.3</v>
+        <v>59.14</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>75.26000000000001</v>
+        <v>56.9</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v/>
+        <v>63.64</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>PRUDENT</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -3192,22 +2992,22 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>804.9</v>
+        <v>3501.6</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>65.29000000000001</v>
+        <v>58.72</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>73.3</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>80.13</v>
+        <v>65.31999999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>AWFIS</t>
+          <t>DIACABS</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -3216,22 +3016,22 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>293.2</v>
+        <v>366.8</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>64.72</v>
+        <v>58.18</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>44.64</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>34.19</v>
+        <v>81.69</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>DYNAMATECH</t>
+          <t>ENTERO</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -3240,22 +3040,22 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>12097</v>
+        <v>1731.8</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>64.64</v>
+        <v>58.07</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>62.02</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>68.84</v>
+        <v>69.19</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>RELIGARE</t>
+          <t>TVSSCS</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -3264,22 +3064,22 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>258.78</v>
+        <v>133.85</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>64.37</v>
+        <v>56.97</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>56.56</v>
+        <v>55.56</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>54.68</v>
+        <v>48.64</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MIDHANI</t>
+          <t>SHRIPISTON</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -3288,22 +3088,22 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>463.35</v>
+        <v>4576.6</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>63.82</v>
+        <v>56.92</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>62.02</v>
+        <v>69.67</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>58.15</v>
+        <v>78.66</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>VARROC</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -3312,22 +3112,22 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>370.3</v>
+        <v>851.15</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>63.75</v>
+        <v>56.89</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>72.97</v>
+        <v>75.97</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>67.38</v>
+        <v>70.64</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>VARROC</t>
+          <t>AARTIDRUGS</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -3336,22 +3136,22 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>872</v>
+        <v>431.8</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>63.68</v>
+        <v>56.83</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>78.3</v>
+        <v>61.77</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>71.09</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>TEXRAIL</t>
+          <t>CSBBANK</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -3360,22 +3160,22 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>117.81</v>
+        <v>336.15</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>63.66</v>
+        <v>56.65</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>57.17</v>
+        <v>46.3</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>46.85</v>
+        <v>46.96</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>TSFINV</t>
+          <t>GODREJAGRO</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -3384,22 +3184,22 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>441.15</v>
+        <v>647.35</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>63.15</v>
+        <v>56.53</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>53.4</v>
+        <v>65.23999999999999</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>55.16</v>
+        <v>54.15</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>INOXINDIA</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -3408,22 +3208,22 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>2246.6</v>
+        <v>218.35</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>63.04</v>
+        <v>56.31</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>81.04000000000001</v>
+        <v>66.52</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>84.12</v>
+        <v>66.61</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>NESCO</t>
+          <t>PRSMJOHNSN</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -3432,22 +3232,22 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>1102.2</v>
+        <v>113.44</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>62.99</v>
+        <v>55.98</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>49.58</v>
+        <v>49.31</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>52.51</v>
+        <v>42.91</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>AKUMS</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -3456,22 +3256,22 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>2200.8</v>
+        <v>766.7</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>62.85</v>
+        <v>55.97</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>75.48</v>
+        <v>74.64</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v/>
+        <v>65.87</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>YATHARTH</t>
+          <t>SKFINDUS</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -3480,22 +3280,22 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>977.2</v>
+        <v>2940.3</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>62.5</v>
+        <v>55.54</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>65.75</v>
+        <v>64.7</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>65.73</v>
+        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>EMIL</t>
+          <t>RATNAMANI</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -3504,22 +3304,22 @@
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>188.38</v>
+        <v>2695</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>62.19</v>
+        <v>55.38</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>71.45</v>
+        <v>61.28</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>61.75</v>
+        <v>55.59</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>SUPRIYA</t>
+          <t>ICIL</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -3528,22 +3328,22 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>901.75</v>
+        <v>447.35</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>62.09</v>
+        <v>55.35</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>58.25</v>
+        <v>64.97</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>60.04</v>
+        <v>63.32</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>JKPAPER</t>
+          <t>TDPOWERSYS</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -3552,22 +3352,22 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>415.15</v>
+        <v>763.75</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>62</v>
+        <v>55.17</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>66.12</v>
+        <v>66.88</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>57.04</v>
+        <v>77.77</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>CRIZAC</t>
+          <t>TEXRAIL</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -3576,22 +3376,22 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>186.68</v>
+        <v>114.66</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>61.94</v>
+        <v>54.94</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>43.88</v>
+        <v>53.66</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v/>
+        <v>45.92</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>SKYGOLD</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -3600,22 +3400,22 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>827.4</v>
+        <v>2169.6</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>61.5</v>
+        <v>54.91</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>78.54000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>82.26000000000001</v>
+        <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>QPOWER</t>
+          <t>SUPRIYA</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -3624,22 +3424,22 @@
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>1458.2</v>
+        <v>877.85</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>60.88</v>
+        <v>54.84</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>63.31</v>
+        <v>58.6</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>68.16</v>
+        <v>60.21</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>WABAG</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -3648,22 +3448,22 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>1584.6</v>
+        <v>2132.6</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>60.67</v>
+        <v>54.78</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>73</v>
+        <v>62.1</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>69.86</v>
+        <v>69.73</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>OPTIEMUS</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -3672,22 +3472,22 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>329.4</v>
+        <v>590.1</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>60.52</v>
+        <v>54.65</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>73.78</v>
+        <v>60.85</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>67.64</v>
+        <v>55.85</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>AZAD</t>
+          <t>QUESS</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -3696,22 +3496,22 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>2849.1</v>
+        <v>353</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>60.41</v>
+        <v>54.63</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>69.16</v>
+        <v>70.11</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>72.58</v>
+        <v>51.48</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>AARTIDRUGS</t>
+          <t>AZAD</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -3720,22 +3520,22 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>437</v>
+        <v>2790.3</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>60.41</v>
+        <v>54.43</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>60.76</v>
+        <v>66.5</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>50.82</v>
+        <v>70.89</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>AKUMS</t>
+          <t>METROPOLIS</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -3744,22 +3544,22 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>776.35</v>
+        <v>586.3</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>60.32</v>
+        <v>54.16</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>74.01000000000001</v>
+        <v>63.61</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>65.41</v>
+        <v>64.27</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>GPPL</t>
+          <t>LXCHEM</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -3768,22 +3568,22 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>162.27</v>
+        <v>178.24</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>60.18</v>
+        <v>53.83</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>58.6</v>
+        <v>60.55</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>54.1</v>
+        <v>47.29</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>METROPOLIS</t>
+          <t>SKIPPER</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -3792,22 +3592,22 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>595.65</v>
+        <v>566.2</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>59.96</v>
+        <v>53.75</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>61.47</v>
+        <v>60.29</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>63.1</v>
+        <v>62.85</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>DIACABS</t>
+          <t>PRICOLLTD</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -3816,22 +3616,22 @@
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>351.5</v>
+        <v>767.5</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>59.7</v>
+        <v>53.75</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>78.01000000000001</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>81.81</v>
+        <v>67.31999999999999</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>CCAVENUE</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -3840,22 +3640,22 @@
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>332.55</v>
+        <v>16.08</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>59.29</v>
+        <v>53.66</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>70.90000000000001</v>
+        <v>51.65</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>73.34</v>
+        <v>45.05</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>CCAVENUE</t>
+          <t>TARC</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -3864,22 +3664,22 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>16.29</v>
+        <v>128.81</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>58.88</v>
+        <v>53.61</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>52.8</v>
+        <v>51.38</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>45.57</v>
+        <v>47.91</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>TARC</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -3888,22 +3688,22 @@
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>569.8</v>
+        <v>128.81</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>58.48</v>
+        <v>53.61</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>68.56999999999999</v>
+        <v>51.38</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>70</v>
+        <v>47.91</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>BECTORFOOD</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -3912,22 +3712,22 @@
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>242.5</v>
+        <v>2216.1</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>58.38</v>
+        <v>53.59</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>61.05</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>52.42</v>
+        <v>84.45999999999999</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>ALIVUS</t>
+          <t>NESCO</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -3936,22 +3736,22 @@
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>1390.2</v>
+        <v>1075.6</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>58.25</v>
+        <v>53.51</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>75.48</v>
+        <v>50.69</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>72.63</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>SUDEEPPHRM</t>
+          <t>RUBICON</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -3960,13 +3760,13 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>1213.5</v>
+        <v>1778.3</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>58.13</v>
+        <v>53.46</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>70.81999999999999</v>
+        <v>75.69</v>
       </c>
       <c r="F63" s="4" t="n">
         <v/>
@@ -3975,7 +3775,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>SFL</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -3984,22 +3784,22 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>697.95</v>
+        <v>362.55</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>57.77</v>
+        <v>53.33</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>54.25</v>
+        <v>72.41</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>48</v>
+        <v>67.16</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>EDELWEISS</t>
+          <t>ALIVUS</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -4008,22 +3808,22 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>132.43</v>
+        <v>1370.6</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>57.57</v>
+        <v>53.26</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>62.07</v>
+        <v>77.68000000000001</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>62.98</v>
+        <v>74.65000000000001</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>SMARTWORKS</t>
+          <t>GPPL</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -4032,22 +3832,22 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>535.55</v>
+        <v>160.35</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>57.42</v>
+        <v>53.17</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>63.04</v>
+        <v>57.25</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v/>
+        <v>53.72</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>CUPID</t>
+          <t>MTARTECH</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -4056,22 +3856,22 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>280</v>
+        <v>7202</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>57.38</v>
+        <v>53.15</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>84.8</v>
+        <v>60.7</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>92.84</v>
+        <v>70.86</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>KRBL</t>
+          <t>WAKEFIT</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -4080,22 +3880,22 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>423.25</v>
+        <v>146.85</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>57.32</v>
+        <v>53.08</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>63.1</v>
+        <v>52.15</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>58.28</v>
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>TMB</t>
+          <t>RELIGARE</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -4104,22 +3904,22 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>910.9</v>
+        <v>249.89</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>56.85</v>
+        <v>52.55</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>70.56999999999999</v>
+        <v>54.61</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>76.06</v>
+        <v>53.96</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>SKYGOLD</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -4128,22 +3928,22 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>2227</v>
+        <v>792.6</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>56.74</v>
+        <v>52.51</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>81.87</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>78.70999999999999</v>
+        <v>79.03</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>RENUKA</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -4152,22 +3952,22 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>24.87</v>
+        <v>320.15</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>56.7</v>
+        <v>52.36</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>53.09</v>
+        <v>69.53</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>41.29</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>MSTCLTD</t>
+          <t>SUDARSCHEM</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -4176,22 +3976,22 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>737.55</v>
+        <v>1205.4</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>56.65</v>
+        <v>51.93</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>67.2</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>60.69</v>
+        <v>61.34</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>ELECTCAST</t>
+          <t>LUMAXTECH</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -4200,22 +4000,22 @@
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>79.86</v>
+        <v>1941.8</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>56.43</v>
+        <v>51.73</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>50.82</v>
+        <v>68.34</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>44.55</v>
+        <v>72.66</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>SKFINDUS</t>
+          <t>SAMHI</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -4224,22 +4024,22 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>2935.4</v>
+        <v>160.27</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>56.34</v>
+        <v>51.59</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>61.79</v>
+        <v>47.59</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v/>
+        <v>46.51</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>RUBICON</t>
+          <t>EQUITASBNK</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -4248,22 +4048,22 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>1790</v>
+        <v>74.09</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>56.27</v>
+        <v>51.07</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>84.27</v>
+        <v>53.98</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v/>
+        <v>54.23</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>TARC</t>
+          <t>KNRCON</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -4272,22 +4072,22 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>128.56</v>
+        <v>124.8</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>56.23</v>
+        <v>50.92</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>50.17</v>
+        <v>45.03</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>47.49</v>
+        <v>35.07</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>TARC</t>
+          <t>TMB</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -4296,22 +4096,22 @@
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>128.56</v>
+        <v>895.75</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>56.23</v>
+        <v>50.92</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>50.17</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>47.49</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>MTARTECH</t>
+          <t>INOXINDIA</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -4320,22 +4120,22 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>7312.5</v>
+        <v>2098.8</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>56.22</v>
+        <v>50.81</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>62.12</v>
+        <v>68.04000000000001</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>71.23</v>
+        <v>80.37</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>WESTLIFE</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -4344,22 +4144,22 @@
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>569.6</v>
+        <v>156.23</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>55.79</v>
+        <v>50.78</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>58.18</v>
+        <v>48.93</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>45.46</v>
+        <v>53.91</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>VOLTAMP</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -4368,22 +4168,22 @@
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>10924</v>
+        <v>820.4</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>55.73</v>
+        <v>50.75</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>64.8</v>
+        <v>59.59</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>59.78</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>RAIN</t>
+          <t>PARKHOSPS</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -4392,22 +4192,22 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>217.28</v>
+        <v>282.05</v>
       </c>
       <c r="D81" s="4" t="n">
-        <v>55.68</v>
+        <v>50.73</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>65.59</v>
+        <v>61.05</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>60.41</v>
+        <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>PGIL</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -4416,22 +4216,22 @@
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>1189.2</v>
+        <v>318.2</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>55.41</v>
+        <v>50.63</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>67.70999999999999</v>
+        <v>67.08</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>72.84999999999999</v>
+        <v>71.25</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>BLUESTONE</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -4440,22 +4240,22 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>1640.3</v>
+        <v>831.2</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>54.82</v>
+        <v>50.51</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>72.79000000000001</v>
+        <v>66.08</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>79.05</v>
+        <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>RBA</t>
+          <t>MANORAMA</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -4464,22 +4264,22 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>98.05</v>
+        <v>1916.4</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>54.75</v>
+        <v>50.49</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>68.73</v>
+        <v>69.2</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>58.95</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>UTLSOLAR</t>
+          <t>WEWORK</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -4488,13 +4288,13 @@
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>441.25</v>
+        <v>682.85</v>
       </c>
       <c r="D85" s="4" t="n">
-        <v>54.5</v>
+        <v>50.39</v>
       </c>
       <c r="E85" s="4" t="n">
-        <v>70.70999999999999</v>
+        <v>55.63</v>
       </c>
       <c r="F85" s="4" t="n">
         <v/>
@@ -4503,7 +4303,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>BBOX</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -4512,22 +4312,22 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>562.4</v>
+        <v>766.4</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>54.48</v>
+        <v>50.15</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>64.73</v>
+        <v>53.41</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>56.54</v>
+        <v>60.98</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>PARAS</t>
+          <t>SKFINDIA</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -4536,22 +4336,22 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>1435.6</v>
+        <v>1546.3</v>
       </c>
       <c r="D87" s="4" t="n">
-        <v>54.02</v>
+        <v>50.13</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>68.14</v>
+        <v>40.09</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>70.31</v>
+        <v>32.69</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>PRIVISCL</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -4560,22 +4360,22 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>207.11</v>
+        <v>3480.7</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>54</v>
+        <v>50.07</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>51.66</v>
+        <v>53.52</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>44.92</v>
+        <v>66.37</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>MANYAVAR</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -4584,22 +4384,22 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>622.4</v>
+        <v>544.25</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>53.58</v>
+        <v>49.51</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>71.48</v>
+        <v>60.78</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>66.56</v>
+        <v>40.13</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>LUMAXTECH</t>
+          <t>CRIZAC</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -4608,22 +4408,22 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>1942.6</v>
+        <v>176.56</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>53.54</v>
+        <v>49.48</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>64.94</v>
+        <v>39.72</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>69.39</v>
+        <v/>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>ICIL</t>
+          <t>TIPSMUSIC</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -4632,22 +4432,22 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>439.45</v>
+        <v>654.55</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>53.4</v>
+        <v>49.4</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>64.42</v>
+        <v>53.54</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>62.82</v>
+        <v>58.25</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>FEDFINA</t>
+          <t>VGUARD</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -4656,22 +4456,22 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>158.88</v>
+        <v>327.15</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>53.14</v>
+        <v>49.31</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>56.66</v>
+        <v>52.94</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>59.67</v>
+        <v>47.72</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>RBA</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -4680,22 +4480,22 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>108.35</v>
+        <v>95.12</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>52.78</v>
+        <v>49.26</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>50.42</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>42.88</v>
+        <v>57.28</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>ARVINDFASN</t>
+          <t>MSTCLTD</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -4704,22 +4504,22 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>453.4</v>
+        <v>695.45</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>52.37</v>
+        <v>49.22</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>46.73</v>
+        <v>66.25</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>48.73</v>
+        <v>60.31</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>GSFC</t>
+          <t>SAFARI</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -4728,22 +4528,22 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>155.95</v>
+        <v>1520.5</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>52.32</v>
+        <v>49.22</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>46.12</v>
+        <v>42.26</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>45.02</v>
+        <v>40.84</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>ATLANTAELE</t>
+          <t>SMARTWORKS</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -4752,13 +4552,13 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>1805.4</v>
+        <v>519.9</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>52.32</v>
+        <v>48.72</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>57.41</v>
+        <v>65.88</v>
       </c>
       <c r="F96" s="4" t="n">
         <v/>
@@ -4767,7 +4567,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>TVSSCS</t>
+          <t>RAIN</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -4776,22 +4576,22 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>130.49</v>
+        <v>206.92</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>52.3</v>
+        <v>48.69</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>53.36</v>
+        <v>60.14</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>47.41</v>
+        <v>59.11</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>PRICOLLTD</t>
+          <t>PGIL</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -4800,22 +4600,22 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>761.4</v>
+        <v>1143.1</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>52.26</v>
+        <v>48.68</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>68.02</v>
+        <v>63.18</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>66.72</v>
+        <v>70.06999999999999</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>BALAMINES</t>
+          <t>PURVA</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -4824,22 +4624,22 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>2342.6</v>
+        <v>213.43</v>
       </c>
       <c r="D99" s="4" t="n">
-        <v>52.19</v>
+        <v>48.59</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>61.11</v>
+        <v>47.5</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>61.88</v>
+        <v>45.01</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>INOXGREEN</t>
+          <t>ORKLAINDIA</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -4848,22 +4648,22 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>178.21</v>
+        <v>578.25</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>52.04</v>
+        <v>48.45</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>48.68</v>
+        <v>49.51</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>52.36</v>
+        <v/>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>QUESS</t>
+          <t>DBL</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -4872,22 +4672,22 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>348</v>
+        <v>406.2</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>51.96</v>
+        <v>48.25</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>69.48999999999999</v>
+        <v>48.93</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>51.11</v>
+        <v>48.52</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>VMART</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -4896,22 +4696,22 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>825.75</v>
+        <v>808.15</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>51.88</v>
+        <v>48.24</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>60.25</v>
+        <v>60.27</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>57.77</v>
+        <v>54.56</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>BLACKBUCK</t>
+          <t>JUSTDIAL</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -4920,22 +4720,22 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>585.9</v>
+        <v>673.7</v>
       </c>
       <c r="D103" s="4" t="n">
-        <v>51.67</v>
+        <v>47.98</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>57.01</v>
+        <v>54.65</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>61.34</v>
+        <v>45.63</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>TIPSMUSIC</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -4944,22 +4744,22 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>658.4</v>
+        <v>1603.1</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>51.48</v>
+        <v>47.91</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>54.27</v>
+        <v>68.41</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>58.54</v>
+        <v>75.98</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>PRIVISCL</t>
+          <t>WESTLIFE</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -4968,22 +4768,22 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>3495.6</v>
+        <v>549.05</v>
       </c>
       <c r="D105" s="4" t="n">
-        <v>51.44</v>
+        <v>47.83</v>
       </c>
       <c r="E105" s="4" t="n">
-        <v>58.4</v>
+        <v>57.21</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>68.08</v>
+        <v>44.97</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>IIFLCAPS</t>
+          <t>AWFIS</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -4992,22 +4792,22 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>337.3</v>
+        <v>264.7</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>50.96</v>
+        <v>47.76</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>54.67</v>
+        <v>40.88</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>58.2</v>
+        <v>31.94</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>SHAILY</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -5016,22 +4816,22 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>3279.5</v>
+        <v>199.64</v>
       </c>
       <c r="D107" s="4" t="n">
-        <v>50.88</v>
+        <v>47.38</v>
       </c>
       <c r="E107" s="4" t="n">
-        <v>66.8</v>
+        <v>48.63</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>73.56</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>AGARWALEYE</t>
+          <t>IXIGO</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -5040,22 +4840,22 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>508.4</v>
+        <v>165.65</v>
       </c>
       <c r="D108" s="4" t="n">
-        <v>50.8</v>
+        <v>47.34</v>
       </c>
       <c r="E108" s="4" t="n">
-        <v>56.96</v>
+        <v>43.44</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>57.76</v>
+        <v>43.57</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>STARCEMENT</t>
+          <t>PNGJL</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -5064,22 +4864,22 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>194.68</v>
+        <v>604.75</v>
       </c>
       <c r="D109" s="4" t="n">
-        <v>50.75</v>
+        <v>47.25</v>
       </c>
       <c r="E109" s="4" t="n">
-        <v>39.36</v>
+        <v>50.59</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>46.44</v>
+        <v>49.44</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>PRUDENT</t>
+          <t>VOLTAMP</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -5088,22 +4888,22 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>3318.8</v>
+        <v>10513</v>
       </c>
       <c r="D110" s="4" t="n">
-        <v>50.68</v>
+        <v>47.22</v>
       </c>
       <c r="E110" s="4" t="n">
-        <v>66.34999999999999</v>
+        <v>60.49</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>63.09</v>
+        <v>58.67</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>STYL</t>
+          <t>SENCO</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -5112,22 +4912,22 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>385.9</v>
+        <v>348</v>
       </c>
       <c r="D111" s="4" t="n">
-        <v>50.59</v>
+        <v>46.81</v>
       </c>
       <c r="E111" s="4" t="n">
-        <v>62.36</v>
+        <v>50.5</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v/>
+        <v>49.73</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>PNGJL</t>
+          <t>PARAS</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -5136,22 +4936,22 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>611.05</v>
+        <v>1370.9</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>50.57</v>
+        <v>46.79</v>
       </c>
       <c r="E112" s="4" t="n">
-        <v>52.04</v>
+        <v>63.48</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>50.19</v>
+        <v>67.38</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>HCC</t>
+          <t>FINPIPE</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -5160,22 +4960,22 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>22.73</v>
+        <v>154.63</v>
       </c>
       <c r="D113" s="4" t="n">
-        <v>50.34</v>
+        <v>46.47</v>
       </c>
       <c r="E113" s="4" t="n">
-        <v>51.97</v>
+        <v>38.91</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>47.28</v>
+        <v>41.16</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>SOUTHBANK</t>
+          <t>INOXGREEN</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -5184,22 +4984,22 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>46.08</v>
+        <v>173.11</v>
       </c>
       <c r="D114" s="4" t="n">
-        <v>50.29</v>
+        <v>46.39</v>
       </c>
       <c r="E114" s="4" t="n">
-        <v>58.8</v>
+        <v>45.61</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>70.04000000000001</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>EPL</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -5208,22 +5008,22 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>535.75</v>
+        <v>239.35</v>
       </c>
       <c r="D115" s="4" t="n">
-        <v>50.16</v>
+        <v>46.24</v>
       </c>
       <c r="E115" s="4" t="n">
-        <v>58.9</v>
+        <v>53.92</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>61.93</v>
+        <v>55.49</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>VMART</t>
+          <t>IIFLCAPS</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -5232,22 +5032,22 @@
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>817.8</v>
+        <v>335.6</v>
       </c>
       <c r="D116" s="4" t="n">
-        <v>49.97</v>
+        <v>46.06</v>
       </c>
       <c r="E116" s="4" t="n">
-        <v>60.41</v>
+        <v>57.61</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>54.6</v>
+        <v>58.89</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>VGUARD</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -5256,22 +5056,22 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>328.75</v>
+        <v>1446.2</v>
       </c>
       <c r="D117" s="4" t="n">
-        <v>49.95</v>
+        <v>45.99</v>
       </c>
       <c r="E117" s="4" t="n">
-        <v>52.08</v>
+        <v>61.16</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>47.42</v>
+        <v>64.69</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>ADVENZYMES</t>
+          <t>JAMNAAUTO</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -5280,22 +5080,22 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>303.35</v>
+        <v>125.03</v>
       </c>
       <c r="D118" s="4" t="n">
-        <v>49.85</v>
+        <v>45.98</v>
       </c>
       <c r="E118" s="4" t="n">
-        <v>40.55</v>
+        <v>49.21</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>46.22</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>OPTIEMUS</t>
+          <t>VIPIND</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -5304,22 +5104,22 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>566.25</v>
+        <v>299.1</v>
       </c>
       <c r="D119" s="4" t="n">
-        <v>49.84</v>
+        <v>45.81</v>
       </c>
       <c r="E119" s="4" t="n">
-        <v>58.09</v>
+        <v>42.4</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>54.59</v>
+        <v>36.18</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>HCG</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -5328,22 +5128,22 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>700.9</v>
+        <v>541.6</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>49.72</v>
+        <v>45.55</v>
       </c>
       <c r="E120" s="4" t="n">
-        <v>60.29</v>
+        <v>62.7</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>61.82</v>
+        <v>68.64</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>ORKLAINDIA</t>
+          <t>INDIASHLTR</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -5352,22 +5152,22 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>578.5</v>
+        <v>661.6</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>49.61</v>
+        <v>45.31</v>
       </c>
       <c r="E121" s="4" t="n">
-        <v>48.18</v>
+        <v>41.3</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v/>
+        <v>43.33</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>SHAKTIPUMP</t>
+          <t>KIRLOSBROS</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -5376,22 +5176,22 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>493.8</v>
+        <v>1811.4</v>
       </c>
       <c r="D122" s="4" t="n">
-        <v>49.53</v>
+        <v>45.27</v>
       </c>
       <c r="E122" s="4" t="n">
-        <v>39.57</v>
+        <v>51.17</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>44.03</v>
+        <v>53.34</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>JAIBALAJI</t>
+          <t>AGARWALEYE</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -5400,22 +5200,22 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>67.53</v>
+        <v>500.15</v>
       </c>
       <c r="D123" s="4" t="n">
-        <v>49.41</v>
+        <v>45.08</v>
       </c>
       <c r="E123" s="4" t="n">
-        <v>46.45</v>
+        <v>54.64</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>41.81</v>
+        <v>56.35</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>BANCOINDIA</t>
+          <t>THYROCARE</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -5424,22 +5224,22 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>619.5</v>
+        <v>559.25</v>
       </c>
       <c r="D124" s="4" t="n">
-        <v>48.67</v>
+        <v>45.08</v>
       </c>
       <c r="E124" s="4" t="n">
-        <v>48.12</v>
+        <v>57.02</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>56.46</v>
+        <v>64.51000000000001</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>BAJAJELEC</t>
+          <t>MAHSCOOTER</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -5448,22 +5248,22 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>337.75</v>
+        <v>13123</v>
       </c>
       <c r="D125" s="4" t="n">
-        <v>48.52</v>
+        <v>45.01</v>
       </c>
       <c r="E125" s="4" t="n">
-        <v>42.08</v>
+        <v>55.28</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>30.94</v>
+        <v>59.02</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>AVL</t>
+          <t>HCC</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -5472,22 +5272,22 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>603.55</v>
+        <v>21.77</v>
       </c>
       <c r="D126" s="4" t="n">
-        <v>48.32</v>
+        <v>44.98</v>
       </c>
       <c r="E126" s="4" t="n">
-        <v>58.29</v>
+        <v>49.17</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>62.35</v>
+        <v>46.36</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>KNRCON</t>
+          <t>AEQUS</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -5496,22 +5296,22 @@
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>123.68</v>
+        <v>231.67</v>
       </c>
       <c r="D127" s="4" t="n">
-        <v>48.13</v>
+        <v>44.92</v>
       </c>
       <c r="E127" s="4" t="n">
-        <v>45.42</v>
+        <v>58.11</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>35.25</v>
+        <v/>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>PURVA</t>
+          <t>GMRP&amp;UI</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -5520,22 +5320,22 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>214.16</v>
+        <v>92.31</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>48.05</v>
+        <v>44.52</v>
       </c>
       <c r="E128" s="4" t="n">
-        <v>46.83</v>
+        <v>37.37</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>44.77</v>
+        <v>47.71</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>SKIPPER</t>
+          <t>SFL</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -5544,22 +5344,22 @@
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>551.55</v>
+        <v>663.05</v>
       </c>
       <c r="D129" s="4" t="n">
-        <v>47.94</v>
+        <v>44.39</v>
       </c>
       <c r="E129" s="4" t="n">
-        <v>58.07</v>
+        <v>49.57</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>61.73</v>
+        <v>46.14</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>SHRIPISTON</t>
+          <t>SUDEEPPHRM</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -5568,22 +5368,22 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>4447.4</v>
+        <v>1105.4</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>47.84</v>
+        <v>44.03</v>
       </c>
       <c r="E130" s="4" t="n">
-        <v>65.56</v>
+        <v>66.56</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>73.76000000000001</v>
+        <v/>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>DBL</t>
+          <t>ASTRAMICRO</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -5592,22 +5392,22 @@
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>407.75</v>
+        <v>1631.2</v>
       </c>
       <c r="D131" s="4" t="n">
-        <v>47.51</v>
+        <v>43.97</v>
       </c>
       <c r="E131" s="4" t="n">
-        <v>42.7</v>
+        <v>57.83</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>45.72</v>
+        <v>68.37</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>LXCHEM</t>
+          <t>POWERMECH</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -5616,22 +5416,22 @@
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>170.63</v>
+        <v>2371.4</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>47.42</v>
+        <v>43.96</v>
       </c>
       <c r="E132" s="4" t="n">
-        <v>59.02</v>
+        <v>45.8</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>46.64</v>
+        <v>49.21</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>APLLTD</t>
+          <t>SAATVIKGL</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -5640,22 +5440,22 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>810.95</v>
+        <v>404.5</v>
       </c>
       <c r="D133" s="4" t="n">
-        <v>47.4</v>
+        <v>43.89</v>
       </c>
       <c r="E133" s="4" t="n">
-        <v>54.84</v>
+        <v>44.85</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>48.69</v>
+        <v/>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>INDIASHLTR</t>
+          <t>SOUTHBANK</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -5664,46 +5464,46 @@
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>672.15</v>
+        <v>45.19</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>47.29</v>
+        <v>43.76</v>
       </c>
       <c r="E134" s="4" t="n">
-        <v>35.28</v>
+        <v>58.41</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>39.84</v>
+        <v>69.93000000000001</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="inlineStr">
-        <is>
-          <t>BALUFORGE</t>
-        </is>
-      </c>
-      <c r="B135" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C135" s="4" t="n">
-        <v>536.65</v>
-      </c>
-      <c r="D135" s="4" t="n">
-        <v>47.19</v>
-      </c>
-      <c r="E135" s="4" t="n">
-        <v>53.66</v>
-      </c>
-      <c r="F135" s="4" t="n">
-        <v>50.57</v>
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>CUPID</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C135" s="7" t="n">
+        <v>265</v>
+      </c>
+      <c r="D135" s="7" t="n">
+        <v>43.74</v>
+      </c>
+      <c r="E135" s="7" t="n">
+        <v>75.70999999999999</v>
+      </c>
+      <c r="F135" s="7" t="n">
+        <v>87.01000000000001</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>STYRENIX</t>
+          <t>MIDHANI</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -5712,22 +5512,22 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>2113.1</v>
+        <v>407.85</v>
       </c>
       <c r="D136" s="4" t="n">
-        <v>47.17</v>
+        <v>43.73</v>
       </c>
       <c r="E136" s="4" t="n">
-        <v>47.04</v>
+        <v>53.37</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>49.87</v>
+        <v>55.49</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>ASTRAMICRO</t>
+          <t>GSFC</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -5736,22 +5536,22 @@
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>1680.6</v>
+        <v>152.27</v>
       </c>
       <c r="D137" s="4" t="n">
-        <v>47.08</v>
+        <v>43.66</v>
       </c>
       <c r="E137" s="4" t="n">
-        <v>61.43</v>
+        <v>41.85</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>70.15000000000001</v>
+        <v>43.61</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>UJJIVANSFB</t>
+          <t>GREAVESCOT</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -5760,22 +5560,22 @@
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>66.52</v>
+        <v>191.72</v>
       </c>
       <c r="D138" s="4" t="n">
-        <v>47.06</v>
+        <v>43.65</v>
       </c>
       <c r="E138" s="4" t="n">
-        <v>54.96</v>
+        <v>50.78</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>60.72</v>
+        <v>51.99</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>RAYMONDLSL</t>
+          <t>AURIONPRO</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -5784,46 +5584,46 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>687.65</v>
+        <v>688</v>
       </c>
       <c r="D139" s="4" t="n">
-        <v>47.06</v>
+        <v>43.61</v>
       </c>
       <c r="E139" s="4" t="n">
+        <v>34.82</v>
+      </c>
+      <c r="F139" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="F139" s="4" t="n">
-        <v>25.89</v>
-      </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>WEWORK</t>
-        </is>
-      </c>
-      <c r="B140" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C140" s="4" t="n">
-        <v>676.95</v>
-      </c>
-      <c r="D140" s="4" t="n">
-        <v>46.29</v>
-      </c>
-      <c r="E140" s="4" t="n">
-        <v>54.12</v>
-      </c>
-      <c r="F140" s="4" t="n">
-        <v/>
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t>SHAILY</t>
+        </is>
+      </c>
+      <c r="B140" s="6" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C140" s="7" t="n">
+        <v>3149.8</v>
+      </c>
+      <c r="D140" s="7" t="n">
+        <v>43.44</v>
+      </c>
+      <c r="E140" s="7" t="n">
+        <v>60.73</v>
+      </c>
+      <c r="F140" s="7" t="n">
+        <v>70.34</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>V2RETAIL</t>
+          <t>RENUKA</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -5832,22 +5632,22 @@
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>218.13</v>
+        <v>23.06</v>
       </c>
       <c r="D141" s="4" t="n">
-        <v>46.18</v>
+        <v>43.37</v>
       </c>
       <c r="E141" s="4" t="n">
-        <v>50.41</v>
+        <v>45.32</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>62.44</v>
+        <v>39.17</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>GMRP&amp;UI</t>
+          <t>STYRENIX</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -5856,22 +5656,22 @@
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>94.06999999999999</v>
+        <v>2067.9</v>
       </c>
       <c r="D142" s="4" t="n">
-        <v>46.14</v>
+        <v>43.31</v>
       </c>
       <c r="E142" s="4" t="n">
-        <v>39.3</v>
+        <v>45.06</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>48.44</v>
+        <v>48.91</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>PARKHOSPS</t>
+          <t>UJJIVANSFB</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -5880,22 +5680,22 @@
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>279.3</v>
+        <v>64.83</v>
       </c>
       <c r="D143" s="4" t="n">
-        <v>45.96</v>
+        <v>43.3</v>
       </c>
       <c r="E143" s="4" t="n">
-        <v>60.05</v>
+        <v>54.07</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v/>
+        <v>60.25</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>BBOX</t>
+          <t>V2RETAIL</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -5904,22 +5704,22 @@
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>744.85</v>
+        <v>214.03</v>
       </c>
       <c r="D144" s="4" t="n">
-        <v>45.9</v>
+        <v>43.1</v>
       </c>
       <c r="E144" s="4" t="n">
-        <v>53.38</v>
+        <v>48.07</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>60.96</v>
+        <v>61.02</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>VIPIND</t>
+          <t>UTLSOLAR</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -5928,22 +5728,22 @@
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>301.55</v>
+        <v>408.95</v>
       </c>
       <c r="D145" s="4" t="n">
-        <v>45.73</v>
+        <v>42.91</v>
       </c>
       <c r="E145" s="4" t="n">
-        <v>42.74</v>
+        <v>63.28</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>36.29</v>
+        <v/>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>JUSTDIAL</t>
+          <t>KRBL</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -5952,22 +5752,22 @@
         </is>
       </c>
       <c r="C146" s="4" t="n">
-        <v>668.75</v>
+        <v>394.85</v>
       </c>
       <c r="D146" s="4" t="n">
-        <v>45.42</v>
+        <v>42.74</v>
       </c>
       <c r="E146" s="4" t="n">
-        <v>54.17</v>
+        <v>53.96</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>45.44</v>
+        <v>54.8</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>JSLL</t>
+          <t>REDTAPE</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -5976,22 +5776,22 @@
         </is>
       </c>
       <c r="C147" s="4" t="n">
-        <v>511.85</v>
+        <v>117.34</v>
       </c>
       <c r="D147" s="4" t="n">
-        <v>45.4</v>
+        <v>42.59</v>
       </c>
       <c r="E147" s="4" t="n">
-        <v>38.89</v>
+        <v>42.21</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>40.72</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>SAMHI</t>
+          <t>VIYASH</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -6000,22 +5800,22 @@
         </is>
       </c>
       <c r="C148" s="4" t="n">
-        <v>157.07</v>
+        <v>249.65</v>
       </c>
       <c r="D148" s="4" t="n">
-        <v>45.29</v>
+        <v>42.55</v>
       </c>
       <c r="E148" s="4" t="n">
-        <v>44.11</v>
+        <v>50.73</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>45.12</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>SAFARI</t>
+          <t>JAYNECOIND</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -6024,22 +5824,22 @@
         </is>
       </c>
       <c r="C149" s="4" t="n">
-        <v>1501.6</v>
+        <v>88.94</v>
       </c>
       <c r="D149" s="4" t="n">
-        <v>45.18</v>
+        <v>42.45</v>
       </c>
       <c r="E149" s="4" t="n">
-        <v>45</v>
+        <v>49.79</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>42.17</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>JAYNECOIND</t>
+          <t>JAIBALAJI</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -6048,22 +5848,22 @@
         </is>
       </c>
       <c r="C150" s="4" t="n">
-        <v>91.29000000000001</v>
+        <v>64.05</v>
       </c>
       <c r="D150" s="4" t="n">
-        <v>45.16</v>
+        <v>42.33</v>
       </c>
       <c r="E150" s="4" t="n">
-        <v>50.42</v>
+        <v>45.95</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>58.93</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>KSB</t>
+          <t>MEDPLUS</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -6072,22 +5872,22 @@
         </is>
       </c>
       <c r="C151" s="4" t="n">
-        <v>804.2</v>
+        <v>659.65</v>
       </c>
       <c r="D151" s="4" t="n">
-        <v>45.08</v>
+        <v>42.32</v>
       </c>
       <c r="E151" s="4" t="n">
-        <v>45.44</v>
+        <v>29.65</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>51.5</v>
+        <v>38.99</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>GAEL</t>
+          <t>BECTORFOOD</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -6096,22 +5896,22 @@
         </is>
       </c>
       <c r="C152" s="4" t="n">
-        <v>164.8</v>
+        <v>221.55</v>
       </c>
       <c r="D152" s="4" t="n">
-        <v>44.94</v>
+        <v>42.31</v>
       </c>
       <c r="E152" s="4" t="n">
-        <v>54.63</v>
+        <v>53.05</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>60.62</v>
+        <v>48.44</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>EPL</t>
+          <t>RATEGAIN</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -6120,22 +5920,22 @@
         </is>
       </c>
       <c r="C153" s="4" t="n">
-        <v>239.3</v>
+        <v>860.95</v>
       </c>
       <c r="D153" s="4" t="n">
-        <v>44.75</v>
+        <v>41.88</v>
       </c>
       <c r="E153" s="4" t="n">
-        <v>53.9</v>
+        <v>55.45</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>55.47</v>
+        <v>60.89</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>VIYASH</t>
+          <t>BALAMINES</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -6144,46 +5944,46 @@
         </is>
       </c>
       <c r="C154" s="4" t="n">
-        <v>257.6</v>
+        <v>2149.8</v>
       </c>
       <c r="D154" s="4" t="n">
-        <v>44.59</v>
+        <v>41.85</v>
       </c>
       <c r="E154" s="4" t="n">
-        <v>53.52</v>
+        <v>57.35</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>61.24</v>
+        <v>59.29</v>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="inlineStr">
-        <is>
-          <t>SKFINDIA</t>
-        </is>
-      </c>
-      <c r="B155" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C155" s="4" t="n">
-        <v>1531.6</v>
-      </c>
-      <c r="D155" s="4" t="n">
-        <v>44.54</v>
-      </c>
-      <c r="E155" s="4" t="n">
-        <v>37.52</v>
-      </c>
-      <c r="F155" s="4" t="n">
-        <v>32.48</v>
+      <c r="A155" s="5" t="inlineStr">
+        <is>
+          <t>HCG</t>
+        </is>
+      </c>
+      <c r="B155" s="6" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C155" s="7" t="n">
+        <v>674.15</v>
+      </c>
+      <c r="D155" s="7" t="n">
+        <v>41.83</v>
+      </c>
+      <c r="E155" s="7" t="n">
+        <v>62.97</v>
+      </c>
+      <c r="F155" s="7" t="n">
+        <v>63.5</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>ZAGGLE</t>
+          <t>CERA</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -6192,22 +5992,22 @@
         </is>
       </c>
       <c r="C156" s="4" t="n">
-        <v>183.93</v>
+        <v>5646</v>
       </c>
       <c r="D156" s="4" t="n">
-        <v>44.35</v>
+        <v>41.57</v>
       </c>
       <c r="E156" s="4" t="n">
-        <v>35.26</v>
+        <v>47.9</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>38.14</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>GOKEX</t>
+          <t>INDIGOPNTS</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -6216,46 +6016,46 @@
         </is>
       </c>
       <c r="C157" s="4" t="n">
-        <v>774.2</v>
+        <v>1081.6</v>
       </c>
       <c r="D157" s="4" t="n">
-        <v>44.32</v>
+        <v>41.48</v>
       </c>
       <c r="E157" s="4" t="n">
-        <v>52.49</v>
+        <v>55.59</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>50.93</v>
+        <v>48.65</v>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="5" t="inlineStr">
-        <is>
-          <t>GRWRHITECH</t>
-        </is>
-      </c>
-      <c r="B158" s="6" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C158" s="7" t="n">
-        <v>6905</v>
-      </c>
-      <c r="D158" s="7" t="n">
-        <v>44.15</v>
-      </c>
-      <c r="E158" s="7" t="n">
-        <v>67.72</v>
-      </c>
-      <c r="F158" s="7" t="n">
-        <v>67.95999999999999</v>
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>JYOTHYLAB</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C158" s="4" t="n">
+        <v>195.41</v>
+      </c>
+      <c r="D158" s="4" t="n">
+        <v>41.35</v>
+      </c>
+      <c r="E158" s="4" t="n">
+        <v>37.76</v>
+      </c>
+      <c r="F158" s="4" t="n">
+        <v>37.04</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>DATAMATICS</t>
+          <t>BALUFORGE</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -6264,22 +6064,22 @@
         </is>
       </c>
       <c r="C159" s="4" t="n">
-        <v>775.45</v>
+        <v>501.45</v>
       </c>
       <c r="D159" s="4" t="n">
-        <v>44.03</v>
+        <v>40.95</v>
       </c>
       <c r="E159" s="4" t="n">
-        <v>45.95</v>
+        <v>52.21</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>52.88</v>
+        <v>50.03</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>SENCO</t>
+          <t>TIMETECHNO</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -6288,22 +6088,22 @@
         </is>
       </c>
       <c r="C160" s="4" t="n">
-        <v>346.4</v>
+        <v>179.24</v>
       </c>
       <c r="D160" s="4" t="n">
-        <v>43.36</v>
+        <v>40.89</v>
       </c>
       <c r="E160" s="4" t="n">
-        <v>50.08</v>
+        <v>45.48</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>49.58</v>
+        <v>50.64</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>SANDUMA</t>
+          <t>FEDFINA</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -6312,22 +6112,22 @@
         </is>
       </c>
       <c r="C161" s="4" t="n">
-        <v>196.74</v>
+        <v>150.76</v>
       </c>
       <c r="D161" s="4" t="n">
-        <v>43.28</v>
+        <v>40.81</v>
       </c>
       <c r="E161" s="4" t="n">
-        <v>43.05</v>
+        <v>53.3</v>
       </c>
       <c r="F161" s="4" t="n">
-        <v>52.26</v>
+        <v>58.24</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>PRAJIND</t>
+          <t>GRINDWELL</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -6336,22 +6136,22 @@
         </is>
       </c>
       <c r="C162" s="4" t="n">
-        <v>326.85</v>
+        <v>1895.6</v>
       </c>
       <c r="D162" s="4" t="n">
-        <v>43.24</v>
+        <v>40.66</v>
       </c>
       <c r="E162" s="4" t="n">
-        <v>44.39</v>
+        <v>49.46</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>42.35</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>SPARC</t>
+          <t>REFEX</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -6360,22 +6160,22 @@
         </is>
       </c>
       <c r="C163" s="4" t="n">
-        <v>196.01</v>
+        <v>271.75</v>
       </c>
       <c r="D163" s="4" t="n">
-        <v>42.63</v>
+        <v>40.55</v>
       </c>
       <c r="E163" s="4" t="n">
-        <v>51.09</v>
+        <v>43.46</v>
       </c>
       <c r="F163" s="4" t="n">
-        <v>52.95</v>
+        <v>47.45</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>MAHSCOOTER</t>
+          <t>JSFB</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -6384,22 +6184,22 @@
         </is>
       </c>
       <c r="C164" s="4" t="n">
-        <v>13098</v>
+        <v>506.6</v>
       </c>
       <c r="D164" s="4" t="n">
-        <v>42.47</v>
+        <v>40.49</v>
       </c>
       <c r="E164" s="4" t="n">
-        <v>49</v>
+        <v>56.51</v>
       </c>
       <c r="F164" s="4" t="n">
-        <v>54.96</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>ROUTE</t>
+          <t>DATAMATICS</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -6408,22 +6208,22 @@
         </is>
       </c>
       <c r="C165" s="4" t="n">
-        <v>500.75</v>
+        <v>758.35</v>
       </c>
       <c r="D165" s="4" t="n">
-        <v>42.45</v>
+        <v>40.47</v>
       </c>
       <c r="E165" s="4" t="n">
-        <v>39.66</v>
+        <v>46.74</v>
       </c>
       <c r="F165" s="4" t="n">
-        <v>29.99</v>
+        <v>53.23</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>VIKRAMSOLR</t>
+          <t>STARCEMENT</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -6432,22 +6232,22 @@
         </is>
       </c>
       <c r="C166" s="4" t="n">
-        <v>165.61</v>
+        <v>187.3</v>
       </c>
       <c r="D166" s="4" t="n">
-        <v>42.43</v>
+        <v>40.44</v>
       </c>
       <c r="E166" s="4" t="n">
-        <v>37.08</v>
+        <v>38.78</v>
       </c>
       <c r="F166" s="4" t="n">
-        <v/>
+        <v>46.19</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>RATEGAIN</t>
+          <t>VIKRAMSOLR</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -6456,22 +6256,22 @@
         </is>
       </c>
       <c r="C167" s="4" t="n">
-        <v>866.45</v>
+        <v>163.37</v>
       </c>
       <c r="D167" s="4" t="n">
-        <v>42.25</v>
+        <v>40.34</v>
       </c>
       <c r="E167" s="4" t="n">
-        <v>57.81</v>
+        <v>36.58</v>
       </c>
       <c r="F167" s="4" t="n">
-        <v>62.21</v>
+        <v/>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENGG</t>
+          <t>ZAGGLE</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -6480,22 +6280,22 @@
         </is>
       </c>
       <c r="C168" s="4" t="n">
-        <v>82.76000000000001</v>
+        <v>177.81</v>
       </c>
       <c r="D168" s="4" t="n">
-        <v>41.97</v>
+        <v>40.19</v>
       </c>
       <c r="E168" s="4" t="n">
-        <v>57.13</v>
+        <v>32.9</v>
       </c>
       <c r="F168" s="4" t="n">
-        <v>60.88</v>
+        <v>37.26</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>GREAVESCOT</t>
+          <t>CMSINFO</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -6504,22 +6304,22 @@
         </is>
       </c>
       <c r="C169" s="4" t="n">
-        <v>193.6</v>
+        <v>230.93</v>
       </c>
       <c r="D169" s="4" t="n">
-        <v>41.92</v>
+        <v>39.72</v>
       </c>
       <c r="E169" s="4" t="n">
-        <v>48.73</v>
+        <v>30.95</v>
       </c>
       <c r="F169" s="4" t="n">
-        <v>51.1</v>
+        <v>31.86</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>ASHOKA</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -6528,22 +6328,22 @@
         </is>
       </c>
       <c r="C170" s="4" t="n">
-        <v>113.53</v>
+        <v>102.01</v>
       </c>
       <c r="D170" s="4" t="n">
-        <v>41.69</v>
+        <v>39.63</v>
       </c>
       <c r="E170" s="4" t="n">
-        <v>37.07</v>
+        <v>48.23</v>
       </c>
       <c r="F170" s="4" t="n">
-        <v>40.9</v>
+        <v>42.13</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>AVANTIFEED</t>
+          <t>MASTEK</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -6552,22 +6352,22 @@
         </is>
       </c>
       <c r="C171" s="4" t="n">
-        <v>815.3</v>
+        <v>1588.2</v>
       </c>
       <c r="D171" s="4" t="n">
-        <v>41.58</v>
+        <v>39.62</v>
       </c>
       <c r="E171" s="4" t="n">
-        <v>35.16</v>
+        <v>43.45</v>
       </c>
       <c r="F171" s="4" t="n">
-        <v>49.17</v>
+        <v>40.89</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>THYROCARE</t>
+          <t>ORIENTCEM</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -6576,22 +6376,22 @@
         </is>
       </c>
       <c r="C172" s="4" t="n">
-        <v>557.7</v>
+        <v>124.55</v>
       </c>
       <c r="D172" s="4" t="n">
-        <v>41.5</v>
+        <v>39.29</v>
       </c>
       <c r="E172" s="4" t="n">
-        <v>56.14</v>
+        <v>31.67</v>
       </c>
       <c r="F172" s="4" t="n">
-        <v>63.82</v>
+        <v>34.22</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>ATLANTAELE</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -6600,22 +6400,22 @@
         </is>
       </c>
       <c r="C173" s="4" t="n">
-        <v>152.78</v>
+        <v>1633.3</v>
       </c>
       <c r="D173" s="4" t="n">
-        <v>41.32</v>
+        <v>39.28</v>
       </c>
       <c r="E173" s="4" t="n">
-        <v>46.91</v>
+        <v>52.62</v>
       </c>
       <c r="F173" s="4" t="n">
-        <v>52.74</v>
+        <v/>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>GOKULAGRO</t>
+          <t>MOIL</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -6624,22 +6424,22 @@
         </is>
       </c>
       <c r="C174" s="4" t="n">
-        <v>226.4</v>
+        <v>243.88</v>
       </c>
       <c r="D174" s="4" t="n">
-        <v>40.94</v>
+        <v>39.21</v>
       </c>
       <c r="E174" s="4" t="n">
-        <v>55.18</v>
+        <v>32.93</v>
       </c>
       <c r="F174" s="4" t="n">
-        <v>62.68</v>
+        <v>40.42</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>POWERMECH</t>
+          <t>RAYMONDLSL</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -6648,22 +6448,22 @@
         </is>
       </c>
       <c r="C175" s="4" t="n">
-        <v>2379.4</v>
+        <v>657.25</v>
       </c>
       <c r="D175" s="4" t="n">
-        <v>40.89</v>
+        <v>39.08</v>
       </c>
       <c r="E175" s="4" t="n">
-        <v>47.56</v>
+        <v>33.87</v>
       </c>
       <c r="F175" s="4" t="n">
-        <v>50</v>
+        <v>23.51</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>SHARDACROP</t>
+          <t>ELECTCAST</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -6672,22 +6472,22 @@
         </is>
       </c>
       <c r="C176" s="4" t="n">
-        <v>765.55</v>
+        <v>73.38</v>
       </c>
       <c r="D176" s="4" t="n">
-        <v>40.81</v>
+        <v>38.48</v>
       </c>
       <c r="E176" s="4" t="n">
-        <v>37.93</v>
+        <v>46.42</v>
       </c>
       <c r="F176" s="4" t="n">
-        <v>49.47</v>
+        <v>43.22</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>TIMETECHNO</t>
+          <t>LLOYDSENT</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -6696,22 +6496,22 @@
         </is>
       </c>
       <c r="C177" s="4" t="n">
-        <v>184.87</v>
+        <v>68.84</v>
       </c>
       <c r="D177" s="4" t="n">
-        <v>40.71</v>
+        <v>38.41</v>
       </c>
       <c r="E177" s="4" t="n">
-        <v>45.51</v>
+        <v>47.62</v>
       </c>
       <c r="F177" s="4" t="n">
-        <v>50.65</v>
+        <v>54.38</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>MASTEK</t>
+          <t>ALKYLAMINE</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -6720,22 +6520,22 @@
         </is>
       </c>
       <c r="C178" s="4" t="n">
-        <v>1610</v>
+        <v>1823.1</v>
       </c>
       <c r="D178" s="4" t="n">
-        <v>40.56</v>
+        <v>38.37</v>
       </c>
       <c r="E178" s="4" t="n">
-        <v>44.96</v>
+        <v>54.24</v>
       </c>
       <c r="F178" s="4" t="n">
-        <v>41.54</v>
+        <v>50.59</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>KIRLPNU</t>
+          <t>STYL</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -6744,22 +6544,22 @@
         </is>
       </c>
       <c r="C179" s="4" t="n">
-        <v>719.7</v>
+        <v>360.35</v>
       </c>
       <c r="D179" s="4" t="n">
-        <v>40.31</v>
+        <v>38.33</v>
       </c>
       <c r="E179" s="4" t="n">
-        <v>47.97</v>
+        <v>55.27</v>
       </c>
       <c r="F179" s="4" t="n">
-        <v>55.05</v>
+        <v/>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>ALKYLAMINE</t>
+          <t>APOLLO</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -6768,22 +6568,22 @@
         </is>
       </c>
       <c r="C180" s="4" t="n">
-        <v>1867.5</v>
+        <v>370.7</v>
       </c>
       <c r="D180" s="4" t="n">
-        <v>40.02</v>
+        <v>38.21</v>
       </c>
       <c r="E180" s="4" t="n">
-        <v>54.54</v>
+        <v>51.98</v>
       </c>
       <c r="F180" s="4" t="n">
-        <v>50.7</v>
+        <v>64.81</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>TRIVENI</t>
+          <t>LLOYDSENGG</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -6792,22 +6592,22 @@
         </is>
       </c>
       <c r="C181" s="4" t="n">
-        <v>263.95</v>
+        <v>80.2</v>
       </c>
       <c r="D181" s="4" t="n">
-        <v>39.81</v>
+        <v>37.83</v>
       </c>
       <c r="E181" s="4" t="n">
-        <v>37.49</v>
+        <v>56.7</v>
       </c>
       <c r="F181" s="4" t="n">
-        <v>41.79</v>
+        <v>60.67</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>FINPIPE</t>
+          <t>BAJAJELEC</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -6816,22 +6616,22 @@
         </is>
       </c>
       <c r="C182" s="4" t="n">
-        <v>153.45</v>
+        <v>322.55</v>
       </c>
       <c r="D182" s="4" t="n">
-        <v>39.73</v>
+        <v>37.78</v>
       </c>
       <c r="E182" s="4" t="n">
-        <v>37.44</v>
+        <v>38.86</v>
       </c>
       <c r="F182" s="4" t="n">
-        <v>40.9</v>
+        <v>29.54</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>MEDPLUS</t>
+          <t>BANCOINDIA</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -6840,22 +6640,22 @@
         </is>
       </c>
       <c r="C183" s="4" t="n">
-        <v>658.05</v>
+        <v>593.15</v>
       </c>
       <c r="D183" s="4" t="n">
-        <v>39.63</v>
+        <v>37.59</v>
       </c>
       <c r="E183" s="4" t="n">
-        <v>29.71</v>
+        <v>46.46</v>
       </c>
       <c r="F183" s="4" t="n">
-        <v>39.02</v>
+        <v>55.62</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>JSFB</t>
+          <t>JSLL</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -6864,22 +6664,22 @@
         </is>
       </c>
       <c r="C184" s="4" t="n">
-        <v>514.75</v>
+        <v>490.75</v>
       </c>
       <c r="D184" s="4" t="n">
-        <v>39.41</v>
+        <v>37.58</v>
       </c>
       <c r="E184" s="4" t="n">
-        <v>54.79</v>
+        <v>38.75</v>
       </c>
       <c r="F184" s="4" t="n">
-        <v>54.96</v>
+        <v>40.68</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>INDIGOPNTS</t>
+          <t>PRAJIND</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -6888,22 +6688,22 @@
         </is>
       </c>
       <c r="C185" s="4" t="n">
-        <v>1077.8</v>
+        <v>316.05</v>
       </c>
       <c r="D185" s="4" t="n">
-        <v>39.07</v>
+        <v>37.46</v>
       </c>
       <c r="E185" s="4" t="n">
-        <v>54.54</v>
+        <v>42.75</v>
       </c>
       <c r="F185" s="4" t="n">
-        <v>48.29</v>
+        <v>41.91</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>EQUITASBNK</t>
+          <t>OSWALPUMPS</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -6912,22 +6712,22 @@
         </is>
       </c>
       <c r="C186" s="4" t="n">
-        <v>72.63</v>
+        <v>278.1</v>
       </c>
       <c r="D186" s="4" t="n">
-        <v>39.01</v>
+        <v>37.43</v>
       </c>
       <c r="E186" s="4" t="n">
-        <v>52.46</v>
+        <v>30.74</v>
       </c>
       <c r="F186" s="4" t="n">
-        <v>53.54</v>
+        <v>26.44</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>JYOTHYLAB</t>
+          <t>GAEL</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -6936,22 +6736,22 @@
         </is>
       </c>
       <c r="C187" s="4" t="n">
-        <v>195.65</v>
+        <v>157.16</v>
       </c>
       <c r="D187" s="4" t="n">
-        <v>38.93</v>
+        <v>37.3</v>
       </c>
       <c r="E187" s="4" t="n">
-        <v>37.75</v>
+        <v>50.44</v>
       </c>
       <c r="F187" s="4" t="n">
-        <v>37.04</v>
+        <v>57.61</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>KIRLOSBROS</t>
+          <t>RALLIS</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -6960,22 +6760,22 @@
         </is>
       </c>
       <c r="C188" s="4" t="n">
-        <v>1818.3</v>
+        <v>203.8</v>
       </c>
       <c r="D188" s="4" t="n">
-        <v>38.64</v>
+        <v>37.3</v>
       </c>
       <c r="E188" s="4" t="n">
-        <v>49.39</v>
+        <v>32.14</v>
       </c>
       <c r="F188" s="4" t="n">
-        <v>52.71</v>
+        <v>41.27</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>ETHOSLTD</t>
+          <t>ADVENZYMES</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -6984,22 +6784,22 @@
         </is>
       </c>
       <c r="C189" s="4" t="n">
-        <v>2687.4</v>
+        <v>288.1</v>
       </c>
       <c r="D189" s="4" t="n">
-        <v>38.62</v>
+        <v>36.81</v>
       </c>
       <c r="E189" s="4" t="n">
-        <v>51.77</v>
+        <v>38.77</v>
       </c>
       <c r="F189" s="4" t="n">
-        <v>52.21</v>
+        <v>45.48</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>GHCL</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -7008,22 +6808,22 @@
         </is>
       </c>
       <c r="C190" s="4" t="n">
-        <v>5081.5</v>
+        <v>421.7</v>
       </c>
       <c r="D190" s="4" t="n">
-        <v>38.34</v>
+        <v>36.55</v>
       </c>
       <c r="E190" s="4" t="n">
-        <v>52.5</v>
+        <v>38.22</v>
       </c>
       <c r="F190" s="4" t="n">
-        <v>66.77</v>
+        <v>40.91</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>SUBROS</t>
+          <t>CENTURYPLY</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -7032,22 +6832,22 @@
         </is>
       </c>
       <c r="C191" s="4" t="n">
-        <v>709.6</v>
+        <v>719.9</v>
       </c>
       <c r="D191" s="4" t="n">
-        <v>38.25</v>
+        <v>36.37</v>
       </c>
       <c r="E191" s="4" t="n">
-        <v>41.04</v>
+        <v>41.43</v>
       </c>
       <c r="F191" s="4" t="n">
-        <v>48.61</v>
+        <v>48.33</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>IFBIND</t>
+          <t>SANDUMA</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -7056,22 +6856,22 @@
         </is>
       </c>
       <c r="C192" s="4" t="n">
-        <v>1283.2</v>
+        <v>185.4</v>
       </c>
       <c r="D192" s="4" t="n">
-        <v>38.07</v>
+        <v>36.19</v>
       </c>
       <c r="E192" s="4" t="n">
-        <v>50.44</v>
+        <v>41.03</v>
       </c>
       <c r="F192" s="4" t="n">
-        <v>49.24</v>
+        <v>51.18</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>WEBELSOLAR</t>
+          <t>SHAKTIPUMP</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -7080,22 +6880,22 @@
         </is>
       </c>
       <c r="C193" s="4" t="n">
-        <v>75.84</v>
+        <v>460.95</v>
       </c>
       <c r="D193" s="4" t="n">
-        <v>37.81</v>
+        <v>35.77</v>
       </c>
       <c r="E193" s="4" t="n">
-        <v>36.89</v>
+        <v>34.89</v>
       </c>
       <c r="F193" s="4" t="n">
-        <v>45.51</v>
+        <v>42.34</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>HGINFRA</t>
+          <t>ETHOSLTD</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -7104,22 +6904,22 @@
         </is>
       </c>
       <c r="C194" s="4" t="n">
-        <v>487.25</v>
+        <v>2612.5</v>
       </c>
       <c r="D194" s="4" t="n">
-        <v>37.76</v>
+        <v>35.76</v>
       </c>
       <c r="E194" s="4" t="n">
-        <v>32.43</v>
+        <v>52.82</v>
       </c>
       <c r="F194" s="4" t="n">
-        <v>33.87</v>
+        <v>52.69</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>CAMPUS</t>
+          <t>WEBELSOLAR</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -7128,22 +6928,22 @@
         </is>
       </c>
       <c r="C195" s="4" t="n">
-        <v>214.36</v>
+        <v>72.94</v>
       </c>
       <c r="D195" s="4" t="n">
-        <v>37.63</v>
+        <v>35.7</v>
       </c>
       <c r="E195" s="4" t="n">
-        <v>38.28</v>
+        <v>35.37</v>
       </c>
       <c r="F195" s="4" t="n">
-        <v>40.13</v>
+        <v>44.85</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>KITEX</t>
+          <t>SUNTECK</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -7152,22 +6952,22 @@
         </is>
       </c>
       <c r="C196" s="4" t="n">
-        <v>125.65</v>
+        <v>279.65</v>
       </c>
       <c r="D196" s="4" t="n">
-        <v>37.63</v>
+        <v>35.42</v>
       </c>
       <c r="E196" s="4" t="n">
-        <v>33.06</v>
+        <v>41.61</v>
       </c>
       <c r="F196" s="4" t="n">
-        <v>42.79</v>
+        <v>40.23</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>NFL</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -7176,22 +6976,22 @@
         </is>
       </c>
       <c r="C197" s="4" t="n">
-        <v>68.48999999999999</v>
+        <v>4927</v>
       </c>
       <c r="D197" s="4" t="n">
-        <v>37.56</v>
+        <v>35.21</v>
       </c>
       <c r="E197" s="4" t="n">
-        <v>37.75</v>
+        <v>51.4</v>
       </c>
       <c r="F197" s="4" t="n">
-        <v>42.03</v>
+        <v>65.87</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>MOIL</t>
+          <t>PICCADIL</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -7200,22 +7000,22 @@
         </is>
       </c>
       <c r="C198" s="4" t="n">
-        <v>250.18</v>
+        <v>599.55</v>
       </c>
       <c r="D198" s="4" t="n">
-        <v>37.51</v>
+        <v>35.19</v>
       </c>
       <c r="E198" s="4" t="n">
-        <v>33.23</v>
+        <v>44.59</v>
       </c>
       <c r="F198" s="4" t="n">
-        <v>40.55</v>
+        <v/>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>SURYAROSNI</t>
+          <t>BIRLACORPN</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -7224,22 +7024,22 @@
         </is>
       </c>
       <c r="C199" s="4" t="n">
-        <v>216.05</v>
+        <v>823.6</v>
       </c>
       <c r="D199" s="4" t="n">
-        <v>37.4</v>
+        <v>35.09</v>
       </c>
       <c r="E199" s="4" t="n">
-        <v>39.42</v>
+        <v>35.8</v>
       </c>
       <c r="F199" s="4" t="n">
-        <v>44.77</v>
+        <v>37.02</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>CERA</t>
+          <t>NETWORK18</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -7248,22 +7048,22 @@
         </is>
       </c>
       <c r="C200" s="4" t="n">
-        <v>5614</v>
+        <v>26.12</v>
       </c>
       <c r="D200" s="4" t="n">
-        <v>36.95</v>
+        <v>34.78</v>
       </c>
       <c r="E200" s="4" t="n">
-        <v>46.43</v>
+        <v>33.97</v>
       </c>
       <c r="F200" s="4" t="n">
-        <v>46.75</v>
+        <v>33.69</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>NETWORK18</t>
+          <t>CAMPUS</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -7272,22 +7072,22 @@
         </is>
       </c>
       <c r="C201" s="4" t="n">
-        <v>26.64</v>
+        <v>211.98</v>
       </c>
       <c r="D201" s="4" t="n">
-        <v>36.7</v>
+        <v>34.71</v>
       </c>
       <c r="E201" s="4" t="n">
-        <v>32.44</v>
+        <v>37.26</v>
       </c>
       <c r="F201" s="4" t="n">
-        <v>33.49</v>
+        <v>39.76</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>SUNTECK</t>
+          <t>JLHL</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -7296,22 +7096,22 @@
         </is>
       </c>
       <c r="C202" s="4" t="n">
-        <v>288</v>
+        <v>280.05</v>
       </c>
       <c r="D202" s="4" t="n">
-        <v>36.53</v>
+        <v>34.47</v>
       </c>
       <c r="E202" s="4" t="n">
-        <v>38.46</v>
+        <v>46.9</v>
       </c>
       <c r="F202" s="4" t="n">
-        <v>39.55</v>
+        <v>50.69</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENT</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -7320,22 +7120,22 @@
         </is>
       </c>
       <c r="C203" s="4" t="n">
-        <v>70.01000000000001</v>
+        <v>185.59</v>
       </c>
       <c r="D203" s="4" t="n">
-        <v>36.49</v>
+        <v>34.27</v>
       </c>
       <c r="E203" s="4" t="n">
-        <v>48.7</v>
+        <v>50.36</v>
       </c>
       <c r="F203" s="4" t="n">
-        <v>54.98</v>
+        <v>52.54</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>VAIBHAVGBL</t>
+          <t>HEMIPROP</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -7344,22 +7144,22 @@
         </is>
       </c>
       <c r="C204" s="4" t="n">
-        <v>215.96</v>
+        <v>120.77</v>
       </c>
       <c r="D204" s="4" t="n">
-        <v>36.4</v>
+        <v>34.15</v>
       </c>
       <c r="E204" s="4" t="n">
-        <v>43.08</v>
+        <v>37.03</v>
       </c>
       <c r="F204" s="4" t="n">
-        <v>44.48</v>
+        <v>43.62</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>IXIGO</t>
+          <t>JKLAKSHMI</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -7368,22 +7168,22 @@
         </is>
       </c>
       <c r="C205" s="4" t="n">
-        <v>158.63</v>
+        <v>510.4</v>
       </c>
       <c r="D205" s="4" t="n">
-        <v>36.33</v>
+        <v>34.14</v>
       </c>
       <c r="E205" s="4" t="n">
-        <v>40.41</v>
+        <v>36.25</v>
       </c>
       <c r="F205" s="4" t="n">
-        <v>41.81</v>
+        <v>37.62</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>SAATVIKGL</t>
+          <t>SHARDACROP</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -7392,22 +7192,22 @@
         </is>
       </c>
       <c r="C206" s="4" t="n">
-        <v>402.05</v>
+        <v>741.7</v>
       </c>
       <c r="D206" s="4" t="n">
-        <v>36.21</v>
+        <v>34.14</v>
       </c>
       <c r="E206" s="4" t="n">
-        <v>40.08</v>
+        <v>36.07</v>
       </c>
       <c r="F206" s="4" t="n">
-        <v/>
+        <v>48.65</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>CSBBANK</t>
+          <t>IMFA</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -7416,22 +7216,22 @@
         </is>
       </c>
       <c r="C207" s="4" t="n">
-        <v>307.6</v>
+        <v>1246.1</v>
       </c>
       <c r="D207" s="4" t="n">
-        <v>35.82</v>
+        <v>34.08</v>
       </c>
       <c r="E207" s="4" t="n">
-        <v>37.25</v>
+        <v>43</v>
       </c>
       <c r="F207" s="4" t="n">
-        <v>43.06</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>REFEX</t>
+          <t>KSB</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -7440,22 +7240,22 @@
         </is>
       </c>
       <c r="C208" s="4" t="n">
-        <v>273.55</v>
+        <v>764.85</v>
       </c>
       <c r="D208" s="4" t="n">
-        <v>35.82</v>
+        <v>34.05</v>
       </c>
       <c r="E208" s="4" t="n">
-        <v>43.94</v>
+        <v>46.92</v>
       </c>
       <c r="F208" s="4" t="n">
-        <v>47.61</v>
+        <v>51.99</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>KANSAINER</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -7464,22 +7264,22 @@
         </is>
       </c>
       <c r="C209" s="4" t="n">
-        <v>191.11</v>
+        <v>461.45</v>
       </c>
       <c r="D209" s="4" t="n">
-        <v>35.64</v>
+        <v>34</v>
       </c>
       <c r="E209" s="4" t="n">
-        <v>40.28</v>
+        <v>35.27</v>
       </c>
       <c r="F209" s="4" t="n">
-        <v>38.11</v>
+        <v>38.29</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>REDTAPE</t>
+          <t>ARVINDFASN</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -7488,22 +7288,22 @@
         </is>
       </c>
       <c r="C210" s="4" t="n">
-        <v>115.06</v>
+        <v>416.35</v>
       </c>
       <c r="D210" s="4" t="n">
-        <v>35.41</v>
+        <v>33.58</v>
       </c>
       <c r="E210" s="4" t="n">
-        <v>41.11</v>
+        <v>41.45</v>
       </c>
       <c r="F210" s="4" t="n">
-        <v>33.99</v>
+        <v>46.35</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>GRINDWELL</t>
+          <t>CRAMC</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -7512,22 +7312,22 @@
         </is>
       </c>
       <c r="C211" s="4" t="n">
-        <v>1907.7</v>
+        <v>234.35</v>
       </c>
       <c r="D211" s="4" t="n">
-        <v>35.28</v>
+        <v>33.55</v>
       </c>
       <c r="E211" s="4" t="n">
-        <v>48.91</v>
+        <v>38.13</v>
       </c>
       <c r="F211" s="4" t="n">
-        <v>52.04</v>
+        <v/>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>CELLO</t>
+          <t>GOKEX</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -7536,22 +7336,22 @@
         </is>
       </c>
       <c r="C212" s="4" t="n">
-        <v>332.8</v>
+        <v>727.75</v>
       </c>
       <c r="D212" s="4" t="n">
-        <v>35.09</v>
+        <v>33.3</v>
       </c>
       <c r="E212" s="4" t="n">
-        <v>32</v>
+        <v>44.96</v>
       </c>
       <c r="F212" s="4" t="n">
-        <v>28.13</v>
+        <v>48.58</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>ORIENTCEM</t>
+          <t>GOKULAGRO</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -7560,22 +7360,22 @@
         </is>
       </c>
       <c r="C213" s="4" t="n">
-        <v>125.58</v>
+        <v>218.43</v>
       </c>
       <c r="D213" s="4" t="n">
-        <v>34.95</v>
+        <v>33.3</v>
       </c>
       <c r="E213" s="4" t="n">
-        <v>32.41</v>
+        <v>53.73</v>
       </c>
       <c r="F213" s="4" t="n">
-        <v>34.37</v>
+        <v>62.02</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>GHCL</t>
+          <t>KIRLPNU</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -7584,22 +7384,22 @@
         </is>
       </c>
       <c r="C214" s="4" t="n">
-        <v>424.7</v>
+        <v>695.2</v>
       </c>
       <c r="D214" s="4" t="n">
-        <v>34.89</v>
+        <v>33.28</v>
       </c>
       <c r="E214" s="4" t="n">
-        <v>37.96</v>
+        <v>45.72</v>
       </c>
       <c r="F214" s="4" t="n">
-        <v>40.86</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>OSWALPUMPS</t>
+          <t>AVANTIFEED</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -7608,22 +7408,22 @@
         </is>
       </c>
       <c r="C215" s="4" t="n">
-        <v>282.45</v>
+        <v>770.35</v>
       </c>
       <c r="D215" s="4" t="n">
-        <v>34.85</v>
+        <v>33.14</v>
       </c>
       <c r="E215" s="4" t="n">
-        <v>31.32</v>
+        <v>33.81</v>
       </c>
       <c r="F215" s="4" t="n">
-        <v>26.64</v>
+        <v>48.29</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>AURIONPRO</t>
+          <t>IFBIND</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -7632,22 +7432,22 @@
         </is>
       </c>
       <c r="C216" s="4" t="n">
-        <v>671.15</v>
+        <v>1241.9</v>
       </c>
       <c r="D216" s="4" t="n">
-        <v>34.72</v>
+        <v>33.06</v>
       </c>
       <c r="E216" s="4" t="n">
-        <v>34.09</v>
+        <v>44.36</v>
       </c>
       <c r="F216" s="4" t="n">
-        <v>37.87</v>
+        <v>47.45</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>VAIBHAVGBL</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -7656,22 +7456,22 @@
         </is>
       </c>
       <c r="C217" s="4" t="n">
-        <v>470.45</v>
+        <v>210.66</v>
       </c>
       <c r="D217" s="4" t="n">
-        <v>34.42</v>
+        <v>32.94</v>
       </c>
       <c r="E217" s="4" t="n">
-        <v>35.8</v>
+        <v>42.14</v>
       </c>
       <c r="F217" s="4" t="n">
-        <v>38.55</v>
+        <v>44.13</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>IMFA</t>
+          <t>SURYAROSNI</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -7680,16 +7480,16 @@
         </is>
       </c>
       <c r="C218" s="4" t="n">
-        <v>1279.1</v>
+        <v>210.62</v>
       </c>
       <c r="D218" s="4" t="n">
-        <v>34.36</v>
+        <v>32.77</v>
       </c>
       <c r="E218" s="4" t="n">
-        <v>42.29</v>
+        <v>38.15</v>
       </c>
       <c r="F218" s="4" t="n">
-        <v>56.57</v>
+        <v>44.31</v>
       </c>
     </row>
     <row r="219">
@@ -7704,13 +7504,13 @@
         </is>
       </c>
       <c r="C219" s="4" t="n">
-        <v>461.95</v>
+        <v>448.95</v>
       </c>
       <c r="D219" s="4" t="n">
-        <v>33.97</v>
+        <v>32.51</v>
       </c>
       <c r="E219" s="4" t="n">
-        <v>37.77</v>
+        <v>42.93</v>
       </c>
       <c r="F219" s="4" t="n">
         <v/>
@@ -7719,7 +7519,7 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>BORORENEW</t>
+          <t>ROUTE</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -7728,22 +7528,22 @@
         </is>
       </c>
       <c r="C220" s="4" t="n">
-        <v>502.2</v>
+        <v>464.4</v>
       </c>
       <c r="D220" s="4" t="n">
-        <v>33.68</v>
+        <v>32</v>
       </c>
       <c r="E220" s="4" t="n">
-        <v>42.85</v>
+        <v>34.69</v>
       </c>
       <c r="F220" s="4" t="n">
-        <v>48.43</v>
+        <v>28.99</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>AEQUS</t>
+          <t>FIEMIND</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -7752,22 +7552,22 @@
         </is>
       </c>
       <c r="C221" s="4" t="n">
-        <v>225.97</v>
+        <v>1937.3</v>
       </c>
       <c r="D221" s="4" t="n">
-        <v>33.59</v>
+        <v>31.69</v>
       </c>
       <c r="E221" s="4" t="n">
-        <v>56.19</v>
+        <v>38.29</v>
       </c>
       <c r="F221" s="4" t="n">
-        <v/>
+        <v>53.93</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>FIEMIND</t>
+          <t>GRWRHITECH</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -7776,22 +7576,22 @@
         </is>
       </c>
       <c r="C222" s="4" t="n">
-        <v>1986.8</v>
+        <v>6431</v>
       </c>
       <c r="D222" s="4" t="n">
-        <v>33.26</v>
+        <v>31.67</v>
       </c>
       <c r="E222" s="4" t="n">
-        <v>41.04</v>
+        <v>63.12</v>
       </c>
       <c r="F222" s="4" t="n">
-        <v>56.39</v>
+        <v>66.39</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>ASHAPURMIN</t>
+          <t>ASHOKA</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -7800,22 +7600,22 @@
         </is>
       </c>
       <c r="C223" s="4" t="n">
-        <v>542.9</v>
+        <v>108.8</v>
       </c>
       <c r="D223" s="4" t="n">
-        <v>32.96</v>
+        <v>31.58</v>
       </c>
       <c r="E223" s="4" t="n">
-        <v>38.96</v>
+        <v>36.76</v>
       </c>
       <c r="F223" s="4" t="n">
-        <v>50.81</v>
+        <v>40.83</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>TANLA</t>
+          <t>NFL</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -7824,22 +7624,22 @@
         </is>
       </c>
       <c r="C224" s="4" t="n">
-        <v>502.8</v>
+        <v>66.84</v>
       </c>
       <c r="D224" s="4" t="n">
-        <v>32.66</v>
+        <v>31.53</v>
       </c>
       <c r="E224" s="4" t="n">
-        <v>43.63</v>
+        <v>34.73</v>
       </c>
       <c r="F224" s="4" t="n">
-        <v>43.77</v>
+        <v>41.26</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>SANOFICONR</t>
+          <t>EMBDL</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -7848,22 +7648,22 @@
         </is>
       </c>
       <c r="C225" s="4" t="n">
-        <v>4089.6</v>
+        <v>53.88</v>
       </c>
       <c r="D225" s="4" t="n">
-        <v>32.24</v>
+        <v>31.24</v>
       </c>
       <c r="E225" s="4" t="n">
-        <v>35.11</v>
+        <v>40.45</v>
       </c>
       <c r="F225" s="4" t="n">
-        <v>38.89</v>
+        <v>39.89</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>EUREKAFORB</t>
+          <t>TRIVENI</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -7872,22 +7672,22 @@
         </is>
       </c>
       <c r="C226" s="4" t="n">
-        <v>394.15</v>
+        <v>239.45</v>
       </c>
       <c r="D226" s="4" t="n">
-        <v>31.73</v>
+        <v>30.76</v>
       </c>
       <c r="E226" s="4" t="n">
-        <v>34.63</v>
+        <v>35.67</v>
       </c>
       <c r="F226" s="4" t="n">
-        <v>36.34</v>
+        <v>40.67</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>CRAMC</t>
+          <t>RTNPOWER</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -7896,22 +7696,22 @@
         </is>
       </c>
       <c r="C227" s="4" t="n">
-        <v>238.9</v>
+        <v>7.14</v>
       </c>
       <c r="D227" s="4" t="n">
-        <v>31</v>
+        <v>30.57</v>
       </c>
       <c r="E227" s="4" t="n">
-        <v>40.26</v>
+        <v>29</v>
       </c>
       <c r="F227" s="4" t="n">
-        <v/>
+        <v>40.74</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>CENTURYPLY</t>
+          <t>KSCL</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -7920,22 +7720,22 @@
         </is>
       </c>
       <c r="C228" s="4" t="n">
-        <v>717.05</v>
+        <v>703.35</v>
       </c>
       <c r="D228" s="4" t="n">
-        <v>30.94</v>
+        <v>29.75</v>
       </c>
       <c r="E228" s="4" t="n">
-        <v>39.9</v>
+        <v>32.72</v>
       </c>
       <c r="F228" s="4" t="n">
-        <v>47.9</v>
+        <v>39.95</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>PICCADIL</t>
+          <t>KANSAINER</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -7944,22 +7744,22 @@
         </is>
       </c>
       <c r="C229" s="4" t="n">
-        <v>600.5</v>
+        <v>183.96</v>
       </c>
       <c r="D229" s="4" t="n">
-        <v>30.7</v>
+        <v>29.68</v>
       </c>
       <c r="E229" s="4" t="n">
-        <v>45.93</v>
+        <v>38.06</v>
       </c>
       <c r="F229" s="4" t="n">
-        <v/>
+        <v>37.17</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>JLHL</t>
+          <t>SWSOLAR</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -7968,22 +7768,22 @@
         </is>
       </c>
       <c r="C230" s="4" t="n">
-        <v>281</v>
+        <v>176.06</v>
       </c>
       <c r="D230" s="4" t="n">
-        <v>30.57</v>
+        <v>29.63</v>
       </c>
       <c r="E230" s="4" t="n">
-        <v>46.44</v>
+        <v>37.36</v>
       </c>
       <c r="F230" s="4" t="n">
-        <v>50.5</v>
+        <v>38.92</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>RCF</t>
+          <t>TANLA</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -7992,22 +7792,22 @@
         </is>
       </c>
       <c r="C231" s="4" t="n">
-        <v>112.57</v>
+        <v>489.25</v>
       </c>
       <c r="D231" s="4" t="n">
-        <v>30.43</v>
+        <v>29.62</v>
       </c>
       <c r="E231" s="4" t="n">
-        <v>34.96</v>
+        <v>41.5</v>
       </c>
       <c r="F231" s="4" t="n">
-        <v>41.91</v>
+        <v>43.02</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>DBREALTY</t>
+          <t>RCF</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -8016,22 +7816,22 @@
         </is>
       </c>
       <c r="C232" s="4" t="n">
-        <v>97.79000000000001</v>
+        <v>108.5</v>
       </c>
       <c r="D232" s="4" t="n">
-        <v>29.73</v>
+        <v>29.45</v>
       </c>
       <c r="E232" s="4" t="n">
-        <v>39.26</v>
+        <v>34.23</v>
       </c>
       <c r="F232" s="4" t="n">
-        <v>41.75</v>
+        <v>41.61</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>CMSINFO</t>
+          <t>CELLO</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -8040,22 +7840,22 @@
         </is>
       </c>
       <c r="C233" s="4" t="n">
-        <v>225.19</v>
+        <v>322.45</v>
       </c>
       <c r="D233" s="4" t="n">
-        <v>29.71</v>
+        <v>29.41</v>
       </c>
       <c r="E233" s="4" t="n">
-        <v>27.12</v>
+        <v>30.07</v>
       </c>
       <c r="F233" s="4" t="n">
-        <v>31.22</v>
+        <v>27.55</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>HAPPSTMNDS</t>
+          <t>SUBROS</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -8064,22 +7864,22 @@
         </is>
       </c>
       <c r="C234" s="4" t="n">
-        <v>332.35</v>
+        <v>678</v>
       </c>
       <c r="D234" s="4" t="n">
-        <v>29.65</v>
+        <v>29.23</v>
       </c>
       <c r="E234" s="4" t="n">
-        <v>38.71</v>
+        <v>43.72</v>
       </c>
       <c r="F234" s="4" t="n">
-        <v>29.83</v>
+        <v>49.41</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>RTNINDIA</t>
+          <t>SANOFICONR</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -8088,22 +7888,22 @@
         </is>
       </c>
       <c r="C235" s="4" t="n">
-        <v>27.6</v>
+        <v>3989.5</v>
       </c>
       <c r="D235" s="4" t="n">
-        <v>29.6</v>
+        <v>28.74</v>
       </c>
       <c r="E235" s="4" t="n">
-        <v>33.99</v>
+        <v>35.56</v>
       </c>
       <c r="F235" s="4" t="n">
-        <v>37.79</v>
+        <v>39.03</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>EMBDL</t>
+          <t>TRANSRAILL</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -8112,22 +7912,22 @@
         </is>
       </c>
       <c r="C236" s="4" t="n">
-        <v>55.28</v>
+        <v>408.75</v>
       </c>
       <c r="D236" s="4" t="n">
-        <v>29.17</v>
+        <v>28.64</v>
       </c>
       <c r="E236" s="4" t="n">
-        <v>41.81</v>
+        <v>31.97</v>
       </c>
       <c r="F236" s="4" t="n">
-        <v>40.3</v>
+        <v>39.43</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>BIRLACORPN</t>
+          <t>KITEX</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -8136,22 +7936,22 @@
         </is>
       </c>
       <c r="C237" s="4" t="n">
-        <v>825.15</v>
+        <v>118.58</v>
       </c>
       <c r="D237" s="4" t="n">
-        <v>28.42</v>
+        <v>27.87</v>
       </c>
       <c r="E237" s="4" t="n">
-        <v>35.93</v>
+        <v>31.41</v>
       </c>
       <c r="F237" s="4" t="n">
-        <v>37.08</v>
+        <v>42.09</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>RALLIS</t>
+          <t>EUREKAFORB</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -8160,22 +7960,22 @@
         </is>
       </c>
       <c r="C238" s="4" t="n">
-        <v>201.99</v>
+        <v>385.3</v>
       </c>
       <c r="D238" s="4" t="n">
-        <v>28.3</v>
+        <v>27.84</v>
       </c>
       <c r="E238" s="4" t="n">
-        <v>30.48</v>
+        <v>33.27</v>
       </c>
       <c r="F238" s="4" t="n">
-        <v>41.03</v>
+        <v>35.67</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>KSCL</t>
+          <t>DBREALTY</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -8184,22 +7984,22 @@
         </is>
       </c>
       <c r="C239" s="4" t="n">
-        <v>718.05</v>
+        <v>95.68000000000001</v>
       </c>
       <c r="D239" s="4" t="n">
-        <v>27.55</v>
+        <v>27.68</v>
       </c>
       <c r="E239" s="4" t="n">
-        <v>34.31</v>
+        <v>38.12</v>
       </c>
       <c r="F239" s="4" t="n">
-        <v>40.71</v>
+        <v>41.38</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>JKLAKSHMI</t>
+          <t>BORORENEW</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -8208,22 +8008,22 @@
         </is>
       </c>
       <c r="C240" s="4" t="n">
-        <v>505.9</v>
+        <v>459.5</v>
       </c>
       <c r="D240" s="4" t="n">
-        <v>27.12</v>
+        <v>27.59</v>
       </c>
       <c r="E240" s="4" t="n">
-        <v>29.06</v>
+        <v>38.19</v>
       </c>
       <c r="F240" s="4" t="n">
-        <v>36.37</v>
+        <v>46.01</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>SWSOLAR</t>
+          <t>HAPPSTMNDS</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -8232,22 +8032,22 @@
         </is>
       </c>
       <c r="C241" s="4" t="n">
-        <v>180.22</v>
+        <v>321.55</v>
       </c>
       <c r="D241" s="4" t="n">
-        <v>26.51</v>
+        <v>27.48</v>
       </c>
       <c r="E241" s="4" t="n">
-        <v>38.73</v>
+        <v>37.08</v>
       </c>
       <c r="F241" s="4" t="n">
-        <v>39.26</v>
+        <v>29.19</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>WAAREERTL</t>
+          <t>ASHAPURMIN</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -8256,22 +8056,22 @@
         </is>
       </c>
       <c r="C242" s="4" t="n">
-        <v>833.85</v>
+        <v>515.7</v>
       </c>
       <c r="D242" s="4" t="n">
-        <v>26.4</v>
+        <v>26.89</v>
       </c>
       <c r="E242" s="4" t="n">
-        <v>35.64</v>
+        <v>37.33</v>
       </c>
       <c r="F242" s="4" t="n">
-        <v>39.56</v>
+        <v>50.02</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>TRANSRAILL</t>
+          <t>WAAREERTL</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -8280,22 +8080,22 @@
         </is>
       </c>
       <c r="C243" s="4" t="n">
-        <v>410.35</v>
+        <v>811.05</v>
       </c>
       <c r="D243" s="4" t="n">
-        <v>25.29</v>
+        <v>26.27</v>
       </c>
       <c r="E243" s="4" t="n">
-        <v>32.18</v>
+        <v>34.44</v>
       </c>
       <c r="F243" s="4" t="n">
-        <v>39.53</v>
+        <v>38.94</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>RTNPOWER</t>
+          <t>ANUP</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -8304,22 +8104,22 @@
         </is>
       </c>
       <c r="C244" s="4" t="n">
-        <v>7.17</v>
+        <v>1638.3</v>
       </c>
       <c r="D244" s="4" t="n">
-        <v>24.92</v>
+        <v>25.89</v>
       </c>
       <c r="E244" s="4" t="n">
-        <v>29.23</v>
+        <v>35.77</v>
       </c>
       <c r="F244" s="4" t="n">
-        <v>40.82</v>
+        <v>43.49</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>ANUP</t>
+          <t>RTNINDIA</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
@@ -8328,22 +8128,22 @@
         </is>
       </c>
       <c r="C245" s="4" t="n">
-        <v>1664.3</v>
+        <v>26.37</v>
       </c>
       <c r="D245" s="4" t="n">
-        <v>24.41</v>
+        <v>23.44</v>
       </c>
       <c r="E245" s="4" t="n">
-        <v>36.61</v>
+        <v>31.81</v>
       </c>
       <c r="F245" s="4" t="n">
-        <v>43.83</v>
+        <v>37.18</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>HEMIPROP</t>
+          <t>HGINFRA</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -8352,22 +8152,22 @@
         </is>
       </c>
       <c r="C246" s="4" t="n">
-        <v>120.95</v>
+        <v>442.45</v>
       </c>
       <c r="D246" s="4" t="n">
-        <v>23.91</v>
+        <v>22.38</v>
       </c>
       <c r="E246" s="4" t="n">
-        <v>36.85</v>
+        <v>27.6</v>
       </c>
       <c r="F246" s="4" t="n">
-        <v>43.58</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>RELAXO</t>
+          <t>AHLUCONT</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -8376,16 +8176,16 @@
         </is>
       </c>
       <c r="C247" s="4" t="n">
-        <v>326.9</v>
+        <v>569.3</v>
       </c>
       <c r="D247" s="4" t="n">
-        <v>23.85</v>
+        <v>21.47</v>
       </c>
       <c r="E247" s="4" t="n">
-        <v>41.96</v>
+        <v>26.47</v>
       </c>
       <c r="F247" s="4" t="n">
-        <v>34.81</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="248">
@@ -8400,22 +8200,22 @@
         </is>
       </c>
       <c r="C248" s="4" t="n">
-        <v>287.5</v>
+        <v>276.35</v>
       </c>
       <c r="D248" s="4" t="n">
-        <v>23.78</v>
+        <v>19.74</v>
       </c>
       <c r="E248" s="4" t="n">
-        <v>25.8</v>
+        <v>26.81</v>
       </c>
       <c r="F248" s="4" t="n">
-        <v>40.35</v>
+        <v>40.52</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>PNCINFRA</t>
+          <t>INDIAGLYCO</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
@@ -8424,22 +8224,22 @@
         </is>
       </c>
       <c r="C249" s="4" t="n">
-        <v>175.4</v>
+        <v>263.7</v>
       </c>
       <c r="D249" s="4" t="n">
-        <v>22.63</v>
+        <v>17.58</v>
       </c>
       <c r="E249" s="4" t="n">
-        <v>32.85</v>
+        <v>24.56</v>
       </c>
       <c r="F249" s="4" t="n">
-        <v>37.55</v>
+        <v>35.36</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>AHLUCONT</t>
+          <t>PNCINFRA</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -8448,22 +8248,22 @@
         </is>
       </c>
       <c r="C250" s="4" t="n">
-        <v>592.3</v>
+        <v>139.55</v>
       </c>
       <c r="D250" s="4" t="n">
-        <v>21.66</v>
+        <v>17.05</v>
       </c>
       <c r="E250" s="4" t="n">
-        <v>27.53</v>
+        <v>25.26</v>
       </c>
       <c r="F250" s="4" t="n">
-        <v>40.01</v>
+        <v>34.18</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>INDIAGLYCO</t>
+          <t>RELAXO</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
@@ -8472,16 +8272,16 @@
         </is>
       </c>
       <c r="C251" s="4" t="n">
-        <v>294.9</v>
+        <v>291.25</v>
       </c>
       <c r="D251" s="4" t="n">
-        <v>18.23</v>
+        <v>16.55</v>
       </c>
       <c r="E251" s="4" t="n">
-        <v>25.15</v>
+        <v>37.43</v>
       </c>
       <c r="F251" s="4" t="n">
-        <v>35.94</v>
+        <v>32.93</v>
       </c>
     </row>
     <row r="252">
@@ -8496,16 +8296,16 @@
         </is>
       </c>
       <c r="C252" s="4" t="n">
-        <v>7.36</v>
+        <v>7.05</v>
       </c>
       <c r="D252" s="4" t="n">
-        <v>12.63</v>
+        <v>14.08</v>
       </c>
       <c r="E252" s="4" t="n">
-        <v>20.07</v>
+        <v>19.32</v>
       </c>
       <c r="F252" s="4" t="n">
-        <v>29.69</v>
+        <v>29.28</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Micro250_stocks.xlsx
+++ b/docs/Micro250_stocks.xlsx
@@ -43,7 +43,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -53,11 +53,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -87,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -99,15 +94,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -475,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:L48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -551,7 +537,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SHAREINDIA</t>
+          <t>GMMPFAUDLR</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -560,37 +546,37 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>228.15</v>
+        <v>1505.2</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>84.09999999999999</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>73.70999999999999</v>
+        <v>82.36</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>57.41</v>
+        <v>60.84</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>40.88</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>162.5</v>
+        <v>1007.12</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>162.16</v>
+        <v>1006.14</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>5635199</v>
+        <v>428110</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>4993</v>
+        <v>6767</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>YATHARTH</t>
+          <t>SANSERA</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -599,37 +585,37 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>1139.5</v>
+        <v>4662.4</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>80.27</v>
+        <v>74.58</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>75.62</v>
+        <v>85.7</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>72.27</v>
+        <v>87.63</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>46.4</v>
+        <v>34.71</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>834.37</v>
+        <v>3157.29</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>806.08</v>
+        <v>2924.09</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>769562</v>
+        <v>218163</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>10980</v>
+        <v>29102</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>SHILPAMED</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -638,37 +624,37 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1021.1</v>
+        <v>630.3</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>70.03</v>
+        <v>73.63</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>92.03</v>
+        <v>74.2</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>85.47</v>
+        <v>61.84</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>49.45</v>
+        <v>33.51</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>620.4</v>
+        <v>514.15</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>574.9299999999999</v>
+        <v>506.52</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>1591545</v>
+        <v>1072684</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>19971</v>
+        <v>9262</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>NEOGEN</t>
+          <t>LLOYDSENGG</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -677,37 +663,37 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>2488.4</v>
+        <v>98.56</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>69.81999999999999</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>72.69</v>
+        <v>69.14</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>67.48999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>28.64</v>
+        <v>28.92</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>1900.98</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>1827.16</v>
+        <v>73.67</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>238874</v>
+        <v>7847222</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>7476</v>
+        <v>15272</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>MAHSEAMLES</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -716,37 +702,37 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>720.2</v>
+        <v>939.55</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>67.83</v>
+        <v>70.19</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>71.75</v>
+        <v>69.13</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>59.25</v>
+        <v>63.01</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>53.85</v>
+        <v>26.04</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>610.24</v>
+        <v>758.5</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>606.74</v>
+        <v>752.98</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>387177</v>
+        <v>662759</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>9615</v>
+        <v>8520</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>JKPAPER</t>
+          <t>SOUTHBANK</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -755,37 +741,37 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>430.6</v>
+        <v>49.95</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>65.56999999999999</v>
+        <v>70.05</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>69.91</v>
+        <v>66.84</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>58.82</v>
+        <v>73.27</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>45.23</v>
+        <v>21.92</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>373.04</v>
+        <v>43.3</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>370.27</v>
+        <v>41.94</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>497377</v>
+        <v>10650999</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>7808</v>
+        <v>13084</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>EMIL</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -794,37 +780,37 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>196.28</v>
+        <v>1767</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>65.37</v>
+        <v>69.08</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>73.34</v>
+        <v>73.64</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>63.03</v>
+        <v>81.54000000000001</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>29.42</v>
+        <v>23.68</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>140.99</v>
+        <v>1358.73</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>137.01</v>
+        <v>1284.11</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>8455167</v>
+        <v>249954</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>7552</v>
+        <v>23453</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>SANSERA</t>
+          <t>YATHARTH</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -833,37 +819,37 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>4259.9</v>
+        <v>1121.4</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>65.02</v>
+        <v>68.64</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>82.23999999999999</v>
+        <v>73.23999999999999</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>86.04000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>31.22</v>
+        <v>52.92</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3047.76</v>
+        <v>854.05</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2827.62</v>
+        <v>822.49</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>227912</v>
+        <v>742684</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>26583</v>
+        <v>10805</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>OPTIEMUS</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -872,37 +858,37 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>568.7</v>
+        <v>758.55</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>63.1</v>
+        <v>68.44</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>65.86</v>
+        <v>73.92</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>67.48</v>
+        <v>62.7</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>20.46</v>
+        <v>33.67</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>478.56</v>
+        <v>530.26</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>468</v>
+        <v>524.86</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1013759</v>
+        <v>965965</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>14098</v>
+        <v>6840</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>WELENT</t>
+          <t>PGIL</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -911,37 +897,37 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>768</v>
+        <v>1329.1</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>62.69</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>77.59999999999999</v>
+        <v>72.04000000000001</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>72.66</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>47.38</v>
+        <v>29.15</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>582.97</v>
+        <v>987.4400000000001</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>567.12</v>
+        <v>940.78</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>899284</v>
+        <v>203871</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>11166</v>
+        <v>12278</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>SMLMAH</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -950,37 +936,37 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>584.85</v>
+        <v>6825.5</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>61.81</v>
+        <v>65.77</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>68.97</v>
+        <v>71.31999999999999</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>58.77</v>
+        <v>72.08</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>31.44</v>
+        <v>37.53</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>506.18</v>
+        <v>4699.92</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>500.08</v>
+        <v>4445.58</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>901561</v>
+        <v>103085</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>8653</v>
+        <v>9878</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>SUPRIYA</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -989,37 +975,37 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>818.8</v>
+        <v>985.2</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>61.46</v>
+        <v>65.34</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>72.92</v>
+        <v>64.27</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>87.76000000000001</v>
+        <v>62.91</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>28.96</v>
+        <v>24.9</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>507.7</v>
+        <v>820.14</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>448.35</v>
+        <v>800.3099999999999</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1689806</v>
+        <v>302959</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>42091</v>
+        <v>7929</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>AKUMS</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1028,37 +1014,37 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>656.25</v>
+        <v>819.55</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>61.36</v>
+        <v>65.13</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>74.8</v>
+        <v>77.47</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>70.87</v>
+        <v>67.86</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>39.82</v>
+        <v>41.81</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>520.02</v>
+        <v>641.39</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>506.89</v>
+        <v>616.79</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>382607</v>
+        <v>343458</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>12937</v>
+        <v>12547</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>SMLMAH</t>
+          <t>EMIL</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1067,37 +1053,37 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>6292.5</v>
+        <v>200.22</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>60.41</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>67.79000000000001</v>
+        <v>74.25</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>70.16</v>
+        <v>63.63</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>41.57</v>
+        <v>27.99</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>4563.3</v>
+        <v>144.34</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>4331.34</v>
+        <v>139.74</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>117304</v>
+        <v>2705090</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>9106</v>
+        <v>7703</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>EDELWEISS</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1106,37 +1092,37 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>136.25</v>
+        <v>587.55</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>60.25</v>
+        <v>63.7</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>64.43000000000001</v>
+        <v>67.47</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>64.12</v>
+        <v>68.3</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>24.43</v>
+        <v>23.07</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>118.13</v>
+        <v>484.14</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>116.44</v>
+        <v>472.62</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>7571363</v>
+        <v>788942</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>12896</v>
+        <v>14420</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>DIACABS</t>
+          <t>MAHSEAMLES</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1145,37 +1131,37 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>366.8</v>
+        <v>715.65</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>58.18</v>
+        <v>63.48</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>77.18000000000001</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>81.69</v>
+        <v>59.13</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>29.92</v>
+        <v>44.41</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>247.88</v>
+        <v>617.75</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>228.11</v>
+        <v>612.58</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1112136</v>
+        <v>398172</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>21937</v>
+        <v>9590</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>ENTERO</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1184,37 +1170,37 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1731.8</v>
+        <v>338.15</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>58.07</v>
+        <v>63.19</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>70.59999999999999</v>
+        <v>72.39</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>69.19</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>58.87</v>
+        <v>33.68</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1323.81</v>
+        <v>273.01</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1290.59</v>
+        <v>260.79</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>384343</v>
+        <v>2461869</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>7540</v>
+        <v>12688</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>VARROC</t>
+          <t>SHILPAMED</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1223,37 +1209,37 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>851.15</v>
+        <v>1013.45</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>56.89</v>
+        <v>62.37</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>75.97</v>
+        <v>90.43000000000001</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>70.64</v>
+        <v>85.34</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>42.62</v>
+        <v>39.26</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>672.98</v>
+        <v>651.12</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>650.46</v>
+        <v>600.6799999999999</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>906032</v>
+        <v>1135089</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>13164</v>
+        <v>19821</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>SHAREINDIA</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1262,37 +1248,37 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>218.35</v>
+        <v>209.62</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>56.31</v>
+        <v>61.93</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>66.52</v>
+        <v>64.64</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>66.61</v>
+        <v>54.67</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>39.06</v>
+        <v>46.4</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>189.6</v>
+        <v>166.14</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>184.04</v>
+        <v>165.14</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2647330</v>
+        <v>5901959</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>7035</v>
+        <v>4587</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>AKUMS</t>
+          <t>ENTERO</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1301,37 +1287,37 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>766.7</v>
+        <v>1821.8</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>55.97</v>
+        <v>61.28</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>74.64</v>
+        <v>73.29000000000001</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>65.87</v>
+        <v>73.61</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>37.6</v>
+        <v>40.76</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>627.16</v>
+        <v>1365.72</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>604.77</v>
+        <v>1324.39</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>419165</v>
+        <v>373870</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>11999</v>
+        <v>7929</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>ICIL</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1340,37 +1326,37 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>447.35</v>
+        <v>374.55</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>55.35</v>
+        <v>61</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>64.97</v>
+        <v>74</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>63.32</v>
+        <v>68.36</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>26.85</v>
+        <v>21.88</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>365.91</v>
+        <v>314.36</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>351.49</v>
+        <v>305.95</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1591294</v>
+        <v>1631213</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>8860</v>
+        <v>14482</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1379,37 +1365,37 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>763.75</v>
+        <v>837.2</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>55.17</v>
+        <v>59.92</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>66.88</v>
+        <v>73.72</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>77.77</v>
+        <v>88.06</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>26.74</v>
+        <v>23.74</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>592.08</v>
+        <v>528.89</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>552.33</v>
+        <v>467.26</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>3014416</v>
+        <v>1581493</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>23864</v>
+        <v>43037</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>OPTIEMUS</t>
+          <t>STAR</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1418,37 +1404,37 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>590.1</v>
+        <v>1184.9</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>54.65</v>
+        <v>59.23</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>60.85</v>
+        <v>63.27</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>55.85</v>
+        <v>63.09</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>20.38</v>
+        <v>27.75</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>515.91</v>
+        <v>1041.13</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>512.74</v>
+        <v>1020.69</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>291647</v>
+        <v>495677</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>5321</v>
+        <v>10922</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>QUESS</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1457,37 +1443,37 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>353</v>
+        <v>336.95</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>54.63</v>
+        <v>58.11</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>70.11</v>
+        <v>72.61</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>51.48</v>
+        <v>68.34</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>28.55</v>
+        <v>27.48</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>278.87</v>
+        <v>261.64</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>276.63</v>
+        <v>250.64</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>723252</v>
+        <v>2609409</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>5253</v>
+        <v>15269</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>AZAD</t>
+          <t>NEOGEN</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1496,37 +1482,37 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2790.3</v>
+        <v>2385.2</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>54.43</v>
+        <v>57.62</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>66.5</v>
+        <v>66.91</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>70.89</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>25.85</v>
+        <v>25.37</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2254.09</v>
+        <v>1931.56</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2147.95</v>
+        <v>1855.89</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>561233</v>
+        <v>236962</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>18020</v>
+        <v>7166</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>EDELWEISS</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1535,37 +1521,37 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2216.1</v>
+        <v>136.83</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>53.59</v>
+        <v>57.47</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>85.98999999999999</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>84.45999999999999</v>
+        <v>64.28</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>35.94</v>
+        <v>24.7</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1634.12</v>
+        <v>119.65</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1515.29</v>
+        <v>117.71</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>683654</v>
+        <v>8717093</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>16973</v>
+        <v>12951</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>MSTCLTD</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1574,37 +1560,37 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>362.55</v>
+        <v>740.8</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>53.33</v>
+        <v>57.11</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>72.41</v>
+        <v>67.63</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>67.16</v>
+        <v>61.39</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>28.02</v>
+        <v>25.7</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>310.49</v>
+        <v>596.88</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>302.77</v>
+        <v>576.22</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1667992</v>
+        <v>398566</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>14209</v>
+        <v>5215</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>ALIVUS</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1613,37 +1599,37 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1370.6</v>
+        <v>645.15</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>53.26</v>
+        <v>56.44</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>77.68000000000001</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>74.65000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>37.26</v>
+        <v>40.97</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1153.26</v>
+        <v>529.74</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>1120.19</v>
+        <v>515.08</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>175094</v>
+        <v>311417</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>17566</v>
+        <v>12719</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>SKYGOLD</t>
+          <t>LUMAXTECH</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1652,37 +1638,37 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>792.6</v>
+        <v>2026.8</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>52.51</v>
+        <v>54.18</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>70.95999999999999</v>
+        <v>63.71</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>79.03</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>31.36</v>
+        <v>29.7</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>583.11</v>
+        <v>1707.18</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>540.59</v>
+        <v>1634.57</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1207763</v>
+        <v>144525</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>12137</v>
+        <v>13814</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>WELENT</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1691,37 +1677,37 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>320.15</v>
+        <v>754.5</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>52.36</v>
+        <v>53.8</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>69.53</v>
+        <v>65.95</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>66.59999999999999</v>
+        <v>69.83</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>32.11</v>
+        <v>42.07</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>256.29</v>
+        <v>602.79</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>245.94</v>
+        <v>583.4299999999999</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>4892714</v>
+        <v>945363</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>14508</v>
+        <v>10232</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>SUDARSCHEM</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1730,37 +1716,37 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1205.4</v>
+        <v>2316.1</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>51.93</v>
+        <v>53.55</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>69.15000000000001</v>
+        <v>72.41</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>61.34</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>30.8</v>
+        <v>28.17</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1037.71</v>
+        <v>1694.13</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>1030.9</v>
+        <v>1567.85</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>552474</v>
+        <v>663733</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>10060</v>
+        <v>15574</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>LUMAXTECH</t>
+          <t>TDPOWERSYS</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1769,37 +1755,37 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1941.8</v>
+        <v>751.55</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>51.73</v>
+        <v>52.58</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>68.34</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>72.66</v>
+        <v>76.42</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>28.46</v>
+        <v>20.84</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1672.3</v>
+        <v>602.4299999999999</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>1603.44</v>
+        <v>562.09</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>369866</v>
+        <v>2181779</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>14332</v>
+        <v>23577</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>TMB</t>
+          <t>ICIL</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1808,37 +1794,37 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>895.75</v>
+        <v>445.75</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>50.92</v>
+        <v>52.12</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>67.65000000000001</v>
+        <v>64.55</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>74.3</v>
+        <v>63.13</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>34.58</v>
+        <v>23.34</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>756.96</v>
+        <v>372.29</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>717.9</v>
+        <v>357.05</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>160697</v>
+        <v>1558203</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>14184</v>
+        <v>8828</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>INOXINDIA</t>
+          <t>SUDARSCHEM</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1847,37 +1833,37 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>2098.8</v>
+        <v>1218.9</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>50.81</v>
+        <v>51.82</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>68.04000000000001</v>
+        <v>63.92</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>80.37</v>
+        <v>59.32</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>26.29</v>
+        <v>22.48</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1733.15</v>
+        <v>1053.07</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>1641.55</v>
+        <v>1042.99</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>403839</v>
+        <v>385630</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>19083</v>
+        <v>9704</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>JKPAPER</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1886,37 +1872,37 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>318.2</v>
+        <v>408.45</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>50.63</v>
+        <v>51.1</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>67.08</v>
+        <v>60.09</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>71.25</v>
+        <v>56.37</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>34.29</v>
+        <v>38.33</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>268.59</v>
+        <v>376.29</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>256.73</v>
+        <v>372.92</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>2599083</v>
+        <v>532452</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>11867</v>
+        <v>7406</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>MANORAMA</t>
+          <t>VARROC</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1925,37 +1911,37 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>1916.4</v>
+        <v>834.85</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>50.49</v>
+        <v>50.54</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>69.2</v>
+        <v>70.23</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>71.8</v>
+        <v>68.08</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>46.15</v>
+        <v>30.88</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>1607.39</v>
+        <v>688.74</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>1553.88</v>
+        <v>664</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>779483</v>
+        <v>341771</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>12416</v>
+        <v>12756</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>RBA</t>
+          <t>AZAD</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1964,37 +1950,37 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>95.12</v>
+        <v>2728</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>49.26</v>
+        <v>50.41</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>64.93000000000001</v>
+        <v>63.71</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>57.28</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>39.55</v>
+        <v>22.37</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>79.06</v>
+        <v>2284.88</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>77.31999999999999</v>
+        <v>2176.35</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>7395983</v>
+        <v>462028</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>6773</v>
+        <v>17618</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>MSTCLTD</t>
+          <t>DIACABS</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -2003,37 +1989,37 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>695.45</v>
+        <v>354.5</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>49.22</v>
+        <v>49.84</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>66.25</v>
+        <v>72.61</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>60.31</v>
+        <v>80.98</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>35.95</v>
+        <v>29.83</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>581.4</v>
+        <v>257.2</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>563.23</v>
+        <v>236.33</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>409740</v>
+        <v>932077</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>5097</v>
+        <v>21202</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>PGIL</t>
+          <t>CUPID</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -2042,37 +2028,37 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>1143.1</v>
+        <v>270</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>48.68</v>
+        <v>49.81</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>63.18</v>
+        <v>76.61</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>70.06999999999999</v>
+        <v>88.87</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>31.13</v>
+        <v>24.29</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>964.14</v>
+        <v>192.88</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>920.22</v>
+        <v>171.1</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>319428</v>
+        <v>21185753</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>10588</v>
+        <v>36306</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>ALIVUS</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -2081,37 +2067,37 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>1603.1</v>
+        <v>1365.6</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>47.91</v>
+        <v>49.77</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>68.41</v>
+        <v>67.95</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>75.98</v>
+        <v>70.94</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>32.96</v>
+        <v>25.17</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>1329.52</v>
+        <v>1176.64</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>1257.22</v>
+        <v>1139.31</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>209101</v>
+        <v>160603</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>21635</v>
+        <v>16766</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>PARAS</t>
+          <t>SKYGOLD</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -2120,37 +2106,37 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>1370.9</v>
+        <v>782.7</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>46.79</v>
+        <v>49.2</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>63.48</v>
+        <v>71.62</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>67.38</v>
+        <v>80.15000000000001</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>28.31</v>
+        <v>22.06</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>1106.23</v>
+        <v>599.15</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>1039.21</v>
+        <v>555.1900000000001</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>1413123</v>
+        <v>772881</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>11062</v>
+        <v>12290</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -2159,31 +2145,226 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>1446.2</v>
+        <v>214.09</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>45.99</v>
+        <v>48.97</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>61.16</v>
+        <v>63.16</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>64.69</v>
+        <v>65.14</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>38.78</v>
+        <v>31.39</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>1222.07</v>
+        <v>191.41</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>1157.64</v>
+        <v>185.69</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>270778</v>
+        <v>2647843</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>9467</v>
+        <v>6898</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>TMB</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>881.9</v>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>47.37</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>65.01000000000001</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>72.77</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>24.78</v>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>767.42</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>728.0700000000001</v>
+      </c>
+      <c r="J44" s="4" t="n">
+        <v>162469</v>
+      </c>
+      <c r="K44" s="4" t="n">
+        <v>13965</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>QUESS</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>340.9</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>45.82</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>65.91</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>50.41</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>24.23</v>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>284.67</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>281.01</v>
+      </c>
+      <c r="J45" s="4" t="n">
+        <v>754925</v>
+      </c>
+      <c r="K45" s="4" t="n">
+        <v>5093</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>MANORAMA</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>1872.8</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>45.67</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>62.25</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>69.67</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>30.08</v>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>1635.02</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>1578.56</v>
+      </c>
+      <c r="J46" s="4" t="n">
+        <v>527008</v>
+      </c>
+      <c r="K46" s="4" t="n">
+        <v>11822</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>SHAILY</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>3142.3</v>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>45.15</v>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>60.39</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>70.16</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>20.15</v>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>2842.25</v>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>2716.22</v>
+      </c>
+      <c r="J47" s="4" t="n">
+        <v>143709</v>
+      </c>
+      <c r="K47" s="4" t="n">
+        <v>14453</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>RBA</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>92.51000000000001</v>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>45.13</v>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>61.66</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>55.87</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>28.92</v>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>78.31</v>
+      </c>
+      <c r="J48" s="4" t="n">
+        <v>4471295</v>
+      </c>
+      <c r="K48" s="4" t="n">
+        <v>6587</v>
       </c>
     </row>
   </sheetData>
@@ -2230,6 +2411,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId47"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2296,22 +2482,22 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>1467</v>
+        <v>1505.2</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>88.56999999999999</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>81.47</v>
+        <v>82.36</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>60.04</v>
+        <v>60.84</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>SHAREINDIA</t>
+          <t>GREAVESCOT</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2320,22 +2506,22 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>228.15</v>
+        <v>234.78</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>84.09999999999999</v>
+        <v>77.84</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>73.70999999999999</v>
+        <v>62.63</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>57.41</v>
+        <v>57.45</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>YATHARTH</t>
+          <t>DYNAMATECH</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2344,22 +2530,22 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1139.5</v>
+        <v>13153</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>80.27</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>75.62</v>
+        <v>67.98</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>72.27</v>
+        <v>71.89</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>LOTUSDEV</t>
+          <t>CAPILLARY</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2368,13 +2554,13 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>215.13</v>
+        <v>599.45</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>72.14</v>
+        <v>75.54000000000001</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>68.95</v>
+        <v>61.09</v>
       </c>
       <c r="F5" s="4" t="n">
         <v/>
@@ -2383,7 +2569,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SHILPAMED</t>
+          <t>SANSERA</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2392,22 +2578,22 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1021.1</v>
+        <v>4662.4</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>70.03</v>
+        <v>74.58</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>92.03</v>
+        <v>85.7</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>85.47</v>
+        <v>87.63</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>NEOGEN</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2416,22 +2602,22 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2488.4</v>
+        <v>630.3</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>69.81999999999999</v>
+        <v>73.63</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>72.69</v>
+        <v>74.2</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>67.48999999999999</v>
+        <v>61.84</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>STAR</t>
+          <t>LLOYDSENGG</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2440,22 +2626,22 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1200.2</v>
+        <v>98.56</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>69.13</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>67.61</v>
+        <v>69.14</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>64.25</v>
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MAHSEAMLES</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2464,22 +2650,22 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>720.2</v>
+        <v>939.55</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>67.83</v>
+        <v>70.19</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>71.75</v>
+        <v>69.13</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>59.25</v>
+        <v>63.01</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>JKPAPER</t>
+          <t>SOUTHBANK</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2488,22 +2674,22 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>430.6</v>
+        <v>49.95</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>65.56999999999999</v>
+        <v>70.05</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>69.91</v>
+        <v>66.84</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>58.82</v>
+        <v>73.27</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>EMIL</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2512,22 +2698,22 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>196.28</v>
+        <v>1767</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>65.37</v>
+        <v>69.08</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>73.34</v>
+        <v>73.64</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>63.03</v>
+        <v>81.54000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SANSERA</t>
+          <t>YATHARTH</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2536,22 +2722,22 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>4259.9</v>
+        <v>1121.4</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>65.02</v>
+        <v>68.64</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>82.23999999999999</v>
+        <v>73.23999999999999</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>86.04000000000001</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>QPOWER</t>
+          <t>OPTIEMUS</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -2560,22 +2746,22 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1536.1</v>
+        <v>758.55</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>64.06</v>
+        <v>68.44</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>67.06</v>
+        <v>73.92</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>70.23999999999999</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>ELLEN</t>
+          <t>LLOYDSENT</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -2584,22 +2770,22 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>371</v>
+        <v>79.67</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>63.92</v>
+        <v>67.89</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>65.51000000000001</v>
+        <v>58.84</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>44.53</v>
+        <v>60.15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>BLACKBUCK</t>
+          <t>LOTUSDEV</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -2608,22 +2794,22 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>632.4</v>
+        <v>217.99</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>63.26</v>
+        <v>67.87</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>57.52</v>
+        <v>69.75</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>61.74</v>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>TEXRAIL</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -2632,22 +2818,22 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>568.7</v>
+        <v>125.67</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>63.1</v>
+        <v>67.23</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>65.86</v>
+        <v>62.36</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>67.48</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>WELENT</t>
+          <t>JAMNAAUTO</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -2656,22 +2842,22 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>768</v>
+        <v>138.2</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>62.69</v>
+        <v>66.8</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>77.59999999999999</v>
+        <v>56.71</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>72.66</v>
+        <v>59.68</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>HERITGFOOD</t>
+          <t>KSCL</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -2680,22 +2866,22 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>408.65</v>
+        <v>804.55</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>62.65</v>
+        <v>66.55</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>68.31</v>
+        <v>47.29</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>54.46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>PGIL</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2704,22 +2890,22 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>584.85</v>
+        <v>1329.1</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>61.81</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>68.97</v>
+        <v>72.04000000000001</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>58.77</v>
+        <v>78.18000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>GMRP&amp;UI</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -2728,22 +2914,22 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>818.8</v>
+        <v>102.68</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>61.46</v>
+        <v>66.39</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>72.92</v>
+        <v>52.29</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>87.76000000000001</v>
+        <v>51.75</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>APLLTD</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -2752,22 +2938,22 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>656.25</v>
+        <v>863.75</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>61.36</v>
+        <v>66.38</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>74.8</v>
+        <v>64.09</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>70.87</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>APLLTD</t>
+          <t>PCJEWELLER</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -2776,22 +2962,22 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>845.75</v>
+        <v>14.11</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>61.35</v>
+        <v>66.34</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>61.25</v>
+        <v>69.81999999999999</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>50.89</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>DYNAMATECH</t>
+          <t>SMLMAH</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -2800,22 +2986,22 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>12061</v>
+        <v>6825.5</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>61</v>
+        <v>65.77</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>61.64</v>
+        <v>71.31999999999999</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>68.72</v>
+        <v>72.08</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>AVL</t>
+          <t>TSFINV</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -2824,22 +3010,22 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>633.25</v>
+        <v>456.85</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>60.93</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>61.56</v>
+        <v>57.23</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>64.20999999999999</v>
+        <v>56.58</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>SMLMAH</t>
+          <t>SUPRIYA</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -2848,22 +3034,22 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>6292.5</v>
+        <v>985.2</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>60.41</v>
+        <v>65.34</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>67.79000000000001</v>
+        <v>64.27</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>70.16</v>
+        <v>62.91</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>EDELWEISS</t>
+          <t>AKUMS</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -2872,22 +3058,22 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>136.25</v>
+        <v>819.55</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>60.25</v>
+        <v>65.13</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>64.43000000000001</v>
+        <v>77.47</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>64.12</v>
+        <v>67.86</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>TSFINV</t>
+          <t>SURYAROSNI</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -2896,22 +3082,22 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>438.5</v>
+        <v>227.45</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>60.01</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>57</v>
+        <v>46.71</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>56.5</v>
+        <v>46.68</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>IONEXCHANG</t>
+          <t>EMIL</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -2920,22 +3106,22 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>426.25</v>
+        <v>200.22</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>59.16</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>59.5</v>
+        <v>74.25</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>51.34</v>
+        <v>63.63</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>PCJEWELLER</t>
+          <t>SHRIPISTON</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -2944,22 +3130,22 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>12.72</v>
+        <v>4746.8</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>59.15</v>
+        <v>64.73</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>64.66</v>
+        <v>72.59</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>57.45</v>
+        <v>80.38</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>AXISCADES</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -2968,22 +3154,22 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1811.2</v>
+        <v>587.55</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>59.14</v>
+        <v>63.7</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>56.9</v>
+        <v>67.47</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>63.64</v>
+        <v>68.3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>PRUDENT</t>
+          <t>MAHSEAMLES</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -2992,22 +3178,22 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>3501.6</v>
+        <v>715.65</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>58.72</v>
+        <v>63.48</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>69.26000000000001</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>65.31999999999999</v>
+        <v>59.13</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>DIACABS</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -3016,22 +3202,22 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>366.8</v>
+        <v>338.15</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>58.18</v>
+        <v>63.19</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>77.18000000000001</v>
+        <v>72.39</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>81.69</v>
+        <v>77.23999999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>ENTERO</t>
+          <t>SHILPAMED</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -3040,22 +3226,22 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1731.8</v>
+        <v>1013.45</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>58.07</v>
+        <v>62.37</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>70.59999999999999</v>
+        <v>90.43000000000001</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>69.19</v>
+        <v>85.34</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>TVSSCS</t>
+          <t>SHAREINDIA</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -3064,22 +3250,22 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>133.85</v>
+        <v>209.62</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>56.97</v>
+        <v>61.93</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>55.56</v>
+        <v>64.64</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>48.64</v>
+        <v>54.67</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>SHRIPISTON</t>
+          <t>ENTERO</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -3088,22 +3274,22 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>4576.6</v>
+        <v>1821.8</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>56.92</v>
+        <v>61.28</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>69.67</v>
+        <v>73.29000000000001</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>78.66</v>
+        <v>73.61</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>VARROC</t>
+          <t>KPIGREEN</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -3112,22 +3298,22 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>851.15</v>
+        <v>339.75</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>56.89</v>
+        <v>61.01</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>75.97</v>
+        <v>43.61</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>70.64</v>
+        <v>44.92</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>AARTIDRUGS</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -3136,22 +3322,22 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>431.8</v>
+        <v>374.55</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>56.83</v>
+        <v>61</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>61.77</v>
+        <v>74</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>51.2</v>
+        <v>68.36</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>CSBBANK</t>
+          <t>AXISCADES</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -3160,22 +3346,22 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>336.15</v>
+        <v>1892.1</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>56.65</v>
+        <v>60.66</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>46.3</v>
+        <v>60</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>46.96</v>
+        <v>65</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GODREJAGRO</t>
+          <t>TRANSRAILL</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -3184,22 +3370,22 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>647.35</v>
+        <v>469.25</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>56.53</v>
+        <v>60.3</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>65.23999999999999</v>
+        <v>46.57</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>54.15</v>
+        <v>44.11</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>PRSMJOHNSN</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -3208,22 +3394,22 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>218.35</v>
+        <v>116.31</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>56.31</v>
+        <v>60.14</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>66.52</v>
+        <v>48.37</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>66.61</v>
+        <v>42.58</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>PRSMJOHNSN</t>
+          <t>IIFLCAPS</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -3232,22 +3418,22 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>113.44</v>
+        <v>346.7</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>55.98</v>
+        <v>59.99</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>49.31</v>
+        <v>58.38</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>42.91</v>
+        <v>59.06</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>AKUMS</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -3256,22 +3442,22 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>766.7</v>
+        <v>837.2</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>55.97</v>
+        <v>59.92</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>74.64</v>
+        <v>73.72</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>65.87</v>
+        <v>88.06</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>SKFINDUS</t>
+          <t>STAR</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -3280,22 +3466,22 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>2940.3</v>
+        <v>1184.9</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>55.54</v>
+        <v>59.23</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>64.7</v>
+        <v>63.27</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v/>
+        <v>63.09</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>RATNAMANI</t>
+          <t>AEQUS</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -3304,22 +3490,22 @@
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>2695</v>
+        <v>246.05</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>55.38</v>
+        <v>59.17</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>61.28</v>
+        <v>62.56</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>55.59</v>
+        <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>ICIL</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -3328,22 +3514,22 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>447.35</v>
+        <v>209.05</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>55.35</v>
+        <v>58.94</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>64.97</v>
+        <v>55.37</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>63.32</v>
+        <v>55.24</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>QPOWER</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -3352,22 +3538,22 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>763.75</v>
+        <v>1517.8</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>55.17</v>
+        <v>58.74</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>66.88</v>
+        <v>65.92</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>77.77</v>
+        <v>69.95</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>TEXRAIL</t>
+          <t>DATAMATICS</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -3376,22 +3562,22 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>114.66</v>
+        <v>807.6</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>54.94</v>
+        <v>58.61</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>53.66</v>
+        <v>52.24</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>45.92</v>
+        <v>55.47</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>ELLEN</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -3400,22 +3586,22 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>2169.6</v>
+        <v>368.5</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>54.91</v>
+        <v>58.39</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>71.8</v>
+        <v>64.12</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v/>
+        <v>43.8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>SUPRIYA</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -3424,22 +3610,22 @@
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>877.85</v>
+        <v>336.95</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>54.84</v>
+        <v>58.11</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>58.6</v>
+        <v>72.61</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>60.21</v>
+        <v>68.34</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>WABAG</t>
+          <t>NEOGEN</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -3448,22 +3634,22 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>2132.6</v>
+        <v>2385.2</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>54.78</v>
+        <v>57.62</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>62.1</v>
+        <v>66.91</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>69.73</v>
+        <v>66.06999999999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>OPTIEMUS</t>
+          <t>GPPL</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -3472,22 +3658,22 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>590.1</v>
+        <v>163.2</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>54.65</v>
+        <v>57.51</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>60.85</v>
+        <v>60.16</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>55.85</v>
+        <v>54.8</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>QUESS</t>
+          <t>EDELWEISS</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -3496,22 +3682,22 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>353</v>
+        <v>136.83</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>54.63</v>
+        <v>57.47</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>70.11</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>51.48</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>AZAD</t>
+          <t>MSTCLTD</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -3520,22 +3706,22 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>2790.3</v>
+        <v>740.8</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>54.43</v>
+        <v>57.11</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>66.5</v>
+        <v>67.63</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>70.89</v>
+        <v>61.39</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>METROPOLIS</t>
+          <t>GSFC</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -3544,22 +3730,22 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>586.3</v>
+        <v>156.8</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>54.16</v>
+        <v>57.08</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>63.61</v>
+        <v>48.11</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>64.27</v>
+        <v>45.33</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>LXCHEM</t>
+          <t>TIPSMUSIC</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -3568,22 +3754,22 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>178.24</v>
+        <v>668.95</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>53.83</v>
+        <v>56.67</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>60.55</v>
+        <v>55.42</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>47.29</v>
+        <v>59.08</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>SKIPPER</t>
+          <t>RATNAMANI</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -3592,22 +3778,22 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>566.2</v>
+        <v>2778.3</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>53.75</v>
+        <v>56.46</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>60.29</v>
+        <v>58.03</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>62.85</v>
+        <v>54.12</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>PRICOLLTD</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -3616,22 +3802,22 @@
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>767.5</v>
+        <v>645.15</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>53.75</v>
+        <v>56.44</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>68.68000000000001</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>67.31999999999999</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>CCAVENUE</t>
+          <t>RAIN</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -3640,22 +3826,22 @@
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>16.08</v>
+        <v>219.35</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>53.66</v>
+        <v>56.26</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>51.65</v>
+        <v>64.5</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>45.05</v>
+        <v>60.88</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>TARC</t>
+          <t>HERITGFOOD</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -3664,22 +3850,22 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>128.81</v>
+        <v>407.4</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>53.61</v>
+        <v>56.25</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>51.38</v>
+        <v>63.71</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>47.91</v>
+        <v>53.39</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>TARC</t>
+          <t>WESTLIFE</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -3688,22 +3874,22 @@
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>128.81</v>
+        <v>578.1</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>53.61</v>
+        <v>55.84</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>51.38</v>
+        <v>59.15</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>47.91</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>CRIZAC</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -3712,22 +3898,22 @@
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>2216.1</v>
+        <v>182.79</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>53.59</v>
+        <v>55.82</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>85.98999999999999</v>
+        <v>43.74</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>84.45999999999999</v>
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>NESCO</t>
+          <t>PARKHOSPS</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -3736,22 +3922,22 @@
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>1075.6</v>
+        <v>286.35</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>53.51</v>
+        <v>55.79</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>50.69</v>
+        <v>62.61</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>52.96</v>
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>RUBICON</t>
+          <t>GODREJAGRO</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -3760,22 +3946,22 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>1778.3</v>
+        <v>657.8</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>53.46</v>
+        <v>55.71</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>75.69</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v/>
+        <v>53.87</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>PRIVISCL</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -3784,22 +3970,22 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>362.55</v>
+        <v>3537.9</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>53.33</v>
+        <v>54.77</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>72.41</v>
+        <v>58.53</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>67.16</v>
+        <v>68.52</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>ALIVUS</t>
+          <t>CSBBANK</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -3808,22 +3994,22 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>1370.6</v>
+        <v>333.7</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>53.26</v>
+        <v>54.63</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>77.68000000000001</v>
+        <v>45.73</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>74.65000000000001</v>
+        <v>46.62</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>GPPL</t>
+          <t>INOXINDIA</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -3832,22 +4018,22 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>160.35</v>
+        <v>2156.8</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>53.17</v>
+        <v>54.19</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>57.25</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>53.72</v>
+        <v>82.98999999999999</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>MTARTECH</t>
+          <t>LUMAXTECH</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -3856,22 +4042,22 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>7202</v>
+        <v>2026.8</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>53.15</v>
+        <v>54.18</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>60.7</v>
+        <v>63.71</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>70.86</v>
+        <v>70.51000000000001</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>WAKEFIT</t>
+          <t>BBOX</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -3880,22 +4066,22 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>146.85</v>
+        <v>799.75</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>53.08</v>
+        <v>54.13</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>52.15</v>
+        <v>53.27</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v/>
+        <v>60.93</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>RELIGARE</t>
+          <t>LXCHEM</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -3904,22 +4090,22 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>249.89</v>
+        <v>180.61</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>52.55</v>
+        <v>54.06</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>54.61</v>
+        <v>62.35</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>53.96</v>
+        <v>48.04</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>SKYGOLD</t>
+          <t>WELENT</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -3928,22 +4114,22 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>792.6</v>
+        <v>754.5</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>52.51</v>
+        <v>53.8</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>70.95999999999999</v>
+        <v>65.95</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>79.03</v>
+        <v>69.83</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>STYL</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -3952,22 +4138,22 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>320.15</v>
+        <v>381.85</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>52.36</v>
+        <v>53.64</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>69.53</v>
+        <v>59.24</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>66.59999999999999</v>
+        <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>SUDARSCHEM</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -3976,22 +4162,22 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>1205.4</v>
+        <v>2316.1</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>51.93</v>
+        <v>53.55</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>69.15000000000001</v>
+        <v>72.41</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>61.34</v>
+        <v>81.26000000000001</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>LUMAXTECH</t>
+          <t>KSB</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -4000,22 +4186,22 @@
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>1941.8</v>
+        <v>819.1</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>51.73</v>
+        <v>52.95</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>68.34</v>
+        <v>47.95</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>72.66</v>
+        <v>52.32</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>SAMHI</t>
+          <t>TARC</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -4024,22 +4210,22 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>160.27</v>
+        <v>129.36</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>51.59</v>
+        <v>52.63</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>47.59</v>
+        <v>48.59</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>46.51</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>EQUITASBNK</t>
+          <t>TARC</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -4048,22 +4234,22 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>74.09</v>
+        <v>129.36</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>51.07</v>
+        <v>52.63</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>53.98</v>
+        <v>48.59</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>54.23</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>KNRCON</t>
+          <t>TDPOWERSYS</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -4072,22 +4258,22 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>124.8</v>
+        <v>751.55</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>50.92</v>
+        <v>52.58</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>45.03</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>35.07</v>
+        <v>76.42</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>TMB</t>
+          <t>SAATVIKGL</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -4096,22 +4282,22 @@
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>895.75</v>
+        <v>427.45</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>50.92</v>
+        <v>52.57</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>67.65000000000001</v>
+        <v>49.16</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>74.3</v>
+        <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>INOXINDIA</t>
+          <t>SKFINDUS</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -4120,22 +4306,22 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>2098.8</v>
+        <v>2918</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>50.81</v>
+        <v>52.47</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>68.04000000000001</v>
+        <v>61.26</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>80.37</v>
+        <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>PRICOLLTD</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -4144,22 +4330,22 @@
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>156.23</v>
+        <v>763.8</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>50.78</v>
+        <v>52.44</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>48.93</v>
+        <v>66.72</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>53.91</v>
+        <v>66.53</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>IONEXCHANG</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -4168,22 +4354,22 @@
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>820.4</v>
+        <v>420.15</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>50.75</v>
+        <v>52.4</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>59.59</v>
+        <v>54.42</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>57.47</v>
+        <v>49.39</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>PARKHOSPS</t>
+          <t>ICIL</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -4192,22 +4378,22 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>282.05</v>
+        <v>445.75</v>
       </c>
       <c r="D81" s="4" t="n">
-        <v>50.73</v>
+        <v>52.12</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>61.05</v>
+        <v>64.55</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v/>
+        <v>63.13</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>INDIGOPNTS</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -4216,22 +4402,22 @@
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>318.2</v>
+        <v>1128.6</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>50.63</v>
+        <v>51.92</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>67.08</v>
+        <v>58.45</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>71.25</v>
+        <v>49.68</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>BLUESTONE</t>
+          <t>SUDARSCHEM</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -4240,22 +4426,22 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>831.2</v>
+        <v>1218.9</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>50.51</v>
+        <v>51.82</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>66.08</v>
+        <v>63.92</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v/>
+        <v>59.32</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>MANORAMA</t>
+          <t>REFEX</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -4264,22 +4450,22 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>1916.4</v>
+        <v>285.8</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>50.49</v>
+        <v>51.72</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>69.2</v>
+        <v>48.42</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>71.8</v>
+        <v>48.81</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>WEWORK</t>
+          <t>RAYMONDLSL</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -4288,22 +4474,22 @@
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>682.85</v>
+        <v>687.6</v>
       </c>
       <c r="D85" s="4" t="n">
-        <v>50.39</v>
+        <v>51.62</v>
       </c>
       <c r="E85" s="4" t="n">
-        <v>55.63</v>
+        <v>40.16</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v/>
+        <v>25.59</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>BBOX</t>
+          <t>AVL</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -4312,22 +4498,22 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>766.4</v>
+        <v>619.5</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>50.15</v>
+        <v>51.57</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>53.41</v>
+        <v>57.44</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>60.98</v>
+        <v>62.64</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>SKFINDIA</t>
+          <t>GRINDWELL</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -4336,22 +4522,22 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>1546.3</v>
+        <v>1972.7</v>
       </c>
       <c r="D87" s="4" t="n">
-        <v>50.13</v>
+        <v>51.48</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>40.09</v>
+        <v>53.66</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>32.69</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>PRIVISCL</t>
+          <t>DBL</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -4360,22 +4546,22 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>3480.7</v>
+        <v>412.45</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>50.07</v>
+        <v>51.17</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>53.52</v>
+        <v>46.03</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>66.37</v>
+        <v>47.02</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>MANYAVAR</t>
+          <t>AARTIDRUGS</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -4384,22 +4570,22 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>544.25</v>
+        <v>427.4</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>49.51</v>
+        <v>51.14</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>60.78</v>
+        <v>59.57</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>40.13</v>
+        <v>50.68</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>CRIZAC</t>
+          <t>JKPAPER</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -4408,22 +4594,22 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>176.56</v>
+        <v>408.45</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>49.48</v>
+        <v>51.1</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>39.72</v>
+        <v>60.09</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v/>
+        <v>56.37</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>TIPSMUSIC</t>
+          <t>SUDEEPPHRM</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -4432,22 +4618,22 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>654.55</v>
+        <v>1164.9</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>49.4</v>
+        <v>51.03</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>53.54</v>
+        <v>67</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>58.25</v>
+        <v/>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>VGUARD</t>
+          <t>SMARTWORKS</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -4456,22 +4642,22 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>327.15</v>
+        <v>529.9</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>49.31</v>
+        <v>50.88</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>52.94</v>
+        <v>60.6</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>47.72</v>
+        <v/>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>RBA</t>
+          <t>JSFB</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -4480,22 +4666,22 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>95.12</v>
+        <v>535.25</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>49.26</v>
+        <v>50.88</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>64.93000000000001</v>
+        <v>57.82</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>57.28</v>
+        <v>57</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>MSTCLTD</t>
+          <t>REDTAPE</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -4504,22 +4690,22 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>695.45</v>
+        <v>121.05</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>49.22</v>
+        <v>50.85</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>66.25</v>
+        <v>45.45</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>60.31</v>
+        <v>34.42</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>SAFARI</t>
+          <t>CCAVENUE</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -4528,22 +4714,22 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>1520.5</v>
+        <v>15.89</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>49.22</v>
+        <v>50.8</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>42.26</v>
+        <v>50.57</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>40.84</v>
+        <v>44.57</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>SMARTWORKS</t>
+          <t>TVSSCS</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -4552,22 +4738,22 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>519.9</v>
+        <v>130.26</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>48.72</v>
+        <v>50.68</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>65.88</v>
+        <v>52.7</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v/>
+        <v>47.32</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>RAIN</t>
+          <t>VARROC</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -4576,22 +4762,22 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>206.92</v>
+        <v>834.85</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>48.69</v>
+        <v>50.54</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>60.14</v>
+        <v>70.23</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>59.11</v>
+        <v>68.08</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>PGIL</t>
+          <t>METROPOLIS</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -4600,22 +4786,22 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>1143.1</v>
+        <v>582.6</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>48.68</v>
+        <v>50.52</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>63.18</v>
+        <v>59.21</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>70.06999999999999</v>
+        <v>62.81</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>PURVA</t>
+          <t>APOLLO</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -4624,22 +4810,22 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>213.43</v>
+        <v>395.6</v>
       </c>
       <c r="D99" s="4" t="n">
-        <v>48.59</v>
+        <v>50.46</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>47.5</v>
+        <v>55.94</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>45.01</v>
+        <v>67.89</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>ORKLAINDIA</t>
+          <t>AZAD</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -4648,22 +4834,22 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>578.25</v>
+        <v>2728</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>48.45</v>
+        <v>50.41</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>49.51</v>
+        <v>63.71</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v/>
+        <v>69.18000000000001</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>DBL</t>
+          <t>SUBROS</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -4672,22 +4858,22 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>406.2</v>
+        <v>720.9</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>48.25</v>
+        <v>49.93</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>48.93</v>
+        <v>43.82</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>48.52</v>
+        <v>49.44</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>VMART</t>
+          <t>DIACABS</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -4696,22 +4882,22 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>808.15</v>
+        <v>354.5</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>48.24</v>
+        <v>49.84</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>60.27</v>
+        <v>72.61</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>54.56</v>
+        <v>80.98</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>JUSTDIAL</t>
+          <t>CUPID</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -4720,22 +4906,22 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>673.7</v>
+        <v>270</v>
       </c>
       <c r="D103" s="4" t="n">
-        <v>47.98</v>
+        <v>49.81</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>54.65</v>
+        <v>76.61</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>45.63</v>
+        <v>88.87</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>ALIVUS</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -4744,22 +4930,22 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>1603.1</v>
+        <v>1365.6</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>47.91</v>
+        <v>49.77</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>68.41</v>
+        <v>67.95</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>75.98</v>
+        <v>70.94</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>WESTLIFE</t>
+          <t>SKFINDIA</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -4768,22 +4954,22 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>549.05</v>
+        <v>1539.8</v>
       </c>
       <c r="D105" s="4" t="n">
-        <v>47.83</v>
+        <v>49.76</v>
       </c>
       <c r="E105" s="4" t="n">
-        <v>57.21</v>
+        <v>39.19</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>44.97</v>
+        <v>32.58</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>AWFIS</t>
+          <t>HCG</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -4792,22 +4978,22 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>264.7</v>
+        <v>698.65</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>47.76</v>
+        <v>49.69</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>40.88</v>
+        <v>60.05</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>31.94</v>
+        <v>62.36</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>VOLTAMP</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -4816,22 +5002,22 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>199.64</v>
+        <v>10709</v>
       </c>
       <c r="D107" s="4" t="n">
-        <v>47.38</v>
+        <v>49.61</v>
       </c>
       <c r="E107" s="4" t="n">
-        <v>48.63</v>
+        <v>58.38</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>43.32</v>
+        <v>57.89</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>IXIGO</t>
+          <t>CELLO</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -4840,22 +5026,22 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>165.65</v>
+        <v>338.5</v>
       </c>
       <c r="D108" s="4" t="n">
-        <v>47.34</v>
+        <v>49.52</v>
       </c>
       <c r="E108" s="4" t="n">
-        <v>43.44</v>
+        <v>36.47</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>43.57</v>
+        <v>28.46</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>PNGJL</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -4864,22 +5050,22 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>604.75</v>
+        <v>549.05</v>
       </c>
       <c r="D109" s="4" t="n">
-        <v>47.25</v>
+        <v>49.44</v>
       </c>
       <c r="E109" s="4" t="n">
-        <v>50.59</v>
+        <v>61.8</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>49.44</v>
+        <v>68.26000000000001</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>VOLTAMP</t>
+          <t>SAMHI</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -4888,22 +5074,22 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>10513</v>
+        <v>158.94</v>
       </c>
       <c r="D110" s="4" t="n">
-        <v>47.22</v>
+        <v>49.42</v>
       </c>
       <c r="E110" s="4" t="n">
-        <v>60.49</v>
+        <v>45.84</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>58.67</v>
+        <v>45.73</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>SENCO</t>
+          <t>NESCO</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -4912,22 +5098,22 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>348</v>
+        <v>1070.3</v>
       </c>
       <c r="D111" s="4" t="n">
-        <v>46.81</v>
+        <v>49.39</v>
       </c>
       <c r="E111" s="4" t="n">
-        <v>50.5</v>
+        <v>45.82</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>49.73</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>PARAS</t>
+          <t>INOXGREEN</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -4936,22 +5122,22 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>1370.9</v>
+        <v>174.64</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>46.79</v>
+        <v>49.36</v>
       </c>
       <c r="E112" s="4" t="n">
-        <v>63.48</v>
+        <v>46.14</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>67.38</v>
+        <v>51.46</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>FINPIPE</t>
+          <t>GAEL</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -4960,22 +5146,22 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>154.63</v>
+        <v>163.87</v>
       </c>
       <c r="D113" s="4" t="n">
-        <v>46.47</v>
+        <v>49.25</v>
       </c>
       <c r="E113" s="4" t="n">
-        <v>38.91</v>
+        <v>54.67</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>41.16</v>
+        <v>61.04</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>INOXGREEN</t>
+          <t>SKYGOLD</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -4984,22 +5170,22 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>173.11</v>
+        <v>782.7</v>
       </c>
       <c r="D114" s="4" t="n">
-        <v>46.39</v>
+        <v>49.2</v>
       </c>
       <c r="E114" s="4" t="n">
-        <v>45.61</v>
+        <v>71.62</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>51.3</v>
+        <v>80.15000000000001</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>EPL</t>
+          <t>BIRLACORPN</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -5008,22 +5194,22 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>239.35</v>
+        <v>850.3</v>
       </c>
       <c r="D115" s="4" t="n">
-        <v>46.24</v>
+        <v>49.04</v>
       </c>
       <c r="E115" s="4" t="n">
-        <v>53.92</v>
+        <v>39.93</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>55.49</v>
+        <v>38.08</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>IIFLCAPS</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -5032,22 +5218,22 @@
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>335.6</v>
+        <v>214.09</v>
       </c>
       <c r="D116" s="4" t="n">
-        <v>46.06</v>
+        <v>48.97</v>
       </c>
       <c r="E116" s="4" t="n">
-        <v>57.61</v>
+        <v>63.16</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>58.89</v>
+        <v>65.14</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>SKIPPER</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -5056,22 +5242,22 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>1446.2</v>
+        <v>551.15</v>
       </c>
       <c r="D117" s="4" t="n">
-        <v>45.99</v>
+        <v>48.76</v>
       </c>
       <c r="E117" s="4" t="n">
-        <v>61.16</v>
+        <v>56.96</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>64.69</v>
+        <v>61.7</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>JAMNAAUTO</t>
+          <t>VIPIND</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -5080,22 +5266,22 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>125.03</v>
+        <v>301.2</v>
       </c>
       <c r="D118" s="4" t="n">
-        <v>45.98</v>
+        <v>48.75</v>
       </c>
       <c r="E118" s="4" t="n">
-        <v>49.21</v>
+        <v>43.43</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>54.9</v>
+        <v>36.42</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>VIPIND</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -5104,22 +5290,22 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>299.1</v>
+        <v>482.55</v>
       </c>
       <c r="D119" s="4" t="n">
-        <v>45.81</v>
+        <v>48.67</v>
       </c>
       <c r="E119" s="4" t="n">
-        <v>42.4</v>
+        <v>39.69</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>36.18</v>
+        <v>39.53</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>PURVA</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -5128,22 +5314,22 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>541.6</v>
+        <v>213.87</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>45.55</v>
+        <v>48.49</v>
       </c>
       <c r="E120" s="4" t="n">
-        <v>62.7</v>
+        <v>47.72</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>68.64</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>INDIASHLTR</t>
+          <t>THYROCARE</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -5152,22 +5338,22 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>661.6</v>
+        <v>566.85</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>45.31</v>
+        <v>48.34</v>
       </c>
       <c r="E121" s="4" t="n">
-        <v>41.3</v>
+        <v>58.65</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>43.33</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>KIRLOSBROS</t>
+          <t>KRBL</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -5176,22 +5362,22 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>1811.4</v>
+        <v>398.65</v>
       </c>
       <c r="D122" s="4" t="n">
-        <v>45.27</v>
+        <v>48.26</v>
       </c>
       <c r="E122" s="4" t="n">
-        <v>51.17</v>
+        <v>56.74</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>53.34</v>
+        <v>56.06</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>AGARWALEYE</t>
+          <t>EMBDL</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -5200,22 +5386,22 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>500.15</v>
+        <v>58.07</v>
       </c>
       <c r="D123" s="4" t="n">
-        <v>45.08</v>
+        <v>48.24</v>
       </c>
       <c r="E123" s="4" t="n">
-        <v>54.64</v>
+        <v>46.13</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>56.35</v>
+        <v>41.13</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>THYROCARE</t>
+          <t>JSLL</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -5224,22 +5410,22 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>559.25</v>
+        <v>508.25</v>
       </c>
       <c r="D124" s="4" t="n">
-        <v>45.08</v>
+        <v>48.18</v>
       </c>
       <c r="E124" s="4" t="n">
-        <v>57.02</v>
+        <v>39.15</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>64.51000000000001</v>
+        <v>40.75</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>MAHSCOOTER</t>
+          <t>MANYAVAR</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -5248,22 +5434,22 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>13123</v>
+        <v>532.5</v>
       </c>
       <c r="D125" s="4" t="n">
-        <v>45.01</v>
+        <v>47.9</v>
       </c>
       <c r="E125" s="4" t="n">
-        <v>55.28</v>
+        <v>59.87</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>59.02</v>
+        <v>39.92</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>HCC</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -5272,22 +5458,22 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>21.77</v>
+        <v>155.09</v>
       </c>
       <c r="D126" s="4" t="n">
-        <v>44.98</v>
+        <v>47.59</v>
       </c>
       <c r="E126" s="4" t="n">
-        <v>49.17</v>
+        <v>48.28</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>46.36</v>
+        <v>53.53</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>AEQUS</t>
+          <t>UTLSOLAR</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -5296,13 +5482,13 @@
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>231.67</v>
+        <v>422.1</v>
       </c>
       <c r="D127" s="4" t="n">
-        <v>44.92</v>
+        <v>47.58</v>
       </c>
       <c r="E127" s="4" t="n">
-        <v>58.11</v>
+        <v>63.76</v>
       </c>
       <c r="F127" s="4" t="n">
         <v/>
@@ -5311,7 +5497,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>GMRP&amp;UI</t>
+          <t>AGARWALEYE</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -5320,22 +5506,22 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>92.31</v>
+        <v>500</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>44.52</v>
+        <v>47.46</v>
       </c>
       <c r="E128" s="4" t="n">
-        <v>37.37</v>
+        <v>54.51</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>47.71</v>
+        <v>56.28</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>SFL</t>
+          <t>RENUKA</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -5344,22 +5530,22 @@
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>663.05</v>
+        <v>23.31</v>
       </c>
       <c r="D129" s="4" t="n">
-        <v>44.39</v>
+        <v>47.42</v>
       </c>
       <c r="E129" s="4" t="n">
-        <v>49.57</v>
+        <v>46.49</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>46.14</v>
+        <v>39.45</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>SUDEEPPHRM</t>
+          <t>TMB</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -5368,22 +5554,22 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>1105.4</v>
+        <v>881.9</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>44.03</v>
+        <v>47.37</v>
       </c>
       <c r="E130" s="4" t="n">
-        <v>66.56</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v/>
+        <v>72.77</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>ASTRAMICRO</t>
+          <t>POWERMECH</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -5392,22 +5578,22 @@
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>1631.2</v>
+        <v>2407.3</v>
       </c>
       <c r="D131" s="4" t="n">
-        <v>43.97</v>
+        <v>47.25</v>
       </c>
       <c r="E131" s="4" t="n">
-        <v>57.83</v>
+        <v>47.31</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>68.37</v>
+        <v>49.77</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>POWERMECH</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -5416,22 +5602,22 @@
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>2371.4</v>
+        <v>5134.5</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>43.96</v>
+        <v>47.24</v>
       </c>
       <c r="E132" s="4" t="n">
-        <v>45.8</v>
+        <v>52.58</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>49.21</v>
+        <v>66.87</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>SAATVIKGL</t>
+          <t>JUSTDIAL</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -5440,22 +5626,22 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>404.5</v>
+        <v>672.2</v>
       </c>
       <c r="D133" s="4" t="n">
-        <v>43.89</v>
+        <v>47.23</v>
       </c>
       <c r="E133" s="4" t="n">
-        <v>44.85</v>
+        <v>55.12</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v/>
+        <v>45.8</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>SOUTHBANK</t>
+          <t>BLACKBUCK</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -5464,46 +5650,46 @@
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>45.19</v>
+        <v>592.95</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>43.76</v>
+        <v>47</v>
       </c>
       <c r="E134" s="4" t="n">
-        <v>58.41</v>
+        <v>52.31</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>69.93000000000001</v>
+        <v>58.29</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="5" t="inlineStr">
-        <is>
-          <t>CUPID</t>
-        </is>
-      </c>
-      <c r="B135" s="6" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C135" s="7" t="n">
-        <v>265</v>
-      </c>
-      <c r="D135" s="7" t="n">
-        <v>43.74</v>
-      </c>
-      <c r="E135" s="7" t="n">
-        <v>75.70999999999999</v>
-      </c>
-      <c r="F135" s="7" t="n">
-        <v>87.01000000000001</v>
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>ASHOKA</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="n">
+        <v>113.12</v>
+      </c>
+      <c r="D135" s="4" t="n">
+        <v>46.82</v>
+      </c>
+      <c r="E135" s="4" t="n">
+        <v>36.53</v>
+      </c>
+      <c r="F135" s="4" t="n">
+        <v>40.78</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>MIDHANI</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -5512,22 +5698,22 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>407.85</v>
+        <v>2117.7</v>
       </c>
       <c r="D136" s="4" t="n">
-        <v>43.73</v>
+        <v>46.82</v>
       </c>
       <c r="E136" s="4" t="n">
-        <v>53.37</v>
+        <v>63.62</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>55.49</v>
+        <v/>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>GSFC</t>
+          <t>FINPIPE</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -5536,22 +5722,22 @@
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>152.27</v>
+        <v>154.16</v>
       </c>
       <c r="D137" s="4" t="n">
-        <v>43.66</v>
+        <v>46.8</v>
       </c>
       <c r="E137" s="4" t="n">
-        <v>41.85</v>
+        <v>38.52</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>43.61</v>
+        <v>41.05</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>GREAVESCOT</t>
+          <t>JAIBALAJI</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -5560,22 +5746,22 @@
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>191.72</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="D138" s="4" t="n">
-        <v>43.65</v>
+        <v>46.62</v>
       </c>
       <c r="E138" s="4" t="n">
-        <v>50.78</v>
+        <v>46.45</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>51.99</v>
+        <v>41.79</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>AURIONPRO</t>
+          <t>V2RETAIL</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -5584,46 +5770,46 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>688</v>
+        <v>214.72</v>
       </c>
       <c r="D139" s="4" t="n">
-        <v>43.61</v>
+        <v>46.59</v>
       </c>
       <c r="E139" s="4" t="n">
-        <v>34.82</v>
+        <v>48.52</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>38</v>
+        <v>61.26</v>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="5" t="inlineStr">
-        <is>
-          <t>SHAILY</t>
-        </is>
-      </c>
-      <c r="B140" s="6" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C140" s="7" t="n">
-        <v>3149.8</v>
-      </c>
-      <c r="D140" s="7" t="n">
-        <v>43.44</v>
-      </c>
-      <c r="E140" s="7" t="n">
-        <v>60.73</v>
-      </c>
-      <c r="F140" s="7" t="n">
-        <v>70.34</v>
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>GRWRHITECH</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="n">
+        <v>6640</v>
+      </c>
+      <c r="D140" s="4" t="n">
+        <v>46.49</v>
+      </c>
+      <c r="E140" s="4" t="n">
+        <v>61.07</v>
+      </c>
+      <c r="F140" s="4" t="n">
+        <v>65.7</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>RENUKA</t>
+          <t>BLUESTONE</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -5632,22 +5818,22 @@
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>23.06</v>
+        <v>809.3</v>
       </c>
       <c r="D141" s="4" t="n">
-        <v>43.37</v>
+        <v>46.48</v>
       </c>
       <c r="E141" s="4" t="n">
-        <v>45.32</v>
+        <v>63.66</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>39.17</v>
+        <v/>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>STYRENIX</t>
+          <t>DBREALTY</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -5656,16 +5842,16 @@
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>2067.9</v>
+        <v>100.08</v>
       </c>
       <c r="D142" s="4" t="n">
-        <v>43.31</v>
+        <v>46.41</v>
       </c>
       <c r="E142" s="4" t="n">
-        <v>45.06</v>
+        <v>41.89</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>48.91</v>
+        <v>42.17</v>
       </c>
     </row>
     <row r="143">
@@ -5680,22 +5866,22 @@
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>64.83</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="D143" s="4" t="n">
-        <v>43.3</v>
+        <v>46.4</v>
       </c>
       <c r="E143" s="4" t="n">
-        <v>54.07</v>
+        <v>53.51</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>60.25</v>
+        <v>59.98</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>V2RETAIL</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -5704,22 +5890,22 @@
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>214.03</v>
+        <v>198.85</v>
       </c>
       <c r="D144" s="4" t="n">
-        <v>43.1</v>
+        <v>46.4</v>
       </c>
       <c r="E144" s="4" t="n">
-        <v>48.07</v>
+        <v>48.14</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>61.02</v>
+        <v>43.05</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>UTLSOLAR</t>
+          <t>EPL</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -5728,22 +5914,22 @@
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>408.95</v>
+        <v>238.1</v>
       </c>
       <c r="D145" s="4" t="n">
-        <v>42.91</v>
+        <v>46.36</v>
       </c>
       <c r="E145" s="4" t="n">
-        <v>63.28</v>
+        <v>53.26</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v/>
+        <v>55.18</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>KRBL</t>
+          <t>MTARTECH</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -5752,22 +5938,22 @@
         </is>
       </c>
       <c r="C146" s="4" t="n">
-        <v>394.85</v>
+        <v>6900</v>
       </c>
       <c r="D146" s="4" t="n">
-        <v>42.74</v>
+        <v>46.36</v>
       </c>
       <c r="E146" s="4" t="n">
-        <v>53.96</v>
+        <v>56.86</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>54.8</v>
+        <v>69.12</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>REDTAPE</t>
+          <t>BALAMINES</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -5776,22 +5962,22 @@
         </is>
       </c>
       <c r="C147" s="4" t="n">
-        <v>117.34</v>
+        <v>2189.6</v>
       </c>
       <c r="D147" s="4" t="n">
-        <v>42.59</v>
+        <v>46.26</v>
       </c>
       <c r="E147" s="4" t="n">
-        <v>42.21</v>
+        <v>57.84</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>34.1</v>
+        <v>59.72</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>VIYASH</t>
+          <t>TIMETECHNO</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -5800,22 +5986,22 @@
         </is>
       </c>
       <c r="C148" s="4" t="n">
-        <v>249.65</v>
+        <v>181.22</v>
       </c>
       <c r="D148" s="4" t="n">
-        <v>42.55</v>
+        <v>46.19</v>
       </c>
       <c r="E148" s="4" t="n">
-        <v>50.73</v>
+        <v>46.89</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>59.47</v>
+        <v>51.09</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>JAYNECOIND</t>
+          <t>MAHSCOOTER</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -5824,22 +6010,22 @@
         </is>
       </c>
       <c r="C149" s="4" t="n">
-        <v>88.94</v>
+        <v>13052</v>
       </c>
       <c r="D149" s="4" t="n">
-        <v>42.45</v>
+        <v>46.08</v>
       </c>
       <c r="E149" s="4" t="n">
-        <v>49.79</v>
+        <v>50.69</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>58.6</v>
+        <v>56.21</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>JAIBALAJI</t>
+          <t>QUESS</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -5848,22 +6034,22 @@
         </is>
       </c>
       <c r="C150" s="4" t="n">
-        <v>64.05</v>
+        <v>340.9</v>
       </c>
       <c r="D150" s="4" t="n">
-        <v>42.33</v>
+        <v>45.82</v>
       </c>
       <c r="E150" s="4" t="n">
-        <v>45.95</v>
+        <v>65.91</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>41.67</v>
+        <v>50.41</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>MEDPLUS</t>
+          <t>MANORAMA</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -5872,22 +6058,22 @@
         </is>
       </c>
       <c r="C151" s="4" t="n">
-        <v>659.65</v>
+        <v>1872.8</v>
       </c>
       <c r="D151" s="4" t="n">
-        <v>42.32</v>
+        <v>45.67</v>
       </c>
       <c r="E151" s="4" t="n">
-        <v>29.65</v>
+        <v>62.25</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>38.99</v>
+        <v>69.67</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>BECTORFOOD</t>
+          <t>PICCADIL</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -5896,22 +6082,22 @@
         </is>
       </c>
       <c r="C152" s="4" t="n">
-        <v>221.55</v>
+        <v>613</v>
       </c>
       <c r="D152" s="4" t="n">
-        <v>42.31</v>
+        <v>45.5</v>
       </c>
       <c r="E152" s="4" t="n">
-        <v>53.05</v>
+        <v>47.88</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>48.44</v>
+        <v/>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>RATEGAIN</t>
+          <t>SHAILY</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -5920,22 +6106,22 @@
         </is>
       </c>
       <c r="C153" s="4" t="n">
-        <v>860.95</v>
+        <v>3142.3</v>
       </c>
       <c r="D153" s="4" t="n">
-        <v>41.88</v>
+        <v>45.15</v>
       </c>
       <c r="E153" s="4" t="n">
-        <v>55.45</v>
+        <v>60.39</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>60.89</v>
+        <v>70.16</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>BALAMINES</t>
+          <t>RBA</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -5944,46 +6130,46 @@
         </is>
       </c>
       <c r="C154" s="4" t="n">
-        <v>2149.8</v>
+        <v>92.51000000000001</v>
       </c>
       <c r="D154" s="4" t="n">
-        <v>41.85</v>
+        <v>45.13</v>
       </c>
       <c r="E154" s="4" t="n">
-        <v>57.35</v>
+        <v>61.66</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>59.29</v>
+        <v>55.87</v>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="5" t="inlineStr">
-        <is>
-          <t>HCG</t>
-        </is>
-      </c>
-      <c r="B155" s="6" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C155" s="7" t="n">
-        <v>674.15</v>
-      </c>
-      <c r="D155" s="7" t="n">
-        <v>41.83</v>
-      </c>
-      <c r="E155" s="7" t="n">
-        <v>62.97</v>
-      </c>
-      <c r="F155" s="7" t="n">
-        <v>63.5</v>
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>WABAG</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C155" s="4" t="n">
+        <v>2008.4</v>
+      </c>
+      <c r="D155" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="E155" s="4" t="n">
+        <v>56.61</v>
+      </c>
+      <c r="F155" s="4" t="n">
+        <v>67.56999999999999</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>CERA</t>
+          <t>ASTRAMICRO</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -5992,22 +6178,22 @@
         </is>
       </c>
       <c r="C156" s="4" t="n">
-        <v>5646</v>
+        <v>1622.4</v>
       </c>
       <c r="D156" s="4" t="n">
-        <v>41.57</v>
+        <v>44.81</v>
       </c>
       <c r="E156" s="4" t="n">
-        <v>47.9</v>
+        <v>57.19</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>47.2</v>
+        <v>67.98</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>INDIGOPNTS</t>
+          <t>KNRCON</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -6016,22 +6202,22 @@
         </is>
       </c>
       <c r="C157" s="4" t="n">
-        <v>1081.6</v>
+        <v>120.27</v>
       </c>
       <c r="D157" s="4" t="n">
-        <v>41.48</v>
+        <v>44.71</v>
       </c>
       <c r="E157" s="4" t="n">
-        <v>55.59</v>
+        <v>42.12</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>48.65</v>
+        <v>33.75</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>JYOTHYLAB</t>
+          <t>STYRENIX</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -6040,16 +6226,16 @@
         </is>
       </c>
       <c r="C158" s="4" t="n">
-        <v>195.41</v>
+        <v>2067</v>
       </c>
       <c r="D158" s="4" t="n">
-        <v>41.35</v>
+        <v>44.66</v>
       </c>
       <c r="E158" s="4" t="n">
-        <v>37.76</v>
+        <v>45.02</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>37.04</v>
+        <v>48.89</v>
       </c>
     </row>
     <row r="159">
@@ -6064,22 +6250,22 @@
         </is>
       </c>
       <c r="C159" s="4" t="n">
-        <v>501.45</v>
+        <v>506.8</v>
       </c>
       <c r="D159" s="4" t="n">
-        <v>40.95</v>
+        <v>44.18</v>
       </c>
       <c r="E159" s="4" t="n">
-        <v>52.21</v>
+        <v>50.2</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>50.03</v>
+        <v>49.31</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>TIMETECHNO</t>
+          <t>RELIGARE</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -6088,16 +6274,16 @@
         </is>
       </c>
       <c r="C160" s="4" t="n">
-        <v>179.24</v>
+        <v>242.27</v>
       </c>
       <c r="D160" s="4" t="n">
-        <v>40.89</v>
+        <v>43.9</v>
       </c>
       <c r="E160" s="4" t="n">
-        <v>45.48</v>
+        <v>49.42</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>50.64</v>
+        <v>51.81</v>
       </c>
     </row>
     <row r="161">
@@ -6112,22 +6298,22 @@
         </is>
       </c>
       <c r="C161" s="4" t="n">
-        <v>150.76</v>
+        <v>151.68</v>
       </c>
       <c r="D161" s="4" t="n">
-        <v>40.81</v>
+        <v>43.89</v>
       </c>
       <c r="E161" s="4" t="n">
-        <v>53.3</v>
+        <v>49.84</v>
       </c>
       <c r="F161" s="4" t="n">
-        <v>58.24</v>
+        <v>56.56</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>GRINDWELL</t>
+          <t>AWFIS</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -6136,22 +6322,22 @@
         </is>
       </c>
       <c r="C162" s="4" t="n">
-        <v>1895.6</v>
+        <v>257.2</v>
       </c>
       <c r="D162" s="4" t="n">
-        <v>40.66</v>
+        <v>43.68</v>
       </c>
       <c r="E162" s="4" t="n">
-        <v>49.46</v>
+        <v>37.28</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>52.3</v>
+        <v>29.51</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>REFEX</t>
+          <t>BANCOINDIA</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -6160,22 +6346,22 @@
         </is>
       </c>
       <c r="C163" s="4" t="n">
-        <v>271.75</v>
+        <v>599.85</v>
       </c>
       <c r="D163" s="4" t="n">
-        <v>40.55</v>
+        <v>43.6</v>
       </c>
       <c r="E163" s="4" t="n">
-        <v>43.46</v>
+        <v>45.82</v>
       </c>
       <c r="F163" s="4" t="n">
-        <v>47.45</v>
+        <v>55.31</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>JSFB</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -6184,22 +6370,22 @@
         </is>
       </c>
       <c r="C164" s="4" t="n">
-        <v>506.6</v>
+        <v>103.47</v>
       </c>
       <c r="D164" s="4" t="n">
-        <v>40.49</v>
+        <v>43.55</v>
       </c>
       <c r="E164" s="4" t="n">
-        <v>56.51</v>
+        <v>46.09</v>
       </c>
       <c r="F164" s="4" t="n">
-        <v>56.1</v>
+        <v>41.46</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>DATAMATICS</t>
+          <t>WAAREERTL</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -6208,22 +6394,22 @@
         </is>
       </c>
       <c r="C165" s="4" t="n">
-        <v>758.35</v>
+        <v>832.9</v>
       </c>
       <c r="D165" s="4" t="n">
-        <v>40.47</v>
+        <v>43.52</v>
       </c>
       <c r="E165" s="4" t="n">
-        <v>46.74</v>
+        <v>36.91</v>
       </c>
       <c r="F165" s="4" t="n">
-        <v>53.23</v>
+        <v>39.61</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>STARCEMENT</t>
+          <t>INDIASHLTR</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -6232,22 +6418,22 @@
         </is>
       </c>
       <c r="C166" s="4" t="n">
-        <v>187.3</v>
+        <v>654.3</v>
       </c>
       <c r="D166" s="4" t="n">
-        <v>40.44</v>
+        <v>43.43</v>
       </c>
       <c r="E166" s="4" t="n">
-        <v>38.78</v>
+        <v>37.78</v>
       </c>
       <c r="F166" s="4" t="n">
-        <v>46.19</v>
+        <v>40.09</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>VIKRAMSOLR</t>
+          <t>CMSINFO</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -6256,22 +6442,22 @@
         </is>
       </c>
       <c r="C167" s="4" t="n">
-        <v>163.37</v>
+        <v>233.17</v>
       </c>
       <c r="D167" s="4" t="n">
-        <v>40.34</v>
+        <v>43.42</v>
       </c>
       <c r="E167" s="4" t="n">
-        <v>36.58</v>
+        <v>32.26</v>
       </c>
       <c r="F167" s="4" t="n">
-        <v/>
+        <v>32.09</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>ZAGGLE</t>
+          <t>WAKEFIT</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -6280,22 +6466,22 @@
         </is>
       </c>
       <c r="C168" s="4" t="n">
-        <v>177.81</v>
+        <v>141.35</v>
       </c>
       <c r="D168" s="4" t="n">
-        <v>40.19</v>
+        <v>43.39</v>
       </c>
       <c r="E168" s="4" t="n">
-        <v>32.9</v>
+        <v>48.95</v>
       </c>
       <c r="F168" s="4" t="n">
-        <v>37.26</v>
+        <v/>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>CMSINFO</t>
+          <t>MIDHANI</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -6304,22 +6490,22 @@
         </is>
       </c>
       <c r="C169" s="4" t="n">
-        <v>230.93</v>
+        <v>405.05</v>
       </c>
       <c r="D169" s="4" t="n">
-        <v>39.72</v>
+        <v>43.33</v>
       </c>
       <c r="E169" s="4" t="n">
-        <v>30.95</v>
+        <v>50.58</v>
       </c>
       <c r="F169" s="4" t="n">
-        <v>31.86</v>
+        <v>54.29</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>JAYNECOIND</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -6328,22 +6514,22 @@
         </is>
       </c>
       <c r="C170" s="4" t="n">
-        <v>102.01</v>
+        <v>88.55</v>
       </c>
       <c r="D170" s="4" t="n">
-        <v>39.63</v>
+        <v>42.81</v>
       </c>
       <c r="E170" s="4" t="n">
-        <v>48.23</v>
+        <v>49.13</v>
       </c>
       <c r="F170" s="4" t="n">
-        <v>42.13</v>
+        <v>58.28</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>MASTEK</t>
+          <t>ZAGGLE</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -6352,22 +6538,22 @@
         </is>
       </c>
       <c r="C171" s="4" t="n">
-        <v>1588.2</v>
+        <v>178.84</v>
       </c>
       <c r="D171" s="4" t="n">
-        <v>39.62</v>
+        <v>42.58</v>
       </c>
       <c r="E171" s="4" t="n">
-        <v>43.45</v>
+        <v>33.06</v>
       </c>
       <c r="F171" s="4" t="n">
-        <v>40.89</v>
+        <v>37.29</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>ORIENTCEM</t>
+          <t>RUBICON</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -6376,22 +6562,22 @@
         </is>
       </c>
       <c r="C172" s="4" t="n">
-        <v>124.55</v>
+        <v>1676.3</v>
       </c>
       <c r="D172" s="4" t="n">
-        <v>39.29</v>
+        <v>42.49</v>
       </c>
       <c r="E172" s="4" t="n">
-        <v>31.67</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="F172" s="4" t="n">
-        <v>34.22</v>
+        <v/>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>ATLANTAELE</t>
+          <t>ADVENZYMES</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -6400,22 +6586,22 @@
         </is>
       </c>
       <c r="C173" s="4" t="n">
-        <v>1633.3</v>
+        <v>291.15</v>
       </c>
       <c r="D173" s="4" t="n">
-        <v>39.28</v>
+        <v>42.43</v>
       </c>
       <c r="E173" s="4" t="n">
-        <v>52.62</v>
+        <v>40.45</v>
       </c>
       <c r="F173" s="4" t="n">
-        <v/>
+        <v>45.92</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>MOIL</t>
+          <t>ALKYLAMINE</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -6424,22 +6610,22 @@
         </is>
       </c>
       <c r="C174" s="4" t="n">
-        <v>243.88</v>
+        <v>1847.7</v>
       </c>
       <c r="D174" s="4" t="n">
-        <v>39.21</v>
+        <v>42.25</v>
       </c>
       <c r="E174" s="4" t="n">
-        <v>32.93</v>
+        <v>53.18</v>
       </c>
       <c r="F174" s="4" t="n">
-        <v>40.42</v>
+        <v>50.23</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>RAYMONDLSL</t>
+          <t>NETWORK18</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -6448,22 +6634,22 @@
         </is>
       </c>
       <c r="C175" s="4" t="n">
-        <v>657.25</v>
+        <v>26.75</v>
       </c>
       <c r="D175" s="4" t="n">
-        <v>39.08</v>
+        <v>42.07</v>
       </c>
       <c r="E175" s="4" t="n">
-        <v>33.87</v>
+        <v>33.41</v>
       </c>
       <c r="F175" s="4" t="n">
-        <v>23.51</v>
+        <v>33.55</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>ELECTCAST</t>
+          <t>GOKULAGRO</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -6472,22 +6658,22 @@
         </is>
       </c>
       <c r="C176" s="4" t="n">
-        <v>73.38</v>
+        <v>221.89</v>
       </c>
       <c r="D176" s="4" t="n">
-        <v>38.48</v>
+        <v>42.03</v>
       </c>
       <c r="E176" s="4" t="n">
-        <v>46.42</v>
+        <v>52.34</v>
       </c>
       <c r="F176" s="4" t="n">
-        <v>43.22</v>
+        <v>61.42</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENT</t>
+          <t>SUNTECK</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -6496,22 +6682,22 @@
         </is>
       </c>
       <c r="C177" s="4" t="n">
-        <v>68.84</v>
+        <v>283</v>
       </c>
       <c r="D177" s="4" t="n">
-        <v>38.41</v>
+        <v>41.84</v>
       </c>
       <c r="E177" s="4" t="n">
-        <v>47.62</v>
+        <v>38.52</v>
       </c>
       <c r="F177" s="4" t="n">
-        <v>54.38</v>
+        <v>39.25</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>ALKYLAMINE</t>
+          <t>HCC</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -6520,22 +6706,22 @@
         </is>
       </c>
       <c r="C178" s="4" t="n">
-        <v>1823.1</v>
+        <v>21.26</v>
       </c>
       <c r="D178" s="4" t="n">
-        <v>38.37</v>
+        <v>41.82</v>
       </c>
       <c r="E178" s="4" t="n">
-        <v>54.24</v>
+        <v>47.7</v>
       </c>
       <c r="F178" s="4" t="n">
-        <v>50.59</v>
+        <v>45.89</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>STYL</t>
+          <t>KIRLOSBROS</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -6544,22 +6730,22 @@
         </is>
       </c>
       <c r="C179" s="4" t="n">
-        <v>360.35</v>
+        <v>1771.9</v>
       </c>
       <c r="D179" s="4" t="n">
-        <v>38.33</v>
+        <v>41.7</v>
       </c>
       <c r="E179" s="4" t="n">
-        <v>55.27</v>
+        <v>48.52</v>
       </c>
       <c r="F179" s="4" t="n">
-        <v/>
+        <v>52.43</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>APOLLO</t>
+          <t>FIEMIND</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -6568,22 +6754,22 @@
         </is>
       </c>
       <c r="C180" s="4" t="n">
-        <v>370.7</v>
+        <v>1965.5</v>
       </c>
       <c r="D180" s="4" t="n">
-        <v>38.21</v>
+        <v>41.6</v>
       </c>
       <c r="E180" s="4" t="n">
-        <v>51.98</v>
+        <v>39.98</v>
       </c>
       <c r="F180" s="4" t="n">
-        <v>64.81</v>
+        <v>54.87</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENGG</t>
+          <t>SHARDACROP</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -6592,22 +6778,22 @@
         </is>
       </c>
       <c r="C181" s="4" t="n">
-        <v>80.2</v>
+        <v>749.6</v>
       </c>
       <c r="D181" s="4" t="n">
-        <v>37.83</v>
+        <v>41.59</v>
       </c>
       <c r="E181" s="4" t="n">
-        <v>56.7</v>
+        <v>37.03</v>
       </c>
       <c r="F181" s="4" t="n">
-        <v>60.67</v>
+        <v>48.88</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>BAJAJELEC</t>
+          <t>MASTEK</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -6616,22 +6802,22 @@
         </is>
       </c>
       <c r="C182" s="4" t="n">
-        <v>322.55</v>
+        <v>1582.8</v>
       </c>
       <c r="D182" s="4" t="n">
-        <v>37.78</v>
+        <v>41.58</v>
       </c>
       <c r="E182" s="4" t="n">
-        <v>38.86</v>
+        <v>43.23</v>
       </c>
       <c r="F182" s="4" t="n">
-        <v>29.54</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>BANCOINDIA</t>
+          <t>MEDPLUS</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -6640,22 +6826,22 @@
         </is>
       </c>
       <c r="C183" s="4" t="n">
-        <v>593.15</v>
+        <v>654.9</v>
       </c>
       <c r="D183" s="4" t="n">
-        <v>37.59</v>
+        <v>41.44</v>
       </c>
       <c r="E183" s="4" t="n">
-        <v>46.46</v>
+        <v>29.13</v>
       </c>
       <c r="F183" s="4" t="n">
-        <v>55.62</v>
+        <v>38.69</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>JSLL</t>
+          <t>JKLAKSHMI</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -6664,22 +6850,22 @@
         </is>
       </c>
       <c r="C184" s="4" t="n">
-        <v>490.75</v>
+        <v>510.35</v>
       </c>
       <c r="D184" s="4" t="n">
-        <v>37.58</v>
+        <v>41.38</v>
       </c>
       <c r="E184" s="4" t="n">
-        <v>38.75</v>
+        <v>33.28</v>
       </c>
       <c r="F184" s="4" t="n">
-        <v>40.68</v>
+        <v>36.59</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>PRAJIND</t>
+          <t>PARAS</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -6688,22 +6874,22 @@
         </is>
       </c>
       <c r="C185" s="4" t="n">
-        <v>316.05</v>
+        <v>1321</v>
       </c>
       <c r="D185" s="4" t="n">
-        <v>37.46</v>
+        <v>41.37</v>
       </c>
       <c r="E185" s="4" t="n">
-        <v>42.75</v>
+        <v>59.86</v>
       </c>
       <c r="F185" s="4" t="n">
-        <v>41.91</v>
+        <v>65.09</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>OSWALPUMPS</t>
+          <t>ATLANTAELE</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -6712,22 +6898,22 @@
         </is>
       </c>
       <c r="C186" s="4" t="n">
-        <v>278.1</v>
+        <v>1625.9</v>
       </c>
       <c r="D186" s="4" t="n">
-        <v>37.43</v>
+        <v>41.21</v>
       </c>
       <c r="E186" s="4" t="n">
-        <v>30.74</v>
+        <v>50.98</v>
       </c>
       <c r="F186" s="4" t="n">
-        <v>26.44</v>
+        <v/>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>GAEL</t>
+          <t>SHAKTIPUMP</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -6736,22 +6922,22 @@
         </is>
       </c>
       <c r="C187" s="4" t="n">
-        <v>157.16</v>
+        <v>466.9</v>
       </c>
       <c r="D187" s="4" t="n">
-        <v>37.3</v>
+        <v>41.2</v>
       </c>
       <c r="E187" s="4" t="n">
-        <v>50.44</v>
+        <v>36.36</v>
       </c>
       <c r="F187" s="4" t="n">
-        <v>57.61</v>
+        <v>42.62</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>RALLIS</t>
+          <t>ORKLAINDIA</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -6760,22 +6946,22 @@
         </is>
       </c>
       <c r="C188" s="4" t="n">
-        <v>203.8</v>
+        <v>555.95</v>
       </c>
       <c r="D188" s="4" t="n">
-        <v>37.3</v>
+        <v>41.14</v>
       </c>
       <c r="E188" s="4" t="n">
-        <v>32.14</v>
+        <v>39.63</v>
       </c>
       <c r="F188" s="4" t="n">
-        <v>41.27</v>
+        <v/>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>ADVENZYMES</t>
+          <t>PNGJL</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -6784,22 +6970,22 @@
         </is>
       </c>
       <c r="C189" s="4" t="n">
-        <v>288.1</v>
+        <v>591.2</v>
       </c>
       <c r="D189" s="4" t="n">
-        <v>36.81</v>
+        <v>40.9</v>
       </c>
       <c r="E189" s="4" t="n">
-        <v>38.77</v>
+        <v>50.72</v>
       </c>
       <c r="F189" s="4" t="n">
-        <v>45.48</v>
+        <v>49.51</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>GHCL</t>
+          <t>STARCEMENT</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -6808,22 +6994,22 @@
         </is>
       </c>
       <c r="C190" s="4" t="n">
-        <v>421.7</v>
+        <v>186.61</v>
       </c>
       <c r="D190" s="4" t="n">
-        <v>36.55</v>
+        <v>40.8</v>
       </c>
       <c r="E190" s="4" t="n">
-        <v>38.22</v>
+        <v>34.12</v>
       </c>
       <c r="F190" s="4" t="n">
-        <v>40.91</v>
+        <v>43.89</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>CENTURYPLY</t>
+          <t>TRIVENI</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -6832,22 +7018,22 @@
         </is>
       </c>
       <c r="C191" s="4" t="n">
-        <v>719.9</v>
+        <v>247.55</v>
       </c>
       <c r="D191" s="4" t="n">
-        <v>36.37</v>
+        <v>40.8</v>
       </c>
       <c r="E191" s="4" t="n">
-        <v>41.43</v>
+        <v>37.4</v>
       </c>
       <c r="F191" s="4" t="n">
-        <v>48.33</v>
+        <v>41.25</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>SANDUMA</t>
+          <t>PRAJIND</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -6856,22 +7042,22 @@
         </is>
       </c>
       <c r="C192" s="4" t="n">
-        <v>185.4</v>
+        <v>315.9</v>
       </c>
       <c r="D192" s="4" t="n">
-        <v>36.19</v>
+        <v>40.49</v>
       </c>
       <c r="E192" s="4" t="n">
-        <v>41.03</v>
+        <v>42.71</v>
       </c>
       <c r="F192" s="4" t="n">
-        <v>51.18</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>SHAKTIPUMP</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -6880,22 +7066,22 @@
         </is>
       </c>
       <c r="C193" s="4" t="n">
-        <v>460.95</v>
+        <v>1381.8</v>
       </c>
       <c r="D193" s="4" t="n">
-        <v>35.77</v>
+        <v>40.22</v>
       </c>
       <c r="E193" s="4" t="n">
-        <v>34.89</v>
+        <v>56.82</v>
       </c>
       <c r="F193" s="4" t="n">
-        <v>42.34</v>
+        <v>62.3</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>ETHOSLTD</t>
+          <t>MOIL</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -6904,22 +7090,22 @@
         </is>
       </c>
       <c r="C194" s="4" t="n">
-        <v>2612.5</v>
+        <v>241.88</v>
       </c>
       <c r="D194" s="4" t="n">
-        <v>35.76</v>
+        <v>40.2</v>
       </c>
       <c r="E194" s="4" t="n">
-        <v>52.82</v>
+        <v>32.34</v>
       </c>
       <c r="F194" s="4" t="n">
-        <v>52.69</v>
+        <v>40.18</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>WEBELSOLAR</t>
+          <t>AURIONPRO</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -6928,22 +7114,22 @@
         </is>
       </c>
       <c r="C195" s="4" t="n">
-        <v>72.94</v>
+        <v>669.7</v>
       </c>
       <c r="D195" s="4" t="n">
-        <v>35.7</v>
+        <v>40.05</v>
       </c>
       <c r="E195" s="4" t="n">
-        <v>35.37</v>
+        <v>33.65</v>
       </c>
       <c r="F195" s="4" t="n">
-        <v>44.85</v>
+        <v>37.62</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>SUNTECK</t>
+          <t>TANLA</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -6952,22 +7138,22 @@
         </is>
       </c>
       <c r="C196" s="4" t="n">
-        <v>279.65</v>
+        <v>494.75</v>
       </c>
       <c r="D196" s="4" t="n">
-        <v>35.42</v>
+        <v>39.76</v>
       </c>
       <c r="E196" s="4" t="n">
-        <v>41.61</v>
+        <v>42.73</v>
       </c>
       <c r="F196" s="4" t="n">
-        <v>40.23</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>VIYASH</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -6976,22 +7162,22 @@
         </is>
       </c>
       <c r="C197" s="4" t="n">
-        <v>4927</v>
+        <v>244.35</v>
       </c>
       <c r="D197" s="4" t="n">
-        <v>35.21</v>
+        <v>39.64</v>
       </c>
       <c r="E197" s="4" t="n">
-        <v>51.4</v>
+        <v>48.9</v>
       </c>
       <c r="F197" s="4" t="n">
-        <v>65.87</v>
+        <v>58.34</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>PICCADIL</t>
+          <t>BECTORFOOD</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -7000,22 +7186,22 @@
         </is>
       </c>
       <c r="C198" s="4" t="n">
-        <v>599.55</v>
+        <v>215.68</v>
       </c>
       <c r="D198" s="4" t="n">
-        <v>35.19</v>
+        <v>39.55</v>
       </c>
       <c r="E198" s="4" t="n">
-        <v>44.59</v>
+        <v>51</v>
       </c>
       <c r="F198" s="4" t="n">
-        <v/>
+        <v>47.33</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>BIRLACORPN</t>
+          <t>SENCO</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -7024,22 +7210,22 @@
         </is>
       </c>
       <c r="C199" s="4" t="n">
-        <v>823.6</v>
+        <v>331.1</v>
       </c>
       <c r="D199" s="4" t="n">
-        <v>35.09</v>
+        <v>39.31</v>
       </c>
       <c r="E199" s="4" t="n">
-        <v>35.8</v>
+        <v>46.07</v>
       </c>
       <c r="F199" s="4" t="n">
-        <v>37.02</v>
+        <v>48.15</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>NETWORK18</t>
+          <t>WEBELSOLAR</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -7048,22 +7234,22 @@
         </is>
       </c>
       <c r="C200" s="4" t="n">
-        <v>26.12</v>
+        <v>73.23</v>
       </c>
       <c r="D200" s="4" t="n">
-        <v>34.78</v>
+        <v>39.26</v>
       </c>
       <c r="E200" s="4" t="n">
-        <v>33.97</v>
+        <v>35.68</v>
       </c>
       <c r="F200" s="4" t="n">
-        <v>33.69</v>
+        <v>44.92</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>CAMPUS</t>
+          <t>HEMIPROP</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -7072,22 +7258,22 @@
         </is>
       </c>
       <c r="C201" s="4" t="n">
-        <v>211.98</v>
+        <v>120.36</v>
       </c>
       <c r="D201" s="4" t="n">
-        <v>34.71</v>
+        <v>39.25</v>
       </c>
       <c r="E201" s="4" t="n">
-        <v>37.26</v>
+        <v>36.72</v>
       </c>
       <c r="F201" s="4" t="n">
-        <v>39.76</v>
+        <v>43.51</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>JLHL</t>
+          <t>OSWALPUMPS</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -7096,22 +7282,22 @@
         </is>
       </c>
       <c r="C202" s="4" t="n">
-        <v>280.05</v>
+        <v>274.95</v>
       </c>
       <c r="D202" s="4" t="n">
-        <v>34.47</v>
+        <v>39.1</v>
       </c>
       <c r="E202" s="4" t="n">
-        <v>46.9</v>
+        <v>30.3</v>
       </c>
       <c r="F202" s="4" t="n">
-        <v>50.69</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>SPARC</t>
+          <t>ANUP</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -7120,22 +7306,22 @@
         </is>
       </c>
       <c r="C203" s="4" t="n">
-        <v>185.59</v>
+        <v>1677.1</v>
       </c>
       <c r="D203" s="4" t="n">
-        <v>34.27</v>
+        <v>39.09</v>
       </c>
       <c r="E203" s="4" t="n">
-        <v>50.36</v>
+        <v>38.05</v>
       </c>
       <c r="F203" s="4" t="n">
-        <v>52.54</v>
+        <v>44.01</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>HEMIPROP</t>
+          <t>PRUDENT</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -7144,22 +7330,22 @@
         </is>
       </c>
       <c r="C204" s="4" t="n">
-        <v>120.77</v>
+        <v>3097.9</v>
       </c>
       <c r="D204" s="4" t="n">
-        <v>34.15</v>
+        <v>38.9</v>
       </c>
       <c r="E204" s="4" t="n">
-        <v>37.03</v>
+        <v>52.37</v>
       </c>
       <c r="F204" s="4" t="n">
-        <v>43.62</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>JKLAKSHMI</t>
+          <t>ARVINDFASN</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -7168,22 +7354,22 @@
         </is>
       </c>
       <c r="C205" s="4" t="n">
-        <v>510.4</v>
+        <v>417.2</v>
       </c>
       <c r="D205" s="4" t="n">
-        <v>34.14</v>
+        <v>38.82</v>
       </c>
       <c r="E205" s="4" t="n">
-        <v>36.25</v>
+        <v>38.66</v>
       </c>
       <c r="F205" s="4" t="n">
-        <v>37.62</v>
+        <v>45.05</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>SHARDACROP</t>
+          <t>BAJAJELEC</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -7192,22 +7378,22 @@
         </is>
       </c>
       <c r="C206" s="4" t="n">
-        <v>741.7</v>
+        <v>318.95</v>
       </c>
       <c r="D206" s="4" t="n">
-        <v>34.14</v>
+        <v>38.71</v>
       </c>
       <c r="E206" s="4" t="n">
-        <v>36.07</v>
+        <v>37.81</v>
       </c>
       <c r="F206" s="4" t="n">
-        <v>48.65</v>
+        <v>29.33</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>IMFA</t>
+          <t>IXIGO</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -7216,22 +7402,22 @@
         </is>
       </c>
       <c r="C207" s="4" t="n">
-        <v>1246.1</v>
+        <v>156.8</v>
       </c>
       <c r="D207" s="4" t="n">
-        <v>34.08</v>
+        <v>38.48</v>
       </c>
       <c r="E207" s="4" t="n">
-        <v>43</v>
+        <v>40.63</v>
       </c>
       <c r="F207" s="4" t="n">
-        <v>56.87</v>
+        <v>41.41</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>KSB</t>
+          <t>IFBIND</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -7240,22 +7426,22 @@
         </is>
       </c>
       <c r="C208" s="4" t="n">
-        <v>764.85</v>
+        <v>1225.2</v>
       </c>
       <c r="D208" s="4" t="n">
-        <v>34.05</v>
+        <v>37.92</v>
       </c>
       <c r="E208" s="4" t="n">
-        <v>46.92</v>
+        <v>44.37</v>
       </c>
       <c r="F208" s="4" t="n">
-        <v>51.99</v>
+        <v>47.46</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>ELECTCAST</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -7264,22 +7450,22 @@
         </is>
       </c>
       <c r="C209" s="4" t="n">
-        <v>461.45</v>
+        <v>72.34</v>
       </c>
       <c r="D209" s="4" t="n">
-        <v>34</v>
+        <v>37.92</v>
       </c>
       <c r="E209" s="4" t="n">
-        <v>35.27</v>
+        <v>45.39</v>
       </c>
       <c r="F209" s="4" t="n">
-        <v>38.29</v>
+        <v>42.91</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>ARVINDFASN</t>
+          <t>VIKRAMSOLR</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -7288,22 +7474,22 @@
         </is>
       </c>
       <c r="C210" s="4" t="n">
-        <v>416.35</v>
+        <v>160.31</v>
       </c>
       <c r="D210" s="4" t="n">
-        <v>33.58</v>
+        <v>37.8</v>
       </c>
       <c r="E210" s="4" t="n">
-        <v>41.45</v>
+        <v>34.81</v>
       </c>
       <c r="F210" s="4" t="n">
-        <v>46.35</v>
+        <v/>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>CRAMC</t>
+          <t>SAFARI</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -7312,22 +7498,22 @@
         </is>
       </c>
       <c r="C211" s="4" t="n">
-        <v>234.35</v>
+        <v>1464.2</v>
       </c>
       <c r="D211" s="4" t="n">
-        <v>33.55</v>
+        <v>37.72</v>
       </c>
       <c r="E211" s="4" t="n">
-        <v>38.13</v>
+        <v>40.05</v>
       </c>
       <c r="F211" s="4" t="n">
-        <v/>
+        <v>40.01</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>GOKEX</t>
+          <t>SANDUMA</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -7336,22 +7522,22 @@
         </is>
       </c>
       <c r="C212" s="4" t="n">
-        <v>727.75</v>
+        <v>183.11</v>
       </c>
       <c r="D212" s="4" t="n">
-        <v>33.3</v>
+        <v>37.56</v>
       </c>
       <c r="E212" s="4" t="n">
-        <v>44.96</v>
+        <v>40.78</v>
       </c>
       <c r="F212" s="4" t="n">
-        <v>48.58</v>
+        <v>51.05</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>GOKULAGRO</t>
+          <t>RTNINDIA</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -7360,22 +7546,22 @@
         </is>
       </c>
       <c r="C213" s="4" t="n">
-        <v>218.43</v>
+        <v>26.96</v>
       </c>
       <c r="D213" s="4" t="n">
-        <v>33.3</v>
+        <v>37.46</v>
       </c>
       <c r="E213" s="4" t="n">
-        <v>53.73</v>
+        <v>33.5</v>
       </c>
       <c r="F213" s="4" t="n">
-        <v>62.02</v>
+        <v>37.4</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>KIRLPNU</t>
+          <t>RATEGAIN</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -7384,22 +7570,22 @@
         </is>
       </c>
       <c r="C214" s="4" t="n">
-        <v>695.2</v>
+        <v>827.75</v>
       </c>
       <c r="D214" s="4" t="n">
-        <v>33.28</v>
+        <v>37.4</v>
       </c>
       <c r="E214" s="4" t="n">
-        <v>45.72</v>
+        <v>51.93</v>
       </c>
       <c r="F214" s="4" t="n">
-        <v>53.9</v>
+        <v>58.96</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>AVANTIFEED</t>
+          <t>GHCL</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -7408,22 +7594,22 @@
         </is>
       </c>
       <c r="C215" s="4" t="n">
-        <v>770.35</v>
+        <v>419.8</v>
       </c>
       <c r="D215" s="4" t="n">
-        <v>33.14</v>
+        <v>37.03</v>
       </c>
       <c r="E215" s="4" t="n">
-        <v>33.81</v>
+        <v>37.63</v>
       </c>
       <c r="F215" s="4" t="n">
-        <v>48.29</v>
+        <v>40.75</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>IFBIND</t>
+          <t>SWSOLAR</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -7432,22 +7618,22 @@
         </is>
       </c>
       <c r="C216" s="4" t="n">
-        <v>1241.9</v>
+        <v>176.65</v>
       </c>
       <c r="D216" s="4" t="n">
-        <v>33.06</v>
+        <v>36.92</v>
       </c>
       <c r="E216" s="4" t="n">
-        <v>44.36</v>
+        <v>37.7</v>
       </c>
       <c r="F216" s="4" t="n">
-        <v>47.45</v>
+        <v>38.97</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>VAIBHAVGBL</t>
+          <t>IMFA</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -7456,22 +7642,22 @@
         </is>
       </c>
       <c r="C217" s="4" t="n">
-        <v>210.66</v>
+        <v>1230.4</v>
       </c>
       <c r="D217" s="4" t="n">
-        <v>32.94</v>
+        <v>36.9</v>
       </c>
       <c r="E217" s="4" t="n">
-        <v>42.14</v>
+        <v>41.63</v>
       </c>
       <c r="F217" s="4" t="n">
-        <v>44.13</v>
+        <v>56.12</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>SURYAROSNI</t>
+          <t>SFL</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -7480,22 +7666,22 @@
         </is>
       </c>
       <c r="C218" s="4" t="n">
-        <v>210.62</v>
+        <v>634.6</v>
       </c>
       <c r="D218" s="4" t="n">
-        <v>32.77</v>
+        <v>36.73</v>
       </c>
       <c r="E218" s="4" t="n">
-        <v>38.15</v>
+        <v>46.7</v>
       </c>
       <c r="F218" s="4" t="n">
-        <v>44.31</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>CAPILLARY</t>
+          <t>ORIENTCEM</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -7504,22 +7690,22 @@
         </is>
       </c>
       <c r="C219" s="4" t="n">
-        <v>448.95</v>
+        <v>122.16</v>
       </c>
       <c r="D219" s="4" t="n">
-        <v>32.51</v>
+        <v>36.7</v>
       </c>
       <c r="E219" s="4" t="n">
-        <v>42.93</v>
+        <v>29.98</v>
       </c>
       <c r="F219" s="4" t="n">
-        <v/>
+        <v>33.86</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>ROUTE</t>
+          <t>KIRLPNU</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -7528,22 +7714,22 @@
         </is>
       </c>
       <c r="C220" s="4" t="n">
-        <v>464.4</v>
+        <v>691.95</v>
       </c>
       <c r="D220" s="4" t="n">
-        <v>32</v>
+        <v>36.62</v>
       </c>
       <c r="E220" s="4" t="n">
-        <v>34.69</v>
+        <v>45.01</v>
       </c>
       <c r="F220" s="4" t="n">
-        <v>28.99</v>
+        <v>53.54</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>FIEMIND</t>
+          <t>HGINFRA</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -7552,22 +7738,22 @@
         </is>
       </c>
       <c r="C221" s="4" t="n">
-        <v>1937.3</v>
+        <v>453.1</v>
       </c>
       <c r="D221" s="4" t="n">
-        <v>31.69</v>
+        <v>36.55</v>
       </c>
       <c r="E221" s="4" t="n">
-        <v>38.29</v>
+        <v>30.46</v>
       </c>
       <c r="F221" s="4" t="n">
-        <v>53.93</v>
+        <v>32.87</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>GRWRHITECH</t>
+          <t>WEWORK</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -7576,22 +7762,22 @@
         </is>
       </c>
       <c r="C222" s="4" t="n">
-        <v>6431</v>
+        <v>652.55</v>
       </c>
       <c r="D222" s="4" t="n">
-        <v>31.67</v>
+        <v>36.28</v>
       </c>
       <c r="E222" s="4" t="n">
-        <v>63.12</v>
+        <v>50.92</v>
       </c>
       <c r="F222" s="4" t="n">
-        <v>66.39</v>
+        <v/>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>ASHOKA</t>
+          <t>NFL</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -7600,22 +7786,22 @@
         </is>
       </c>
       <c r="C223" s="4" t="n">
-        <v>108.8</v>
+        <v>66.67</v>
       </c>
       <c r="D223" s="4" t="n">
-        <v>31.58</v>
+        <v>36.21</v>
       </c>
       <c r="E223" s="4" t="n">
-        <v>36.76</v>
+        <v>34.52</v>
       </c>
       <c r="F223" s="4" t="n">
-        <v>40.83</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>NFL</t>
+          <t>KITEX</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -7624,22 +7810,22 @@
         </is>
       </c>
       <c r="C224" s="4" t="n">
-        <v>66.84</v>
+        <v>117.68</v>
       </c>
       <c r="D224" s="4" t="n">
-        <v>31.53</v>
+        <v>36.2</v>
       </c>
       <c r="E224" s="4" t="n">
-        <v>34.73</v>
+        <v>30.9</v>
       </c>
       <c r="F224" s="4" t="n">
-        <v>41.26</v>
+        <v>41.88</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>EMBDL</t>
+          <t>ETHOSLTD</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -7648,22 +7834,22 @@
         </is>
       </c>
       <c r="C225" s="4" t="n">
-        <v>53.88</v>
+        <v>2552.8</v>
       </c>
       <c r="D225" s="4" t="n">
-        <v>31.24</v>
+        <v>36.03</v>
       </c>
       <c r="E225" s="4" t="n">
-        <v>40.45</v>
+        <v>48.11</v>
       </c>
       <c r="F225" s="4" t="n">
-        <v>39.89</v>
+        <v>50.75</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>TRIVENI</t>
+          <t>RCF</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -7672,22 +7858,22 @@
         </is>
       </c>
       <c r="C226" s="4" t="n">
-        <v>239.45</v>
+        <v>108.58</v>
       </c>
       <c r="D226" s="4" t="n">
-        <v>30.76</v>
+        <v>35.81</v>
       </c>
       <c r="E226" s="4" t="n">
-        <v>35.67</v>
+        <v>33.86</v>
       </c>
       <c r="F226" s="4" t="n">
-        <v>40.67</v>
+        <v>41.46</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>RTNPOWER</t>
+          <t>JYOTHYLAB</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -7696,22 +7882,22 @@
         </is>
       </c>
       <c r="C227" s="4" t="n">
-        <v>7.14</v>
+        <v>191.07</v>
       </c>
       <c r="D227" s="4" t="n">
-        <v>30.57</v>
+        <v>35.42</v>
       </c>
       <c r="E227" s="4" t="n">
-        <v>29</v>
+        <v>35.86</v>
       </c>
       <c r="F227" s="4" t="n">
-        <v>40.74</v>
+        <v>36.62</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>KSCL</t>
+          <t>ROUTE</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -7720,22 +7906,22 @@
         </is>
       </c>
       <c r="C228" s="4" t="n">
-        <v>703.35</v>
+        <v>463</v>
       </c>
       <c r="D228" s="4" t="n">
-        <v>29.75</v>
+        <v>35.39</v>
       </c>
       <c r="E228" s="4" t="n">
-        <v>32.72</v>
+        <v>34.47</v>
       </c>
       <c r="F228" s="4" t="n">
-        <v>39.95</v>
+        <v>28.94</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>KANSAINER</t>
+          <t>CRAMC</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -7744,22 +7930,22 @@
         </is>
       </c>
       <c r="C229" s="4" t="n">
-        <v>183.96</v>
+        <v>230.45</v>
       </c>
       <c r="D229" s="4" t="n">
-        <v>29.68</v>
+        <v>34.58</v>
       </c>
       <c r="E229" s="4" t="n">
-        <v>38.06</v>
+        <v>36.63</v>
       </c>
       <c r="F229" s="4" t="n">
-        <v>37.17</v>
+        <v/>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>SWSOLAR</t>
+          <t>AVANTIFEED</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -7768,22 +7954,22 @@
         </is>
       </c>
       <c r="C230" s="4" t="n">
-        <v>176.06</v>
+        <v>753.15</v>
       </c>
       <c r="D230" s="4" t="n">
-        <v>29.63</v>
+        <v>33.96</v>
       </c>
       <c r="E230" s="4" t="n">
-        <v>37.36</v>
+        <v>32.62</v>
       </c>
       <c r="F230" s="4" t="n">
-        <v>38.92</v>
+        <v>47.54</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>TANLA</t>
+          <t>CENTURYPLY</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -7792,22 +7978,22 @@
         </is>
       </c>
       <c r="C231" s="4" t="n">
-        <v>489.25</v>
+        <v>694.45</v>
       </c>
       <c r="D231" s="4" t="n">
-        <v>29.62</v>
+        <v>33.71</v>
       </c>
       <c r="E231" s="4" t="n">
-        <v>41.5</v>
+        <v>36.41</v>
       </c>
       <c r="F231" s="4" t="n">
-        <v>43.02</v>
+        <v>46.26</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>RCF</t>
+          <t>VMART</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -7816,22 +8002,22 @@
         </is>
       </c>
       <c r="C232" s="4" t="n">
-        <v>108.5</v>
+        <v>760.1</v>
       </c>
       <c r="D232" s="4" t="n">
-        <v>29.45</v>
+        <v>33.15</v>
       </c>
       <c r="E232" s="4" t="n">
-        <v>34.23</v>
+        <v>52.2</v>
       </c>
       <c r="F232" s="4" t="n">
-        <v>41.61</v>
+        <v>51.83</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>CELLO</t>
+          <t>AHLUCONT</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -7840,22 +8026,22 @@
         </is>
       </c>
       <c r="C233" s="4" t="n">
-        <v>322.45</v>
+        <v>585.55</v>
       </c>
       <c r="D233" s="4" t="n">
-        <v>29.41</v>
+        <v>32.82</v>
       </c>
       <c r="E233" s="4" t="n">
-        <v>30.07</v>
+        <v>26.76</v>
       </c>
       <c r="F233" s="4" t="n">
-        <v>27.55</v>
+        <v>39.55</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>SUBROS</t>
+          <t>VAIBHAVGBL</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -7864,22 +8050,22 @@
         </is>
       </c>
       <c r="C234" s="4" t="n">
-        <v>678</v>
+        <v>206.38</v>
       </c>
       <c r="D234" s="4" t="n">
-        <v>29.23</v>
+        <v>32.35</v>
       </c>
       <c r="E234" s="4" t="n">
-        <v>43.72</v>
+        <v>40.87</v>
       </c>
       <c r="F234" s="4" t="n">
-        <v>49.41</v>
+        <v>43.68</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>SANOFICONR</t>
+          <t>RALLIS</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -7888,22 +8074,22 @@
         </is>
       </c>
       <c r="C235" s="4" t="n">
-        <v>3989.5</v>
+        <v>200.38</v>
       </c>
       <c r="D235" s="4" t="n">
-        <v>28.74</v>
+        <v>32.16</v>
       </c>
       <c r="E235" s="4" t="n">
-        <v>35.56</v>
+        <v>30.65</v>
       </c>
       <c r="F235" s="4" t="n">
-        <v>39.03</v>
+        <v>40.81</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>TRANSRAILL</t>
+          <t>CAMPUS</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -7912,22 +8098,22 @@
         </is>
       </c>
       <c r="C236" s="4" t="n">
-        <v>408.75</v>
+        <v>209.99</v>
       </c>
       <c r="D236" s="4" t="n">
-        <v>28.64</v>
+        <v>31.73</v>
       </c>
       <c r="E236" s="4" t="n">
-        <v>31.97</v>
+        <v>36.27</v>
       </c>
       <c r="F236" s="4" t="n">
-        <v>39.43</v>
+        <v>39.42</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>KITEX</t>
+          <t>CERA</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -7936,22 +8122,22 @@
         </is>
       </c>
       <c r="C237" s="4" t="n">
-        <v>118.58</v>
+        <v>5396.5</v>
       </c>
       <c r="D237" s="4" t="n">
-        <v>27.87</v>
+        <v>31.11</v>
       </c>
       <c r="E237" s="4" t="n">
-        <v>31.41</v>
+        <v>42.48</v>
       </c>
       <c r="F237" s="4" t="n">
-        <v>42.09</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>EUREKAFORB</t>
+          <t>ALOKINDS</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -7960,22 +8146,22 @@
         </is>
       </c>
       <c r="C238" s="4" t="n">
-        <v>385.3</v>
+        <v>7.5</v>
       </c>
       <c r="D238" s="4" t="n">
-        <v>27.84</v>
+        <v>31</v>
       </c>
       <c r="E238" s="4" t="n">
-        <v>33.27</v>
+        <v>23.77</v>
       </c>
       <c r="F238" s="4" t="n">
-        <v>35.67</v>
+        <v>29.88</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>DBREALTY</t>
+          <t>BORORENEW</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -7984,22 +8170,22 @@
         </is>
       </c>
       <c r="C239" s="4" t="n">
-        <v>95.68000000000001</v>
+        <v>455.15</v>
       </c>
       <c r="D239" s="4" t="n">
-        <v>27.68</v>
+        <v>30.88</v>
       </c>
       <c r="E239" s="4" t="n">
-        <v>38.12</v>
+        <v>37.66</v>
       </c>
       <c r="F239" s="4" t="n">
-        <v>41.38</v>
+        <v>45.74</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>BORORENEW</t>
+          <t>ASHAPURMIN</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -8008,22 +8194,22 @@
         </is>
       </c>
       <c r="C240" s="4" t="n">
-        <v>459.5</v>
+        <v>506.5</v>
       </c>
       <c r="D240" s="4" t="n">
-        <v>27.59</v>
+        <v>30.78</v>
       </c>
       <c r="E240" s="4" t="n">
-        <v>38.19</v>
+        <v>35.77</v>
       </c>
       <c r="F240" s="4" t="n">
-        <v>46.01</v>
+        <v>49.29</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>HAPPSTMNDS</t>
+          <t>KANSAINER</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -8032,22 +8218,22 @@
         </is>
       </c>
       <c r="C241" s="4" t="n">
-        <v>321.55</v>
+        <v>180.63</v>
       </c>
       <c r="D241" s="4" t="n">
-        <v>27.48</v>
+        <v>30.74</v>
       </c>
       <c r="E241" s="4" t="n">
-        <v>37.08</v>
+        <v>36.51</v>
       </c>
       <c r="F241" s="4" t="n">
-        <v>29.19</v>
+        <v>36.52</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>ASHAPURMIN</t>
+          <t>VGUARD</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -8056,22 +8242,22 @@
         </is>
       </c>
       <c r="C242" s="4" t="n">
-        <v>515.7</v>
+        <v>304.35</v>
       </c>
       <c r="D242" s="4" t="n">
-        <v>26.89</v>
+        <v>30.54</v>
       </c>
       <c r="E242" s="4" t="n">
-        <v>37.33</v>
+        <v>42.65</v>
       </c>
       <c r="F242" s="4" t="n">
-        <v>50.02</v>
+        <v>44.17</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>WAAREERTL</t>
+          <t>EQUITASBNK</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -8080,22 +8266,22 @@
         </is>
       </c>
       <c r="C243" s="4" t="n">
-        <v>811.05</v>
+        <v>67.03</v>
       </c>
       <c r="D243" s="4" t="n">
-        <v>26.27</v>
+        <v>30.26</v>
       </c>
       <c r="E243" s="4" t="n">
-        <v>34.44</v>
+        <v>42.89</v>
       </c>
       <c r="F243" s="4" t="n">
-        <v>38.94</v>
+        <v>49.34</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>ANUP</t>
+          <t>GOKEX</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -8104,22 +8290,22 @@
         </is>
       </c>
       <c r="C244" s="4" t="n">
-        <v>1638.3</v>
+        <v>689.6</v>
       </c>
       <c r="D244" s="4" t="n">
-        <v>25.89</v>
+        <v>29.68</v>
       </c>
       <c r="E244" s="4" t="n">
-        <v>35.77</v>
+        <v>40.79</v>
       </c>
       <c r="F244" s="4" t="n">
-        <v>43.49</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>RTNINDIA</t>
+          <t>SANOFICONR</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
@@ -8128,22 +8314,22 @@
         </is>
       </c>
       <c r="C245" s="4" t="n">
-        <v>26.37</v>
+        <v>3945.3</v>
       </c>
       <c r="D245" s="4" t="n">
-        <v>23.44</v>
+        <v>29.59</v>
       </c>
       <c r="E245" s="4" t="n">
-        <v>31.81</v>
+        <v>33.39</v>
       </c>
       <c r="F245" s="4" t="n">
-        <v>37.18</v>
+        <v>37.81</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>HGINFRA</t>
+          <t>RTNPOWER</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -8152,22 +8338,22 @@
         </is>
       </c>
       <c r="C246" s="4" t="n">
-        <v>442.45</v>
+        <v>7</v>
       </c>
       <c r="D246" s="4" t="n">
-        <v>22.38</v>
+        <v>28.82</v>
       </c>
       <c r="E246" s="4" t="n">
-        <v>27.6</v>
+        <v>27.9</v>
       </c>
       <c r="F246" s="4" t="n">
-        <v>32.53</v>
+        <v>40.35</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>AHLUCONT</t>
+          <t>RELAXO</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -8176,22 +8362,22 @@
         </is>
       </c>
       <c r="C247" s="4" t="n">
-        <v>569.3</v>
+        <v>297</v>
       </c>
       <c r="D247" s="4" t="n">
-        <v>21.47</v>
+        <v>28.24</v>
       </c>
       <c r="E247" s="4" t="n">
-        <v>26.47</v>
+        <v>38.79</v>
       </c>
       <c r="F247" s="4" t="n">
-        <v>39.5</v>
+        <v>33.27</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>KPIGREEN</t>
+          <t>INDIAGLYCO</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -8200,22 +8386,22 @@
         </is>
       </c>
       <c r="C248" s="4" t="n">
-        <v>276.35</v>
+        <v>309.9</v>
       </c>
       <c r="D248" s="4" t="n">
-        <v>19.74</v>
+        <v>27.96</v>
       </c>
       <c r="E248" s="4" t="n">
-        <v>26.81</v>
+        <v>27.3</v>
       </c>
       <c r="F248" s="4" t="n">
-        <v>40.52</v>
+        <v>36.22</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>INDIAGLYCO</t>
+          <t>HAPPSTMNDS</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
@@ -8224,22 +8410,22 @@
         </is>
       </c>
       <c r="C249" s="4" t="n">
-        <v>263.7</v>
+        <v>310.5</v>
       </c>
       <c r="D249" s="4" t="n">
-        <v>17.58</v>
+        <v>26.38</v>
       </c>
       <c r="E249" s="4" t="n">
-        <v>24.56</v>
+        <v>35.44</v>
       </c>
       <c r="F249" s="4" t="n">
-        <v>35.36</v>
+        <v>28.56</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>PNCINFRA</t>
+          <t>JLHL</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -8248,22 +8434,22 @@
         </is>
       </c>
       <c r="C250" s="4" t="n">
-        <v>139.55</v>
+        <v>265.65</v>
       </c>
       <c r="D250" s="4" t="n">
-        <v>17.05</v>
+        <v>23.71</v>
       </c>
       <c r="E250" s="4" t="n">
-        <v>25.26</v>
+        <v>40.85</v>
       </c>
       <c r="F250" s="4" t="n">
-        <v>34.18</v>
+        <v>47.92</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>RELAXO</t>
+          <t>EUREKAFORB</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
@@ -8272,22 +8458,22 @@
         </is>
       </c>
       <c r="C251" s="4" t="n">
-        <v>291.25</v>
+        <v>370.85</v>
       </c>
       <c r="D251" s="4" t="n">
-        <v>16.55</v>
+        <v>23</v>
       </c>
       <c r="E251" s="4" t="n">
-        <v>37.43</v>
+        <v>31.12</v>
       </c>
       <c r="F251" s="4" t="n">
-        <v>32.93</v>
+        <v>34.64</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>ALOKINDS</t>
+          <t>PNCINFRA</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
@@ -8296,16 +8482,16 @@
         </is>
       </c>
       <c r="C252" s="4" t="n">
-        <v>7.05</v>
+        <v>135.45</v>
       </c>
       <c r="D252" s="4" t="n">
-        <v>14.08</v>
+        <v>17.6</v>
       </c>
       <c r="E252" s="4" t="n">
-        <v>19.32</v>
+        <v>24.78</v>
       </c>
       <c r="F252" s="4" t="n">
-        <v>29.28</v>
+        <v>33.95</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Micro250_stocks.xlsx
+++ b/docs/Micro250_stocks.xlsx
@@ -43,7 +43,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +53,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -94,6 +99,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -461,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L48"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -537,7 +551,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>GMMPFAUDLR</t>
+          <t>AXISCADES</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -546,37 +560,37 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>1505.2</v>
+        <v>2307.3</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>78.79000000000001</v>
+        <v>78.14</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>82.36</v>
+        <v>71.47</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>60.84</v>
+        <v>70.70999999999999</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>69.29000000000001</v>
+        <v>30.03</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1007.12</v>
+        <v>1688.43</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>1006.14</v>
+        <v>1638.95</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>428110</v>
+        <v>260846</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>6767</v>
+        <v>9833</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>SANSERA</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -585,37 +599,37 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>4662.4</v>
+        <v>955.35</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>74.58</v>
+        <v>71.81</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>85.7</v>
+        <v>78.17</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>87.63</v>
+        <v>89.70999999999999</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>34.71</v>
+        <v>23.49</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>3157.29</v>
+        <v>547.64</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>2924.09</v>
+        <v>483.82</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>218163</v>
+        <v>1792855</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>29102</v>
+        <v>49110</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>OPTIEMUS</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -624,37 +638,37 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>630.3</v>
+        <v>803.7</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>73.63</v>
+        <v>67.98</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>74.2</v>
+        <v>76.31</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>61.84</v>
+        <v>64.28</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>33.51</v>
+        <v>40.07</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>514.15</v>
+        <v>543.85</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>506.52</v>
+        <v>534.73</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>1072684</v>
+        <v>1122893</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>9262</v>
+        <v>7267</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENGG</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -663,37 +677,37 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>98.56</v>
+        <v>968.5</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>71.84999999999999</v>
+        <v>67.66</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>69.14</v>
+        <v>71.58</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>67.59999999999999</v>
+        <v>64.11</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>28.92</v>
+        <v>28.78</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>76.59999999999999</v>
+        <v>768.5599999999999</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>73.67</v>
+        <v>760.75</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>7847222</v>
+        <v>713151</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>15272</v>
+        <v>8887</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>GMMPFAUDLR</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -702,37 +716,37 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>939.55</v>
+        <v>1443.4</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>70.19</v>
+        <v>67.37</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>69.13</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>63.01</v>
+        <v>59.23</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>26.04</v>
+        <v>67.05</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>758.5</v>
+        <v>1030.95</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>752.98</v>
+        <v>1024.02</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>662759</v>
+        <v>443563</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>8520</v>
+        <v>6510</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>SOUTHBANK</t>
+          <t>CUPID</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -741,37 +755,37 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>49.95</v>
+        <v>312.5</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>70.05</v>
+        <v>67.16</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>66.84</v>
+        <v>82.45999999999999</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>73.27</v>
+        <v>93.91</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>21.92</v>
+        <v>23.08</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>43.3</v>
+        <v>198.15</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>41.94</v>
+        <v>175.93</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>10650999</v>
+        <v>19648932</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>13084</v>
+        <v>41927</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>SHILPAMED</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -780,37 +794,37 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1767</v>
+        <v>1064.1</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>69.08</v>
+        <v>67.14</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>73.64</v>
+        <v>91.48</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>81.54000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>23.68</v>
+        <v>35.76</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1358.73</v>
+        <v>671.72</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1284.11</v>
+        <v>618.11</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>249954</v>
+        <v>1150119</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>23453</v>
+        <v>20810</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>YATHARTH</t>
+          <t>LLOYDSENGG</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -819,37 +833,37 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1121.4</v>
+        <v>98.31</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>68.64</v>
+        <v>64.08</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>73.23999999999999</v>
+        <v>68.73</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>71.8</v>
+        <v>67.39</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>52.92</v>
+        <v>31.4</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>854.05</v>
+        <v>77.75</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>822.49</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>742684</v>
+        <v>10180605</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>10805</v>
+        <v>15224</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>OPTIEMUS</t>
+          <t>EMIL</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -858,37 +872,37 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>758.55</v>
+        <v>204.05</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>68.44</v>
+        <v>63.59</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>73.92</v>
+        <v>75.14</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>62.7</v>
+        <v>64.03</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>33.67</v>
+        <v>30.99</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>530.26</v>
+        <v>147.16</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>524.86</v>
+        <v>142.09</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>965965</v>
+        <v>3275903</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>6840</v>
+        <v>7849</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>PGIL</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -897,37 +911,37 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1329.1</v>
+        <v>384.7</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>66.43000000000001</v>
+        <v>62.74</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>72.04000000000001</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>78.18000000000001</v>
+        <v>68.11</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>29.15</v>
+        <v>22.38</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>987.4400000000001</v>
+        <v>318.88</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>940.78</v>
+        <v>309.75</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>203871</v>
+        <v>1721789</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>12278</v>
+        <v>14807</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SMLMAH</t>
+          <t>GPPL</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -936,37 +950,37 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>6825.5</v>
+        <v>165.88</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>65.77</v>
+        <v>60.37</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>71.31999999999999</v>
+        <v>62.75</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>72.08</v>
+        <v>55.57</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>37.53</v>
+        <v>24.68</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>4699.92</v>
+        <v>155.69</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>4445.58</v>
+        <v>155.68</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>103085</v>
+        <v>1744222</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>9878</v>
+        <v>8023</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>SUPRIYA</t>
+          <t>AKUMS</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -975,37 +989,37 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>985.2</v>
+        <v>813.1</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>65.34</v>
+        <v>59.91</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>64.27</v>
+        <v>76.51000000000001</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>62.91</v>
+        <v>67.16</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>24.9</v>
+        <v>39.93</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>820.14</v>
+        <v>650.3099999999999</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>800.3099999999999</v>
+        <v>624.54</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>302959</v>
+        <v>316640</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>7929</v>
+        <v>12490</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>AKUMS</t>
+          <t>QPOWER</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1014,37 +1028,37 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>819.55</v>
+        <v>1564.6</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>65.13</v>
+        <v>59.59</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>77.47</v>
+        <v>67.22</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>67.86</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>41.81</v>
+        <v>21.27</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>641.39</v>
+        <v>1203.08</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>616.79</v>
+        <v>1135.16</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>343458</v>
+        <v>328136</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>12547</v>
+        <v>12043</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>EMIL</t>
+          <t>NEOGEN</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1053,37 +1067,37 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>200.22</v>
+        <v>2407.1</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>64.93000000000001</v>
+        <v>57.42</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>74.25</v>
+        <v>67.58</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>63.63</v>
+        <v>65.7</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>27.99</v>
+        <v>23.6</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>144.34</v>
+        <v>1956.96</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>139.74</v>
+        <v>1877.55</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2705090</v>
+        <v>189624</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>7703</v>
+        <v>7240</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>SHAREINDIA</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1092,37 +1106,37 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>587.55</v>
+        <v>205.09</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>63.7</v>
+        <v>57.31</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>67.47</v>
+        <v>63.36</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>68.3</v>
+        <v>53.94</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>23.07</v>
+        <v>43.71</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>484.14</v>
+        <v>168.15</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>472.62</v>
+        <v>166.57</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>788942</v>
+        <v>5976567</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>14420</v>
+        <v>4525</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>MAHSEAMLES</t>
+          <t>PGIL</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1131,37 +1145,37 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>715.65</v>
+        <v>1263</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>63.48</v>
+        <v>56.98</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>71.15000000000001</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>59.13</v>
+        <v>75.73</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>44.41</v>
+        <v>31.75</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>617.75</v>
+        <v>1002.77</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>612.58</v>
+        <v>954.16</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>398172</v>
+        <v>208132</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>9590</v>
+        <v>11787</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>AZAD</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1170,37 +1184,37 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>338.15</v>
+        <v>2860.9</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>63.19</v>
+        <v>56.14</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>72.39</v>
+        <v>66.73</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>77.23999999999999</v>
+        <v>70.97</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>33.68</v>
+        <v>21.9</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>273.01</v>
+        <v>2314.98</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>260.79</v>
+        <v>2202.92</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>2461869</v>
+        <v>747122</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>12688</v>
+        <v>18425</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>SHILPAMED</t>
+          <t>EDELWEISS</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1209,37 +1223,37 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1013.45</v>
+        <v>137.9</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>62.37</v>
+        <v>56</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>90.43000000000001</v>
+        <v>65.09</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>85.34</v>
+        <v>63.38</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>39.26</v>
+        <v>22.39</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>651.12</v>
+        <v>120.63</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>600.6799999999999</v>
+        <v>118.52</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1135089</v>
+        <v>9027923</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>19821</v>
+        <v>12996</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>SHAREINDIA</t>
+          <t>SKYGOLD</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1248,37 +1262,37 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>209.62</v>
+        <v>810.65</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>61.93</v>
+        <v>55.8</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>64.64</v>
+        <v>72.55</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>54.67</v>
+        <v>81.83</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>46.4</v>
+        <v>20.25</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>166.14</v>
+        <v>612.55</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>165.14</v>
+        <v>567.54</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>5901959</v>
+        <v>832298</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>4587</v>
+        <v>12498</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>ENTERO</t>
+          <t>SANSERA</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1287,37 +1301,37 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1821.8</v>
+        <v>4276.6</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>61.28</v>
+        <v>53.13</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>73.29000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>73.61</v>
+        <v>80.55</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>40.76</v>
+        <v>28.83</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1365.72</v>
+        <v>3222.1</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1324.39</v>
+        <v>2981.58</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>373870</v>
+        <v>264491</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>7929</v>
+        <v>26582</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>MAHSEAMLES</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1326,37 +1340,37 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>374.55</v>
+        <v>698.75</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>61</v>
+        <v>53.02</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>74</v>
+        <v>64.87</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>68.36</v>
+        <v>56.9</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>21.88</v>
+        <v>41.11</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>314.36</v>
+        <v>622.9400000000001</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>305.95</v>
+        <v>616.62</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1631213</v>
+        <v>471878</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>14482</v>
+        <v>9317</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1365,37 +1379,37 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>837.2</v>
+        <v>589.15</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>59.92</v>
+        <v>52.47</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>73.72</v>
+        <v>62.19</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>88.06</v>
+        <v>58.18</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>23.74</v>
+        <v>31.27</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>528.89</v>
+        <v>518.95</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>467.26</v>
+        <v>510.5</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1581493</v>
+        <v>1016302</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>43037</v>
+        <v>8614</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>STAR</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1404,37 +1418,37 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1184.9</v>
+        <v>1670</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>59.23</v>
+        <v>52.09</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>63.27</v>
+        <v>64.78</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>63.09</v>
+        <v>78.15000000000001</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>27.75</v>
+        <v>23.81</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1041.13</v>
+        <v>1377.18</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1020.69</v>
+        <v>1300.93</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>495677</v>
+        <v>278799</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>10922</v>
+        <v>22059</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>ALIVUS</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1443,37 +1457,37 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>336.95</v>
+        <v>1374.2</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>58.11</v>
+        <v>51.63</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>72.61</v>
+        <v>68.88</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>68.34</v>
+        <v>71.58</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>27.48</v>
+        <v>20.48</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>261.64</v>
+        <v>1186.46</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>250.64</v>
+        <v>1148.59</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2609409</v>
+        <v>168329</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>15269</v>
+        <v>16942</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>NEOGEN</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1482,37 +1496,37 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2385.2</v>
+        <v>2280.2</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>57.62</v>
+        <v>50.97</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>66.91</v>
+        <v>69.23</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>66.06999999999999</v>
+        <v>79.27</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>25.37</v>
+        <v>22.05</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1931.56</v>
+        <v>1733.33</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1855.89</v>
+        <v>1603.32</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>236962</v>
+        <v>627475</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>7166</v>
+        <v>15196</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>EDELWEISS</t>
+          <t>ICIL</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1521,37 +1535,37 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>136.83</v>
+        <v>443.65</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>57.47</v>
+        <v>50.88</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>64.79000000000001</v>
+        <v>64.28</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>64.28</v>
+        <v>62.72</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>24.7</v>
+        <v>23.49</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>119.65</v>
+        <v>376.03</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>117.71</v>
+        <v>360.37</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>8717093</v>
+        <v>657786</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>12951</v>
+        <v>8809</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>MSTCLTD</t>
+          <t>YATHARTH</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1560,37 +1574,37 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>740.8</v>
+        <v>1033.7</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>57.11</v>
+        <v>50.55</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>67.63</v>
+        <v>63.06</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>61.39</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>25.7</v>
+        <v>46.32</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>596.88</v>
+        <v>865.16</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>576.22</v>
+        <v>832.0599999999999</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>398566</v>
+        <v>784897</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>5215</v>
+        <v>9973</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1599,37 +1613,37 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>645.15</v>
+        <v>325.6</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>56.44</v>
+        <v>50.09</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>71.65000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>69.3</v>
+        <v>67.3</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>40.97</v>
+        <v>22.56</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>529.74</v>
+        <v>265.19</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>515.08</v>
+        <v>253.64</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>311417</v>
+        <v>2319541</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>12719</v>
+        <v>14639</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>LUMAXTECH</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1638,37 +1652,37 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2026.8</v>
+        <v>321.6</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>54.18</v>
+        <v>49.28</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>63.71</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>70.51000000000001</v>
+        <v>73.56</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>29.7</v>
+        <v>28.99</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1707.18</v>
+        <v>276.45</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>1634.57</v>
+        <v>263.97</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>144525</v>
+        <v>2114776</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>13814</v>
+        <v>12249</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>WELENT</t>
+          <t>LUMAXTECH</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1677,37 +1691,37 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>754.5</v>
+        <v>1978.9</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>53.8</v>
+        <v>48.81</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>65.95</v>
+        <v>60.35</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>69.83</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>42.07</v>
+        <v>28.04</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>602.79</v>
+        <v>1723.65</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>583.4299999999999</v>
+        <v>1649.78</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>945363</v>
+        <v>146626</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>10232</v>
+        <v>13420</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>VARROC</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1716,37 +1730,37 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2316.1</v>
+        <v>830.6</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>53.55</v>
+        <v>48.69</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>72.41</v>
+        <v>69.01000000000001</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>81.26000000000001</v>
+        <v>67.42</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>28.17</v>
+        <v>27.89</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1694.13</v>
+        <v>696.85</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>1567.85</v>
+        <v>671.16</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>663733</v>
+        <v>340192</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>15574</v>
+        <v>12667</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>MANORAMA</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1755,37 +1769,37 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>751.55</v>
+        <v>1880.3</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>52.58</v>
+        <v>47.37</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>65.06999999999999</v>
+        <v>62.98</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>76.42</v>
+        <v>69.37</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>20.84</v>
+        <v>24.3</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>602.4299999999999</v>
+        <v>1646.98</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>562.09</v>
+        <v>1589.8</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>2181779</v>
+        <v>219058</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>23577</v>
+        <v>11930</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>ICIL</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1794,37 +1808,37 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>445.75</v>
+        <v>618.15</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>52.12</v>
+        <v>47.17</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>64.55</v>
+        <v>64.5</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>63.13</v>
+        <v>65.54000000000001</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>23.34</v>
+        <v>35.92</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>372.29</v>
+        <v>534.98</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>357.05</v>
+        <v>519.33</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>1558203</v>
+        <v>322794</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>8828</v>
+        <v>12183</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>SUDARSCHEM</t>
+          <t>WELENT</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1833,37 +1847,37 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1218.9</v>
+        <v>724.45</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>51.82</v>
+        <v>46.89</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>63.92</v>
+        <v>61.14</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>59.32</v>
+        <v>67.26000000000001</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>22.48</v>
+        <v>34.58</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1053.07</v>
+        <v>609.9</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>1042.99</v>
+        <v>589.46</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>385630</v>
+        <v>964948</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>9704</v>
+        <v>9778</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>JKPAPER</t>
+          <t>DIACABS</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1872,37 +1886,37 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>408.45</v>
+        <v>345</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>51.1</v>
+        <v>46.53</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>60.09</v>
+        <v>70.70999999999999</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>56.37</v>
+        <v>78.53</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>38.33</v>
+        <v>23.26</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>376.29</v>
+        <v>261.9</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>372.92</v>
+        <v>240.7</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>532452</v>
+        <v>908428</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>7406</v>
+        <v>20891</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>VARROC</t>
+          <t>TMB</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1911,37 +1925,37 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>834.85</v>
+        <v>872.05</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>50.54</v>
+        <v>45.96</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>70.23</v>
+        <v>65.34</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>68.08</v>
+        <v>71.67</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>30.88</v>
+        <v>23.08</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>688.74</v>
+        <v>772.58</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>664</v>
+        <v>733.42</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>341771</v>
+        <v>166317</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>12756</v>
+        <v>14014</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>AZAD</t>
+          <t>ENTERO</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1950,37 +1964,37 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>2728</v>
+        <v>1680.8</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>50.41</v>
+        <v>45.88</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>63.71</v>
+        <v>63.11</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>69.18000000000001</v>
+        <v>66.56999999999999</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>22.37</v>
+        <v>33</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>2284.88</v>
+        <v>1385.02</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>2176.35</v>
+        <v>1340.97</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>462028</v>
+        <v>382846</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>17618</v>
+        <v>7290</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>DIACABS</t>
+          <t>RBA</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1989,382 +2003,31 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>354.5</v>
+        <v>92.22</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>49.84</v>
+        <v>45.29</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>72.61</v>
+        <v>61.01</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>80.98</v>
+        <v>55.67</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>29.83</v>
+        <v>24.99</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>257.2</v>
+        <v>80.8</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>236.33</v>
+        <v>78.81999999999999</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>932077</v>
+        <v>3388589</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>21202</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>CUPID</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="n">
-        <v>270</v>
-      </c>
-      <c r="D40" s="4" t="n">
-        <v>49.81</v>
-      </c>
-      <c r="E40" s="4" t="n">
-        <v>76.61</v>
-      </c>
-      <c r="F40" s="4" t="n">
-        <v>88.87</v>
-      </c>
-      <c r="G40" s="4" t="n">
-        <v>24.29</v>
-      </c>
-      <c r="H40" s="4" t="n">
-        <v>192.88</v>
-      </c>
-      <c r="I40" s="4" t="n">
-        <v>171.1</v>
-      </c>
-      <c r="J40" s="4" t="n">
-        <v>21185753</v>
-      </c>
-      <c r="K40" s="4" t="n">
-        <v>36306</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>ALIVUS</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="n">
-        <v>1365.6</v>
-      </c>
-      <c r="D41" s="4" t="n">
-        <v>49.77</v>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>67.95</v>
-      </c>
-      <c r="F41" s="4" t="n">
-        <v>70.94</v>
-      </c>
-      <c r="G41" s="4" t="n">
-        <v>25.17</v>
-      </c>
-      <c r="H41" s="4" t="n">
-        <v>1176.64</v>
-      </c>
-      <c r="I41" s="4" t="n">
-        <v>1139.31</v>
-      </c>
-      <c r="J41" s="4" t="n">
-        <v>160603</v>
-      </c>
-      <c r="K41" s="4" t="n">
-        <v>16766</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>SKYGOLD</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>782.7</v>
-      </c>
-      <c r="D42" s="4" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>71.62</v>
-      </c>
-      <c r="F42" s="4" t="n">
-        <v>80.15000000000001</v>
-      </c>
-      <c r="G42" s="4" t="n">
-        <v>22.06</v>
-      </c>
-      <c r="H42" s="4" t="n">
-        <v>599.15</v>
-      </c>
-      <c r="I42" s="4" t="n">
-        <v>555.1900000000001</v>
-      </c>
-      <c r="J42" s="4" t="n">
-        <v>772881</v>
-      </c>
-      <c r="K42" s="4" t="n">
-        <v>12290</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>DCBBANK</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="n">
-        <v>214.09</v>
-      </c>
-      <c r="D43" s="4" t="n">
-        <v>48.97</v>
-      </c>
-      <c r="E43" s="4" t="n">
-        <v>63.16</v>
-      </c>
-      <c r="F43" s="4" t="n">
-        <v>65.14</v>
-      </c>
-      <c r="G43" s="4" t="n">
-        <v>31.39</v>
-      </c>
-      <c r="H43" s="4" t="n">
-        <v>191.41</v>
-      </c>
-      <c r="I43" s="4" t="n">
-        <v>185.69</v>
-      </c>
-      <c r="J43" s="4" t="n">
-        <v>2647843</v>
-      </c>
-      <c r="K43" s="4" t="n">
-        <v>6898</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>TMB</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="n">
-        <v>881.9</v>
-      </c>
-      <c r="D44" s="4" t="n">
-        <v>47.37</v>
-      </c>
-      <c r="E44" s="4" t="n">
-        <v>65.01000000000001</v>
-      </c>
-      <c r="F44" s="4" t="n">
-        <v>72.77</v>
-      </c>
-      <c r="G44" s="4" t="n">
-        <v>24.78</v>
-      </c>
-      <c r="H44" s="4" t="n">
-        <v>767.42</v>
-      </c>
-      <c r="I44" s="4" t="n">
-        <v>728.0700000000001</v>
-      </c>
-      <c r="J44" s="4" t="n">
-        <v>162469</v>
-      </c>
-      <c r="K44" s="4" t="n">
-        <v>13965</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>QUESS</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="n">
-        <v>340.9</v>
-      </c>
-      <c r="D45" s="4" t="n">
-        <v>45.82</v>
-      </c>
-      <c r="E45" s="4" t="n">
-        <v>65.91</v>
-      </c>
-      <c r="F45" s="4" t="n">
-        <v>50.41</v>
-      </c>
-      <c r="G45" s="4" t="n">
-        <v>24.23</v>
-      </c>
-      <c r="H45" s="4" t="n">
-        <v>284.67</v>
-      </c>
-      <c r="I45" s="4" t="n">
-        <v>281.01</v>
-      </c>
-      <c r="J45" s="4" t="n">
-        <v>754925</v>
-      </c>
-      <c r="K45" s="4" t="n">
-        <v>5093</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>MANORAMA</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="n">
-        <v>1872.8</v>
-      </c>
-      <c r="D46" s="4" t="n">
-        <v>45.67</v>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>62.25</v>
-      </c>
-      <c r="F46" s="4" t="n">
-        <v>69.67</v>
-      </c>
-      <c r="G46" s="4" t="n">
-        <v>30.08</v>
-      </c>
-      <c r="H46" s="4" t="n">
-        <v>1635.02</v>
-      </c>
-      <c r="I46" s="4" t="n">
-        <v>1578.56</v>
-      </c>
-      <c r="J46" s="4" t="n">
-        <v>527008</v>
-      </c>
-      <c r="K46" s="4" t="n">
-        <v>11822</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>SHAILY</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="n">
-        <v>3142.3</v>
-      </c>
-      <c r="D47" s="4" t="n">
-        <v>45.15</v>
-      </c>
-      <c r="E47" s="4" t="n">
-        <v>60.39</v>
-      </c>
-      <c r="F47" s="4" t="n">
-        <v>70.16</v>
-      </c>
-      <c r="G47" s="4" t="n">
-        <v>20.15</v>
-      </c>
-      <c r="H47" s="4" t="n">
-        <v>2842.25</v>
-      </c>
-      <c r="I47" s="4" t="n">
-        <v>2716.22</v>
-      </c>
-      <c r="J47" s="4" t="n">
-        <v>143709</v>
-      </c>
-      <c r="K47" s="4" t="n">
-        <v>14453</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>RBA</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="n">
-        <v>92.51000000000001</v>
-      </c>
-      <c r="D48" s="4" t="n">
-        <v>45.13</v>
-      </c>
-      <c r="E48" s="4" t="n">
-        <v>61.66</v>
-      </c>
-      <c r="F48" s="4" t="n">
-        <v>55.87</v>
-      </c>
-      <c r="G48" s="4" t="n">
-        <v>28.92</v>
-      </c>
-      <c r="H48" s="4" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="I48" s="4" t="n">
-        <v>78.31</v>
-      </c>
-      <c r="J48" s="4" t="n">
-        <v>4471295</v>
-      </c>
-      <c r="K48" s="4" t="n">
-        <v>6587</v>
+        <v>6552</v>
       </c>
     </row>
   </sheetData>
@@ -2407,15 +2070,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId47"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2473,7 +2127,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>GMMPFAUDLR</t>
+          <t>DYNAMATECH</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2482,22 +2136,22 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>1505.2</v>
+        <v>13756</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>78.79000000000001</v>
+        <v>79.88</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>82.36</v>
+        <v>71.03</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>60.84</v>
+        <v>73.40000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>GREAVESCOT</t>
+          <t>AXISCADES</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2506,22 +2160,22 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>234.78</v>
+        <v>2307.3</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>77.84</v>
+        <v>78.14</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>62.63</v>
+        <v>71.47</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>57.45</v>
+        <v>70.70999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>DYNAMATECH</t>
+          <t>AEQUS</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2530,22 +2184,22 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>13153</v>
+        <v>275.05</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>76.09999999999999</v>
+        <v>72.36</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>67.98</v>
+        <v>69.36</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>71.89</v>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>CAPILLARY</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2554,22 +2208,22 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>599.45</v>
+        <v>955.35</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>75.54000000000001</v>
+        <v>71.81</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>61.09</v>
+        <v>78.17</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v/>
+        <v>89.70999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SANSERA</t>
+          <t>LOTUSDEV</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2578,22 +2232,22 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>4662.4</v>
+        <v>230.07</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>74.58</v>
+        <v>69.62</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>85.7</v>
+        <v>72.91</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>87.63</v>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>OPTIEMUS</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2602,22 +2256,22 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>630.3</v>
+        <v>803.7</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>73.63</v>
+        <v>67.98</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>74.2</v>
+        <v>76.31</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>61.84</v>
+        <v>64.28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENGG</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2626,22 +2280,22 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>98.56</v>
+        <v>968.5</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>71.84999999999999</v>
+        <v>67.66</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>69.14</v>
+        <v>71.58</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>67.59999999999999</v>
+        <v>64.11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>GMMPFAUDLR</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2650,22 +2304,22 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>939.55</v>
+        <v>1443.4</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>70.19</v>
+        <v>67.37</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>69.13</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>63.01</v>
+        <v>59.23</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>SOUTHBANK</t>
+          <t>CUPID</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2674,22 +2328,22 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>49.95</v>
+        <v>312.5</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>70.05</v>
+        <v>67.16</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>66.84</v>
+        <v>82.45999999999999</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>73.27</v>
+        <v>93.91</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>SHILPAMED</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2698,22 +2352,22 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1767</v>
+        <v>1064.1</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>69.08</v>
+        <v>67.14</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>73.64</v>
+        <v>91.48</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>81.54000000000001</v>
+        <v>86.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>YATHARTH</t>
+          <t>GREAVESCOT</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2722,22 +2376,22 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1121.4</v>
+        <v>225.98</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>68.64</v>
+        <v>64.31999999999999</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>73.23999999999999</v>
+        <v>58.32</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>71.8</v>
+        <v>56.06</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>OPTIEMUS</t>
+          <t>LLOYDSENGG</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -2746,22 +2400,22 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>758.55</v>
+        <v>98.31</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>68.44</v>
+        <v>64.08</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>73.92</v>
+        <v>68.73</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>62.7</v>
+        <v>67.39</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENT</t>
+          <t>EMIL</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -2770,22 +2424,22 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>79.67</v>
+        <v>204.05</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>67.89</v>
+        <v>63.59</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>58.84</v>
+        <v>75.14</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>60.15</v>
+        <v>64.03</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>LOTUSDEV</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -2794,22 +2448,22 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>217.99</v>
+        <v>384.7</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>67.87</v>
+        <v>62.74</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>69.75</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v/>
+        <v>68.11</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>TEXRAIL</t>
+          <t>MTARTECH</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -2818,22 +2472,22 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>125.67</v>
+        <v>7797</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>67.23</v>
+        <v>62.62</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>62.36</v>
+        <v>63.94</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>49.05</v>
+        <v>72.75</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>JAMNAAUTO</t>
+          <t>TEXRAIL</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -2842,22 +2496,22 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>138.2</v>
+        <v>126.86</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>66.8</v>
+        <v>61.91</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>56.71</v>
+        <v>63.42</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>59.68</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>KSCL</t>
+          <t>GPPL</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -2866,22 +2520,22 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>804.55</v>
+        <v>165.88</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>66.55</v>
+        <v>60.37</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>47.29</v>
+        <v>62.75</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>45</v>
+        <v>55.57</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>PGIL</t>
+          <t>AKUMS</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2890,22 +2544,22 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1329.1</v>
+        <v>813.1</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>66.43000000000001</v>
+        <v>59.91</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>72.04000000000001</v>
+        <v>76.51000000000001</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>78.18000000000001</v>
+        <v>67.16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>GMRP&amp;UI</t>
+          <t>TRANSRAILL</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -2914,22 +2568,22 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>102.68</v>
+        <v>474.9</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>66.39</v>
+        <v>59.91</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>52.29</v>
+        <v>46.76</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>51.75</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>APLLTD</t>
+          <t>CAPILLARY</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -2938,22 +2592,22 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>863.75</v>
+        <v>554.7</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>66.38</v>
+        <v>59.76</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>64.09</v>
+        <v>53.6</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>52</v>
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>PCJEWELLER</t>
+          <t>QPOWER</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -2962,22 +2616,22 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>14.11</v>
+        <v>1564.6</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>66.34</v>
+        <v>59.59</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>69.81999999999999</v>
+        <v>67.22</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>60.5</v>
+        <v>70.20999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>SMLMAH</t>
+          <t>LLOYDSENT</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -2986,22 +2640,22 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>6825.5</v>
+        <v>77.95</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>65.77</v>
+        <v>59.24</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>71.31999999999999</v>
+        <v>56.25</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>72.08</v>
+        <v>59.06</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>TSFINV</t>
+          <t>GMRP&amp;UI</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3010,22 +2664,22 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>456.85</v>
+        <v>101.87</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>65.59999999999999</v>
+        <v>59.03</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>57.23</v>
+        <v>50.79</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>56.58</v>
+        <v>51.28</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>SUPRIYA</t>
+          <t>TDPOWERSYS</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -3034,22 +2688,22 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>985.2</v>
+        <v>792.15</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>65.34</v>
+        <v>58.08</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>64.27</v>
+        <v>68.23</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>62.91</v>
+        <v>79.77</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>AKUMS</t>
+          <t>WESTLIFE</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -3058,22 +2712,22 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>819.55</v>
+        <v>588.05</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>65.13</v>
+        <v>57.66</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>77.47</v>
+        <v>60.12</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>67.86</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>SURYAROSNI</t>
+          <t>NEOGEN</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -3082,22 +2736,22 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>227.45</v>
+        <v>2407.1</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>64.98999999999999</v>
+        <v>57.42</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>46.71</v>
+        <v>67.58</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>46.68</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>EMIL</t>
+          <t>KPIGREEN</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -3106,22 +2760,22 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>200.22</v>
+        <v>345.6</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>64.93000000000001</v>
+        <v>57.38</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>74.25</v>
+        <v>44.63</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>63.63</v>
+        <v>45.51</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>SHRIPISTON</t>
+          <t>SHAREINDIA</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3130,22 +2784,22 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>4746.8</v>
+        <v>205.09</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>64.73</v>
+        <v>57.31</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>72.59</v>
+        <v>63.36</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>80.38</v>
+        <v>53.94</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>IIFLCAPS</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -3154,22 +2808,22 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>587.55</v>
+        <v>345.6</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>63.7</v>
+        <v>56.99</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>67.47</v>
+        <v>57.2</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>68.3</v>
+        <v>58.92</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>MAHSEAMLES</t>
+          <t>PGIL</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -3178,22 +2832,22 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>715.65</v>
+        <v>1263</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>63.48</v>
+        <v>56.98</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>71.15000000000001</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>59.13</v>
+        <v>75.73</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>SUDARSCHEM</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -3202,22 +2856,22 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>338.15</v>
+        <v>1241.5</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>63.19</v>
+        <v>56.37</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>72.39</v>
+        <v>65.41</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>77.23999999999999</v>
+        <v>59.86</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>SHILPAMED</t>
+          <t>AZAD</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -3226,22 +2880,22 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1013.45</v>
+        <v>2860.9</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>62.37</v>
+        <v>56.14</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>90.43000000000001</v>
+        <v>66.73</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>85.34</v>
+        <v>70.97</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>SHAREINDIA</t>
+          <t>PRIVISCL</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -3250,22 +2904,22 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>209.62</v>
+        <v>3573</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>61.93</v>
+        <v>56.03</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>64.64</v>
+        <v>57.23</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>54.67</v>
+        <v>68.08</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>ENTERO</t>
+          <t>EDELWEISS</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -3274,22 +2928,22 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1821.8</v>
+        <v>137.9</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>61.28</v>
+        <v>56</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>73.29000000000001</v>
+        <v>65.09</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>73.61</v>
+        <v>63.38</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>KPIGREEN</t>
+          <t>SKYGOLD</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -3298,22 +2952,22 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>339.75</v>
+        <v>810.65</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>61.01</v>
+        <v>55.8</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>43.61</v>
+        <v>72.55</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>44.92</v>
+        <v>81.83</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>MIDHANI</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -3322,22 +2976,22 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>374.55</v>
+        <v>433.6</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>61</v>
+        <v>55.19</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>74</v>
+        <v>56.27</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>68.36</v>
+        <v>56.94</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>AXISCADES</t>
+          <t>SUDEEPPHRM</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -3346,22 +3000,22 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>1892.1</v>
+        <v>1199.8</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>60.66</v>
+        <v>54.94</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>60</v>
+        <v>68.8</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>65</v>
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>TRANSRAILL</t>
+          <t>INOXINDIA</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -3370,22 +3024,22 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>469.25</v>
+        <v>2168.3</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>60.3</v>
+        <v>54.89</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>46.57</v>
+        <v>70.01000000000001</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>44.11</v>
+        <v>79.48</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>PRSMJOHNSN</t>
+          <t>LXCHEM</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -3394,22 +3048,22 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>116.31</v>
+        <v>181.39</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>60.14</v>
+        <v>54.7</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>48.37</v>
+        <v>63.3</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>42.58</v>
+        <v>48.11</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>IIFLCAPS</t>
+          <t>POWERMECH</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -3418,22 +3072,22 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>346.7</v>
+        <v>2476.2</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>59.99</v>
+        <v>54.33</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>58.38</v>
+        <v>50.1</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>59.06</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>HERITGFOOD</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -3442,22 +3096,22 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>837.2</v>
+        <v>402.9</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>59.92</v>
+        <v>53.99</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>73.72</v>
+        <v>61.5</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>88.06</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>STAR</t>
+          <t>GRWRHITECH</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -3466,22 +3120,22 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>1184.9</v>
+        <v>6925.5</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>59.23</v>
+        <v>53.48</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>63.27</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>63.09</v>
+        <v>68.04000000000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>AEQUS</t>
+          <t>SUPRIYA</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -3490,22 +3144,22 @@
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>246.05</v>
+        <v>931</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>59.17</v>
+        <v>53.25</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>62.56</v>
+        <v>57.77</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v/>
+        <v>60.65</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>SPARC</t>
+          <t>SANSERA</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -3514,22 +3168,22 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>209.05</v>
+        <v>4276.6</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>58.94</v>
+        <v>53.13</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>55.37</v>
+        <v>70.8</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>55.24</v>
+        <v>80.55</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>QPOWER</t>
+          <t>SURYAROSNI</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -3538,22 +3192,22 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>1517.8</v>
+        <v>220.67</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>58.74</v>
+        <v>53.05</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>65.92</v>
+        <v>44.19</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>69.95</v>
+        <v>45.64</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>DATAMATICS</t>
+          <t>MAHSEAMLES</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -3562,22 +3216,22 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>807.6</v>
+        <v>698.75</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>58.61</v>
+        <v>53.02</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>52.24</v>
+        <v>64.87</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>55.47</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>ELLEN</t>
+          <t>SOUTHBANK</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -3586,22 +3240,22 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>368.5</v>
+        <v>47.44</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>58.39</v>
+        <v>52.93</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>64.12</v>
+        <v>58.74</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>43.8</v>
+        <v>70.08</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>JAMNAAUTO</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -3610,22 +3264,22 @@
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>336.95</v>
+        <v>131.66</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>58.11</v>
+        <v>52.77</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>72.61</v>
+        <v>52.83</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>68.34</v>
+        <v>57.01</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>NEOGEN</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -3634,22 +3288,22 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>2385.2</v>
+        <v>589.15</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>57.62</v>
+        <v>52.47</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>66.91</v>
+        <v>62.19</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>66.06999999999999</v>
+        <v>58.18</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GPPL</t>
+          <t>BBOX</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -3658,22 +3312,22 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>163.2</v>
+        <v>795.85</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>57.51</v>
+        <v>52.33</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>60.16</v>
+        <v>52.86</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>54.8</v>
+        <v>60.58</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>EDELWEISS</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -3682,22 +3336,22 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>136.83</v>
+        <v>1670</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>57.47</v>
+        <v>52.09</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>64.79000000000001</v>
+        <v>64.78</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>64.28</v>
+        <v>78.15000000000001</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>MSTCLTD</t>
+          <t>GRINDWELL</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -3706,22 +3360,22 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>740.8</v>
+        <v>1975.8</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>57.11</v>
+        <v>52.05</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>67.63</v>
+        <v>54.05</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>61.39</v>
+        <v>54.45</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GSFC</t>
+          <t>ATLANTAELE</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -3730,22 +3384,22 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>156.8</v>
+        <v>1716.5</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>57.08</v>
+        <v>51.87</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>48.11</v>
+        <v>54.45</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>45.33</v>
+        <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>TIPSMUSIC</t>
+          <t>PCJEWELLER</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -3754,22 +3408,22 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>668.95</v>
+        <v>12.82</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>56.67</v>
+        <v>51.8</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>55.42</v>
+        <v>61.54</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>59.08</v>
+        <v>57.29</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>RATNAMANI</t>
+          <t>ALIVUS</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -3778,22 +3432,22 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>2778.3</v>
+        <v>1374.2</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>56.46</v>
+        <v>51.63</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>58.03</v>
+        <v>68.88</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>54.12</v>
+        <v>71.58</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>SMLMAH</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -3802,22 +3456,22 @@
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>645.15</v>
+        <v>6251</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>56.44</v>
+        <v>51.52</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>71.65000000000001</v>
+        <v>63.27</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>69.3</v>
+        <v>68.23</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>RAIN</t>
+          <t>BLACKBUCK</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -3826,22 +3480,22 @@
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>219.35</v>
+        <v>606.15</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>56.26</v>
+        <v>51.19</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>64.5</v>
+        <v>53.52</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>60.88</v>
+        <v>58.98</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>HERITGFOOD</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -3850,22 +3504,22 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>407.4</v>
+        <v>2280.2</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>56.25</v>
+        <v>50.97</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>63.71</v>
+        <v>69.23</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>53.39</v>
+        <v>79.27</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>WESTLIFE</t>
+          <t>ICIL</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -3874,22 +3528,22 @@
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>578.1</v>
+        <v>443.65</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>55.84</v>
+        <v>50.88</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>59.15</v>
+        <v>64.28</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>46.4</v>
+        <v>62.72</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>CRIZAC</t>
+          <t>DATAMATICS</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -3898,22 +3552,22 @@
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>182.79</v>
+        <v>790.3</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>55.82</v>
+        <v>50.85</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>43.74</v>
+        <v>49.96</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v/>
+        <v>54.37</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>PARKHOSPS</t>
+          <t>YATHARTH</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -3922,22 +3576,22 @@
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>286.35</v>
+        <v>1033.7</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>55.79</v>
+        <v>50.55</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>62.61</v>
+        <v>63.06</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v/>
+        <v>69.26000000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>GODREJAGRO</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -3946,22 +3600,22 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>657.8</v>
+        <v>325.6</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>55.71</v>
+        <v>50.09</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>64.18000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>53.87</v>
+        <v>67.3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>PRIVISCL</t>
+          <t>JAYNECOIND</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -3970,22 +3624,22 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>3537.9</v>
+        <v>91.28</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>54.77</v>
+        <v>49.76</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>58.53</v>
+        <v>52.43</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>68.52</v>
+        <v>59.49</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>CSBBANK</t>
+          <t>UJJIVANSFB</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -3994,22 +3648,22 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>333.7</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>54.63</v>
+        <v>49.69</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>45.73</v>
+        <v>54.94</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>46.62</v>
+        <v>60.64</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>INOXINDIA</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -4018,22 +3672,22 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>2156.8</v>
+        <v>321.6</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>54.19</v>
+        <v>49.28</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>70.06999999999999</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>82.98999999999999</v>
+        <v>73.56</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>LUMAXTECH</t>
+          <t>APOLLO</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -4042,22 +3696,22 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>2026.8</v>
+        <v>394</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>54.18</v>
+        <v>48.84</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>63.71</v>
+        <v>55.74</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>70.51000000000001</v>
+        <v>66.92</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>BBOX</t>
+          <t>LUMAXTECH</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -4066,22 +3720,22 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>799.75</v>
+        <v>1978.9</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>54.13</v>
+        <v>48.81</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>53.27</v>
+        <v>60.35</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>60.93</v>
+        <v>68.65000000000001</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>LXCHEM</t>
+          <t>VARROC</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -4090,22 +3744,22 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>180.61</v>
+        <v>830.6</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>54.06</v>
+        <v>48.69</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>62.35</v>
+        <v>69.01000000000001</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>48.04</v>
+        <v>67.42</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>WELENT</t>
+          <t>KSB</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -4114,22 +3768,22 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>754.5</v>
+        <v>806.45</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>53.8</v>
+        <v>48.68</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>65.95</v>
+        <v>45.99</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>69.83</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>STYL</t>
+          <t>SHRIPISTON</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -4138,22 +3792,22 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>381.85</v>
+        <v>4490.5</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>53.64</v>
+        <v>48.55</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>59.24</v>
+        <v>61.95</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v/>
+        <v>75.51000000000001</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>MSTCLTD</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -4162,22 +3816,22 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>2316.1</v>
+        <v>705.8</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>53.55</v>
+        <v>47.5</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>72.41</v>
+        <v>61.83</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>81.26000000000001</v>
+        <v>59.13</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>KSB</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -4186,22 +3840,22 @@
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>819.1</v>
+        <v>542.55</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>52.95</v>
+        <v>47.49</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>47.95</v>
+        <v>58.83</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>52.32</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>TARC</t>
+          <t>MANORAMA</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -4210,22 +3864,22 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>129.36</v>
+        <v>1880.3</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>52.63</v>
+        <v>47.37</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>48.59</v>
+        <v>62.98</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>46.98</v>
+        <v>69.37</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>TARC</t>
+          <t>ELECTCAST</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -4234,22 +3888,22 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>129.36</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>52.63</v>
+        <v>47.29</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>48.59</v>
+        <v>48.01</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>46.98</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -4258,22 +3912,22 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>751.55</v>
+        <v>618.15</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>52.58</v>
+        <v>47.17</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>65.06999999999999</v>
+        <v>64.5</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>76.42</v>
+        <v>65.54000000000001</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>SAATVIKGL</t>
+          <t>TVSSCS</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -4282,22 +3936,22 @@
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>427.45</v>
+        <v>128.42</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>52.57</v>
+        <v>47.12</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>49.16</v>
+        <v>50.93</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v/>
+        <v>46.67</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>SKFINDUS</t>
+          <t>ELLEN</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -4306,22 +3960,22 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>2918</v>
+        <v>341.7</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>52.47</v>
+        <v>47.05</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>61.26</v>
+        <v>56.51</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v/>
+        <v>39.93</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>PRICOLLTD</t>
+          <t>IXIGO</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -4330,22 +3984,22 @@
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>763.8</v>
+        <v>161.9</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>52.44</v>
+        <v>46.94</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>66.72</v>
+        <v>42.92</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>66.53</v>
+        <v>42.51</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>IONEXCHANG</t>
+          <t>GODREJAGRO</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -4354,22 +4008,22 @@
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>420.15</v>
+        <v>631.9</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>52.4</v>
+        <v>46.91</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>54.42</v>
+        <v>57.61</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>49.39</v>
+        <v>51.91</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>ICIL</t>
+          <t>WELENT</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -4378,22 +4032,22 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>445.75</v>
+        <v>724.45</v>
       </c>
       <c r="D81" s="4" t="n">
-        <v>52.12</v>
+        <v>46.89</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>64.55</v>
+        <v>61.14</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>63.13</v>
+        <v>67.26000000000001</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>INDIGOPNTS</t>
+          <t>SKIPPER</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -4402,22 +4056,22 @@
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>1128.6</v>
+        <v>541.2</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>51.92</v>
+        <v>46.79</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>58.45</v>
+        <v>55.37</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>49.68</v>
+        <v>60.53</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>SUDARSCHEM</t>
+          <t>RAIN</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -4426,22 +4080,22 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>1218.9</v>
+        <v>208.52</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>51.82</v>
+        <v>46.77</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>63.92</v>
+        <v>58.56</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>59.32</v>
+        <v>58.91</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>REFEX</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -4450,22 +4104,22 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>285.8</v>
+        <v>154.79</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>51.72</v>
+        <v>46.72</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>48.42</v>
+        <v>48.12</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>48.81</v>
+        <v>53.37</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>RAYMONDLSL</t>
+          <t>DIACABS</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -4474,22 +4128,22 @@
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>687.6</v>
+        <v>345</v>
       </c>
       <c r="D85" s="4" t="n">
-        <v>51.62</v>
+        <v>46.53</v>
       </c>
       <c r="E85" s="4" t="n">
-        <v>40.16</v>
+        <v>70.70999999999999</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>25.59</v>
+        <v>78.53</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>AVL</t>
+          <t>ASTRAMICRO</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -4498,22 +4152,22 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>619.5</v>
+        <v>1624.5</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>51.57</v>
+        <v>46.31</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>57.44</v>
+        <v>57.16</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>62.64</v>
+        <v>68.03</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>GRINDWELL</t>
+          <t>AARTIDRUGS</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -4522,22 +4176,22 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>1972.7</v>
+        <v>421</v>
       </c>
       <c r="D87" s="4" t="n">
-        <v>51.48</v>
+        <v>46.27</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>53.66</v>
+        <v>55.5</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>54.4</v>
+        <v>49.82</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>DBL</t>
+          <t>TMB</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -4546,22 +4200,22 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>412.45</v>
+        <v>872.05</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>51.17</v>
+        <v>45.96</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>46.03</v>
+        <v>65.34</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>47.02</v>
+        <v>71.67</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>AARTIDRUGS</t>
+          <t>STYRENIX</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -4570,22 +4224,22 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>427.4</v>
+        <v>2055</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>51.14</v>
+        <v>45.89</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>59.57</v>
+        <v>44.68</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>50.68</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>JKPAPER</t>
+          <t>ENTERO</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -4594,22 +4248,22 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>408.45</v>
+        <v>1680.8</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>51.1</v>
+        <v>45.88</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>60.09</v>
+        <v>63.11</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>56.37</v>
+        <v>66.56999999999999</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>SUDEEPPHRM</t>
+          <t>WABAG</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -4618,22 +4272,22 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>1164.9</v>
+        <v>2004.9</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>51.03</v>
+        <v>45.78</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>67</v>
+        <v>56.63</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v/>
+        <v>66.28</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>SMARTWORKS</t>
+          <t>TARC</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -4642,22 +4296,22 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>529.9</v>
+        <v>125.58</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>50.88</v>
+        <v>45.7</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>60.6</v>
+        <v>46.01</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v/>
+        <v>46.02</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>JSFB</t>
+          <t>TARC</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -4666,22 +4320,22 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>535.25</v>
+        <v>125.58</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>50.88</v>
+        <v>45.7</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>57.82</v>
+        <v>46.01</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>57</v>
+        <v>46.02</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>REDTAPE</t>
+          <t>STYL</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -4690,22 +4344,22 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>121.05</v>
+        <v>366</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>50.85</v>
+        <v>45.51</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>45.45</v>
+        <v>55.11</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>34.42</v>
+        <v/>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>CCAVENUE</t>
+          <t>SAMHI</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -4714,22 +4368,22 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>15.89</v>
+        <v>154.37</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>50.8</v>
+        <v>45.46</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>50.57</v>
+        <v>42.98</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>44.57</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>TVSSCS</t>
+          <t>RBA</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -4738,22 +4392,22 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>130.26</v>
+        <v>92.22</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>50.68</v>
+        <v>45.29</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>52.7</v>
+        <v>61.01</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>47.32</v>
+        <v>55.67</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>VARROC</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -4762,22 +4416,22 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>834.85</v>
+        <v>1414.7</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>50.54</v>
+        <v>45.17</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>70.23</v>
+        <v>58.57</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>68.08</v>
+        <v>63.43</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>METROPOLIS</t>
+          <t>IONEXCHANG</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -4786,22 +4440,22 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>582.6</v>
+        <v>406.4</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>50.52</v>
+        <v>45.02</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>59.21</v>
+        <v>51.33</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>62.81</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>APOLLO</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -4810,22 +4464,22 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>395.6</v>
+        <v>475.05</v>
       </c>
       <c r="D99" s="4" t="n">
-        <v>50.46</v>
+        <v>44.81</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>55.94</v>
+        <v>38.09</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>67.89</v>
+        <v>38.86</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>AZAD</t>
+          <t>KIRLOSBROS</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -4834,22 +4488,22 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>2728</v>
+        <v>1767.6</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>50.41</v>
+        <v>44.73</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>63.71</v>
+        <v>48.89</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>69.18000000000001</v>
+        <v>52.33</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>SUBROS</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -4858,22 +4512,22 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>720.9</v>
+        <v>194.13</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>49.93</v>
+        <v>44.54</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>43.82</v>
+        <v>50.09</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>49.44</v>
+        <v>52.54</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>DIACABS</t>
+          <t>EMBDL</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -4882,22 +4536,22 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>354.5</v>
+        <v>56.13</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>49.84</v>
+        <v>44.5</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>72.61</v>
+        <v>43.9</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>80.98</v>
+        <v>40.49</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>CUPID</t>
+          <t>VOLTAMP</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -4906,22 +4560,22 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>270</v>
+        <v>10426</v>
       </c>
       <c r="D103" s="4" t="n">
-        <v>49.81</v>
+        <v>44.38</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>76.61</v>
+        <v>55.39</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>88.87</v>
+        <v>56.63</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>ALIVUS</t>
+          <t>RATNAMANI</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -4930,22 +4584,22 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>1365.6</v>
+        <v>2619.4</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>49.77</v>
+        <v>44.36</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>67.95</v>
+        <v>52.19</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>70.94</v>
+        <v>50.69</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>SKFINDIA</t>
+          <t>BLUESTONE</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -4954,22 +4608,22 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>1539.8</v>
+        <v>787.95</v>
       </c>
       <c r="D105" s="4" t="n">
-        <v>49.76</v>
+        <v>44.24</v>
       </c>
       <c r="E105" s="4" t="n">
-        <v>39.19</v>
+        <v>59.86</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>32.58</v>
+        <v/>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>HCG</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -4978,22 +4632,22 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>698.65</v>
+        <v>534.05</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>49.69</v>
+        <v>44.04</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>60.05</v>
+        <v>58.6</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>62.36</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>VOLTAMP</t>
+          <t>APLLTD</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -5002,22 +4656,22 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>10709</v>
+        <v>815.25</v>
       </c>
       <c r="D107" s="4" t="n">
-        <v>49.61</v>
+        <v>43.97</v>
       </c>
       <c r="E107" s="4" t="n">
-        <v>58.38</v>
+        <v>53.58</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>57.89</v>
+        <v>48.91</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>CELLO</t>
+          <t>CCAVENUE</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -5026,22 +4680,22 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>338.5</v>
+        <v>15.28</v>
       </c>
       <c r="D108" s="4" t="n">
-        <v>49.52</v>
+        <v>43.63</v>
       </c>
       <c r="E108" s="4" t="n">
-        <v>36.47</v>
+        <v>47.48</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>28.46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>TIMETECHNO</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -5050,22 +4704,22 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>549.05</v>
+        <v>179.68</v>
       </c>
       <c r="D109" s="4" t="n">
-        <v>49.44</v>
+        <v>43.61</v>
       </c>
       <c r="E109" s="4" t="n">
-        <v>61.8</v>
+        <v>46.39</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>68.26000000000001</v>
+        <v>50.69</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>SAMHI</t>
+          <t>QUESS</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -5074,22 +4728,22 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>158.94</v>
+        <v>336.2</v>
       </c>
       <c r="D110" s="4" t="n">
-        <v>49.42</v>
+        <v>43.5</v>
       </c>
       <c r="E110" s="4" t="n">
-        <v>45.84</v>
+        <v>63.4</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>45.73</v>
+        <v>49.96</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>NESCO</t>
+          <t>KSCL</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -5098,22 +4752,22 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>1070.3</v>
+        <v>715.1</v>
       </c>
       <c r="D111" s="4" t="n">
-        <v>49.39</v>
+        <v>43.49</v>
       </c>
       <c r="E111" s="4" t="n">
-        <v>45.82</v>
+        <v>39.53</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>50.85</v>
+        <v>40.65</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>INOXGREEN</t>
+          <t>TIPSMUSIC</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -5122,22 +4776,22 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>174.64</v>
+        <v>644.2</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>49.36</v>
+        <v>43.46</v>
       </c>
       <c r="E112" s="4" t="n">
-        <v>46.14</v>
+        <v>51.04</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>51.46</v>
+        <v>56.77</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>GAEL</t>
+          <t>REFEX</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -5146,22 +4800,22 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>163.87</v>
+        <v>271.3</v>
       </c>
       <c r="D113" s="4" t="n">
-        <v>49.25</v>
+        <v>43.31</v>
       </c>
       <c r="E113" s="4" t="n">
-        <v>54.67</v>
+        <v>43.96</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>61.04</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>SKYGOLD</t>
+          <t>WAKEFIT</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -5170,22 +4824,22 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>782.7</v>
+        <v>139.88</v>
       </c>
       <c r="D114" s="4" t="n">
-        <v>49.2</v>
+        <v>43.1</v>
       </c>
       <c r="E114" s="4" t="n">
-        <v>71.62</v>
+        <v>47.89</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>80.15000000000001</v>
+        <v/>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>BIRLACORPN</t>
+          <t>WEWORK</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -5194,22 +4848,22 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>850.3</v>
+        <v>659.6</v>
       </c>
       <c r="D115" s="4" t="n">
-        <v>49.04</v>
+        <v>42.81</v>
       </c>
       <c r="E115" s="4" t="n">
-        <v>39.93</v>
+        <v>52.5</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>38.08</v>
+        <v/>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>RATEGAIN</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -5218,22 +4872,22 @@
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>214.09</v>
+        <v>840.65</v>
       </c>
       <c r="D116" s="4" t="n">
-        <v>48.97</v>
+        <v>42.81</v>
       </c>
       <c r="E116" s="4" t="n">
-        <v>63.16</v>
+        <v>52.82</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>65.14</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>SKIPPER</t>
+          <t>SMARTWORKS</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -5242,22 +4896,22 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>551.15</v>
+        <v>510.65</v>
       </c>
       <c r="D117" s="4" t="n">
-        <v>48.76</v>
+        <v>42.67</v>
       </c>
       <c r="E117" s="4" t="n">
-        <v>56.96</v>
+        <v>54.68</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>61.7</v>
+        <v>54.26</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>VIPIND</t>
+          <t>SAATVIKGL</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -5266,22 +4920,22 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>301.2</v>
+        <v>405.55</v>
       </c>
       <c r="D118" s="4" t="n">
-        <v>48.75</v>
+        <v>42.53</v>
       </c>
       <c r="E118" s="4" t="n">
-        <v>43.43</v>
+        <v>44.21</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>36.42</v>
+        <v/>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>MANYAVAR</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -5290,22 +4944,22 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>482.55</v>
+        <v>519.2</v>
       </c>
       <c r="D119" s="4" t="n">
-        <v>48.67</v>
+        <v>42.45</v>
       </c>
       <c r="E119" s="4" t="n">
-        <v>39.69</v>
+        <v>56.52</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>39.53</v>
+        <v>39.17</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>PURVA</t>
+          <t>INDIASHLTR</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -5314,22 +4968,22 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>213.87</v>
+        <v>645.6</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>48.49</v>
+        <v>42.39</v>
       </c>
       <c r="E120" s="4" t="n">
-        <v>47.72</v>
+        <v>36.75</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>45.1</v>
+        <v>39.72</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>THYROCARE</t>
+          <t>GAEL</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -5338,22 +4992,22 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>566.85</v>
+        <v>157.69</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>48.34</v>
+        <v>42.16</v>
       </c>
       <c r="E121" s="4" t="n">
-        <v>58.65</v>
+        <v>50.29</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>65.8</v>
+        <v>57.86</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>KRBL</t>
+          <t>FEDFINA</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -5362,22 +5016,22 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>398.65</v>
+        <v>149.77</v>
       </c>
       <c r="D122" s="4" t="n">
-        <v>48.26</v>
+        <v>42.14</v>
       </c>
       <c r="E122" s="4" t="n">
-        <v>56.74</v>
+        <v>48.69</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>56.06</v>
+        <v>55.66</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>EMBDL</t>
+          <t>EPL</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -5386,22 +5040,22 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>58.07</v>
+        <v>232.39</v>
       </c>
       <c r="D123" s="4" t="n">
-        <v>48.24</v>
+        <v>41.89</v>
       </c>
       <c r="E123" s="4" t="n">
-        <v>46.13</v>
+        <v>49.16</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>41.13</v>
+        <v>53.76</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>JSLL</t>
+          <t>BIRLACORPN</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -5410,22 +5064,22 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>508.25</v>
+        <v>828.95</v>
       </c>
       <c r="D124" s="4" t="n">
-        <v>48.18</v>
+        <v>41.86</v>
       </c>
       <c r="E124" s="4" t="n">
-        <v>39.15</v>
+        <v>37.92</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>40.75</v>
+        <v>37.19</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>MANYAVAR</t>
+          <t>DBL</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -5434,22 +5088,22 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>532.5</v>
+        <v>399.1</v>
       </c>
       <c r="D125" s="4" t="n">
-        <v>47.9</v>
+        <v>41.82</v>
       </c>
       <c r="E125" s="4" t="n">
-        <v>59.87</v>
+        <v>42.75</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>39.92</v>
+        <v>45.35</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>MEDPLUS</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -5458,22 +5112,22 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>155.09</v>
+        <v>654.3</v>
       </c>
       <c r="D126" s="4" t="n">
-        <v>47.59</v>
+        <v>41.61</v>
       </c>
       <c r="E126" s="4" t="n">
-        <v>48.28</v>
+        <v>28.58</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>53.53</v>
+        <v>38.65</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>UTLSOLAR</t>
+          <t>PRUDENT</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -5482,22 +5136,22 @@
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>422.1</v>
+        <v>3119.1</v>
       </c>
       <c r="D127" s="4" t="n">
-        <v>47.58</v>
+        <v>41.53</v>
       </c>
       <c r="E127" s="4" t="n">
-        <v>63.76</v>
+        <v>52.48</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v/>
+        <v>58.52</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>AGARWALEYE</t>
+          <t>UTLSOLAR</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -5506,46 +5160,46 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>500</v>
+        <v>401.65</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>47.46</v>
+        <v>41.52</v>
       </c>
       <c r="E128" s="4" t="n">
-        <v>54.51</v>
+        <v>58.65</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>56.28</v>
+        <v/>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>RENUKA</t>
-        </is>
-      </c>
-      <c r="B129" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C129" s="4" t="n">
-        <v>23.31</v>
-      </c>
-      <c r="D129" s="4" t="n">
-        <v>47.42</v>
-      </c>
-      <c r="E129" s="4" t="n">
-        <v>46.49</v>
-      </c>
-      <c r="F129" s="4" t="n">
-        <v>39.45</v>
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>PRICOLLTD</t>
+        </is>
+      </c>
+      <c r="B129" s="6" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C129" s="7" t="n">
+        <v>734.5</v>
+      </c>
+      <c r="D129" s="7" t="n">
+        <v>41.48</v>
+      </c>
+      <c r="E129" s="7" t="n">
+        <v>62.14</v>
+      </c>
+      <c r="F129" s="7" t="n">
+        <v>64.14</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>TMB</t>
+          <t>SUNTECK</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -5554,22 +5208,22 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>881.9</v>
+        <v>279.45</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>47.37</v>
+        <v>41.38</v>
       </c>
       <c r="E130" s="4" t="n">
-        <v>65.01000000000001</v>
+        <v>38.12</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>72.77</v>
+        <v>39.07</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>POWERMECH</t>
+          <t>STAR</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -5578,22 +5232,22 @@
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>2407.3</v>
+        <v>1084.8</v>
       </c>
       <c r="D131" s="4" t="n">
-        <v>47.25</v>
+        <v>41.31</v>
       </c>
       <c r="E131" s="4" t="n">
-        <v>47.31</v>
+        <v>52.81</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>49.77</v>
+        <v>58.56</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>JUSTDIAL</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -5602,22 +5256,22 @@
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>5134.5</v>
+        <v>653.15</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>47.24</v>
+        <v>41.25</v>
       </c>
       <c r="E132" s="4" t="n">
-        <v>52.58</v>
+        <v>51.41</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>66.87</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>JUSTDIAL</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -5626,22 +5280,22 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>672.2</v>
+        <v>4861</v>
       </c>
       <c r="D133" s="4" t="n">
-        <v>47.23</v>
+        <v>41.1</v>
       </c>
       <c r="E133" s="4" t="n">
-        <v>55.12</v>
+        <v>48.84</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>45.8</v>
+        <v>63.77</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>BLACKBUCK</t>
+          <t>MASTEK</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -5650,22 +5304,22 @@
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>592.95</v>
+        <v>1555.6</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>47</v>
+        <v>41.04</v>
       </c>
       <c r="E134" s="4" t="n">
-        <v>52.31</v>
+        <v>42.09</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>58.29</v>
+        <v>40.33</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>ASHOKA</t>
+          <t>BECTORFOOD</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -5674,22 +5328,22 @@
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>113.12</v>
+        <v>213.03</v>
       </c>
       <c r="D135" s="4" t="n">
-        <v>46.82</v>
+        <v>41</v>
       </c>
       <c r="E135" s="4" t="n">
-        <v>36.53</v>
+        <v>49.5</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>40.78</v>
+        <v>47.11</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>AGARWALEYE</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -5698,22 +5352,22 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>2117.7</v>
+        <v>486.45</v>
       </c>
       <c r="D136" s="4" t="n">
-        <v>46.82</v>
+        <v>40.97</v>
       </c>
       <c r="E136" s="4" t="n">
-        <v>63.62</v>
+        <v>51.07</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v/>
+        <v>53.94</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>FINPIPE</t>
+          <t>HCG</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -5722,22 +5376,22 @@
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>154.16</v>
+        <v>668.75</v>
       </c>
       <c r="D137" s="4" t="n">
-        <v>46.8</v>
+        <v>40.94</v>
       </c>
       <c r="E137" s="4" t="n">
-        <v>38.52</v>
+        <v>50.59</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>41.05</v>
+        <v>59.01</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>JAIBALAJI</t>
+          <t>BANCOINDIA</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -5746,22 +5400,22 @@
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>64.95999999999999</v>
+        <v>589.85</v>
       </c>
       <c r="D138" s="4" t="n">
-        <v>46.62</v>
+        <v>40.78</v>
       </c>
       <c r="E138" s="4" t="n">
-        <v>46.45</v>
+        <v>44.33</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>41.79</v>
+        <v>54.49</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>V2RETAIL</t>
+          <t>RUBICON</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -5770,22 +5424,22 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>214.72</v>
+        <v>1630.9</v>
       </c>
       <c r="D139" s="4" t="n">
-        <v>46.59</v>
+        <v>40.4</v>
       </c>
       <c r="E139" s="4" t="n">
-        <v>48.52</v>
+        <v>64.98</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>61.26</v>
+        <v/>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>GRWRHITECH</t>
+          <t>CRIZAC</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -5794,22 +5448,22 @@
         </is>
       </c>
       <c r="C140" s="4" t="n">
-        <v>6640</v>
+        <v>166.89</v>
       </c>
       <c r="D140" s="4" t="n">
-        <v>46.49</v>
+        <v>40.26</v>
       </c>
       <c r="E140" s="4" t="n">
-        <v>61.07</v>
+        <v>38.66</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>65.7</v>
+        <v>20.86</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>BLUESTONE</t>
+          <t>SKFINDUS</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -5818,13 +5472,13 @@
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>809.3</v>
+        <v>2734.2</v>
       </c>
       <c r="D141" s="4" t="n">
-        <v>46.48</v>
+        <v>40.13</v>
       </c>
       <c r="E141" s="4" t="n">
-        <v>63.66</v>
+        <v>50.98</v>
       </c>
       <c r="F141" s="4" t="n">
         <v/>
@@ -5833,7 +5487,7 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>DBREALTY</t>
+          <t>REDTAPE</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -5842,22 +5496,22 @@
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>100.08</v>
+        <v>115.29</v>
       </c>
       <c r="D142" s="4" t="n">
-        <v>46.41</v>
+        <v>40.07</v>
       </c>
       <c r="E142" s="4" t="n">
-        <v>41.89</v>
+        <v>41.26</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>42.17</v>
+        <v>33.9</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>UJJIVANSFB</t>
+          <t>PURVA</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -5866,22 +5520,22 @@
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>64.70999999999999</v>
+        <v>204.64</v>
       </c>
       <c r="D143" s="4" t="n">
-        <v>46.4</v>
+        <v>40.07</v>
       </c>
       <c r="E143" s="4" t="n">
-        <v>53.51</v>
+        <v>45.85</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>59.98</v>
+        <v>43.56</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>BALUFORGE</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -5890,22 +5544,22 @@
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>198.85</v>
+        <v>488.95</v>
       </c>
       <c r="D144" s="4" t="n">
-        <v>46.4</v>
+        <v>39.97</v>
       </c>
       <c r="E144" s="4" t="n">
-        <v>48.14</v>
+        <v>47.89</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>43.05</v>
+        <v>48.47</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>EPL</t>
+          <t>PNGJL</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -5914,22 +5568,22 @@
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>238.1</v>
+        <v>581.95</v>
       </c>
       <c r="D145" s="4" t="n">
-        <v>46.36</v>
+        <v>39.95</v>
       </c>
       <c r="E145" s="4" t="n">
-        <v>53.26</v>
+        <v>45.98</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>55.18</v>
+        <v>47.35</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>MTARTECH</t>
+          <t>NESCO</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -5938,22 +5592,22 @@
         </is>
       </c>
       <c r="C146" s="4" t="n">
-        <v>6900</v>
+        <v>1028.2</v>
       </c>
       <c r="D146" s="4" t="n">
-        <v>46.36</v>
+        <v>39.82</v>
       </c>
       <c r="E146" s="4" t="n">
-        <v>56.86</v>
+        <v>41.13</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>69.12</v>
+        <v>48.46</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>BALAMINES</t>
+          <t>EQUITASBNK</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -5962,22 +5616,22 @@
         </is>
       </c>
       <c r="C147" s="4" t="n">
-        <v>2189.6</v>
+        <v>68.41</v>
       </c>
       <c r="D147" s="4" t="n">
-        <v>46.26</v>
+        <v>39.31</v>
       </c>
       <c r="E147" s="4" t="n">
-        <v>57.84</v>
+        <v>44.91</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>59.72</v>
+        <v>50.21</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>TIMETECHNO</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -5986,22 +5640,22 @@
         </is>
       </c>
       <c r="C148" s="4" t="n">
-        <v>181.22</v>
+        <v>2029.4</v>
       </c>
       <c r="D148" s="4" t="n">
-        <v>46.19</v>
+        <v>38.97</v>
       </c>
       <c r="E148" s="4" t="n">
-        <v>46.89</v>
+        <v>55.76</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>51.09</v>
+        <v/>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>MAHSCOOTER</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -6010,22 +5664,22 @@
         </is>
       </c>
       <c r="C149" s="4" t="n">
-        <v>13052</v>
+        <v>100.7</v>
       </c>
       <c r="D149" s="4" t="n">
-        <v>46.08</v>
+        <v>38.96</v>
       </c>
       <c r="E149" s="4" t="n">
-        <v>50.69</v>
+        <v>44.01</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>56.21</v>
+        <v>40.74</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>QUESS</t>
+          <t>SHAILY</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -6034,22 +5688,22 @@
         </is>
       </c>
       <c r="C150" s="4" t="n">
-        <v>340.9</v>
+        <v>3009.1</v>
       </c>
       <c r="D150" s="4" t="n">
-        <v>45.82</v>
+        <v>38.83</v>
       </c>
       <c r="E150" s="4" t="n">
-        <v>65.91</v>
+        <v>54.96</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>50.41</v>
+        <v>66.91</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>MANORAMA</t>
+          <t>KITEX</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -6058,22 +5712,22 @@
         </is>
       </c>
       <c r="C151" s="4" t="n">
-        <v>1872.8</v>
+        <v>116.68</v>
       </c>
       <c r="D151" s="4" t="n">
-        <v>45.67</v>
+        <v>38.71</v>
       </c>
       <c r="E151" s="4" t="n">
-        <v>62.25</v>
+        <v>30.53</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>69.67</v>
+        <v>41.69</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>PICCADIL</t>
+          <t>CELLO</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -6082,22 +5736,22 @@
         </is>
       </c>
       <c r="C152" s="4" t="n">
-        <v>613</v>
+        <v>323.1</v>
       </c>
       <c r="D152" s="4" t="n">
-        <v>45.5</v>
+        <v>38.57</v>
       </c>
       <c r="E152" s="4" t="n">
-        <v>47.88</v>
+        <v>34.01</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v/>
+        <v>27.58</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>SHAILY</t>
+          <t>JAIBALAJI</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -6106,22 +5760,22 @@
         </is>
       </c>
       <c r="C153" s="4" t="n">
-        <v>3142.3</v>
+        <v>61.72</v>
       </c>
       <c r="D153" s="4" t="n">
-        <v>45.15</v>
+        <v>38.28</v>
       </c>
       <c r="E153" s="4" t="n">
-        <v>60.39</v>
+        <v>42.88</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>70.16</v>
+        <v>41.02</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>RBA</t>
+          <t>JSLL</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -6130,22 +5784,22 @@
         </is>
       </c>
       <c r="C154" s="4" t="n">
-        <v>92.51000000000001</v>
+        <v>480.8</v>
       </c>
       <c r="D154" s="4" t="n">
-        <v>45.13</v>
+        <v>38.11</v>
       </c>
       <c r="E154" s="4" t="n">
-        <v>61.66</v>
+        <v>36.19</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>55.87</v>
+        <v>40.05</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>WABAG</t>
+          <t>FINPIPE</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -6154,22 +5808,22 @@
         </is>
       </c>
       <c r="C155" s="4" t="n">
-        <v>2008.4</v>
+        <v>150.49</v>
       </c>
       <c r="D155" s="4" t="n">
-        <v>45</v>
+        <v>38.04</v>
       </c>
       <c r="E155" s="4" t="n">
-        <v>56.61</v>
+        <v>35.69</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>67.56999999999999</v>
+        <v>40.25</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>ASTRAMICRO</t>
+          <t>BALAMINES</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -6178,22 +5832,22 @@
         </is>
       </c>
       <c r="C156" s="4" t="n">
-        <v>1622.4</v>
+        <v>2052.2</v>
       </c>
       <c r="D156" s="4" t="n">
-        <v>44.81</v>
+        <v>37.77</v>
       </c>
       <c r="E156" s="4" t="n">
-        <v>57.19</v>
+        <v>53.11</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>67.98</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>KNRCON</t>
+          <t>TANLA</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -6202,22 +5856,22 @@
         </is>
       </c>
       <c r="C157" s="4" t="n">
-        <v>120.27</v>
+        <v>487.75</v>
       </c>
       <c r="D157" s="4" t="n">
-        <v>44.71</v>
+        <v>37.76</v>
       </c>
       <c r="E157" s="4" t="n">
-        <v>42.12</v>
+        <v>41.41</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>33.75</v>
+        <v>42.91</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>STYRENIX</t>
+          <t>INDIGOPNTS</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -6226,22 +5880,22 @@
         </is>
       </c>
       <c r="C158" s="4" t="n">
-        <v>2067</v>
+        <v>1053.5</v>
       </c>
       <c r="D158" s="4" t="n">
-        <v>44.66</v>
+        <v>37.75</v>
       </c>
       <c r="E158" s="4" t="n">
-        <v>45.02</v>
+        <v>49.36</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>48.89</v>
+        <v>46.99</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>BALUFORGE</t>
+          <t>JKPAPER</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -6250,22 +5904,22 @@
         </is>
       </c>
       <c r="C159" s="4" t="n">
-        <v>506.8</v>
+        <v>382.6</v>
       </c>
       <c r="D159" s="4" t="n">
-        <v>44.18</v>
+        <v>37.73</v>
       </c>
       <c r="E159" s="4" t="n">
-        <v>50.2</v>
+        <v>51.36</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>49.31</v>
+        <v>52.76</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>RELIGARE</t>
+          <t>SUBROS</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -6274,22 +5928,22 @@
         </is>
       </c>
       <c r="C160" s="4" t="n">
-        <v>242.27</v>
+        <v>684.9</v>
       </c>
       <c r="D160" s="4" t="n">
-        <v>43.9</v>
+        <v>37.68</v>
       </c>
       <c r="E160" s="4" t="n">
-        <v>49.42</v>
+        <v>38.89</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>51.81</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>FEDFINA</t>
+          <t>ETHOSLTD</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -6298,22 +5952,22 @@
         </is>
       </c>
       <c r="C161" s="4" t="n">
-        <v>151.68</v>
+        <v>2531.9</v>
       </c>
       <c r="D161" s="4" t="n">
-        <v>43.89</v>
+        <v>37.49</v>
       </c>
       <c r="E161" s="4" t="n">
-        <v>49.84</v>
+        <v>47.94</v>
       </c>
       <c r="F161" s="4" t="n">
-        <v>56.56</v>
+        <v>50.39</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>AWFIS</t>
+          <t>KRBL</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -6322,22 +5976,22 @@
         </is>
       </c>
       <c r="C162" s="4" t="n">
-        <v>257.2</v>
+        <v>375.9</v>
       </c>
       <c r="D162" s="4" t="n">
-        <v>43.68</v>
+        <v>37.39</v>
       </c>
       <c r="E162" s="4" t="n">
-        <v>37.28</v>
+        <v>49.67</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>29.51</v>
+        <v>53.38</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>BANCOINDIA</t>
+          <t>JSFB</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -6346,22 +6000,22 @@
         </is>
       </c>
       <c r="C163" s="4" t="n">
-        <v>599.85</v>
+        <v>482.4</v>
       </c>
       <c r="D163" s="4" t="n">
-        <v>43.6</v>
+        <v>37.17</v>
       </c>
       <c r="E163" s="4" t="n">
-        <v>45.82</v>
+        <v>47.65</v>
       </c>
       <c r="F163" s="4" t="n">
-        <v>55.31</v>
+        <v>51.47</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>PARAS</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -6370,22 +6024,22 @@
         </is>
       </c>
       <c r="C164" s="4" t="n">
-        <v>103.47</v>
+        <v>1276</v>
       </c>
       <c r="D164" s="4" t="n">
-        <v>43.55</v>
+        <v>36.72</v>
       </c>
       <c r="E164" s="4" t="n">
-        <v>46.09</v>
+        <v>56.95</v>
       </c>
       <c r="F164" s="4" t="n">
-        <v>41.46</v>
+        <v>63.12</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>WAAREERTL</t>
+          <t>KIRLPNU</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -6394,22 +6048,22 @@
         </is>
       </c>
       <c r="C165" s="4" t="n">
-        <v>832.9</v>
+        <v>681.95</v>
       </c>
       <c r="D165" s="4" t="n">
-        <v>43.52</v>
+        <v>36.58</v>
       </c>
       <c r="E165" s="4" t="n">
-        <v>36.91</v>
+        <v>44.56</v>
       </c>
       <c r="F165" s="4" t="n">
-        <v>39.61</v>
+        <v>52.99</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>INDIASHLTR</t>
+          <t>CSBBANK</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -6418,22 +6072,22 @@
         </is>
       </c>
       <c r="C166" s="4" t="n">
-        <v>654.3</v>
+        <v>304.75</v>
       </c>
       <c r="D166" s="4" t="n">
-        <v>43.43</v>
+        <v>36.53</v>
       </c>
       <c r="E166" s="4" t="n">
-        <v>37.78</v>
+        <v>39.77</v>
       </c>
       <c r="F166" s="4" t="n">
-        <v>40.09</v>
+        <v>42.89</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>CMSINFO</t>
+          <t>PICCADIL</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -6442,22 +6096,22 @@
         </is>
       </c>
       <c r="C167" s="4" t="n">
-        <v>233.17</v>
+        <v>581.05</v>
       </c>
       <c r="D167" s="4" t="n">
-        <v>43.42</v>
+        <v>36.51</v>
       </c>
       <c r="E167" s="4" t="n">
-        <v>32.26</v>
+        <v>44.84</v>
       </c>
       <c r="F167" s="4" t="n">
-        <v>32.09</v>
+        <v>48.38</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>WAKEFIT</t>
+          <t>RCF</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -6466,22 +6120,22 @@
         </is>
       </c>
       <c r="C168" s="4" t="n">
-        <v>141.35</v>
+        <v>106.8</v>
       </c>
       <c r="D168" s="4" t="n">
-        <v>43.39</v>
+        <v>36.39</v>
       </c>
       <c r="E168" s="4" t="n">
-        <v>48.95</v>
+        <v>32.27</v>
       </c>
       <c r="F168" s="4" t="n">
-        <v/>
+        <v>40.88</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>MIDHANI</t>
+          <t>SHAKTIPUMP</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -6490,22 +6144,22 @@
         </is>
       </c>
       <c r="C169" s="4" t="n">
-        <v>405.05</v>
+        <v>454.1</v>
       </c>
       <c r="D169" s="4" t="n">
-        <v>43.33</v>
+        <v>36.31</v>
       </c>
       <c r="E169" s="4" t="n">
-        <v>50.58</v>
+        <v>34.36</v>
       </c>
       <c r="F169" s="4" t="n">
-        <v>54.29</v>
+        <v>41.99</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>JAYNECOIND</t>
+          <t>MAHSCOOTER</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -6514,22 +6168,22 @@
         </is>
       </c>
       <c r="C170" s="4" t="n">
-        <v>88.55</v>
+        <v>12380</v>
       </c>
       <c r="D170" s="4" t="n">
-        <v>42.81</v>
+        <v>36.31</v>
       </c>
       <c r="E170" s="4" t="n">
-        <v>49.13</v>
+        <v>45.2</v>
       </c>
       <c r="F170" s="4" t="n">
-        <v>58.28</v>
+        <v>52.77</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>ZAGGLE</t>
+          <t>SENCO</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -6538,22 +6192,22 @@
         </is>
       </c>
       <c r="C171" s="4" t="n">
-        <v>178.84</v>
+        <v>317.4</v>
       </c>
       <c r="D171" s="4" t="n">
-        <v>42.58</v>
+        <v>36.23</v>
       </c>
       <c r="E171" s="4" t="n">
-        <v>33.06</v>
+        <v>42.74</v>
       </c>
       <c r="F171" s="4" t="n">
-        <v>37.29</v>
+        <v>46.92</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>RUBICON</t>
+          <t>PARKHOSPS</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -6562,13 +6216,13 @@
         </is>
       </c>
       <c r="C172" s="4" t="n">
-        <v>1676.3</v>
+        <v>270.8</v>
       </c>
       <c r="D172" s="4" t="n">
-        <v>42.49</v>
+        <v>36.14</v>
       </c>
       <c r="E172" s="4" t="n">
-        <v>68.98999999999999</v>
+        <v>53.76</v>
       </c>
       <c r="F172" s="4" t="n">
         <v/>
@@ -6577,7 +6231,7 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>ADVENZYMES</t>
+          <t>THYROCARE</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -6586,22 +6240,22 @@
         </is>
       </c>
       <c r="C173" s="4" t="n">
-        <v>291.15</v>
+        <v>533.6</v>
       </c>
       <c r="D173" s="4" t="n">
-        <v>42.43</v>
+        <v>36</v>
       </c>
       <c r="E173" s="4" t="n">
-        <v>40.45</v>
+        <v>51.79</v>
       </c>
       <c r="F173" s="4" t="n">
-        <v>45.92</v>
+        <v>62.06</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>ALKYLAMINE</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -6610,22 +6264,22 @@
         </is>
       </c>
       <c r="C174" s="4" t="n">
-        <v>1847.7</v>
+        <v>199.71</v>
       </c>
       <c r="D174" s="4" t="n">
-        <v>42.25</v>
+        <v>35.8</v>
       </c>
       <c r="E174" s="4" t="n">
-        <v>53.18</v>
+        <v>53.52</v>
       </c>
       <c r="F174" s="4" t="n">
-        <v>50.23</v>
+        <v>60.48</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>NETWORK18</t>
+          <t>KNRCON</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -6634,22 +6288,22 @@
         </is>
       </c>
       <c r="C175" s="4" t="n">
-        <v>26.75</v>
+        <v>113.29</v>
       </c>
       <c r="D175" s="4" t="n">
-        <v>42.07</v>
+        <v>35.7</v>
       </c>
       <c r="E175" s="4" t="n">
-        <v>33.41</v>
+        <v>38.15</v>
       </c>
       <c r="F175" s="4" t="n">
-        <v>33.55</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>GOKULAGRO</t>
+          <t>HCC</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -6658,22 +6312,22 @@
         </is>
       </c>
       <c r="C176" s="4" t="n">
-        <v>221.89</v>
+        <v>20.23</v>
       </c>
       <c r="D176" s="4" t="n">
-        <v>42.03</v>
+        <v>35.56</v>
       </c>
       <c r="E176" s="4" t="n">
-        <v>52.34</v>
+        <v>44.79</v>
       </c>
       <c r="F176" s="4" t="n">
-        <v>61.42</v>
+        <v>44.96</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>SUNTECK</t>
+          <t>TSFINV</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -6682,22 +6336,22 @@
         </is>
       </c>
       <c r="C177" s="4" t="n">
-        <v>283</v>
+        <v>409.15</v>
       </c>
       <c r="D177" s="4" t="n">
-        <v>41.84</v>
+        <v>35.47</v>
       </c>
       <c r="E177" s="4" t="n">
-        <v>38.52</v>
+        <v>46.47</v>
       </c>
       <c r="F177" s="4" t="n">
-        <v>39.25</v>
+        <v>52.81</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>HCC</t>
+          <t>ORKLAINDIA</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -6706,22 +6360,22 @@
         </is>
       </c>
       <c r="C178" s="4" t="n">
-        <v>21.26</v>
+        <v>537.2</v>
       </c>
       <c r="D178" s="4" t="n">
-        <v>41.82</v>
+        <v>35.29</v>
       </c>
       <c r="E178" s="4" t="n">
-        <v>47.7</v>
+        <v>36.46</v>
       </c>
       <c r="F178" s="4" t="n">
-        <v>45.89</v>
+        <v/>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>KIRLOSBROS</t>
+          <t>ZAGGLE</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -6730,22 +6384,22 @@
         </is>
       </c>
       <c r="C179" s="4" t="n">
-        <v>1771.9</v>
+        <v>171.73</v>
       </c>
       <c r="D179" s="4" t="n">
-        <v>41.7</v>
+        <v>35.16</v>
       </c>
       <c r="E179" s="4" t="n">
-        <v>48.52</v>
+        <v>31.02</v>
       </c>
       <c r="F179" s="4" t="n">
-        <v>52.43</v>
+        <v>36.68</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>FIEMIND</t>
+          <t>WAAREERTL</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -6754,22 +6408,22 @@
         </is>
       </c>
       <c r="C180" s="4" t="n">
-        <v>1965.5</v>
+        <v>808.8</v>
       </c>
       <c r="D180" s="4" t="n">
-        <v>41.6</v>
+        <v>35.14</v>
       </c>
       <c r="E180" s="4" t="n">
-        <v>39.98</v>
+        <v>34.48</v>
       </c>
       <c r="F180" s="4" t="n">
-        <v>54.87</v>
+        <v>38.38</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>SHARDACROP</t>
+          <t>RAYMONDLSL</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -6778,22 +6432,22 @@
         </is>
       </c>
       <c r="C181" s="4" t="n">
-        <v>749.6</v>
+        <v>627.7</v>
       </c>
       <c r="D181" s="4" t="n">
-        <v>41.59</v>
+        <v>34.98</v>
       </c>
       <c r="E181" s="4" t="n">
-        <v>37.03</v>
+        <v>34.52</v>
       </c>
       <c r="F181" s="4" t="n">
-        <v>48.88</v>
+        <v>23.04</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>MASTEK</t>
+          <t>GSFC</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -6802,22 +6456,22 @@
         </is>
       </c>
       <c r="C182" s="4" t="n">
-        <v>1582.8</v>
+        <v>146.9</v>
       </c>
       <c r="D182" s="4" t="n">
-        <v>41.58</v>
+        <v>34.84</v>
       </c>
       <c r="E182" s="4" t="n">
-        <v>43.23</v>
+        <v>39.33</v>
       </c>
       <c r="F182" s="4" t="n">
-        <v>40.8</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>MEDPLUS</t>
+          <t>STARCEMENT</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -6826,22 +6480,22 @@
         </is>
       </c>
       <c r="C183" s="4" t="n">
-        <v>654.9</v>
+        <v>178.39</v>
       </c>
       <c r="D183" s="4" t="n">
-        <v>41.44</v>
+        <v>34.74</v>
       </c>
       <c r="E183" s="4" t="n">
-        <v>29.13</v>
+        <v>29.43</v>
       </c>
       <c r="F183" s="4" t="n">
-        <v>38.69</v>
+        <v>41.74</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>JKLAKSHMI</t>
+          <t>VAIBHAVGBL</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -6850,22 +6504,22 @@
         </is>
       </c>
       <c r="C184" s="4" t="n">
-        <v>510.35</v>
+        <v>203.53</v>
       </c>
       <c r="D184" s="4" t="n">
-        <v>41.38</v>
+        <v>34.64</v>
       </c>
       <c r="E184" s="4" t="n">
-        <v>33.28</v>
+        <v>40.14</v>
       </c>
       <c r="F184" s="4" t="n">
-        <v>36.59</v>
+        <v>43.31</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>PARAS</t>
+          <t>AVL</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -6874,22 +6528,22 @@
         </is>
       </c>
       <c r="C185" s="4" t="n">
-        <v>1321</v>
+        <v>572.3</v>
       </c>
       <c r="D185" s="4" t="n">
-        <v>41.37</v>
+        <v>34.57</v>
       </c>
       <c r="E185" s="4" t="n">
-        <v>59.86</v>
+        <v>48.33</v>
       </c>
       <c r="F185" s="4" t="n">
-        <v>65.09</v>
+        <v>56.31</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>ATLANTAELE</t>
+          <t>GOKEX</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -6898,22 +6552,22 @@
         </is>
       </c>
       <c r="C186" s="4" t="n">
-        <v>1625.9</v>
+        <v>688.75</v>
       </c>
       <c r="D186" s="4" t="n">
-        <v>41.21</v>
+        <v>34.14</v>
       </c>
       <c r="E186" s="4" t="n">
-        <v>50.98</v>
+        <v>40.1</v>
       </c>
       <c r="F186" s="4" t="n">
-        <v/>
+        <v>47.11</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>SHAKTIPUMP</t>
+          <t>AWFIS</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -6922,22 +6576,22 @@
         </is>
       </c>
       <c r="C187" s="4" t="n">
-        <v>466.9</v>
+        <v>235.26</v>
       </c>
       <c r="D187" s="4" t="n">
-        <v>41.2</v>
+        <v>33.77</v>
       </c>
       <c r="E187" s="4" t="n">
-        <v>36.36</v>
+        <v>33.48</v>
       </c>
       <c r="F187" s="4" t="n">
-        <v>42.62</v>
+        <v>28.22</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>ORKLAINDIA</t>
+          <t>SANDUMA</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -6946,22 +6600,22 @@
         </is>
       </c>
       <c r="C188" s="4" t="n">
-        <v>555.95</v>
+        <v>177.67</v>
       </c>
       <c r="D188" s="4" t="n">
-        <v>41.14</v>
+        <v>33.77</v>
       </c>
       <c r="E188" s="4" t="n">
-        <v>39.63</v>
+        <v>37.65</v>
       </c>
       <c r="F188" s="4" t="n">
-        <v/>
+        <v>49.5</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>PNGJL</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -6970,22 +6624,22 @@
         </is>
       </c>
       <c r="C189" s="4" t="n">
-        <v>591.2</v>
+        <v>184</v>
       </c>
       <c r="D189" s="4" t="n">
-        <v>40.9</v>
+        <v>33.45</v>
       </c>
       <c r="E189" s="4" t="n">
-        <v>50.72</v>
+        <v>42.21</v>
       </c>
       <c r="F189" s="4" t="n">
-        <v>49.51</v>
+        <v>40.36</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>STARCEMENT</t>
+          <t>MOIL</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -6994,22 +6648,22 @@
         </is>
       </c>
       <c r="C190" s="4" t="n">
-        <v>186.61</v>
+        <v>232.66</v>
       </c>
       <c r="D190" s="4" t="n">
-        <v>40.8</v>
+        <v>33.26</v>
       </c>
       <c r="E190" s="4" t="n">
-        <v>34.12</v>
+        <v>29.72</v>
       </c>
       <c r="F190" s="4" t="n">
-        <v>43.89</v>
+        <v>39.05</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>TRIVENI</t>
+          <t>VIPIND</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -7018,22 +6672,22 @@
         </is>
       </c>
       <c r="C191" s="4" t="n">
-        <v>247.55</v>
+        <v>280.75</v>
       </c>
       <c r="D191" s="4" t="n">
-        <v>40.8</v>
+        <v>33.23</v>
       </c>
       <c r="E191" s="4" t="n">
-        <v>37.4</v>
+        <v>36.37</v>
       </c>
       <c r="F191" s="4" t="n">
-        <v>41.25</v>
+        <v>34.13</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>PRAJIND</t>
+          <t>OSWALPUMPS</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -7042,22 +6696,22 @@
         </is>
       </c>
       <c r="C192" s="4" t="n">
-        <v>315.9</v>
+        <v>264.25</v>
       </c>
       <c r="D192" s="4" t="n">
-        <v>40.49</v>
+        <v>33.06</v>
       </c>
       <c r="E192" s="4" t="n">
-        <v>42.71</v>
+        <v>28.85</v>
       </c>
       <c r="F192" s="4" t="n">
-        <v>41.9</v>
+        <v>25.82</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>RENUKA</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -7066,22 +6720,22 @@
         </is>
       </c>
       <c r="C193" s="4" t="n">
-        <v>1381.8</v>
+        <v>21.34</v>
       </c>
       <c r="D193" s="4" t="n">
-        <v>40.22</v>
+        <v>32.97</v>
       </c>
       <c r="E193" s="4" t="n">
-        <v>56.82</v>
+        <v>39.62</v>
       </c>
       <c r="F193" s="4" t="n">
-        <v>62.3</v>
+        <v>37.3</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>MOIL</t>
+          <t>TRIVENI</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -7090,22 +6744,22 @@
         </is>
       </c>
       <c r="C194" s="4" t="n">
-        <v>241.88</v>
+        <v>230.92</v>
       </c>
       <c r="D194" s="4" t="n">
-        <v>40.2</v>
+        <v>32.78</v>
       </c>
       <c r="E194" s="4" t="n">
-        <v>32.34</v>
+        <v>35.65</v>
       </c>
       <c r="F194" s="4" t="n">
-        <v>40.18</v>
+        <v>40.14</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>AURIONPRO</t>
+          <t>NETWORK18</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -7114,22 +6768,22 @@
         </is>
       </c>
       <c r="C195" s="4" t="n">
-        <v>669.7</v>
+        <v>25.43</v>
       </c>
       <c r="D195" s="4" t="n">
-        <v>40.05</v>
+        <v>32.65</v>
       </c>
       <c r="E195" s="4" t="n">
-        <v>33.65</v>
+        <v>30.42</v>
       </c>
       <c r="F195" s="4" t="n">
-        <v>37.62</v>
+        <v>32.85</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>TANLA</t>
+          <t>SKFINDIA</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -7138,22 +6792,22 @@
         </is>
       </c>
       <c r="C196" s="4" t="n">
-        <v>494.75</v>
+        <v>1450.2</v>
       </c>
       <c r="D196" s="4" t="n">
-        <v>39.76</v>
+        <v>32.31</v>
       </c>
       <c r="E196" s="4" t="n">
-        <v>42.73</v>
+        <v>33.79</v>
       </c>
       <c r="F196" s="4" t="n">
-        <v>43.32</v>
+        <v>31.81</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>VIYASH</t>
+          <t>SFL</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -7162,22 +6816,22 @@
         </is>
       </c>
       <c r="C197" s="4" t="n">
-        <v>244.35</v>
+        <v>616.65</v>
       </c>
       <c r="D197" s="4" t="n">
-        <v>39.64</v>
+        <v>32.27</v>
       </c>
       <c r="E197" s="4" t="n">
-        <v>48.9</v>
+        <v>44.6</v>
       </c>
       <c r="F197" s="4" t="n">
-        <v>58.34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>BECTORFOOD</t>
+          <t>CMSINFO</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -7186,22 +6840,22 @@
         </is>
       </c>
       <c r="C198" s="4" t="n">
-        <v>215.68</v>
+        <v>220.69</v>
       </c>
       <c r="D198" s="4" t="n">
-        <v>39.55</v>
+        <v>32.15</v>
       </c>
       <c r="E198" s="4" t="n">
-        <v>51</v>
+        <v>29.03</v>
       </c>
       <c r="F198" s="4" t="n">
-        <v>47.33</v>
+        <v>30.87</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>SENCO</t>
+          <t>RALLIS</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -7210,22 +6864,22 @@
         </is>
       </c>
       <c r="C199" s="4" t="n">
-        <v>331.1</v>
+        <v>199.69</v>
       </c>
       <c r="D199" s="4" t="n">
-        <v>39.31</v>
+        <v>32.07</v>
       </c>
       <c r="E199" s="4" t="n">
-        <v>46.07</v>
+        <v>30.44</v>
       </c>
       <c r="F199" s="4" t="n">
-        <v>48.15</v>
+        <v>40.72</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>WEBELSOLAR</t>
+          <t>DBREALTY</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -7234,22 +6888,22 @@
         </is>
       </c>
       <c r="C200" s="4" t="n">
-        <v>73.23</v>
+        <v>91.7</v>
       </c>
       <c r="D200" s="4" t="n">
-        <v>39.26</v>
+        <v>32.07</v>
       </c>
       <c r="E200" s="4" t="n">
-        <v>35.68</v>
+        <v>37.24</v>
       </c>
       <c r="F200" s="4" t="n">
-        <v>44.92</v>
+        <v>40.62</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>HEMIPROP</t>
+          <t>PRAJIND</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -7258,22 +6912,22 @@
         </is>
       </c>
       <c r="C201" s="4" t="n">
-        <v>120.36</v>
+        <v>303.25</v>
       </c>
       <c r="D201" s="4" t="n">
-        <v>39.25</v>
+        <v>31.89</v>
       </c>
       <c r="E201" s="4" t="n">
-        <v>36.72</v>
+        <v>39.29</v>
       </c>
       <c r="F201" s="4" t="n">
-        <v>43.51</v>
+        <v>41</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>OSWALPUMPS</t>
+          <t>ALKYLAMINE</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -7282,22 +6936,22 @@
         </is>
       </c>
       <c r="C202" s="4" t="n">
-        <v>274.95</v>
+        <v>1741.4</v>
       </c>
       <c r="D202" s="4" t="n">
-        <v>39.1</v>
+        <v>31.62</v>
       </c>
       <c r="E202" s="4" t="n">
-        <v>30.3</v>
+        <v>46.22</v>
       </c>
       <c r="F202" s="4" t="n">
-        <v>26.3</v>
+        <v>47.82</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>ANUP</t>
+          <t>METROPOLIS</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -7306,22 +6960,22 @@
         </is>
       </c>
       <c r="C203" s="4" t="n">
-        <v>1677.1</v>
+        <v>537.9</v>
       </c>
       <c r="D203" s="4" t="n">
-        <v>39.09</v>
+        <v>31.5</v>
       </c>
       <c r="E203" s="4" t="n">
-        <v>38.05</v>
+        <v>48.37</v>
       </c>
       <c r="F203" s="4" t="n">
-        <v>44.01</v>
+        <v>55.88</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>PRUDENT</t>
+          <t>CENTURYPLY</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -7330,22 +6984,22 @@
         </is>
       </c>
       <c r="C204" s="4" t="n">
-        <v>3097.9</v>
+        <v>666.45</v>
       </c>
       <c r="D204" s="4" t="n">
-        <v>38.9</v>
+        <v>31.49</v>
       </c>
       <c r="E204" s="4" t="n">
-        <v>52.37</v>
+        <v>31.79</v>
       </c>
       <c r="F204" s="4" t="n">
-        <v>58.2</v>
+        <v>44.31</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>ARVINDFASN</t>
+          <t>VIYASH</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -7354,22 +7008,22 @@
         </is>
       </c>
       <c r="C205" s="4" t="n">
-        <v>417.2</v>
+        <v>231.75</v>
       </c>
       <c r="D205" s="4" t="n">
-        <v>38.82</v>
+        <v>31.43</v>
       </c>
       <c r="E205" s="4" t="n">
-        <v>38.66</v>
+        <v>44.84</v>
       </c>
       <c r="F205" s="4" t="n">
-        <v>45.05</v>
+        <v>55.77</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>BAJAJELEC</t>
+          <t>BORORENEW</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -7378,22 +7032,22 @@
         </is>
       </c>
       <c r="C206" s="4" t="n">
-        <v>318.95</v>
+        <v>449.6</v>
       </c>
       <c r="D206" s="4" t="n">
-        <v>38.71</v>
+        <v>31.31</v>
       </c>
       <c r="E206" s="4" t="n">
-        <v>37.81</v>
+        <v>37</v>
       </c>
       <c r="F206" s="4" t="n">
-        <v>29.33</v>
+        <v>45.35</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>IXIGO</t>
+          <t>INOXGREEN</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -7402,22 +7056,22 @@
         </is>
       </c>
       <c r="C207" s="4" t="n">
-        <v>156.8</v>
+        <v>159</v>
       </c>
       <c r="D207" s="4" t="n">
-        <v>38.48</v>
+        <v>31.19</v>
       </c>
       <c r="E207" s="4" t="n">
-        <v>40.63</v>
+        <v>40.29</v>
       </c>
       <c r="F207" s="4" t="n">
-        <v>41.41</v>
+        <v>49.29</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>IFBIND</t>
+          <t>ASHAPURMIN</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -7426,22 +7080,22 @@
         </is>
       </c>
       <c r="C208" s="4" t="n">
-        <v>1225.2</v>
+        <v>489.95</v>
       </c>
       <c r="D208" s="4" t="n">
-        <v>37.92</v>
+        <v>30.88</v>
       </c>
       <c r="E208" s="4" t="n">
-        <v>44.37</v>
+        <v>34.09</v>
       </c>
       <c r="F208" s="4" t="n">
-        <v>47.46</v>
+        <v>48.55</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>ELECTCAST</t>
+          <t>VMART</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -7450,22 +7104,22 @@
         </is>
       </c>
       <c r="C209" s="4" t="n">
-        <v>72.34</v>
+        <v>746.1</v>
       </c>
       <c r="D209" s="4" t="n">
-        <v>37.92</v>
+        <v>30.84</v>
       </c>
       <c r="E209" s="4" t="n">
-        <v>45.39</v>
+        <v>49.38</v>
       </c>
       <c r="F209" s="4" t="n">
-        <v>42.91</v>
+        <v>51.05</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>VIKRAMSOLR</t>
+          <t>RELIGARE</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -7474,22 +7128,22 @@
         </is>
       </c>
       <c r="C210" s="4" t="n">
-        <v>160.31</v>
+        <v>224.59</v>
       </c>
       <c r="D210" s="4" t="n">
-        <v>37.8</v>
+        <v>30.68</v>
       </c>
       <c r="E210" s="4" t="n">
-        <v>34.81</v>
+        <v>42.1</v>
       </c>
       <c r="F210" s="4" t="n">
-        <v/>
+        <v>48.07</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>SAFARI</t>
+          <t>GOKULAGRO</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -7498,22 +7152,22 @@
         </is>
       </c>
       <c r="C211" s="4" t="n">
-        <v>1464.2</v>
+        <v>210.1</v>
       </c>
       <c r="D211" s="4" t="n">
-        <v>37.72</v>
+        <v>30.61</v>
       </c>
       <c r="E211" s="4" t="n">
-        <v>40.05</v>
+        <v>46.36</v>
       </c>
       <c r="F211" s="4" t="n">
-        <v>40.01</v>
+        <v>58.52</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>SANDUMA</t>
+          <t>SHARDACROP</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -7522,22 +7176,22 @@
         </is>
       </c>
       <c r="C212" s="4" t="n">
-        <v>183.11</v>
+        <v>709.2</v>
       </c>
       <c r="D212" s="4" t="n">
-        <v>37.56</v>
+        <v>30.56</v>
       </c>
       <c r="E212" s="4" t="n">
-        <v>40.78</v>
+        <v>33.93</v>
       </c>
       <c r="F212" s="4" t="n">
-        <v>51.05</v>
+        <v>47.43</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>RTNINDIA</t>
+          <t>PRSMJOHNSN</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -7546,22 +7200,22 @@
         </is>
       </c>
       <c r="C213" s="4" t="n">
-        <v>26.96</v>
+        <v>103.61</v>
       </c>
       <c r="D213" s="4" t="n">
-        <v>37.46</v>
+        <v>30.45</v>
       </c>
       <c r="E213" s="4" t="n">
-        <v>33.5</v>
+        <v>35.83</v>
       </c>
       <c r="F213" s="4" t="n">
-        <v>37.4</v>
+        <v>37.78</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>RATEGAIN</t>
+          <t>WEBELSOLAR</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -7570,22 +7224,22 @@
         </is>
       </c>
       <c r="C214" s="4" t="n">
-        <v>827.75</v>
+        <v>68.7</v>
       </c>
       <c r="D214" s="4" t="n">
-        <v>37.4</v>
+        <v>30.28</v>
       </c>
       <c r="E214" s="4" t="n">
-        <v>51.93</v>
+        <v>32.38</v>
       </c>
       <c r="F214" s="4" t="n">
-        <v>58.96</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>GHCL</t>
+          <t>RTNINDIA</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -7594,22 +7248,22 @@
         </is>
       </c>
       <c r="C215" s="4" t="n">
-        <v>419.8</v>
+        <v>25.32</v>
       </c>
       <c r="D215" s="4" t="n">
-        <v>37.03</v>
+        <v>30.15</v>
       </c>
       <c r="E215" s="4" t="n">
-        <v>37.63</v>
+        <v>30.4</v>
       </c>
       <c r="F215" s="4" t="n">
-        <v>40.75</v>
+        <v>36.52</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>SWSOLAR</t>
+          <t>ASHOKA</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -7618,22 +7272,22 @@
         </is>
       </c>
       <c r="C216" s="4" t="n">
-        <v>176.65</v>
+        <v>105.31</v>
       </c>
       <c r="D216" s="4" t="n">
-        <v>36.92</v>
+        <v>29.98</v>
       </c>
       <c r="E216" s="4" t="n">
-        <v>37.7</v>
+        <v>31.18</v>
       </c>
       <c r="F216" s="4" t="n">
-        <v>38.97</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>IMFA</t>
+          <t>KANSAINER</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -7642,22 +7296,22 @@
         </is>
       </c>
       <c r="C217" s="4" t="n">
-        <v>1230.4</v>
+        <v>175.27</v>
       </c>
       <c r="D217" s="4" t="n">
-        <v>36.9</v>
+        <v>29.87</v>
       </c>
       <c r="E217" s="4" t="n">
-        <v>41.63</v>
+        <v>33.67</v>
       </c>
       <c r="F217" s="4" t="n">
-        <v>56.12</v>
+        <v>35.48</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>SFL</t>
+          <t>V2RETAIL</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -7666,22 +7320,22 @@
         </is>
       </c>
       <c r="C218" s="4" t="n">
-        <v>634.6</v>
+        <v>201.39</v>
       </c>
       <c r="D218" s="4" t="n">
-        <v>36.73</v>
+        <v>29.74</v>
       </c>
       <c r="E218" s="4" t="n">
-        <v>46.7</v>
+        <v>40.9</v>
       </c>
       <c r="F218" s="4" t="n">
-        <v>44.9</v>
+        <v>56.72</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>ORIENTCEM</t>
+          <t>VIKRAMSOLR</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -7690,22 +7344,22 @@
         </is>
       </c>
       <c r="C219" s="4" t="n">
-        <v>122.16</v>
+        <v>154.35</v>
       </c>
       <c r="D219" s="4" t="n">
-        <v>36.7</v>
+        <v>29.66</v>
       </c>
       <c r="E219" s="4" t="n">
-        <v>29.98</v>
+        <v>33.01</v>
       </c>
       <c r="F219" s="4" t="n">
-        <v>33.86</v>
+        <v/>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>KIRLPNU</t>
+          <t>IMFA</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -7714,22 +7368,22 @@
         </is>
       </c>
       <c r="C220" s="4" t="n">
-        <v>691.95</v>
+        <v>1176.8</v>
       </c>
       <c r="D220" s="4" t="n">
-        <v>36.62</v>
+        <v>29.49</v>
       </c>
       <c r="E220" s="4" t="n">
-        <v>45.01</v>
+        <v>39.09</v>
       </c>
       <c r="F220" s="4" t="n">
-        <v>53.54</v>
+        <v>54.33</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>HGINFRA</t>
+          <t>IFBIND</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -7738,22 +7392,22 @@
         </is>
       </c>
       <c r="C221" s="4" t="n">
-        <v>453.1</v>
+        <v>1166.2</v>
       </c>
       <c r="D221" s="4" t="n">
-        <v>36.55</v>
+        <v>29.29</v>
       </c>
       <c r="E221" s="4" t="n">
-        <v>30.46</v>
+        <v>40.92</v>
       </c>
       <c r="F221" s="4" t="n">
-        <v>32.87</v>
+        <v>46.08</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>WEWORK</t>
+          <t>JYOTHYLAB</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -7762,22 +7416,22 @@
         </is>
       </c>
       <c r="C222" s="4" t="n">
-        <v>652.55</v>
+        <v>182.91</v>
       </c>
       <c r="D222" s="4" t="n">
-        <v>36.28</v>
+        <v>28.92</v>
       </c>
       <c r="E222" s="4" t="n">
-        <v>50.92</v>
+        <v>32.69</v>
       </c>
       <c r="F222" s="4" t="n">
-        <v/>
+        <v>35.75</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>NFL</t>
+          <t>PNCINFRA</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -7786,22 +7440,22 @@
         </is>
       </c>
       <c r="C223" s="4" t="n">
-        <v>66.67</v>
+        <v>138.16</v>
       </c>
       <c r="D223" s="4" t="n">
-        <v>36.21</v>
+        <v>28.8</v>
       </c>
       <c r="E223" s="4" t="n">
-        <v>34.52</v>
+        <v>26.66</v>
       </c>
       <c r="F223" s="4" t="n">
-        <v>41.2</v>
+        <v>34.61</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>KITEX</t>
+          <t>ADVENZYMES</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -7810,22 +7464,22 @@
         </is>
       </c>
       <c r="C224" s="4" t="n">
-        <v>117.68</v>
+        <v>274.25</v>
       </c>
       <c r="D224" s="4" t="n">
-        <v>36.2</v>
+        <v>28.44</v>
       </c>
       <c r="E224" s="4" t="n">
-        <v>30.9</v>
+        <v>35.27</v>
       </c>
       <c r="F224" s="4" t="n">
-        <v>41.88</v>
+        <v>43.71</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>ETHOSLTD</t>
+          <t>JLHL</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -7834,22 +7488,22 @@
         </is>
       </c>
       <c r="C225" s="4" t="n">
-        <v>2552.8</v>
+        <v>259.85</v>
       </c>
       <c r="D225" s="4" t="n">
-        <v>36.03</v>
+        <v>28.44</v>
       </c>
       <c r="E225" s="4" t="n">
-        <v>48.11</v>
+        <v>39.06</v>
       </c>
       <c r="F225" s="4" t="n">
-        <v>50.75</v>
+        <v>47.11</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>RCF</t>
+          <t>INDIAGLYCO</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -7858,22 +7512,22 @@
         </is>
       </c>
       <c r="C226" s="4" t="n">
-        <v>108.58</v>
+        <v>298.8</v>
       </c>
       <c r="D226" s="4" t="n">
-        <v>35.81</v>
+        <v>28.26</v>
       </c>
       <c r="E226" s="4" t="n">
-        <v>33.86</v>
+        <v>27.05</v>
       </c>
       <c r="F226" s="4" t="n">
-        <v>41.46</v>
+        <v>36</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>JYOTHYLAB</t>
+          <t>ANUP</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -7882,22 +7536,22 @@
         </is>
       </c>
       <c r="C227" s="4" t="n">
-        <v>191.07</v>
+        <v>1566.7</v>
       </c>
       <c r="D227" s="4" t="n">
-        <v>35.42</v>
+        <v>28.15</v>
       </c>
       <c r="E227" s="4" t="n">
-        <v>35.86</v>
+        <v>34.27</v>
       </c>
       <c r="F227" s="4" t="n">
-        <v>36.62</v>
+        <v>42.52</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>ROUTE</t>
+          <t>AHLUCONT</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -7906,22 +7560,22 @@
         </is>
       </c>
       <c r="C228" s="4" t="n">
-        <v>463</v>
+        <v>555.9</v>
       </c>
       <c r="D228" s="4" t="n">
-        <v>35.39</v>
+        <v>28.1</v>
       </c>
       <c r="E228" s="4" t="n">
-        <v>34.47</v>
+        <v>24.5</v>
       </c>
       <c r="F228" s="4" t="n">
-        <v>28.94</v>
+        <v>38.78</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>CRAMC</t>
+          <t>BAJAJELEC</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -7930,22 +7584,22 @@
         </is>
       </c>
       <c r="C229" s="4" t="n">
-        <v>230.45</v>
+        <v>299.8</v>
       </c>
       <c r="D229" s="4" t="n">
-        <v>34.58</v>
+        <v>28.05</v>
       </c>
       <c r="E229" s="4" t="n">
-        <v>36.63</v>
+        <v>33.29</v>
       </c>
       <c r="F229" s="4" t="n">
-        <v/>
+        <v>28.35</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>AVANTIFEED</t>
+          <t>FIEMIND</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -7954,22 +7608,22 @@
         </is>
       </c>
       <c r="C230" s="4" t="n">
-        <v>753.15</v>
+        <v>1794.8</v>
       </c>
       <c r="D230" s="4" t="n">
-        <v>33.96</v>
+        <v>27.95</v>
       </c>
       <c r="E230" s="4" t="n">
-        <v>32.62</v>
+        <v>33.91</v>
       </c>
       <c r="F230" s="4" t="n">
-        <v>47.54</v>
+        <v>49.48</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>CENTURYPLY</t>
+          <t>AVANTIFEED</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -7978,22 +7632,22 @@
         </is>
       </c>
       <c r="C231" s="4" t="n">
-        <v>694.45</v>
+        <v>711.55</v>
       </c>
       <c r="D231" s="4" t="n">
-        <v>33.71</v>
+        <v>27.46</v>
       </c>
       <c r="E231" s="4" t="n">
-        <v>36.41</v>
+        <v>30.44</v>
       </c>
       <c r="F231" s="4" t="n">
-        <v>46.26</v>
+        <v>46.13</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>VMART</t>
+          <t>JKLAKSHMI</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -8002,22 +7656,22 @@
         </is>
       </c>
       <c r="C232" s="4" t="n">
-        <v>760.1</v>
+        <v>476.6</v>
       </c>
       <c r="D232" s="4" t="n">
-        <v>33.15</v>
+        <v>27.4</v>
       </c>
       <c r="E232" s="4" t="n">
-        <v>52.2</v>
+        <v>28.65</v>
       </c>
       <c r="F232" s="4" t="n">
-        <v>51.83</v>
+        <v>34.92</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>AHLUCONT</t>
+          <t>ROUTE</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -8026,22 +7680,22 @@
         </is>
       </c>
       <c r="C233" s="4" t="n">
-        <v>585.55</v>
+        <v>436.4</v>
       </c>
       <c r="D233" s="4" t="n">
-        <v>32.82</v>
+        <v>26.97</v>
       </c>
       <c r="E233" s="4" t="n">
-        <v>26.76</v>
+        <v>30.79</v>
       </c>
       <c r="F233" s="4" t="n">
-        <v>39.55</v>
+        <v>28.07</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>VAIBHAVGBL</t>
+          <t>VGUARD</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -8050,22 +7704,22 @@
         </is>
       </c>
       <c r="C234" s="4" t="n">
-        <v>206.38</v>
+        <v>294.55</v>
       </c>
       <c r="D234" s="4" t="n">
-        <v>32.35</v>
+        <v>26.77</v>
       </c>
       <c r="E234" s="4" t="n">
-        <v>40.87</v>
+        <v>38.79</v>
       </c>
       <c r="F234" s="4" t="n">
-        <v>43.68</v>
+        <v>42.68</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>RALLIS</t>
+          <t>ORIENTCEM</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -8074,22 +7728,22 @@
         </is>
       </c>
       <c r="C235" s="4" t="n">
-        <v>200.38</v>
+        <v>115.91</v>
       </c>
       <c r="D235" s="4" t="n">
-        <v>32.16</v>
+        <v>26.69</v>
       </c>
       <c r="E235" s="4" t="n">
-        <v>30.65</v>
+        <v>26.22</v>
       </c>
       <c r="F235" s="4" t="n">
-        <v>40.81</v>
+        <v>32.93</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>CAMPUS</t>
+          <t>SWSOLAR</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -8098,22 +7752,22 @@
         </is>
       </c>
       <c r="C236" s="4" t="n">
-        <v>209.99</v>
+        <v>164.82</v>
       </c>
       <c r="D236" s="4" t="n">
-        <v>31.73</v>
+        <v>26.67</v>
       </c>
       <c r="E236" s="4" t="n">
-        <v>36.27</v>
+        <v>33.91</v>
       </c>
       <c r="F236" s="4" t="n">
-        <v>39.42</v>
+        <v>37.99</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>CERA</t>
+          <t>CAMPUS</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -8122,16 +7776,16 @@
         </is>
       </c>
       <c r="C237" s="4" t="n">
-        <v>5396.5</v>
+        <v>205.83</v>
       </c>
       <c r="D237" s="4" t="n">
-        <v>31.11</v>
+        <v>26.53</v>
       </c>
       <c r="E237" s="4" t="n">
-        <v>42.48</v>
+        <v>34.43</v>
       </c>
       <c r="F237" s="4" t="n">
-        <v>45.3</v>
+        <v>38.72</v>
       </c>
     </row>
     <row r="238">
@@ -8146,22 +7800,22 @@
         </is>
       </c>
       <c r="C238" s="4" t="n">
-        <v>7.5</v>
+        <v>7.06</v>
       </c>
       <c r="D238" s="4" t="n">
-        <v>31</v>
+        <v>26.43</v>
       </c>
       <c r="E238" s="4" t="n">
-        <v>23.77</v>
+        <v>22.5</v>
       </c>
       <c r="F238" s="4" t="n">
-        <v>29.88</v>
+        <v>29.29</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>BORORENEW</t>
+          <t>HAPPSTMNDS</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -8170,22 +7824,22 @@
         </is>
       </c>
       <c r="C239" s="4" t="n">
-        <v>455.15</v>
+        <v>304.7</v>
       </c>
       <c r="D239" s="4" t="n">
-        <v>30.88</v>
+        <v>26.41</v>
       </c>
       <c r="E239" s="4" t="n">
-        <v>37.66</v>
+        <v>34.62</v>
       </c>
       <c r="F239" s="4" t="n">
-        <v>45.74</v>
+        <v>28.22</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>ASHAPURMIN</t>
+          <t>HGINFRA</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -8194,22 +7848,22 @@
         </is>
       </c>
       <c r="C240" s="4" t="n">
-        <v>506.5</v>
+        <v>419.9</v>
       </c>
       <c r="D240" s="4" t="n">
-        <v>30.78</v>
+        <v>26.19</v>
       </c>
       <c r="E240" s="4" t="n">
-        <v>35.77</v>
+        <v>26.72</v>
       </c>
       <c r="F240" s="4" t="n">
-        <v>49.29</v>
+        <v>31.82</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>KANSAINER</t>
+          <t>NFL</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -8218,22 +7872,22 @@
         </is>
       </c>
       <c r="C241" s="4" t="n">
-        <v>180.63</v>
+        <v>63.85</v>
       </c>
       <c r="D241" s="4" t="n">
-        <v>30.74</v>
+        <v>26.19</v>
       </c>
       <c r="E241" s="4" t="n">
-        <v>36.51</v>
+        <v>29.93</v>
       </c>
       <c r="F241" s="4" t="n">
-        <v>36.52</v>
+        <v>39.94</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>VGUARD</t>
+          <t>AURIONPRO</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -8242,22 +7896,22 @@
         </is>
       </c>
       <c r="C242" s="4" t="n">
-        <v>304.35</v>
+        <v>607.8</v>
       </c>
       <c r="D242" s="4" t="n">
-        <v>30.54</v>
+        <v>25.78</v>
       </c>
       <c r="E242" s="4" t="n">
-        <v>42.65</v>
+        <v>28.24</v>
       </c>
       <c r="F242" s="4" t="n">
-        <v>44.17</v>
+        <v>35.96</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>EQUITASBNK</t>
+          <t>ARVINDFASN</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -8266,22 +7920,22 @@
         </is>
       </c>
       <c r="C243" s="4" t="n">
-        <v>67.03</v>
+        <v>379.7</v>
       </c>
       <c r="D243" s="4" t="n">
-        <v>30.26</v>
+        <v>25.55</v>
       </c>
       <c r="E243" s="4" t="n">
-        <v>42.89</v>
+        <v>31.38</v>
       </c>
       <c r="F243" s="4" t="n">
-        <v>49.34</v>
+        <v>41.02</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>GOKEX</t>
+          <t>CRAMC</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -8290,22 +7944,22 @@
         </is>
       </c>
       <c r="C244" s="4" t="n">
-        <v>689.6</v>
+        <v>216.52</v>
       </c>
       <c r="D244" s="4" t="n">
-        <v>29.68</v>
+        <v>25.09</v>
       </c>
       <c r="E244" s="4" t="n">
-        <v>40.79</v>
+        <v>31.44</v>
       </c>
       <c r="F244" s="4" t="n">
-        <v>47.13</v>
+        <v/>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>SANOFICONR</t>
+          <t>HEMIPROP</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
@@ -8314,22 +7968,22 @@
         </is>
       </c>
       <c r="C245" s="4" t="n">
-        <v>3945.3</v>
+        <v>111.5</v>
       </c>
       <c r="D245" s="4" t="n">
-        <v>29.59</v>
+        <v>24.87</v>
       </c>
       <c r="E245" s="4" t="n">
-        <v>33.39</v>
+        <v>30.92</v>
       </c>
       <c r="F245" s="4" t="n">
-        <v>37.81</v>
+        <v>41.08</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>RTNPOWER</t>
+          <t>SAFARI</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -8338,16 +7992,16 @@
         </is>
       </c>
       <c r="C246" s="4" t="n">
-        <v>7</v>
+        <v>1378.8</v>
       </c>
       <c r="D246" s="4" t="n">
-        <v>28.82</v>
+        <v>24.46</v>
       </c>
       <c r="E246" s="4" t="n">
-        <v>27.9</v>
+        <v>35.05</v>
       </c>
       <c r="F246" s="4" t="n">
-        <v>40.35</v>
+        <v>38.14</v>
       </c>
     </row>
     <row r="247">
@@ -8362,22 +8016,22 @@
         </is>
       </c>
       <c r="C247" s="4" t="n">
-        <v>297</v>
+        <v>285.35</v>
       </c>
       <c r="D247" s="4" t="n">
-        <v>28.24</v>
+        <v>24.28</v>
       </c>
       <c r="E247" s="4" t="n">
-        <v>38.79</v>
+        <v>36.58</v>
       </c>
       <c r="F247" s="4" t="n">
-        <v>33.27</v>
+        <v>32.56</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>INDIAGLYCO</t>
+          <t>GHCL</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -8386,22 +8040,22 @@
         </is>
       </c>
       <c r="C248" s="4" t="n">
-        <v>309.9</v>
+        <v>401.75</v>
       </c>
       <c r="D248" s="4" t="n">
-        <v>27.96</v>
+        <v>23.56</v>
       </c>
       <c r="E248" s="4" t="n">
-        <v>27.3</v>
+        <v>32.54</v>
       </c>
       <c r="F248" s="4" t="n">
-        <v>36.22</v>
+        <v>39.28</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>HAPPSTMNDS</t>
+          <t>SANOFICONR</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
@@ -8410,22 +8064,22 @@
         </is>
       </c>
       <c r="C249" s="4" t="n">
-        <v>310.5</v>
+        <v>3787.2</v>
       </c>
       <c r="D249" s="4" t="n">
-        <v>26.38</v>
+        <v>23.5</v>
       </c>
       <c r="E249" s="4" t="n">
-        <v>35.44</v>
+        <v>29.62</v>
       </c>
       <c r="F249" s="4" t="n">
-        <v>28.56</v>
+        <v>35.79</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>JLHL</t>
+          <t>RTNPOWER</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -8434,22 +8088,22 @@
         </is>
       </c>
       <c r="C250" s="4" t="n">
-        <v>265.65</v>
+        <v>6.74</v>
       </c>
       <c r="D250" s="4" t="n">
-        <v>23.71</v>
+        <v>23.48</v>
       </c>
       <c r="E250" s="4" t="n">
-        <v>40.85</v>
+        <v>26.21</v>
       </c>
       <c r="F250" s="4" t="n">
-        <v>47.92</v>
+        <v>39.63</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>EUREKAFORB</t>
+          <t>CERA</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
@@ -8458,22 +8112,22 @@
         </is>
       </c>
       <c r="C251" s="4" t="n">
-        <v>370.85</v>
+        <v>5096.5</v>
       </c>
       <c r="D251" s="4" t="n">
-        <v>23</v>
+        <v>22.18</v>
       </c>
       <c r="E251" s="4" t="n">
-        <v>31.12</v>
+        <v>36.86</v>
       </c>
       <c r="F251" s="4" t="n">
-        <v>34.64</v>
+        <v>43.22</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>PNCINFRA</t>
+          <t>EUREKAFORB</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
@@ -8482,16 +8136,16 @@
         </is>
       </c>
       <c r="C252" s="4" t="n">
-        <v>135.45</v>
+        <v>352.5</v>
       </c>
       <c r="D252" s="4" t="n">
-        <v>17.6</v>
+        <v>18.38</v>
       </c>
       <c r="E252" s="4" t="n">
-        <v>24.78</v>
+        <v>28.29</v>
       </c>
       <c r="F252" s="4" t="n">
-        <v>33.95</v>
+        <v>33.36</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Micro250_stocks.xlsx
+++ b/docs/Micro250_stocks.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -551,7 +551,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AXISCADES</t>
+          <t>CUPID</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -560,37 +560,37 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>2307.3</v>
+        <v>366.1</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>78.14</v>
+        <v>78.68000000000001</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>71.47</v>
+        <v>87</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>70.70999999999999</v>
+        <v>95.03</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>30.03</v>
+        <v>25.84</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1688.43</v>
+        <v>205.63</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>1638.95</v>
+        <v>182.17</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>260846</v>
+        <v>22664031</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>9833</v>
+        <v>49228</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>SKYGOLD</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -599,37 +599,37 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>955.35</v>
+        <v>921</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>71.81</v>
+        <v>75.44</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>78.17</v>
+        <v>78.83</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>89.70999999999999</v>
+        <v>84.51000000000001</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>23.49</v>
+        <v>25.74</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>547.64</v>
+        <v>625.62</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>483.82</v>
+        <v>578.87</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>1792855</v>
+        <v>1099816</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>49110</v>
+        <v>14264</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>OPTIEMUS</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -638,37 +638,37 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>803.7</v>
+        <v>1015.2</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>67.98</v>
+        <v>75.42</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>76.31</v>
+        <v>80.01000000000001</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>64.28</v>
+        <v>90.41</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>40.07</v>
+        <v>38.81</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>543.85</v>
+        <v>570.24</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>534.73</v>
+        <v>502.31</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>1122893</v>
+        <v>2020749</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>7267</v>
+        <v>52187</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>PCJEWELLER</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -677,37 +677,37 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>968.5</v>
+        <v>14.81</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>67.66</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>71.58</v>
+        <v>67.75</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>64.11</v>
+        <v>62.1</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>28.78</v>
+        <v>28.51</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>768.5599999999999</v>
+        <v>10.83</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>760.75</v>
+        <v>10.82</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>713151</v>
+        <v>379285700</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>8887</v>
+        <v>14525</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>GMMPFAUDLR</t>
+          <t>BBOX</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -716,37 +716,37 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1443.4</v>
+        <v>892.1</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>67.37</v>
+        <v>64.81</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>76.43000000000001</v>
+        <v>60.83</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>59.23</v>
+        <v>64.14</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>67.05</v>
+        <v>37.82</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1030.95</v>
+        <v>758.89</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>1024.02</v>
+        <v>729.83</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>443563</v>
+        <v>923781</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>6510</v>
+        <v>15844</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>CUPID</t>
+          <t>MANORAMA</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>312.5</v>
+        <v>2043.4</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>67.16</v>
+        <v>64.56</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>82.45999999999999</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>93.91</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>23.08</v>
+        <v>25.13</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>198.15</v>
+        <v>1662.94</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>175.93</v>
+        <v>1603.73</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>19648932</v>
+        <v>232032</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>41927</v>
+        <v>12898</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>SHILPAMED</t>
+          <t>OPTIEMUS</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -794,37 +794,37 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1064.1</v>
+        <v>815.85</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>67.14</v>
+        <v>61.62</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>91.48</v>
+        <v>76.8</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>86.2</v>
+        <v>64.69</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>35.76</v>
+        <v>43.35</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>671.72</v>
+        <v>562.1</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>618.11</v>
+        <v>549.08</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1150119</v>
+        <v>1480378</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>20810</v>
+        <v>7356</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENGG</t>
+          <t>PGIL</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -833,37 +833,37 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>98.31</v>
+        <v>1281.1</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>64.08</v>
+        <v>59.2</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>68.73</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>67.39</v>
+        <v>77.13</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>31.4</v>
+        <v>34.86</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>77.75</v>
+        <v>1016.27</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>74.65000000000001</v>
+        <v>966.01</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>10180605</v>
+        <v>220268</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>15224</v>
+        <v>11835</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>EMIL</t>
+          <t>GPPL</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -872,37 +872,37 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>204.05</v>
+        <v>167.9</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>63.59</v>
+        <v>58.19</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>75.14</v>
+        <v>64.58</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>64.03</v>
+        <v>56.32</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>30.99</v>
+        <v>26.15</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>147.16</v>
+        <v>156.5</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>142.09</v>
+        <v>156.29</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3275903</v>
+        <v>1592132</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>7849</v>
+        <v>8120</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>AXISCADES</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>384.7</v>
+        <v>2082.3</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>62.74</v>
+        <v>57.91</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>75.79000000000001</v>
+        <v>61.22</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>68.11</v>
+        <v>65.54000000000001</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>22.38</v>
+        <v>34.16</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>318.88</v>
+        <v>1715.68</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>309.75</v>
+        <v>1659.54</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1721789</v>
+        <v>281632</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>14807</v>
+        <v>8857</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>GPPL</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -950,37 +950,37 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>165.88</v>
+        <v>1748.1</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>60.37</v>
+        <v>57.86</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>62.75</v>
+        <v>68.45</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>55.57</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>24.68</v>
+        <v>30.12</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>155.69</v>
+        <v>1395.12</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>155.68</v>
+        <v>1316.55</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1744222</v>
+        <v>320065</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>8023</v>
+        <v>23202</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>AKUMS</t>
+          <t>TDPOWERSYS</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -989,37 +989,37 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>813.1</v>
+        <v>793.75</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>59.91</v>
+        <v>56.18</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>76.51000000000001</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>67.16</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>39.93</v>
+        <v>31.56</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>650.3099999999999</v>
+        <v>619.3200000000001</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>624.54</v>
+        <v>577.04</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>316640</v>
+        <v>2852428</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>12490</v>
+        <v>24900</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>QPOWER</t>
+          <t>SHILPAMED</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1028,37 +1028,37 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1564.6</v>
+        <v>1021.7</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>59.59</v>
+        <v>55.64</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>67.22</v>
+        <v>83.22</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>70.20999999999999</v>
+        <v>83.28</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>21.27</v>
+        <v>38.12</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1203.08</v>
+        <v>690.71</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1135.16</v>
+        <v>634.27</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>328136</v>
+        <v>1060661</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>12043</v>
+        <v>19983</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>NEOGEN</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1067,37 +1067,37 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2407.1</v>
+        <v>377.65</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>57.42</v>
+        <v>55.25</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>67.58</v>
+        <v>71.34</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>65.7</v>
+        <v>66.5</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>23.6</v>
+        <v>26.19</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1956.96</v>
+        <v>321.9</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1877.55</v>
+        <v>312.34</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>189624</v>
+        <v>1850914</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>7240</v>
+        <v>14528</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>SHAREINDIA</t>
+          <t>AZAD</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1106,37 +1106,37 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>205.09</v>
+        <v>2910.2</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>57.31</v>
+        <v>54.97</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>63.36</v>
+        <v>68.03</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>53.94</v>
+        <v>72.41</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>43.71</v>
+        <v>24.3</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>168.15</v>
+        <v>2346.87</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>166.57</v>
+        <v>2230.1</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>5976567</v>
+        <v>813845</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>4525</v>
+        <v>18795</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>PGIL</t>
+          <t>QPOWER</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1145,37 +1145,37 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1263</v>
+        <v>1547.4</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>56.98</v>
+        <v>53.97</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>66.98999999999999</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>75.73</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>31.75</v>
+        <v>21.35</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1002.77</v>
+        <v>1221.72</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>954.16</v>
+        <v>1150.4</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>208132</v>
+        <v>352319</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>11787</v>
+        <v>11984</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>AZAD</t>
+          <t>NEOGEN</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1184,37 +1184,37 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2860.9</v>
+        <v>2378.2</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>56.14</v>
+        <v>53.22</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>66.73</v>
+        <v>65.83</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>70.97</v>
+        <v>64.88</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>21.9</v>
+        <v>24.94</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2314.98</v>
+        <v>1975.68</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2202.92</v>
+        <v>1893.35</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>747122</v>
+        <v>184807</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>18425</v>
+        <v>7145</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>EDELWEISS</t>
+          <t>LLOYDSENGG</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1223,37 +1223,37 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>137.9</v>
+        <v>94.42</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>56</v>
+        <v>53.1</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>65.09</v>
+        <v>63.71</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>63.38</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>22.39</v>
+        <v>32.34</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>120.63</v>
+        <v>78.83</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>118.52</v>
+        <v>75.56</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>9027923</v>
+        <v>11398857</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>12996</v>
+        <v>14631</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>SKYGOLD</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1262,37 +1262,37 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>810.65</v>
+        <v>592.7</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>55.8</v>
+        <v>50.98</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>72.55</v>
+        <v>63.39</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>81.83</v>
+        <v>58.59</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>20.25</v>
+        <v>25.62</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>612.55</v>
+        <v>523.42</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>567.54</v>
+        <v>514.04</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>832298</v>
+        <v>1085018</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>12498</v>
+        <v>8709</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>SANSERA</t>
+          <t>WELENT</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1301,37 +1301,37 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>4276.6</v>
+        <v>735.9</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>53.13</v>
+        <v>50.69</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>70.8</v>
+        <v>62.62</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>80.55</v>
+        <v>68.52</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>28.83</v>
+        <v>29.35</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>3222.1</v>
+        <v>614.98</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2981.58</v>
+        <v>593.95</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>264491</v>
+        <v>719326</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>26582</v>
+        <v>9980</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>MAHSEAMLES</t>
+          <t>EMIL</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1340,37 +1340,37 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>698.75</v>
+        <v>191.17</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>53.02</v>
+        <v>50.05</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>64.87</v>
+        <v>66.76000000000001</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>56.9</v>
+        <v>60.62</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>41.11</v>
+        <v>34.72</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>622.9400000000001</v>
+        <v>149.99</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>616.62</v>
+        <v>144.47</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>471878</v>
+        <v>4121337</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>9317</v>
+        <v>7355</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>YATHARTH</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1379,37 +1379,37 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>589.15</v>
+        <v>1022.2</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>52.47</v>
+        <v>49</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>62.19</v>
+        <v>61.7</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>58.18</v>
+        <v>68.44</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>31.27</v>
+        <v>34.56</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>518.95</v>
+        <v>872.8200000000001</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>510.5</v>
+        <v>838.74</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1016302</v>
+        <v>740612</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>8614</v>
+        <v>9849</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>SANSERA</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1418,37 +1418,37 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1670</v>
+        <v>4124.7</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>52.09</v>
+        <v>47.53</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>64.78</v>
+        <v>66.62</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>78.15000000000001</v>
+        <v>77.14</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>23.81</v>
+        <v>25.13</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1377.18</v>
+        <v>3264.46</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1300.93</v>
+        <v>3019.41</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>278799</v>
+        <v>288915</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>22059</v>
+        <v>25745</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>ALIVUS</t>
+          <t>ICIL</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1457,37 +1457,37 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1374.2</v>
+        <v>436.3</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>51.63</v>
+        <v>47.41</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>68.88</v>
+        <v>61.85</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>71.58</v>
+        <v>61.78</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>20.48</v>
+        <v>30.54</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1186.46</v>
+        <v>379.46</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1148.59</v>
+        <v>363.36</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>168329</v>
+        <v>643788</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>16942</v>
+        <v>8641</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>GMMPFAUDLR</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1496,37 +1496,37 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2280.2</v>
+        <v>1299.8</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>50.97</v>
+        <v>46.39</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>69.23</v>
+        <v>63.66</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>79.27</v>
+        <v>54.76</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>22.05</v>
+        <v>52.68</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1733.33</v>
+        <v>1051.14</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1603.32</v>
+        <v>1040.18</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>627475</v>
+        <v>463958</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>15196</v>
+        <v>5844</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>ICIL</t>
+          <t>ENTERO</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1535,499 +1535,31 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>443.65</v>
+        <v>1676.2</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>50.88</v>
+        <v>45.34</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>64.28</v>
+        <v>63.16</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>62.72</v>
+        <v>66.34</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>23.49</v>
+        <v>28.67</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>376.03</v>
+        <v>1405.05</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>360.37</v>
+        <v>1358.04</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>657786</v>
+        <v>265690</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>8809</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>YATHARTH</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>1033.7</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>50.55</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>63.06</v>
-      </c>
-      <c r="F28" s="4" t="n">
-        <v>69.26000000000001</v>
-      </c>
-      <c r="G28" s="4" t="n">
-        <v>46.32</v>
-      </c>
-      <c r="H28" s="4" t="n">
-        <v>865.16</v>
-      </c>
-      <c r="I28" s="4" t="n">
-        <v>832.0599999999999</v>
-      </c>
-      <c r="J28" s="4" t="n">
-        <v>784897</v>
-      </c>
-      <c r="K28" s="4" t="n">
-        <v>9973</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>MARKSANS</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>325.6</v>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>50.09</v>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>66.59999999999999</v>
-      </c>
-      <c r="F29" s="4" t="n">
-        <v>67.3</v>
-      </c>
-      <c r="G29" s="4" t="n">
-        <v>22.56</v>
-      </c>
-      <c r="H29" s="4" t="n">
-        <v>265.19</v>
-      </c>
-      <c r="I29" s="4" t="n">
-        <v>253.64</v>
-      </c>
-      <c r="J29" s="4" t="n">
-        <v>2319541</v>
-      </c>
-      <c r="K29" s="4" t="n">
-        <v>14639</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>KTKBANK</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>321.6</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>49.28</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>66.23999999999999</v>
-      </c>
-      <c r="F30" s="4" t="n">
-        <v>73.56</v>
-      </c>
-      <c r="G30" s="4" t="n">
-        <v>28.99</v>
-      </c>
-      <c r="H30" s="4" t="n">
-        <v>276.45</v>
-      </c>
-      <c r="I30" s="4" t="n">
-        <v>263.97</v>
-      </c>
-      <c r="J30" s="4" t="n">
-        <v>2114776</v>
-      </c>
-      <c r="K30" s="4" t="n">
-        <v>12249</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>LUMAXTECH</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>1978.9</v>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>48.81</v>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>60.35</v>
-      </c>
-      <c r="F31" s="4" t="n">
-        <v>68.65000000000001</v>
-      </c>
-      <c r="G31" s="4" t="n">
-        <v>28.04</v>
-      </c>
-      <c r="H31" s="4" t="n">
-        <v>1723.65</v>
-      </c>
-      <c r="I31" s="4" t="n">
-        <v>1649.78</v>
-      </c>
-      <c r="J31" s="4" t="n">
-        <v>146626</v>
-      </c>
-      <c r="K31" s="4" t="n">
-        <v>13420</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>VARROC</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>830.6</v>
-      </c>
-      <c r="D32" s="4" t="n">
-        <v>48.69</v>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>69.01000000000001</v>
-      </c>
-      <c r="F32" s="4" t="n">
-        <v>67.42</v>
-      </c>
-      <c r="G32" s="4" t="n">
-        <v>27.89</v>
-      </c>
-      <c r="H32" s="4" t="n">
-        <v>696.85</v>
-      </c>
-      <c r="I32" s="4" t="n">
-        <v>671.16</v>
-      </c>
-      <c r="J32" s="4" t="n">
-        <v>340192</v>
-      </c>
-      <c r="K32" s="4" t="n">
-        <v>12667</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>MANORAMA</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>1880.3</v>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>47.37</v>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>62.98</v>
-      </c>
-      <c r="F33" s="4" t="n">
-        <v>69.37</v>
-      </c>
-      <c r="G33" s="4" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="H33" s="4" t="n">
-        <v>1646.98</v>
-      </c>
-      <c r="I33" s="4" t="n">
-        <v>1589.8</v>
-      </c>
-      <c r="J33" s="4" t="n">
-        <v>219058</v>
-      </c>
-      <c r="K33" s="4" t="n">
-        <v>11930</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>ASKAUTOLTD</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v>618.15</v>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>47.17</v>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="F34" s="4" t="n">
-        <v>65.54000000000001</v>
-      </c>
-      <c r="G34" s="4" t="n">
-        <v>35.92</v>
-      </c>
-      <c r="H34" s="4" t="n">
-        <v>534.98</v>
-      </c>
-      <c r="I34" s="4" t="n">
-        <v>519.33</v>
-      </c>
-      <c r="J34" s="4" t="n">
-        <v>322794</v>
-      </c>
-      <c r="K34" s="4" t="n">
-        <v>12183</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>WELENT</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="n">
-        <v>724.45</v>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>46.89</v>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>61.14</v>
-      </c>
-      <c r="F35" s="4" t="n">
-        <v>67.26000000000001</v>
-      </c>
-      <c r="G35" s="4" t="n">
-        <v>34.58</v>
-      </c>
-      <c r="H35" s="4" t="n">
-        <v>609.9</v>
-      </c>
-      <c r="I35" s="4" t="n">
-        <v>589.46</v>
-      </c>
-      <c r="J35" s="4" t="n">
-        <v>964948</v>
-      </c>
-      <c r="K35" s="4" t="n">
-        <v>9778</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>DIACABS</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="n">
-        <v>345</v>
-      </c>
-      <c r="D36" s="4" t="n">
-        <v>46.53</v>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>70.70999999999999</v>
-      </c>
-      <c r="F36" s="4" t="n">
-        <v>78.53</v>
-      </c>
-      <c r="G36" s="4" t="n">
-        <v>23.26</v>
-      </c>
-      <c r="H36" s="4" t="n">
-        <v>261.9</v>
-      </c>
-      <c r="I36" s="4" t="n">
-        <v>240.7</v>
-      </c>
-      <c r="J36" s="4" t="n">
-        <v>908428</v>
-      </c>
-      <c r="K36" s="4" t="n">
-        <v>20891</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>TMB</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>872.05</v>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>45.96</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>65.34</v>
-      </c>
-      <c r="F37" s="4" t="n">
-        <v>71.67</v>
-      </c>
-      <c r="G37" s="4" t="n">
-        <v>23.08</v>
-      </c>
-      <c r="H37" s="4" t="n">
-        <v>772.58</v>
-      </c>
-      <c r="I37" s="4" t="n">
-        <v>733.42</v>
-      </c>
-      <c r="J37" s="4" t="n">
-        <v>166317</v>
-      </c>
-      <c r="K37" s="4" t="n">
-        <v>14014</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>ENTERO</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>1680.8</v>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>45.88</v>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>63.11</v>
-      </c>
-      <c r="F38" s="4" t="n">
-        <v>66.56999999999999</v>
-      </c>
-      <c r="G38" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="H38" s="4" t="n">
-        <v>1385.02</v>
-      </c>
-      <c r="I38" s="4" t="n">
-        <v>1340.97</v>
-      </c>
-      <c r="J38" s="4" t="n">
-        <v>382846</v>
-      </c>
-      <c r="K38" s="4" t="n">
-        <v>7290</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>RBA</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>92.22</v>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>45.29</v>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>61.01</v>
-      </c>
-      <c r="F39" s="4" t="n">
-        <v>55.67</v>
-      </c>
-      <c r="G39" s="4" t="n">
-        <v>24.99</v>
-      </c>
-      <c r="H39" s="4" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="I39" s="4" t="n">
-        <v>78.81999999999999</v>
-      </c>
-      <c r="J39" s="4" t="n">
-        <v>3388589</v>
-      </c>
-      <c r="K39" s="4" t="n">
-        <v>6552</v>
+        <v>7295</v>
       </c>
     </row>
   </sheetData>
@@ -2058,18 +1590,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId38"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2127,7 +1647,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>DYNAMATECH</t>
+          <t>CUPID</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2136,22 +1656,22 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>13756</v>
+        <v>366.1</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>79.88</v>
+        <v>78.68000000000001</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>71.03</v>
+        <v>87</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>73.40000000000001</v>
+        <v>95.03</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>AXISCADES</t>
+          <t>SKYGOLD</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2160,22 +1680,22 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>2307.3</v>
+        <v>921</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>78.14</v>
+        <v>75.44</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>71.47</v>
+        <v>78.83</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>70.70999999999999</v>
+        <v>84.51000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>AEQUS</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2184,22 +1704,22 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>275.05</v>
+        <v>1015.2</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>72.36</v>
+        <v>75.42</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>69.36</v>
+        <v>80.01000000000001</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v/>
+        <v>90.41</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>PCJEWELLER</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2208,16 +1728,16 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>955.35</v>
+        <v>14.81</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>71.81</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>78.17</v>
+        <v>67.75</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>89.70999999999999</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="6">
@@ -2232,13 +1752,13 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>230.07</v>
+        <v>239.75</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>69.62</v>
+        <v>67.28</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>72.91</v>
+        <v>74.52</v>
       </c>
       <c r="F6" s="4" t="n">
         <v/>
@@ -2247,7 +1767,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>OPTIEMUS</t>
+          <t>BBOX</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2256,22 +1776,22 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>803.7</v>
+        <v>892.1</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>67.98</v>
+        <v>64.81</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>76.31</v>
+        <v>60.83</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>64.28</v>
+        <v>64.14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>MANORAMA</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2280,22 +1800,22 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>968.5</v>
+        <v>2043.4</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>67.66</v>
+        <v>64.56</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>71.58</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>64.11</v>
+        <v>72.31999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>GMMPFAUDLR</t>
+          <t>ALOKINDS</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2304,22 +1824,22 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1443.4</v>
+        <v>9</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>67.37</v>
+        <v>63.71</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>76.43000000000001</v>
+        <v>38.52</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>59.23</v>
+        <v>35.33</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>CUPID</t>
+          <t>OPTIEMUS</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2328,22 +1848,22 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>312.5</v>
+        <v>815.85</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>67.16</v>
+        <v>61.62</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>82.45999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>93.91</v>
+        <v>64.69</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SHILPAMED</t>
+          <t>AEQUS</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2352,22 +1872,22 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1064.1</v>
+        <v>273.5</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>67.14</v>
+        <v>60.72</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>91.48</v>
+        <v>68.84</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>86.2</v>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>GREAVESCOT</t>
+          <t>DIACABS</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2376,22 +1896,22 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>225.98</v>
+        <v>380.95</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>64.31999999999999</v>
+        <v>60.66</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>58.32</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>56.06</v>
+        <v>82.55</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENGG</t>
+          <t>MTARTECH</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -2400,22 +1920,22 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>98.31</v>
+        <v>7781.5</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>64.08</v>
+        <v>60.14</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>68.73</v>
+        <v>63.91</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>67.39</v>
+        <v>72.62</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>EMIL</t>
+          <t>DYNAMATECH</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -2424,22 +1944,22 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>204.05</v>
+        <v>13321</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>63.59</v>
+        <v>60.08</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>75.14</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>64.03</v>
+        <v>71.06</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>VMART</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -2448,22 +1968,22 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>384.7</v>
+        <v>821.95</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>62.74</v>
+        <v>59.77</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>75.79000000000001</v>
+        <v>59.6</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>68.11</v>
+        <v>54.91</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>MTARTECH</t>
+          <t>JAMNAAUTO</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -2472,22 +1992,22 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>7797</v>
+        <v>142.67</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>62.62</v>
+        <v>59.26</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>63.94</v>
+        <v>58</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>72.75</v>
+        <v>61.08</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>TEXRAIL</t>
+          <t>PGIL</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -2496,22 +2016,22 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>126.86</v>
+        <v>1281.1</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>61.91</v>
+        <v>59.2</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>63.42</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>49.3</v>
+        <v>77.13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GPPL</t>
+          <t>JAIBALAJI</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -2520,22 +2040,22 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>165.88</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>60.37</v>
+        <v>58.34</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>62.75</v>
+        <v>50.5</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>55.57</v>
+        <v>43.26</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>AKUMS</t>
+          <t>GPPL</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2544,22 +2064,22 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>813.1</v>
+        <v>167.9</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>59.91</v>
+        <v>58.19</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>76.51000000000001</v>
+        <v>64.58</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>67.16</v>
+        <v>56.32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>TRANSRAILL</t>
+          <t>CELLO</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -2568,22 +2088,22 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>474.9</v>
+        <v>364.95</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>59.91</v>
+        <v>57.96</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>46.76</v>
+        <v>46.77</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>44.6</v>
+        <v>33.38</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>CAPILLARY</t>
+          <t>AXISCADES</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -2592,22 +2112,22 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>554.7</v>
+        <v>2082.3</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>59.76</v>
+        <v>57.91</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>53.6</v>
+        <v>61.22</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v/>
+        <v>65.54000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>QPOWER</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -2616,22 +2136,22 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1564.6</v>
+        <v>1748.1</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>59.59</v>
+        <v>57.86</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>67.22</v>
+        <v>68.45</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>70.20999999999999</v>
+        <v>81.29000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENT</t>
+          <t>CAPILLARY</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -2640,22 +2160,22 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>77.95</v>
+        <v>566.65</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>59.24</v>
+        <v>57.83</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>56.25</v>
+        <v>55.43</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>59.06</v>
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GMRP&amp;UI</t>
+          <t>MASTEK</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -2664,16 +2184,16 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>101.87</v>
+        <v>1679.9</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>59.03</v>
+        <v>56.62</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>50.79</v>
+        <v>48.85</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>51.28</v>
+        <v>43.39</v>
       </c>
     </row>
     <row r="25">
@@ -2688,22 +2208,22 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>792.15</v>
+        <v>793.75</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>58.08</v>
+        <v>56.18</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>68.23</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>79.77</v>
+        <v>79.81999999999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>WESTLIFE</t>
+          <t>SHILPAMED</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -2712,22 +2232,22 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>588.05</v>
+        <v>1021.7</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>57.66</v>
+        <v>55.64</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>60.12</v>
+        <v>83.22</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>47.49</v>
+        <v>83.28</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>NEOGEN</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -2736,22 +2256,22 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2407.1</v>
+        <v>377.65</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>57.42</v>
+        <v>55.25</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>67.58</v>
+        <v>71.34</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>65.7</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>KPIGREEN</t>
+          <t>AZAD</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -2760,22 +2280,22 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>345.6</v>
+        <v>2910.2</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>57.38</v>
+        <v>54.97</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>44.63</v>
+        <v>68.03</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>45.51</v>
+        <v>72.41</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>SHAREINDIA</t>
+          <t>MIDHANI</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -2784,22 +2304,22 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>205.09</v>
+        <v>440.5</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>57.31</v>
+        <v>54.45</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>63.36</v>
+        <v>58.26</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>53.94</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>IIFLCAPS</t>
+          <t>GRWRHITECH</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -2808,22 +2328,22 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>345.6</v>
+        <v>6997.5</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>56.99</v>
+        <v>53.98</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>57.2</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>58.92</v>
+        <v>68.72</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>PGIL</t>
+          <t>QPOWER</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -2832,22 +2352,22 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1263</v>
+        <v>1547.4</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>56.98</v>
+        <v>53.97</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>66.98999999999999</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>75.73</v>
+        <v>69.54000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>SUDARSCHEM</t>
+          <t>SOUTHBANK</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -2856,22 +2376,22 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1241.5</v>
+        <v>47.91</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>56.37</v>
+        <v>53.92</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>65.41</v>
+        <v>59.58</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>59.86</v>
+        <v>71.13</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>AZAD</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -2880,22 +2400,22 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>2860.9</v>
+        <v>328.2</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>56.14</v>
+        <v>53.54</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>66.73</v>
+        <v>66.84</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>70.97</v>
+        <v>75.98999999999999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>PRIVISCL</t>
+          <t>NEOGEN</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -2904,22 +2424,22 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>3573</v>
+        <v>2378.2</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>56.03</v>
+        <v>53.22</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>57.23</v>
+        <v>65.83</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>68.08</v>
+        <v>64.88</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>EDELWEISS</t>
+          <t>WESTLIFE</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -2928,22 +2448,22 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>137.9</v>
+        <v>580.6</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>56</v>
+        <v>53.18</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>65.09</v>
+        <v>58.92</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>63.38</v>
+        <v>46.73</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>SKYGOLD</t>
+          <t>TRANSRAILL</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -2952,22 +2472,22 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>810.65</v>
+        <v>464.65</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>55.8</v>
+        <v>53.1</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>72.55</v>
+        <v>45.8</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>81.83</v>
+        <v>43.87</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>MIDHANI</t>
+          <t>LLOYDSENGG</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -2976,22 +2496,22 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>433.6</v>
+        <v>94.42</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>55.19</v>
+        <v>53.1</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>56.27</v>
+        <v>63.71</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>56.94</v>
+        <v>64.79000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>SUDEEPPHRM</t>
+          <t>RAIN</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -3000,22 +2520,22 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>1199.8</v>
+        <v>215.42</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>54.94</v>
+        <v>52.61</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>68.8</v>
+        <v>60.99</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v/>
+        <v>60.35</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>INOXINDIA</t>
+          <t>ATLANTAELE</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -3024,22 +2544,22 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>2168.3</v>
+        <v>1769.5</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>54.89</v>
+        <v>52.46</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>70.01000000000001</v>
+        <v>56.38</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>79.48</v>
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>LXCHEM</t>
+          <t>IIFLCAPS</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -3048,22 +2568,22 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>181.39</v>
+        <v>343.75</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>54.7</v>
+        <v>52.04</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>63.3</v>
+        <v>56.26</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>48.11</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>POWERMECH</t>
+          <t>GRINDWELL</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -3072,22 +2592,22 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>2476.2</v>
+        <v>1990.6</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>54.33</v>
+        <v>51.86</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>50.1</v>
+        <v>54.66</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>50.87</v>
+        <v>54.91</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>HERITGFOOD</t>
+          <t>LXCHEM</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -3096,22 +2616,22 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>402.9</v>
+        <v>180.34</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>53.99</v>
+        <v>51.26</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>61.5</v>
+        <v>61.25</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>52.93</v>
+        <v>47.84</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GRWRHITECH</t>
+          <t>PNGJL</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -3120,22 +2640,22 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>6925.5</v>
+        <v>599.95</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>53.48</v>
+        <v>51.04</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>64.54000000000001</v>
+        <v>49.94</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>68.04000000000001</v>
+        <v>49.08</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>SUPRIYA</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -3144,22 +2664,22 @@
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>931</v>
+        <v>592.7</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>53.25</v>
+        <v>50.98</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>57.77</v>
+        <v>63.39</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>60.65</v>
+        <v>58.59</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>SANSERA</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -3168,22 +2688,22 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>4276.6</v>
+        <v>2300.5</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>53.13</v>
+        <v>50.94</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>70.8</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>80.55</v>
+        <v>80.02</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>SURYAROSNI</t>
+          <t>GAEL</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -3192,22 +2712,22 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>220.67</v>
+        <v>163.43</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>53.05</v>
+        <v>50.87</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>44.19</v>
+        <v>54.01</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>45.64</v>
+        <v>60.32</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>MAHSEAMLES</t>
+          <t>WELENT</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -3216,22 +2736,22 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>698.75</v>
+        <v>735.9</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>53.02</v>
+        <v>50.69</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>64.87</v>
+        <v>62.62</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>56.9</v>
+        <v>68.52</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>SOUTHBANK</t>
+          <t>PRUDENT</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -3240,22 +2760,22 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>47.44</v>
+        <v>3254.7</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>52.93</v>
+        <v>50.48</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>58.74</v>
+        <v>57.04</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>70.08</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>JAMNAAUTO</t>
+          <t>EMIL</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -3264,22 +2784,22 @@
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>131.66</v>
+        <v>191.17</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>52.77</v>
+        <v>50.05</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>52.83</v>
+        <v>66.76000000000001</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>57.01</v>
+        <v>60.62</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>ELLEN</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -3288,22 +2808,22 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>589.15</v>
+        <v>348.15</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>52.47</v>
+        <v>49.87</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>62.19</v>
+        <v>57.88</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>58.18</v>
+        <v>40.73</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>BBOX</t>
+          <t>GMRP&amp;UI</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -3312,22 +2832,22 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>795.85</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>52.33</v>
+        <v>49.87</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>52.86</v>
+        <v>46.66</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>60.58</v>
+        <v>49.85</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>BLUESTONE</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -3336,22 +2856,22 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>1670</v>
+        <v>817.65</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>52.09</v>
+        <v>49.86</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>64.78</v>
+        <v>63.28</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>78.15000000000001</v>
+        <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GRINDWELL</t>
+          <t>WEWORK</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -3360,22 +2880,22 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>1975.8</v>
+        <v>669.45</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>52.05</v>
+        <v>49.75</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>54.05</v>
+        <v>53.53</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>54.45</v>
+        <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>ATLANTAELE</t>
+          <t>ASTRAMICRO</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -3384,22 +2904,22 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>1716.5</v>
+        <v>1652.9</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>51.87</v>
+        <v>49.47</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>54.45</v>
+        <v>59.01</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v/>
+        <v>68.95999999999999</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>PCJEWELLER</t>
+          <t>KPIGREEN</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -3408,22 +2928,22 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>12.82</v>
+        <v>325.3</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>51.8</v>
+        <v>49.15</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>61.54</v>
+        <v>41.14</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>57.29</v>
+        <v>44.13</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>ALIVUS</t>
+          <t>YATHARTH</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -3432,22 +2952,22 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>1374.2</v>
+        <v>1022.2</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>51.63</v>
+        <v>49</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>68.88</v>
+        <v>61.7</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>71.58</v>
+        <v>68.44</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>SMLMAH</t>
+          <t>JAYNECOIND</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -3456,22 +2976,22 @@
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>6251</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>51.52</v>
+        <v>48.95</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>63.27</v>
+        <v>51.89</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>68.23</v>
+        <v>59.55</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>BLACKBUCK</t>
+          <t>ORKLAINDIA</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -3480,22 +3000,22 @@
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>606.15</v>
+        <v>559.2</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>51.19</v>
+        <v>48.72</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>53.52</v>
+        <v>42.66</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>58.98</v>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>SENCO</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -3504,22 +3024,22 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>2280.2</v>
+        <v>334.75</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>50.97</v>
+        <v>48.69</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>69.23</v>
+        <v>47.85</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>79.27</v>
+        <v>48.66</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>ICIL</t>
+          <t>ELECTCAST</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -3528,22 +3048,22 @@
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>443.65</v>
+        <v>75.18000000000001</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>50.88</v>
+        <v>48.63</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>64.28</v>
+        <v>48.81</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>62.72</v>
+        <v>43.87</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>DATAMATICS</t>
+          <t>POWERMECH</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -3552,22 +3072,22 @@
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>790.3</v>
+        <v>2419</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>50.85</v>
+        <v>48.33</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>49.96</v>
+        <v>47.85</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>54.37</v>
+        <v>49.87</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>YATHARTH</t>
+          <t>RATEGAIN</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -3576,22 +3096,22 @@
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>1033.7</v>
+        <v>853.65</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>50.55</v>
+        <v>48.17</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>63.06</v>
+        <v>54.65</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>69.26000000000001</v>
+        <v>60.54</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>INOXINDIA</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -3600,22 +3120,22 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>325.6</v>
+        <v>2056.9</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>50.09</v>
+        <v>48.1</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>66.59999999999999</v>
+        <v>61.84</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>67.3</v>
+        <v>77.61</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>JAYNECOIND</t>
+          <t>TMB</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -3624,22 +3144,22 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>91.28</v>
+        <v>874.8</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>49.76</v>
+        <v>47.97</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>52.43</v>
+        <v>63.44</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>59.49</v>
+        <v>71.79000000000001</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>UJJIVANSFB</t>
+          <t>HERITGFOOD</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -3648,22 +3168,22 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>65.59999999999999</v>
+        <v>390.15</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>49.69</v>
+        <v>47.79</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>54.94</v>
+        <v>56.7</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>60.64</v>
+        <v>51.38</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>SANSERA</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -3672,22 +3192,22 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>321.6</v>
+        <v>4124.7</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>49.28</v>
+        <v>47.53</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>66.23999999999999</v>
+        <v>66.62</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>73.56</v>
+        <v>77.14</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>APOLLO</t>
+          <t>ICIL</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -3696,22 +3216,22 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>394</v>
+        <v>436.3</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>48.84</v>
+        <v>47.41</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>55.74</v>
+        <v>61.85</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>66.92</v>
+        <v>61.78</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>LUMAXTECH</t>
+          <t>KRBL</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -3720,22 +3240,22 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>1978.9</v>
+        <v>389.2</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>48.81</v>
+        <v>47.36</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>60.35</v>
+        <v>53.5</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>68.65000000000001</v>
+        <v>54.84</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>VARROC</t>
+          <t>BLACKBUCK</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -3744,22 +3264,22 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>830.6</v>
+        <v>592.05</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>48.69</v>
+        <v>47.02</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>69.01000000000001</v>
+        <v>51.08</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>67.42</v>
+        <v>56.73</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>KSB</t>
+          <t>GREAVESCOT</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -3768,22 +3288,22 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>806.45</v>
+        <v>207.22</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>48.68</v>
+        <v>46.99</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>45.99</v>
+        <v>52.16</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>51.26</v>
+        <v>52.82</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>SHRIPISTON</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -3792,22 +3312,22 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>4490.5</v>
+        <v>541</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>48.55</v>
+        <v>46.77</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>61.95</v>
+        <v>58.21</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>75.51000000000001</v>
+        <v>64.39</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>MSTCLTD</t>
+          <t>LLOYDSENT</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -3816,22 +3336,22 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>705.8</v>
+        <v>73.73</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>47.5</v>
+        <v>46.64</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>61.83</v>
+        <v>51.91</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>59.13</v>
+        <v>56.27</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>GMMPFAUDLR</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -3840,22 +3360,22 @@
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>542.55</v>
+        <v>1299.8</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>47.49</v>
+        <v>46.39</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>58.83</v>
+        <v>63.66</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>64.5</v>
+        <v>54.76</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>MANORAMA</t>
+          <t>APOLLO</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -3864,22 +3384,22 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>1880.3</v>
+        <v>388.35</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>47.37</v>
+        <v>45.99</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>62.98</v>
+        <v>54.46</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>69.37</v>
+        <v>66.04000000000001</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>ELECTCAST</t>
+          <t>GODREJAGRO</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -3888,22 +3408,22 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>74.54000000000001</v>
+        <v>628.45</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>47.29</v>
+        <v>45.84</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>48.01</v>
+        <v>56.49</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>43.6</v>
+        <v>51.61</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>UTLSOLAR</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -3912,22 +3432,22 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>618.15</v>
+        <v>409.05</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>47.17</v>
+        <v>45.75</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>64.5</v>
+        <v>60.01</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>65.54000000000001</v>
+        <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>TVSSCS</t>
+          <t>PURVA</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -3936,22 +3456,22 @@
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>128.42</v>
+        <v>207.26</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>47.12</v>
+        <v>45.65</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>50.93</v>
+        <v>44.98</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>46.67</v>
+        <v>44.04</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>ELLEN</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -3960,22 +3480,22 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>341.7</v>
+        <v>203.79</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>47.05</v>
+        <v>45.48</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>56.51</v>
+        <v>55.47</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>39.93</v>
+        <v>61.78</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>IXIGO</t>
+          <t>ENTERO</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -3984,22 +3504,22 @@
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>161.9</v>
+        <v>1676.2</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>46.94</v>
+        <v>45.34</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>42.92</v>
+        <v>63.16</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>42.51</v>
+        <v>66.34</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GODREJAGRO</t>
+          <t>AWFIS</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -4008,22 +3528,22 @@
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>631.9</v>
+        <v>247.03</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>46.91</v>
+        <v>45.25</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>57.61</v>
+        <v>37.18</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>51.91</v>
+        <v>29.19</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>WELENT</t>
+          <t>TANLA</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -4032,22 +3552,22 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>724.45</v>
+        <v>498.35</v>
       </c>
       <c r="D81" s="4" t="n">
-        <v>46.89</v>
+        <v>45.17</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>61.14</v>
+        <v>44.08</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>67.26000000000001</v>
+        <v>43.66</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>SKIPPER</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -4056,22 +3576,22 @@
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>541.2</v>
+        <v>855.5</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>46.79</v>
+        <v>45.05</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>55.37</v>
+        <v>56.99</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>60.53</v>
+        <v>57.41</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>RAIN</t>
+          <t>ALKYLAMINE</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -4080,22 +3600,22 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>208.52</v>
+        <v>1807.6</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>46.77</v>
+        <v>44.99</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>58.56</v>
+        <v>50.61</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>58.91</v>
+        <v>49.41</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>SKIPPER</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -4104,22 +3624,22 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>154.79</v>
+        <v>530.25</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>46.72</v>
+        <v>44.92</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>48.12</v>
+        <v>52.44</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>53.37</v>
+        <v>59.53</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>DIACABS</t>
+          <t>KANSAINER</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -4128,22 +3648,22 @@
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>345</v>
+        <v>181.29</v>
       </c>
       <c r="D85" s="4" t="n">
-        <v>46.53</v>
+        <v>44.85</v>
       </c>
       <c r="E85" s="4" t="n">
-        <v>70.70999999999999</v>
+        <v>38.98</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>78.53</v>
+        <v>37.17</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>ASTRAMICRO</t>
+          <t>FINPIPE</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -4152,22 +3672,22 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>1624.5</v>
+        <v>151.16</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>46.31</v>
+        <v>44.57</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>57.16</v>
+        <v>36.5</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>68.03</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>AARTIDRUGS</t>
+          <t>NESCO</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -4176,22 +3696,22 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>421</v>
+        <v>1038.5</v>
       </c>
       <c r="D87" s="4" t="n">
-        <v>46.27</v>
+        <v>44.56</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>55.5</v>
+        <v>42.87</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>49.82</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>TMB</t>
+          <t>TIPSMUSIC</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -4200,22 +3720,22 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>872.05</v>
+        <v>636.35</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>45.96</v>
+        <v>44.52</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>65.34</v>
+        <v>49.1</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>71.67</v>
+        <v>55.94</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>STYRENIX</t>
+          <t>KSB</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -4224,22 +3744,22 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>2055</v>
+        <v>784.55</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>45.89</v>
+        <v>44.44</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>44.68</v>
+        <v>42.58</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>48.7</v>
+        <v>50.06</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>ENTERO</t>
+          <t>SHAILY</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -4248,22 +3768,22 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>1680.8</v>
+        <v>3063.4</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>45.88</v>
+        <v>44.16</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>63.11</v>
+        <v>56.39</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>66.56999999999999</v>
+        <v>68.25</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>WABAG</t>
+          <t>JYOTHYLAB</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -4272,22 +3792,22 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>2004.9</v>
+        <v>187.94</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>45.78</v>
+        <v>44.11</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>56.63</v>
+        <v>36.49</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>66.28</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>TARC</t>
+          <t>PARKHOSPS</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -4296,22 +3816,22 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>125.58</v>
+        <v>270.8</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>45.7</v>
+        <v>44.09</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>46.01</v>
+        <v>54.13</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>46.02</v>
+        <v/>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>TARC</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -4320,22 +3840,22 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>125.58</v>
+        <v>4889.5</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>45.7</v>
+        <v>43.91</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>46.01</v>
+        <v>49.14</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>46.02</v>
+        <v>64.09</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>STYL</t>
+          <t>TEXRAIL</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -4344,22 +3864,22 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>366</v>
+        <v>110.99</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>45.51</v>
+        <v>43.79</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>55.11</v>
+        <v>48.32</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v/>
+        <v>45.45</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>SAMHI</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -4368,22 +3888,22 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>154.37</v>
+        <v>1386.1</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>45.46</v>
+        <v>43.67</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>42.98</v>
+        <v>56.46</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>44.5</v>
+        <v>62.31</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>RBA</t>
+          <t>INDIASHLTR</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -4392,22 +3912,22 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>92.22</v>
+        <v>643.45</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>45.29</v>
+        <v>43.52</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>61.01</v>
+        <v>36.44</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>55.67</v>
+        <v>39.44</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>RBA</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -4416,22 +3936,22 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>1414.7</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>45.17</v>
+        <v>43.47</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>58.57</v>
+        <v>59.8</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>63.43</v>
+        <v>55.11</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>IONEXCHANG</t>
+          <t>AARTIDRUGS</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -4440,22 +3960,22 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>406.4</v>
+        <v>413.3</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>45.02</v>
+        <v>43.44</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>51.33</v>
+        <v>52.8</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>48.1</v>
+        <v>48.87</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>ARVINDFASN</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -4464,22 +3984,22 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>475.05</v>
+        <v>402.8</v>
       </c>
       <c r="D99" s="4" t="n">
-        <v>44.81</v>
+        <v>43.39</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>38.09</v>
+        <v>39.02</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>38.86</v>
+        <v>44.05</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>KIRLOSBROS</t>
+          <t>BIRLACORPN</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -4488,22 +4008,22 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>1767.6</v>
+        <v>817.3</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>44.73</v>
+        <v>43.35</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>48.89</v>
+        <v>36.7</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>52.33</v>
+        <v>36.71</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>SPARC</t>
+          <t>SMLMAH</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -4512,22 +4032,22 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>194.13</v>
+        <v>5811.5</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>44.54</v>
+        <v>43.25</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>50.09</v>
+        <v>57.91</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>52.54</v>
+        <v>64.59</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>EMBDL</t>
+          <t>EDELWEISS</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -4536,22 +4056,22 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>56.13</v>
+        <v>127.89</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>44.5</v>
+        <v>43.18</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>43.9</v>
+        <v>54.69</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>40.49</v>
+        <v>58.72</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>VOLTAMP</t>
+          <t>BANCOINDIA</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -4560,22 +4080,22 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>10426</v>
+        <v>590.8</v>
       </c>
       <c r="D103" s="4" t="n">
-        <v>44.38</v>
+        <v>43.02</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>55.39</v>
+        <v>44.42</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>56.63</v>
+        <v>54.56</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>RATNAMANI</t>
+          <t>BALAMINES</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -4584,22 +4104,22 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>2619.4</v>
+        <v>2040.8</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>44.36</v>
+        <v>43</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>52.19</v>
+        <v>52.56</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>50.69</v>
+        <v>56.22</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>BLUESTONE</t>
+          <t>JUSTDIAL</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -4608,22 +4128,22 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>787.95</v>
+        <v>648.05</v>
       </c>
       <c r="D105" s="4" t="n">
-        <v>44.24</v>
+        <v>42.94</v>
       </c>
       <c r="E105" s="4" t="n">
-        <v>59.86</v>
+        <v>50.77</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v/>
+        <v>44.44</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>EMBDL</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -4632,22 +4152,22 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>534.05</v>
+        <v>55.51</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>44.04</v>
+        <v>42.94</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>58.6</v>
+        <v>43.35</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>66.2</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>APLLTD</t>
+          <t>EPL</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -4656,22 +4176,22 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>815.25</v>
+        <v>232.43</v>
       </c>
       <c r="D107" s="4" t="n">
-        <v>43.97</v>
+        <v>42.76</v>
       </c>
       <c r="E107" s="4" t="n">
-        <v>53.58</v>
+        <v>50.25</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>48.91</v>
+        <v>53.77</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>CCAVENUE</t>
+          <t>PRIVISCL</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -4680,22 +4200,22 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>15.28</v>
+        <v>3424.1</v>
       </c>
       <c r="D108" s="4" t="n">
-        <v>43.63</v>
+        <v>42.61</v>
       </c>
       <c r="E108" s="4" t="n">
-        <v>47.48</v>
+        <v>51.29</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>43</v>
+        <v>64.37</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>TIMETECHNO</t>
+          <t>STAR</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -4704,22 +4224,22 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>179.68</v>
+        <v>1085.3</v>
       </c>
       <c r="D109" s="4" t="n">
-        <v>43.61</v>
+        <v>42.56</v>
       </c>
       <c r="E109" s="4" t="n">
-        <v>46.39</v>
+        <v>52.84</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>50.69</v>
+        <v>58.59</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>QUESS</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -4728,46 +4248,46 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>336.2</v>
+        <v>148</v>
       </c>
       <c r="D110" s="4" t="n">
-        <v>43.5</v>
+        <v>42.46</v>
       </c>
       <c r="E110" s="4" t="n">
-        <v>63.4</v>
+        <v>47.19</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>49.96</v>
+        <v>52.79</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>KSCL</t>
-        </is>
-      </c>
-      <c r="B111" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C111" s="4" t="n">
-        <v>715.1</v>
-      </c>
-      <c r="D111" s="4" t="n">
-        <v>43.49</v>
-      </c>
-      <c r="E111" s="4" t="n">
-        <v>39.53</v>
-      </c>
-      <c r="F111" s="4" t="n">
-        <v>40.65</v>
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>MARKSANS</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="n">
+        <v>309.1</v>
+      </c>
+      <c r="D111" s="7" t="n">
+        <v>42.46</v>
+      </c>
+      <c r="E111" s="7" t="n">
+        <v>61.07</v>
+      </c>
+      <c r="F111" s="7" t="n">
+        <v>64.23</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>TIPSMUSIC</t>
+          <t>AVL</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -4776,22 +4296,22 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>644.2</v>
+        <v>581.05</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>43.46</v>
+        <v>42.45</v>
       </c>
       <c r="E112" s="4" t="n">
-        <v>51.04</v>
+        <v>49.69</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>56.77</v>
+        <v>57.64</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>REFEX</t>
+          <t>VOLTAMP</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -4800,22 +4320,22 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>271.3</v>
+        <v>10302</v>
       </c>
       <c r="D113" s="4" t="n">
-        <v>43.31</v>
+        <v>42.25</v>
       </c>
       <c r="E113" s="4" t="n">
-        <v>43.96</v>
+        <v>53.48</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>47.5</v>
+        <v>56.06</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>WAKEFIT</t>
+          <t>ETHOSLTD</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -4824,46 +4344,46 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>139.88</v>
+        <v>2563.1</v>
       </c>
       <c r="D114" s="4" t="n">
-        <v>43.1</v>
+        <v>42.21</v>
       </c>
       <c r="E114" s="4" t="n">
-        <v>47.89</v>
+        <v>48.73</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v/>
+        <v>50.95</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>WEWORK</t>
-        </is>
-      </c>
-      <c r="B115" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C115" s="4" t="n">
-        <v>659.6</v>
-      </c>
-      <c r="D115" s="4" t="n">
-        <v>42.81</v>
-      </c>
-      <c r="E115" s="4" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="F115" s="4" t="n">
-        <v/>
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>ALIVUS</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C115" s="7" t="n">
+        <v>1326.3</v>
+      </c>
+      <c r="D115" s="7" t="n">
+        <v>42.11</v>
+      </c>
+      <c r="E115" s="7" t="n">
+        <v>62.01</v>
+      </c>
+      <c r="F115" s="7" t="n">
+        <v>67.70999999999999</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>RATEGAIN</t>
+          <t>DBL</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -4872,22 +4392,22 @@
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>840.65</v>
+        <v>395.65</v>
       </c>
       <c r="D116" s="4" t="n">
-        <v>42.81</v>
+        <v>42.07</v>
       </c>
       <c r="E116" s="4" t="n">
-        <v>52.82</v>
+        <v>42.2</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>59.7</v>
+        <v>44.94</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>SMARTWORKS</t>
+          <t>SUDARSCHEM</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -4896,22 +4416,22 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>510.65</v>
+        <v>1166.8</v>
       </c>
       <c r="D117" s="4" t="n">
-        <v>42.67</v>
+        <v>41.92</v>
       </c>
       <c r="E117" s="4" t="n">
-        <v>54.68</v>
+        <v>57.27</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>54.26</v>
+        <v>57.01</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>SAATVIKGL</t>
+          <t>JSFB</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -4920,22 +4440,22 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>405.55</v>
+        <v>489.35</v>
       </c>
       <c r="D118" s="4" t="n">
-        <v>42.53</v>
+        <v>41.49</v>
       </c>
       <c r="E118" s="4" t="n">
-        <v>44.21</v>
+        <v>48.84</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v/>
+        <v>52.18</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>MANYAVAR</t>
+          <t>TVSSCS</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -4944,22 +4464,22 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>519.2</v>
+        <v>124.54</v>
       </c>
       <c r="D119" s="4" t="n">
-        <v>42.45</v>
+        <v>41.36</v>
       </c>
       <c r="E119" s="4" t="n">
-        <v>56.52</v>
+        <v>48.22</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>39.17</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>INDIASHLTR</t>
+          <t>CCAVENUE</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -4968,46 +4488,46 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>645.6</v>
+        <v>14.9</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>42.39</v>
+        <v>41.29</v>
       </c>
       <c r="E120" s="4" t="n">
-        <v>36.75</v>
+        <v>45.14</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>39.72</v>
+        <v>42.05</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>GAEL</t>
-        </is>
-      </c>
-      <c r="B121" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C121" s="4" t="n">
-        <v>157.69</v>
-      </c>
-      <c r="D121" s="4" t="n">
-        <v>42.16</v>
-      </c>
-      <c r="E121" s="4" t="n">
-        <v>50.29</v>
-      </c>
-      <c r="F121" s="4" t="n">
-        <v>57.86</v>
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>AKUMS</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C121" s="7" t="n">
+        <v>751.85</v>
+      </c>
+      <c r="D121" s="7" t="n">
+        <v>41.28</v>
+      </c>
+      <c r="E121" s="7" t="n">
+        <v>62.33</v>
+      </c>
+      <c r="F121" s="7" t="n">
+        <v>60.71</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>FEDFINA</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -5016,46 +4536,46 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>149.77</v>
+        <v>2024</v>
       </c>
       <c r="D122" s="4" t="n">
-        <v>42.14</v>
+        <v>41.27</v>
       </c>
       <c r="E122" s="4" t="n">
-        <v>48.69</v>
+        <v>55.94</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>55.66</v>
+        <v/>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>EPL</t>
-        </is>
-      </c>
-      <c r="B123" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C123" s="4" t="n">
-        <v>232.39</v>
-      </c>
-      <c r="D123" s="4" t="n">
-        <v>41.89</v>
-      </c>
-      <c r="E123" s="4" t="n">
-        <v>49.16</v>
-      </c>
-      <c r="F123" s="4" t="n">
-        <v>53.76</v>
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>VARROC</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C123" s="7" t="n">
+        <v>793.6</v>
+      </c>
+      <c r="D123" s="7" t="n">
+        <v>41.24</v>
+      </c>
+      <c r="E123" s="7" t="n">
+        <v>61.92</v>
+      </c>
+      <c r="F123" s="7" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>BIRLACORPN</t>
+          <t>STYRENIX</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -5064,22 +4584,22 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>828.95</v>
+        <v>1999.2</v>
       </c>
       <c r="D124" s="4" t="n">
-        <v>41.86</v>
+        <v>41.22</v>
       </c>
       <c r="E124" s="4" t="n">
-        <v>37.92</v>
+        <v>41.77</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>37.19</v>
+        <v>47.39</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>DBL</t>
+          <t>GSFC</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -5088,22 +4608,22 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>399.1</v>
+        <v>147.28</v>
       </c>
       <c r="D125" s="4" t="n">
-        <v>41.82</v>
+        <v>41.21</v>
       </c>
       <c r="E125" s="4" t="n">
-        <v>42.75</v>
+        <v>39.42</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>45.35</v>
+        <v>42.22</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>MEDPLUS</t>
+          <t>WABAG</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -5112,22 +4632,22 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>654.3</v>
+        <v>1936.8</v>
       </c>
       <c r="D126" s="4" t="n">
-        <v>41.61</v>
+        <v>41.19</v>
       </c>
       <c r="E126" s="4" t="n">
-        <v>28.58</v>
+        <v>53.46</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>38.65</v>
+        <v>63.76</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>PRUDENT</t>
+          <t>RATNAMANI</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -5136,22 +4656,22 @@
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>3119.1</v>
+        <v>2523.6</v>
       </c>
       <c r="D127" s="4" t="n">
-        <v>41.53</v>
+        <v>41.05</v>
       </c>
       <c r="E127" s="4" t="n">
-        <v>52.48</v>
+        <v>48.96</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>58.52</v>
+        <v>48.68</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>UTLSOLAR</t>
+          <t>MSTCLTD</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -5160,46 +4680,46 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>401.65</v>
+        <v>672</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>41.52</v>
+        <v>40.98</v>
       </c>
       <c r="E128" s="4" t="n">
-        <v>58.65</v>
+        <v>56.98</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v/>
+        <v>57</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="5" t="inlineStr">
-        <is>
-          <t>PRICOLLTD</t>
-        </is>
-      </c>
-      <c r="B129" s="6" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C129" s="7" t="n">
-        <v>734.5</v>
-      </c>
-      <c r="D129" s="7" t="n">
-        <v>41.48</v>
-      </c>
-      <c r="E129" s="7" t="n">
-        <v>62.14</v>
-      </c>
-      <c r="F129" s="7" t="n">
-        <v>64.14</v>
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>PARAS</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="n">
+        <v>1267.9</v>
+      </c>
+      <c r="D129" s="4" t="n">
+        <v>40.92</v>
+      </c>
+      <c r="E129" s="4" t="n">
+        <v>56.26</v>
+      </c>
+      <c r="F129" s="4" t="n">
+        <v>62.77</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>SUNTECK</t>
+          <t>MOIL</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -5208,22 +4728,22 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>279.45</v>
+        <v>234.96</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>41.38</v>
+        <v>40.92</v>
       </c>
       <c r="E130" s="4" t="n">
-        <v>38.12</v>
+        <v>31.2</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>39.07</v>
+        <v>39.33</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>STAR</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -5232,22 +4752,22 @@
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>1084.8</v>
+        <v>588.15</v>
       </c>
       <c r="D131" s="4" t="n">
-        <v>41.31</v>
+        <v>40.88</v>
       </c>
       <c r="E131" s="4" t="n">
-        <v>52.81</v>
+        <v>57.68</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>58.56</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>JUSTDIAL</t>
+          <t>BALUFORGE</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -5256,22 +4776,22 @@
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>653.15</v>
+        <v>481.2</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>41.25</v>
+        <v>40.7</v>
       </c>
       <c r="E132" s="4" t="n">
-        <v>51.41</v>
+        <v>46.88</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>44.73</v>
+        <v>48.09</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>RENUKA</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -5280,22 +4800,22 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>4861</v>
+        <v>21.72</v>
       </c>
       <c r="D133" s="4" t="n">
-        <v>41.1</v>
+        <v>40.7</v>
       </c>
       <c r="E133" s="4" t="n">
-        <v>48.84</v>
+        <v>41.24</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>63.77</v>
+        <v>37.72</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>MASTEK</t>
+          <t>LUMAXTECH</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -5304,22 +4824,22 @@
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>1555.6</v>
+        <v>1827.4</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>41.04</v>
+        <v>40.38</v>
       </c>
       <c r="E134" s="4" t="n">
-        <v>42.09</v>
+        <v>52.96</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>40.33</v>
+        <v>63.71</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>BECTORFOOD</t>
+          <t>APLLTD</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -5328,22 +4848,22 @@
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>213.03</v>
+        <v>800.95</v>
       </c>
       <c r="D135" s="4" t="n">
-        <v>41</v>
+        <v>40.29</v>
       </c>
       <c r="E135" s="4" t="n">
-        <v>49.5</v>
+        <v>50.07</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>47.11</v>
+        <v>47.98</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>AGARWALEYE</t>
+          <t>SHRIPISTON</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -5352,22 +4872,22 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>486.45</v>
+        <v>4284.5</v>
       </c>
       <c r="D136" s="4" t="n">
-        <v>40.97</v>
+        <v>40.27</v>
       </c>
       <c r="E136" s="4" t="n">
-        <v>51.07</v>
+        <v>56.2</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>53.94</v>
+        <v>70.72</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>HCG</t>
+          <t>DATAMATICS</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -5376,22 +4896,22 @@
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>668.75</v>
+        <v>745.8</v>
       </c>
       <c r="D137" s="4" t="n">
-        <v>40.94</v>
+        <v>40.18</v>
       </c>
       <c r="E137" s="4" t="n">
-        <v>50.59</v>
+        <v>44.5</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>59.01</v>
+        <v>51.67</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>BANCOINDIA</t>
+          <t>SHARDACROP</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -5400,22 +4920,22 @@
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>589.85</v>
+        <v>723.9</v>
       </c>
       <c r="D138" s="4" t="n">
-        <v>40.78</v>
+        <v>40.1</v>
       </c>
       <c r="E138" s="4" t="n">
-        <v>44.33</v>
+        <v>35.94</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>54.49</v>
+        <v>47.97</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>RUBICON</t>
+          <t>SUPRIYA</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -5424,22 +4944,22 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>1630.9</v>
+        <v>847.65</v>
       </c>
       <c r="D139" s="4" t="n">
-        <v>40.4</v>
+        <v>39.98</v>
       </c>
       <c r="E139" s="4" t="n">
-        <v>64.98</v>
+        <v>50.65</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v/>
+        <v>56.25</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>CRIZAC</t>
+          <t>TIMETECHNO</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -5448,22 +4968,22 @@
         </is>
       </c>
       <c r="C140" s="4" t="n">
-        <v>166.89</v>
+        <v>176.35</v>
       </c>
       <c r="D140" s="4" t="n">
-        <v>40.26</v>
+        <v>39.93</v>
       </c>
       <c r="E140" s="4" t="n">
-        <v>38.66</v>
+        <v>43.74</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>20.86</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>SKFINDUS</t>
+          <t>KNRCON</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -5472,22 +4992,22 @@
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>2734.2</v>
+        <v>112.92</v>
       </c>
       <c r="D141" s="4" t="n">
-        <v>40.13</v>
+        <v>39.48</v>
       </c>
       <c r="E141" s="4" t="n">
-        <v>50.98</v>
+        <v>37.83</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v/>
+        <v>32.54</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>REDTAPE</t>
+          <t>SUBROS</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -5496,22 +5016,22 @@
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>115.29</v>
+        <v>676.75</v>
       </c>
       <c r="D142" s="4" t="n">
-        <v>40.07</v>
+        <v>39.46</v>
       </c>
       <c r="E142" s="4" t="n">
-        <v>41.26</v>
+        <v>38.36</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>33.9</v>
+        <v>47.31</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>PURVA</t>
+          <t>PICCADIL</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -5520,22 +5040,22 @@
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>204.64</v>
+        <v>580.7</v>
       </c>
       <c r="D143" s="4" t="n">
-        <v>40.07</v>
+        <v>39.43</v>
       </c>
       <c r="E143" s="4" t="n">
-        <v>45.85</v>
+        <v>44.03</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>43.56</v>
+        <v>48.34</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>BALUFORGE</t>
+          <t>MANYAVAR</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -5544,22 +5064,22 @@
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>488.95</v>
+        <v>500.75</v>
       </c>
       <c r="D144" s="4" t="n">
-        <v>39.97</v>
+        <v>39.43</v>
       </c>
       <c r="E144" s="4" t="n">
-        <v>47.89</v>
+        <v>52.79</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>48.47</v>
+        <v>38.19</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>PNGJL</t>
+          <t>UJJIVANSFB</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -5568,22 +5088,22 @@
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>581.95</v>
+        <v>61.45</v>
       </c>
       <c r="D145" s="4" t="n">
-        <v>39.95</v>
+        <v>39.42</v>
       </c>
       <c r="E145" s="4" t="n">
-        <v>45.98</v>
+        <v>47.58</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>47.35</v>
+        <v>56.83</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>NESCO</t>
+          <t>CRIZAC</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -5592,22 +5112,22 @@
         </is>
       </c>
       <c r="C146" s="4" t="n">
-        <v>1028.2</v>
+        <v>162.94</v>
       </c>
       <c r="D146" s="4" t="n">
-        <v>39.82</v>
+        <v>39.41</v>
       </c>
       <c r="E146" s="4" t="n">
-        <v>41.13</v>
+        <v>37.72</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>48.46</v>
+        <v>20.37</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>EQUITASBNK</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -5616,22 +5136,22 @@
         </is>
       </c>
       <c r="C147" s="4" t="n">
-        <v>68.41</v>
+        <v>185.6</v>
       </c>
       <c r="D147" s="4" t="n">
-        <v>39.31</v>
+        <v>39.33</v>
       </c>
       <c r="E147" s="4" t="n">
-        <v>44.91</v>
+        <v>47.19</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>50.21</v>
+        <v>50.81</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>IONEXCHANG</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -5640,22 +5160,22 @@
         </is>
       </c>
       <c r="C148" s="4" t="n">
-        <v>2029.4</v>
+        <v>390.75</v>
       </c>
       <c r="D148" s="4" t="n">
-        <v>38.97</v>
+        <v>39.27</v>
       </c>
       <c r="E148" s="4" t="n">
-        <v>55.76</v>
+        <v>48.29</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v/>
+        <v>46.67</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>AGARWALEYE</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -5664,22 +5184,22 @@
         </is>
       </c>
       <c r="C149" s="4" t="n">
-        <v>100.7</v>
+        <v>477.75</v>
       </c>
       <c r="D149" s="4" t="n">
-        <v>38.96</v>
+        <v>39.24</v>
       </c>
       <c r="E149" s="4" t="n">
-        <v>44.01</v>
+        <v>47.98</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>40.74</v>
+        <v>52.67</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>SHAILY</t>
+          <t>TRIVENI</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -5688,22 +5208,22 @@
         </is>
       </c>
       <c r="C150" s="4" t="n">
-        <v>3009.1</v>
+        <v>235.67</v>
       </c>
       <c r="D150" s="4" t="n">
-        <v>38.83</v>
+        <v>39.14</v>
       </c>
       <c r="E150" s="4" t="n">
-        <v>54.96</v>
+        <v>36.47</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>66.91</v>
+        <v>40.47</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>KITEX</t>
+          <t>SAATVIKGL</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -5712,22 +5232,22 @@
         </is>
       </c>
       <c r="C151" s="4" t="n">
-        <v>116.68</v>
+        <v>395.95</v>
       </c>
       <c r="D151" s="4" t="n">
-        <v>38.71</v>
+        <v>38.93</v>
       </c>
       <c r="E151" s="4" t="n">
-        <v>30.53</v>
+        <v>41.9</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>41.69</v>
+        <v/>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>CELLO</t>
+          <t>VIYASH</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -5736,22 +5256,22 @@
         </is>
       </c>
       <c r="C152" s="4" t="n">
-        <v>323.1</v>
+        <v>234.06</v>
       </c>
       <c r="D152" s="4" t="n">
-        <v>38.57</v>
+        <v>38.9</v>
       </c>
       <c r="E152" s="4" t="n">
-        <v>34.01</v>
+        <v>45.67</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>27.58</v>
+        <v>56.24</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>JAIBALAJI</t>
+          <t>STYL</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -5760,22 +5280,22 @@
         </is>
       </c>
       <c r="C153" s="4" t="n">
-        <v>61.72</v>
+        <v>349.05</v>
       </c>
       <c r="D153" s="4" t="n">
-        <v>38.28</v>
+        <v>38.88</v>
       </c>
       <c r="E153" s="4" t="n">
-        <v>42.88</v>
+        <v>51.44</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>41.02</v>
+        <v/>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>JSLL</t>
+          <t>KIRLOSBROS</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -5784,22 +5304,22 @@
         </is>
       </c>
       <c r="C154" s="4" t="n">
-        <v>480.8</v>
+        <v>1690.1</v>
       </c>
       <c r="D154" s="4" t="n">
-        <v>38.11</v>
+        <v>38.6</v>
       </c>
       <c r="E154" s="4" t="n">
-        <v>36.19</v>
+        <v>43.16</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>40.05</v>
+        <v>50.51</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>FINPIPE</t>
+          <t>FEDFINA</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -5808,22 +5328,22 @@
         </is>
       </c>
       <c r="C155" s="4" t="n">
-        <v>150.49</v>
+        <v>146.39</v>
       </c>
       <c r="D155" s="4" t="n">
-        <v>38.04</v>
+        <v>38.31</v>
       </c>
       <c r="E155" s="4" t="n">
-        <v>35.69</v>
+        <v>44.95</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>40.25</v>
+        <v>54.09</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>BALAMINES</t>
+          <t>RALLIS</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -5832,22 +5352,22 @@
         </is>
       </c>
       <c r="C156" s="4" t="n">
-        <v>2052.2</v>
+        <v>198.06</v>
       </c>
       <c r="D156" s="4" t="n">
-        <v>37.77</v>
+        <v>38.27</v>
       </c>
       <c r="E156" s="4" t="n">
-        <v>53.11</v>
+        <v>29.6</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>56.48</v>
+        <v>40.49</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>TANLA</t>
+          <t>TSFINV</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -5856,22 +5376,22 @@
         </is>
       </c>
       <c r="C157" s="4" t="n">
-        <v>487.75</v>
+        <v>403.9</v>
       </c>
       <c r="D157" s="4" t="n">
-        <v>37.76</v>
+        <v>38.14</v>
       </c>
       <c r="E157" s="4" t="n">
-        <v>41.41</v>
+        <v>45.49</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>42.91</v>
+        <v>52.31</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>INDIGOPNTS</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -5880,22 +5400,22 @@
         </is>
       </c>
       <c r="C158" s="4" t="n">
-        <v>1053.5</v>
+        <v>455.05</v>
       </c>
       <c r="D158" s="4" t="n">
-        <v>37.75</v>
+        <v>38.12</v>
       </c>
       <c r="E158" s="4" t="n">
-        <v>49.36</v>
+        <v>34.86</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>46.99</v>
+        <v>37.21</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>JKPAPER</t>
+          <t>SKFINDUS</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -5904,22 +5424,22 @@
         </is>
       </c>
       <c r="C159" s="4" t="n">
-        <v>382.6</v>
+        <v>2655.9</v>
       </c>
       <c r="D159" s="4" t="n">
-        <v>37.73</v>
+        <v>38.08</v>
       </c>
       <c r="E159" s="4" t="n">
-        <v>51.36</v>
+        <v>49.72</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>52.76</v>
+        <v/>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>SUBROS</t>
+          <t>SHAREINDIA</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -5928,22 +5448,22 @@
         </is>
       </c>
       <c r="C160" s="4" t="n">
-        <v>684.9</v>
+        <v>182.71</v>
       </c>
       <c r="D160" s="4" t="n">
-        <v>37.68</v>
+        <v>38.07</v>
       </c>
       <c r="E160" s="4" t="n">
-        <v>38.89</v>
+        <v>53.65</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>47.7</v>
+        <v>49.72</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>ETHOSLTD</t>
+          <t>WAAREERTL</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -5952,22 +5472,22 @@
         </is>
       </c>
       <c r="C161" s="4" t="n">
-        <v>2531.9</v>
+        <v>802.45</v>
       </c>
       <c r="D161" s="4" t="n">
-        <v>37.49</v>
+        <v>37.87</v>
       </c>
       <c r="E161" s="4" t="n">
-        <v>47.94</v>
+        <v>33.71</v>
       </c>
       <c r="F161" s="4" t="n">
-        <v>50.39</v>
+        <v>38.05</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>KRBL</t>
+          <t>VAIBHAVGBL</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -5976,22 +5496,22 @@
         </is>
       </c>
       <c r="C162" s="4" t="n">
-        <v>375.9</v>
+        <v>201.67</v>
       </c>
       <c r="D162" s="4" t="n">
-        <v>37.39</v>
+        <v>37.69</v>
       </c>
       <c r="E162" s="4" t="n">
-        <v>49.67</v>
+        <v>39.13</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>53.38</v>
+        <v>43.06</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>JSFB</t>
+          <t>KITEX</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -6000,22 +5520,22 @@
         </is>
       </c>
       <c r="C163" s="4" t="n">
-        <v>482.4</v>
+        <v>115.01</v>
       </c>
       <c r="D163" s="4" t="n">
-        <v>37.17</v>
+        <v>37.45</v>
       </c>
       <c r="E163" s="4" t="n">
-        <v>47.65</v>
+        <v>29.81</v>
       </c>
       <c r="F163" s="4" t="n">
-        <v>51.47</v>
+        <v>41.42</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>PARAS</t>
+          <t>SANDUMA</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -6024,16 +5544,16 @@
         </is>
       </c>
       <c r="C164" s="4" t="n">
-        <v>1276</v>
+        <v>177.68</v>
       </c>
       <c r="D164" s="4" t="n">
-        <v>36.72</v>
+        <v>37.42</v>
       </c>
       <c r="E164" s="4" t="n">
-        <v>56.95</v>
+        <v>37.85</v>
       </c>
       <c r="F164" s="4" t="n">
-        <v>63.12</v>
+        <v>49.51</v>
       </c>
     </row>
     <row r="165">
@@ -6048,22 +5568,22 @@
         </is>
       </c>
       <c r="C165" s="4" t="n">
-        <v>681.95</v>
+        <v>667.25</v>
       </c>
       <c r="D165" s="4" t="n">
-        <v>36.58</v>
+        <v>37.35</v>
       </c>
       <c r="E165" s="4" t="n">
-        <v>44.56</v>
+        <v>42.27</v>
       </c>
       <c r="F165" s="4" t="n">
-        <v>52.99</v>
+        <v>52.19</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>CSBBANK</t>
+          <t>IMFA</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -6072,22 +5592,22 @@
         </is>
       </c>
       <c r="C166" s="4" t="n">
-        <v>304.75</v>
+        <v>1182.5</v>
       </c>
       <c r="D166" s="4" t="n">
-        <v>36.53</v>
+        <v>37.27</v>
       </c>
       <c r="E166" s="4" t="n">
-        <v>39.77</v>
+        <v>38.94</v>
       </c>
       <c r="F166" s="4" t="n">
-        <v>42.89</v>
+        <v>54.52</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>PICCADIL</t>
+          <t>KSCL</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -6096,22 +5616,22 @@
         </is>
       </c>
       <c r="C167" s="4" t="n">
-        <v>581.05</v>
+        <v>676.8</v>
       </c>
       <c r="D167" s="4" t="n">
-        <v>36.51</v>
+        <v>37.12</v>
       </c>
       <c r="E167" s="4" t="n">
-        <v>44.84</v>
+        <v>36.9</v>
       </c>
       <c r="F167" s="4" t="n">
-        <v>48.38</v>
+        <v>39.07</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>RCF</t>
+          <t>SUDEEPPHRM</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -6120,22 +5640,22 @@
         </is>
       </c>
       <c r="C168" s="4" t="n">
-        <v>106.8</v>
+        <v>1050.3</v>
       </c>
       <c r="D168" s="4" t="n">
-        <v>36.39</v>
+        <v>37.12</v>
       </c>
       <c r="E168" s="4" t="n">
-        <v>32.27</v>
+        <v>56.17</v>
       </c>
       <c r="F168" s="4" t="n">
-        <v>40.88</v>
+        <v/>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>SHAKTIPUMP</t>
+          <t>QUESS</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -6144,22 +5664,22 @@
         </is>
       </c>
       <c r="C169" s="4" t="n">
-        <v>454.1</v>
+        <v>321.35</v>
       </c>
       <c r="D169" s="4" t="n">
-        <v>36.31</v>
+        <v>37.1</v>
       </c>
       <c r="E169" s="4" t="n">
-        <v>34.36</v>
+        <v>58.64</v>
       </c>
       <c r="F169" s="4" t="n">
-        <v>41.99</v>
+        <v>48.47</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>MAHSCOOTER</t>
+          <t>INDIAGLYCO</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -6168,22 +5688,22 @@
         </is>
       </c>
       <c r="C170" s="4" t="n">
-        <v>12380</v>
+        <v>329.6</v>
       </c>
       <c r="D170" s="4" t="n">
-        <v>36.31</v>
+        <v>37.08</v>
       </c>
       <c r="E170" s="4" t="n">
-        <v>45.2</v>
+        <v>29.01</v>
       </c>
       <c r="F170" s="4" t="n">
-        <v>52.77</v>
+        <v>36.96</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>SENCO</t>
+          <t>REDTAPE</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -6192,22 +5712,22 @@
         </is>
       </c>
       <c r="C171" s="4" t="n">
-        <v>317.4</v>
+        <v>112.77</v>
       </c>
       <c r="D171" s="4" t="n">
-        <v>36.23</v>
+        <v>36.67</v>
       </c>
       <c r="E171" s="4" t="n">
-        <v>42.74</v>
+        <v>39.92</v>
       </c>
       <c r="F171" s="4" t="n">
-        <v>46.92</v>
+        <v>33.67</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>PARKHOSPS</t>
+          <t>CRAMC</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -6216,13 +5736,13 @@
         </is>
       </c>
       <c r="C172" s="4" t="n">
-        <v>270.8</v>
+        <v>219.95</v>
       </c>
       <c r="D172" s="4" t="n">
-        <v>36.14</v>
+        <v>36.43</v>
       </c>
       <c r="E172" s="4" t="n">
-        <v>53.76</v>
+        <v>33.89</v>
       </c>
       <c r="F172" s="4" t="n">
         <v/>
@@ -6231,7 +5751,7 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>THYROCARE</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -6240,22 +5760,22 @@
         </is>
       </c>
       <c r="C173" s="4" t="n">
-        <v>533.6</v>
+        <v>509.45</v>
       </c>
       <c r="D173" s="4" t="n">
-        <v>36</v>
+        <v>36.38</v>
       </c>
       <c r="E173" s="4" t="n">
-        <v>51.79</v>
+        <v>52.35</v>
       </c>
       <c r="F173" s="4" t="n">
-        <v>62.06</v>
+        <v>62.95</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>BECTORFOOD</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -6264,22 +5784,22 @@
         </is>
       </c>
       <c r="C174" s="4" t="n">
-        <v>199.71</v>
+        <v>205.41</v>
       </c>
       <c r="D174" s="4" t="n">
-        <v>35.8</v>
+        <v>36.09</v>
       </c>
       <c r="E174" s="4" t="n">
-        <v>53.52</v>
+        <v>47.44</v>
       </c>
       <c r="F174" s="4" t="n">
-        <v>60.48</v>
+        <v>45.54</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>KNRCON</t>
+          <t>CENTURYPLY</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -6288,22 +5808,22 @@
         </is>
       </c>
       <c r="C175" s="4" t="n">
-        <v>113.29</v>
+        <v>665.7</v>
       </c>
       <c r="D175" s="4" t="n">
-        <v>35.7</v>
+        <v>35.92</v>
       </c>
       <c r="E175" s="4" t="n">
-        <v>38.15</v>
+        <v>32.13</v>
       </c>
       <c r="F175" s="4" t="n">
-        <v>32.6</v>
+        <v>44.26</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>HCC</t>
+          <t>RCF</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -6312,22 +5832,22 @@
         </is>
       </c>
       <c r="C176" s="4" t="n">
-        <v>20.23</v>
+        <v>104.44</v>
       </c>
       <c r="D176" s="4" t="n">
-        <v>35.56</v>
+        <v>35.84</v>
       </c>
       <c r="E176" s="4" t="n">
-        <v>44.79</v>
+        <v>30.71</v>
       </c>
       <c r="F176" s="4" t="n">
-        <v>44.96</v>
+        <v>40.18</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>TSFINV</t>
+          <t>MAHSCOOTER</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -6336,22 +5856,22 @@
         </is>
       </c>
       <c r="C177" s="4" t="n">
-        <v>409.15</v>
+        <v>12155</v>
       </c>
       <c r="D177" s="4" t="n">
-        <v>35.47</v>
+        <v>35.64</v>
       </c>
       <c r="E177" s="4" t="n">
-        <v>46.47</v>
+        <v>43.76</v>
       </c>
       <c r="F177" s="4" t="n">
-        <v>52.81</v>
+        <v>51.65</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>ORKLAINDIA</t>
+          <t>GOKEX</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -6360,22 +5880,22 @@
         </is>
       </c>
       <c r="C178" s="4" t="n">
-        <v>537.2</v>
+        <v>667.7</v>
       </c>
       <c r="D178" s="4" t="n">
-        <v>35.29</v>
+        <v>35.6</v>
       </c>
       <c r="E178" s="4" t="n">
-        <v>36.46</v>
+        <v>38.43</v>
       </c>
       <c r="F178" s="4" t="n">
-        <v/>
+        <v>46.29</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>ZAGGLE</t>
+          <t>SURYAROSNI</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -6384,22 +5904,22 @@
         </is>
       </c>
       <c r="C179" s="4" t="n">
-        <v>171.73</v>
+        <v>208.33</v>
       </c>
       <c r="D179" s="4" t="n">
-        <v>35.16</v>
+        <v>35.56</v>
       </c>
       <c r="E179" s="4" t="n">
-        <v>31.02</v>
+        <v>39.66</v>
       </c>
       <c r="F179" s="4" t="n">
-        <v>36.68</v>
+        <v>43.96</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>WAAREERTL</t>
+          <t>ZAGGLE</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -6408,22 +5928,22 @@
         </is>
       </c>
       <c r="C180" s="4" t="n">
-        <v>808.8</v>
+        <v>168.3</v>
       </c>
       <c r="D180" s="4" t="n">
-        <v>35.14</v>
+        <v>35.42</v>
       </c>
       <c r="E180" s="4" t="n">
-        <v>34.48</v>
+        <v>30.07</v>
       </c>
       <c r="F180" s="4" t="n">
-        <v>38.38</v>
+        <v>36.37</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>RAYMONDLSL</t>
+          <t>SUNTECK</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -6432,22 +5952,22 @@
         </is>
       </c>
       <c r="C181" s="4" t="n">
-        <v>627.7</v>
+        <v>271.15</v>
       </c>
       <c r="D181" s="4" t="n">
-        <v>34.98</v>
+        <v>35.18</v>
       </c>
       <c r="E181" s="4" t="n">
-        <v>34.52</v>
+        <v>35.33</v>
       </c>
       <c r="F181" s="4" t="n">
-        <v>23.04</v>
+        <v>38.22</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>GSFC</t>
+          <t>INDIGOPNTS</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -6456,22 +5976,22 @@
         </is>
       </c>
       <c r="C182" s="4" t="n">
-        <v>146.9</v>
+        <v>1022.7</v>
       </c>
       <c r="D182" s="4" t="n">
-        <v>34.84</v>
+        <v>35.01</v>
       </c>
       <c r="E182" s="4" t="n">
-        <v>39.33</v>
+        <v>46.38</v>
       </c>
       <c r="F182" s="4" t="n">
-        <v>42.1</v>
+        <v>45.93</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>STARCEMENT</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -6480,22 +6000,22 @@
         </is>
       </c>
       <c r="C183" s="4" t="n">
-        <v>178.39</v>
+        <v>179.96</v>
       </c>
       <c r="D183" s="4" t="n">
-        <v>34.74</v>
+        <v>34.93</v>
       </c>
       <c r="E183" s="4" t="n">
-        <v>29.43</v>
+        <v>40.74</v>
       </c>
       <c r="F183" s="4" t="n">
-        <v>41.74</v>
+        <v>39.69</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>VAIBHAVGBL</t>
+          <t>GOKULAGRO</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -6504,22 +6024,22 @@
         </is>
       </c>
       <c r="C184" s="4" t="n">
-        <v>203.53</v>
+        <v>206.74</v>
       </c>
       <c r="D184" s="4" t="n">
-        <v>34.64</v>
+        <v>34.9</v>
       </c>
       <c r="E184" s="4" t="n">
-        <v>40.14</v>
+        <v>44.27</v>
       </c>
       <c r="F184" s="4" t="n">
-        <v>43.31</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>AVL</t>
+          <t>CSBBANK</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -6528,22 +6048,22 @@
         </is>
       </c>
       <c r="C185" s="4" t="n">
-        <v>572.3</v>
+        <v>300.35</v>
       </c>
       <c r="D185" s="4" t="n">
-        <v>34.57</v>
+        <v>34.8</v>
       </c>
       <c r="E185" s="4" t="n">
-        <v>48.33</v>
+        <v>38.66</v>
       </c>
       <c r="F185" s="4" t="n">
-        <v>56.31</v>
+        <v>42.35</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>GOKEX</t>
+          <t>EQUITASBNK</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -6552,22 +6072,22 @@
         </is>
       </c>
       <c r="C186" s="4" t="n">
-        <v>688.75</v>
+        <v>66.02</v>
       </c>
       <c r="D186" s="4" t="n">
-        <v>34.14</v>
+        <v>34.65</v>
       </c>
       <c r="E186" s="4" t="n">
-        <v>40.1</v>
+        <v>42.01</v>
       </c>
       <c r="F186" s="4" t="n">
-        <v>47.11</v>
+        <v>48.58</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>AWFIS</t>
+          <t>JLHL</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -6576,22 +6096,22 @@
         </is>
       </c>
       <c r="C187" s="4" t="n">
-        <v>235.26</v>
+        <v>255.7</v>
       </c>
       <c r="D187" s="4" t="n">
-        <v>33.77</v>
+        <v>34.56</v>
       </c>
       <c r="E187" s="4" t="n">
-        <v>33.48</v>
+        <v>37.17</v>
       </c>
       <c r="F187" s="4" t="n">
-        <v>28.22</v>
+        <v>46.26</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>SANDUMA</t>
+          <t>AHLUCONT</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -6600,22 +6120,22 @@
         </is>
       </c>
       <c r="C188" s="4" t="n">
-        <v>177.67</v>
+        <v>557.6</v>
       </c>
       <c r="D188" s="4" t="n">
-        <v>33.77</v>
+        <v>34.44</v>
       </c>
       <c r="E188" s="4" t="n">
-        <v>37.65</v>
+        <v>25.09</v>
       </c>
       <c r="F188" s="4" t="n">
-        <v>49.5</v>
+        <v>38.87</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>WAKEFIT</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -6624,22 +6144,22 @@
         </is>
       </c>
       <c r="C189" s="4" t="n">
-        <v>184</v>
+        <v>131.39</v>
       </c>
       <c r="D189" s="4" t="n">
-        <v>33.45</v>
+        <v>34.38</v>
       </c>
       <c r="E189" s="4" t="n">
-        <v>42.21</v>
+        <v>43.42</v>
       </c>
       <c r="F189" s="4" t="n">
-        <v>40.36</v>
+        <v/>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>MOIL</t>
+          <t>RUBICON</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -6648,22 +6168,22 @@
         </is>
       </c>
       <c r="C190" s="4" t="n">
-        <v>232.66</v>
+        <v>1548.5</v>
       </c>
       <c r="D190" s="4" t="n">
-        <v>33.26</v>
+        <v>34.24</v>
       </c>
       <c r="E190" s="4" t="n">
-        <v>29.72</v>
+        <v>58.91</v>
       </c>
       <c r="F190" s="4" t="n">
-        <v>39.05</v>
+        <v/>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>VIPIND</t>
+          <t>IXIGO</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -6672,22 +6192,22 @@
         </is>
       </c>
       <c r="C191" s="4" t="n">
-        <v>280.75</v>
+        <v>150.75</v>
       </c>
       <c r="D191" s="4" t="n">
-        <v>33.23</v>
+        <v>34.24</v>
       </c>
       <c r="E191" s="4" t="n">
-        <v>36.37</v>
+        <v>39.35</v>
       </c>
       <c r="F191" s="4" t="n">
-        <v>34.13</v>
+        <v>39.98</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>OSWALPUMPS</t>
+          <t>IFBIND</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -6696,22 +6216,22 @@
         </is>
       </c>
       <c r="C192" s="4" t="n">
-        <v>264.25</v>
+        <v>1161</v>
       </c>
       <c r="D192" s="4" t="n">
-        <v>33.06</v>
+        <v>34.22</v>
       </c>
       <c r="E192" s="4" t="n">
-        <v>28.85</v>
+        <v>39.6</v>
       </c>
       <c r="F192" s="4" t="n">
-        <v>25.82</v>
+        <v>45.96</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>RENUKA</t>
+          <t>BAJAJELEC</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -6720,22 +6240,22 @@
         </is>
       </c>
       <c r="C193" s="4" t="n">
-        <v>21.34</v>
+        <v>298</v>
       </c>
       <c r="D193" s="4" t="n">
-        <v>32.97</v>
+        <v>34.2</v>
       </c>
       <c r="E193" s="4" t="n">
-        <v>39.62</v>
+        <v>32.91</v>
       </c>
       <c r="F193" s="4" t="n">
-        <v>37.3</v>
+        <v>28.25</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>TRIVENI</t>
+          <t>NETWORK18</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -6744,22 +6264,22 @@
         </is>
       </c>
       <c r="C194" s="4" t="n">
-        <v>230.92</v>
+        <v>24.69</v>
       </c>
       <c r="D194" s="4" t="n">
-        <v>32.78</v>
+        <v>34.09</v>
       </c>
       <c r="E194" s="4" t="n">
-        <v>35.65</v>
+        <v>29.01</v>
       </c>
       <c r="F194" s="4" t="n">
-        <v>40.14</v>
+        <v>32.46</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>NETWORK18</t>
+          <t>METROPOLIS</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -6768,22 +6288,22 @@
         </is>
       </c>
       <c r="C195" s="4" t="n">
-        <v>25.43</v>
+        <v>529.25</v>
       </c>
       <c r="D195" s="4" t="n">
-        <v>32.65</v>
+        <v>34.08</v>
       </c>
       <c r="E195" s="4" t="n">
-        <v>30.42</v>
+        <v>46.57</v>
       </c>
       <c r="F195" s="4" t="n">
-        <v>32.85</v>
+        <v>54.63</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>SKFINDIA</t>
+          <t>MAHSEAMLES</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -6792,22 +6312,22 @@
         </is>
       </c>
       <c r="C196" s="4" t="n">
-        <v>1450.2</v>
+        <v>618.1</v>
       </c>
       <c r="D196" s="4" t="n">
-        <v>32.31</v>
+        <v>34.05</v>
       </c>
       <c r="E196" s="4" t="n">
-        <v>33.79</v>
+        <v>47.66</v>
       </c>
       <c r="F196" s="4" t="n">
-        <v>31.81</v>
+        <v>50.67</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>SFL</t>
+          <t>SWSOLAR</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -6816,22 +6336,22 @@
         </is>
       </c>
       <c r="C197" s="4" t="n">
-        <v>616.65</v>
+        <v>162.12</v>
       </c>
       <c r="D197" s="4" t="n">
-        <v>32.27</v>
+        <v>33.91</v>
       </c>
       <c r="E197" s="4" t="n">
-        <v>44.6</v>
+        <v>32.95</v>
       </c>
       <c r="F197" s="4" t="n">
-        <v>44</v>
+        <v>37.76</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>CMSINFO</t>
+          <t>REFEX</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -6840,22 +6360,22 @@
         </is>
       </c>
       <c r="C198" s="4" t="n">
-        <v>220.69</v>
+        <v>254.4</v>
       </c>
       <c r="D198" s="4" t="n">
-        <v>32.15</v>
+        <v>33.82</v>
       </c>
       <c r="E198" s="4" t="n">
-        <v>29.03</v>
+        <v>39.64</v>
       </c>
       <c r="F198" s="4" t="n">
-        <v>30.87</v>
+        <v>45.79</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>RALLIS</t>
+          <t>TARC</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -6864,22 +6384,22 @@
         </is>
       </c>
       <c r="C199" s="4" t="n">
-        <v>199.69</v>
+        <v>117.47</v>
       </c>
       <c r="D199" s="4" t="n">
-        <v>32.07</v>
+        <v>33.68</v>
       </c>
       <c r="E199" s="4" t="n">
-        <v>30.44</v>
+        <v>40.6</v>
       </c>
       <c r="F199" s="4" t="n">
-        <v>40.72</v>
+        <v>44.15</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>DBREALTY</t>
+          <t>TARC</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -6888,22 +6408,22 @@
         </is>
       </c>
       <c r="C200" s="4" t="n">
-        <v>91.7</v>
+        <v>117.47</v>
       </c>
       <c r="D200" s="4" t="n">
-        <v>32.07</v>
+        <v>33.68</v>
       </c>
       <c r="E200" s="4" t="n">
-        <v>37.24</v>
+        <v>40.6</v>
       </c>
       <c r="F200" s="4" t="n">
-        <v>40.62</v>
+        <v>44.15</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>PRAJIND</t>
+          <t>JKPAPER</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -6912,22 +6432,22 @@
         </is>
       </c>
       <c r="C201" s="4" t="n">
-        <v>303.25</v>
+        <v>365.5</v>
       </c>
       <c r="D201" s="4" t="n">
-        <v>31.89</v>
+        <v>33.63</v>
       </c>
       <c r="E201" s="4" t="n">
-        <v>39.29</v>
+        <v>46.14</v>
       </c>
       <c r="F201" s="4" t="n">
-        <v>41</v>
+        <v>50.29</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>ALKYLAMINE</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -6936,22 +6456,22 @@
         </is>
       </c>
       <c r="C202" s="4" t="n">
-        <v>1741.4</v>
+        <v>96.75</v>
       </c>
       <c r="D202" s="4" t="n">
-        <v>31.62</v>
+        <v>33.55</v>
       </c>
       <c r="E202" s="4" t="n">
-        <v>46.22</v>
+        <v>40.76</v>
       </c>
       <c r="F202" s="4" t="n">
-        <v>47.82</v>
+        <v>39.72</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>METROPOLIS</t>
+          <t>RELAXO</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -6960,22 +6480,22 @@
         </is>
       </c>
       <c r="C203" s="4" t="n">
-        <v>537.9</v>
+        <v>286</v>
       </c>
       <c r="D203" s="4" t="n">
-        <v>31.5</v>
+        <v>32.68</v>
       </c>
       <c r="E203" s="4" t="n">
-        <v>48.37</v>
+        <v>37.21</v>
       </c>
       <c r="F203" s="4" t="n">
-        <v>55.88</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>CENTURYPLY</t>
+          <t>PRICOLLTD</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -6984,22 +6504,22 @@
         </is>
       </c>
       <c r="C204" s="4" t="n">
-        <v>666.45</v>
+        <v>670.85</v>
       </c>
       <c r="D204" s="4" t="n">
-        <v>31.49</v>
+        <v>32.64</v>
       </c>
       <c r="E204" s="4" t="n">
-        <v>31.79</v>
+        <v>49.3</v>
       </c>
       <c r="F204" s="4" t="n">
-        <v>44.31</v>
+        <v>58.58</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>VIYASH</t>
+          <t>RAYMONDLSL</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -7008,22 +6528,22 @@
         </is>
       </c>
       <c r="C205" s="4" t="n">
-        <v>231.75</v>
+        <v>596.4</v>
       </c>
       <c r="D205" s="4" t="n">
-        <v>31.43</v>
+        <v>32.36</v>
       </c>
       <c r="E205" s="4" t="n">
-        <v>44.84</v>
+        <v>32.27</v>
       </c>
       <c r="F205" s="4" t="n">
-        <v>55.77</v>
+        <v>22.34</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>BORORENEW</t>
+          <t>HAPPSTMNDS</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -7032,22 +6552,22 @@
         </is>
       </c>
       <c r="C206" s="4" t="n">
-        <v>449.6</v>
+        <v>306.1</v>
       </c>
       <c r="D206" s="4" t="n">
-        <v>31.31</v>
+        <v>32.35</v>
       </c>
       <c r="E206" s="4" t="n">
-        <v>37</v>
+        <v>34.99</v>
       </c>
       <c r="F206" s="4" t="n">
-        <v>45.35</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>INOXGREEN</t>
+          <t>RTNINDIA</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -7056,22 +6576,22 @@
         </is>
       </c>
       <c r="C207" s="4" t="n">
-        <v>159</v>
+        <v>24.95</v>
       </c>
       <c r="D207" s="4" t="n">
-        <v>31.19</v>
+        <v>32.19</v>
       </c>
       <c r="E207" s="4" t="n">
-        <v>40.29</v>
+        <v>29.66</v>
       </c>
       <c r="F207" s="4" t="n">
-        <v>49.29</v>
+        <v>36.32</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>ASHAPURMIN</t>
+          <t>SAMHI</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -7080,22 +6600,22 @@
         </is>
       </c>
       <c r="C208" s="4" t="n">
-        <v>489.95</v>
+        <v>141.9</v>
       </c>
       <c r="D208" s="4" t="n">
-        <v>30.88</v>
+        <v>32.12</v>
       </c>
       <c r="E208" s="4" t="n">
-        <v>34.09</v>
+        <v>36.43</v>
       </c>
       <c r="F208" s="4" t="n">
-        <v>48.55</v>
+        <v>41.51</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>VMART</t>
+          <t>HCC</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -7104,22 +6624,22 @@
         </is>
       </c>
       <c r="C209" s="4" t="n">
-        <v>746.1</v>
+        <v>19.01</v>
       </c>
       <c r="D209" s="4" t="n">
-        <v>30.84</v>
+        <v>31.75</v>
       </c>
       <c r="E209" s="4" t="n">
-        <v>49.38</v>
+        <v>41.55</v>
       </c>
       <c r="F209" s="4" t="n">
-        <v>51.05</v>
+        <v>43.83</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>RELIGARE</t>
+          <t>SMARTWORKS</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -7128,22 +6648,22 @@
         </is>
       </c>
       <c r="C210" s="4" t="n">
-        <v>224.59</v>
+        <v>474.3</v>
       </c>
       <c r="D210" s="4" t="n">
-        <v>30.68</v>
+        <v>31.68</v>
       </c>
       <c r="E210" s="4" t="n">
-        <v>42.1</v>
+        <v>47.02</v>
       </c>
       <c r="F210" s="4" t="n">
-        <v>48.07</v>
+        <v>48.84</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>GOKULAGRO</t>
+          <t>AURIONPRO</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -7152,22 +6672,22 @@
         </is>
       </c>
       <c r="C211" s="4" t="n">
-        <v>210.1</v>
+        <v>601.6</v>
       </c>
       <c r="D211" s="4" t="n">
-        <v>30.61</v>
+        <v>31.14</v>
       </c>
       <c r="E211" s="4" t="n">
-        <v>46.36</v>
+        <v>28.56</v>
       </c>
       <c r="F211" s="4" t="n">
-        <v>58.52</v>
+        <v>35.79</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>SHARDACROP</t>
+          <t>VGUARD</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -7176,22 +6696,22 @@
         </is>
       </c>
       <c r="C212" s="4" t="n">
-        <v>709.2</v>
+        <v>288.2</v>
       </c>
       <c r="D212" s="4" t="n">
-        <v>30.56</v>
+        <v>30.65</v>
       </c>
       <c r="E212" s="4" t="n">
-        <v>33.93</v>
+        <v>36.59</v>
       </c>
       <c r="F212" s="4" t="n">
-        <v>47.43</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>PRSMJOHNSN</t>
+          <t>SFL</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -7200,22 +6720,22 @@
         </is>
       </c>
       <c r="C213" s="4" t="n">
-        <v>103.61</v>
+        <v>603.65</v>
       </c>
       <c r="D213" s="4" t="n">
-        <v>30.45</v>
+        <v>30.6</v>
       </c>
       <c r="E213" s="4" t="n">
-        <v>35.83</v>
+        <v>42.93</v>
       </c>
       <c r="F213" s="4" t="n">
-        <v>37.78</v>
+        <v>43.38</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>WEBELSOLAR</t>
+          <t>VIPIND</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -7224,22 +6744,22 @@
         </is>
       </c>
       <c r="C214" s="4" t="n">
-        <v>68.7</v>
+        <v>269.55</v>
       </c>
       <c r="D214" s="4" t="n">
-        <v>30.28</v>
+        <v>30.52</v>
       </c>
       <c r="E214" s="4" t="n">
-        <v>32.38</v>
+        <v>33.45</v>
       </c>
       <c r="F214" s="4" t="n">
-        <v>43.8</v>
+        <v>32.96</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>RTNINDIA</t>
+          <t>WEBELSOLAR</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -7248,22 +6768,22 @@
         </is>
       </c>
       <c r="C215" s="4" t="n">
-        <v>25.32</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="D215" s="4" t="n">
-        <v>30.15</v>
+        <v>30.25</v>
       </c>
       <c r="E215" s="4" t="n">
-        <v>30.4</v>
+        <v>31.27</v>
       </c>
       <c r="F215" s="4" t="n">
-        <v>36.52</v>
+        <v>43.03</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>ASHOKA</t>
+          <t>MEDPLUS</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -7272,22 +6792,22 @@
         </is>
       </c>
       <c r="C216" s="4" t="n">
-        <v>105.31</v>
+        <v>625.3</v>
       </c>
       <c r="D216" s="4" t="n">
-        <v>29.98</v>
+        <v>30.16</v>
       </c>
       <c r="E216" s="4" t="n">
-        <v>31.18</v>
+        <v>25.81</v>
       </c>
       <c r="F216" s="4" t="n">
-        <v>39.5</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>KANSAINER</t>
+          <t>ASHAPURMIN</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -7296,22 +6816,22 @@
         </is>
       </c>
       <c r="C217" s="4" t="n">
-        <v>175.27</v>
+        <v>470.8</v>
       </c>
       <c r="D217" s="4" t="n">
-        <v>29.87</v>
+        <v>30.1</v>
       </c>
       <c r="E217" s="4" t="n">
-        <v>33.67</v>
+        <v>32.54</v>
       </c>
       <c r="F217" s="4" t="n">
-        <v>35.48</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>V2RETAIL</t>
+          <t>HEMIPROP</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -7320,22 +6840,22 @@
         </is>
       </c>
       <c r="C218" s="4" t="n">
-        <v>201.39</v>
+        <v>110.35</v>
       </c>
       <c r="D218" s="4" t="n">
-        <v>29.74</v>
+        <v>29.82</v>
       </c>
       <c r="E218" s="4" t="n">
-        <v>40.9</v>
+        <v>30.13</v>
       </c>
       <c r="F218" s="4" t="n">
-        <v>56.72</v>
+        <v>40.77</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>VIKRAMSOLR</t>
+          <t>RELIGARE</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -7344,22 +6864,22 @@
         </is>
       </c>
       <c r="C219" s="4" t="n">
-        <v>154.35</v>
+        <v>217.59</v>
       </c>
       <c r="D219" s="4" t="n">
-        <v>29.66</v>
+        <v>29.69</v>
       </c>
       <c r="E219" s="4" t="n">
-        <v>33.01</v>
+        <v>39.85</v>
       </c>
       <c r="F219" s="4" t="n">
-        <v/>
+        <v>46.65</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>IMFA</t>
+          <t>JKLAKSHMI</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -7368,22 +6888,22 @@
         </is>
       </c>
       <c r="C220" s="4" t="n">
-        <v>1176.8</v>
+        <v>467.3</v>
       </c>
       <c r="D220" s="4" t="n">
-        <v>29.49</v>
+        <v>29.69</v>
       </c>
       <c r="E220" s="4" t="n">
-        <v>39.09</v>
+        <v>27.86</v>
       </c>
       <c r="F220" s="4" t="n">
-        <v>54.33</v>
+        <v>34.47</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>IFBIND</t>
+          <t>PRAJIND</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -7392,22 +6912,22 @@
         </is>
       </c>
       <c r="C221" s="4" t="n">
-        <v>1166.2</v>
+        <v>285.8</v>
       </c>
       <c r="D221" s="4" t="n">
-        <v>29.29</v>
+        <v>29.28</v>
       </c>
       <c r="E221" s="4" t="n">
-        <v>40.92</v>
+        <v>35.03</v>
       </c>
       <c r="F221" s="4" t="n">
-        <v>46.08</v>
+        <v>39.75</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>JYOTHYLAB</t>
+          <t>NFL</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -7416,22 +6936,22 @@
         </is>
       </c>
       <c r="C222" s="4" t="n">
-        <v>182.91</v>
+        <v>61.74</v>
       </c>
       <c r="D222" s="4" t="n">
-        <v>28.92</v>
+        <v>29.01</v>
       </c>
       <c r="E222" s="4" t="n">
-        <v>32.69</v>
+        <v>27.06</v>
       </c>
       <c r="F222" s="4" t="n">
-        <v>35.75</v>
+        <v>39.01</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>PNCINFRA</t>
+          <t>FIEMIND</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -7440,22 +6960,22 @@
         </is>
       </c>
       <c r="C223" s="4" t="n">
-        <v>138.16</v>
+        <v>1747.7</v>
       </c>
       <c r="D223" s="4" t="n">
-        <v>28.8</v>
+        <v>28.64</v>
       </c>
       <c r="E223" s="4" t="n">
-        <v>26.66</v>
+        <v>32.47</v>
       </c>
       <c r="F223" s="4" t="n">
-        <v>34.61</v>
+        <v>48.12</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>ADVENZYMES</t>
+          <t>ASHOKA</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -7464,22 +6984,22 @@
         </is>
       </c>
       <c r="C224" s="4" t="n">
-        <v>274.25</v>
+        <v>102.02</v>
       </c>
       <c r="D224" s="4" t="n">
-        <v>28.44</v>
+        <v>28.59</v>
       </c>
       <c r="E224" s="4" t="n">
-        <v>35.27</v>
+        <v>29.21</v>
       </c>
       <c r="F224" s="4" t="n">
-        <v>43.71</v>
+        <v>38.96</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>JLHL</t>
+          <t>THYROCARE</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -7488,22 +7008,22 @@
         </is>
       </c>
       <c r="C225" s="4" t="n">
-        <v>259.85</v>
+        <v>499.7</v>
       </c>
       <c r="D225" s="4" t="n">
-        <v>28.44</v>
+        <v>28.57</v>
       </c>
       <c r="E225" s="4" t="n">
-        <v>39.06</v>
+        <v>46.64</v>
       </c>
       <c r="F225" s="4" t="n">
-        <v>47.11</v>
+        <v>58.43</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>INDIAGLYCO</t>
+          <t>INOXGREEN</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -7512,22 +7032,22 @@
         </is>
       </c>
       <c r="C226" s="4" t="n">
-        <v>298.8</v>
+        <v>128.92</v>
       </c>
       <c r="D226" s="4" t="n">
-        <v>28.26</v>
+        <v>28.45</v>
       </c>
       <c r="E226" s="4" t="n">
-        <v>27.05</v>
+        <v>31.16</v>
       </c>
       <c r="F226" s="4" t="n">
-        <v>36</v>
+        <v>44.67</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>ANUP</t>
+          <t>AVANTIFEED</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -7536,22 +7056,22 @@
         </is>
       </c>
       <c r="C227" s="4" t="n">
-        <v>1566.7</v>
+        <v>699.1</v>
       </c>
       <c r="D227" s="4" t="n">
-        <v>28.15</v>
+        <v>28.43</v>
       </c>
       <c r="E227" s="4" t="n">
-        <v>34.27</v>
+        <v>29.71</v>
       </c>
       <c r="F227" s="4" t="n">
-        <v>42.52</v>
+        <v>45.69</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>AHLUCONT</t>
+          <t>BORORENEW</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -7560,22 +7080,22 @@
         </is>
       </c>
       <c r="C228" s="4" t="n">
-        <v>555.9</v>
+        <v>430.4</v>
       </c>
       <c r="D228" s="4" t="n">
-        <v>28.1</v>
+        <v>28.3</v>
       </c>
       <c r="E228" s="4" t="n">
-        <v>24.5</v>
+        <v>34.54</v>
       </c>
       <c r="F228" s="4" t="n">
-        <v>38.78</v>
+        <v>44.11</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>BAJAJELEC</t>
+          <t>PNCINFRA</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -7584,22 +7104,22 @@
         </is>
       </c>
       <c r="C229" s="4" t="n">
-        <v>299.8</v>
+        <v>134.74</v>
       </c>
       <c r="D229" s="4" t="n">
-        <v>28.05</v>
+        <v>28.25</v>
       </c>
       <c r="E229" s="4" t="n">
-        <v>33.29</v>
+        <v>25.56</v>
       </c>
       <c r="F229" s="4" t="n">
-        <v>28.35</v>
+        <v>34.03</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>FIEMIND</t>
+          <t>SAFARI</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -7608,22 +7128,22 @@
         </is>
       </c>
       <c r="C230" s="4" t="n">
-        <v>1794.8</v>
+        <v>1319.6</v>
       </c>
       <c r="D230" s="4" t="n">
-        <v>27.95</v>
+        <v>28.03</v>
       </c>
       <c r="E230" s="4" t="n">
-        <v>33.91</v>
+        <v>32.6</v>
       </c>
       <c r="F230" s="4" t="n">
-        <v>49.48</v>
+        <v>36.91</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>AVANTIFEED</t>
+          <t>SKFINDIA</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -7632,22 +7152,22 @@
         </is>
       </c>
       <c r="C231" s="4" t="n">
-        <v>711.55</v>
+        <v>1398.8</v>
       </c>
       <c r="D231" s="4" t="n">
-        <v>27.46</v>
+        <v>28.03</v>
       </c>
       <c r="E231" s="4" t="n">
-        <v>30.44</v>
+        <v>30.79</v>
       </c>
       <c r="F231" s="4" t="n">
-        <v>46.13</v>
+        <v>31.36</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>JKLAKSHMI</t>
+          <t>CMSINFO</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -7656,22 +7176,22 @@
         </is>
       </c>
       <c r="C232" s="4" t="n">
-        <v>476.6</v>
+        <v>213.85</v>
       </c>
       <c r="D232" s="4" t="n">
-        <v>27.4</v>
+        <v>27.92</v>
       </c>
       <c r="E232" s="4" t="n">
-        <v>28.65</v>
+        <v>27.31</v>
       </c>
       <c r="F232" s="4" t="n">
-        <v>34.92</v>
+        <v>30.19</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>ROUTE</t>
+          <t>ADVENZYMES</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -7680,22 +7200,22 @@
         </is>
       </c>
       <c r="C233" s="4" t="n">
-        <v>436.4</v>
+        <v>267.15</v>
       </c>
       <c r="D233" s="4" t="n">
-        <v>26.97</v>
+        <v>27.63</v>
       </c>
       <c r="E233" s="4" t="n">
-        <v>30.79</v>
+        <v>33.26</v>
       </c>
       <c r="F233" s="4" t="n">
-        <v>28.07</v>
+        <v>42.81</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>VGUARD</t>
+          <t>OSWALPUMPS</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -7704,22 +7224,22 @@
         </is>
       </c>
       <c r="C234" s="4" t="n">
-        <v>294.55</v>
+        <v>254.35</v>
       </c>
       <c r="D234" s="4" t="n">
-        <v>26.77</v>
+        <v>27.53</v>
       </c>
       <c r="E234" s="4" t="n">
-        <v>38.79</v>
+        <v>27.46</v>
       </c>
       <c r="F234" s="4" t="n">
-        <v>42.68</v>
+        <v>25.36</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>ORIENTCEM</t>
+          <t>HGINFRA</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -7728,22 +7248,22 @@
         </is>
       </c>
       <c r="C235" s="4" t="n">
-        <v>115.91</v>
+        <v>401.75</v>
       </c>
       <c r="D235" s="4" t="n">
-        <v>26.69</v>
+        <v>27.28</v>
       </c>
       <c r="E235" s="4" t="n">
-        <v>26.22</v>
+        <v>25.15</v>
       </c>
       <c r="F235" s="4" t="n">
-        <v>32.93</v>
+        <v>31.25</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>SWSOLAR</t>
+          <t>CERA</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -7752,22 +7272,22 @@
         </is>
       </c>
       <c r="C236" s="4" t="n">
-        <v>164.82</v>
+        <v>5002.5</v>
       </c>
       <c r="D236" s="4" t="n">
-        <v>26.67</v>
+        <v>27.16</v>
       </c>
       <c r="E236" s="4" t="n">
-        <v>33.91</v>
+        <v>35.49</v>
       </c>
       <c r="F236" s="4" t="n">
-        <v>37.99</v>
+        <v>42.53</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>CAMPUS</t>
+          <t>PRSMJOHNSN</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -7776,22 +7296,22 @@
         </is>
       </c>
       <c r="C237" s="4" t="n">
-        <v>205.83</v>
+        <v>97.47</v>
       </c>
       <c r="D237" s="4" t="n">
-        <v>26.53</v>
+        <v>27.01</v>
       </c>
       <c r="E237" s="4" t="n">
-        <v>34.43</v>
+        <v>31.49</v>
       </c>
       <c r="F237" s="4" t="n">
-        <v>38.72</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>ALOKINDS</t>
+          <t>SHAKTIPUMP</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -7800,22 +7320,22 @@
         </is>
       </c>
       <c r="C238" s="4" t="n">
-        <v>7.06</v>
+        <v>419</v>
       </c>
       <c r="D238" s="4" t="n">
-        <v>26.43</v>
+        <v>26.69</v>
       </c>
       <c r="E238" s="4" t="n">
-        <v>22.5</v>
+        <v>30.13</v>
       </c>
       <c r="F238" s="4" t="n">
-        <v>29.29</v>
+        <v>40.33</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>HAPPSTMNDS</t>
+          <t>STARCEMENT</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -7824,22 +7344,22 @@
         </is>
       </c>
       <c r="C239" s="4" t="n">
-        <v>304.7</v>
+        <v>168.46</v>
       </c>
       <c r="D239" s="4" t="n">
-        <v>26.41</v>
+        <v>26.53</v>
       </c>
       <c r="E239" s="4" t="n">
-        <v>34.62</v>
+        <v>25.84</v>
       </c>
       <c r="F239" s="4" t="n">
-        <v>28.22</v>
+        <v>39.44</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>HGINFRA</t>
+          <t>HCG</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -7848,22 +7368,22 @@
         </is>
       </c>
       <c r="C240" s="4" t="n">
-        <v>419.9</v>
+        <v>589.2</v>
       </c>
       <c r="D240" s="4" t="n">
-        <v>26.19</v>
+        <v>26.5</v>
       </c>
       <c r="E240" s="4" t="n">
-        <v>26.72</v>
+        <v>37.51</v>
       </c>
       <c r="F240" s="4" t="n">
-        <v>31.82</v>
+        <v>51.34</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>NFL</t>
+          <t>ANUP</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -7872,22 +7392,22 @@
         </is>
       </c>
       <c r="C241" s="4" t="n">
-        <v>63.85</v>
+        <v>1488.2</v>
       </c>
       <c r="D241" s="4" t="n">
-        <v>26.19</v>
+        <v>26.16</v>
       </c>
       <c r="E241" s="4" t="n">
-        <v>29.93</v>
+        <v>31.92</v>
       </c>
       <c r="F241" s="4" t="n">
-        <v>39.94</v>
+        <v>41.47</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>AURIONPRO</t>
+          <t>ORIENTCEM</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -7896,22 +7416,22 @@
         </is>
       </c>
       <c r="C242" s="4" t="n">
-        <v>607.8</v>
+        <v>111.62</v>
       </c>
       <c r="D242" s="4" t="n">
-        <v>25.78</v>
+        <v>25.96</v>
       </c>
       <c r="E242" s="4" t="n">
-        <v>28.24</v>
+        <v>23.76</v>
       </c>
       <c r="F242" s="4" t="n">
-        <v>35.96</v>
+        <v>32.29</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>ARVINDFASN</t>
+          <t>RTNPOWER</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -7920,22 +7440,22 @@
         </is>
       </c>
       <c r="C243" s="4" t="n">
-        <v>379.7</v>
+        <v>6.54</v>
       </c>
       <c r="D243" s="4" t="n">
-        <v>25.55</v>
+        <v>25.71</v>
       </c>
       <c r="E243" s="4" t="n">
-        <v>31.38</v>
+        <v>24.5</v>
       </c>
       <c r="F243" s="4" t="n">
-        <v>41.02</v>
+        <v>39.08</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>CRAMC</t>
+          <t>CAMPUS</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -7944,22 +7464,22 @@
         </is>
       </c>
       <c r="C244" s="4" t="n">
-        <v>216.52</v>
+        <v>197</v>
       </c>
       <c r="D244" s="4" t="n">
-        <v>25.09</v>
+        <v>24.84</v>
       </c>
       <c r="E244" s="4" t="n">
-        <v>31.44</v>
+        <v>30.65</v>
       </c>
       <c r="F244" s="4" t="n">
-        <v/>
+        <v>37.3</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>HEMIPROP</t>
+          <t>DBREALTY</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
@@ -7968,22 +7488,22 @@
         </is>
       </c>
       <c r="C245" s="4" t="n">
-        <v>111.5</v>
+        <v>84.98</v>
       </c>
       <c r="D245" s="4" t="n">
-        <v>24.87</v>
+        <v>24.44</v>
       </c>
       <c r="E245" s="4" t="n">
-        <v>30.92</v>
+        <v>33.98</v>
       </c>
       <c r="F245" s="4" t="n">
-        <v>41.08</v>
+        <v>39.42</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>SAFARI</t>
+          <t>EUREKAFORB</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -7992,22 +7512,22 @@
         </is>
       </c>
       <c r="C246" s="4" t="n">
-        <v>1378.8</v>
+        <v>339</v>
       </c>
       <c r="D246" s="4" t="n">
-        <v>24.46</v>
+        <v>23.42</v>
       </c>
       <c r="E246" s="4" t="n">
-        <v>35.05</v>
+        <v>26.87</v>
       </c>
       <c r="F246" s="4" t="n">
-        <v>38.14</v>
+        <v>32.45</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>RELAXO</t>
+          <t>ROUTE</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -8016,16 +7536,16 @@
         </is>
       </c>
       <c r="C247" s="4" t="n">
-        <v>285.35</v>
+        <v>416.7</v>
       </c>
       <c r="D247" s="4" t="n">
-        <v>24.28</v>
+        <v>23.18</v>
       </c>
       <c r="E247" s="4" t="n">
-        <v>36.58</v>
+        <v>27.87</v>
       </c>
       <c r="F247" s="4" t="n">
-        <v>32.56</v>
+        <v>27.42</v>
       </c>
     </row>
     <row r="248">
@@ -8040,22 +7560,22 @@
         </is>
       </c>
       <c r="C248" s="4" t="n">
-        <v>401.75</v>
+        <v>386.25</v>
       </c>
       <c r="D248" s="4" t="n">
-        <v>23.56</v>
+        <v>22.79</v>
       </c>
       <c r="E248" s="4" t="n">
-        <v>32.54</v>
+        <v>28.83</v>
       </c>
       <c r="F248" s="4" t="n">
-        <v>39.28</v>
+        <v>38.03</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>SANOFICONR</t>
+          <t>JSLL</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
@@ -8064,22 +7584,22 @@
         </is>
       </c>
       <c r="C249" s="4" t="n">
-        <v>3787.2</v>
+        <v>385.15</v>
       </c>
       <c r="D249" s="4" t="n">
-        <v>23.5</v>
+        <v>21.46</v>
       </c>
       <c r="E249" s="4" t="n">
-        <v>29.62</v>
+        <v>28.07</v>
       </c>
       <c r="F249" s="4" t="n">
-        <v>35.79</v>
+        <v>37.81</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>RTNPOWER</t>
+          <t>VIKRAMSOLR</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -8088,22 +7608,22 @@
         </is>
       </c>
       <c r="C250" s="4" t="n">
-        <v>6.74</v>
+        <v>142.32</v>
       </c>
       <c r="D250" s="4" t="n">
-        <v>23.48</v>
+        <v>19.65</v>
       </c>
       <c r="E250" s="4" t="n">
-        <v>26.21</v>
+        <v>29.16</v>
       </c>
       <c r="F250" s="4" t="n">
-        <v>39.63</v>
+        <v/>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>CERA</t>
+          <t>SANOFICONR</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
@@ -8112,22 +7632,22 @@
         </is>
       </c>
       <c r="C251" s="4" t="n">
-        <v>5096.5</v>
+        <v>3581.7</v>
       </c>
       <c r="D251" s="4" t="n">
-        <v>22.18</v>
+        <v>15.77</v>
       </c>
       <c r="E251" s="4" t="n">
-        <v>36.86</v>
+        <v>26.02</v>
       </c>
       <c r="F251" s="4" t="n">
-        <v>43.22</v>
+        <v>33.31</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>EUREKAFORB</t>
+          <t>V2RETAIL</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
@@ -8136,16 +7656,16 @@
         </is>
       </c>
       <c r="C252" s="4" t="n">
-        <v>352.5</v>
+        <v>154.5</v>
       </c>
       <c r="D252" s="4" t="n">
-        <v>18.38</v>
+        <v>14.48</v>
       </c>
       <c r="E252" s="4" t="n">
-        <v>28.29</v>
+        <v>26.12</v>
       </c>
       <c r="F252" s="4" t="n">
-        <v>33.36</v>
+        <v>44.7</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Micro250_stocks.xlsx
+++ b/docs/Micro250_stocks.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -551,7 +551,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CUPID</t>
+          <t>SKYGOLD</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -560,37 +560,37 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>366.1</v>
+        <v>1001.45</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>78.68000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>87</v>
+        <v>83.73999999999999</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>95.03</v>
+        <v>86.94</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>25.84</v>
+        <v>32.35</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>205.63</v>
+        <v>644.01</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>182.17</v>
+        <v>594.74</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>22664031</v>
+        <v>1336285</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>49228</v>
+        <v>16426</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>SKYGOLD</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -599,37 +599,37 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>921</v>
+        <v>418.15</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>75.44</v>
+        <v>73.73</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>78.83</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>84.51000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>25.74</v>
+        <v>35.37</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>625.62</v>
+        <v>327.38</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>578.87</v>
+        <v>316.85</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>1099816</v>
+        <v>1608625</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>14264</v>
+        <v>17085</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>PCJEWELLER</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -638,37 +638,37 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1015.2</v>
+        <v>16.28</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>75.42</v>
+        <v>71.19</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>80.01000000000001</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>90.41</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>38.81</v>
+        <v>28.6</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>570.24</v>
+        <v>11.09</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>502.31</v>
+        <v>11.03</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>2020749</v>
+        <v>412549372</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>52187</v>
+        <v>15967</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>PCJEWELLER</t>
+          <t>CUPID</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -677,37 +677,37 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>14.81</v>
+        <v>353.7</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>67.81999999999999</v>
+        <v>70.05</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>67.75</v>
+        <v>81.79000000000001</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>62.1</v>
+        <v>94.81</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>28.51</v>
+        <v>22.88</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>10.83</v>
+        <v>215.27</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>10.82</v>
+        <v>190.6</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>379285700</v>
+        <v>22759042</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>14525</v>
+        <v>47561</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>BBOX</t>
+          <t>SOUTHBANK</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -716,37 +716,37 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>892.1</v>
+        <v>51.45</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>64.81</v>
+        <v>66.89</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>60.83</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>64.14</v>
+        <v>74.55</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>37.82</v>
+        <v>21.6</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>758.89</v>
+        <v>44.14</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>729.83</v>
+        <v>42.74</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>923781</v>
+        <v>16472005</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>15844</v>
+        <v>13477</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>MANORAMA</t>
+          <t>BBOX</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2043.4</v>
+        <v>880.2</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>64.56</v>
+        <v>57.47</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>68.81999999999999</v>
+        <v>61.92</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>72.31999999999999</v>
+        <v>64.61</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>25.13</v>
+        <v>41.69</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1662.94</v>
+        <v>767.01</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1603.73</v>
+        <v>737.0700000000001</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>232032</v>
+        <v>1054066</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>12898</v>
+        <v>16113</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>OPTIEMUS</t>
+          <t>LLOYDSENGG</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -794,37 +794,37 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>815.85</v>
+        <v>96.37</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>61.62</v>
+        <v>55.66</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>76.8</v>
+        <v>65.11</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>64.69</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>43.35</v>
+        <v>24.07</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>562.1</v>
+        <v>79.77</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>549.08</v>
+        <v>76.44</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1480378</v>
+        <v>12714894</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>7356</v>
+        <v>14933</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>PGIL</t>
+          <t>NEOGEN</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -833,31 +833,31 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1281.1</v>
+        <v>2484.8</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>59.2</v>
+        <v>54.8</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>66.70999999999999</v>
+        <v>68.89</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>77.13</v>
+        <v>67.47</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>34.86</v>
+        <v>27.24</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1016.27</v>
+        <v>2013.19</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>966.01</v>
+        <v>1925.98</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>220268</v>
+        <v>229498</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>11835</v>
+        <v>7465</v>
       </c>
     </row>
     <row r="10">
@@ -872,37 +872,37 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>167.9</v>
+        <v>168.09</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>58.19</v>
+        <v>53.38</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>64.58</v>
+        <v>61.94</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>56.32</v>
+        <v>55.74</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>26.15</v>
+        <v>31.11</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>156.5</v>
+        <v>157.31</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>156.29</v>
+        <v>156.9</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1592132</v>
+        <v>1454962</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>8120</v>
+        <v>8042</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AXISCADES</t>
+          <t>OPTIEMUS</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2082.3</v>
+        <v>760</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>57.91</v>
+        <v>53.22</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>61.22</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>65.54000000000001</v>
+        <v>63.76</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>34.16</v>
+        <v>36.8</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1715.68</v>
+        <v>573.47</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1659.54</v>
+        <v>558.34</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>281632</v>
+        <v>1546778</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>8857</v>
+        <v>7111</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>PGIL</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -950,37 +950,37 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1748.1</v>
+        <v>1263.3</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>57.86</v>
+        <v>52.66</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>68.45</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>81.29000000000001</v>
+        <v>77.37</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>30.12</v>
+        <v>30.09</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1395.12</v>
+        <v>1030.81</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1316.55</v>
+        <v>979.01</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>320065</v>
+        <v>223134</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>23202</v>
+        <v>11910</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>AXISCADES</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -989,37 +989,37 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>793.75</v>
+        <v>2020.5</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>56.18</v>
+        <v>52.35</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>68.29000000000001</v>
+        <v>62.09</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>79.81999999999999</v>
+        <v>66.45</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>31.56</v>
+        <v>28.39</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>619.3200000000001</v>
+        <v>1733.44</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>577.04</v>
+        <v>1675.13</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2852428</v>
+        <v>275087</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>24900</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>SHILPAMED</t>
+          <t>MANORAMA</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1028,37 +1028,37 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1021.7</v>
+        <v>1927.4</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>55.64</v>
+        <v>48.59</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>83.22</v>
+        <v>60.07</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>83.28</v>
+        <v>69.97</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>38.12</v>
+        <v>22.45</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>690.71</v>
+        <v>1679.28</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>634.27</v>
+        <v>1618.63</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1060661</v>
+        <v>216529</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>19983</v>
+        <v>12064</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>WELENT</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1067,37 +1067,37 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>377.65</v>
+        <v>727.7</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>55.25</v>
+        <v>48.29</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>71.34</v>
+        <v>61.27</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>66.5</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>26.19</v>
+        <v>27.43</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>321.9</v>
+        <v>621.25</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>312.34</v>
+        <v>599.51</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1850914</v>
+        <v>653406</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>14528</v>
+        <v>9860</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>AZAD</t>
+          <t>GMMPFAUDLR</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1106,37 +1106,37 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2910.2</v>
+        <v>1312.1</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>54.97</v>
+        <v>47.56</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>68.03</v>
+        <v>64.2</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>72.41</v>
+        <v>55.12</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>24.3</v>
+        <v>38.44</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2346.87</v>
+        <v>1069.58</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2230.1</v>
+        <v>1055.06</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>813845</v>
+        <v>457775</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>18795</v>
+        <v>5899</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>QPOWER</t>
+          <t>ICIL</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1145,37 +1145,37 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1547.4</v>
+        <v>437.5</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>53.97</v>
+        <v>47.53</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>66.29000000000001</v>
+        <v>62.7</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>69.54000000000001</v>
+        <v>62.37</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>21.35</v>
+        <v>27.01</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1221.72</v>
+        <v>383.2</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1150.4</v>
+        <v>366.88</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>352319</v>
+        <v>504119</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>11984</v>
+        <v>8734</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>NEOGEN</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1184,382 +1184,31 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2378.2</v>
+        <v>865.9</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>53.22</v>
+        <v>46.89</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>65.83</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>64.88</v>
+        <v>84.3</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>24.94</v>
+        <v>33.53</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1975.68</v>
+        <v>593.33</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1893.35</v>
+        <v>523.1</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>184807</v>
+        <v>1990823</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>7145</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>LLOYDSENGG</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>94.42</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>63.71</v>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>64.79000000000001</v>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>32.34</v>
-      </c>
-      <c r="H19" s="4" t="n">
-        <v>78.83</v>
-      </c>
-      <c r="I19" s="4" t="n">
-        <v>75.56</v>
-      </c>
-      <c r="J19" s="4" t="n">
-        <v>11398857</v>
-      </c>
-      <c r="K19" s="4" t="n">
-        <v>14631</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>GNFC</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>592.7</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>50.98</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>63.39</v>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>58.59</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>25.62</v>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>523.42</v>
-      </c>
-      <c r="I20" s="4" t="n">
-        <v>514.04</v>
-      </c>
-      <c r="J20" s="4" t="n">
-        <v>1085018</v>
-      </c>
-      <c r="K20" s="4" t="n">
-        <v>8709</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>WELENT</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>735.9</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>50.69</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>62.62</v>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>68.52</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>29.35</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>614.98</v>
-      </c>
-      <c r="I21" s="4" t="n">
-        <v>593.95</v>
-      </c>
-      <c r="J21" s="4" t="n">
-        <v>719326</v>
-      </c>
-      <c r="K21" s="4" t="n">
-        <v>9980</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>EMIL</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>191.17</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>50.05</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>66.76000000000001</v>
-      </c>
-      <c r="F22" s="4" t="n">
-        <v>60.62</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>34.72</v>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>149.99</v>
-      </c>
-      <c r="I22" s="4" t="n">
-        <v>144.47</v>
-      </c>
-      <c r="J22" s="4" t="n">
-        <v>4121337</v>
-      </c>
-      <c r="K22" s="4" t="n">
-        <v>7355</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>YATHARTH</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>1022.2</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>61.7</v>
-      </c>
-      <c r="F23" s="4" t="n">
-        <v>68.44</v>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>34.56</v>
-      </c>
-      <c r="H23" s="4" t="n">
-        <v>872.8200000000001</v>
-      </c>
-      <c r="I23" s="4" t="n">
-        <v>838.74</v>
-      </c>
-      <c r="J23" s="4" t="n">
-        <v>740612</v>
-      </c>
-      <c r="K23" s="4" t="n">
-        <v>9849</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>SANSERA</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>4124.7</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>47.53</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>66.62</v>
-      </c>
-      <c r="F24" s="4" t="n">
-        <v>77.14</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>25.13</v>
-      </c>
-      <c r="H24" s="4" t="n">
-        <v>3264.46</v>
-      </c>
-      <c r="I24" s="4" t="n">
-        <v>3019.41</v>
-      </c>
-      <c r="J24" s="4" t="n">
-        <v>288915</v>
-      </c>
-      <c r="K24" s="4" t="n">
-        <v>25745</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>ICIL</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>436.3</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>47.41</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>61.85</v>
-      </c>
-      <c r="F25" s="4" t="n">
-        <v>61.78</v>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>30.54</v>
-      </c>
-      <c r="H25" s="4" t="n">
-        <v>379.46</v>
-      </c>
-      <c r="I25" s="4" t="n">
-        <v>363.36</v>
-      </c>
-      <c r="J25" s="4" t="n">
-        <v>643788</v>
-      </c>
-      <c r="K25" s="4" t="n">
-        <v>8641</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>GMMPFAUDLR</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>1299.8</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>46.39</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>63.66</v>
-      </c>
-      <c r="F26" s="4" t="n">
-        <v>54.76</v>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>52.68</v>
-      </c>
-      <c r="H26" s="4" t="n">
-        <v>1051.14</v>
-      </c>
-      <c r="I26" s="4" t="n">
-        <v>1040.18</v>
-      </c>
-      <c r="J26" s="4" t="n">
-        <v>463958</v>
-      </c>
-      <c r="K26" s="4" t="n">
-        <v>5844</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>ENTERO</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>1676.2</v>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>45.34</v>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>63.16</v>
-      </c>
-      <c r="F27" s="4" t="n">
-        <v>66.34</v>
-      </c>
-      <c r="G27" s="4" t="n">
-        <v>28.67</v>
-      </c>
-      <c r="H27" s="4" t="n">
-        <v>1405.05</v>
-      </c>
-      <c r="I27" s="4" t="n">
-        <v>1358.04</v>
-      </c>
-      <c r="J27" s="4" t="n">
-        <v>265690</v>
-      </c>
-      <c r="K27" s="4" t="n">
-        <v>7295</v>
+        <v>44512</v>
       </c>
     </row>
   </sheetData>
@@ -1581,15 +1230,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1647,7 +1287,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CUPID</t>
+          <t>SKYGOLD</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1656,22 +1296,22 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>366.1</v>
+        <v>1001.45</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>78.68000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>87</v>
+        <v>83.73999999999999</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>95.03</v>
+        <v>86.94</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>SKYGOLD</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -1680,22 +1320,22 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>921</v>
+        <v>418.15</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>75.44</v>
+        <v>73.73</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>78.83</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>84.51000000000001</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>PCJEWELLER</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -1704,22 +1344,22 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1015.2</v>
+        <v>16.28</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>75.42</v>
+        <v>71.19</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>80.01000000000001</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>90.41</v>
+        <v>64.84999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>PCJEWELLER</t>
+          <t>CUPID</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -1728,22 +1368,22 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>14.81</v>
+        <v>353.7</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>67.81999999999999</v>
+        <v>70.05</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>67.75</v>
+        <v>81.79000000000001</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>62.1</v>
+        <v>94.81</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>LOTUSDEV</t>
+          <t>JAIBALAJI</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -1752,22 +1392,22 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>239.75</v>
+        <v>74.91</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>67.28</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>74.52</v>
+        <v>54.11</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v/>
+        <v>44.53</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>BBOX</t>
+          <t>LOTUSDEV</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1776,22 +1416,22 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>892.1</v>
+        <v>246.25</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>64.81</v>
+        <v>67.14</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>60.83</v>
+        <v>75.8</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>64.14</v>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>MANORAMA</t>
+          <t>SOUTHBANK</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1800,22 +1440,22 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>2043.4</v>
+        <v>51.45</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>64.56</v>
+        <v>66.89</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>68.81999999999999</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>72.31999999999999</v>
+        <v>74.55</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>ALOKINDS</t>
+          <t>TANLA</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -1824,22 +1464,22 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>9</v>
+        <v>559.65</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>63.71</v>
+        <v>66.05</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>38.52</v>
+        <v>55.99</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>35.33</v>
+        <v>48.02</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>OPTIEMUS</t>
+          <t>JUSTDIAL</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1848,22 +1488,22 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>815.85</v>
+        <v>713.25</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>61.62</v>
+        <v>64.38</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>76.8</v>
+        <v>60.4</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>64.69</v>
+        <v>48.58</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AEQUS</t>
+          <t>JAYNECOIND</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -1872,22 +1512,22 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>273.5</v>
+        <v>100.62</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>60.72</v>
+        <v>63.29</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>68.84</v>
+        <v>60.02</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v/>
+        <v>62.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>DIACABS</t>
+          <t>MASTEK</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1896,22 +1536,22 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>380.95</v>
+        <v>1756.2</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>60.66</v>
+        <v>63.16</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>74.15000000000001</v>
+        <v>55.63</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>82.55</v>
+        <v>46.76</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>MTARTECH</t>
+          <t>FEDFINA</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1920,22 +1560,22 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>7781.5</v>
+        <v>161.86</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>60.14</v>
+        <v>63.05</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>63.91</v>
+        <v>58.2</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>72.62</v>
+        <v>60.01</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>DYNAMATECH</t>
+          <t>APOLLO</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1944,22 +1584,22 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>13321</v>
+        <v>429</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>60.08</v>
+        <v>60.98</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>66.23999999999999</v>
+        <v>60.81</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>71.06</v>
+        <v>70.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>VMART</t>
+          <t>CELLO</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1968,22 +1608,22 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>821.95</v>
+        <v>376.6</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>59.77</v>
+        <v>60.62</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>59.6</v>
+        <v>49.8</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>54.91</v>
+        <v>34.89</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>JAMNAAUTO</t>
+          <t>GAEL</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1992,22 +1632,22 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>142.67</v>
+        <v>173.7</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>59.26</v>
+        <v>58.98</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>58</v>
+        <v>59.71</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>61.08</v>
+        <v>63.71</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>PGIL</t>
+          <t>IIFLCAPS</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -2016,22 +1656,22 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1281.1</v>
+        <v>347.1</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>59.2</v>
+        <v>58.68</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>66.70999999999999</v>
+        <v>58.31</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>77.13</v>
+        <v>59.15</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>JAIBALAJI</t>
+          <t>DYNAMATECH</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -2040,22 +1680,22 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>68.40000000000001</v>
+        <v>13774</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>58.34</v>
+        <v>58.56</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>50.5</v>
+        <v>68.53</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>43.26</v>
+        <v>73.45</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>GPPL</t>
+          <t>RAIN</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2064,22 +1704,22 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>167.9</v>
+        <v>228.55</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>58.19</v>
+        <v>58.38</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>64.58</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>56.32</v>
+        <v>62.23</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>CELLO</t>
+          <t>BBOX</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -2088,22 +1728,22 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>364.95</v>
+        <v>880.2</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>57.96</v>
+        <v>57.47</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>46.77</v>
+        <v>61.92</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>33.38</v>
+        <v>64.61</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>AXISCADES</t>
+          <t>HAPPSTMNDS</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -2112,22 +1752,22 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2082.3</v>
+        <v>335.9</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>57.91</v>
+        <v>56.95</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>61.22</v>
+        <v>43.2</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>65.54000000000001</v>
+        <v>32.17</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -2136,22 +1776,22 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1748.1</v>
+        <v>335.95</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>57.86</v>
+        <v>56.41</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>68.45</v>
+        <v>67.27</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>81.29000000000001</v>
+        <v>76.40000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>CAPILLARY</t>
+          <t>DIACABS</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -2160,22 +1800,22 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>566.65</v>
+        <v>373.75</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>57.83</v>
+        <v>56.22</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>55.43</v>
+        <v>68.08</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v/>
+        <v>81.48999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>MASTEK</t>
+          <t>TIPSMUSIC</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -2184,22 +1824,22 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1679.9</v>
+        <v>684.4</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>56.62</v>
+        <v>55.7</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>48.85</v>
+        <v>64.66</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>43.39</v>
+        <v>64.39</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>JAMNAAUTO</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -2208,22 +1848,22 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>793.75</v>
+        <v>142.54</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>56.18</v>
+        <v>55.66</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>68.29000000000001</v>
+        <v>56.92</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>79.81999999999999</v>
+        <v>60.53</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>SHILPAMED</t>
+          <t>LLOYDSENGG</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -2232,22 +1872,22 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1021.7</v>
+        <v>96.37</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>55.64</v>
+        <v>55.66</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>83.22</v>
+        <v>65.11</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>83.28</v>
+        <v>66.06999999999999</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>RALLIS</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -2256,22 +1896,22 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>377.65</v>
+        <v>204.93</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>55.25</v>
+        <v>55.6</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>71.34</v>
+        <v>36.68</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>66.5</v>
+        <v>41.79</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>AZAD</t>
+          <t>GRWRHITECH</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -2280,22 +1920,22 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2910.2</v>
+        <v>7094.5</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>54.97</v>
+        <v>54.96</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>68.03</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>72.41</v>
+        <v>68.45999999999999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>MIDHANI</t>
+          <t>NEOGEN</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -2304,22 +1944,22 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>440.5</v>
+        <v>2484.8</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>54.45</v>
+        <v>54.8</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>58.26</v>
+        <v>68.89</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>57.7</v>
+        <v>67.47</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GRWRHITECH</t>
+          <t>VAIBHAVGBL</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -2328,22 +1968,22 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>6997.5</v>
+        <v>210.88</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>53.98</v>
+        <v>54.39</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>66.15000000000001</v>
+        <v>44.35</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>68.72</v>
+        <v>44.55</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>QPOWER</t>
+          <t>DATAMATICS</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -2352,22 +1992,22 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1547.4</v>
+        <v>793</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>53.97</v>
+        <v>54.35</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>66.29000000000001</v>
+        <v>50.21</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>69.54000000000001</v>
+        <v>54.31</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>SOUTHBANK</t>
+          <t>FINPIPE</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -2376,22 +2016,22 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>47.91</v>
+        <v>154.75</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>53.92</v>
+        <v>53.98</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>59.58</v>
+        <v>40.09</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>71.13</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>HERITGFOOD</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -2400,22 +2040,22 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>328.2</v>
+        <v>405.4</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>53.54</v>
+        <v>53.95</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>66.84</v>
+        <v>60.87</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>75.98999999999999</v>
+        <v>53.21</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>NEOGEN</t>
+          <t>GPPL</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -2424,22 +2064,22 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2378.2</v>
+        <v>168.09</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>53.22</v>
+        <v>53.38</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>65.83</v>
+        <v>61.94</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>64.88</v>
+        <v>55.74</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>WESTLIFE</t>
+          <t>OPTIEMUS</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -2448,22 +2088,22 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>580.6</v>
+        <v>760</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>53.18</v>
+        <v>53.22</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>58.92</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>46.73</v>
+        <v>63.76</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>TRANSRAILL</t>
+          <t>GOKEX</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -2472,22 +2112,22 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>464.65</v>
+        <v>716.2</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>53.1</v>
+        <v>53.03</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>45.8</v>
+        <v>45.92</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>43.87</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENGG</t>
+          <t>ALOKINDS</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -2496,22 +2136,22 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>94.42</v>
+        <v>8.5</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>53.1</v>
+        <v>52.97</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>63.71</v>
+        <v>36.43</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>64.79000000000001</v>
+        <v>33.86</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>RAIN</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -2520,22 +2160,22 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>215.42</v>
+        <v>5098</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>52.61</v>
+        <v>52.93</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>60.99</v>
+        <v>52.21</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>60.35</v>
+        <v>66.28</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>ATLANTAELE</t>
+          <t>PGIL</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -2544,22 +2184,22 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>1769.5</v>
+        <v>1263.3</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>52.46</v>
+        <v>52.66</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>56.38</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v/>
+        <v>77.37</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>IIFLCAPS</t>
+          <t>PNGJL</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -2568,22 +2208,22 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>343.75</v>
+        <v>603.35</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>52.04</v>
+        <v>52.58</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>56.26</v>
+        <v>50.57</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>58.6</v>
+        <v>49.41</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GRINDWELL</t>
+          <t>AEQUS</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -2592,22 +2232,22 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>1990.6</v>
+        <v>262.2</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>51.86</v>
+        <v>52.45</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>54.66</v>
+        <v>63.51</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>54.91</v>
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>LXCHEM</t>
+          <t>TRANSRAILL</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -2616,22 +2256,22 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>180.34</v>
+        <v>465.85</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>51.26</v>
+        <v>52.37</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>61.25</v>
+        <v>46.07</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>47.84</v>
+        <v>43.96</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>PNGJL</t>
+          <t>AXISCADES</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -2640,22 +2280,22 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>599.95</v>
+        <v>2020.5</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>51.04</v>
+        <v>52.35</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>49.94</v>
+        <v>62.09</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>49.08</v>
+        <v>66.45</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>STYRENIX</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -2664,22 +2304,22 @@
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>592.7</v>
+        <v>2072.1</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>50.98</v>
+        <v>52.27</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>63.39</v>
+        <v>45.69</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>58.59</v>
+        <v>48.84</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>EDELWEISS</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -2688,22 +2328,22 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>2300.5</v>
+        <v>134.47</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>50.94</v>
+        <v>52.21</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>70.18000000000001</v>
+        <v>59.66</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>80.02</v>
+        <v>61.87</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GAEL</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -2712,22 +2352,22 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>163.43</v>
+        <v>210.79</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>50.87</v>
+        <v>52.09</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>54.01</v>
+        <v>58.44</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>60.32</v>
+        <v>62.96</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>WELENT</t>
+          <t>NETWORK18</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -2736,22 +2376,22 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>735.9</v>
+        <v>26.68</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>50.69</v>
+        <v>51.96</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>62.62</v>
+        <v>37.04</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>68.52</v>
+        <v>33.75</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>PRUDENT</t>
+          <t>ELECTCAST</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -2760,22 +2400,22 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>3254.7</v>
+        <v>76.7</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>50.48</v>
+        <v>51.82</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>57.04</v>
+        <v>50.69</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>60.16</v>
+        <v>44.51</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>EMIL</t>
+          <t>GMRP&amp;UI</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -2784,22 +2424,22 @@
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>191.17</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>50.05</v>
+        <v>51.81</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>66.76000000000001</v>
+        <v>50.65</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>60.62</v>
+        <v>51.04</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>ELLEN</t>
+          <t>JKPAPER</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -2808,22 +2448,22 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>348.15</v>
+        <v>396.1</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>49.87</v>
+        <v>51.47</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>57.88</v>
+        <v>54.59</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>40.73</v>
+        <v>54.82</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GMRP&amp;UI</t>
+          <t>CAPILLARY</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -2832,22 +2472,22 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>98.09999999999999</v>
+        <v>545.4</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>49.87</v>
+        <v>51.4</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>46.66</v>
+        <v>52.17</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>49.85</v>
+        <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>BLUESTONE</t>
+          <t>KANSAINER</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -2856,22 +2496,22 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>817.65</v>
+        <v>185.23</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>49.86</v>
+        <v>51.37</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>63.28</v>
+        <v>42</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v/>
+        <v>38.5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>WEWORK</t>
+          <t>SENCO</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -2880,22 +2520,22 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>669.45</v>
+        <v>337.25</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>49.75</v>
+        <v>51.24</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>53.53</v>
+        <v>48.56</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v/>
+        <v>48.91</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>ASTRAMICRO</t>
+          <t>KSCL</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -2904,22 +2544,22 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>1652.9</v>
+        <v>730.2</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>49.47</v>
+        <v>51.14</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>59.01</v>
+        <v>42.95</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>68.95999999999999</v>
+        <v>41.45</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>KPIGREEN</t>
+          <t>VMART</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -2928,22 +2568,22 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>325.3</v>
+        <v>802.25</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>49.15</v>
+        <v>50.84</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>41.14</v>
+        <v>54.95</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>44.13</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>YATHARTH</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -2952,22 +2592,22 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>1022.2</v>
+        <v>548.85</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>49</v>
+        <v>50.55</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>61.7</v>
+        <v>59.86</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>68.44</v>
+        <v>65.16</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>JAYNECOIND</t>
+          <t>JYOTHYLAB</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -2976,22 +2616,22 @@
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>91.40000000000001</v>
+        <v>191.61</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>48.95</v>
+        <v>50.46</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>51.89</v>
+        <v>38.29</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>59.55</v>
+        <v>36.83</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>ORKLAINDIA</t>
+          <t>BANCOINDIA</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -3000,22 +2640,22 @@
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>559.2</v>
+        <v>602.15</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>48.72</v>
+        <v>50.28</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>42.66</v>
+        <v>47.33</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v/>
+        <v>55.65</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>SENCO</t>
+          <t>MANYAVAR</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -3024,22 +2664,22 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>334.75</v>
+        <v>519.85</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>48.69</v>
+        <v>49.94</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>47.85</v>
+        <v>56.25</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>48.66</v>
+        <v>39.21</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>ELECTCAST</t>
+          <t>LXCHEM</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -3048,22 +2688,22 @@
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>75.18000000000001</v>
+        <v>179.02</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>48.63</v>
+        <v>49.79</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>48.81</v>
+        <v>59.86</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>43.87</v>
+        <v>47.51</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>POWERMECH</t>
+          <t>TRIVENI</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -3072,22 +2712,22 @@
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>2419</v>
+        <v>250.35</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>48.33</v>
+        <v>49.73</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>47.85</v>
+        <v>39.64</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>49.87</v>
+        <v>41.94</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>RATEGAIN</t>
+          <t>KRBL</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -3096,22 +2736,22 @@
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>853.65</v>
+        <v>393.8</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>48.17</v>
+        <v>49.59</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>54.65</v>
+        <v>54.78</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>60.54</v>
+        <v>55.34</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>INOXINDIA</t>
+          <t>EPL</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -3120,22 +2760,22 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>2056.9</v>
+        <v>236.35</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>48.1</v>
+        <v>48.84</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>61.84</v>
+        <v>50.05</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>77.61</v>
+        <v>53.68</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>TMB</t>
+          <t>BLACKBUCK</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -3144,22 +2784,22 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>874.8</v>
+        <v>594.45</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>47.97</v>
+        <v>48.83</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>63.44</v>
+        <v>51.45</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>71.79000000000001</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>HERITGFOOD</t>
+          <t>POWERMECH</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -3168,22 +2808,22 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>390.15</v>
+        <v>2422.3</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>47.79</v>
+        <v>48.77</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>56.7</v>
+        <v>46.55</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>51.38</v>
+        <v>49.33</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>SANSERA</t>
+          <t>WESTLIFE</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -3192,22 +2832,22 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>4124.7</v>
+        <v>573.6</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>47.53</v>
+        <v>48.68</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>66.62</v>
+        <v>58.59</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>77.14</v>
+        <v>46.59</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>ICIL</t>
+          <t>LUMAXTECH</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -3216,22 +2856,22 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>436.3</v>
+        <v>1912.8</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>47.41</v>
+        <v>48.63</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>61.85</v>
+        <v>58.4</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>61.78</v>
+        <v>68.29000000000001</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>KRBL</t>
+          <t>MANORAMA</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -3240,22 +2880,22 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>389.2</v>
+        <v>1927.4</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>47.36</v>
+        <v>48.59</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>53.5</v>
+        <v>60.07</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>54.84</v>
+        <v>69.97</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>BLACKBUCK</t>
+          <t>CRAMC</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -3264,22 +2904,22 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>592.05</v>
+        <v>226.74</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>47.02</v>
+        <v>48.56</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>51.08</v>
+        <v>39.98</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>56.73</v>
+        <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GREAVESCOT</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -3288,22 +2928,22 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>207.22</v>
+        <v>149.93</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>46.99</v>
+        <v>48.56</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>52.16</v>
+        <v>48.65</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>52.82</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>SMLMAH</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -3312,22 +2952,22 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>541</v>
+        <v>6031.5</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>46.77</v>
+        <v>48.51</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>58.21</v>
+        <v>60.48</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>64.39</v>
+        <v>67.14</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENT</t>
+          <t>VARROC</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -3336,22 +2976,22 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>73.73</v>
+        <v>820.4</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>46.64</v>
+        <v>48.49</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>51.91</v>
+        <v>64.55</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>56.27</v>
+        <v>66.17</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GMMPFAUDLR</t>
+          <t>NESCO</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -3360,22 +3000,22 @@
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>1299.8</v>
+        <v>1048.2</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>46.39</v>
+        <v>48.31</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>63.66</v>
+        <v>44.6</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>54.76</v>
+        <v>49.78</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>APOLLO</t>
+          <t>WELENT</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -3384,22 +3024,22 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>388.35</v>
+        <v>727.7</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>45.99</v>
+        <v>48.29</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>54.46</v>
+        <v>61.27</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>66.04000000000001</v>
+        <v>67.54000000000001</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GODREJAGRO</t>
+          <t>ALKYLAMINE</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -3408,22 +3048,22 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>628.45</v>
+        <v>1838.5</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>45.84</v>
+        <v>48.02</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>56.49</v>
+        <v>52.86</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>51.61</v>
+        <v>50.29</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>UTLSOLAR</t>
+          <t>TARC</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -3432,22 +3072,22 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>409.05</v>
+        <v>123.69</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>45.75</v>
+        <v>47.96</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>60.01</v>
+        <v>46.18</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v/>
+        <v>45.71</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>PURVA</t>
+          <t>TARC</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -3456,22 +3096,22 @@
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>207.26</v>
+        <v>123.69</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>45.65</v>
+        <v>47.96</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>44.98</v>
+        <v>46.18</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>44.04</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>RBA</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -3480,22 +3120,22 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>203.79</v>
+        <v>92.31999999999999</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>45.48</v>
+        <v>47.84</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>55.47</v>
+        <v>60.91</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>61.78</v>
+        <v>55.71</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>ENTERO</t>
+          <t>SHAREINDIA</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -3504,22 +3144,22 @@
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>1676.2</v>
+        <v>193.42</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>45.34</v>
+        <v>47.7</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>63.16</v>
+        <v>56.71</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>66.34</v>
+        <v>51.57</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>AWFIS</t>
+          <t>KPIGREEN</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -3528,22 +3168,22 @@
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>247.03</v>
+        <v>321.85</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>45.25</v>
+        <v>47.66</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>37.18</v>
+        <v>40.13</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>29.19</v>
+        <v>43.77</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>TANLA</t>
+          <t>GMMPFAUDLR</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -3552,22 +3192,22 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>498.35</v>
+        <v>1312.1</v>
       </c>
       <c r="D81" s="4" t="n">
-        <v>45.17</v>
+        <v>47.56</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>44.08</v>
+        <v>64.2</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>43.66</v>
+        <v>55.12</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>ICIL</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -3576,22 +3216,22 @@
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>855.5</v>
+        <v>437.5</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>45.05</v>
+        <v>47.53</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>56.99</v>
+        <v>62.7</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>57.41</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>ALKYLAMINE</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -3600,22 +3240,22 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>1807.6</v>
+        <v>471.75</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>44.99</v>
+        <v>47.03</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>50.61</v>
+        <v>41.55</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>49.41</v>
+        <v>39.17</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>SKIPPER</t>
+          <t>TIMETECHNO</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -3624,22 +3264,22 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>530.25</v>
+        <v>179.5</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>44.92</v>
+        <v>47.03</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>52.44</v>
+        <v>46.31</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>59.53</v>
+        <v>50.65</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>KANSAINER</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -3648,22 +3288,22 @@
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>181.29</v>
+        <v>865.9</v>
       </c>
       <c r="D85" s="4" t="n">
-        <v>44.85</v>
+        <v>46.89</v>
       </c>
       <c r="E85" s="4" t="n">
-        <v>38.98</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>37.17</v>
+        <v>84.3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>FINPIPE</t>
+          <t>TEXRAIL</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -3672,22 +3312,22 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>151.16</v>
+        <v>112.89</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>44.57</v>
+        <v>46.78</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>36.5</v>
+        <v>50.12</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>40.4</v>
+        <v>45.96</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>NESCO</t>
+          <t>PARAS</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -3696,22 +3336,22 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>1038.5</v>
+        <v>1298.9</v>
       </c>
       <c r="D87" s="4" t="n">
-        <v>44.56</v>
+        <v>46.78</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>42.87</v>
+        <v>57.95</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>49.06</v>
+        <v>64.12</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>TIPSMUSIC</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -3720,22 +3360,22 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>636.35</v>
+        <v>525.7</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>44.52</v>
+        <v>46.6</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>49.1</v>
+        <v>55.45</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>55.94</v>
+        <v>65.06</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>KSB</t>
+          <t>QUESS</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -3744,22 +3384,22 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>784.55</v>
+        <v>332.95</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>44.44</v>
+        <v>46.48</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>42.58</v>
+        <v>61.41</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>50.06</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>SHAILY</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -3768,22 +3408,22 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>3063.4</v>
+        <v>863.8</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>44.16</v>
+        <v>46.42</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>56.39</v>
+        <v>58.4</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>68.25</v>
+        <v>58.45</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>JYOTHYLAB</t>
+          <t>GOKULAGRO</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -3792,22 +3432,22 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>187.94</v>
+        <v>213.66</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>44.11</v>
+        <v>46.2</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>36.49</v>
+        <v>48.1</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>36.4</v>
+        <v>59.27</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>PARKHOSPS</t>
+          <t>VOLTAMP</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -3816,22 +3456,22 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>270.8</v>
+        <v>10394</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>44.09</v>
+        <v>46.16</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>54.13</v>
+        <v>56.72</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v/>
+        <v>57.4</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -3840,22 +3480,22 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>4889.5</v>
+        <v>101</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>43.91</v>
+        <v>46.13</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>49.14</v>
+        <v>45.2</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>64.09</v>
+        <v>40.82</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>TEXRAIL</t>
+          <t>CSBBANK</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -3864,22 +3504,22 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>110.99</v>
+        <v>311.05</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>43.79</v>
+        <v>46.09</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>48.32</v>
+        <v>41.33</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>45.45</v>
+        <v>43.42</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>ORKLAINDIA</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -3888,22 +3528,22 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>1386.1</v>
+        <v>550.35</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>43.67</v>
+        <v>45.9</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>56.46</v>
+        <v>42.06</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>62.31</v>
+        <v/>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>INDIASHLTR</t>
+          <t>ALIVUS</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -3912,22 +3552,22 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>643.45</v>
+        <v>1341.8</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>43.52</v>
+        <v>45.84</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>36.44</v>
+        <v>59.87</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>39.44</v>
+        <v>66.45</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>RBA</t>
+          <t>SHAILY</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -3936,22 +3576,22 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>91.09999999999999</v>
+        <v>3083.3</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>43.47</v>
+        <v>45.7</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>59.8</v>
+        <v>57.96</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>55.11</v>
+        <v>68.78</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>AARTIDRUGS</t>
+          <t>PICCADIL</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -3960,22 +3600,22 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>413.3</v>
+        <v>589.9</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>43.44</v>
+        <v>45.51</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>52.8</v>
+        <v>45.47</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>48.87</v>
+        <v>49.26</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>ARVINDFASN</t>
+          <t>INOXINDIA</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -3984,22 +3624,22 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>402.8</v>
+        <v>2025</v>
       </c>
       <c r="D99" s="4" t="n">
-        <v>43.39</v>
+        <v>45.42</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>39.02</v>
+        <v>57.16</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>44.05</v>
+        <v>73.62</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>BIRLACORPN</t>
+          <t>ATLANTAELE</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -4008,22 +3648,22 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>817.3</v>
+        <v>1695.2</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>43.35</v>
+        <v>45.38</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>36.7</v>
+        <v>52.97</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>36.71</v>
+        <v/>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>SMLMAH</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -4032,22 +3672,22 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>5811.5</v>
+        <v>2044.8</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>43.25</v>
+        <v>45.36</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>57.91</v>
+        <v>54.32</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>64.59</v>
+        <v/>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>EDELWEISS</t>
+          <t>MIDHANI</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -4056,22 +3696,22 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>127.89</v>
+        <v>419.65</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>43.18</v>
+        <v>45.32</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>54.69</v>
+        <v>52.75</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>58.72</v>
+        <v>55.27</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>BANCOINDIA</t>
+          <t>ASTRAMICRO</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -4080,22 +3720,22 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>590.8</v>
+        <v>1621.1</v>
       </c>
       <c r="D103" s="4" t="n">
-        <v>43.02</v>
+        <v>45.32</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>44.42</v>
+        <v>56.64</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>54.56</v>
+        <v>68.06999999999999</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>BALAMINES</t>
+          <t>SUPRIYA</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -4104,22 +3744,22 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>2040.8</v>
+        <v>872.6</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>43</v>
+        <v>45.23</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>52.56</v>
+        <v>53.68</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>56.22</v>
+        <v>58.19</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>JUSTDIAL</t>
+          <t>UJJIVANSFB</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -4128,22 +3768,22 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>648.05</v>
+        <v>63.25</v>
       </c>
       <c r="D105" s="4" t="n">
-        <v>42.94</v>
+        <v>45.23</v>
       </c>
       <c r="E105" s="4" t="n">
-        <v>50.77</v>
+        <v>50.67</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>44.44</v>
+        <v>58.43</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>EMBDL</t>
+          <t>RATNAMANI</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -4152,22 +3792,22 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>55.51</v>
+        <v>2565.1</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>42.94</v>
+        <v>45.22</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>43.35</v>
+        <v>48.97</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>40.3</v>
+        <v>48.69</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>EPL</t>
+          <t>WEWORK</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -4176,22 +3816,22 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>232.43</v>
+        <v>661.2</v>
       </c>
       <c r="D107" s="4" t="n">
-        <v>42.76</v>
+        <v>45.16</v>
       </c>
       <c r="E107" s="4" t="n">
-        <v>50.25</v>
+        <v>52.03</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>53.77</v>
+        <v/>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>PRIVISCL</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -4200,22 +3840,22 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>3424.1</v>
+        <v>186.73</v>
       </c>
       <c r="D108" s="4" t="n">
-        <v>42.61</v>
+        <v>45.13</v>
       </c>
       <c r="E108" s="4" t="n">
-        <v>51.29</v>
+        <v>44.24</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>64.37</v>
+        <v>40.83</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>STAR</t>
+          <t>ELLEN</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -4224,22 +3864,22 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>1085.3</v>
+        <v>335.5</v>
       </c>
       <c r="D109" s="4" t="n">
-        <v>42.56</v>
+        <v>45.11</v>
       </c>
       <c r="E109" s="4" t="n">
-        <v>52.84</v>
+        <v>55.4</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>58.59</v>
+        <v>39.61</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>YATHARTH</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -4248,22 +3888,22 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>148</v>
+        <v>991.5</v>
       </c>
       <c r="D110" s="4" t="n">
-        <v>42.46</v>
+        <v>45.01</v>
       </c>
       <c r="E110" s="4" t="n">
-        <v>47.19</v>
+        <v>58.49</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>52.79</v>
+        <v>66.25</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>AZAD</t>
         </is>
       </c>
       <c r="B111" s="6" t="inlineStr">
@@ -4272,22 +3912,22 @@
         </is>
       </c>
       <c r="C111" s="7" t="n">
-        <v>309.1</v>
+        <v>2741</v>
       </c>
       <c r="D111" s="7" t="n">
-        <v>42.46</v>
+        <v>44.92</v>
       </c>
       <c r="E111" s="7" t="n">
-        <v>61.07</v>
+        <v>60.44</v>
       </c>
       <c r="F111" s="7" t="n">
-        <v>64.23</v>
+        <v>67.68000000000001</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>AVL</t>
+          <t>EQUITASBNK</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -4296,22 +3936,22 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>581.05</v>
+        <v>68.28</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>42.45</v>
+        <v>44.91</v>
       </c>
       <c r="E112" s="4" t="n">
-        <v>49.69</v>
+        <v>49.16</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>57.64</v>
+        <v>51.56</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>VOLTAMP</t>
+          <t>KSB</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -4320,22 +3960,22 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>10302</v>
+        <v>779.6</v>
       </c>
       <c r="D113" s="4" t="n">
-        <v>42.25</v>
+        <v>44.87</v>
       </c>
       <c r="E113" s="4" t="n">
-        <v>53.48</v>
+        <v>41.84</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>56.06</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>ETHOSLTD</t>
+          <t>RENUKA</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -4344,46 +3984,46 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>2563.1</v>
+        <v>22.15</v>
       </c>
       <c r="D114" s="4" t="n">
-        <v>42.21</v>
+        <v>44.83</v>
       </c>
       <c r="E114" s="4" t="n">
-        <v>48.73</v>
+        <v>43.37</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>50.95</v>
+        <v>38.39</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="5" t="inlineStr">
-        <is>
-          <t>ALIVUS</t>
-        </is>
-      </c>
-      <c r="B115" s="6" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C115" s="7" t="n">
-        <v>1326.3</v>
-      </c>
-      <c r="D115" s="7" t="n">
-        <v>42.11</v>
-      </c>
-      <c r="E115" s="7" t="n">
-        <v>62.01</v>
-      </c>
-      <c r="F115" s="7" t="n">
-        <v>67.70999999999999</v>
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>SURYAROSNI</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="n">
+        <v>212.52</v>
+      </c>
+      <c r="D115" s="4" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="E115" s="4" t="n">
+        <v>41.73</v>
+      </c>
+      <c r="F115" s="4" t="n">
+        <v>44.5</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>DBL</t>
+          <t>EMIL</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -4392,22 +4032,22 @@
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>395.65</v>
+        <v>182.81</v>
       </c>
       <c r="D116" s="4" t="n">
-        <v>42.07</v>
+        <v>44.69</v>
       </c>
       <c r="E116" s="4" t="n">
-        <v>42.2</v>
+        <v>61.94</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>44.94</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>SUDARSCHEM</t>
+          <t>ETHOSLTD</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -4416,46 +4056,46 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>1166.8</v>
+        <v>2573.4</v>
       </c>
       <c r="D117" s="4" t="n">
-        <v>41.92</v>
+        <v>44.61</v>
       </c>
       <c r="E117" s="4" t="n">
-        <v>57.27</v>
+        <v>51.04</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>57.01</v>
+        <v>51.78</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>JSFB</t>
-        </is>
-      </c>
-      <c r="B118" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C118" s="4" t="n">
-        <v>489.35</v>
-      </c>
-      <c r="D118" s="4" t="n">
-        <v>41.49</v>
-      </c>
-      <c r="E118" s="4" t="n">
-        <v>48.84</v>
-      </c>
-      <c r="F118" s="4" t="n">
-        <v>52.18</v>
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>SANSERA</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C118" s="7" t="n">
+        <v>4054.5</v>
+      </c>
+      <c r="D118" s="7" t="n">
+        <v>44.57</v>
+      </c>
+      <c r="E118" s="7" t="n">
+        <v>66.48999999999999</v>
+      </c>
+      <c r="F118" s="7" t="n">
+        <v>77.05</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>TVSSCS</t>
+          <t>GREAVESCOT</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -4464,22 +4104,22 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>124.54</v>
+        <v>204.3</v>
       </c>
       <c r="D119" s="4" t="n">
-        <v>41.36</v>
+        <v>44.54</v>
       </c>
       <c r="E119" s="4" t="n">
-        <v>48.22</v>
+        <v>51.16</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>45.34</v>
+        <v>52.35</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>CCAVENUE</t>
+          <t>UTLSOLAR</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -4488,94 +4128,94 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>14.9</v>
+        <v>402.4</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>41.29</v>
+        <v>44.46</v>
       </c>
       <c r="E120" s="4" t="n">
-        <v>45.14</v>
+        <v>56.58</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>42.05</v>
+        <v/>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="5" t="inlineStr">
-        <is>
-          <t>AKUMS</t>
-        </is>
-      </c>
-      <c r="B121" s="6" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C121" s="7" t="n">
-        <v>751.85</v>
-      </c>
-      <c r="D121" s="7" t="n">
-        <v>41.28</v>
-      </c>
-      <c r="E121" s="7" t="n">
-        <v>62.33</v>
-      </c>
-      <c r="F121" s="7" t="n">
-        <v>60.71</v>
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>PNCINFRA</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="n">
+        <v>144.26</v>
+      </c>
+      <c r="D121" s="4" t="n">
+        <v>44.46</v>
+      </c>
+      <c r="E121" s="4" t="n">
+        <v>30.83</v>
+      </c>
+      <c r="F121" s="4" t="n">
+        <v>35.63</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>CORONA</t>
-        </is>
-      </c>
-      <c r="B122" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C122" s="4" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D122" s="4" t="n">
-        <v>41.27</v>
-      </c>
-      <c r="E122" s="4" t="n">
-        <v>55.94</v>
-      </c>
-      <c r="F122" s="4" t="n">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>MARKSANS</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C122" s="7" t="n">
+        <v>311</v>
+      </c>
+      <c r="D122" s="7" t="n">
+        <v>44.43</v>
+      </c>
+      <c r="E122" s="7" t="n">
+        <v>61.53</v>
+      </c>
+      <c r="F122" s="7" t="n">
+        <v>64.61</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>BLUESTONE</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="n">
+        <v>778.9</v>
+      </c>
+      <c r="D123" s="4" t="n">
+        <v>44.39</v>
+      </c>
+      <c r="E123" s="4" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="F123" s="4" t="n">
         <v/>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="5" t="inlineStr">
-        <is>
-          <t>VARROC</t>
-        </is>
-      </c>
-      <c r="B123" s="6" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C123" s="7" t="n">
-        <v>793.6</v>
-      </c>
-      <c r="D123" s="7" t="n">
-        <v>41.24</v>
-      </c>
-      <c r="E123" s="7" t="n">
-        <v>61.92</v>
-      </c>
-      <c r="F123" s="7" t="n">
-        <v>64</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>STYRENIX</t>
+          <t>TDPOWERSYS</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -4584,22 +4224,22 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>1999.2</v>
+        <v>735.15</v>
       </c>
       <c r="D124" s="4" t="n">
-        <v>41.22</v>
+        <v>44.25</v>
       </c>
       <c r="E124" s="4" t="n">
-        <v>41.77</v>
+        <v>59.48</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>47.39</v>
+        <v>73.66</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>GSFC</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -4608,46 +4248,46 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>147.28</v>
+        <v>572.15</v>
       </c>
       <c r="D125" s="4" t="n">
-        <v>41.21</v>
+        <v>44.22</v>
       </c>
       <c r="E125" s="4" t="n">
-        <v>39.42</v>
+        <v>56.55</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>42.22</v>
+        <v>55.45</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>WABAG</t>
-        </is>
-      </c>
-      <c r="B126" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C126" s="4" t="n">
-        <v>1936.8</v>
-      </c>
-      <c r="D126" s="4" t="n">
-        <v>41.19</v>
-      </c>
-      <c r="E126" s="4" t="n">
-        <v>53.46</v>
-      </c>
-      <c r="F126" s="4" t="n">
-        <v>63.76</v>
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>SHRIPISTON</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C126" s="7" t="n">
+        <v>4333</v>
+      </c>
+      <c r="D126" s="7" t="n">
+        <v>43.71</v>
+      </c>
+      <c r="E126" s="7" t="n">
+        <v>63.17</v>
+      </c>
+      <c r="F126" s="7" t="n">
+        <v>79.14</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>RATNAMANI</t>
+          <t>ARVINDFASN</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -4656,22 +4296,22 @@
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>2523.6</v>
+        <v>398.9</v>
       </c>
       <c r="D127" s="4" t="n">
-        <v>41.05</v>
+        <v>43.58</v>
       </c>
       <c r="E127" s="4" t="n">
-        <v>48.96</v>
+        <v>38.4</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>48.68</v>
+        <v>43.64</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>MSTCLTD</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -4680,22 +4320,22 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>672</v>
+        <v>188.64</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>40.98</v>
+        <v>43.52</v>
       </c>
       <c r="E128" s="4" t="n">
-        <v>56.98</v>
+        <v>48.31</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>57</v>
+        <v>51.41</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>PARAS</t>
+          <t>SKFINDIA</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -4704,22 +4344,22 @@
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>1267.9</v>
+        <v>1451.1</v>
       </c>
       <c r="D129" s="4" t="n">
-        <v>40.92</v>
+        <v>43.49</v>
       </c>
       <c r="E129" s="4" t="n">
-        <v>56.26</v>
+        <v>36.49</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>62.77</v>
+        <v>31.81</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>MOIL</t>
+          <t>AURIONPRO</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -4728,22 +4368,22 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>234.96</v>
+        <v>627.25</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>40.92</v>
+        <v>43.42</v>
       </c>
       <c r="E130" s="4" t="n">
-        <v>31.2</v>
+        <v>34.37</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>39.33</v>
+        <v>37.03</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>BALAMINES</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -4752,46 +4392,46 @@
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>588.15</v>
+        <v>2043.4</v>
       </c>
       <c r="D131" s="4" t="n">
-        <v>40.88</v>
+        <v>43.37</v>
       </c>
       <c r="E131" s="4" t="n">
-        <v>57.68</v>
+        <v>53.42</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>61.77</v>
+        <v>56.83</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>BALUFORGE</t>
-        </is>
-      </c>
-      <c r="B132" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C132" s="4" t="n">
-        <v>481.2</v>
-      </c>
-      <c r="D132" s="4" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="E132" s="4" t="n">
-        <v>46.88</v>
-      </c>
-      <c r="F132" s="4" t="n">
-        <v>48.09</v>
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>SHILPAMED</t>
+        </is>
+      </c>
+      <c r="B132" s="6" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C132" s="7" t="n">
+        <v>937.6</v>
+      </c>
+      <c r="D132" s="7" t="n">
+        <v>43.24</v>
+      </c>
+      <c r="E132" s="7" t="n">
+        <v>69.77</v>
+      </c>
+      <c r="F132" s="7" t="n">
+        <v>75.63</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>RENUKA</t>
+          <t>QPOWER</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -4800,22 +4440,22 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>21.72</v>
+        <v>1433.8</v>
       </c>
       <c r="D133" s="4" t="n">
-        <v>40.7</v>
+        <v>42.95</v>
       </c>
       <c r="E133" s="4" t="n">
-        <v>41.24</v>
+        <v>59.85</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>37.72</v>
+        <v>66.11</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>LUMAXTECH</t>
+          <t>SFL</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -4824,22 +4464,22 @@
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>1827.4</v>
+        <v>616.85</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>40.38</v>
+        <v>42.85</v>
       </c>
       <c r="E134" s="4" t="n">
-        <v>52.96</v>
+        <v>45.05</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>63.71</v>
+        <v>44.01</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>APLLTD</t>
+          <t>MAHSCOOTER</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -4848,22 +4488,22 @@
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>800.95</v>
+        <v>12408</v>
       </c>
       <c r="D135" s="4" t="n">
-        <v>40.29</v>
+        <v>42.82</v>
       </c>
       <c r="E135" s="4" t="n">
-        <v>50.07</v>
+        <v>46.06</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>47.98</v>
+        <v>52.87</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>SHRIPISTON</t>
+          <t>AWFIS</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -4872,22 +4512,22 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>4284.5</v>
+        <v>241.63</v>
       </c>
       <c r="D136" s="4" t="n">
-        <v>40.27</v>
+        <v>42.8</v>
       </c>
       <c r="E136" s="4" t="n">
-        <v>56.2</v>
+        <v>36.76</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>70.72</v>
+        <v>28.85</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>DATAMATICS</t>
+          <t>GODREJAGRO</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -4896,22 +4536,22 @@
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>745.8</v>
+        <v>620.2</v>
       </c>
       <c r="D137" s="4" t="n">
-        <v>40.18</v>
+        <v>42.74</v>
       </c>
       <c r="E137" s="4" t="n">
-        <v>44.5</v>
+        <v>57.37</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>51.67</v>
+        <v>52</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>SHARDACROP</t>
+          <t>EMBDL</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -4920,22 +4560,22 @@
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>723.9</v>
+        <v>55.16</v>
       </c>
       <c r="D138" s="4" t="n">
-        <v>40.1</v>
+        <v>42.7</v>
       </c>
       <c r="E138" s="4" t="n">
-        <v>35.94</v>
+        <v>42.95</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>47.97</v>
+        <v>40.19</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>SUPRIYA</t>
+          <t>PURVA</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -4944,22 +4584,22 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>847.65</v>
+        <v>203.9</v>
       </c>
       <c r="D139" s="4" t="n">
-        <v>39.98</v>
+        <v>42.66</v>
       </c>
       <c r="E139" s="4" t="n">
-        <v>50.65</v>
+        <v>42.98</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>56.25</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>TIMETECHNO</t>
+          <t>FIEMIND</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -4968,22 +4608,22 @@
         </is>
       </c>
       <c r="C140" s="4" t="n">
-        <v>176.35</v>
+        <v>1825.5</v>
       </c>
       <c r="D140" s="4" t="n">
-        <v>39.93</v>
+        <v>42.63</v>
       </c>
       <c r="E140" s="4" t="n">
-        <v>43.74</v>
+        <v>42.22</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>49.9</v>
+        <v>53.27</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>KNRCON</t>
+          <t>BECTORFOOD</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -4992,22 +4632,22 @@
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>112.92</v>
+        <v>209.1</v>
       </c>
       <c r="D141" s="4" t="n">
-        <v>39.48</v>
+        <v>42.63</v>
       </c>
       <c r="E141" s="4" t="n">
-        <v>37.83</v>
+        <v>49.38</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>32.54</v>
+        <v>46.58</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>SUBROS</t>
+          <t>TMB</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -5016,22 +4656,22 @@
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>676.75</v>
+        <v>854.9</v>
       </c>
       <c r="D142" s="4" t="n">
-        <v>39.46</v>
+        <v>42.47</v>
       </c>
       <c r="E142" s="4" t="n">
-        <v>38.36</v>
+        <v>59.88</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>47.31</v>
+        <v>70.08</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>PICCADIL</t>
+          <t>PRUDENT</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -5040,22 +4680,22 @@
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>580.7</v>
+        <v>3110.3</v>
       </c>
       <c r="D143" s="4" t="n">
-        <v>39.43</v>
+        <v>42.16</v>
       </c>
       <c r="E143" s="4" t="n">
-        <v>44.03</v>
+        <v>50.13</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>48.34</v>
+        <v>57.39</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>MANYAVAR</t>
+          <t>AGARWALEYE</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -5064,22 +4704,22 @@
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>500.75</v>
+        <v>477.15</v>
       </c>
       <c r="D144" s="4" t="n">
-        <v>39.43</v>
+        <v>42.16</v>
       </c>
       <c r="E144" s="4" t="n">
-        <v>52.79</v>
+        <v>44.74</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>38.19</v>
+        <v>50.79</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>UJJIVANSFB</t>
+          <t>BALUFORGE</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -5088,22 +4728,22 @@
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>61.45</v>
+        <v>480.7</v>
       </c>
       <c r="D145" s="4" t="n">
-        <v>39.42</v>
+        <v>42.13</v>
       </c>
       <c r="E145" s="4" t="n">
-        <v>47.58</v>
+        <v>46.81</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>56.83</v>
+        <v>48.07</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>CRIZAC</t>
+          <t>IFBIND</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -5112,22 +4752,22 @@
         </is>
       </c>
       <c r="C146" s="4" t="n">
-        <v>162.94</v>
+        <v>1191.1</v>
       </c>
       <c r="D146" s="4" t="n">
-        <v>39.41</v>
+        <v>42.06</v>
       </c>
       <c r="E146" s="4" t="n">
-        <v>37.72</v>
+        <v>44.21</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>20.37</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>SPARC</t>
+          <t>SKIPPER</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -5136,22 +4776,22 @@
         </is>
       </c>
       <c r="C147" s="4" t="n">
-        <v>185.6</v>
+        <v>520.4</v>
       </c>
       <c r="D147" s="4" t="n">
-        <v>39.33</v>
+        <v>41.93</v>
       </c>
       <c r="E147" s="4" t="n">
-        <v>47.19</v>
+        <v>51.61</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>50.81</v>
+        <v>59.03</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>IONEXCHANG</t>
+          <t>AVANTIFEED</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -5160,22 +4800,22 @@
         </is>
       </c>
       <c r="C148" s="4" t="n">
-        <v>390.75</v>
+        <v>729.15</v>
       </c>
       <c r="D148" s="4" t="n">
-        <v>39.27</v>
+        <v>41.87</v>
       </c>
       <c r="E148" s="4" t="n">
-        <v>48.29</v>
+        <v>32.68</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>46.67</v>
+        <v>46.54</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>AGARWALEYE</t>
+          <t>MTARTECH</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -5184,22 +4824,22 @@
         </is>
       </c>
       <c r="C149" s="4" t="n">
-        <v>477.75</v>
+        <v>7054.5</v>
       </c>
       <c r="D149" s="4" t="n">
-        <v>39.24</v>
+        <v>41.78</v>
       </c>
       <c r="E149" s="4" t="n">
-        <v>47.98</v>
+        <v>55.22</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>52.67</v>
+        <v>66.91</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>TRIVENI</t>
+          <t>AKUMS</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -5208,22 +4848,22 @@
         </is>
       </c>
       <c r="C150" s="4" t="n">
-        <v>235.67</v>
+        <v>749.8</v>
       </c>
       <c r="D150" s="4" t="n">
-        <v>39.14</v>
+        <v>41.77</v>
       </c>
       <c r="E150" s="4" t="n">
-        <v>36.47</v>
+        <v>58.59</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>40.47</v>
+        <v>58.82</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>SAATVIKGL</t>
+          <t>RELAXO</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -5232,22 +4872,22 @@
         </is>
       </c>
       <c r="C151" s="4" t="n">
-        <v>395.95</v>
+        <v>294.35</v>
       </c>
       <c r="D151" s="4" t="n">
-        <v>38.93</v>
+        <v>41.69</v>
       </c>
       <c r="E151" s="4" t="n">
-        <v>41.9</v>
+        <v>40.19</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v/>
+        <v>33.68</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>VIYASH</t>
+          <t>RATEGAIN</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -5256,22 +4896,22 @@
         </is>
       </c>
       <c r="C152" s="4" t="n">
-        <v>234.06</v>
+        <v>827.4</v>
       </c>
       <c r="D152" s="4" t="n">
-        <v>38.9</v>
+        <v>41.55</v>
       </c>
       <c r="E152" s="4" t="n">
-        <v>45.67</v>
+        <v>51.34</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>56.24</v>
+        <v>58.81</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>STYL</t>
+          <t>DBL</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -5280,22 +4920,22 @@
         </is>
       </c>
       <c r="C153" s="4" t="n">
-        <v>349.05</v>
+        <v>393.45</v>
       </c>
       <c r="D153" s="4" t="n">
-        <v>38.88</v>
+        <v>41.45</v>
       </c>
       <c r="E153" s="4" t="n">
-        <v>51.44</v>
+        <v>44.2</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v/>
+        <v>45.69</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>KIRLOSBROS</t>
+          <t>MOIL</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -5304,22 +4944,22 @@
         </is>
       </c>
       <c r="C154" s="4" t="n">
-        <v>1690.1</v>
+        <v>233.63</v>
       </c>
       <c r="D154" s="4" t="n">
-        <v>38.6</v>
+        <v>41.37</v>
       </c>
       <c r="E154" s="4" t="n">
-        <v>43.16</v>
+        <v>30.79</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>50.51</v>
+        <v>39.17</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>FEDFINA</t>
+          <t>SHARDACROP</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -5328,22 +4968,22 @@
         </is>
       </c>
       <c r="C155" s="4" t="n">
-        <v>146.39</v>
+        <v>724.05</v>
       </c>
       <c r="D155" s="4" t="n">
-        <v>38.31</v>
+        <v>41.32</v>
       </c>
       <c r="E155" s="4" t="n">
-        <v>44.95</v>
+        <v>36.17</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>54.09</v>
+        <v>48.03</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>RALLIS</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -5352,22 +4992,22 @@
         </is>
       </c>
       <c r="C156" s="4" t="n">
-        <v>198.06</v>
+        <v>588</v>
       </c>
       <c r="D156" s="4" t="n">
-        <v>38.27</v>
+        <v>41.26</v>
       </c>
       <c r="E156" s="4" t="n">
-        <v>29.6</v>
+        <v>57.65</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>40.49</v>
+        <v>61.75</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>TSFINV</t>
+          <t>KITEX</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -5376,22 +5016,22 @@
         </is>
       </c>
       <c r="C157" s="4" t="n">
-        <v>403.9</v>
+        <v>116.19</v>
       </c>
       <c r="D157" s="4" t="n">
-        <v>38.14</v>
+        <v>41.17</v>
       </c>
       <c r="E157" s="4" t="n">
-        <v>45.49</v>
+        <v>36.47</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>52.31</v>
+        <v>42.79</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>GSFC</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -5400,22 +5040,22 @@
         </is>
       </c>
       <c r="C158" s="4" t="n">
-        <v>455.05</v>
+        <v>146.6</v>
       </c>
       <c r="D158" s="4" t="n">
-        <v>38.12</v>
+        <v>41.12</v>
       </c>
       <c r="E158" s="4" t="n">
-        <v>34.86</v>
+        <v>41.47</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>37.21</v>
+        <v>42.69</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>SKFINDUS</t>
+          <t>WEBELSOLAR</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -5424,22 +5064,22 @@
         </is>
       </c>
       <c r="C159" s="4" t="n">
-        <v>2655.9</v>
+        <v>68.27</v>
       </c>
       <c r="D159" s="4" t="n">
-        <v>38.08</v>
+        <v>41.09</v>
       </c>
       <c r="E159" s="4" t="n">
-        <v>49.72</v>
+        <v>34.45</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v/>
+        <v>43.69</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>SHAREINDIA</t>
+          <t>SWSOLAR</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -5448,22 +5088,22 @@
         </is>
       </c>
       <c r="C160" s="4" t="n">
-        <v>182.71</v>
+        <v>165.47</v>
       </c>
       <c r="D160" s="4" t="n">
-        <v>38.07</v>
+        <v>41.01</v>
       </c>
       <c r="E160" s="4" t="n">
-        <v>53.65</v>
+        <v>35.11</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>49.72</v>
+        <v>38.04</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>WAAREERTL</t>
+          <t>ROUTE</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -5472,22 +5112,22 @@
         </is>
       </c>
       <c r="C161" s="4" t="n">
-        <v>802.45</v>
+        <v>437.95</v>
       </c>
       <c r="D161" s="4" t="n">
-        <v>37.87</v>
+        <v>40.86</v>
       </c>
       <c r="E161" s="4" t="n">
-        <v>33.71</v>
+        <v>37.24</v>
       </c>
       <c r="F161" s="4" t="n">
-        <v>38.05</v>
+        <v>28.69</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>VAIBHAVGBL</t>
+          <t>SUNTECK</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -5496,22 +5136,22 @@
         </is>
       </c>
       <c r="C162" s="4" t="n">
-        <v>201.67</v>
+        <v>274.1</v>
       </c>
       <c r="D162" s="4" t="n">
-        <v>37.69</v>
+        <v>40.8</v>
       </c>
       <c r="E162" s="4" t="n">
-        <v>39.13</v>
+        <v>37.19</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>43.06</v>
+        <v>38.56</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>KITEX</t>
+          <t>LLOYDSENT</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -5520,22 +5160,22 @@
         </is>
       </c>
       <c r="C163" s="4" t="n">
-        <v>115.01</v>
+        <v>70.42</v>
       </c>
       <c r="D163" s="4" t="n">
-        <v>37.45</v>
+        <v>40.67</v>
       </c>
       <c r="E163" s="4" t="n">
-        <v>29.81</v>
+        <v>48.42</v>
       </c>
       <c r="F163" s="4" t="n">
-        <v>41.42</v>
+        <v>54.27</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>SANDUMA</t>
+          <t>SAATVIKGL</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -5544,22 +5184,22 @@
         </is>
       </c>
       <c r="C164" s="4" t="n">
-        <v>177.68</v>
+        <v>395.7</v>
       </c>
       <c r="D164" s="4" t="n">
-        <v>37.42</v>
+        <v>40.23</v>
       </c>
       <c r="E164" s="4" t="n">
-        <v>37.85</v>
+        <v>42.15</v>
       </c>
       <c r="F164" s="4" t="n">
-        <v>49.51</v>
+        <v/>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>KIRLPNU</t>
+          <t>INDIGOPNTS</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -5568,22 +5208,22 @@
         </is>
       </c>
       <c r="C165" s="4" t="n">
-        <v>667.25</v>
+        <v>1035.8</v>
       </c>
       <c r="D165" s="4" t="n">
-        <v>37.35</v>
+        <v>40.21</v>
       </c>
       <c r="E165" s="4" t="n">
-        <v>42.27</v>
+        <v>48.54</v>
       </c>
       <c r="F165" s="4" t="n">
-        <v>52.19</v>
+        <v>46.58</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>IMFA</t>
+          <t>WAAREERTL</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -5592,22 +5232,22 @@
         </is>
       </c>
       <c r="C166" s="4" t="n">
-        <v>1182.5</v>
+        <v>806.4</v>
       </c>
       <c r="D166" s="4" t="n">
-        <v>37.27</v>
+        <v>40.2</v>
       </c>
       <c r="E166" s="4" t="n">
-        <v>38.94</v>
+        <v>40.42</v>
       </c>
       <c r="F166" s="4" t="n">
-        <v>54.52</v>
+        <v>40.35</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>KSCL</t>
+          <t>ZAGGLE</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -5616,22 +5256,22 @@
         </is>
       </c>
       <c r="C167" s="4" t="n">
-        <v>676.8</v>
+        <v>169.21</v>
       </c>
       <c r="D167" s="4" t="n">
-        <v>37.12</v>
+        <v>40.15</v>
       </c>
       <c r="E167" s="4" t="n">
-        <v>36.9</v>
+        <v>30.93</v>
       </c>
       <c r="F167" s="4" t="n">
-        <v>39.07</v>
+        <v>36.49</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>SUDEEPPHRM</t>
+          <t>ORIENTCEM</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -5640,22 +5280,22 @@
         </is>
       </c>
       <c r="C168" s="4" t="n">
-        <v>1050.3</v>
+        <v>114.87</v>
       </c>
       <c r="D168" s="4" t="n">
-        <v>37.12</v>
+        <v>40.11</v>
       </c>
       <c r="E168" s="4" t="n">
-        <v>56.17</v>
+        <v>28.88</v>
       </c>
       <c r="F168" s="4" t="n">
-        <v/>
+        <v>32.77</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>QUESS</t>
+          <t>AHLUCONT</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -5664,22 +5304,22 @@
         </is>
       </c>
       <c r="C169" s="4" t="n">
-        <v>321.35</v>
+        <v>563.25</v>
       </c>
       <c r="D169" s="4" t="n">
-        <v>37.1</v>
+        <v>40</v>
       </c>
       <c r="E169" s="4" t="n">
-        <v>58.64</v>
+        <v>24.9</v>
       </c>
       <c r="F169" s="4" t="n">
-        <v>48.47</v>
+        <v>38.74</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>INDIAGLYCO</t>
+          <t>PRIVISCL</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -5688,22 +5328,22 @@
         </is>
       </c>
       <c r="C170" s="4" t="n">
-        <v>329.6</v>
+        <v>3365.1</v>
       </c>
       <c r="D170" s="4" t="n">
-        <v>37.08</v>
+        <v>39.98</v>
       </c>
       <c r="E170" s="4" t="n">
-        <v>29.01</v>
+        <v>48.42</v>
       </c>
       <c r="F170" s="4" t="n">
-        <v>36.96</v>
+        <v>62.64</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>REDTAPE</t>
+          <t>JSFB</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -5712,22 +5352,22 @@
         </is>
       </c>
       <c r="C171" s="4" t="n">
-        <v>112.77</v>
+        <v>480.35</v>
       </c>
       <c r="D171" s="4" t="n">
-        <v>36.67</v>
+        <v>39.97</v>
       </c>
       <c r="E171" s="4" t="n">
-        <v>39.92</v>
+        <v>49.08</v>
       </c>
       <c r="F171" s="4" t="n">
-        <v>33.67</v>
+        <v>52.29</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>CRAMC</t>
+          <t>REFEX</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -5736,22 +5376,22 @@
         </is>
       </c>
       <c r="C172" s="4" t="n">
-        <v>219.95</v>
+        <v>256.55</v>
       </c>
       <c r="D172" s="4" t="n">
-        <v>36.43</v>
+        <v>39.92</v>
       </c>
       <c r="E172" s="4" t="n">
-        <v>33.89</v>
+        <v>40.47</v>
       </c>
       <c r="F172" s="4" t="n">
-        <v/>
+        <v>45.99</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>PRSMJOHNSN</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -5760,22 +5400,22 @@
         </is>
       </c>
       <c r="C173" s="4" t="n">
-        <v>509.45</v>
+        <v>101.54</v>
       </c>
       <c r="D173" s="4" t="n">
-        <v>36.38</v>
+        <v>39.86</v>
       </c>
       <c r="E173" s="4" t="n">
-        <v>52.35</v>
+        <v>36.88</v>
       </c>
       <c r="F173" s="4" t="n">
-        <v>62.95</v>
+        <v>37.15</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>BECTORFOOD</t>
+          <t>KIRLOSBROS</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -5784,22 +5424,22 @@
         </is>
       </c>
       <c r="C174" s="4" t="n">
-        <v>205.41</v>
+        <v>1693.4</v>
       </c>
       <c r="D174" s="4" t="n">
-        <v>36.09</v>
+        <v>39.68</v>
       </c>
       <c r="E174" s="4" t="n">
-        <v>47.44</v>
+        <v>42.71</v>
       </c>
       <c r="F174" s="4" t="n">
-        <v>45.54</v>
+        <v>50.35</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>CENTURYPLY</t>
+          <t>GRINDWELL</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -5808,22 +5448,22 @@
         </is>
       </c>
       <c r="C175" s="4" t="n">
-        <v>665.7</v>
+        <v>1897.7</v>
       </c>
       <c r="D175" s="4" t="n">
-        <v>35.92</v>
+        <v>39.57</v>
       </c>
       <c r="E175" s="4" t="n">
-        <v>32.13</v>
+        <v>47.71</v>
       </c>
       <c r="F175" s="4" t="n">
-        <v>44.26</v>
+        <v>51.66</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>RCF</t>
+          <t>ASHOKA</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -5832,22 +5472,22 @@
         </is>
       </c>
       <c r="C176" s="4" t="n">
-        <v>104.44</v>
+        <v>105.02</v>
       </c>
       <c r="D176" s="4" t="n">
-        <v>35.84</v>
+        <v>39.54</v>
       </c>
       <c r="E176" s="4" t="n">
-        <v>30.71</v>
+        <v>33.22</v>
       </c>
       <c r="F176" s="4" t="n">
-        <v>40.18</v>
+        <v>39.44</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>MAHSCOOTER</t>
+          <t>INDIAGLYCO</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -5856,22 +5496,22 @@
         </is>
       </c>
       <c r="C177" s="4" t="n">
-        <v>12155</v>
+        <v>331.95</v>
       </c>
       <c r="D177" s="4" t="n">
-        <v>35.64</v>
+        <v>39.4</v>
       </c>
       <c r="E177" s="4" t="n">
-        <v>43.76</v>
+        <v>29.17</v>
       </c>
       <c r="F177" s="4" t="n">
-        <v>51.65</v>
+        <v>37.04</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>GOKEX</t>
+          <t>BAJAJELEC</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -5880,22 +5520,22 @@
         </is>
       </c>
       <c r="C178" s="4" t="n">
-        <v>667.7</v>
+        <v>301.3</v>
       </c>
       <c r="D178" s="4" t="n">
-        <v>35.6</v>
+        <v>39.33</v>
       </c>
       <c r="E178" s="4" t="n">
-        <v>38.43</v>
+        <v>34.45</v>
       </c>
       <c r="F178" s="4" t="n">
-        <v>46.29</v>
+        <v>28.43</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>SURYAROSNI</t>
+          <t>AVL</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -5904,22 +5544,22 @@
         </is>
       </c>
       <c r="C179" s="4" t="n">
-        <v>208.33</v>
+        <v>568</v>
       </c>
       <c r="D179" s="4" t="n">
-        <v>35.56</v>
+        <v>39.21</v>
       </c>
       <c r="E179" s="4" t="n">
-        <v>39.66</v>
+        <v>47.8</v>
       </c>
       <c r="F179" s="4" t="n">
-        <v>43.96</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>ZAGGLE</t>
+          <t>CENTURYPLY</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -5928,22 +5568,22 @@
         </is>
       </c>
       <c r="C180" s="4" t="n">
-        <v>168.3</v>
+        <v>671.6</v>
       </c>
       <c r="D180" s="4" t="n">
-        <v>35.42</v>
+        <v>39.08</v>
       </c>
       <c r="E180" s="4" t="n">
-        <v>30.07</v>
+        <v>34.44</v>
       </c>
       <c r="F180" s="4" t="n">
-        <v>36.37</v>
+        <v>44.78</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>SUNTECK</t>
+          <t>WAKEFIT</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -5952,22 +5592,22 @@
         </is>
       </c>
       <c r="C181" s="4" t="n">
-        <v>271.15</v>
+        <v>133.26</v>
       </c>
       <c r="D181" s="4" t="n">
-        <v>35.18</v>
+        <v>39.07</v>
       </c>
       <c r="E181" s="4" t="n">
-        <v>35.33</v>
+        <v>47.46</v>
       </c>
       <c r="F181" s="4" t="n">
-        <v>38.22</v>
+        <v/>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>INDIGOPNTS</t>
+          <t>IMFA</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -5976,22 +5616,22 @@
         </is>
       </c>
       <c r="C182" s="4" t="n">
-        <v>1022.7</v>
+        <v>1179.8</v>
       </c>
       <c r="D182" s="4" t="n">
-        <v>35.01</v>
+        <v>38.83</v>
       </c>
       <c r="E182" s="4" t="n">
-        <v>46.38</v>
+        <v>38.77</v>
       </c>
       <c r="F182" s="4" t="n">
-        <v>45.93</v>
+        <v>54.43</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>REDTAPE</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -6000,22 +5640,22 @@
         </is>
       </c>
       <c r="C183" s="4" t="n">
-        <v>179.96</v>
+        <v>112.82</v>
       </c>
       <c r="D183" s="4" t="n">
-        <v>34.93</v>
+        <v>38.81</v>
       </c>
       <c r="E183" s="4" t="n">
-        <v>40.74</v>
+        <v>41.27</v>
       </c>
       <c r="F183" s="4" t="n">
-        <v>39.69</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>GOKULAGRO</t>
+          <t>HCC</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -6024,22 +5664,22 @@
         </is>
       </c>
       <c r="C184" s="4" t="n">
-        <v>206.74</v>
+        <v>19.43</v>
       </c>
       <c r="D184" s="4" t="n">
-        <v>34.9</v>
+        <v>38.77</v>
       </c>
       <c r="E184" s="4" t="n">
-        <v>44.27</v>
+        <v>43.08</v>
       </c>
       <c r="F184" s="4" t="n">
-        <v>57.7</v>
+        <v>44.21</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>CSBBANK</t>
+          <t>SUDARSCHEM</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -6048,22 +5688,22 @@
         </is>
       </c>
       <c r="C185" s="4" t="n">
-        <v>300.35</v>
+        <v>1144.6</v>
       </c>
       <c r="D185" s="4" t="n">
-        <v>34.8</v>
+        <v>38.48</v>
       </c>
       <c r="E185" s="4" t="n">
-        <v>38.66</v>
+        <v>54.5</v>
       </c>
       <c r="F185" s="4" t="n">
-        <v>42.35</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>EQUITASBNK</t>
+          <t>APLLTD</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -6072,22 +5712,22 @@
         </is>
       </c>
       <c r="C186" s="4" t="n">
-        <v>66.02</v>
+        <v>789.45</v>
       </c>
       <c r="D186" s="4" t="n">
-        <v>34.65</v>
+        <v>38.36</v>
       </c>
       <c r="E186" s="4" t="n">
-        <v>42.01</v>
+        <v>47.88</v>
       </c>
       <c r="F186" s="4" t="n">
-        <v>48.58</v>
+        <v>47.26</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>JLHL</t>
+          <t>SAMHI</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -6096,22 +5736,22 @@
         </is>
       </c>
       <c r="C187" s="4" t="n">
-        <v>255.7</v>
+        <v>144.99</v>
       </c>
       <c r="D187" s="4" t="n">
-        <v>34.56</v>
+        <v>38.32</v>
       </c>
       <c r="E187" s="4" t="n">
-        <v>37.17</v>
+        <v>40.87</v>
       </c>
       <c r="F187" s="4" t="n">
-        <v>46.26</v>
+        <v>42.82</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>AHLUCONT</t>
+          <t>KNRCON</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -6120,22 +5760,22 @@
         </is>
       </c>
       <c r="C188" s="4" t="n">
-        <v>557.6</v>
+        <v>111.48</v>
       </c>
       <c r="D188" s="4" t="n">
-        <v>34.44</v>
+        <v>38.31</v>
       </c>
       <c r="E188" s="4" t="n">
-        <v>25.09</v>
+        <v>36.97</v>
       </c>
       <c r="F188" s="4" t="n">
-        <v>38.87</v>
+        <v>32.31</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>WAKEFIT</t>
+          <t>RCF</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -6144,22 +5784,22 @@
         </is>
       </c>
       <c r="C189" s="4" t="n">
-        <v>131.39</v>
+        <v>104.78</v>
       </c>
       <c r="D189" s="4" t="n">
-        <v>34.38</v>
+        <v>38.19</v>
       </c>
       <c r="E189" s="4" t="n">
-        <v>43.42</v>
+        <v>31.29</v>
       </c>
       <c r="F189" s="4" t="n">
-        <v/>
+        <v>40.28</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>RUBICON</t>
+          <t>NFL</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -6168,22 +5808,22 @@
         </is>
       </c>
       <c r="C190" s="4" t="n">
-        <v>1548.5</v>
+        <v>62.88</v>
       </c>
       <c r="D190" s="4" t="n">
-        <v>34.24</v>
+        <v>38.19</v>
       </c>
       <c r="E190" s="4" t="n">
-        <v>58.91</v>
+        <v>30.94</v>
       </c>
       <c r="F190" s="4" t="n">
-        <v/>
+        <v>39.5</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>IXIGO</t>
+          <t>TVSSCS</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -6192,22 +5832,22 @@
         </is>
       </c>
       <c r="C191" s="4" t="n">
-        <v>150.75</v>
+        <v>122.17</v>
       </c>
       <c r="D191" s="4" t="n">
-        <v>34.24</v>
+        <v>37.91</v>
       </c>
       <c r="E191" s="4" t="n">
-        <v>39.35</v>
+        <v>46.83</v>
       </c>
       <c r="F191" s="4" t="n">
-        <v>39.98</v>
+        <v>44.74</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>IFBIND</t>
+          <t>RTNINDIA</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -6216,22 +5856,22 @@
         </is>
       </c>
       <c r="C192" s="4" t="n">
-        <v>1161</v>
+        <v>25.31</v>
       </c>
       <c r="D192" s="4" t="n">
-        <v>34.22</v>
+        <v>37.86</v>
       </c>
       <c r="E192" s="4" t="n">
-        <v>39.6</v>
+        <v>31.84</v>
       </c>
       <c r="F192" s="4" t="n">
-        <v>45.96</v>
+        <v>36.59</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>BAJAJELEC</t>
+          <t>CMSINFO</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -6240,22 +5880,22 @@
         </is>
       </c>
       <c r="C193" s="4" t="n">
-        <v>298</v>
+        <v>218.01</v>
       </c>
       <c r="D193" s="4" t="n">
-        <v>34.2</v>
+        <v>37.64</v>
       </c>
       <c r="E193" s="4" t="n">
-        <v>32.91</v>
+        <v>29.89</v>
       </c>
       <c r="F193" s="4" t="n">
-        <v>28.25</v>
+        <v>30.59</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>NETWORK18</t>
+          <t>WABAG</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -6264,22 +5904,22 @@
         </is>
       </c>
       <c r="C194" s="4" t="n">
-        <v>24.69</v>
+        <v>1884.8</v>
       </c>
       <c r="D194" s="4" t="n">
-        <v>34.09</v>
+        <v>37.5</v>
       </c>
       <c r="E194" s="4" t="n">
-        <v>29.01</v>
+        <v>51.23</v>
       </c>
       <c r="F194" s="4" t="n">
-        <v>32.46</v>
+        <v>61.95</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>METROPOLIS</t>
+          <t>JKLAKSHMI</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -6288,22 +5928,22 @@
         </is>
       </c>
       <c r="C195" s="4" t="n">
-        <v>529.25</v>
+        <v>473.2</v>
       </c>
       <c r="D195" s="4" t="n">
-        <v>34.08</v>
+        <v>37.15</v>
       </c>
       <c r="E195" s="4" t="n">
-        <v>46.57</v>
+        <v>31.12</v>
       </c>
       <c r="F195" s="4" t="n">
-        <v>54.63</v>
+        <v>35</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>MAHSEAMLES</t>
+          <t>CRIZAC</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -6312,22 +5952,22 @@
         </is>
       </c>
       <c r="C196" s="4" t="n">
-        <v>618.1</v>
+        <v>156.35</v>
       </c>
       <c r="D196" s="4" t="n">
-        <v>34.05</v>
+        <v>37.04</v>
       </c>
       <c r="E196" s="4" t="n">
-        <v>47.66</v>
+        <v>35.84</v>
       </c>
       <c r="F196" s="4" t="n">
-        <v>50.67</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>SWSOLAR</t>
+          <t>SUBROS</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -6336,22 +5976,22 @@
         </is>
       </c>
       <c r="C197" s="4" t="n">
-        <v>162.12</v>
+        <v>665.2</v>
       </c>
       <c r="D197" s="4" t="n">
-        <v>33.91</v>
+        <v>36.92</v>
       </c>
       <c r="E197" s="4" t="n">
-        <v>32.95</v>
+        <v>36.98</v>
       </c>
       <c r="F197" s="4" t="n">
-        <v>37.76</v>
+        <v>46.76</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>REFEX</t>
+          <t>HEMIPROP</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -6360,22 +6000,22 @@
         </is>
       </c>
       <c r="C198" s="4" t="n">
-        <v>254.4</v>
+        <v>111.78</v>
       </c>
       <c r="D198" s="4" t="n">
-        <v>33.82</v>
+        <v>36.82</v>
       </c>
       <c r="E198" s="4" t="n">
-        <v>39.64</v>
+        <v>32.13</v>
       </c>
       <c r="F198" s="4" t="n">
-        <v>45.79</v>
+        <v>41.16</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>TARC</t>
+          <t>BIRLACORPN</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -6384,22 +6024,22 @@
         </is>
       </c>
       <c r="C199" s="4" t="n">
-        <v>117.47</v>
+        <v>793.4</v>
       </c>
       <c r="D199" s="4" t="n">
-        <v>33.68</v>
+        <v>36.81</v>
       </c>
       <c r="E199" s="4" t="n">
-        <v>40.6</v>
+        <v>35.53</v>
       </c>
       <c r="F199" s="4" t="n">
-        <v>44.15</v>
+        <v>36.23</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>TARC</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -6408,22 +6048,22 @@
         </is>
       </c>
       <c r="C200" s="4" t="n">
-        <v>117.47</v>
+        <v>1538.6</v>
       </c>
       <c r="D200" s="4" t="n">
-        <v>33.68</v>
+        <v>36.67</v>
       </c>
       <c r="E200" s="4" t="n">
-        <v>40.6</v>
+        <v>54.49</v>
       </c>
       <c r="F200" s="4" t="n">
-        <v>44.15</v>
+        <v>69.44</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>JKPAPER</t>
+          <t>DBREALTY</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -6432,22 +6072,22 @@
         </is>
       </c>
       <c r="C201" s="4" t="n">
-        <v>365.5</v>
+        <v>87.12</v>
       </c>
       <c r="D201" s="4" t="n">
-        <v>33.63</v>
+        <v>36.33</v>
       </c>
       <c r="E201" s="4" t="n">
-        <v>46.14</v>
+        <v>35.9</v>
       </c>
       <c r="F201" s="4" t="n">
-        <v>50.29</v>
+        <v>39.79</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>SUDEEPPHRM</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -6456,22 +6096,22 @@
         </is>
       </c>
       <c r="C202" s="4" t="n">
-        <v>96.75</v>
+        <v>1008.1</v>
       </c>
       <c r="D202" s="4" t="n">
-        <v>33.55</v>
+        <v>36.24</v>
       </c>
       <c r="E202" s="4" t="n">
-        <v>40.76</v>
+        <v>52.76</v>
       </c>
       <c r="F202" s="4" t="n">
-        <v>39.72</v>
+        <v/>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>RELAXO</t>
+          <t>INDIASHLTR</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -6480,22 +6120,22 @@
         </is>
       </c>
       <c r="C203" s="4" t="n">
-        <v>286</v>
+        <v>624.75</v>
       </c>
       <c r="D203" s="4" t="n">
-        <v>32.68</v>
+        <v>36.17</v>
       </c>
       <c r="E203" s="4" t="n">
-        <v>37.21</v>
+        <v>33.58</v>
       </c>
       <c r="F203" s="4" t="n">
-        <v>32.6</v>
+        <v>37.18</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>PRICOLLTD</t>
+          <t>MSTCLTD</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -6504,22 +6144,22 @@
         </is>
       </c>
       <c r="C204" s="4" t="n">
-        <v>670.85</v>
+        <v>649.4</v>
       </c>
       <c r="D204" s="4" t="n">
-        <v>32.64</v>
+        <v>36.16</v>
       </c>
       <c r="E204" s="4" t="n">
-        <v>49.3</v>
+        <v>53.5</v>
       </c>
       <c r="F204" s="4" t="n">
-        <v>58.58</v>
+        <v>55.49</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>RAYMONDLSL</t>
+          <t>ENTERO</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -6528,22 +6168,22 @@
         </is>
       </c>
       <c r="C205" s="4" t="n">
-        <v>596.4</v>
+        <v>1581.1</v>
       </c>
       <c r="D205" s="4" t="n">
-        <v>32.36</v>
+        <v>35.89</v>
       </c>
       <c r="E205" s="4" t="n">
-        <v>32.27</v>
+        <v>57.4</v>
       </c>
       <c r="F205" s="4" t="n">
-        <v>22.34</v>
+        <v>62.05</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>HAPPSTMNDS</t>
+          <t>STAR</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -6552,22 +6192,22 @@
         </is>
       </c>
       <c r="C206" s="4" t="n">
-        <v>306.1</v>
+        <v>1045.2</v>
       </c>
       <c r="D206" s="4" t="n">
-        <v>32.35</v>
+        <v>35.89</v>
       </c>
       <c r="E206" s="4" t="n">
-        <v>34.99</v>
+        <v>49.07</v>
       </c>
       <c r="F206" s="4" t="n">
-        <v>28.3</v>
+        <v>56.28</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>RTNINDIA</t>
+          <t>RELIGARE</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -6576,22 +6216,22 @@
         </is>
       </c>
       <c r="C207" s="4" t="n">
-        <v>24.95</v>
+        <v>220.21</v>
       </c>
       <c r="D207" s="4" t="n">
-        <v>32.19</v>
+        <v>35.54</v>
       </c>
       <c r="E207" s="4" t="n">
-        <v>29.66</v>
+        <v>41.36</v>
       </c>
       <c r="F207" s="4" t="n">
-        <v>36.32</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>SAMHI</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -6600,22 +6240,22 @@
         </is>
       </c>
       <c r="C208" s="4" t="n">
-        <v>141.9</v>
+        <v>1987.3</v>
       </c>
       <c r="D208" s="4" t="n">
-        <v>32.12</v>
+        <v>35.17</v>
       </c>
       <c r="E208" s="4" t="n">
-        <v>36.43</v>
+        <v>54.85</v>
       </c>
       <c r="F208" s="4" t="n">
-        <v>41.51</v>
+        <v>68.59999999999999</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>HCC</t>
+          <t>SANDUMA</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -6624,22 +6264,22 @@
         </is>
       </c>
       <c r="C209" s="4" t="n">
-        <v>19.01</v>
+        <v>175.21</v>
       </c>
       <c r="D209" s="4" t="n">
-        <v>31.75</v>
+        <v>34.96</v>
       </c>
       <c r="E209" s="4" t="n">
-        <v>41.55</v>
+        <v>36.64</v>
       </c>
       <c r="F209" s="4" t="n">
-        <v>43.83</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>SMARTWORKS</t>
+          <t>STARCEMENT</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -6648,22 +6288,22 @@
         </is>
       </c>
       <c r="C210" s="4" t="n">
-        <v>474.3</v>
+        <v>171.54</v>
       </c>
       <c r="D210" s="4" t="n">
-        <v>31.68</v>
+        <v>34.9</v>
       </c>
       <c r="E210" s="4" t="n">
-        <v>47.02</v>
+        <v>29.73</v>
       </c>
       <c r="F210" s="4" t="n">
-        <v>48.84</v>
+        <v>40.27</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>AURIONPRO</t>
+          <t>VIPIND</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -6672,22 +6312,22 @@
         </is>
       </c>
       <c r="C211" s="4" t="n">
-        <v>601.6</v>
+        <v>270.85</v>
       </c>
       <c r="D211" s="4" t="n">
-        <v>31.14</v>
+        <v>34.83</v>
       </c>
       <c r="E211" s="4" t="n">
-        <v>28.56</v>
+        <v>33.56</v>
       </c>
       <c r="F211" s="4" t="n">
-        <v>35.79</v>
+        <v>32.98</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>VGUARD</t>
+          <t>TSFINV</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -6696,22 +6336,22 @@
         </is>
       </c>
       <c r="C212" s="4" t="n">
-        <v>288.2</v>
+        <v>396.05</v>
       </c>
       <c r="D212" s="4" t="n">
-        <v>30.65</v>
+        <v>34.64</v>
       </c>
       <c r="E212" s="4" t="n">
-        <v>36.59</v>
+        <v>45.81</v>
       </c>
       <c r="F212" s="4" t="n">
-        <v>41.7</v>
+        <v>52.44</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>SFL</t>
+          <t>AARTIDRUGS</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -6720,22 +6360,22 @@
         </is>
       </c>
       <c r="C213" s="4" t="n">
-        <v>603.65</v>
+        <v>396.35</v>
       </c>
       <c r="D213" s="4" t="n">
-        <v>30.6</v>
+        <v>34.56</v>
       </c>
       <c r="E213" s="4" t="n">
-        <v>42.93</v>
+        <v>45.84</v>
       </c>
       <c r="F213" s="4" t="n">
-        <v>43.38</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>VIPIND</t>
+          <t>METROPOLIS</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -6744,22 +6384,22 @@
         </is>
       </c>
       <c r="C214" s="4" t="n">
-        <v>269.55</v>
+        <v>523</v>
       </c>
       <c r="D214" s="4" t="n">
-        <v>30.52</v>
+        <v>34.09</v>
       </c>
       <c r="E214" s="4" t="n">
-        <v>33.45</v>
+        <v>46.84</v>
       </c>
       <c r="F214" s="4" t="n">
-        <v>32.96</v>
+        <v>54.78</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>WEBELSOLAR</t>
+          <t>VGUARD</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -6768,22 +6408,22 @@
         </is>
       </c>
       <c r="C215" s="4" t="n">
-        <v>65.56999999999999</v>
+        <v>288</v>
       </c>
       <c r="D215" s="4" t="n">
-        <v>30.25</v>
+        <v>34.03</v>
       </c>
       <c r="E215" s="4" t="n">
-        <v>31.27</v>
+        <v>36.37</v>
       </c>
       <c r="F215" s="4" t="n">
-        <v>43.03</v>
+        <v>41.61</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>MEDPLUS</t>
+          <t>OSWALPUMPS</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -6792,22 +6432,22 @@
         </is>
       </c>
       <c r="C216" s="4" t="n">
-        <v>625.3</v>
+        <v>257.85</v>
       </c>
       <c r="D216" s="4" t="n">
-        <v>30.16</v>
+        <v>33.82</v>
       </c>
       <c r="E216" s="4" t="n">
-        <v>25.81</v>
+        <v>26.66</v>
       </c>
       <c r="F216" s="4" t="n">
-        <v>36.8</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>ASHAPURMIN</t>
+          <t>V2RETAIL</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -6816,22 +6456,22 @@
         </is>
       </c>
       <c r="C217" s="4" t="n">
-        <v>470.8</v>
+        <v>166.25</v>
       </c>
       <c r="D217" s="4" t="n">
-        <v>30.1</v>
+        <v>33.71</v>
       </c>
       <c r="E217" s="4" t="n">
-        <v>32.54</v>
+        <v>35.47</v>
       </c>
       <c r="F217" s="4" t="n">
-        <v>47.7</v>
+        <v>48.48</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>HEMIPROP</t>
+          <t>VIYASH</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -6840,22 +6480,22 @@
         </is>
       </c>
       <c r="C218" s="4" t="n">
-        <v>110.35</v>
+        <v>226</v>
       </c>
       <c r="D218" s="4" t="n">
-        <v>29.82</v>
+        <v>33.63</v>
       </c>
       <c r="E218" s="4" t="n">
-        <v>30.13</v>
+        <v>43.02</v>
       </c>
       <c r="F218" s="4" t="n">
-        <v>40.77</v>
+        <v>54.61</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>RELIGARE</t>
+          <t>IONEXCHANG</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -6864,22 +6504,22 @@
         </is>
       </c>
       <c r="C219" s="4" t="n">
-        <v>217.59</v>
+        <v>377.5</v>
       </c>
       <c r="D219" s="4" t="n">
-        <v>29.69</v>
+        <v>33.5</v>
       </c>
       <c r="E219" s="4" t="n">
-        <v>39.85</v>
+        <v>45.7</v>
       </c>
       <c r="F219" s="4" t="n">
-        <v>46.65</v>
+        <v>45.52</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>JKLAKSHMI</t>
+          <t>PRICOLLTD</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -6888,22 +6528,22 @@
         </is>
       </c>
       <c r="C220" s="4" t="n">
-        <v>467.3</v>
+        <v>666.9</v>
       </c>
       <c r="D220" s="4" t="n">
-        <v>29.69</v>
+        <v>33.41</v>
       </c>
       <c r="E220" s="4" t="n">
-        <v>27.86</v>
+        <v>49.01</v>
       </c>
       <c r="F220" s="4" t="n">
-        <v>34.47</v>
+        <v>58.43</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>PRAJIND</t>
+          <t>CERA</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -6912,22 +6552,22 @@
         </is>
       </c>
       <c r="C221" s="4" t="n">
-        <v>285.8</v>
+        <v>5046</v>
       </c>
       <c r="D221" s="4" t="n">
-        <v>29.28</v>
+        <v>32.93</v>
       </c>
       <c r="E221" s="4" t="n">
-        <v>35.03</v>
+        <v>38.27</v>
       </c>
       <c r="F221" s="4" t="n">
-        <v>39.75</v>
+        <v>43.22</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>NFL</t>
+          <t>SKFINDUS</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -6936,22 +6576,22 @@
         </is>
       </c>
       <c r="C222" s="4" t="n">
-        <v>61.74</v>
+        <v>2514.6</v>
       </c>
       <c r="D222" s="4" t="n">
-        <v>29.01</v>
+        <v>32.92</v>
       </c>
       <c r="E222" s="4" t="n">
-        <v>27.06</v>
+        <v>44.59</v>
       </c>
       <c r="F222" s="4" t="n">
-        <v>39.01</v>
+        <v/>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>FIEMIND</t>
+          <t>HGINFRA</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -6960,22 +6600,22 @@
         </is>
       </c>
       <c r="C223" s="4" t="n">
-        <v>1747.7</v>
+        <v>407.95</v>
       </c>
       <c r="D223" s="4" t="n">
-        <v>28.64</v>
+        <v>32.77</v>
       </c>
       <c r="E223" s="4" t="n">
-        <v>32.47</v>
+        <v>26.75</v>
       </c>
       <c r="F223" s="4" t="n">
-        <v>48.12</v>
+        <v>31.43</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>ASHOKA</t>
+          <t>PRAJIND</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -6984,22 +6624,22 @@
         </is>
       </c>
       <c r="C224" s="4" t="n">
-        <v>102.02</v>
+        <v>287.15</v>
       </c>
       <c r="D224" s="4" t="n">
-        <v>28.59</v>
+        <v>32.01</v>
       </c>
       <c r="E224" s="4" t="n">
-        <v>29.21</v>
+        <v>35.6</v>
       </c>
       <c r="F224" s="4" t="n">
-        <v>38.96</v>
+        <v>39.84</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>THYROCARE</t>
+          <t>ASHAPURMIN</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -7008,22 +6648,22 @@
         </is>
       </c>
       <c r="C225" s="4" t="n">
-        <v>499.7</v>
+        <v>465</v>
       </c>
       <c r="D225" s="4" t="n">
-        <v>28.57</v>
+        <v>31.99</v>
       </c>
       <c r="E225" s="4" t="n">
-        <v>46.64</v>
+        <v>31.97</v>
       </c>
       <c r="F225" s="4" t="n">
-        <v>58.43</v>
+        <v>47.43</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>INOXGREEN</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -7032,22 +6672,22 @@
         </is>
       </c>
       <c r="C226" s="4" t="n">
-        <v>128.92</v>
+        <v>1231.2</v>
       </c>
       <c r="D226" s="4" t="n">
-        <v>28.45</v>
+        <v>31.93</v>
       </c>
       <c r="E226" s="4" t="n">
-        <v>31.16</v>
+        <v>42.93</v>
       </c>
       <c r="F226" s="4" t="n">
-        <v>44.67</v>
+        <v>54.08</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>AVANTIFEED</t>
+          <t>KIRLPNU</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -7056,22 +6696,22 @@
         </is>
       </c>
       <c r="C227" s="4" t="n">
-        <v>699.1</v>
+        <v>637.15</v>
       </c>
       <c r="D227" s="4" t="n">
-        <v>28.43</v>
+        <v>31.83</v>
       </c>
       <c r="E227" s="4" t="n">
-        <v>29.71</v>
+        <v>39.05</v>
       </c>
       <c r="F227" s="4" t="n">
-        <v>45.69</v>
+        <v>50.56</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>BORORENEW</t>
+          <t>EUREKAFORB</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -7080,22 +6720,22 @@
         </is>
       </c>
       <c r="C228" s="4" t="n">
-        <v>430.4</v>
+        <v>342.1</v>
       </c>
       <c r="D228" s="4" t="n">
-        <v>28.3</v>
+        <v>31.76</v>
       </c>
       <c r="E228" s="4" t="n">
-        <v>34.54</v>
+        <v>29.7</v>
       </c>
       <c r="F228" s="4" t="n">
-        <v>44.11</v>
+        <v>33.01</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>PNCINFRA</t>
+          <t>CCAVENUE</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -7104,22 +6744,22 @@
         </is>
       </c>
       <c r="C229" s="4" t="n">
-        <v>134.74</v>
+        <v>138.3</v>
       </c>
       <c r="D229" s="4" t="n">
-        <v>28.25</v>
+        <v>31.69</v>
       </c>
       <c r="E229" s="4" t="n">
-        <v>25.56</v>
+        <v>39.96</v>
       </c>
       <c r="F229" s="4" t="n">
-        <v>34.03</v>
+        <v>41.31</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>SAFARI</t>
+          <t>VIKRAMSOLR</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -7128,22 +6768,22 @@
         </is>
       </c>
       <c r="C230" s="4" t="n">
-        <v>1319.6</v>
+        <v>144</v>
       </c>
       <c r="D230" s="4" t="n">
-        <v>28.03</v>
+        <v>31.57</v>
       </c>
       <c r="E230" s="4" t="n">
-        <v>32.6</v>
+        <v>30.32</v>
       </c>
       <c r="F230" s="4" t="n">
-        <v>36.91</v>
+        <v/>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>SKFINDIA</t>
+          <t>MAHSEAMLES</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -7152,22 +6792,22 @@
         </is>
       </c>
       <c r="C231" s="4" t="n">
-        <v>1398.8</v>
+        <v>585.4</v>
       </c>
       <c r="D231" s="4" t="n">
-        <v>28.03</v>
+        <v>31.33</v>
       </c>
       <c r="E231" s="4" t="n">
-        <v>30.79</v>
+        <v>42.53</v>
       </c>
       <c r="F231" s="4" t="n">
-        <v>31.36</v>
+        <v>48.52</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>CMSINFO</t>
+          <t>SAFARI</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -7176,22 +6816,22 @@
         </is>
       </c>
       <c r="C232" s="4" t="n">
-        <v>213.85</v>
+        <v>1312.3</v>
       </c>
       <c r="D232" s="4" t="n">
-        <v>27.92</v>
+        <v>31.18</v>
       </c>
       <c r="E232" s="4" t="n">
-        <v>27.31</v>
+        <v>32.38</v>
       </c>
       <c r="F232" s="4" t="n">
-        <v>30.19</v>
+        <v>36.82</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>ADVENZYMES</t>
+          <t>RTNPOWER</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -7200,22 +6840,22 @@
         </is>
       </c>
       <c r="C233" s="4" t="n">
-        <v>267.15</v>
+        <v>6.54</v>
       </c>
       <c r="D233" s="4" t="n">
-        <v>27.63</v>
+        <v>31.02</v>
       </c>
       <c r="E233" s="4" t="n">
-        <v>33.26</v>
+        <v>24.5</v>
       </c>
       <c r="F233" s="4" t="n">
-        <v>42.81</v>
+        <v>39.08</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>OSWALPUMPS</t>
+          <t>BORORENEW</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -7224,22 +6864,22 @@
         </is>
       </c>
       <c r="C234" s="4" t="n">
-        <v>254.35</v>
+        <v>427.55</v>
       </c>
       <c r="D234" s="4" t="n">
-        <v>27.53</v>
+        <v>30.88</v>
       </c>
       <c r="E234" s="4" t="n">
-        <v>27.46</v>
+        <v>34.3</v>
       </c>
       <c r="F234" s="4" t="n">
-        <v>25.36</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>HGINFRA</t>
+          <t>SMARTWORKS</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -7248,22 +6888,22 @@
         </is>
       </c>
       <c r="C235" s="4" t="n">
-        <v>401.75</v>
+        <v>469.05</v>
       </c>
       <c r="D235" s="4" t="n">
-        <v>27.28</v>
+        <v>30.55</v>
       </c>
       <c r="E235" s="4" t="n">
-        <v>25.15</v>
+        <v>45.39</v>
       </c>
       <c r="F235" s="4" t="n">
-        <v>31.25</v>
+        <v>47.79</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>CERA</t>
+          <t>STYL</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -7272,22 +6912,22 @@
         </is>
       </c>
       <c r="C236" s="4" t="n">
-        <v>5002.5</v>
+        <v>328.95</v>
       </c>
       <c r="D236" s="4" t="n">
-        <v>27.16</v>
+        <v>30.45</v>
       </c>
       <c r="E236" s="4" t="n">
-        <v>35.49</v>
+        <v>47.2</v>
       </c>
       <c r="F236" s="4" t="n">
-        <v>42.53</v>
+        <v/>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>PRSMJOHNSN</t>
+          <t>SHAKTIPUMP</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -7296,22 +6936,22 @@
         </is>
       </c>
       <c r="C237" s="4" t="n">
-        <v>97.47</v>
+        <v>419.1</v>
       </c>
       <c r="D237" s="4" t="n">
-        <v>27.01</v>
+        <v>29.92</v>
       </c>
       <c r="E237" s="4" t="n">
-        <v>31.49</v>
+        <v>31.15</v>
       </c>
       <c r="F237" s="4" t="n">
-        <v>35.98</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>SHAKTIPUMP</t>
+          <t>THYROCARE</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -7320,22 +6960,22 @@
         </is>
       </c>
       <c r="C238" s="4" t="n">
-        <v>419</v>
+        <v>487.55</v>
       </c>
       <c r="D238" s="4" t="n">
-        <v>26.69</v>
+        <v>29.82</v>
       </c>
       <c r="E238" s="4" t="n">
-        <v>30.13</v>
+        <v>44.45</v>
       </c>
       <c r="F238" s="4" t="n">
-        <v>40.33</v>
+        <v>57.01</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>STARCEMENT</t>
+          <t>HCG</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -7344,22 +6984,22 @@
         </is>
       </c>
       <c r="C239" s="4" t="n">
-        <v>168.46</v>
+        <v>590.6</v>
       </c>
       <c r="D239" s="4" t="n">
-        <v>26.53</v>
+        <v>29.79</v>
       </c>
       <c r="E239" s="4" t="n">
-        <v>25.84</v>
+        <v>37.37</v>
       </c>
       <c r="F239" s="4" t="n">
-        <v>39.44</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>HCG</t>
+          <t>RAYMONDLSL</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -7368,22 +7008,22 @@
         </is>
       </c>
       <c r="C240" s="4" t="n">
-        <v>589.2</v>
+        <v>574.2</v>
       </c>
       <c r="D240" s="4" t="n">
-        <v>26.5</v>
+        <v>29.6</v>
       </c>
       <c r="E240" s="4" t="n">
-        <v>37.51</v>
+        <v>30.62</v>
       </c>
       <c r="F240" s="4" t="n">
-        <v>51.34</v>
+        <v>21.88</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>ANUP</t>
+          <t>PARKHOSPS</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -7392,22 +7032,22 @@
         </is>
       </c>
       <c r="C241" s="4" t="n">
-        <v>1488.2</v>
+        <v>235.7</v>
       </c>
       <c r="D241" s="4" t="n">
-        <v>26.16</v>
+        <v>29.45</v>
       </c>
       <c r="E241" s="4" t="n">
-        <v>31.92</v>
+        <v>39.96</v>
       </c>
       <c r="F241" s="4" t="n">
-        <v>41.47</v>
+        <v/>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>ORIENTCEM</t>
+          <t>ANUP</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -7416,22 +7056,22 @@
         </is>
       </c>
       <c r="C242" s="4" t="n">
-        <v>111.62</v>
+        <v>1483</v>
       </c>
       <c r="D242" s="4" t="n">
-        <v>25.96</v>
+        <v>28.3</v>
       </c>
       <c r="E242" s="4" t="n">
-        <v>23.76</v>
+        <v>31.94</v>
       </c>
       <c r="F242" s="4" t="n">
-        <v>32.29</v>
+        <v>41.48</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>RTNPOWER</t>
+          <t>RUBICON</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -7440,22 +7080,22 @@
         </is>
       </c>
       <c r="C243" s="4" t="n">
-        <v>6.54</v>
+        <v>1477.1</v>
       </c>
       <c r="D243" s="4" t="n">
-        <v>25.71</v>
+        <v>27.73</v>
       </c>
       <c r="E243" s="4" t="n">
-        <v>24.5</v>
+        <v>56.08</v>
       </c>
       <c r="F243" s="4" t="n">
-        <v>39.08</v>
+        <v/>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>CAMPUS</t>
+          <t>MEDPLUS</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -7464,22 +7104,22 @@
         </is>
       </c>
       <c r="C244" s="4" t="n">
-        <v>197</v>
+        <v>612.8</v>
       </c>
       <c r="D244" s="4" t="n">
-        <v>24.84</v>
+        <v>26.82</v>
       </c>
       <c r="E244" s="4" t="n">
-        <v>30.65</v>
+        <v>24.45</v>
       </c>
       <c r="F244" s="4" t="n">
-        <v>37.3</v>
+        <v>36.01</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>DBREALTY</t>
+          <t>INOXGREEN</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
@@ -7488,22 +7128,22 @@
         </is>
       </c>
       <c r="C245" s="4" t="n">
-        <v>84.98</v>
+        <v>118.69</v>
       </c>
       <c r="D245" s="4" t="n">
-        <v>24.44</v>
+        <v>26.75</v>
       </c>
       <c r="E245" s="4" t="n">
-        <v>33.98</v>
+        <v>28.74</v>
       </c>
       <c r="F245" s="4" t="n">
-        <v>39.42</v>
+        <v>43.29</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>EUREKAFORB</t>
+          <t>CAMPUS</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -7512,22 +7152,22 @@
         </is>
       </c>
       <c r="C246" s="4" t="n">
-        <v>339</v>
+        <v>197.01</v>
       </c>
       <c r="D246" s="4" t="n">
-        <v>23.42</v>
+        <v>26.59</v>
       </c>
       <c r="E246" s="4" t="n">
-        <v>26.87</v>
+        <v>35.56</v>
       </c>
       <c r="F246" s="4" t="n">
-        <v>32.45</v>
+        <v>38.22</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>ROUTE</t>
+          <t>ADVENZYMES</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -7536,22 +7176,22 @@
         </is>
       </c>
       <c r="C247" s="4" t="n">
-        <v>416.7</v>
+        <v>262.9</v>
       </c>
       <c r="D247" s="4" t="n">
-        <v>23.18</v>
+        <v>26.16</v>
       </c>
       <c r="E247" s="4" t="n">
-        <v>27.87</v>
+        <v>33.21</v>
       </c>
       <c r="F247" s="4" t="n">
-        <v>27.42</v>
+        <v>42.79</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>GHCL</t>
+          <t>JSLL</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -7560,22 +7200,22 @@
         </is>
       </c>
       <c r="C248" s="4" t="n">
-        <v>386.25</v>
+        <v>388.7</v>
       </c>
       <c r="D248" s="4" t="n">
-        <v>22.79</v>
+        <v>25.62</v>
       </c>
       <c r="E248" s="4" t="n">
-        <v>28.83</v>
+        <v>28.64</v>
       </c>
       <c r="F248" s="4" t="n">
-        <v>38.03</v>
+        <v>37.88</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>JSLL</t>
+          <t>JLHL</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
@@ -7584,22 +7224,22 @@
         </is>
       </c>
       <c r="C249" s="4" t="n">
-        <v>385.15</v>
+        <v>239.65</v>
       </c>
       <c r="D249" s="4" t="n">
-        <v>21.46</v>
+        <v>25.32</v>
       </c>
       <c r="E249" s="4" t="n">
-        <v>28.07</v>
+        <v>34.16</v>
       </c>
       <c r="F249" s="4" t="n">
-        <v>37.81</v>
+        <v>44.68</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>VIKRAMSOLR</t>
+          <t>IXIGO</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -7608,22 +7248,22 @@
         </is>
       </c>
       <c r="C250" s="4" t="n">
-        <v>142.32</v>
+        <v>138.12</v>
       </c>
       <c r="D250" s="4" t="n">
-        <v>19.65</v>
+        <v>24.97</v>
       </c>
       <c r="E250" s="4" t="n">
-        <v>29.16</v>
+        <v>37.45</v>
       </c>
       <c r="F250" s="4" t="n">
-        <v/>
+        <v>38.69</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>SANOFICONR</t>
+          <t>GHCL</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
@@ -7632,22 +7272,22 @@
         </is>
       </c>
       <c r="C251" s="4" t="n">
-        <v>3581.7</v>
+        <v>385.35</v>
       </c>
       <c r="D251" s="4" t="n">
-        <v>15.77</v>
+        <v>24.55</v>
       </c>
       <c r="E251" s="4" t="n">
-        <v>26.02</v>
+        <v>31.24</v>
       </c>
       <c r="F251" s="4" t="n">
-        <v>33.31</v>
+        <v>38.38</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>V2RETAIL</t>
+          <t>SANOFICONR</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
@@ -7656,16 +7296,16 @@
         </is>
       </c>
       <c r="C252" s="4" t="n">
-        <v>154.5</v>
+        <v>3573.3</v>
       </c>
       <c r="D252" s="4" t="n">
-        <v>14.48</v>
+        <v>21.7</v>
       </c>
       <c r="E252" s="4" t="n">
-        <v>26.12</v>
+        <v>25.45</v>
       </c>
       <c r="F252" s="4" t="n">
-        <v>44.7</v>
+        <v>32.95</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Micro250_stocks.xlsx
+++ b/docs/Micro250_stocks.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -560,37 +560,37 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>1001.45</v>
+        <v>1043.05</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>80.3</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>83.73999999999999</v>
+        <v>81.73</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>86.94</v>
+        <v>86.73999999999999</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>32.35</v>
+        <v>40.37</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>644.01</v>
+        <v>664.83</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>594.74</v>
+        <v>612.54</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>1336285</v>
+        <v>1423975</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>16426</v>
+        <v>16213</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>PCJEWELLER</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -599,37 +599,37 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>418.15</v>
+        <v>18.04</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>73.73</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>78.93000000000001</v>
+        <v>75.53</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>72.5</v>
+        <v>67.66</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>35.37</v>
+        <v>35.75</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>327.38</v>
+        <v>11.46</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>316.85</v>
+        <v>11.3</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>1608625</v>
+        <v>464682574</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>17085</v>
+        <v>17693</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>PCJEWELLER</t>
+          <t>SOUTHBANK</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -638,37 +638,37 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>16.28</v>
+        <v>52.57</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>71.19</v>
+        <v>60.52</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>71.68000000000001</v>
+        <v>68.04000000000001</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>64.84999999999999</v>
+        <v>75.36</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>28.6</v>
+        <v>28.61</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>11.09</v>
+        <v>44.67</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>11.03</v>
+        <v>43.18</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>412549372</v>
+        <v>19841925</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>15967</v>
+        <v>13771</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>CUPID</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -677,37 +677,37 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>353.7</v>
+        <v>402.15</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>70.05</v>
+        <v>58.24</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>81.79000000000001</v>
+        <v>70.93000000000001</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>94.81</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>22.88</v>
+        <v>33.76</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>215.27</v>
+        <v>331.05</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>190.6</v>
+        <v>319.96</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>22759042</v>
+        <v>1735494</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>47561</v>
+        <v>16431</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SOUTHBANK</t>
+          <t>PGIL</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -716,37 +716,37 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>51.45</v>
+        <v>1224</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>66.89</v>
+        <v>46.87</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>66.23999999999999</v>
+        <v>60.91</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>74.55</v>
+        <v>72.88</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>21.6</v>
+        <v>25.48</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>44.14</v>
+        <v>1044.47</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>42.74</v>
+        <v>991.67</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>16472005</v>
+        <v>217787</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>13477</v>
+        <v>11307</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>BBOX</t>
+          <t>CUPID</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -755,460 +755,31 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>880.2</v>
+        <v>306.45</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>57.47</v>
+        <v>45.38</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>61.92</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>64.61</v>
+        <v>91.86</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>41.69</v>
+        <v>21.56</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>767.01</v>
+        <v>221</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>737.0700000000001</v>
+        <v>195.9</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1054066</v>
+        <v>24591679</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>16113</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>LLOYDSENGG</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>96.37</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>55.66</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>65.11</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>66.06999999999999</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>24.07</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>79.77</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>76.44</v>
-      </c>
-      <c r="J8" s="4" t="n">
-        <v>12714894</v>
-      </c>
-      <c r="K8" s="4" t="n">
-        <v>14933</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>NEOGEN</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>2484.8</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>68.89</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>67.47</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>27.24</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>2013.19</v>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>1925.98</v>
-      </c>
-      <c r="J9" s="4" t="n">
-        <v>229498</v>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>7465</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>GPPL</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>168.09</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>53.38</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>61.94</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>55.74</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>31.11</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>157.31</v>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>156.9</v>
-      </c>
-      <c r="J10" s="4" t="n">
-        <v>1454962</v>
-      </c>
-      <c r="K10" s="4" t="n">
-        <v>8042</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>OPTIEMUS</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>760</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>53.22</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>72.45999999999999</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>63.76</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>573.47</v>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>558.34</v>
-      </c>
-      <c r="J11" s="4" t="n">
-        <v>1546778</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>7111</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>PGIL</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>1263.3</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>52.66</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>67.09999999999999</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>77.37</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>30.09</v>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>1030.81</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>979.01</v>
-      </c>
-      <c r="J12" s="4" t="n">
-        <v>223134</v>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>11910</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>AXISCADES</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>2020.5</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>52.35</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>62.09</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>66.45</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>28.39</v>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>1733.44</v>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>1675.13</v>
-      </c>
-      <c r="J13" s="4" t="n">
-        <v>275087</v>
-      </c>
-      <c r="K13" s="4" t="n">
-        <v>9000</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>MANORAMA</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>1927.4</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>48.59</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>60.07</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>69.97</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>22.45</v>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>1679.28</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>1618.63</v>
-      </c>
-      <c r="J14" s="4" t="n">
-        <v>216529</v>
-      </c>
-      <c r="K14" s="4" t="n">
-        <v>12064</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>WELENT</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>727.7</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>48.29</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>61.27</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>67.54000000000001</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>27.43</v>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>621.25</v>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>599.51</v>
-      </c>
-      <c r="J15" s="4" t="n">
-        <v>653406</v>
-      </c>
-      <c r="K15" s="4" t="n">
-        <v>9860</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>GMMPFAUDLR</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>1312.1</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>47.56</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>64.2</v>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>55.12</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>38.44</v>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>1069.58</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>1055.06</v>
-      </c>
-      <c r="J16" s="4" t="n">
-        <v>457775</v>
-      </c>
-      <c r="K16" s="4" t="n">
-        <v>5899</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>ICIL</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>437.5</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>47.53</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>62.7</v>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>62.37</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>27.01</v>
-      </c>
-      <c r="H17" s="4" t="n">
-        <v>383.2</v>
-      </c>
-      <c r="I17" s="4" t="n">
-        <v>366.88</v>
-      </c>
-      <c r="J17" s="4" t="n">
-        <v>504119</v>
-      </c>
-      <c r="K17" s="4" t="n">
-        <v>8734</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>STLTECH</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>865.9</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>46.89</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>65.20999999999999</v>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>84.3</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>33.53</v>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>593.33</v>
-      </c>
-      <c r="I18" s="4" t="n">
-        <v>523.1</v>
-      </c>
-      <c r="J18" s="4" t="n">
-        <v>1990823</v>
-      </c>
-      <c r="K18" s="4" t="n">
-        <v>44512</v>
+        <v>41207</v>
       </c>
     </row>
   </sheetData>
@@ -1219,17 +790,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1296,22 +856,22 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>1001.45</v>
+        <v>1043.05</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>80.3</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>83.73999999999999</v>
+        <v>81.73</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>86.94</v>
+        <v>86.73999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>PCJEWELLER</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -1320,22 +880,22 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>418.15</v>
+        <v>18.04</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>73.73</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>78.93000000000001</v>
+        <v>75.53</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>72.5</v>
+        <v>67.66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>PCJEWELLER</t>
+          <t>JUSTDIAL</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -1344,22 +904,22 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>16.28</v>
+        <v>759.55</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>71.19</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>71.68000000000001</v>
+        <v>59.01</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>64.84999999999999</v>
+        <v>48.12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>CUPID</t>
+          <t>TANLA</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -1368,22 +928,22 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>353.7</v>
+        <v>581.3</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>70.05</v>
+        <v>69.73999999999999</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>81.79000000000001</v>
+        <v>55.47</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>94.81</v>
+        <v>47.86</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>JAIBALAJI</t>
+          <t>SOUTHBANK</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -1392,22 +952,22 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>74.91</v>
+        <v>52.57</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>68.09999999999999</v>
+        <v>60.52</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>54.11</v>
+        <v>68.04000000000001</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>44.53</v>
+        <v>75.36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>LOTUSDEV</t>
+          <t>TIPSMUSIC</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1416,22 +976,22 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>246.25</v>
+        <v>723.25</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>67.14</v>
+        <v>59.15</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>75.8</v>
+        <v>60.42</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v/>
+        <v>62.95</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>SOUTHBANK</t>
+          <t>LOTUSDEV</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1440,22 +1000,22 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>51.45</v>
+        <v>237.36</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>66.89</v>
+        <v>59.06</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>66.23999999999999</v>
+        <v>64.64</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>74.55</v>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>TANLA</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -1464,22 +1024,22 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>559.65</v>
+        <v>402.15</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>66.05</v>
+        <v>58.24</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>55.99</v>
+        <v>70.93000000000001</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>48.02</v>
+        <v>71.01000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>JUSTDIAL</t>
+          <t>MASTEK</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1488,22 +1048,22 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>713.25</v>
+        <v>1761.6</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>64.38</v>
+        <v>56.56</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>60.4</v>
+        <v>52.21</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>48.58</v>
+        <v>45.27</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>JAYNECOIND</t>
+          <t>CELLO</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -1512,22 +1072,22 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>100.62</v>
+        <v>363.85</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>63.29</v>
+        <v>53.82</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>60.02</v>
+        <v>44.5</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>62.8</v>
+        <v>31.9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>MASTEK</t>
+          <t>GRWRHITECH</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1536,22 +1096,22 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1756.2</v>
+        <v>7034</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>63.16</v>
+        <v>53.44</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>55.63</v>
+        <v>66.36</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>46.76</v>
+        <v>68.98</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>FEDFINA</t>
+          <t>SUNTECK</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1560,22 +1120,22 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>161.86</v>
+        <v>282.5</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>63.05</v>
+        <v>53.32</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>58.2</v>
+        <v>35.92</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>60.01</v>
+        <v>38.17</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>APOLLO</t>
+          <t>CAPILLARY</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1584,22 +1144,22 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>429</v>
+        <v>547.8</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>60.98</v>
+        <v>52.29</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>60.81</v>
+        <v>55.62</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>70.3</v>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>CELLO</t>
+          <t>IIFLCAPS</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1608,22 +1168,22 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>376.6</v>
+        <v>344.55</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>60.62</v>
+        <v>51.8</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>49.8</v>
+        <v>54.31</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>34.89</v>
+        <v>58.32</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GAEL</t>
+          <t>KSCL</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1632,22 +1192,22 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>173.7</v>
+        <v>730.05</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>58.98</v>
+        <v>50.82</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>59.71</v>
+        <v>42.86</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>63.71</v>
+        <v>41.38</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>IIFLCAPS</t>
+          <t>SAMHI</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1656,22 +1216,22 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>347.1</v>
+        <v>150.49</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>58.68</v>
+        <v>49.64</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>58.31</v>
+        <v>44.63</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>59.15</v>
+        <v>44.07</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>DYNAMATECH</t>
+          <t>WESTLIFE</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1680,22 +1240,22 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>13774</v>
+        <v>567.9</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>58.56</v>
+        <v>49.52</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>68.53</v>
+        <v>55.98</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>73.45</v>
+        <v>45.49</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>RAIN</t>
+          <t>GODREJAGRO</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1704,22 +1264,22 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>228.55</v>
+        <v>633</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>58.38</v>
+        <v>49.43</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>65.26000000000001</v>
+        <v>50.97</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>62.23</v>
+        <v>49.72</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>BBOX</t>
+          <t>KANSAINER</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1728,22 +1288,22 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>880.2</v>
+        <v>183.23</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>57.47</v>
+        <v>49.08</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>61.92</v>
+        <v>39.83</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>64.61</v>
+        <v>37.14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>HAPPSTMNDS</t>
+          <t>AXISCADES</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1752,22 +1312,22 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>335.9</v>
+        <v>1961.3</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>56.95</v>
+        <v>47.46</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>43.2</v>
+        <v>54.35</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>32.17</v>
+        <v>61.44</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1776,22 +1336,22 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>335.95</v>
+        <v>2043.8</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>56.41</v>
+        <v>47.15</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>67.27</v>
+        <v>57.44</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>76.40000000000001</v>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>DIACABS</t>
+          <t>PGIL</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1800,22 +1360,22 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>373.75</v>
+        <v>1224</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>56.22</v>
+        <v>46.87</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>68.08</v>
+        <v>60.91</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>81.48999999999999</v>
+        <v>72.88</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>TIPSMUSIC</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1824,22 +1384,22 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>684.4</v>
+        <v>206.09</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>55.7</v>
+        <v>46.64</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>64.66</v>
+        <v>52.14</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>64.39</v>
+        <v>60.48</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>JAMNAAUTO</t>
+          <t>FIEMIND</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1848,22 +1408,22 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>142.54</v>
+        <v>1846.2</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>55.66</v>
+        <v>46.64</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>56.92</v>
+        <v>36.83</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>60.53</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENGG</t>
+          <t>JKLAKSHMI</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1872,22 +1432,22 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>96.37</v>
+        <v>484.65</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>55.66</v>
+        <v>46.29</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>65.11</v>
+        <v>30.78</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>66.06999999999999</v>
+        <v>34.88</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>RALLIS</t>
+          <t>ALOKINDS</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1896,22 +1456,22 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>204.93</v>
+        <v>8.09</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>55.6</v>
+        <v>45.95</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>36.68</v>
+        <v>34.76</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>41.79</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GRWRHITECH</t>
+          <t>JAYNECOIND</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1920,22 +1480,22 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>7094.5</v>
+        <v>91.04000000000001</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>54.96</v>
+        <v>45.66</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>65.40000000000001</v>
+        <v>48.58</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>68.45999999999999</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>NEOGEN</t>
+          <t>CUPID</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1944,22 +1504,22 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2484.8</v>
+        <v>306.45</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>54.8</v>
+        <v>45.38</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>68.89</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>67.47</v>
+        <v>91.86</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>VAIBHAVGBL</t>
+          <t>ORIENTCEM</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1968,22 +1528,22 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>210.88</v>
+        <v>115.98</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>54.39</v>
+        <v>45.28</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>44.35</v>
+        <v>30.59</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>44.55</v>
+        <v>32.94</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>DATAMATICS</t>
+          <t>ORKLAINDIA</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1992,22 +1552,22 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>793</v>
+        <v>547</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>54.35</v>
+        <v>45.24</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>50.21</v>
+        <v>36.15</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>54.31</v>
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>FINPIPE</t>
+          <t>SHRIPISTON</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -2016,22 +1576,22 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>154.75</v>
+        <v>4337</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>53.98</v>
+        <v>44.63</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>40.09</v>
+        <v>55.1</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>41.2</v>
+        <v>71.83</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>HERITGFOOD</t>
+          <t>GMMPFAUDLR</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -2040,22 +1600,22 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>405.4</v>
+        <v>1275</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>53.95</v>
+        <v>44.39</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>60.87</v>
+        <v>56.79</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>53.21</v>
+        <v>52.32</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GPPL</t>
+          <t>FEDFINA</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -2064,22 +1624,22 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>168.09</v>
+        <v>149.71</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>53.38</v>
+        <v>44.28</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>61.94</v>
+        <v>48.35</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>55.74</v>
+        <v>55.63</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>OPTIEMUS</t>
+          <t>GMRP&amp;UI</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -2088,16 +1648,16 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>760</v>
+        <v>95.67</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>53.22</v>
+        <v>44.19</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>72.45999999999999</v>
+        <v>44.33</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>63.76</v>
+        <v>48.96</v>
       </c>
     </row>
     <row r="36">
@@ -2112,22 +1672,22 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>716.2</v>
+        <v>685.25</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>53.03</v>
+        <v>43.93</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>45.92</v>
+        <v>41.26</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>48.3</v>
+        <v>46.54</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>ALOKINDS</t>
+          <t>BBOX</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -2136,46 +1696,46 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>8.5</v>
+        <v>805.1</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>52.97</v>
+        <v>43.46</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>36.43</v>
+        <v>51.51</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>33.86</v>
+        <v>61.12</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>THANGAMAYL</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>5098</v>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>52.93</v>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>52.21</v>
-      </c>
-      <c r="F38" s="4" t="n">
-        <v>66.28</v>
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>STLTECH</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>826.65</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>43.31</v>
+      </c>
+      <c r="E38" s="7" t="n">
+        <v>61.96</v>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>80.44</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>PGIL</t>
+          <t>JAIBALAJI</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -2184,22 +1744,22 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>1263.3</v>
+        <v>63.45</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>52.66</v>
+        <v>43.13</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>67.09999999999999</v>
+        <v>45.96</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>77.37</v>
+        <v>41.58</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>PNGJL</t>
+          <t>CSBBANK</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -2208,22 +1768,22 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>603.35</v>
+        <v>305.8</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>52.58</v>
+        <v>43</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>50.57</v>
+        <v>42.25</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>49.41</v>
+        <v>43.82</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>AEQUS</t>
+          <t>MAHSCOOTER</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -2232,22 +1792,22 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>262.2</v>
+        <v>12282</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>52.45</v>
+        <v>42.95</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>63.51</v>
+        <v>42.01</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v/>
+        <v>50.26</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>TRANSRAILL</t>
+          <t>JKPAPER</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -2256,22 +1816,22 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>465.85</v>
+        <v>377.05</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>52.37</v>
+        <v>42.95</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>46.07</v>
+        <v>44.9</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>43.96</v>
+        <v>49.14</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>AXISCADES</t>
+          <t>GPPL</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -2280,22 +1840,22 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>2020.5</v>
+        <v>160.72</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>52.35</v>
+        <v>42.93</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>62.09</v>
+        <v>49.45</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>66.45</v>
+        <v>52.09</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>STYRENIX</t>
+          <t>BLUESTONE</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -2304,22 +1864,22 @@
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>2072.1</v>
+        <v>760.7</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>52.27</v>
+        <v>42.86</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>45.69</v>
+        <v>52.6</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>48.84</v>
+        <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>EDELWEISS</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -2328,46 +1888,46 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>134.47</v>
+        <v>460.65</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>52.21</v>
+        <v>42.79</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>59.66</v>
+        <v>41.52</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>61.87</v>
+        <v>39.16</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>DCBBANK</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="n">
-        <v>210.79</v>
-      </c>
-      <c r="D46" s="4" t="n">
-        <v>52.09</v>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>58.44</v>
-      </c>
-      <c r="F46" s="4" t="n">
-        <v>62.96</v>
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>SANSERA</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="n">
+        <v>3977.7</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>42.71</v>
+      </c>
+      <c r="E46" s="7" t="n">
+        <v>62.02</v>
+      </c>
+      <c r="F46" s="7" t="n">
+        <v>74.11</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>NETWORK18</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -2376,22 +1936,22 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>26.68</v>
+        <v>4782.5</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>51.96</v>
+        <v>42.46</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>37.04</v>
+        <v>46.32</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>33.75</v>
+        <v>61.95</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>ELECTCAST</t>
+          <t>LLOYDSENGG</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -2400,22 +1960,22 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>76.7</v>
+        <v>87.31999999999999</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>51.82</v>
+        <v>42.35</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>50.69</v>
+        <v>52.1</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>44.51</v>
+        <v>59.04</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GMRP&amp;UI</t>
+          <t>IXIGO</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -2424,22 +1984,22 @@
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>99.68000000000001</v>
+        <v>146.58</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>51.81</v>
+        <v>42.29</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>50.65</v>
+        <v>38.53</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>51.04</v>
+        <v>39.11</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>JKPAPER</t>
+          <t>PNGJL</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -2448,22 +2008,22 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>396.1</v>
+        <v>577.15</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>51.47</v>
+        <v>42.22</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>54.59</v>
+        <v>44.99</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>54.82</v>
+        <v>46.51</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>CAPILLARY</t>
+          <t>OPTIEMUS</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -2472,22 +2032,22 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>545.4</v>
+        <v>673.7</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>51.4</v>
+        <v>42.13</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>52.17</v>
+        <v>57.64</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v/>
+        <v>57.68</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>KANSAINER</t>
+          <t>KITEX</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -2496,22 +2056,22 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>185.23</v>
+        <v>115.37</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>51.37</v>
+        <v>42.12</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>42</v>
+        <v>31.74</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>38.5</v>
+        <v>40.88</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>SENCO</t>
+          <t>WAKEFIT</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -2520,22 +2080,22 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>337.25</v>
+        <v>133.99</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>51.24</v>
+        <v>42.1</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>48.56</v>
+        <v>44.61</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>48.91</v>
+        <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>KSCL</t>
+          <t>PNCINFRA</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -2544,22 +2104,22 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>730.2</v>
+        <v>140.56</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>51.14</v>
+        <v>42.04</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>42.95</v>
+        <v>28.62</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>41.45</v>
+        <v>34.01</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>VMART</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -2568,22 +2128,22 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>802.25</v>
+        <v>828.8</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>50.84</v>
+        <v>41.81</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>54.95</v>
+        <v>52.95</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>53.4</v>
+        <v>55.53</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>METROPOLIS</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -2592,22 +2152,22 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>548.85</v>
+        <v>530.6</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>50.55</v>
+        <v>41.62</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>59.86</v>
+        <v>45.2</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>65.16</v>
+        <v>53.75</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>JYOTHYLAB</t>
+          <t>RELAXO</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -2616,22 +2176,22 @@
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>191.61</v>
+        <v>291.35</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>50.46</v>
+        <v>41.45</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>38.29</v>
+        <v>37.13</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>36.83</v>
+        <v>32.18</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>BANCOINDIA</t>
+          <t>VMART</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -2640,22 +2200,22 @@
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>602.15</v>
+        <v>771.05</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>50.28</v>
+        <v>41.07</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>47.33</v>
+        <v>53.03</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>55.65</v>
+        <v>52.72</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>MANYAVAR</t>
+          <t>EQUITASBNK</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -2664,22 +2224,22 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>519.85</v>
+        <v>66.66</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>49.94</v>
+        <v>41.02</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>56.25</v>
+        <v>43.12</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>39.21</v>
+        <v>48.42</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>LXCHEM</t>
+          <t>LUMAXTECH</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -2688,22 +2248,22 @@
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>179.02</v>
+        <v>1807.7</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>49.79</v>
+        <v>40.93</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>59.86</v>
+        <v>51.14</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>47.51</v>
+        <v>63.12</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>TRIVENI</t>
+          <t>DYNAMATECH</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -2712,22 +2272,22 @@
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>250.35</v>
+        <v>12296</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>49.73</v>
+        <v>40.88</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>39.64</v>
+        <v>55.33</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>41.94</v>
+        <v>64.86</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>KRBL</t>
+          <t>GRINDWELL</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -2736,22 +2296,22 @@
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>393.8</v>
+        <v>1877.5</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>49.59</v>
+        <v>40.82</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>54.78</v>
+        <v>45.83</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>55.34</v>
+        <v>50.77</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>EPL</t>
+          <t>WEWORK</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -2760,22 +2320,22 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>236.35</v>
+        <v>652.1</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>48.84</v>
+        <v>40.69</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>50.05</v>
+        <v>46.94</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>53.68</v>
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>BLACKBUCK</t>
+          <t>TRANSRAILL</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -2784,22 +2344,22 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>594.45</v>
+        <v>428.8</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>48.83</v>
+        <v>40.67</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>51.45</v>
+        <v>39.54</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>57.1</v>
+        <v>41.52</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>POWERMECH</t>
+          <t>VARROC</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -2808,22 +2368,22 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>2422.3</v>
+        <v>791</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>48.77</v>
+        <v>40.36</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>46.55</v>
+        <v>55.36</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>49.33</v>
+        <v>61.53</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>WESTLIFE</t>
+          <t>APOLLO</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -2832,22 +2392,22 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>573.6</v>
+        <v>374.75</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>48.68</v>
+        <v>40.14</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>58.59</v>
+        <v>50.66</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>46.59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>LUMAXTECH</t>
+          <t>PRIVISCL</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -2856,22 +2416,22 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>1912.8</v>
+        <v>3330.6</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>48.63</v>
+        <v>40.03</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>58.4</v>
+        <v>44.86</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>68.29000000000001</v>
+        <v>60.51</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>MANORAMA</t>
+          <t>AGARWALEYE</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -2880,22 +2440,22 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>1927.4</v>
+        <v>468.55</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>48.59</v>
+        <v>39.9</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>60.07</v>
+        <v>47.34</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>69.97</v>
+        <v>52.05</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>CRAMC</t>
+          <t>ICIL</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -2904,22 +2464,22 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>226.74</v>
+        <v>405.75</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>48.56</v>
+        <v>39.87</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>39.98</v>
+        <v>50.61</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v/>
+        <v>56.89</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>TMB</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -2928,22 +2488,22 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>149.93</v>
+        <v>841.25</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>48.56</v>
+        <v>39.76</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>48.65</v>
+        <v>50.1</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>53.6</v>
+        <v>64.43000000000001</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>SMLMAH</t>
+          <t>RAIN</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -2952,22 +2512,22 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>6031.5</v>
+        <v>198.18</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>48.51</v>
+        <v>39.52</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>60.48</v>
+        <v>51.27</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>67.14</v>
+        <v>56.72</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>VARROC</t>
+          <t>ATLANTAELE</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -2976,22 +2536,22 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>820.4</v>
+        <v>1619.5</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>48.49</v>
+        <v>39.35</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>64.55</v>
+        <v>49.68</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>66.17</v>
+        <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>NESCO</t>
+          <t>VOLTAMP</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -3000,22 +2560,22 @@
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>1048.2</v>
+        <v>9947</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>48.31</v>
+        <v>39.17</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>44.6</v>
+        <v>45.88</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>49.78</v>
+        <v>53.11</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>WELENT</t>
+          <t>GAEL</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -3024,22 +2584,22 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>727.7</v>
+        <v>153.83</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>48.29</v>
+        <v>39.06</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>61.27</v>
+        <v>47.64</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>67.54000000000001</v>
+        <v>55.96</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>ALKYLAMINE</t>
+          <t>HAPPSTMNDS</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -3048,22 +2608,22 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>1838.5</v>
+        <v>307.5</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>48.02</v>
+        <v>39.06</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>52.86</v>
+        <v>37.29</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>50.29</v>
+        <v>28.01</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>TARC</t>
+          <t>SHAILY</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -3072,22 +2632,22 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>123.69</v>
+        <v>2987</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>47.96</v>
+        <v>39.01</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>46.18</v>
+        <v>50.62</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>45.71</v>
+        <v>65.20999999999999</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>TARC</t>
+          <t>SHAREINDIA</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -3096,22 +2656,22 @@
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>123.69</v>
+        <v>179.79</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>47.96</v>
+        <v>38.82</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>46.18</v>
+        <v>49.42</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>45.71</v>
+        <v>47.87</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>RBA</t>
+          <t>TSFINV</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -3120,22 +2680,22 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>92.31999999999999</v>
+        <v>394</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>47.84</v>
+        <v>38.54</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>60.91</v>
+        <v>41.51</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>55.71</v>
+        <v>50.44</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>SHAREINDIA</t>
+          <t>ELLEN</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -3144,22 +2704,22 @@
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>193.42</v>
+        <v>315.3</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>47.7</v>
+        <v>38.43</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>56.71</v>
+        <v>46.86</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>51.57</v>
+        <v>35.74</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>KPIGREEN</t>
+          <t>NEOGEN</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -3168,22 +2728,22 @@
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>321.85</v>
+        <v>2173.7</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>47.66</v>
+        <v>38.24</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>40.13</v>
+        <v>53.78</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>43.77</v>
+        <v>59.64</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>GMMPFAUDLR</t>
+          <t>MANYAVAR</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -3192,22 +2752,22 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>1312.1</v>
+        <v>490.05</v>
       </c>
       <c r="D81" s="4" t="n">
-        <v>47.56</v>
+        <v>38.2</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>64.2</v>
+        <v>48.55</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>55.12</v>
+        <v>37.21</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>ICIL</t>
+          <t>QUESS</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -3216,22 +2776,22 @@
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>437.5</v>
+        <v>315.45</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>47.53</v>
+        <v>38.2</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>62.7</v>
+        <v>53.51</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>62.37</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>INOXINDIA</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -3240,22 +2800,22 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>471.75</v>
+        <v>1919.7</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>47.03</v>
+        <v>38.03</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>41.55</v>
+        <v>49.87</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>39.17</v>
+        <v>67.15000000000001</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>TIMETECHNO</t>
+          <t>INDIGOPNTS</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -3264,22 +2824,22 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>179.5</v>
+        <v>1013.9</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>47.03</v>
+        <v>37.89</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>46.31</v>
+        <v>45.64</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>50.65</v>
+        <v>45.64</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>SENCO</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -3288,22 +2848,22 @@
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>865.9</v>
+        <v>309.3</v>
       </c>
       <c r="D85" s="4" t="n">
-        <v>46.89</v>
+        <v>37.87</v>
       </c>
       <c r="E85" s="4" t="n">
-        <v>65.20999999999999</v>
+        <v>41.75</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>84.3</v>
+        <v>46.18</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>TEXRAIL</t>
+          <t>AVL</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -3312,22 +2872,22 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>112.89</v>
+        <v>555.95</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>46.78</v>
+        <v>37.83</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>50.12</v>
+        <v>44.92</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>45.96</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>PARAS</t>
+          <t>UTLSOLAR</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -3336,22 +2896,22 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>1298.9</v>
+        <v>369</v>
       </c>
       <c r="D87" s="4" t="n">
-        <v>46.78</v>
+        <v>37.65</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>57.95</v>
+        <v>49.51</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>64.12</v>
+        <v/>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>TARC</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -3360,22 +2920,22 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>525.7</v>
+        <v>116.06</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>46.6</v>
+        <v>37.59</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>55.45</v>
+        <v>38</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>65.06</v>
+        <v>42.51</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>QUESS</t>
+          <t>TARC</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -3384,22 +2944,22 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>332.95</v>
+        <v>116.06</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>46.48</v>
+        <v>37.59</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>61.41</v>
+        <v>38</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>49.63</v>
+        <v>42.51</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>AZAD</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -3408,22 +2968,22 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>863.8</v>
+        <v>2555.8</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>46.42</v>
+        <v>37.29</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>58.4</v>
+        <v>50.94</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>58.45</v>
+        <v>61.46</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>GOKULAGRO</t>
+          <t>KIRLOSBROS</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -3432,22 +2992,22 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>213.66</v>
+        <v>1659.3</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>46.2</v>
+        <v>37.25</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>48.1</v>
+        <v>37.71</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>59.27</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>VOLTAMP</t>
+          <t>RBA</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -3456,22 +3016,22 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>10394</v>
+        <v>86.34</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>46.16</v>
+        <v>37.01</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>56.72</v>
+        <v>55.39</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>57.4</v>
+        <v>53.58</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>JAMNAAUTO</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -3480,22 +3040,22 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>101</v>
+        <v>123.16</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>46.13</v>
+        <v>36.99</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>45.2</v>
+        <v>47.57</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>40.82</v>
+        <v>53.54</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>CSBBANK</t>
+          <t>KPIGREEN</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -3504,22 +3064,22 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>311.05</v>
+        <v>295.85</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>46.09</v>
+        <v>36.93</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>41.33</v>
+        <v>34.7</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>43.42</v>
+        <v>41.76</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>ORKLAINDIA</t>
+          <t>SKFINDIA</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -3528,22 +3088,22 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>550.35</v>
+        <v>1415.6</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>45.9</v>
+        <v>36.87</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>42.06</v>
+        <v>33.75</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v/>
+        <v>31.4</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>ALIVUS</t>
+          <t>VAIBHAVGBL</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -3552,22 +3112,22 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>1341.8</v>
+        <v>195.22</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>45.84</v>
+        <v>36.65</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>59.87</v>
+        <v>35.92</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>66.45</v>
+        <v>41.25</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>SHAILY</t>
+          <t>TRIVENI</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -3576,22 +3136,22 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>3083.3</v>
+        <v>227.52</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>45.7</v>
+        <v>36.52</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>57.96</v>
+        <v>36.58</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>68.78</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>PICCADIL</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -3600,22 +3160,22 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>589.9</v>
+        <v>294.45</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>45.51</v>
+        <v>36.5</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>45.47</v>
+        <v>52.94</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>49.26</v>
+        <v>60.12</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>INOXINDIA</t>
+          <t>SUPRIYA</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -3624,22 +3184,22 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>2025</v>
+        <v>818.55</v>
       </c>
       <c r="D99" s="4" t="n">
-        <v>45.42</v>
+        <v>36.45</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>57.16</v>
+        <v>48.09</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>73.62</v>
+        <v>54.86</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>ATLANTAELE</t>
+          <t>BALAMINES</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -3648,22 +3208,22 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>1695.2</v>
+        <v>1897.8</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>45.38</v>
+        <v>36.45</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>52.97</v>
+        <v>45.33</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v/>
+        <v>51.74</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>STYRENIX</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -3672,22 +3232,22 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>2044.8</v>
+        <v>1936.7</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>45.36</v>
+        <v>36.39</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>54.32</v>
+        <v>39.89</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v/>
+        <v>46.06</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>MIDHANI</t>
+          <t>SKIPPER</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -3696,22 +3256,22 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>419.65</v>
+        <v>497</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>45.32</v>
+        <v>36.31</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>52.75</v>
+        <v>41.77</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>55.27</v>
+        <v>52.94</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>ASTRAMICRO</t>
+          <t>BIRLACORPN</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -3720,22 +3280,22 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>1621.1</v>
+        <v>784.4</v>
       </c>
       <c r="D103" s="4" t="n">
-        <v>45.32</v>
+        <v>36.21</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>56.64</v>
+        <v>32.91</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>68.06999999999999</v>
+        <v>35.16</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>SUPRIYA</t>
+          <t>AEQUS</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -3744,22 +3304,22 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>872.6</v>
+        <v>235.55</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>45.23</v>
+        <v>36.08</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>53.68</v>
+        <v>53.08</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>58.19</v>
+        <v/>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>UJJIVANSFB</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -3768,22 +3328,22 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>63.25</v>
+        <v>1984</v>
       </c>
       <c r="D105" s="4" t="n">
-        <v>45.23</v>
+        <v>35.92</v>
       </c>
       <c r="E105" s="4" t="n">
-        <v>50.67</v>
+        <v>49.95</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>58.43</v>
+        <v>64.72</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>RATNAMANI</t>
+          <t>SHILPAMED</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -3792,22 +3352,22 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>2565.1</v>
+        <v>860.8</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>45.22</v>
+        <v>35.86</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>48.97</v>
+        <v>60.58</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>48.69</v>
+        <v>70.03</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>WEWORK</t>
+          <t>DBL</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -3816,22 +3376,22 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>661.2</v>
+        <v>380.55</v>
       </c>
       <c r="D107" s="4" t="n">
-        <v>45.16</v>
+        <v>35.84</v>
       </c>
       <c r="E107" s="4" t="n">
-        <v>52.03</v>
+        <v>35.54</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v/>
+        <v>41.2</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>NESCO</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -3840,22 +3400,22 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>186.73</v>
+        <v>1007</v>
       </c>
       <c r="D108" s="4" t="n">
-        <v>45.13</v>
+        <v>35.8</v>
       </c>
       <c r="E108" s="4" t="n">
-        <v>44.24</v>
+        <v>37.75</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>40.83</v>
+        <v>46.01</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>ELLEN</t>
+          <t>APLLTD</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -3864,22 +3424,22 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>335.5</v>
+        <v>781.3</v>
       </c>
       <c r="D109" s="4" t="n">
-        <v>45.11</v>
+        <v>35.7</v>
       </c>
       <c r="E109" s="4" t="n">
-        <v>55.4</v>
+        <v>42.75</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>39.61</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>YATHARTH</t>
+          <t>DIACABS</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -3888,46 +3448,46 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>991.5</v>
+        <v>326.65</v>
       </c>
       <c r="D110" s="4" t="n">
-        <v>45.01</v>
+        <v>35.58</v>
       </c>
       <c r="E110" s="4" t="n">
-        <v>58.49</v>
+        <v>55.57</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>66.25</v>
+        <v>71.51000000000001</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="5" t="inlineStr">
-        <is>
-          <t>AZAD</t>
-        </is>
-      </c>
-      <c r="B111" s="6" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C111" s="7" t="n">
-        <v>2741</v>
-      </c>
-      <c r="D111" s="7" t="n">
-        <v>44.92</v>
-      </c>
-      <c r="E111" s="7" t="n">
-        <v>60.44</v>
-      </c>
-      <c r="F111" s="7" t="n">
-        <v>67.68000000000001</v>
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>ARVINDFASN</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="n">
+        <v>376.95</v>
+      </c>
+      <c r="D111" s="4" t="n">
+        <v>35.54</v>
+      </c>
+      <c r="E111" s="4" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="F111" s="4" t="n">
+        <v>39.36</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>EQUITASBNK</t>
+          <t>V2RETAIL</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -3936,22 +3496,22 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>68.28</v>
+        <v>162.81</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>44.91</v>
+        <v>35.5</v>
       </c>
       <c r="E112" s="4" t="n">
-        <v>49.16</v>
+        <v>33.13</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>51.56</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>KSB</t>
+          <t>UJJIVANSFB</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -3960,22 +3520,22 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>779.6</v>
+        <v>58.1</v>
       </c>
       <c r="D113" s="4" t="n">
-        <v>44.87</v>
+        <v>35.45</v>
       </c>
       <c r="E113" s="4" t="n">
-        <v>41.84</v>
+        <v>42.88</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>49.8</v>
+        <v>54.09</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>RENUKA</t>
+          <t>RALLIS</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -3984,22 +3544,22 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>22.15</v>
+        <v>194.57</v>
       </c>
       <c r="D114" s="4" t="n">
-        <v>44.83</v>
+        <v>35.39</v>
       </c>
       <c r="E114" s="4" t="n">
-        <v>43.37</v>
+        <v>31.53</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>38.39</v>
+        <v>40.01</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>SURYAROSNI</t>
+          <t>CRAMC</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -4008,22 +3568,22 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>212.52</v>
+        <v>212.13</v>
       </c>
       <c r="D115" s="4" t="n">
-        <v>44.8</v>
+        <v>35.38</v>
       </c>
       <c r="E115" s="4" t="n">
-        <v>41.73</v>
+        <v>31.92</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>44.5</v>
+        <v/>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>EMIL</t>
+          <t>RATEGAIN</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -4032,16 +3592,16 @@
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>182.81</v>
+        <v>788.1</v>
       </c>
       <c r="D116" s="4" t="n">
-        <v>44.69</v>
+        <v>35.18</v>
       </c>
       <c r="E116" s="4" t="n">
-        <v>61.94</v>
+        <v>44.41</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>58.6</v>
+        <v>54.95</v>
       </c>
     </row>
     <row r="117">
@@ -4056,46 +3616,46 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>2573.4</v>
+        <v>2456</v>
       </c>
       <c r="D117" s="4" t="n">
-        <v>44.61</v>
+        <v>35.13</v>
       </c>
       <c r="E117" s="4" t="n">
-        <v>51.04</v>
+        <v>42.49</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>51.78</v>
+        <v>48.28</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="5" t="inlineStr">
-        <is>
-          <t>SANSERA</t>
-        </is>
-      </c>
-      <c r="B118" s="6" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C118" s="7" t="n">
-        <v>4054.5</v>
-      </c>
-      <c r="D118" s="7" t="n">
-        <v>44.57</v>
-      </c>
-      <c r="E118" s="7" t="n">
-        <v>66.48999999999999</v>
-      </c>
-      <c r="F118" s="7" t="n">
-        <v>77.05</v>
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>WELENT</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="n">
+        <v>666.9</v>
+      </c>
+      <c r="D118" s="4" t="n">
+        <v>35.13</v>
+      </c>
+      <c r="E118" s="4" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="F118" s="4" t="n">
+        <v>58.76</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>GREAVESCOT</t>
+          <t>AHLUCONT</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -4104,22 +3664,22 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>204.3</v>
+        <v>540.15</v>
       </c>
       <c r="D119" s="4" t="n">
-        <v>44.54</v>
+        <v>35.08</v>
       </c>
       <c r="E119" s="4" t="n">
-        <v>51.16</v>
+        <v>23.79</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>52.35</v>
+        <v>38.18</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>UTLSOLAR</t>
+          <t>DATAMATICS</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -4128,22 +3688,22 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>402.4</v>
+        <v>710.95</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>44.46</v>
+        <v>34.83</v>
       </c>
       <c r="E120" s="4" t="n">
-        <v>56.58</v>
+        <v>41.86</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v/>
+        <v>49.73</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>PNCINFRA</t>
+          <t>YATHARTH</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -4152,46 +3712,46 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>144.26</v>
+        <v>920.8</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>44.46</v>
+        <v>34.72</v>
       </c>
       <c r="E121" s="4" t="n">
-        <v>30.83</v>
+        <v>52.58</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>35.63</v>
+        <v>62.26</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="5" t="inlineStr">
-        <is>
-          <t>MARKSANS</t>
-        </is>
-      </c>
-      <c r="B122" s="6" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C122" s="7" t="n">
-        <v>311</v>
-      </c>
-      <c r="D122" s="7" t="n">
-        <v>44.43</v>
-      </c>
-      <c r="E122" s="7" t="n">
-        <v>61.53</v>
-      </c>
-      <c r="F122" s="7" t="n">
-        <v>64.61</v>
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>ALIVUS</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="n">
+        <v>1269</v>
+      </c>
+      <c r="D122" s="4" t="n">
+        <v>34.66</v>
+      </c>
+      <c r="E122" s="4" t="n">
+        <v>52.95</v>
+      </c>
+      <c r="F122" s="4" t="n">
+        <v>62.38</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>BLUESTONE</t>
+          <t>HERITGFOOD</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -4200,22 +3760,22 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>778.9</v>
+        <v>349.3</v>
       </c>
       <c r="D123" s="4" t="n">
-        <v>44.39</v>
+        <v>34.64</v>
       </c>
       <c r="E123" s="4" t="n">
-        <v>58.2</v>
+        <v>44.04</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v/>
+        <v>46.92</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>VIPIND</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -4224,22 +3784,22 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>735.15</v>
+        <v>269.95</v>
       </c>
       <c r="D124" s="4" t="n">
-        <v>44.25</v>
+        <v>34.62</v>
       </c>
       <c r="E124" s="4" t="n">
-        <v>59.48</v>
+        <v>32.08</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>73.66</v>
+        <v>32.45</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>BLACKBUCK</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -4248,46 +3808,46 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>572.15</v>
+        <v>543.45</v>
       </c>
       <c r="D125" s="4" t="n">
-        <v>44.22</v>
+        <v>34.47</v>
       </c>
       <c r="E125" s="4" t="n">
-        <v>56.55</v>
+        <v>43.87</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>55.45</v>
+        <v>50.12</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="5" t="inlineStr">
-        <is>
-          <t>SHRIPISTON</t>
-        </is>
-      </c>
-      <c r="B126" s="6" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C126" s="7" t="n">
-        <v>4333</v>
-      </c>
-      <c r="D126" s="7" t="n">
-        <v>43.71</v>
-      </c>
-      <c r="E126" s="7" t="n">
-        <v>63.17</v>
-      </c>
-      <c r="F126" s="7" t="n">
-        <v>79.14</v>
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>KTKBANK</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="n">
+        <v>300.55</v>
+      </c>
+      <c r="D126" s="4" t="n">
+        <v>34.43</v>
+      </c>
+      <c r="E126" s="4" t="n">
+        <v>53.93</v>
+      </c>
+      <c r="F126" s="4" t="n">
+        <v>66.76000000000001</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>ARVINDFASN</t>
+          <t>EDELWEISS</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -4296,22 +3856,22 @@
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>398.9</v>
+        <v>119.53</v>
       </c>
       <c r="D127" s="4" t="n">
-        <v>43.58</v>
+        <v>34.32</v>
       </c>
       <c r="E127" s="4" t="n">
-        <v>38.4</v>
+        <v>47.34</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>43.64</v>
+        <v>55.32</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>SPARC</t>
+          <t>PURVA</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -4320,22 +3880,22 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>188.64</v>
+        <v>194.58</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>43.52</v>
+        <v>34.12</v>
       </c>
       <c r="E128" s="4" t="n">
-        <v>48.31</v>
+        <v>35.74</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>51.41</v>
+        <v>40.48</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>SKFINDIA</t>
+          <t>ROUTE</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -4344,22 +3904,22 @@
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>1451.1</v>
+        <v>416</v>
       </c>
       <c r="D129" s="4" t="n">
-        <v>43.49</v>
+        <v>34.1</v>
       </c>
       <c r="E129" s="4" t="n">
-        <v>36.49</v>
+        <v>32.58</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>31.81</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>AURIONPRO</t>
+          <t>INDIAGLYCO</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -4368,22 +3928,22 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>627.25</v>
+        <v>287.45</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>43.42</v>
+        <v>33.99</v>
       </c>
       <c r="E130" s="4" t="n">
-        <v>34.37</v>
+        <v>27.91</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>37.03</v>
+        <v>35.77</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>BALAMINES</t>
+          <t>JLHL</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -4392,46 +3952,46 @@
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>2043.4</v>
+        <v>243.05</v>
       </c>
       <c r="D131" s="4" t="n">
-        <v>43.37</v>
+        <v>33.97</v>
       </c>
       <c r="E131" s="4" t="n">
-        <v>53.42</v>
+        <v>33.15</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>56.83</v>
+        <v>44.17</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="5" t="inlineStr">
-        <is>
-          <t>SHILPAMED</t>
-        </is>
-      </c>
-      <c r="B132" s="6" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C132" s="7" t="n">
-        <v>937.6</v>
-      </c>
-      <c r="D132" s="7" t="n">
-        <v>43.24</v>
-      </c>
-      <c r="E132" s="7" t="n">
-        <v>69.77</v>
-      </c>
-      <c r="F132" s="7" t="n">
-        <v>75.63</v>
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>EPL</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="n">
+        <v>221.81</v>
+      </c>
+      <c r="D132" s="4" t="n">
+        <v>33.93</v>
+      </c>
+      <c r="E132" s="4" t="n">
+        <v>44.41</v>
+      </c>
+      <c r="F132" s="4" t="n">
+        <v>51.27</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>QPOWER</t>
+          <t>LXCHEM</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -4440,22 +4000,22 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>1433.8</v>
+        <v>150.46</v>
       </c>
       <c r="D133" s="4" t="n">
-        <v>42.95</v>
+        <v>33.76</v>
       </c>
       <c r="E133" s="4" t="n">
-        <v>59.85</v>
+        <v>39.18</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>66.11</v>
+        <v>41.59</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>SFL</t>
+          <t>PICCADIL</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -4464,22 +4024,22 @@
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>616.85</v>
+        <v>550.8</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>42.85</v>
+        <v>33.74</v>
       </c>
       <c r="E134" s="4" t="n">
-        <v>45.05</v>
+        <v>39.57</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>44.01</v>
+        <v>44.69</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>MAHSCOOTER</t>
+          <t>MANORAMA</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -4488,22 +4048,22 @@
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>12408</v>
+        <v>1746.2</v>
       </c>
       <c r="D135" s="4" t="n">
-        <v>42.82</v>
+        <v>33.72</v>
       </c>
       <c r="E135" s="4" t="n">
-        <v>46.06</v>
+        <v>52.2</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>52.87</v>
+        <v>65.03</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>AWFIS</t>
+          <t>GOKULAGRO</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -4512,22 +4072,22 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>241.63</v>
+        <v>201.36</v>
       </c>
       <c r="D136" s="4" t="n">
-        <v>42.8</v>
+        <v>33.67</v>
       </c>
       <c r="E136" s="4" t="n">
-        <v>36.76</v>
+        <v>40.18</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>28.85</v>
+        <v>55.26</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>GODREJAGRO</t>
+          <t>BECTORFOOD</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -4536,22 +4096,22 @@
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>620.2</v>
+        <v>197.94</v>
       </c>
       <c r="D137" s="4" t="n">
-        <v>42.74</v>
+        <v>33.62</v>
       </c>
       <c r="E137" s="4" t="n">
-        <v>57.37</v>
+        <v>42.64</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>52</v>
+        <v>42.96</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>EMBDL</t>
+          <t>PARAS</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -4560,22 +4120,22 @@
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>55.16</v>
+        <v>1177.2</v>
       </c>
       <c r="D138" s="4" t="n">
-        <v>42.7</v>
+        <v>33.56</v>
       </c>
       <c r="E138" s="4" t="n">
-        <v>42.95</v>
+        <v>49.82</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>40.19</v>
+        <v>59.11</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>PURVA</t>
+          <t>AWFIS</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -4584,22 +4144,22 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>203.9</v>
+        <v>221.4</v>
       </c>
       <c r="D139" s="4" t="n">
-        <v>42.66</v>
+        <v>33.55</v>
       </c>
       <c r="E139" s="4" t="n">
-        <v>42.98</v>
+        <v>32.67</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>43.28</v>
+        <v>27.43</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>FIEMIND</t>
+          <t>PRSMJOHNSN</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -4608,22 +4168,22 @@
         </is>
       </c>
       <c r="C140" s="4" t="n">
-        <v>1825.5</v>
+        <v>96.34</v>
       </c>
       <c r="D140" s="4" t="n">
-        <v>42.63</v>
+        <v>33.46</v>
       </c>
       <c r="E140" s="4" t="n">
-        <v>42.22</v>
+        <v>33.28</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>53.27</v>
+        <v>35.66</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>BECTORFOOD</t>
+          <t>RATNAMANI</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -4632,22 +4192,22 @@
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>209.1</v>
+        <v>2373</v>
       </c>
       <c r="D141" s="4" t="n">
-        <v>42.63</v>
+        <v>33.45</v>
       </c>
       <c r="E141" s="4" t="n">
-        <v>49.38</v>
+        <v>42.32</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>46.58</v>
+        <v>44.79</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>TMB</t>
+          <t>EMBDL</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -4656,22 +4216,22 @@
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>854.9</v>
+        <v>51.72</v>
       </c>
       <c r="D142" s="4" t="n">
-        <v>42.47</v>
+        <v>33.4</v>
       </c>
       <c r="E142" s="4" t="n">
-        <v>59.88</v>
+        <v>36.05</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>70.08</v>
+        <v>38.19</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>PRUDENT</t>
+          <t>TEXRAIL</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -4680,22 +4240,22 @@
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>3110.3</v>
+        <v>98.5</v>
       </c>
       <c r="D143" s="4" t="n">
-        <v>42.16</v>
+        <v>33.39</v>
       </c>
       <c r="E143" s="4" t="n">
-        <v>50.13</v>
+        <v>40.27</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>57.39</v>
+        <v>42.81</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>AGARWALEYE</t>
+          <t>QPOWER</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -4704,22 +4264,22 @@
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>477.15</v>
+        <v>1305.4</v>
       </c>
       <c r="D144" s="4" t="n">
-        <v>42.16</v>
+        <v>33.08</v>
       </c>
       <c r="E144" s="4" t="n">
-        <v>44.74</v>
+        <v>51.27</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>50.79</v>
+        <v>61.28</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>BALUFORGE</t>
+          <t>SUDEEPPHRM</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -4728,22 +4288,22 @@
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>480.7</v>
+        <v>966.2</v>
       </c>
       <c r="D145" s="4" t="n">
-        <v>42.13</v>
+        <v>33.06</v>
       </c>
       <c r="E145" s="4" t="n">
-        <v>46.81</v>
+        <v>50.46</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>48.07</v>
+        <v/>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>IFBIND</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -4752,22 +4312,22 @@
         </is>
       </c>
       <c r="C146" s="4" t="n">
-        <v>1191.1</v>
+        <v>94.58</v>
       </c>
       <c r="D146" s="4" t="n">
-        <v>42.06</v>
+        <v>32.83</v>
       </c>
       <c r="E146" s="4" t="n">
-        <v>44.21</v>
+        <v>36.45</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>46.98</v>
+        <v>37.72</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>SKIPPER</t>
+          <t>ALKYLAMINE</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -4776,22 +4336,22 @@
         </is>
       </c>
       <c r="C147" s="4" t="n">
-        <v>520.4</v>
+        <v>1634.8</v>
       </c>
       <c r="D147" s="4" t="n">
-        <v>41.93</v>
+        <v>32.82</v>
       </c>
       <c r="E147" s="4" t="n">
-        <v>51.61</v>
+        <v>41.38</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>59.03</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>AVANTIFEED</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -4800,16 +4360,16 @@
         </is>
       </c>
       <c r="C148" s="4" t="n">
-        <v>729.15</v>
+        <v>480.9</v>
       </c>
       <c r="D148" s="4" t="n">
-        <v>41.87</v>
+        <v>32.58</v>
       </c>
       <c r="E148" s="4" t="n">
-        <v>32.68</v>
+        <v>46.49</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>46.54</v>
+        <v>59.56</v>
       </c>
     </row>
     <row r="149">
@@ -4824,22 +4384,22 @@
         </is>
       </c>
       <c r="C149" s="4" t="n">
-        <v>7054.5</v>
+        <v>6460</v>
       </c>
       <c r="D149" s="4" t="n">
-        <v>41.78</v>
+        <v>32.56</v>
       </c>
       <c r="E149" s="4" t="n">
-        <v>55.22</v>
+        <v>49.31</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>66.91</v>
+        <v>62.86</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>AKUMS</t>
+          <t>SFL</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -4848,22 +4408,22 @@
         </is>
       </c>
       <c r="C150" s="4" t="n">
-        <v>749.8</v>
+        <v>584.3</v>
       </c>
       <c r="D150" s="4" t="n">
-        <v>41.77</v>
+        <v>32.55</v>
       </c>
       <c r="E150" s="4" t="n">
-        <v>58.59</v>
+        <v>39.03</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>58.82</v>
+        <v>41.66</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>RELAXO</t>
+          <t>IFBIND</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -4872,22 +4432,22 @@
         </is>
       </c>
       <c r="C151" s="4" t="n">
-        <v>294.35</v>
+        <v>1089.8</v>
       </c>
       <c r="D151" s="4" t="n">
-        <v>41.69</v>
+        <v>32.3</v>
       </c>
       <c r="E151" s="4" t="n">
-        <v>40.19</v>
+        <v>34.23</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>33.68</v>
+        <v>43.57</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>RATEGAIN</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -4896,22 +4456,22 @@
         </is>
       </c>
       <c r="C152" s="4" t="n">
-        <v>827.4</v>
+        <v>173.09</v>
       </c>
       <c r="D152" s="4" t="n">
-        <v>41.55</v>
+        <v>32.23</v>
       </c>
       <c r="E152" s="4" t="n">
-        <v>51.34</v>
+        <v>42.89</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>58.81</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>DBL</t>
+          <t>ASTRAMICRO</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -4920,22 +4480,22 @@
         </is>
       </c>
       <c r="C153" s="4" t="n">
-        <v>393.45</v>
+        <v>1485</v>
       </c>
       <c r="D153" s="4" t="n">
-        <v>41.45</v>
+        <v>32.22</v>
       </c>
       <c r="E153" s="4" t="n">
-        <v>44.2</v>
+        <v>46.47</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>45.69</v>
+        <v>62.09</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>MOIL</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -4944,22 +4504,22 @@
         </is>
       </c>
       <c r="C154" s="4" t="n">
-        <v>233.63</v>
+        <v>548.15</v>
       </c>
       <c r="D154" s="4" t="n">
-        <v>41.37</v>
+        <v>32.2</v>
       </c>
       <c r="E154" s="4" t="n">
-        <v>30.79</v>
+        <v>50</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>39.17</v>
+        <v>57.64</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>SHARDACROP</t>
+          <t>RTNPOWER</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -4968,22 +4528,22 @@
         </is>
       </c>
       <c r="C155" s="4" t="n">
-        <v>724.05</v>
+        <v>6.28</v>
       </c>
       <c r="D155" s="4" t="n">
-        <v>41.32</v>
+        <v>32.13</v>
       </c>
       <c r="E155" s="4" t="n">
-        <v>36.17</v>
+        <v>22.61</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>48.03</v>
+        <v>38.38</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>CENTURYPLY</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -4992,22 +4552,22 @@
         </is>
       </c>
       <c r="C156" s="4" t="n">
-        <v>588</v>
+        <v>650.8</v>
       </c>
       <c r="D156" s="4" t="n">
-        <v>41.26</v>
+        <v>32.02</v>
       </c>
       <c r="E156" s="4" t="n">
-        <v>57.65</v>
+        <v>28.91</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>61.75</v>
+        <v>42.19</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>KITEX</t>
+          <t>NETWORK18</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -5016,22 +4576,22 @@
         </is>
       </c>
       <c r="C157" s="4" t="n">
-        <v>116.19</v>
+        <v>23.5</v>
       </c>
       <c r="D157" s="4" t="n">
-        <v>41.17</v>
+        <v>31.89</v>
       </c>
       <c r="E157" s="4" t="n">
-        <v>36.47</v>
+        <v>30.77</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>42.79</v>
+        <v>31.84</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>GSFC</t>
+          <t>THYROCARE</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -5040,22 +4600,22 @@
         </is>
       </c>
       <c r="C158" s="4" t="n">
-        <v>146.6</v>
+        <v>472.1</v>
       </c>
       <c r="D158" s="4" t="n">
-        <v>41.12</v>
+        <v>31.87</v>
       </c>
       <c r="E158" s="4" t="n">
-        <v>41.47</v>
+        <v>41.26</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>42.69</v>
+        <v>54.96</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>WEBELSOLAR</t>
+          <t>CAMPUS</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -5064,22 +4624,22 @@
         </is>
       </c>
       <c r="C159" s="4" t="n">
-        <v>68.27</v>
+        <v>191.16</v>
       </c>
       <c r="D159" s="4" t="n">
-        <v>41.09</v>
+        <v>31.86</v>
       </c>
       <c r="E159" s="4" t="n">
-        <v>34.45</v>
+        <v>30.15</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>43.69</v>
+        <v>36.12</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>SWSOLAR</t>
+          <t>EMIL</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -5088,22 +4648,22 @@
         </is>
       </c>
       <c r="C160" s="4" t="n">
-        <v>165.47</v>
+        <v>159.62</v>
       </c>
       <c r="D160" s="4" t="n">
-        <v>41.01</v>
+        <v>31.71</v>
       </c>
       <c r="E160" s="4" t="n">
-        <v>35.11</v>
+        <v>48.69</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>38.04</v>
+        <v>52.47</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>ROUTE</t>
+          <t>TDPOWERSYS</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -5112,22 +4672,22 @@
         </is>
       </c>
       <c r="C161" s="4" t="n">
-        <v>437.95</v>
+        <v>639.55</v>
       </c>
       <c r="D161" s="4" t="n">
-        <v>40.86</v>
+        <v>31.5</v>
       </c>
       <c r="E161" s="4" t="n">
-        <v>37.24</v>
+        <v>48.49</v>
       </c>
       <c r="F161" s="4" t="n">
-        <v>28.69</v>
+        <v>64.64</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>SUNTECK</t>
+          <t>GHCL</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -5136,22 +4696,22 @@
         </is>
       </c>
       <c r="C162" s="4" t="n">
-        <v>274.1</v>
+        <v>387.85</v>
       </c>
       <c r="D162" s="4" t="n">
-        <v>40.8</v>
+        <v>31.45</v>
       </c>
       <c r="E162" s="4" t="n">
-        <v>37.19</v>
+        <v>27.88</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>38.56</v>
+        <v>37.24</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENT</t>
+          <t>ELECTCAST</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -5160,22 +4720,22 @@
         </is>
       </c>
       <c r="C163" s="4" t="n">
-        <v>70.42</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="D163" s="4" t="n">
-        <v>40.67</v>
+        <v>31.4</v>
       </c>
       <c r="E163" s="4" t="n">
-        <v>48.42</v>
+        <v>39.87</v>
       </c>
       <c r="F163" s="4" t="n">
-        <v>54.27</v>
+        <v>40.99</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>SAATVIKGL</t>
+          <t>JYOTHYLAB</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -5184,22 +4744,22 @@
         </is>
       </c>
       <c r="C164" s="4" t="n">
-        <v>395.7</v>
+        <v>175.36</v>
       </c>
       <c r="D164" s="4" t="n">
-        <v>40.23</v>
+        <v>31.04</v>
       </c>
       <c r="E164" s="4" t="n">
-        <v>42.15</v>
+        <v>31.78</v>
       </c>
       <c r="F164" s="4" t="n">
-        <v/>
+        <v>34.95</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>INDIGOPNTS</t>
+          <t>INDIASHLTR</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -5208,22 +4768,22 @@
         </is>
       </c>
       <c r="C165" s="4" t="n">
-        <v>1035.8</v>
+        <v>608.9</v>
       </c>
       <c r="D165" s="4" t="n">
-        <v>40.21</v>
+        <v>30.95</v>
       </c>
       <c r="E165" s="4" t="n">
-        <v>48.54</v>
+        <v>32.7</v>
       </c>
       <c r="F165" s="4" t="n">
-        <v>46.58</v>
+        <v>36.62</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>WAAREERTL</t>
+          <t>AURIONPRO</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -5232,22 +4792,22 @@
         </is>
       </c>
       <c r="C166" s="4" t="n">
-        <v>806.4</v>
+        <v>569.6</v>
       </c>
       <c r="D166" s="4" t="n">
-        <v>40.2</v>
+        <v>30.77</v>
       </c>
       <c r="E166" s="4" t="n">
-        <v>40.42</v>
+        <v>28.19</v>
       </c>
       <c r="F166" s="4" t="n">
-        <v>40.35</v>
+        <v>34.44</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>ZAGGLE</t>
+          <t>ENTERO</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -5256,22 +4816,22 @@
         </is>
       </c>
       <c r="C167" s="4" t="n">
-        <v>169.21</v>
+        <v>1498.9</v>
       </c>
       <c r="D167" s="4" t="n">
-        <v>40.15</v>
+        <v>30.74</v>
       </c>
       <c r="E167" s="4" t="n">
-        <v>30.93</v>
+        <v>51.01</v>
       </c>
       <c r="F167" s="4" t="n">
-        <v>36.49</v>
+        <v>57.32</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>ORIENTCEM</t>
+          <t>FINPIPE</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -5280,22 +4840,22 @@
         </is>
       </c>
       <c r="C168" s="4" t="n">
-        <v>114.87</v>
+        <v>142.4</v>
       </c>
       <c r="D168" s="4" t="n">
-        <v>40.11</v>
+        <v>30.66</v>
       </c>
       <c r="E168" s="4" t="n">
-        <v>28.88</v>
+        <v>31.42</v>
       </c>
       <c r="F168" s="4" t="n">
-        <v>32.77</v>
+        <v>38.49</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>AHLUCONT</t>
+          <t>KRBL</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -5304,22 +4864,22 @@
         </is>
       </c>
       <c r="C169" s="4" t="n">
-        <v>563.25</v>
+        <v>349.35</v>
       </c>
       <c r="D169" s="4" t="n">
-        <v>40</v>
+        <v>30.63</v>
       </c>
       <c r="E169" s="4" t="n">
-        <v>24.9</v>
+        <v>43.37</v>
       </c>
       <c r="F169" s="4" t="n">
-        <v>38.74</v>
+        <v>50.41</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>PRIVISCL</t>
+          <t>SKFINDUS</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -5328,22 +4888,22 @@
         </is>
       </c>
       <c r="C170" s="4" t="n">
-        <v>3365.1</v>
+        <v>2459.2</v>
       </c>
       <c r="D170" s="4" t="n">
-        <v>39.98</v>
+        <v>30.5</v>
       </c>
       <c r="E170" s="4" t="n">
-        <v>48.42</v>
+        <v>39.29</v>
       </c>
       <c r="F170" s="4" t="n">
-        <v>62.64</v>
+        <v/>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>JSFB</t>
+          <t>BANCOINDIA</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -5352,22 +4912,22 @@
         </is>
       </c>
       <c r="C171" s="4" t="n">
-        <v>480.35</v>
+        <v>558.4</v>
       </c>
       <c r="D171" s="4" t="n">
-        <v>39.97</v>
+        <v>30.44</v>
       </c>
       <c r="E171" s="4" t="n">
-        <v>49.08</v>
+        <v>39.81</v>
       </c>
       <c r="F171" s="4" t="n">
-        <v>52.29</v>
+        <v>52.15</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>REFEX</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -5376,22 +4936,22 @@
         </is>
       </c>
       <c r="C172" s="4" t="n">
-        <v>256.55</v>
+        <v>491.15</v>
       </c>
       <c r="D172" s="4" t="n">
-        <v>39.92</v>
+        <v>30.09</v>
       </c>
       <c r="E172" s="4" t="n">
-        <v>40.47</v>
+        <v>48.14</v>
       </c>
       <c r="F172" s="4" t="n">
-        <v>45.99</v>
+        <v>58.27</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>PRSMJOHNSN</t>
+          <t>SMARTWORKS</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -5400,22 +4960,22 @@
         </is>
       </c>
       <c r="C173" s="4" t="n">
-        <v>101.54</v>
+        <v>454.75</v>
       </c>
       <c r="D173" s="4" t="n">
-        <v>39.86</v>
+        <v>29.95</v>
       </c>
       <c r="E173" s="4" t="n">
-        <v>36.88</v>
+        <v>40.41</v>
       </c>
       <c r="F173" s="4" t="n">
-        <v>37.15</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>KIRLOSBROS</t>
+          <t>GREAVESCOT</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -5424,22 +4984,22 @@
         </is>
       </c>
       <c r="C174" s="4" t="n">
-        <v>1693.4</v>
+        <v>183.52</v>
       </c>
       <c r="D174" s="4" t="n">
-        <v>39.68</v>
+        <v>29.94</v>
       </c>
       <c r="E174" s="4" t="n">
-        <v>42.71</v>
+        <v>44.61</v>
       </c>
       <c r="F174" s="4" t="n">
-        <v>50.35</v>
+        <v>49.23</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>GRINDWELL</t>
+          <t>REFEX</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -5448,22 +5008,22 @@
         </is>
       </c>
       <c r="C175" s="4" t="n">
-        <v>1897.7</v>
+        <v>235.45</v>
       </c>
       <c r="D175" s="4" t="n">
-        <v>39.57</v>
+        <v>29.81</v>
       </c>
       <c r="E175" s="4" t="n">
-        <v>47.71</v>
+        <v>33.59</v>
       </c>
       <c r="F175" s="4" t="n">
-        <v>51.66</v>
+        <v>43.31</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>ASHOKA</t>
+          <t>SMLMAH</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -5472,22 +5032,22 @@
         </is>
       </c>
       <c r="C176" s="4" t="n">
-        <v>105.02</v>
+        <v>4843.5</v>
       </c>
       <c r="D176" s="4" t="n">
-        <v>39.54</v>
+        <v>29.66</v>
       </c>
       <c r="E176" s="4" t="n">
-        <v>33.22</v>
+        <v>47.65</v>
       </c>
       <c r="F176" s="4" t="n">
-        <v>39.44</v>
+        <v>57.78</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>INDIAGLYCO</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -5496,22 +5056,22 @@
         </is>
       </c>
       <c r="C177" s="4" t="n">
-        <v>331.95</v>
+        <v>513.1</v>
       </c>
       <c r="D177" s="4" t="n">
-        <v>39.4</v>
+        <v>29.35</v>
       </c>
       <c r="E177" s="4" t="n">
-        <v>29.17</v>
+        <v>44.46</v>
       </c>
       <c r="F177" s="4" t="n">
-        <v>37.04</v>
+        <v>49.29</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>BAJAJELEC</t>
+          <t>AKUMS</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -5520,22 +5080,22 @@
         </is>
       </c>
       <c r="C178" s="4" t="n">
-        <v>301.3</v>
+        <v>680.2</v>
       </c>
       <c r="D178" s="4" t="n">
-        <v>39.33</v>
+        <v>29.16</v>
       </c>
       <c r="E178" s="4" t="n">
-        <v>34.45</v>
+        <v>48.91</v>
       </c>
       <c r="F178" s="4" t="n">
-        <v>28.43</v>
+        <v>53.72</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>AVL</t>
+          <t>LLOYDSENT</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -5544,22 +5104,22 @@
         </is>
       </c>
       <c r="C179" s="4" t="n">
-        <v>568</v>
+        <v>63.74</v>
       </c>
       <c r="D179" s="4" t="n">
-        <v>39.21</v>
+        <v>29.13</v>
       </c>
       <c r="E179" s="4" t="n">
-        <v>47.8</v>
+        <v>41.16</v>
       </c>
       <c r="F179" s="4" t="n">
-        <v>56.1</v>
+        <v>49.93</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>CENTURYPLY</t>
+          <t>TIMETECHNO</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -5568,22 +5128,22 @@
         </is>
       </c>
       <c r="C180" s="4" t="n">
-        <v>671.6</v>
+        <v>164.22</v>
       </c>
       <c r="D180" s="4" t="n">
-        <v>39.08</v>
+        <v>29.12</v>
       </c>
       <c r="E180" s="4" t="n">
-        <v>34.44</v>
+        <v>34.3</v>
       </c>
       <c r="F180" s="4" t="n">
-        <v>44.78</v>
+        <v>45.74</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>WAKEFIT</t>
+          <t>SURYAROSNI</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -5592,22 +5152,22 @@
         </is>
       </c>
       <c r="C181" s="4" t="n">
-        <v>133.26</v>
+        <v>195.56</v>
       </c>
       <c r="D181" s="4" t="n">
-        <v>39.07</v>
+        <v>29.1</v>
       </c>
       <c r="E181" s="4" t="n">
-        <v>47.46</v>
+        <v>36.2</v>
       </c>
       <c r="F181" s="4" t="n">
-        <v/>
+        <v>42.34</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>IMFA</t>
+          <t>AVANTIFEED</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -5616,22 +5176,22 @@
         </is>
       </c>
       <c r="C182" s="4" t="n">
-        <v>1179.8</v>
+        <v>679.4</v>
       </c>
       <c r="D182" s="4" t="n">
-        <v>38.83</v>
+        <v>29.07</v>
       </c>
       <c r="E182" s="4" t="n">
-        <v>38.77</v>
+        <v>29.96</v>
       </c>
       <c r="F182" s="4" t="n">
-        <v>54.43</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>REDTAPE</t>
+          <t>STAR</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -5640,22 +5200,22 @@
         </is>
       </c>
       <c r="C183" s="4" t="n">
-        <v>112.82</v>
+        <v>998.4</v>
       </c>
       <c r="D183" s="4" t="n">
-        <v>38.81</v>
+        <v>29.01</v>
       </c>
       <c r="E183" s="4" t="n">
-        <v>41.27</v>
+        <v>46.37</v>
       </c>
       <c r="F183" s="4" t="n">
-        <v>33.8</v>
+        <v>54.65</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>HCC</t>
+          <t>WEBELSOLAR</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -5664,22 +5224,22 @@
         </is>
       </c>
       <c r="C184" s="4" t="n">
-        <v>19.43</v>
+        <v>61.17</v>
       </c>
       <c r="D184" s="4" t="n">
-        <v>38.77</v>
+        <v>28.72</v>
       </c>
       <c r="E184" s="4" t="n">
-        <v>43.08</v>
+        <v>30.09</v>
       </c>
       <c r="F184" s="4" t="n">
-        <v>44.21</v>
+        <v>41.82</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>SUDARSCHEM</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -5688,22 +5248,22 @@
         </is>
       </c>
       <c r="C185" s="4" t="n">
-        <v>1144.6</v>
+        <v>1412.7</v>
       </c>
       <c r="D185" s="4" t="n">
-        <v>38.48</v>
+        <v>28.67</v>
       </c>
       <c r="E185" s="4" t="n">
-        <v>54.5</v>
+        <v>48.14</v>
       </c>
       <c r="F185" s="4" t="n">
-        <v>55.8</v>
+        <v>62.75</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>APLLTD</t>
+          <t>BALUFORGE</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -5712,22 +5272,22 @@
         </is>
       </c>
       <c r="C186" s="4" t="n">
-        <v>789.45</v>
+        <v>422.05</v>
       </c>
       <c r="D186" s="4" t="n">
-        <v>38.36</v>
+        <v>28.58</v>
       </c>
       <c r="E186" s="4" t="n">
-        <v>47.88</v>
+        <v>39.51</v>
       </c>
       <c r="F186" s="4" t="n">
-        <v>47.26</v>
+        <v>45.43</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>SAMHI</t>
+          <t>AARTIDRUGS</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -5736,22 +5296,22 @@
         </is>
       </c>
       <c r="C187" s="4" t="n">
-        <v>144.99</v>
+        <v>380.05</v>
       </c>
       <c r="D187" s="4" t="n">
-        <v>38.32</v>
+        <v>28.54</v>
       </c>
       <c r="E187" s="4" t="n">
-        <v>40.87</v>
+        <v>38.85</v>
       </c>
       <c r="F187" s="4" t="n">
-        <v>42.82</v>
+        <v>44.62</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>KNRCON</t>
+          <t>ZAGGLE</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -5760,22 +5320,22 @@
         </is>
       </c>
       <c r="C188" s="4" t="n">
-        <v>111.48</v>
+        <v>156.81</v>
       </c>
       <c r="D188" s="4" t="n">
-        <v>38.31</v>
+        <v>28.22</v>
       </c>
       <c r="E188" s="4" t="n">
-        <v>36.97</v>
+        <v>25.81</v>
       </c>
       <c r="F188" s="4" t="n">
-        <v>32.31</v>
+        <v>34.86</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>RCF</t>
+          <t>GSFC</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -5784,22 +5344,22 @@
         </is>
       </c>
       <c r="C189" s="4" t="n">
-        <v>104.78</v>
+        <v>135.02</v>
       </c>
       <c r="D189" s="4" t="n">
-        <v>38.19</v>
+        <v>28.03</v>
       </c>
       <c r="E189" s="4" t="n">
-        <v>31.29</v>
+        <v>31.45</v>
       </c>
       <c r="F189" s="4" t="n">
-        <v>40.28</v>
+        <v>38.87</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>NFL</t>
+          <t>PRUDENT</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -5808,22 +5368,22 @@
         </is>
       </c>
       <c r="C190" s="4" t="n">
-        <v>62.88</v>
+        <v>2797.8</v>
       </c>
       <c r="D190" s="4" t="n">
-        <v>38.19</v>
+        <v>27.86</v>
       </c>
       <c r="E190" s="4" t="n">
-        <v>30.94</v>
+        <v>43.07</v>
       </c>
       <c r="F190" s="4" t="n">
-        <v>39.5</v>
+        <v>53.49</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>TVSSCS</t>
+          <t>KSB</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -5832,16 +5392,16 @@
         </is>
       </c>
       <c r="C191" s="4" t="n">
-        <v>122.17</v>
+        <v>681.75</v>
       </c>
       <c r="D191" s="4" t="n">
-        <v>37.91</v>
+        <v>27.83</v>
       </c>
       <c r="E191" s="4" t="n">
-        <v>46.83</v>
+        <v>30.51</v>
       </c>
       <c r="F191" s="4" t="n">
-        <v>44.74</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="192">
@@ -5856,22 +5416,22 @@
         </is>
       </c>
       <c r="C192" s="4" t="n">
-        <v>25.31</v>
+        <v>23.56</v>
       </c>
       <c r="D192" s="4" t="n">
-        <v>37.86</v>
+        <v>27.73</v>
       </c>
       <c r="E192" s="4" t="n">
-        <v>31.84</v>
+        <v>27.45</v>
       </c>
       <c r="F192" s="4" t="n">
-        <v>36.59</v>
+        <v>35.35</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>CMSINFO</t>
+          <t>KNRCON</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -5880,22 +5440,22 @@
         </is>
       </c>
       <c r="C193" s="4" t="n">
-        <v>218.01</v>
+        <v>103.21</v>
       </c>
       <c r="D193" s="4" t="n">
-        <v>37.64</v>
+        <v>27.7</v>
       </c>
       <c r="E193" s="4" t="n">
-        <v>29.89</v>
+        <v>30.12</v>
       </c>
       <c r="F193" s="4" t="n">
-        <v>30.59</v>
+        <v>30.28</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>WABAG</t>
+          <t>RUBICON</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -5904,22 +5464,22 @@
         </is>
       </c>
       <c r="C194" s="4" t="n">
-        <v>1884.8</v>
+        <v>1436.6</v>
       </c>
       <c r="D194" s="4" t="n">
-        <v>37.5</v>
+        <v>27.69</v>
       </c>
       <c r="E194" s="4" t="n">
-        <v>51.23</v>
+        <v>50.56</v>
       </c>
       <c r="F194" s="4" t="n">
-        <v>61.95</v>
+        <v/>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>JKLAKSHMI</t>
+          <t>MIDHANI</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -5928,16 +5488,16 @@
         </is>
       </c>
       <c r="C195" s="4" t="n">
-        <v>473.2</v>
+        <v>361.65</v>
       </c>
       <c r="D195" s="4" t="n">
-        <v>37.15</v>
+        <v>27.69</v>
       </c>
       <c r="E195" s="4" t="n">
-        <v>31.12</v>
+        <v>41.11</v>
       </c>
       <c r="F195" s="4" t="n">
-        <v>35</v>
+        <v>49.28</v>
       </c>
     </row>
     <row r="196">
@@ -5952,22 +5512,22 @@
         </is>
       </c>
       <c r="C196" s="4" t="n">
-        <v>156.35</v>
+        <v>142.72</v>
       </c>
       <c r="D196" s="4" t="n">
-        <v>37.04</v>
+        <v>27.65</v>
       </c>
       <c r="E196" s="4" t="n">
-        <v>35.84</v>
+        <v>31.27</v>
       </c>
       <c r="F196" s="4" t="n">
-        <v>19.6</v>
+        <v>17.77</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>SUBROS</t>
+          <t>ASHOKA</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -5976,22 +5536,22 @@
         </is>
       </c>
       <c r="C197" s="4" t="n">
-        <v>665.2</v>
+        <v>98.48999999999999</v>
       </c>
       <c r="D197" s="4" t="n">
-        <v>36.92</v>
+        <v>27.51</v>
       </c>
       <c r="E197" s="4" t="n">
-        <v>36.98</v>
+        <v>29.28</v>
       </c>
       <c r="F197" s="4" t="n">
-        <v>46.76</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>HEMIPROP</t>
+          <t>MOIL</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -6000,22 +5560,22 @@
         </is>
       </c>
       <c r="C198" s="4" t="n">
-        <v>111.78</v>
+        <v>215.52</v>
       </c>
       <c r="D198" s="4" t="n">
-        <v>36.82</v>
+        <v>27.37</v>
       </c>
       <c r="E198" s="4" t="n">
-        <v>32.13</v>
+        <v>25.77</v>
       </c>
       <c r="F198" s="4" t="n">
-        <v>41.16</v>
+        <v>37.05</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>BIRLACORPN</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -6024,22 +5584,22 @@
         </is>
       </c>
       <c r="C199" s="4" t="n">
-        <v>793.4</v>
+        <v>161.39</v>
       </c>
       <c r="D199" s="4" t="n">
-        <v>36.81</v>
+        <v>27.22</v>
       </c>
       <c r="E199" s="4" t="n">
-        <v>35.53</v>
+        <v>35.73</v>
       </c>
       <c r="F199" s="4" t="n">
-        <v>36.23</v>
+        <v>36.84</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>SAATVIKGL</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -6048,22 +5608,22 @@
         </is>
       </c>
       <c r="C200" s="4" t="n">
-        <v>1538.6</v>
+        <v>363.65</v>
       </c>
       <c r="D200" s="4" t="n">
-        <v>36.67</v>
+        <v>27.09</v>
       </c>
       <c r="E200" s="4" t="n">
-        <v>54.49</v>
+        <v>33.59</v>
       </c>
       <c r="F200" s="4" t="n">
-        <v>69.44</v>
+        <v/>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>DBREALTY</t>
+          <t>TVSSCS</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -6072,22 +5632,22 @@
         </is>
       </c>
       <c r="C201" s="4" t="n">
-        <v>87.12</v>
+        <v>113.07</v>
       </c>
       <c r="D201" s="4" t="n">
-        <v>36.33</v>
+        <v>27.08</v>
       </c>
       <c r="E201" s="4" t="n">
-        <v>35.9</v>
+        <v>37.78</v>
       </c>
       <c r="F201" s="4" t="n">
-        <v>39.79</v>
+        <v>40.63</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>SUDEEPPHRM</t>
+          <t>HCC</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -6096,22 +5656,22 @@
         </is>
       </c>
       <c r="C202" s="4" t="n">
-        <v>1008.1</v>
+        <v>17.38</v>
       </c>
       <c r="D202" s="4" t="n">
-        <v>36.24</v>
+        <v>27.05</v>
       </c>
       <c r="E202" s="4" t="n">
-        <v>52.76</v>
+        <v>37.88</v>
       </c>
       <c r="F202" s="4" t="n">
-        <v/>
+        <v>42.41</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>INDIASHLTR</t>
+          <t>IMFA</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -6120,22 +5680,22 @@
         </is>
       </c>
       <c r="C203" s="4" t="n">
-        <v>624.75</v>
+        <v>1095.1</v>
       </c>
       <c r="D203" s="4" t="n">
-        <v>36.17</v>
+        <v>27.04</v>
       </c>
       <c r="E203" s="4" t="n">
-        <v>33.58</v>
+        <v>33.92</v>
       </c>
       <c r="F203" s="4" t="n">
-        <v>37.18</v>
+        <v>51.82</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>MSTCLTD</t>
+          <t>RELIGARE</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -6144,22 +5704,22 @@
         </is>
       </c>
       <c r="C204" s="4" t="n">
-        <v>649.4</v>
+        <v>208.01</v>
       </c>
       <c r="D204" s="4" t="n">
-        <v>36.16</v>
+        <v>27.03</v>
       </c>
       <c r="E204" s="4" t="n">
-        <v>53.5</v>
+        <v>37.65</v>
       </c>
       <c r="F204" s="4" t="n">
-        <v>55.49</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>ENTERO</t>
+          <t>STYL</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -6168,22 +5728,22 @@
         </is>
       </c>
       <c r="C205" s="4" t="n">
-        <v>1581.1</v>
+        <v>310.9</v>
       </c>
       <c r="D205" s="4" t="n">
-        <v>35.89</v>
+        <v>26.99</v>
       </c>
       <c r="E205" s="4" t="n">
-        <v>57.4</v>
+        <v>43.27</v>
       </c>
       <c r="F205" s="4" t="n">
-        <v>62.05</v>
+        <v/>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>STAR</t>
+          <t>POWERMECH</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -6192,22 +5752,22 @@
         </is>
       </c>
       <c r="C206" s="4" t="n">
-        <v>1045.2</v>
+        <v>2124.7</v>
       </c>
       <c r="D206" s="4" t="n">
-        <v>35.89</v>
+        <v>26.94</v>
       </c>
       <c r="E206" s="4" t="n">
-        <v>49.07</v>
+        <v>37.53</v>
       </c>
       <c r="F206" s="4" t="n">
-        <v>56.28</v>
+        <v>45.29</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>RELIGARE</t>
+          <t>MSTCLTD</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -6216,22 +5776,22 @@
         </is>
       </c>
       <c r="C207" s="4" t="n">
-        <v>220.21</v>
+        <v>597.7</v>
       </c>
       <c r="D207" s="4" t="n">
-        <v>35.54</v>
+        <v>26.81</v>
       </c>
       <c r="E207" s="4" t="n">
-        <v>41.36</v>
+        <v>44.96</v>
       </c>
       <c r="F207" s="4" t="n">
-        <v>47.22</v>
+        <v>51.55</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>SWSOLAR</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -6240,22 +5800,22 @@
         </is>
       </c>
       <c r="C208" s="4" t="n">
-        <v>1987.3</v>
+        <v>142.13</v>
       </c>
       <c r="D208" s="4" t="n">
-        <v>35.17</v>
+        <v>26.78</v>
       </c>
       <c r="E208" s="4" t="n">
-        <v>54.85</v>
+        <v>28.29</v>
       </c>
       <c r="F208" s="4" t="n">
-        <v>68.59999999999999</v>
+        <v>36.19</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>SANDUMA</t>
+          <t>INOXGREEN</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -6264,22 +5824,22 @@
         </is>
       </c>
       <c r="C209" s="4" t="n">
-        <v>175.21</v>
+        <v>116.11</v>
       </c>
       <c r="D209" s="4" t="n">
-        <v>34.96</v>
+        <v>26.75</v>
       </c>
       <c r="E209" s="4" t="n">
-        <v>36.64</v>
+        <v>27.11</v>
       </c>
       <c r="F209" s="4" t="n">
-        <v>48.9</v>
+        <v>42.35</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>STARCEMENT</t>
+          <t>JSFB</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -6288,22 +5848,22 @@
         </is>
       </c>
       <c r="C210" s="4" t="n">
-        <v>171.54</v>
+        <v>403.1</v>
       </c>
       <c r="D210" s="4" t="n">
-        <v>34.9</v>
+        <v>26.7</v>
       </c>
       <c r="E210" s="4" t="n">
-        <v>29.73</v>
+        <v>34.14</v>
       </c>
       <c r="F210" s="4" t="n">
-        <v>40.27</v>
+        <v>43.09</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>VIPIND</t>
+          <t>SAFARI</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -6312,22 +5872,22 @@
         </is>
       </c>
       <c r="C211" s="4" t="n">
-        <v>270.85</v>
+        <v>1265.1</v>
       </c>
       <c r="D211" s="4" t="n">
-        <v>34.83</v>
+        <v>26.68</v>
       </c>
       <c r="E211" s="4" t="n">
-        <v>33.56</v>
+        <v>28.45</v>
       </c>
       <c r="F211" s="4" t="n">
-        <v>32.98</v>
+        <v>35.11</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>TSFINV</t>
+          <t>BAJAJELEC</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -6336,22 +5896,22 @@
         </is>
       </c>
       <c r="C212" s="4" t="n">
-        <v>396.05</v>
+        <v>278.8</v>
       </c>
       <c r="D212" s="4" t="n">
-        <v>34.64</v>
+        <v>26.65</v>
       </c>
       <c r="E212" s="4" t="n">
-        <v>45.81</v>
+        <v>29.37</v>
       </c>
       <c r="F212" s="4" t="n">
-        <v>52.44</v>
+        <v>27.25</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>AARTIDRUGS</t>
+          <t>HGINFRA</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -6360,22 +5920,22 @@
         </is>
       </c>
       <c r="C213" s="4" t="n">
-        <v>396.35</v>
+        <v>390.3</v>
       </c>
       <c r="D213" s="4" t="n">
-        <v>34.56</v>
+        <v>26.63</v>
       </c>
       <c r="E213" s="4" t="n">
-        <v>45.84</v>
+        <v>24.17</v>
       </c>
       <c r="F213" s="4" t="n">
-        <v>46.9</v>
+        <v>30.63</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>METROPOLIS</t>
+          <t>RENUKA</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -6384,22 +5944,22 @@
         </is>
       </c>
       <c r="C214" s="4" t="n">
-        <v>523</v>
+        <v>18.7</v>
       </c>
       <c r="D214" s="4" t="n">
-        <v>34.09</v>
+        <v>26.6</v>
       </c>
       <c r="E214" s="4" t="n">
-        <v>46.84</v>
+        <v>33.04</v>
       </c>
       <c r="F214" s="4" t="n">
-        <v>54.78</v>
+        <v>34.64</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>VGUARD</t>
+          <t>STARCEMENT</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -6408,22 +5968,22 @@
         </is>
       </c>
       <c r="C215" s="4" t="n">
-        <v>288</v>
+        <v>162.25</v>
       </c>
       <c r="D215" s="4" t="n">
-        <v>34.03</v>
+        <v>26.17</v>
       </c>
       <c r="E215" s="4" t="n">
-        <v>36.37</v>
+        <v>25.15</v>
       </c>
       <c r="F215" s="4" t="n">
-        <v>41.61</v>
+        <v>37.72</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>OSWALPUMPS</t>
+          <t>REDTAPE</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -6432,22 +5992,22 @@
         </is>
       </c>
       <c r="C216" s="4" t="n">
-        <v>257.85</v>
+        <v>104.06</v>
       </c>
       <c r="D216" s="4" t="n">
-        <v>33.82</v>
+        <v>25.98</v>
       </c>
       <c r="E216" s="4" t="n">
-        <v>26.66</v>
+        <v>35.07</v>
       </c>
       <c r="F216" s="4" t="n">
-        <v>25.1</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>V2RETAIL</t>
+          <t>KIRLPNU</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -6456,22 +6016,22 @@
         </is>
       </c>
       <c r="C217" s="4" t="n">
-        <v>166.25</v>
+        <v>603.25</v>
       </c>
       <c r="D217" s="4" t="n">
-        <v>33.71</v>
+        <v>25.94</v>
       </c>
       <c r="E217" s="4" t="n">
-        <v>35.47</v>
+        <v>34.17</v>
       </c>
       <c r="F217" s="4" t="n">
-        <v>48.48</v>
+        <v>47.96</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>VIYASH</t>
+          <t>WABAG</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -6480,22 +6040,22 @@
         </is>
       </c>
       <c r="C218" s="4" t="n">
-        <v>226</v>
+        <v>1710.4</v>
       </c>
       <c r="D218" s="4" t="n">
-        <v>33.63</v>
+        <v>25.94</v>
       </c>
       <c r="E218" s="4" t="n">
-        <v>43.02</v>
+        <v>44.51</v>
       </c>
       <c r="F218" s="4" t="n">
-        <v>54.61</v>
+        <v>56.59</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>IONEXCHANG</t>
+          <t>CMSINFO</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -6504,22 +6064,22 @@
         </is>
       </c>
       <c r="C219" s="4" t="n">
-        <v>377.5</v>
+        <v>204.01</v>
       </c>
       <c r="D219" s="4" t="n">
-        <v>33.5</v>
+        <v>25.65</v>
       </c>
       <c r="E219" s="4" t="n">
-        <v>45.7</v>
+        <v>26.09</v>
       </c>
       <c r="F219" s="4" t="n">
-        <v>45.52</v>
+        <v>29.12</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>PRICOLLTD</t>
+          <t>VGUARD</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -6528,22 +6088,22 @@
         </is>
       </c>
       <c r="C220" s="4" t="n">
-        <v>666.9</v>
+        <v>272.55</v>
       </c>
       <c r="D220" s="4" t="n">
-        <v>33.41</v>
+        <v>25.65</v>
       </c>
       <c r="E220" s="4" t="n">
-        <v>49.01</v>
+        <v>30.46</v>
       </c>
       <c r="F220" s="4" t="n">
-        <v>58.43</v>
+        <v>39.05</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>CERA</t>
+          <t>PRICOLLTD</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -6552,22 +6112,22 @@
         </is>
       </c>
       <c r="C221" s="4" t="n">
-        <v>5046</v>
+        <v>630.05</v>
       </c>
       <c r="D221" s="4" t="n">
-        <v>32.93</v>
+        <v>25.58</v>
       </c>
       <c r="E221" s="4" t="n">
-        <v>38.27</v>
+        <v>43.18</v>
       </c>
       <c r="F221" s="4" t="n">
-        <v>43.22</v>
+        <v>55.49</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>SKFINDUS</t>
+          <t>DBREALTY</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -6576,22 +6136,22 @@
         </is>
       </c>
       <c r="C222" s="4" t="n">
-        <v>2514.6</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="D222" s="4" t="n">
-        <v>32.92</v>
+        <v>25.45</v>
       </c>
       <c r="E222" s="4" t="n">
-        <v>44.59</v>
+        <v>31.7</v>
       </c>
       <c r="F222" s="4" t="n">
-        <v/>
+        <v>38.26</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>HGINFRA</t>
+          <t>EUREKAFORB</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -6600,22 +6160,22 @@
         </is>
       </c>
       <c r="C223" s="4" t="n">
-        <v>407.95</v>
+        <v>316.8</v>
       </c>
       <c r="D223" s="4" t="n">
-        <v>32.77</v>
+        <v>25.05</v>
       </c>
       <c r="E223" s="4" t="n">
-        <v>26.75</v>
+        <v>25.01</v>
       </c>
       <c r="F223" s="4" t="n">
-        <v>31.43</v>
+        <v>30.63</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>PRAJIND</t>
+          <t>ASHAPURMIN</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -6624,22 +6184,22 @@
         </is>
       </c>
       <c r="C224" s="4" t="n">
-        <v>287.15</v>
+        <v>432.7</v>
       </c>
       <c r="D224" s="4" t="n">
-        <v>32.01</v>
+        <v>24.8</v>
       </c>
       <c r="E224" s="4" t="n">
-        <v>35.6</v>
+        <v>28.27</v>
       </c>
       <c r="F224" s="4" t="n">
-        <v>39.84</v>
+        <v>45.63</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>ASHAPURMIN</t>
+          <t>SHARDACROP</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -6648,22 +6208,22 @@
         </is>
       </c>
       <c r="C225" s="4" t="n">
-        <v>465</v>
+        <v>659.6</v>
       </c>
       <c r="D225" s="4" t="n">
-        <v>31.99</v>
+        <v>24.76</v>
       </c>
       <c r="E225" s="4" t="n">
-        <v>31.97</v>
+        <v>29.51</v>
       </c>
       <c r="F225" s="4" t="n">
-        <v>47.43</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>SUBROS</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -6672,22 +6232,22 @@
         </is>
       </c>
       <c r="C226" s="4" t="n">
-        <v>1231.2</v>
+        <v>614.95</v>
       </c>
       <c r="D226" s="4" t="n">
-        <v>31.93</v>
+        <v>24.57</v>
       </c>
       <c r="E226" s="4" t="n">
-        <v>42.93</v>
+        <v>29.39</v>
       </c>
       <c r="F226" s="4" t="n">
-        <v>54.08</v>
+        <v>43.43</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>KIRLPNU</t>
+          <t>MAHSEAMLES</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -6696,22 +6256,22 @@
         </is>
       </c>
       <c r="C227" s="4" t="n">
-        <v>637.15</v>
+        <v>539.3</v>
       </c>
       <c r="D227" s="4" t="n">
-        <v>31.83</v>
+        <v>24.54</v>
       </c>
       <c r="E227" s="4" t="n">
-        <v>39.05</v>
+        <v>35.83</v>
       </c>
       <c r="F227" s="4" t="n">
-        <v>50.56</v>
+        <v>45.41</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>EUREKAFORB</t>
+          <t>HCG</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -6720,22 +6280,22 @@
         </is>
       </c>
       <c r="C228" s="4" t="n">
-        <v>342.1</v>
+        <v>550.65</v>
       </c>
       <c r="D228" s="4" t="n">
-        <v>31.76</v>
+        <v>23.5</v>
       </c>
       <c r="E228" s="4" t="n">
-        <v>29.7</v>
+        <v>32.33</v>
       </c>
       <c r="F228" s="4" t="n">
-        <v>33.01</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>CCAVENUE</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -6744,22 +6304,22 @@
         </is>
       </c>
       <c r="C229" s="4" t="n">
-        <v>138.3</v>
+        <v>1018.5</v>
       </c>
       <c r="D229" s="4" t="n">
-        <v>31.69</v>
+        <v>23.33</v>
       </c>
       <c r="E229" s="4" t="n">
-        <v>39.96</v>
+        <v>38.1</v>
       </c>
       <c r="F229" s="4" t="n">
-        <v>41.31</v>
+        <v>50.78</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>VIKRAMSOLR</t>
+          <t>PARKHOSPS</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -6768,13 +6328,13 @@
         </is>
       </c>
       <c r="C230" s="4" t="n">
-        <v>144</v>
+        <v>215.1</v>
       </c>
       <c r="D230" s="4" t="n">
-        <v>31.57</v>
+        <v>22.52</v>
       </c>
       <c r="E230" s="4" t="n">
-        <v>30.32</v>
+        <v>34.29</v>
       </c>
       <c r="F230" s="4" t="n">
         <v/>
@@ -6783,7 +6343,7 @@
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>MAHSEAMLES</t>
+          <t>NFL</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -6792,22 +6352,22 @@
         </is>
       </c>
       <c r="C231" s="4" t="n">
-        <v>585.4</v>
+        <v>57.12</v>
       </c>
       <c r="D231" s="4" t="n">
-        <v>31.33</v>
+        <v>22.25</v>
       </c>
       <c r="E231" s="4" t="n">
-        <v>42.53</v>
+        <v>24</v>
       </c>
       <c r="F231" s="4" t="n">
-        <v>48.52</v>
+        <v>37.11</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>SAFARI</t>
+          <t>SUDARSCHEM</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -6816,22 +6376,22 @@
         </is>
       </c>
       <c r="C232" s="4" t="n">
-        <v>1312.3</v>
+        <v>1019.6</v>
       </c>
       <c r="D232" s="4" t="n">
-        <v>31.18</v>
+        <v>22.23</v>
       </c>
       <c r="E232" s="4" t="n">
-        <v>32.38</v>
+        <v>44.79</v>
       </c>
       <c r="F232" s="4" t="n">
-        <v>36.82</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>RTNPOWER</t>
+          <t>HEMIPROP</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -6840,22 +6400,22 @@
         </is>
       </c>
       <c r="C233" s="4" t="n">
-        <v>6.54</v>
+        <v>101.85</v>
       </c>
       <c r="D233" s="4" t="n">
-        <v>31.02</v>
+        <v>22.15</v>
       </c>
       <c r="E233" s="4" t="n">
-        <v>24.5</v>
+        <v>26.46</v>
       </c>
       <c r="F233" s="4" t="n">
-        <v>39.08</v>
+        <v>38.61</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>BORORENEW</t>
+          <t>VIYASH</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -6864,22 +6424,22 @@
         </is>
       </c>
       <c r="C234" s="4" t="n">
-        <v>427.55</v>
+        <v>204.18</v>
       </c>
       <c r="D234" s="4" t="n">
-        <v>30.88</v>
+        <v>22.08</v>
       </c>
       <c r="E234" s="4" t="n">
-        <v>34.3</v>
+        <v>36.79</v>
       </c>
       <c r="F234" s="4" t="n">
-        <v>43.99</v>
+        <v>50.63</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>SMARTWORKS</t>
+          <t>RAYMONDLSL</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -6888,22 +6448,22 @@
         </is>
       </c>
       <c r="C235" s="4" t="n">
-        <v>469.05</v>
+        <v>530.85</v>
       </c>
       <c r="D235" s="4" t="n">
-        <v>30.55</v>
+        <v>22.02</v>
       </c>
       <c r="E235" s="4" t="n">
-        <v>45.39</v>
+        <v>26.45</v>
       </c>
       <c r="F235" s="4" t="n">
-        <v>47.79</v>
+        <v>20.65</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>STYL</t>
+          <t>BORORENEW</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -6912,16 +6472,16 @@
         </is>
       </c>
       <c r="C236" s="4" t="n">
-        <v>328.95</v>
+        <v>396.4</v>
       </c>
       <c r="D236" s="4" t="n">
-        <v>30.45</v>
+        <v>22</v>
       </c>
       <c r="E236" s="4" t="n">
-        <v>47.2</v>
+        <v>29.26</v>
       </c>
       <c r="F236" s="4" t="n">
-        <v/>
+        <v>41.41</v>
       </c>
     </row>
     <row r="237">
@@ -6936,22 +6496,22 @@
         </is>
       </c>
       <c r="C237" s="4" t="n">
-        <v>419.1</v>
+        <v>386.6</v>
       </c>
       <c r="D237" s="4" t="n">
-        <v>29.92</v>
+        <v>21.85</v>
       </c>
       <c r="E237" s="4" t="n">
-        <v>31.15</v>
+        <v>27.07</v>
       </c>
       <c r="F237" s="4" t="n">
-        <v>40.5</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>THYROCARE</t>
+          <t>ANUP</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -6960,22 +6520,22 @@
         </is>
       </c>
       <c r="C238" s="4" t="n">
-        <v>487.55</v>
+        <v>1383</v>
       </c>
       <c r="D238" s="4" t="n">
-        <v>29.82</v>
+        <v>21.7</v>
       </c>
       <c r="E238" s="4" t="n">
-        <v>44.45</v>
+        <v>27.63</v>
       </c>
       <c r="F238" s="4" t="n">
-        <v>57.01</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>HCG</t>
+          <t>RCF</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -6984,22 +6544,22 @@
         </is>
       </c>
       <c r="C239" s="4" t="n">
-        <v>590.6</v>
+        <v>94.39</v>
       </c>
       <c r="D239" s="4" t="n">
-        <v>29.79</v>
+        <v>21.64</v>
       </c>
       <c r="E239" s="4" t="n">
-        <v>37.37</v>
+        <v>24.51</v>
       </c>
       <c r="F239" s="4" t="n">
-        <v>51.26</v>
+        <v>37.43</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>RAYMONDLSL</t>
+          <t>WAAREERTL</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -7008,22 +6568,22 @@
         </is>
       </c>
       <c r="C240" s="4" t="n">
-        <v>574.2</v>
+        <v>678.25</v>
       </c>
       <c r="D240" s="4" t="n">
-        <v>29.6</v>
+        <v>21.59</v>
       </c>
       <c r="E240" s="4" t="n">
-        <v>30.62</v>
+        <v>26.95</v>
       </c>
       <c r="F240" s="4" t="n">
-        <v>21.88</v>
+        <v>32.67</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>PARKHOSPS</t>
+          <t>ADVENZYMES</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -7032,22 +6592,22 @@
         </is>
       </c>
       <c r="C241" s="4" t="n">
-        <v>235.7</v>
+        <v>248.35</v>
       </c>
       <c r="D241" s="4" t="n">
-        <v>29.45</v>
+        <v>21.44</v>
       </c>
       <c r="E241" s="4" t="n">
-        <v>39.96</v>
+        <v>28.42</v>
       </c>
       <c r="F241" s="4" t="n">
-        <v/>
+        <v>40.59</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>ANUP</t>
+          <t>MEDPLUS</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -7056,22 +6616,22 @@
         </is>
       </c>
       <c r="C242" s="4" t="n">
-        <v>1483</v>
+        <v>594.7</v>
       </c>
       <c r="D242" s="4" t="n">
-        <v>28.3</v>
+        <v>21.07</v>
       </c>
       <c r="E242" s="4" t="n">
-        <v>31.94</v>
+        <v>22.83</v>
       </c>
       <c r="F242" s="4" t="n">
-        <v>41.48</v>
+        <v>35.06</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>RUBICON</t>
+          <t>IONEXCHANG</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -7080,22 +6640,22 @@
         </is>
       </c>
       <c r="C243" s="4" t="n">
-        <v>1477.1</v>
+        <v>337.75</v>
       </c>
       <c r="D243" s="4" t="n">
-        <v>27.73</v>
+        <v>20.67</v>
       </c>
       <c r="E243" s="4" t="n">
-        <v>56.08</v>
+        <v>38.96</v>
       </c>
       <c r="F243" s="4" t="n">
-        <v/>
+        <v>42.39</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>MEDPLUS</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -7104,22 +6664,22 @@
         </is>
       </c>
       <c r="C244" s="4" t="n">
-        <v>612.8</v>
+        <v>133.37</v>
       </c>
       <c r="D244" s="4" t="n">
-        <v>26.82</v>
+        <v>20.29</v>
       </c>
       <c r="E244" s="4" t="n">
-        <v>24.45</v>
+        <v>38.72</v>
       </c>
       <c r="F244" s="4" t="n">
-        <v>36.01</v>
+        <v>47.34</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>INOXGREEN</t>
+          <t>SANDUMA</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
@@ -7128,22 +6688,22 @@
         </is>
       </c>
       <c r="C245" s="4" t="n">
-        <v>118.69</v>
+        <v>156.58</v>
       </c>
       <c r="D245" s="4" t="n">
-        <v>26.75</v>
+        <v>19.7</v>
       </c>
       <c r="E245" s="4" t="n">
-        <v>28.74</v>
+        <v>29.95</v>
       </c>
       <c r="F245" s="4" t="n">
-        <v>43.29</v>
+        <v>45.33</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>CAMPUS</t>
+          <t>CERA</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -7152,22 +6712,22 @@
         </is>
       </c>
       <c r="C246" s="4" t="n">
-        <v>197.01</v>
+        <v>4530</v>
       </c>
       <c r="D246" s="4" t="n">
-        <v>26.59</v>
+        <v>19.69</v>
       </c>
       <c r="E246" s="4" t="n">
-        <v>35.56</v>
+        <v>29.95</v>
       </c>
       <c r="F246" s="4" t="n">
-        <v>38.22</v>
+        <v>39.47</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>ADVENZYMES</t>
+          <t>OSWALPUMPS</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -7176,22 +6736,22 @@
         </is>
       </c>
       <c r="C247" s="4" t="n">
-        <v>262.9</v>
+        <v>230.75</v>
       </c>
       <c r="D247" s="4" t="n">
-        <v>26.16</v>
+        <v>19.62</v>
       </c>
       <c r="E247" s="4" t="n">
-        <v>33.21</v>
+        <v>23.09</v>
       </c>
       <c r="F247" s="4" t="n">
-        <v>42.79</v>
+        <v>23.88</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>JSLL</t>
+          <t>VIKRAMSOLR</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -7200,22 +6760,22 @@
         </is>
       </c>
       <c r="C248" s="4" t="n">
-        <v>388.7</v>
+        <v>127.98</v>
       </c>
       <c r="D248" s="4" t="n">
-        <v>25.62</v>
+        <v>19.44</v>
       </c>
       <c r="E248" s="4" t="n">
-        <v>28.64</v>
+        <v>25.95</v>
       </c>
       <c r="F248" s="4" t="n">
-        <v>37.88</v>
+        <v/>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>JLHL</t>
+          <t>CCAVENUE</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
@@ -7224,22 +6784,22 @@
         </is>
       </c>
       <c r="C249" s="4" t="n">
-        <v>239.65</v>
+        <v>116.94</v>
       </c>
       <c r="D249" s="4" t="n">
-        <v>25.32</v>
+        <v>18.41</v>
       </c>
       <c r="E249" s="4" t="n">
-        <v>34.16</v>
+        <v>31.8</v>
       </c>
       <c r="F249" s="4" t="n">
-        <v>44.68</v>
+        <v>36.92</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>IXIGO</t>
+          <t>JSLL</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -7248,22 +6808,22 @@
         </is>
       </c>
       <c r="C250" s="4" t="n">
-        <v>138.12</v>
+        <v>341.55</v>
       </c>
       <c r="D250" s="4" t="n">
-        <v>24.97</v>
+        <v>18.21</v>
       </c>
       <c r="E250" s="4" t="n">
-        <v>37.45</v>
+        <v>25.44</v>
       </c>
       <c r="F250" s="4" t="n">
-        <v>38.69</v>
+        <v>36.87</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>GHCL</t>
+          <t>PRAJIND</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
@@ -7272,16 +6832,16 @@
         </is>
       </c>
       <c r="C251" s="4" t="n">
-        <v>385.35</v>
+        <v>251.2</v>
       </c>
       <c r="D251" s="4" t="n">
-        <v>24.55</v>
+        <v>18.19</v>
       </c>
       <c r="E251" s="4" t="n">
-        <v>31.24</v>
+        <v>28.37</v>
       </c>
       <c r="F251" s="4" t="n">
-        <v>38.38</v>
+        <v>37.49</v>
       </c>
     </row>
     <row r="252">
@@ -7296,16 +6856,16 @@
         </is>
       </c>
       <c r="C252" s="4" t="n">
-        <v>3573.3</v>
+        <v>3262.8</v>
       </c>
       <c r="D252" s="4" t="n">
-        <v>21.7</v>
+        <v>12.44</v>
       </c>
       <c r="E252" s="4" t="n">
-        <v>25.45</v>
+        <v>20.48</v>
       </c>
       <c r="F252" s="4" t="n">
-        <v>32.95</v>
+        <v>29.59</v>
       </c>
     </row>
   </sheetData>
